--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="1447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="1448">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,94 +44,94 @@
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447938919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93978834152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82799768447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78057098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943164825439</t>
+    <t xml:space="preserve">4.02447891235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93978905677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82799816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78057193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943188667297</t>
   </si>
   <si>
     <t xml:space="preserve">3.75685834884644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74330759048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80089807510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040886878967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571877479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66539263725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56376481056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65184187889099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72636985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70265650749207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65861749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6924934387207</t>
+    <t xml:space="preserve">3.74330735206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8008975982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040839195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571805953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66539287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56376457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65184235572815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72637009620667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70265603065491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65861773490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69249367713928</t>
   </si>
   <si>
     <t xml:space="preserve">3.74669528007507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59764075279236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59086561203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58408951759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49601173400879</t>
+    <t xml:space="preserve">3.59764051437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59086585044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58409023284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49601197242737</t>
   </si>
   <si>
     <t xml:space="preserve">3.4621365070343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51633810997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38760900497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40793442726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50956249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55698943138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56715250015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61119151115417</t>
+    <t xml:space="preserve">3.51633787155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38760924339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40793466567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50956201553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55698871612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56715202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61119079589844</t>
   </si>
   <si>
     <t xml:space="preserve">3.57731509208679</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">3.54682660102844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52650022506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50278759002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5603768825531</t>
+    <t xml:space="preserve">3.5265007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50278687477112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56037664413452</t>
   </si>
   <si>
     <t xml:space="preserve">3.58070254325867</t>
@@ -155,196 +155,196 @@
     <t xml:space="preserve">3.60102820396423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54343891143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57053971290588</t>
+    <t xml:space="preserve">3.54343843460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57053923606873</t>
   </si>
   <si>
     <t xml:space="preserve">3.64506769180298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78734636306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84154868125916</t>
+    <t xml:space="preserve">3.78734707832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84154915809631</t>
   </si>
   <si>
     <t xml:space="preserve">3.86526131629944</t>
   </si>
   <si>
+    <t xml:space="preserve">3.85171175003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92962598800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93640160560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607594490051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90252542495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89575052261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285108566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90930104255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97027802467346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87881183624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85848641395569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94317650794983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89913845062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94656348228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95672750473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9635021686554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91268801689148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97366452217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91946387290955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87203741073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8870484828949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87291383743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85877919197083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83757615089417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86231184005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87644696235657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89411544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9011824131012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89058136940002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94358706474304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95418810844421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96125507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01426029205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02486181259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08846759796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05666446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03899669647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305868148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00719404220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97538924217224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97185611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80224013328552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78103756904602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75630211830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74923419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90471601486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92238402366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065450668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03546237945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75983572006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80930662155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83050918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86937975883484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82344174385071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80577373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84111070632935</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.85171127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92962646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9364013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607642173767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9025251865387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89574933052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285084724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90930032730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9702775478363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87881231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85848617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94317698478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89913725852966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94656348228455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95672702789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96350240707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91268873214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97366499900818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91946339607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87203669548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88704800605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87291312217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85877871513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83757591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86231231689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87644720077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89411520957947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90118193626404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058113098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94358682632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95418810844421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96125626564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01426076889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02486133575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08846759796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05666446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03899574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305844306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00719356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97539019584656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97185659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80223989486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78103709220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75630164146423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7492344379425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90471601486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92238473892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03546237945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75983572006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80930662155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83050966262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86937952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82344198226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80577349662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84110999107361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85171103477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8163743019104</t>
+    <t xml:space="preserve">3.81637454032898</t>
   </si>
   <si>
     <t xml:space="preserve">3.8658459186554</t>
@@ -356,130 +356,130 @@
     <t xml:space="preserve">3.93651962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90825057029724</t>
+    <t xml:space="preserve">3.9082498550415</t>
   </si>
   <si>
     <t xml:space="preserve">3.91531705856323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97892379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00012540817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02132797241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95772123336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84464406967163</t>
+    <t xml:space="preserve">3.97892355918884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00012588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02132749557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95772099494934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84464335441589</t>
   </si>
   <si>
     <t xml:space="preserve">3.81284117698669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77043676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690340042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76336908340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74570107460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7244987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77396965026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78810524940491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81990838050842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72803235054016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73863363265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7315661907196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73509979248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65382504463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63969039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66089224815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.618488073349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61142063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62555623054504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61495494842529</t>
+    <t xml:space="preserve">3.77043652534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690292358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76336884498596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7457013130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72449827194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77397012710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78810501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81990814208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72803258895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73863339424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73156595230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73510003089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65382432937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63968992233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66089177131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61848855018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61142134666443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62555599212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61495447158813</t>
   </si>
   <si>
     <t xml:space="preserve">3.64675760269165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7421669960022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91885113716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98599076271057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99659252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87997984886169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88351392745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7951717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82697463035583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79163861274719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84817719459534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7103636264801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8552451133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03192901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04253005981445</t>
+    <t xml:space="preserve">3.74216675758362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91885137557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98599028587341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9965922832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87998080253601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88351440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79517197608948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82697558403015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79163813591003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8481776714325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71036338806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85524439811707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03192853927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04252910614014</t>
   </si>
   <si>
     <t xml:space="preserve">4.08493423461914</t>
@@ -494,43 +494,43 @@
     <t xml:space="preserve">4.04959726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09200096130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10966920852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07786655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07433319091797</t>
+    <t xml:space="preserve">4.09200143814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07786703109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07433271408081</t>
   </si>
   <si>
     <t xml:space="preserve">4.04606342315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06373119354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10613584518433</t>
+    <t xml:space="preserve">4.0637321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10613632202148</t>
   </si>
   <si>
     <t xml:space="preserve">4.10260248184204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13440608978271</t>
+    <t xml:space="preserve">4.13440561294556</t>
   </si>
   <si>
     <t xml:space="preserve">4.12733793258667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16974258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18387699127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1591420173645</t>
+    <t xml:space="preserve">4.16974210739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18387651443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15914154052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.24041557312012</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.21568012237549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27575302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34642601013184</t>
+    <t xml:space="preserve">4.27575254440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34642696380615</t>
   </si>
   <si>
     <t xml:space="preserve">4.36762809753418</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">4.35349369049072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31108951568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38176345825195</t>
+    <t xml:space="preserve">4.31108903884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30402231216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38176298141479</t>
   </si>
   <si>
     <t xml:space="preserve">4.50897550582886</t>
@@ -569,52 +569,52 @@
     <t xml:space="preserve">4.91181516647339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94715213775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19450950622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22277927398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22984600067139</t>
+    <t xml:space="preserve">4.94715166091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19450902938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22277879714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2298469543457</t>
   </si>
   <si>
     <t xml:space="preserve">5.2263126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09203290939331</t>
+    <t xml:space="preserve">5.09203243255615</t>
   </si>
   <si>
     <t xml:space="preserve">5.07436418533325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08496570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11676836013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10616731643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15210580825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15917301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17330741882324</t>
+    <t xml:space="preserve">5.08496618270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1167688369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10616779327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1521053314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15917205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1733078956604</t>
   </si>
   <si>
     <t xml:space="preserve">5.1909761428833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14503860473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13090372085571</t>
+    <t xml:space="preserve">5.14503765106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13090324401855</t>
   </si>
   <si>
     <t xml:space="preserve">5.2475152015686</t>
@@ -623,34 +623,34 @@
     <t xml:space="preserve">5.26871681213379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59734869003296</t>
+    <t xml:space="preserve">5.59734916687012</t>
   </si>
   <si>
     <t xml:space="preserve">5.51254081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35705852508545</t>
+    <t xml:space="preserve">5.35705900192261</t>
   </si>
   <si>
     <t xml:space="preserve">5.47720336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37119388580322</t>
+    <t xml:space="preserve">5.37119340896606</t>
   </si>
   <si>
     <t xml:space="preserve">5.44186687469482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53020811080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61199760437012</t>
+    <t xml:space="preserve">5.53020858764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61199712753296</t>
   </si>
   <si>
     <t xml:space="preserve">5.65216112136841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68867444992065</t>
+    <t xml:space="preserve">5.68867349624634</t>
   </si>
   <si>
     <t xml:space="preserve">5.6229510307312</t>
@@ -659,43 +659,43 @@
     <t xml:space="preserve">5.619300365448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59739208221436</t>
+    <t xml:space="preserve">5.59739255905151</t>
   </si>
   <si>
     <t xml:space="preserve">5.42213201522827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41847991943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55357694625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56087923049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49880790710449</t>
+    <t xml:space="preserve">5.41848087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5535774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56087970733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49880838394165</t>
   </si>
   <si>
     <t xml:space="preserve">5.46229553222656</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55722808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45499324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36736249923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37466478347778</t>
+    <t xml:space="preserve">5.55722856521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45499277114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36736297607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3746657371521</t>
   </si>
   <si>
     <t xml:space="preserve">5.43308591842651</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40387487411499</t>
+    <t xml:space="preserve">5.40387582778931</t>
   </si>
   <si>
     <t xml:space="preserve">5.47690010070801</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">5.48055171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49515771865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54627466201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60104417800903</t>
+    <t xml:space="preserve">5.49515676498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54627418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60104370117188</t>
   </si>
   <si>
     <t xml:space="preserve">5.41117715835571</t>
@@ -725,37 +725,37 @@
     <t xml:space="preserve">5.54992628097534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45134162902832</t>
+    <t xml:space="preserve">5.45134210586548</t>
   </si>
   <si>
     <t xml:space="preserve">5.61564874649048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50611114501953</t>
+    <t xml:space="preserve">5.50611019134521</t>
   </si>
   <si>
     <t xml:space="preserve">5.34545469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37101364135742</t>
+    <t xml:space="preserve">5.37101459503174</t>
   </si>
   <si>
     <t xml:space="preserve">5.31259346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28703498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15558862686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12637901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27242946624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31989526748657</t>
+    <t xml:space="preserve">5.28703451156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15558910369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12637853622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2724289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31989574432373</t>
   </si>
   <si>
     <t xml:space="preserve">5.14098358154297</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">5.40752696990967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38926982879639</t>
+    <t xml:space="preserve">5.38927030563354</t>
   </si>
   <si>
     <t xml:space="preserve">5.37831592559814</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">5.24321937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46959733963013</t>
+    <t xml:space="preserve">5.46959781646729</t>
   </si>
   <si>
     <t xml:space="preserve">5.41482877731323</t>
@@ -782,34 +782,34 @@
     <t xml:space="preserve">5.42578268051147</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44038820266724</t>
+    <t xml:space="preserve">5.44038724899292</t>
   </si>
   <si>
     <t xml:space="preserve">5.48420333862305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35275745391846</t>
+    <t xml:space="preserve">5.3527569770813</t>
   </si>
   <si>
     <t xml:space="preserve">5.48785400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50245904922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57183313369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57913589477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56453132629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52071523666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53897142410278</t>
+    <t xml:space="preserve">5.50245952606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57183361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57913541793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56453084945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52071571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53897190093994</t>
   </si>
   <si>
     <t xml:space="preserve">5.65581226348877</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">5.58643865585327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57548522949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50976228713989</t>
+    <t xml:space="preserve">5.57548475265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50976133346558</t>
   </si>
   <si>
     <t xml:space="preserve">5.53166961669922</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">5.60469484329224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59008979797363</t>
+    <t xml:space="preserve">5.59009027481079</t>
   </si>
   <si>
     <t xml:space="preserve">5.75804805755615</t>
@@ -839,31 +839,31 @@
     <t xml:space="preserve">5.79456090927124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92965698242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94426298141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99903202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93696022033691</t>
+    <t xml:space="preserve">5.92965745925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94426345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99903154373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93696069717407</t>
   </si>
   <si>
     <t xml:space="preserve">5.98807716369629</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83107376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88584232330322</t>
+    <t xml:space="preserve">5.83107328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88584327697754</t>
   </si>
   <si>
     <t xml:space="preserve">5.83472442626953</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9588680267334</t>
+    <t xml:space="preserve">5.95886754989624</t>
   </si>
   <si>
     <t xml:space="preserve">5.76900196075439</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">5.783607006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85298156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7032790184021</t>
+    <t xml:space="preserve">5.85298109054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70327854156494</t>
   </si>
   <si>
     <t xml:space="preserve">5.82742214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86393451690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75439739227295</t>
+    <t xml:space="preserve">5.8639349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75439691543579</t>
   </si>
   <si>
     <t xml:space="preserve">5.72883796691895</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">5.66676616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88949394226074</t>
+    <t xml:space="preserve">5.88949346542358</t>
   </si>
   <si>
     <t xml:space="preserve">5.78725814819336</t>
@@ -923,16 +923,16 @@
     <t xml:space="preserve">5.6083459854126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63025331497192</t>
+    <t xml:space="preserve">5.63025379180908</t>
   </si>
   <si>
     <t xml:space="preserve">5.53532075881958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76169872283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62660217285156</t>
+    <t xml:space="preserve">5.76169967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6266016960144</t>
   </si>
   <si>
     <t xml:space="preserve">5.68137168884277</t>
@@ -944,34 +944,34 @@
     <t xml:space="preserve">5.76535081863403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80916547775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80551385879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82377099990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87853956222534</t>
+    <t xml:space="preserve">5.80916595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80551481246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82377004623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87854051589966</t>
   </si>
   <si>
     <t xml:space="preserve">5.82011938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90409851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92235517501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95156526565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02459001541138</t>
+    <t xml:space="preserve">5.90409898757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92235469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95156478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02459049224854</t>
   </si>
   <si>
     <t xml:space="preserve">6.06110429763794</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">6.09031391143799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2290620803833</t>
+    <t xml:space="preserve">6.22906160354614</t>
   </si>
   <si>
     <t xml:space="preserve">6.18524694442749</t>
@@ -992,52 +992,52 @@
     <t xml:space="preserve">6.03189325332642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03919553756714</t>
+    <t xml:space="preserve">6.03919506072998</t>
   </si>
   <si>
     <t xml:space="preserve">6.04649782180786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25096988677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20715379714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14143085479736</t>
+    <t xml:space="preserve">6.25096940994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20715427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14143037796021</t>
   </si>
   <si>
     <t xml:space="preserve">6.12682580947876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79821252822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72518682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96617078781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00268363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89314460754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84933042526245</t>
+    <t xml:space="preserve">5.79821157455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72518634796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96617031097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00268268585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8931450843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84932994842529</t>
   </si>
   <si>
     <t xml:space="preserve">5.973473072052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99537992477417</t>
+    <t xml:space="preserve">5.99538087844849</t>
   </si>
   <si>
     <t xml:space="preserve">6.11952352523804</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15603637695312</t>
+    <t xml:space="preserve">6.15603590011597</t>
   </si>
   <si>
     <t xml:space="preserve">6.10491800308228</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">5.90044784545898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14873313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09761524200439</t>
+    <t xml:space="preserve">6.14873361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09761571884155</t>
   </si>
   <si>
     <t xml:space="preserve">6.05380058288574</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">6.17794418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17064142227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24366569519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28017950057983</t>
+    <t xml:space="preserve">6.17064094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24366664886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28017997741699</t>
   </si>
   <si>
     <t xml:space="preserve">6.38636541366577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31810283660889</t>
+    <t xml:space="preserve">6.31810331344604</t>
   </si>
   <si>
     <t xml:space="preserve">6.23467063903809</t>
@@ -1091,55 +1091,55 @@
     <t xml:space="preserve">6.15882253646851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2725944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26500988006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21191549301147</t>
+    <t xml:space="preserve">6.27259397506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26500940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21191596984863</t>
   </si>
   <si>
     <t xml:space="preserve">6.1815767288208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15123796463013</t>
+    <t xml:space="preserve">6.15123844146729</t>
   </si>
   <si>
     <t xml:space="preserve">6.02988195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05263662338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25742435455322</t>
+    <t xml:space="preserve">6.05263614654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25742483139038</t>
   </si>
   <si>
     <t xml:space="preserve">6.22708559036255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.249840259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29534912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37119579315186</t>
+    <t xml:space="preserve">6.24983978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29534959793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3711953163147</t>
   </si>
   <si>
     <t xml:space="preserve">6.1891622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16640758514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20433187484741</t>
+    <t xml:space="preserve">6.1664080619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20433139801025</t>
   </si>
   <si>
     <t xml:space="preserve">6.0147123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04505109786987</t>
+    <t xml:space="preserve">6.04505157470703</t>
   </si>
   <si>
     <t xml:space="preserve">6.00712776184082</t>
@@ -1148,10 +1148,10 @@
     <t xml:space="preserve">5.98437309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12089920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13606882095337</t>
+    <t xml:space="preserve">6.12089872360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13606834411621</t>
   </si>
   <si>
     <t xml:space="preserve">6.11331510543823</t>
@@ -1163,67 +1163,67 @@
     <t xml:space="preserve">5.96161890029907</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08297491073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14365339279175</t>
+    <t xml:space="preserve">6.0829758644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14365386962891</t>
   </si>
   <si>
     <t xml:space="preserve">6.1057300567627</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06022071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99954319000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95403432846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93886518478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06780624389648</t>
+    <t xml:space="preserve">6.06022119522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9995436668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95403480529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93886566162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06780576705933</t>
   </si>
   <si>
     <t xml:space="preserve">5.91611051559448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94645023345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818717956543</t>
+    <t xml:space="preserve">5.94644927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818670272827</t>
   </si>
   <si>
     <t xml:space="preserve">6.03746700286865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02229690551758</t>
+    <t xml:space="preserve">6.02229785919189</t>
   </si>
   <si>
     <t xml:space="preserve">5.99195861816406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86301755905151</t>
+    <t xml:space="preserve">5.8630166053772</t>
   </si>
   <si>
     <t xml:space="preserve">6.07539081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24225473403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738313674927</t>
+    <t xml:space="preserve">6.24225425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738265991211</t>
   </si>
   <si>
     <t xml:space="preserve">6.63666248321533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46221303939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57598447799683</t>
+    <t xml:space="preserve">6.46221351623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57598495483398</t>
   </si>
   <si>
     <t xml:space="preserve">6.56081485748291</t>
@@ -1232,58 +1232,58 @@
     <t xml:space="preserve">6.6063232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55323076248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65183210372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53806066513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48496675491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61390829086304</t>
+    <t xml:space="preserve">6.55323123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65183258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53806018829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48496723175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6139087677002</t>
   </si>
   <si>
     <t xml:space="preserve">6.66700172424316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59873867034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34085655212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39395093917847</t>
+    <t xml:space="preserve">6.59873914718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34085750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39395046234131</t>
   </si>
   <si>
     <t xml:space="preserve">6.4167046546936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42428922653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53047609329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59115409851074</t>
+    <t xml:space="preserve">6.42428970336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5911545753479</t>
   </si>
   <si>
     <t xml:space="preserve">6.54564571380615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56839942932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44704389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34844207763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21950101852417</t>
+    <t xml:space="preserve">6.56840038299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44704437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34844160079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21950006484985</t>
   </si>
   <si>
     <t xml:space="preserve">6.40912008285522</t>
@@ -1292,31 +1292,31 @@
     <t xml:space="preserve">6.32568788528442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28776359558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68975639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6745867729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74284934997559</t>
+    <t xml:space="preserve">6.2877631187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6897554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67458629608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74284982681274</t>
   </si>
   <si>
     <t xml:space="preserve">6.75043344497681</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62149238586426</t>
+    <t xml:space="preserve">6.62149333953857</t>
   </si>
   <si>
     <t xml:space="preserve">6.37878084182739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36361169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46979856491089</t>
+    <t xml:space="preserve">6.36361122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46979808807373</t>
   </si>
   <si>
     <t xml:space="preserve">6.51530694961548</t>
@@ -1328,25 +1328,25 @@
     <t xml:space="preserve">6.3560266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19674682617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40153455734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72009468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75801801681519</t>
+    <t xml:space="preserve">6.19674634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40153503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72009515762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75801849365234</t>
   </si>
   <si>
     <t xml:space="preserve">6.80352735519409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78835868835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73526430130005</t>
+    <t xml:space="preserve">6.78835773468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73526382446289</t>
   </si>
   <si>
     <t xml:space="preserve">6.84903573989868</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">6.84145164489746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81869697570801</t>
+    <t xml:space="preserve">6.81869649887085</t>
   </si>
   <si>
     <t xml:space="preserve">6.90213012695312</t>
@@ -1370,25 +1370,25 @@
     <t xml:space="preserve">6.9931468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89454507827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94005250930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05382347106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10691785812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15242671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11450242996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01590061187744</t>
+    <t xml:space="preserve">6.89454412460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94005298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05382442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10691738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15242624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.114501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0159010887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.08416366577148</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">7.04623985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09174871444702</t>
+    <t xml:space="preserve">7.09174823760986</t>
   </si>
   <si>
     <t xml:space="preserve">7.39513826370239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35721445083618</t>
+    <t xml:space="preserve">7.35721349716187</t>
   </si>
   <si>
     <t xml:space="preserve">7.34204530715942</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">7.12208700180054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13725614547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12967157363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2510290145874</t>
+    <t xml:space="preserve">7.13725662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12967109680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25102806091309</t>
   </si>
   <si>
     <t xml:space="preserve">7.22827291488647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20551824569702</t>
+    <t xml:space="preserve">7.20551919937134</t>
   </si>
   <si>
     <t xml:space="preserve">7.1979341506958</t>
@@ -1439,67 +1439,67 @@
     <t xml:space="preserve">7.43306255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49374055862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5392484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54683351516724</t>
+    <t xml:space="preserve">7.49373960494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53924894332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54683399200439</t>
   </si>
   <si>
     <t xml:space="preserve">7.75162172317505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79713106155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64543437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69094371795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57717084884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45581436157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5164942741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59992694854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50890922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56200313568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58475828170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5544171333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47857093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47098588943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44823122024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70611333847046</t>
+    <t xml:space="preserve">7.79713010787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64543581008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69094467163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57717180252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45581579208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51649522781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59992742538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50890970230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56200361251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58475732803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55441808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47856950759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4709849357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44823026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70611381530762</t>
   </si>
   <si>
     <t xml:space="preserve">7.90331745147705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88814640045166</t>
+    <t xml:space="preserve">7.88814687728882</t>
   </si>
   <si>
     <t xml:space="preserve">8.25221633911133</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">8.61628437042236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49492740631104</t>
+    <t xml:space="preserve">8.49492835998535</t>
   </si>
   <si>
     <t xml:space="preserve">8.17636680603027</t>
@@ -1520,40 +1520,40 @@
     <t xml:space="preserve">8.1187686920166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08742237091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93068885803223</t>
+    <t xml:space="preserve">8.08742141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9306902885437</t>
   </si>
   <si>
     <t xml:space="preserve">8.04040336608887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96203565597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2598295211792</t>
+    <t xml:space="preserve">7.96203708648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25982856750488</t>
   </si>
   <si>
     <t xml:space="preserve">8.02472972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86799621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73477411270142</t>
+    <t xml:space="preserve">7.86799764633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7347731590271</t>
   </si>
   <si>
     <t xml:space="preserve">7.83664989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8209753036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91501665115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97770929336548</t>
+    <t xml:space="preserve">7.82097578048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91501712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97771024703979</t>
   </si>
   <si>
     <t xml:space="preserve">8.07174968719482</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">8.05607604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85232305526733</t>
+    <t xml:space="preserve">7.85232353210449</t>
   </si>
   <si>
     <t xml:space="preserve">8.40088844299316</t>
@@ -1571,31 +1571,31 @@
     <t xml:space="preserve">8.46358108520508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62031555175781</t>
+    <t xml:space="preserve">8.6203145980835</t>
   </si>
   <si>
     <t xml:space="preserve">8.30684947967529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16578960418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33819484710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21280860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27550220489502</t>
+    <t xml:space="preserve">8.1657886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33819580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21280765533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27550315856934</t>
   </si>
   <si>
     <t xml:space="preserve">8.36954212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15011596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18146228790283</t>
+    <t xml:space="preserve">8.15011501312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18146133422852</t>
   </si>
   <si>
     <t xml:space="preserve">8.13444232940674</t>
@@ -1604,58 +1604,58 @@
     <t xml:space="preserve">8.22848224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43223571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99338340759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19713687896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7582836151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89934206008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82881164550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88366889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313991546631</t>
+    <t xml:space="preserve">8.43223476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99338388442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19713592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75828313827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89934349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82881259918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88367033004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81314039230347</t>
   </si>
   <si>
     <t xml:space="preserve">7.67991781234741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79746580123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41656017303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80530214309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68775367736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74261045455933</t>
+    <t xml:space="preserve">7.79746675491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4165620803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80530309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68775320053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74260950088501</t>
   </si>
   <si>
     <t xml:space="preserve">8.00905609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94636249542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75044727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71910047531128</t>
+    <t xml:space="preserve">7.94636297225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75044584274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7190990447998</t>
   </si>
   <si>
     <t xml:space="preserve">8.10309600830078</t>
@@ -1664,19 +1664,19 @@
     <t xml:space="preserve">8.82406806945801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.372633934021</t>
+    <t xml:space="preserve">9.37263298034668</t>
   </si>
   <si>
     <t xml:space="preserve">9.60773277282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.482346534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79581260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93687343597412</t>
+    <t xml:space="preserve">9.48234558105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79581165313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9368724822998</t>
   </si>
   <si>
     <t xml:space="preserve">9.87417984008789</t>
@@ -1688,19 +1688,19 @@
     <t xml:space="preserve">10.1562976837158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5011100769043</t>
+    <t xml:space="preserve">10.5011110305786</t>
   </si>
   <si>
     <t xml:space="preserve">10.3757238388062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5481300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2189922332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1719703674316</t>
+    <t xml:space="preserve">10.5481309890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2189912796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.171971321106</t>
   </si>
   <si>
     <t xml:space="preserve">9.95254516601562</t>
@@ -1712,22 +1712,22 @@
     <t xml:space="preserve">9.88985252380371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92119979858398</t>
+    <t xml:space="preserve">9.92119884490967</t>
   </si>
   <si>
     <t xml:space="preserve">9.73311996459961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76446533203125</t>
+    <t xml:space="preserve">9.76446723937988</t>
   </si>
   <si>
     <t xml:space="preserve">9.57638549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96821880340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0309114456177</t>
+    <t xml:space="preserve">9.96821784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0309104919434</t>
   </si>
   <si>
     <t xml:space="preserve">10.4854373931885</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">10.0152387619019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1249513626099</t>
+    <t xml:space="preserve">10.1249523162842</t>
   </si>
   <si>
     <t xml:space="preserve">10.3600511550903</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.2973585128784</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3130311965942</t>
+    <t xml:space="preserve">10.3130302429199</t>
   </si>
   <si>
     <t xml:space="preserve">10.4384174346924</t>
@@ -1757,19 +1757,19 @@
     <t xml:space="preserve">10.6264972686768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6578435897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6108236312866</t>
+    <t xml:space="preserve">10.657844543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6108245849609</t>
   </si>
   <si>
     <t xml:space="preserve">10.5951509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5794792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6421709060669</t>
+    <t xml:space="preserve">10.5794773101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6421699523926</t>
   </si>
   <si>
     <t xml:space="preserve">10.7518835067749</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">10.9556360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1280431747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0183296203613</t>
+    <t xml:space="preserve">11.1280422210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0183305740356</t>
   </si>
   <si>
     <t xml:space="preserve">11.2377557754517</t>
@@ -1793,25 +1793,25 @@
     <t xml:space="preserve">11.1593894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0966968536377</t>
+    <t xml:space="preserve">11.0966958999634</t>
   </si>
   <si>
     <t xml:space="preserve">11.1750631332397</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1123704910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0810232162476</t>
+    <t xml:space="preserve">11.1123685836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0810222625732</t>
   </si>
   <si>
     <t xml:space="preserve">10.9713096618652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7989025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622577667236</t>
+    <t xml:space="preserve">10.798903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622587203979</t>
   </si>
   <si>
     <t xml:space="preserve">10.0936050415039</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">9.6860990524292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29426574707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54503917694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98079967498779</t>
+    <t xml:space="preserve">9.294264793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5450382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98080062866211</t>
   </si>
   <si>
     <t xml:space="preserve">8.54194736480713</t>
@@ -1835,16 +1835,16 @@
     <t xml:space="preserve">7.31943130493164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50751066207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53885698318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49183797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66733551025391</t>
+    <t xml:space="preserve">7.5075101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53885746002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49183702468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66733455657959</t>
   </si>
   <si>
     <t xml:space="preserve">8.44790744781494</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">8.38521480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52627563476562</t>
+    <t xml:space="preserve">8.52627468109131</t>
   </si>
   <si>
     <t xml:space="preserve">9.01214694976807</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">9.38830661773682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88676166534424</t>
+    <t xml:space="preserve">8.88676071166992</t>
   </si>
   <si>
     <t xml:space="preserve">8.87108707427979</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">9.12186050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9181079864502</t>
+    <t xml:space="preserve">8.91810703277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.15320777893066</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.21590042114258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96512699127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30298042297363</t>
+    <t xml:space="preserve">8.96512889862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30298137664795</t>
   </si>
   <si>
     <t xml:space="preserve">9.12407779693604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01022911071777</t>
+    <t xml:space="preserve">9.01023006439209</t>
   </si>
   <si>
     <t xml:space="preserve">8.68494987487793</t>
@@ -1916,19 +1916,19 @@
     <t xml:space="preserve">8.50604724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70121383666992</t>
+    <t xml:space="preserve">8.70121479034424</t>
   </si>
   <si>
     <t xml:space="preserve">9.18913269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92890930175781</t>
+    <t xml:space="preserve">8.92891025543213</t>
   </si>
   <si>
     <t xml:space="preserve">8.76626968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71747970581055</t>
+    <t xml:space="preserve">8.71747875213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.97770214080811</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">9.33550834655762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48188400268555</t>
+    <t xml:space="preserve">9.48188495635986</t>
   </si>
   <si>
     <t xml:space="preserve">9.61199474334717</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">10.2625541687012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0673866271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3113460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1812343597412</t>
+    <t xml:space="preserve">10.0673875808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3113470077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812353134155</t>
   </si>
   <si>
     <t xml:space="preserve">10.2137622833252</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">10.2300252914429</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95353889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88848400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69331455230713</t>
+    <t xml:space="preserve">9.953537940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88848304748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69331550598145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1324424743652</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">10.1974983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3276100158691</t>
+    <t xml:space="preserve">10.3276090621948</t>
   </si>
   <si>
     <t xml:space="preserve">10.2462902069092</t>
@@ -2015,22 +2015,22 @@
     <t xml:space="preserve">10.9781684875488</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1245441436768</t>
+    <t xml:space="preserve">11.1245422363281</t>
   </si>
   <si>
     <t xml:space="preserve">11.1408081054688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.287181854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3847665786743</t>
+    <t xml:space="preserve">11.2871828079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3847675323486</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474061965942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4335594177246</t>
+    <t xml:space="preserve">11.4335584640503</t>
   </si>
   <si>
     <t xml:space="preserve">11.4498224258423</t>
@@ -2042,49 +2042,49 @@
     <t xml:space="preserve">11.4823503494263</t>
   </si>
   <si>
-    <t xml:space="preserve">11.335973739624</t>
+    <t xml:space="preserve">11.3359746932983</t>
   </si>
   <si>
     <t xml:space="preserve">11.2058629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2221269607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8643188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.539041519165</t>
+    <t xml:space="preserve">11.2221279144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8643198013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5390405654907</t>
   </si>
   <si>
     <t xml:space="preserve">10.5227766036987</t>
   </si>
   <si>
-    <t xml:space="preserve">10.701681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8155279159546</t>
+    <t xml:space="preserve">10.7016801834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8155288696289</t>
   </si>
   <si>
     <t xml:space="preserve">10.604097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7342071533203</t>
+    <t xml:space="preserve">10.7342081069946</t>
   </si>
   <si>
     <t xml:space="preserve">10.6203603744507</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7179441452026</t>
+    <t xml:space="preserve">10.717945098877</t>
   </si>
   <si>
     <t xml:space="preserve">10.5065135955811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5878343582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4577207565308</t>
+    <t xml:space="preserve">10.587833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4577217102051</t>
   </si>
   <si>
     <t xml:space="preserve">10.3764019012451</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">10.9944324493408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6691522598267</t>
+    <t xml:space="preserve">10.669153213501</t>
   </si>
   <si>
     <t xml:space="preserve">10.7829999923706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9619045257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9456405639648</t>
+    <t xml:space="preserve">10.9619035720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9456396102905</t>
   </si>
   <si>
     <t xml:space="preserve">11.2709188461304</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1895999908447</t>
+    <t xml:space="preserve">11.1895990371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.5799341201782</t>
@@ -2138,28 +2138,28 @@
     <t xml:space="preserve">10.0836505889893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4414577484131</t>
+    <t xml:space="preserve">10.4414567947388</t>
   </si>
   <si>
     <t xml:space="preserve">10.7504730224609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1570720672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1082792282104</t>
+    <t xml:space="preserve">11.1570711135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1082782745361</t>
   </si>
   <si>
     <t xml:space="preserve">11.0269594192505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9131116867065</t>
+    <t xml:space="preserve">10.9131126403809</t>
   </si>
   <si>
     <t xml:space="preserve">11.2546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3522386550903</t>
+    <t xml:space="preserve">11.3522396087646</t>
   </si>
   <si>
     <t xml:space="preserve">11.4010305404663</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">11.3197107315063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1733341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0106964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5311422348022</t>
+    <t xml:space="preserve">11.1733350753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0106954574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5311412811279</t>
   </si>
   <si>
     <t xml:space="preserve">11.7751016616821</t>
@@ -2183,37 +2183,37 @@
     <t xml:space="preserve">11.7100458145142</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7425727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.019061088562</t>
+    <t xml:space="preserve">11.7425737380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0190601348877</t>
   </si>
   <si>
     <t xml:space="preserve">12.3118124008179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5882987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1979646682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8726854324341</t>
+    <t xml:space="preserve">12.5882978439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1979627609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8726844787598</t>
   </si>
   <si>
     <t xml:space="preserve">12.00279712677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8076305389404</t>
+    <t xml:space="preserve">11.8076295852661</t>
   </si>
   <si>
     <t xml:space="preserve">11.8564214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5961980819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9540042877197</t>
+    <t xml:space="preserve">11.5961990356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.954005241394</t>
   </si>
   <si>
     <t xml:space="preserve">11.9865322113037</t>
@@ -2222,10 +2222,10 @@
     <t xml:space="preserve">12.100380897522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1817007064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.116644859314</t>
+    <t xml:space="preserve">12.1816997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1166439056396</t>
   </si>
   <si>
     <t xml:space="preserve">12.2792835235596</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">12.4093952178955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5069799423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4581861495972</t>
+    <t xml:space="preserve">12.5069789886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4581880569458</t>
   </si>
   <si>
     <t xml:space="preserve">12.4907150268555</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">13.0111618041992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9786348342896</t>
+    <t xml:space="preserve">12.9786338806152</t>
   </si>
   <si>
     <t xml:space="preserve">12.8647861480713</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">13.1738023757935</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2713851928711</t>
+    <t xml:space="preserve">13.2713842391968</t>
   </si>
   <si>
     <t xml:space="preserve">13.3527050018311</t>
@@ -2279,16 +2279,16 @@
     <t xml:space="preserve">13.8243598937988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0520553588867</t>
+    <t xml:space="preserve">14.052056312561</t>
   </si>
   <si>
     <t xml:space="preserve">14.2309579849243</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634868621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2146940231323</t>
+    <t xml:space="preserve">14.2634878158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2146949768066</t>
   </si>
   <si>
     <t xml:space="preserve">13.9056787490845</t>
@@ -2297,37 +2297,37 @@
     <t xml:space="preserve">13.6129283905029</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8080949783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8894147872925</t>
+    <t xml:space="preserve">13.8080940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8894157409668</t>
   </si>
   <si>
     <t xml:space="preserve">13.6454563140869</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8406248092651</t>
+    <t xml:space="preserve">13.8406229019165</t>
   </si>
   <si>
     <t xml:space="preserve">13.7918310165405</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0032625198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9544706344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3448066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1496381759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2472238540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4749164581299</t>
+    <t xml:space="preserve">14.0032615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9544696807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3448057174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1496391296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2472229003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4749174118042</t>
   </si>
   <si>
     <t xml:space="preserve">14.557915687561</t>
@@ -2339,19 +2339,19 @@
     <t xml:space="preserve">14.1595239639282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1429233551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2757215499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3753185272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1097249984741</t>
+    <t xml:space="preserve">14.1429243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2757225036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2923212051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.375319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1097240447998</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425212860107</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">14.2093238830566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9935283660889</t>
+    <t xml:space="preserve">13.9935274124146</t>
   </si>
   <si>
     <t xml:space="preserve">13.8109292984009</t>
@@ -2372,13 +2372,13 @@
     <t xml:space="preserve">14.3089189529419</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0599269866943</t>
+    <t xml:space="preserve">14.05992603302</t>
   </si>
   <si>
     <t xml:space="preserve">14.0101251602173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9769268035889</t>
+    <t xml:space="preserve">13.9769258499146</t>
   </si>
   <si>
     <t xml:space="preserve">14.0433263778687</t>
@@ -2390,16 +2390,16 @@
     <t xml:space="preserve">14.2259216308594</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3421201705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1761226654053</t>
+    <t xml:space="preserve">14.3421211242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1761236190796</t>
   </si>
   <si>
     <t xml:space="preserve">13.9437265396118</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0931234359741</t>
+    <t xml:space="preserve">14.0931243896484</t>
   </si>
   <si>
     <t xml:space="preserve">13.9603271484375</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">14.524715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.026725769043</t>
+    <t xml:space="preserve">14.0267248153687</t>
   </si>
   <si>
     <t xml:space="preserve">14.7073125839233</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">14.6907119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7405128479004</t>
+    <t xml:space="preserve">14.7405118942261</t>
   </si>
   <si>
     <t xml:space="preserve">14.9397077560425</t>
@@ -2438,31 +2438,31 @@
     <t xml:space="preserve">15.1057062149048</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3214988708496</t>
+    <t xml:space="preserve">15.3214998245239</t>
   </si>
   <si>
     <t xml:space="preserve">15.1721048355103</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8899087905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3712997436523</t>
+    <t xml:space="preserve">14.8899097442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.371298789978</t>
   </si>
   <si>
     <t xml:space="preserve">15.7032918930054</t>
   </si>
   <si>
-    <t xml:space="preserve">15.537296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3878984451294</t>
+    <t xml:space="preserve">15.5372953414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.387900352478</t>
   </si>
   <si>
     <t xml:space="preserve">15.2883014678955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2717018127441</t>
+    <t xml:space="preserve">15.2717008590698</t>
   </si>
   <si>
     <t xml:space="preserve">15.0725059509277</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">14.9895076751709</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8567113876343</t>
+    <t xml:space="preserve">14.85671043396</t>
   </si>
   <si>
     <t xml:space="preserve">14.8235101699829</t>
@@ -2489,16 +2489,16 @@
     <t xml:space="preserve">15.1389045715332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9729089736938</t>
+    <t xml:space="preserve">14.9729099273682</t>
   </si>
   <si>
     <t xml:space="preserve">14.873309135437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8069114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8607301712036</t>
+    <t xml:space="preserve">14.8069105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8607292175293</t>
   </si>
   <si>
     <t xml:space="preserve">13.6947317123413</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">14.4417171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5745143890381</t>
+    <t xml:space="preserve">14.5745134353638</t>
   </si>
   <si>
     <t xml:space="preserve">14.541316986084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4251184463501</t>
+    <t xml:space="preserve">14.4251194000244</t>
   </si>
   <si>
     <t xml:space="preserve">14.4085187911987</t>
@@ -2525,13 +2525,13 @@
     <t xml:space="preserve">14.3919191360474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4708986282349</t>
+    <t xml:space="preserve">15.4708976745605</t>
   </si>
   <si>
     <t xml:space="preserve">15.2053022384644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0227069854736</t>
+    <t xml:space="preserve">15.0227079391479</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915151596069</t>
@@ -2546,25 +2546,25 @@
     <t xml:space="preserve">13.6449337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445306777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.528736114502</t>
+    <t xml:space="preserve">13.7445316314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5287351608276</t>
   </si>
   <si>
     <t xml:space="preserve">13.5619354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4125375747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1137447357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2797412872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3627395629883</t>
+    <t xml:space="preserve">13.4125385284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1137437820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2797403335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.362738609314</t>
   </si>
   <si>
     <t xml:space="preserve">13.5121374130249</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">13.080545425415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3129405975342</t>
+    <t xml:space="preserve">13.3129396438599</t>
   </si>
   <si>
     <t xml:space="preserve">13.196741104126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7983493804932</t>
+    <t xml:space="preserve">12.7983503341675</t>
   </si>
   <si>
     <t xml:space="preserve">12.4497566223145</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">12.7153511047363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4331569671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5991535186768</t>
+    <t xml:space="preserve">12.4331560134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5991544723511</t>
   </si>
   <si>
     <t xml:space="preserve">12.3335590362549</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">12.0679636001587</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8521671295166</t>
+    <t xml:space="preserve">11.8521680831909</t>
   </si>
   <si>
     <t xml:space="preserve">11.6695728302002</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">11.8189687728882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6031732559204</t>
+    <t xml:space="preserve">11.6031723022461</t>
   </si>
   <si>
     <t xml:space="preserve">11.7027721405029</t>
@@ -2645,10 +2645,10 @@
     <t xml:space="preserve">11.5367746353149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3209791183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1715812683105</t>
+    <t xml:space="preserve">11.3209800720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1715822219849</t>
   </si>
   <si>
     <t xml:space="preserve">11.221381187439</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">10.8395881652832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2088012695312</t>
+    <t xml:space="preserve">10.2088003158569</t>
   </si>
   <si>
     <t xml:space="preserve">10.6735906600952</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">10.6237926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2586002349854</t>
+    <t xml:space="preserve">10.258599281311</t>
   </si>
   <si>
     <t xml:space="preserve">10.1922006607056</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">9.36221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62781238555908</t>
+    <t xml:space="preserve">9.6278133392334</t>
   </si>
   <si>
     <t xml:space="preserve">9.32901763916016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52821350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0096063613892</t>
+    <t xml:space="preserve">9.52821445465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0096054077148</t>
   </si>
   <si>
     <t xml:space="preserve">9.39541625976562</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">10.3913974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6071939468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3083992004395</t>
+    <t xml:space="preserve">10.6071929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3083982467651</t>
   </si>
   <si>
     <t xml:space="preserve">10.4909954071045</t>
@@ -2717,10 +2717,10 @@
     <t xml:space="preserve">10.1092023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1424016952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0594034194946</t>
+    <t xml:space="preserve">10.1424007415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0594024658203</t>
   </si>
   <si>
     <t xml:space="preserve">9.86020755767822</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">9.89340591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69421100616455</t>
+    <t xml:space="preserve">9.69421195983887</t>
   </si>
   <si>
     <t xml:space="preserve">9.61121273040771</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">9.17962074279785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27921867370605</t>
+    <t xml:space="preserve">9.27921962738037</t>
   </si>
   <si>
     <t xml:space="preserve">9.37881660461426</t>
@@ -2756,13 +2756,13 @@
     <t xml:space="preserve">9.42861461639404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77720832824707</t>
+    <t xml:space="preserve">9.77720928192139</t>
   </si>
   <si>
     <t xml:space="preserve">9.64441108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0262031555176</t>
+    <t xml:space="preserve">10.0262041091919</t>
   </si>
   <si>
     <t xml:space="preserve">10.5407943725586</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">9.66899490356445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70334339141846</t>
+    <t xml:space="preserve">9.70334434509277</t>
   </si>
   <si>
     <t xml:space="preserve">9.7205171585083</t>
@@ -2789,28 +2789,28 @@
     <t xml:space="preserve">10.0639991760254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0983467102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2529125213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85790920257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0811729431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.35595703125</t>
+    <t xml:space="preserve">10.0983476638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2529134750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0811719894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3559579849243</t>
   </si>
   <si>
     <t xml:space="preserve">10.2700872421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6479167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7681341171265</t>
+    <t xml:space="preserve">10.6479158401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7681350708008</t>
   </si>
   <si>
     <t xml:space="preserve">10.9570503234863</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">11.1631383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.060094833374</t>
+    <t xml:space="preserve">11.0600938796997</t>
   </si>
   <si>
     <t xml:space="preserve">11.1803121566772</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">10.0296506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0124759674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3903064727783</t>
+    <t xml:space="preserve">10.0124769210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.390305519104</t>
   </si>
   <si>
     <t xml:space="preserve">10.1498689651489</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">10.1326951980591</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97812843322754</t>
+    <t xml:space="preserve">9.97812747955322</t>
   </si>
   <si>
     <t xml:space="preserve">9.87508392333984</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">10.2872610092163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2013912200928</t>
+    <t xml:space="preserve">10.2013921737671</t>
   </si>
   <si>
     <t xml:space="preserve">10.3044357299805</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">10.1842164993286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0468244552612</t>
+    <t xml:space="preserve">10.0468254089355</t>
   </si>
   <si>
     <t xml:space="preserve">10.5620460510254</t>
@@ -2888,13 +2888,13 @@
     <t xml:space="preserve">10.4418277740479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7166118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4590015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5105228424072</t>
+    <t xml:space="preserve">10.7166128158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.459002494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5105237960815</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509613037109</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">10.1155204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75486469268799</t>
+    <t xml:space="preserve">9.7548656463623</t>
   </si>
   <si>
     <t xml:space="preserve">9.61747264862061</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">9.51442813873291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63464832305908</t>
+    <t xml:space="preserve">9.63464736938477</t>
   </si>
   <si>
     <t xml:space="preserve">9.80638790130615</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">9.39420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2224702835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.325514793396</t>
+    <t xml:space="preserve">9.22246932983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32551383972168</t>
   </si>
   <si>
     <t xml:space="preserve">9.25681781768799</t>
@@ -2954,19 +2954,19 @@
     <t xml:space="preserve">9.0850772857666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54877662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56595134735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58312606811523</t>
+    <t xml:space="preserve">9.54877758026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56595039367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58312511444092</t>
   </si>
   <si>
     <t xml:space="preserve">9.65182113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.823561668396</t>
+    <t xml:space="preserve">9.82356071472168</t>
   </si>
   <si>
     <t xml:space="preserve">10.3387832641602</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">11.0429201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8883543014526</t>
+    <t xml:space="preserve">10.8883533477783</t>
   </si>
   <si>
     <t xml:space="preserve">10.9398756027222</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">12.0733642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4683666229248</t>
+    <t xml:space="preserve">12.4683675765991</t>
   </si>
   <si>
     <t xml:space="preserve">12.5027151107788</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">12.485541343689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6401081085205</t>
+    <t xml:space="preserve">12.6401071548462</t>
   </si>
   <si>
     <t xml:space="preserve">12.2451038360596</t>
@@ -3113,10 +3113,10 @@
     <t xml:space="preserve">13.3442440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6362028121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6018552780151</t>
+    <t xml:space="preserve">13.6362037658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6018543243408</t>
   </si>
   <si>
     <t xml:space="preserve">13.550332069397</t>
@@ -3125,16 +3125,16 @@
     <t xml:space="preserve">13.5675067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4644622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3957662582397</t>
+    <t xml:space="preserve">13.4644632339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3957653045654</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6190280914307</t>
+    <t xml:space="preserve">13.619029045105</t>
   </si>
   <si>
     <t xml:space="preserve">14.0827283859253</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">13.7048988342285</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7220726013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8766393661499</t>
+    <t xml:space="preserve">13.7220735549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8766403198242</t>
   </si>
   <si>
     <t xml:space="preserve">14.6151237487793</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">14.6494722366333</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8040380477905</t>
+    <t xml:space="preserve">14.8040390014648</t>
   </si>
   <si>
     <t xml:space="preserve">14.6838207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7868633270264</t>
+    <t xml:space="preserve">14.7868642807007</t>
   </si>
   <si>
     <t xml:space="preserve">14.7181673049927</t>
@@ -3176,43 +3176,43 @@
     <t xml:space="preserve">15.0101270675659</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0616512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1990432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2505645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2162160873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9757804870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9242563247681</t>
+    <t xml:space="preserve">15.0616502761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.387957572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1990423202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2505664825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818685531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.216215133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9757795333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9242553710938</t>
   </si>
   <si>
     <t xml:space="preserve">14.4262094497681</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3918609619141</t>
+    <t xml:space="preserve">14.3918619155884</t>
   </si>
   <si>
     <t xml:space="preserve">14.9586057662964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5464286804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1131715774536</t>
+    <t xml:space="preserve">14.5464296340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1131706237793</t>
   </si>
   <si>
     <t xml:space="preserve">15.1303462982178</t>
@@ -3224,34 +3224,34 @@
     <t xml:space="preserve">15.2677392959595</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4223031997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9031782150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9375257492065</t>
+    <t xml:space="preserve">15.4223041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9031801223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9375267028809</t>
   </si>
   <si>
     <t xml:space="preserve">16.1436138153076</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8516550064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9546995162964</t>
+    <t xml:space="preserve">15.851655960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9547004699707</t>
   </si>
   <si>
     <t xml:space="preserve">15.7829599380493</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7142639160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5253496170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5596981048584</t>
+    <t xml:space="preserve">15.7142629623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5253486633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5596990585327</t>
   </si>
   <si>
     <t xml:space="preserve">14.8383884429932</t>
@@ -3263,31 +3263,31 @@
     <t xml:space="preserve">14.3059902191162</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2888154983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5120792388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6322994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7009944915771</t>
+    <t xml:space="preserve">14.2888164520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5120782852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6323003768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7009954452515</t>
   </si>
   <si>
     <t xml:space="preserve">14.5807752609253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5292539596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3746862411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1431245803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2678127288818</t>
+    <t xml:space="preserve">14.5292549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3746871948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1431255340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2678136825562</t>
   </si>
   <si>
     <t xml:space="preserve">14.321249961853</t>
@@ -3299,10 +3299,10 @@
     <t xml:space="preserve">14.6774997711182</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6062488555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0540628433228</t>
+    <t xml:space="preserve">14.6062498092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0540618896484</t>
   </si>
   <si>
     <t xml:space="preserve">14.0362501144409</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">14.0184373855591</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0006246566772</t>
+    <t xml:space="preserve">14.0006256103516</t>
   </si>
   <si>
     <t xml:space="preserve">13.733437538147</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">13.875937461853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.285626411438</t>
+    <t xml:space="preserve">14.2856254577637</t>
   </si>
   <si>
     <t xml:space="preserve">14.0896873474121</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">14.1609373092651</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1253128051758</t>
+    <t xml:space="preserve">14.1253118515015</t>
   </si>
   <si>
     <t xml:space="preserve">14.4459371566772</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">14.178750038147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9828128814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9293746948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6978120803833</t>
+    <t xml:space="preserve">13.9828119277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9293756484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6978130340576</t>
   </si>
   <si>
     <t xml:space="preserve">13.6799993515015</t>
@@ -3365,16 +3365,16 @@
     <t xml:space="preserve">13.5731248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8403120040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8581256866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9115619659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4840631484985</t>
+    <t xml:space="preserve">13.8403129577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8581247329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9115629196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4840621948242</t>
   </si>
   <si>
     <t xml:space="preserve">13.1278123855591</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">13.8046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7690620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8225011825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3034362792969</t>
+    <t xml:space="preserve">13.7690629959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8225002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3034372329712</t>
   </si>
   <si>
     <t xml:space="preserve">14.3924999237061</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">14.624062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4993762969971</t>
+    <t xml:space="preserve">14.4993753433228</t>
   </si>
   <si>
     <t xml:space="preserve">14.5349998474121</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">14.25</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0718746185303</t>
+    <t xml:space="preserve">14.0718755722046</t>
   </si>
   <si>
     <t xml:space="preserve">13.359375</t>
@@ -3428,22 +3428,22 @@
     <t xml:space="preserve">13.5018749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5196886062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2321872711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6265621185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812505722046</t>
+    <t xml:space="preserve">13.5196876525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2321863174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6265630722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812496185303</t>
   </si>
   <si>
     <t xml:space="preserve">13.0565624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1100006103516</t>
+    <t xml:space="preserve">13.1099996566772</t>
   </si>
   <si>
     <t xml:space="preserve">12.842812538147</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">12.8249998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7181243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221872329712</t>
+    <t xml:space="preserve">12.7181253433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221881866455</t>
   </si>
   <si>
     <t xml:space="preserve">12.397500038147</t>
@@ -3476,25 +3476,25 @@
     <t xml:space="preserve">12.4865627288818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2906246185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2193746566772</t>
+    <t xml:space="preserve">12.2906255722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2193756103516</t>
   </si>
   <si>
     <t xml:space="preserve">12.2550001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1481246948242</t>
+    <t xml:space="preserve">12.1481256484985</t>
   </si>
   <si>
     <t xml:space="preserve">12.1659374237061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1303129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165620803833</t>
+    <t xml:space="preserve">12.1303119659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165630340576</t>
   </si>
   <si>
     <t xml:space="preserve">11.578125</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">11.3287506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2931251525879</t>
+    <t xml:space="preserve">11.2931261062622</t>
   </si>
   <si>
     <t xml:space="preserve">11.1328125</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">10.9012498855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9190626144409</t>
+    <t xml:space="preserve">10.9190635681152</t>
   </si>
   <si>
     <t xml:space="preserve">11.061562538147</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">11.0971879959106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1684370040894</t>
+    <t xml:space="preserve">11.1684379577637</t>
   </si>
   <si>
     <t xml:space="preserve">11.204062461853</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">11.4534368515015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8631248474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0768747329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453121185303</t>
+    <t xml:space="preserve">11.8631238937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0768756866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453130722046</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809375762939</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">11.9878120422363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2015628814697</t>
+    <t xml:space="preserve">12.2015619277954</t>
   </si>
   <si>
     <t xml:space="preserve">12.6468753814697</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">12.7003126144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3618755340576</t>
+    <t xml:space="preserve">12.3618745803833</t>
   </si>
   <si>
     <t xml:space="preserve">12.3440628051758</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">12.094687461853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0590629577637</t>
+    <t xml:space="preserve">12.0590620040894</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056247711182</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">11.4178123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4356260299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7384386062622</t>
+    <t xml:space="preserve">11.4356250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7384376525879</t>
   </si>
   <si>
     <t xml:space="preserve">11.7562494277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5959377288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8275003433228</t>
+    <t xml:space="preserve">11.5959386825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8274993896484</t>
   </si>
   <si>
     <t xml:space="preserve">11.7206249237061</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">11.2396869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424995422363</t>
+    <t xml:space="preserve">11.5425004959106</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028131484985</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">11.9700002670288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5246868133545</t>
+    <t xml:space="preserve">11.5246877670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.9724998474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1149997711182</t>
+    <t xml:space="preserve">11.1149988174438</t>
   </si>
   <si>
     <t xml:space="preserve">11.3382139205933</t>
@@ -4353,6 +4353,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.06999969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80000019073486</t>
   </si>
 </sst>
 </file>
@@ -69327,7 +69330,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6495138889</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>64516</v>
@@ -69348,6 +69351,32 @@
         <v>1439</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6496180556</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>65088</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="1448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="1449">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04141759872437</t>
+    <t xml:space="preserve">4.04141712188721</t>
   </si>
   <si>
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447891235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93978905677795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82799816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78057193756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943188667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75685834884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74330735206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8008975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040839195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571805953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66539287567139</t>
+    <t xml:space="preserve">4.02447938919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93978929519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82799792289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78057146072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943140983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75685906410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74330711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80089640617371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040815353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66539263725281</t>
   </si>
   <si>
     <t xml:space="preserve">3.56376457214355</t>
@@ -83,25 +83,25 @@
     <t xml:space="preserve">3.65184235572815</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72637009620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70265603065491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65861773490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69249367713928</t>
+    <t xml:space="preserve">3.72636985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7026572227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65861749649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69249296188354</t>
   </si>
   <si>
     <t xml:space="preserve">3.74669528007507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59764051437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59086585044861</t>
+    <t xml:space="preserve">3.59764122962952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59086537361145</t>
   </si>
   <si>
     <t xml:space="preserve">3.58409023284912</t>
@@ -110,226 +110,226 @@
     <t xml:space="preserve">3.49601197242737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4621365070343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51633787155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38760924339294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40793466567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50956201553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55698871612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56715202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57731509208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54682660102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5265007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50278687477112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56037664413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58070254325867</t>
+    <t xml:space="preserve">3.46213674545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51633739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38760900497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40793490409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50956296920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55698895454407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56715226173401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61119103431702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57731461524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54682683944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52650046348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50278735160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56037712097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58070230484009</t>
   </si>
   <si>
     <t xml:space="preserve">3.60102820396423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54343843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57053923606873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64506769180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78734707832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84154915809631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86526131629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85171175003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92962598800659</t>
+    <t xml:space="preserve">3.54343914985657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57053971290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64506697654724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78734683990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84154868125916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86526226997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85171103477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92962622642517</t>
   </si>
   <si>
     <t xml:space="preserve">3.93640160560608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91607594490051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90252542495728</t>
+    <t xml:space="preserve">3.91607618331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90252494812012</t>
   </si>
   <si>
     <t xml:space="preserve">3.89575052261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92285108566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90930104255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97027802467346</t>
+    <t xml:space="preserve">3.92285060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90930032730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97027826309204</t>
   </si>
   <si>
     <t xml:space="preserve">3.87881183624268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85848641395569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94317650794983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89913845062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94656348228455</t>
+    <t xml:space="preserve">3.85848689079285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94317698478699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89913725852966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94656467437744</t>
   </si>
   <si>
     <t xml:space="preserve">3.95672750473022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9635021686554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91268801689148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97366452217102</t>
+    <t xml:space="preserve">3.96350240707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91268849372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97366547584534</t>
   </si>
   <si>
     <t xml:space="preserve">3.91946387290955</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87203741073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8870484828949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87291383743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85877919197083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83757615089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86231184005737</t>
+    <t xml:space="preserve">3.87203693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88704800605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87291288375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85877871513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83757591247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86231303215027</t>
   </si>
   <si>
     <t xml:space="preserve">3.87644696235657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89411544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9011824131012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058136940002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94358706474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95418810844421</t>
+    <t xml:space="preserve">3.89411520957947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90118265151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8905816078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94358682632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95418787002563</t>
   </si>
   <si>
     <t xml:space="preserve">3.96125507354736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01426029205322</t>
+    <t xml:space="preserve">4.01425981521606</t>
   </si>
   <si>
     <t xml:space="preserve">4.02486181259155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08846759796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05666446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03899669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305868148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00719404220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97538924217224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97185611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80224013328552</t>
+    <t xml:space="preserve">4.08846807479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05666399002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03899621963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305844306946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00719356536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97539067268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97185659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80223941802979</t>
   </si>
   <si>
     <t xml:space="preserve">3.78103756904602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75630211830139</t>
+    <t xml:space="preserve">3.75630187988281</t>
   </si>
   <si>
     <t xml:space="preserve">3.74923419952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90471601486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92238402366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065450668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03546237945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75983572006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80930662155151</t>
+    <t xml:space="preserve">3.90471577644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92238545417786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065426826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03546333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75983548164368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80930709838867</t>
   </si>
   <si>
     <t xml:space="preserve">3.83050918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86937975883484</t>
+    <t xml:space="preserve">3.86937928199768</t>
   </si>
   <si>
     <t xml:space="preserve">3.82344174385071</t>
@@ -338,31 +338,31 @@
     <t xml:space="preserve">3.80577373504639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84111070632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85171127319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81637454032898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8658459186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89764881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93651962280273</t>
+    <t xml:space="preserve">3.84110999107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85171055793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8163743019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86584615707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89764904975891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93651914596558</t>
   </si>
   <si>
     <t xml:space="preserve">3.9082498550415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91531705856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97892355918884</t>
+    <t xml:space="preserve">3.91531777381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97892427444458</t>
   </si>
   <si>
     <t xml:space="preserve">4.00012588500977</t>
@@ -371,88 +371,88 @@
     <t xml:space="preserve">4.02132749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95772099494934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84464335441589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81284117698669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77043652534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690292358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76336884498596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7457013130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72449827194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77397012710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78810501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81990814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72803258895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73863339424133</t>
+    <t xml:space="preserve">3.9577214717865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84464406967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81284070014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77043676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690268516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76336860656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74570059776306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72449851036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77397036552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78810524940491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81990838050842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72803211212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73863363265991</t>
   </si>
   <si>
     <t xml:space="preserve">3.73156595230103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73510003089905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65382432937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63968992233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66089177131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61848855018616</t>
+    <t xml:space="preserve">3.73509955406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65382480621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6396906375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66089272499084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.618488073349</t>
   </si>
   <si>
     <t xml:space="preserve">3.61142134666443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62555599212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61495447158813</t>
+    <t xml:space="preserve">3.62555575370789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61495399475098</t>
   </si>
   <si>
     <t xml:space="preserve">3.64675760269165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74216675758362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91885137557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98599028587341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9965922832489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87998080253601</t>
+    <t xml:space="preserve">3.7421669960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91885185241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98599076271057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99659252166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87998032569885</t>
   </si>
   <si>
     <t xml:space="preserve">3.88351440429688</t>
@@ -461,25 +461,25 @@
     <t xml:space="preserve">3.79517197608948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82697558403015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79163813591003</t>
+    <t xml:space="preserve">3.82697510719299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79163837432861</t>
   </si>
   <si>
     <t xml:space="preserve">3.8481776714325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71036338806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85524439811707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03192853927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04252910614014</t>
+    <t xml:space="preserve">3.7103636264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85524415969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03192949295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04252958297729</t>
   </si>
   <si>
     <t xml:space="preserve">4.08493423461914</t>
@@ -488,25 +488,25 @@
     <t xml:space="preserve">4.0990686416626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05313110351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04959726333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09200143814087</t>
+    <t xml:space="preserve">4.05313158035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04959774017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09200096130371</t>
   </si>
   <si>
     <t xml:space="preserve">4.10966968536377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07786703109741</t>
+    <t xml:space="preserve">4.07786655426025</t>
   </si>
   <si>
     <t xml:space="preserve">4.07433271408081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04606342315674</t>
+    <t xml:space="preserve">4.04606294631958</t>
   </si>
   <si>
     <t xml:space="preserve">4.0637321472168</t>
@@ -515,19 +515,19 @@
     <t xml:space="preserve">4.10613632202148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10260248184204</t>
+    <t xml:space="preserve">4.10260200500488</t>
   </si>
   <si>
     <t xml:space="preserve">4.13440561294556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12733793258667</t>
+    <t xml:space="preserve">4.12733840942383</t>
   </si>
   <si>
     <t xml:space="preserve">4.16974210739136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18387651443481</t>
+    <t xml:space="preserve">4.18387699127197</t>
   </si>
   <si>
     <t xml:space="preserve">4.15914154052734</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">4.27575254440308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34642696380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36762809753418</t>
+    <t xml:space="preserve">4.34642601013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36762857437134</t>
   </si>
   <si>
     <t xml:space="preserve">4.35349369049072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31108903884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30402231216431</t>
+    <t xml:space="preserve">4.31108951568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30402278900146</t>
   </si>
   <si>
     <t xml:space="preserve">4.38176298141479</t>
@@ -563,22 +563,22 @@
     <t xml:space="preserve">4.50897550582886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72806358337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91181516647339</t>
+    <t xml:space="preserve">4.72806406021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91181564331055</t>
   </si>
   <si>
     <t xml:space="preserve">4.94715166091919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19450902938843</t>
+    <t xml:space="preserve">5.19450950622559</t>
   </si>
   <si>
     <t xml:space="preserve">5.22277879714966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2298469543457</t>
+    <t xml:space="preserve">5.22984647750854</t>
   </si>
   <si>
     <t xml:space="preserve">5.2263126373291</t>
@@ -587,43 +587,43 @@
     <t xml:space="preserve">5.09203243255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07436418533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08496618270874</t>
+    <t xml:space="preserve">5.07436370849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08496522903442</t>
   </si>
   <si>
     <t xml:space="preserve">5.1167688369751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10616779327393</t>
+    <t xml:space="preserve">5.10616731643677</t>
   </si>
   <si>
     <t xml:space="preserve">5.1521053314209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15917205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1733078956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1909761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14503765106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13090324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2475152015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26871681213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59734916687012</t>
+    <t xml:space="preserve">5.15917348861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17330741882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19097661972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14503812789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13090372085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24751567840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26871728897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59734964370728</t>
   </si>
   <si>
     <t xml:space="preserve">5.51254081726074</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">5.35705900192261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47720336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37119340896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44186687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53020858764648</t>
+    <t xml:space="preserve">5.47720432281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37119388580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44186735153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53020906448364</t>
   </si>
   <si>
     <t xml:space="preserve">5.61199712753296</t>
@@ -650,25 +650,25 @@
     <t xml:space="preserve">5.65216112136841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68867349624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6229510307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.619300365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59739255905151</t>
+    <t xml:space="preserve">5.6886739730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62295150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61929988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59739208221436</t>
   </si>
   <si>
     <t xml:space="preserve">5.42213201522827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41848087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5535774230957</t>
+    <t xml:space="preserve">5.41848039627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55357694625854</t>
   </si>
   <si>
     <t xml:space="preserve">5.56087970733643</t>
@@ -680,31 +680,31 @@
     <t xml:space="preserve">5.46229553222656</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55722856521606</t>
+    <t xml:space="preserve">5.55722904205322</t>
   </si>
   <si>
     <t xml:space="preserve">5.45499277114868</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36736297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3746657371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43308591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40387582778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47690010070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4476900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48055171966553</t>
+    <t xml:space="preserve">5.36736249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37466478347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43308544158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40387535095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47690057754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44769048690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48055267333984</t>
   </si>
   <si>
     <t xml:space="preserve">5.49515676498413</t>
@@ -713,19 +713,19 @@
     <t xml:space="preserve">5.54627418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60104370117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41117715835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5134129524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54992628097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45134210586548</t>
+    <t xml:space="preserve">5.60104322433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41117763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51341342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54992580413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45134162902832</t>
   </si>
   <si>
     <t xml:space="preserve">5.61564874649048</t>
@@ -734,16 +734,16 @@
     <t xml:space="preserve">5.50611019134521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34545469284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37101459503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31259346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28703451156616</t>
+    <t xml:space="preserve">5.34545516967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37101364135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31259298324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28703498840332</t>
   </si>
   <si>
     <t xml:space="preserve">5.15558910369873</t>
@@ -752,16 +752,16 @@
     <t xml:space="preserve">5.12637853622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2724289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31989574432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14098358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40752696990967</t>
+    <t xml:space="preserve">5.27242946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31989622116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14098405838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40752649307251</t>
   </si>
   <si>
     <t xml:space="preserve">5.38927030563354</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">5.37831592559814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24321937561035</t>
+    <t xml:space="preserve">5.24321889877319</t>
   </si>
   <si>
     <t xml:space="preserve">5.46959781646729</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">5.42578268051147</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44038724899292</t>
+    <t xml:space="preserve">5.44038772583008</t>
   </si>
   <si>
     <t xml:space="preserve">5.48420333862305</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">5.50245952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57183361053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57913541793823</t>
+    <t xml:space="preserve">5.57183313369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57913589477539</t>
   </si>
   <si>
     <t xml:space="preserve">5.56453084945679</t>
@@ -815,34 +815,34 @@
     <t xml:space="preserve">5.65581226348877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58643865585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57548475265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50976133346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53166961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60469484329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59009027481079</t>
+    <t xml:space="preserve">5.58643817901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57548427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50976228713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53166913986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60469532012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59008979797363</t>
   </si>
   <si>
     <t xml:space="preserve">5.75804805755615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79456090927124</t>
+    <t xml:space="preserve">5.79456043243408</t>
   </si>
   <si>
     <t xml:space="preserve">5.92965745925903</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94426345825195</t>
+    <t xml:space="preserve">5.94426298141479</t>
   </si>
   <si>
     <t xml:space="preserve">5.99903154373169</t>
@@ -851,19 +851,19 @@
     <t xml:space="preserve">5.93696069717407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98807716369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83107328414917</t>
+    <t xml:space="preserve">5.98807764053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83107376098633</t>
   </si>
   <si>
     <t xml:space="preserve">5.88584327697754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83472442626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95886754989624</t>
+    <t xml:space="preserve">5.83472490310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95886707305908</t>
   </si>
   <si>
     <t xml:space="preserve">5.76900196075439</t>
@@ -878,25 +878,25 @@
     <t xml:space="preserve">5.84202718734741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87123680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.783607006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85298109054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70327854156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82742214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8639349937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75439691543579</t>
+    <t xml:space="preserve">5.87123727798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78360748291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85298156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7032790184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82742261886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86393404006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75439643859863</t>
   </si>
   <si>
     <t xml:space="preserve">5.72883796691895</t>
@@ -905,82 +905,82 @@
     <t xml:space="preserve">5.68502235412598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66676616668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88949346542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78725814819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77995634078979</t>
+    <t xml:space="preserve">5.66676664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88949394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78725862503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77995538711548</t>
   </si>
   <si>
     <t xml:space="preserve">5.73614025115967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6083459854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63025379180908</t>
+    <t xml:space="preserve">5.60834646224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63025331497192</t>
   </si>
   <si>
     <t xml:space="preserve">5.53532075881958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76169967651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6266016960144</t>
+    <t xml:space="preserve">5.76169919967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62660264968872</t>
   </si>
   <si>
     <t xml:space="preserve">5.68137168884277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73979139328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76535081863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80916595458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80551481246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82377004623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87854051589966</t>
+    <t xml:space="preserve">5.73979187011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76535034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80916547775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80551385879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82377099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8785400390625</t>
   </si>
   <si>
     <t xml:space="preserve">5.82011938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90409898757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600631713867</t>
+    <t xml:space="preserve">5.90409851074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600584030151</t>
   </si>
   <si>
     <t xml:space="preserve">5.92235469818115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95156478881836</t>
+    <t xml:space="preserve">5.95156526565552</t>
   </si>
   <si>
     <t xml:space="preserve">6.02459049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06110429763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00998497009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09031391143799</t>
+    <t xml:space="preserve">6.06110382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00998544692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09031343460083</t>
   </si>
   <si>
     <t xml:space="preserve">6.22906160354614</t>
@@ -992,52 +992,52 @@
     <t xml:space="preserve">6.03189325332642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03919506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04649782180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25096940994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20715427398682</t>
+    <t xml:space="preserve">6.03919553756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04649829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25096845626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20715379714966</t>
   </si>
   <si>
     <t xml:space="preserve">6.14143037796021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12682580947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79821157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72518634796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96617031097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00268268585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8931450843811</t>
+    <t xml:space="preserve">6.12682628631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7982120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72518682479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96617078781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00268316268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89314460754395</t>
   </si>
   <si>
     <t xml:space="preserve">5.84932994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.973473072052</t>
+    <t xml:space="preserve">5.97347259521484</t>
   </si>
   <si>
     <t xml:space="preserve">5.99538087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11952352523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15603590011597</t>
+    <t xml:space="preserve">6.1195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15603637695312</t>
   </si>
   <si>
     <t xml:space="preserve">6.10491800308228</t>
@@ -1046,25 +1046,25 @@
     <t xml:space="preserve">5.98077487945557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90044784545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14873361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09761571884155</t>
+    <t xml:space="preserve">5.90044736862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1487340927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09761619567871</t>
   </si>
   <si>
     <t xml:space="preserve">6.05380058288574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07570791244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08301115036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17794418334961</t>
+    <t xml:space="preserve">6.07570838928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08301067352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17794370651245</t>
   </si>
   <si>
     <t xml:space="preserve">6.17064094543457</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">6.24366664886475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28017997741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38636541366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31810331344604</t>
+    <t xml:space="preserve">6.28017950057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38636589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31810283660889</t>
   </si>
   <si>
     <t xml:space="preserve">6.23467063903809</t>
@@ -1088,46 +1088,46 @@
     <t xml:space="preserve">6.28017902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15882253646851</t>
+    <t xml:space="preserve">6.15882301330566</t>
   </si>
   <si>
     <t xml:space="preserve">6.27259397506714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26500940322876</t>
+    <t xml:space="preserve">6.26500988006592</t>
   </si>
   <si>
     <t xml:space="preserve">6.21191596984863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1815767288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15123844146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02988195419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05263614654541</t>
+    <t xml:space="preserve">6.18157720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15123796463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02988147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05263662338257</t>
   </si>
   <si>
     <t xml:space="preserve">6.25742483139038</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22708559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24983978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29534959793091</t>
+    <t xml:space="preserve">6.22708606719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24983930587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29534912109375</t>
   </si>
   <si>
     <t xml:space="preserve">6.3711953163147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1891622543335</t>
+    <t xml:space="preserve">6.18916130065918</t>
   </si>
   <si>
     <t xml:space="preserve">6.1664080619812</t>
@@ -1142,25 +1142,25 @@
     <t xml:space="preserve">6.04505157470703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00712776184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98437309265137</t>
+    <t xml:space="preserve">6.00712823867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98437356948853</t>
   </si>
   <si>
     <t xml:space="preserve">6.12089872360229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13606834411621</t>
+    <t xml:space="preserve">6.13606882095337</t>
   </si>
   <si>
     <t xml:space="preserve">6.11331510543823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09055995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96161890029907</t>
+    <t xml:space="preserve">6.09055948257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96161937713623</t>
   </si>
   <si>
     <t xml:space="preserve">6.0829758644104</t>
@@ -1169,19 +1169,19 @@
     <t xml:space="preserve">6.14365386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1057300567627</t>
+    <t xml:space="preserve">6.10572957992554</t>
   </si>
   <si>
     <t xml:space="preserve">6.06022119522095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9995436668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95403480529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93886566162109</t>
+    <t xml:space="preserve">5.99954319000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95403432846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93886470794678</t>
   </si>
   <si>
     <t xml:space="preserve">6.06780576705933</t>
@@ -1190,31 +1190,31 @@
     <t xml:space="preserve">5.91611051559448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94644927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818670272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746700286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02229785919189</t>
+    <t xml:space="preserve">5.94644975662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818717956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746652603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02229738235474</t>
   </si>
   <si>
     <t xml:space="preserve">5.99195861816406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8630166053772</t>
+    <t xml:space="preserve">5.86301755905151</t>
   </si>
   <si>
     <t xml:space="preserve">6.07539081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24225425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738265991211</t>
+    <t xml:space="preserve">6.24225521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738313674927</t>
   </si>
   <si>
     <t xml:space="preserve">6.63666248321533</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">6.46221351623535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57598495483398</t>
+    <t xml:space="preserve">6.57598400115967</t>
   </si>
   <si>
     <t xml:space="preserve">6.56081485748291</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">6.6063232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55323123931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65183258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53806018829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48496723175049</t>
+    <t xml:space="preserve">6.55323076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65183210372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53806066513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48496770858765</t>
   </si>
   <si>
     <t xml:space="preserve">6.6139087677002</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">6.59873914718628</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34085750579834</t>
+    <t xml:space="preserve">6.34085655212402</t>
   </si>
   <si>
     <t xml:space="preserve">6.39395046234131</t>
@@ -1262,37 +1262,37 @@
     <t xml:space="preserve">6.4167046546936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42428970336914</t>
+    <t xml:space="preserve">6.4242901802063</t>
   </si>
   <si>
     <t xml:space="preserve">6.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5911545753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54564571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56840038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44704437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34844160079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21950006484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40912008285522</t>
+    <t xml:space="preserve">6.59115362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54564619064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56839942932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44704341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34844207763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21950054168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40911960601807</t>
   </si>
   <si>
     <t xml:space="preserve">6.32568788528442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2877631187439</t>
+    <t xml:space="preserve">6.28776359558105</t>
   </si>
   <si>
     <t xml:space="preserve">6.6897554397583</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">6.75043344497681</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62149333953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37878084182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36361122131348</t>
+    <t xml:space="preserve">6.62149286270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37878036499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36361169815063</t>
   </si>
   <si>
     <t xml:space="preserve">6.46979808807373</t>
@@ -1322,34 +1322,34 @@
     <t xml:space="preserve">6.51530694961548</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31051778793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3560266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19674634933472</t>
+    <t xml:space="preserve">6.31051826477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35602712631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19674730300903</t>
   </si>
   <si>
     <t xml:space="preserve">6.40153503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72009515762329</t>
+    <t xml:space="preserve">6.72009420394897</t>
   </si>
   <si>
     <t xml:space="preserve">6.75801849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80352735519409</t>
+    <t xml:space="preserve">6.80352687835693</t>
   </si>
   <si>
     <t xml:space="preserve">6.78835773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73526382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84903573989868</t>
+    <t xml:space="preserve">6.73526430130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84903621673584</t>
   </si>
   <si>
     <t xml:space="preserve">6.86420583724976</t>
@@ -1358,28 +1358,28 @@
     <t xml:space="preserve">6.81111145019531</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84145164489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81869649887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90213012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9931468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89454412460327</t>
+    <t xml:space="preserve">6.8414511680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81869697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90212965011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99314546585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89454460144043</t>
   </si>
   <si>
     <t xml:space="preserve">6.94005298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05382442474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10691738128662</t>
+    <t xml:space="preserve">7.05382394790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10691833496094</t>
   </si>
   <si>
     <t xml:space="preserve">7.15242624282837</t>
@@ -1391,22 +1391,22 @@
     <t xml:space="preserve">7.0159010887146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08416366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04623985290527</t>
+    <t xml:space="preserve">7.08416414260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04623937606812</t>
   </si>
   <si>
     <t xml:space="preserve">7.09174823760986</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39513826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35721349716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34204530715942</t>
+    <t xml:space="preserve">7.39513874053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35721397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34204626083374</t>
   </si>
   <si>
     <t xml:space="preserve">7.12208700180054</t>
@@ -1415,103 +1415,103 @@
     <t xml:space="preserve">7.13725662231445</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12967109680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25102806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22827291488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20551919937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1979341506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16759586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37996816635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43306255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49373960494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53924894332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54683399200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75162172317505</t>
+    <t xml:space="preserve">7.12967157363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2510290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22827434539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2055196762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19793367385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16759538650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37996864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43306159973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49374055862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5392484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54683303833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75162267684937</t>
   </si>
   <si>
     <t xml:space="preserve">7.79713010787964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64543581008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69094467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57717180252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45581579208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51649522781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59992742538452</t>
+    <t xml:space="preserve">7.64543437957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69094562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57717275619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45581769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51649332046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59992694854736</t>
   </si>
   <si>
     <t xml:space="preserve">7.50890970230103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56200361251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58475732803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55441808700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47856950759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4709849357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44823026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70611381530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88814687728882</t>
+    <t xml:space="preserve">7.56200313568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58475828170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55441761016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47857046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47098588943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4482307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70611238479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88814735412598</t>
   </si>
   <si>
     <t xml:space="preserve">8.25221633911133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61628437042236</t>
+    <t xml:space="preserve">8.61628341674805</t>
   </si>
   <si>
     <t xml:space="preserve">8.49492835998535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17636680603027</t>
+    <t xml:space="preserve">8.17636871337891</t>
   </si>
   <si>
     <t xml:space="preserve">8.41908168792725</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">8.1187686920166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08742141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9306902885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04040336608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96203708648682</t>
+    <t xml:space="preserve">8.08742237091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93068885803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04040241241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96203565597534</t>
   </si>
   <si>
     <t xml:space="preserve">8.25982856750488</t>
@@ -1538,103 +1538,103 @@
     <t xml:space="preserve">8.02472972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86799764633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7347731590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83664989471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82097578048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91501712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97771024703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07174968719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05607604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85232353210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40088844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46358108520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6203145980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30684947967529</t>
+    <t xml:space="preserve">7.86799621582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73477411270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83665037155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82097721099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91501665115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97770929336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07175064086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05607509613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85232305526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40088939666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46358203887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62031555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30684852600098</t>
   </si>
   <si>
     <t xml:space="preserve">8.1657886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33819580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21280765533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27550315856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36954212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15011501312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18146133422852</t>
+    <t xml:space="preserve">8.33819484710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21280860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27550220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36954307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15011596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18146228790283</t>
   </si>
   <si>
     <t xml:space="preserve">8.13444232940674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22848224639893</t>
+    <t xml:space="preserve">8.22848129272461</t>
   </si>
   <si>
     <t xml:space="preserve">8.43223476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99338388442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19713592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75828313827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89934349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82881259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88367033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81314039230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67991781234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79746675491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4165620803833</t>
+    <t xml:space="preserve">7.99338245391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19713687896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75828266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89934206008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82881355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88366985321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313991546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6799168586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79746580123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41656112670898</t>
   </si>
   <si>
     <t xml:space="preserve">7.80530309677124</t>
@@ -1643,22 +1643,22 @@
     <t xml:space="preserve">7.68775320053101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74260950088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00905609130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94636297225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75044584274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7190990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10309600830078</t>
+    <t xml:space="preserve">7.74261045455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00905704498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.946364402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75044727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71909952163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10309505462646</t>
   </si>
   <si>
     <t xml:space="preserve">8.82406806945801</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">9.48234558105469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79581165313721</t>
+    <t xml:space="preserve">9.79581260681152</t>
   </si>
   <si>
     <t xml:space="preserve">9.9368724822998</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">9.99956512451172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1562976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5011110305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3757238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5481309890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2189912796021</t>
+    <t xml:space="preserve">10.1562986373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5011100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3757228851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5481300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2189903259277</t>
   </si>
   <si>
     <t xml:space="preserve">10.171971321106</t>
@@ -1709,37 +1709,37 @@
     <t xml:space="preserve">9.90552520751953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88985252380371</t>
+    <t xml:space="preserve">9.88985061645508</t>
   </si>
   <si>
     <t xml:space="preserve">9.92119884490967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73311996459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76446723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57638549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96821784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0309104919434</t>
+    <t xml:space="preserve">9.73311901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76446533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57638645172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96821880340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.030912399292</t>
   </si>
   <si>
     <t xml:space="preserve">10.4854373931885</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2503385543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0152387619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1249523162842</t>
+    <t xml:space="preserve">10.2503366470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0152368545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1249504089355</t>
   </si>
   <si>
     <t xml:space="preserve">10.3600511550903</t>
@@ -1748,10 +1748,10 @@
     <t xml:space="preserve">10.2973585128784</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3130302429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4384174346924</t>
+    <t xml:space="preserve">10.3130321502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4384183883667</t>
   </si>
   <si>
     <t xml:space="preserve">10.6264972686768</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">10.657844543457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6108245849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5951509475708</t>
+    <t xml:space="preserve">10.6108226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5951499938965</t>
   </si>
   <si>
     <t xml:space="preserve">10.5794773101807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6421699523926</t>
+    <t xml:space="preserve">10.6421709060669</t>
   </si>
   <si>
     <t xml:space="preserve">10.7518835067749</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">10.9556360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1280422210693</t>
+    <t xml:space="preserve">11.128041267395</t>
   </si>
   <si>
     <t xml:space="preserve">11.0183305740356</t>
@@ -1790,16 +1790,16 @@
     <t xml:space="preserve">11.2377557754517</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1593894958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0966958999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1750631332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1123685836792</t>
+    <t xml:space="preserve">11.1593885421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1750621795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1123695373535</t>
   </si>
   <si>
     <t xml:space="preserve">11.0810222625732</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">10.9713096618652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.798903465271</t>
+    <t xml:space="preserve">10.7989025115967</t>
   </si>
   <si>
     <t xml:space="preserve">10.0622587203979</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">9.6860990524292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.294264793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5450382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98080062866211</t>
+    <t xml:space="preserve">9.29426670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54504013061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98080158233643</t>
   </si>
   <si>
     <t xml:space="preserve">8.54194736480713</t>
@@ -1835,19 +1835,19 @@
     <t xml:space="preserve">7.31943130493164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5075101852417</t>
+    <t xml:space="preserve">7.50751066207886</t>
   </si>
   <si>
     <t xml:space="preserve">7.53885746002197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49183702468872</t>
+    <t xml:space="preserve">7.49183797836304</t>
   </si>
   <si>
     <t xml:space="preserve">8.66733455657959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44790744781494</t>
+    <t xml:space="preserve">8.44790840148926</t>
   </si>
   <si>
     <t xml:space="preserve">8.38521480560303</t>
@@ -1859,37 +1859,37 @@
     <t xml:space="preserve">9.01214694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45100116729736</t>
+    <t xml:space="preserve">9.45100021362305</t>
   </si>
   <si>
     <t xml:space="preserve">9.10618686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9337797164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38830661773682</t>
+    <t xml:space="preserve">8.93378067016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3883056640625</t>
   </si>
   <si>
     <t xml:space="preserve">8.88676071166992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87108707427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12186050415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91810703277588</t>
+    <t xml:space="preserve">8.87108612060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12185955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9181079864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.15320777893066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90243434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05916690826416</t>
+    <t xml:space="preserve">8.90243339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05916786193848</t>
   </si>
   <si>
     <t xml:space="preserve">9.04349422454834</t>
@@ -1898,10 +1898,10 @@
     <t xml:space="preserve">9.21590042114258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96512889862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30298137664795</t>
+    <t xml:space="preserve">8.96512794494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30298042297363</t>
   </si>
   <si>
     <t xml:space="preserve">9.12407779693604</t>
@@ -1910,25 +1910,25 @@
     <t xml:space="preserve">9.01023006439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68494987487793</t>
+    <t xml:space="preserve">8.68495082855225</t>
   </si>
   <si>
     <t xml:space="preserve">8.50604724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70121479034424</t>
+    <t xml:space="preserve">8.70121383666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.18913269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92891025543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76626968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71747875213623</t>
+    <t xml:space="preserve">8.92890930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76627063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71747970581055</t>
   </si>
   <si>
     <t xml:space="preserve">8.97770214080811</t>
@@ -1940,19 +1940,19 @@
     <t xml:space="preserve">9.48188495635986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61199474334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2625541687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0673875808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3113470077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1812353134155</t>
+    <t xml:space="preserve">9.61199569702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2625532150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0673866271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3113460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812343597412</t>
   </si>
   <si>
     <t xml:space="preserve">10.2137622833252</t>
@@ -1961,13 +1961,13 @@
     <t xml:space="preserve">10.2788181304932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2300252914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.953537940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88848304748535</t>
+    <t xml:space="preserve">10.2300262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95353889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88848400115967</t>
   </si>
   <si>
     <t xml:space="preserve">9.69331550598145</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">10.1974983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3276090621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2462902069092</t>
+    <t xml:space="preserve">10.3276100158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2462911605835</t>
   </si>
   <si>
     <t xml:space="preserve">10.555305480957</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">10.8480567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8805847167969</t>
+    <t xml:space="preserve">10.8805837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.8317918777466</t>
@@ -2003,19 +2003,19 @@
     <t xml:space="preserve">10.9293756484985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.685417175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.636625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7667360305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9781684875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1245422363281</t>
+    <t xml:space="preserve">10.6854181289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6366243362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7667350769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9781675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1245431900024</t>
   </si>
   <si>
     <t xml:space="preserve">11.1408081054688</t>
@@ -2024,16 +2024,16 @@
     <t xml:space="preserve">11.2871828079224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3847675323486</t>
+    <t xml:space="preserve">11.3847665786743</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474061965942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4335584640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4498224258423</t>
+    <t xml:space="preserve">11.4335594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4498233795166</t>
   </si>
   <si>
     <t xml:space="preserve">11.4660873413086</t>
@@ -2045,13 +2045,13 @@
     <t xml:space="preserve">11.3359746932983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2058629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2221279144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8643198013306</t>
+    <t xml:space="preserve">11.2058639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2221260070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8643188476562</t>
   </si>
   <si>
     <t xml:space="preserve">10.5390405654907</t>
@@ -2060,61 +2060,61 @@
     <t xml:space="preserve">10.5227766036987</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7016801834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8155288696289</t>
+    <t xml:space="preserve">10.701681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8155279159546</t>
   </si>
   <si>
     <t xml:space="preserve">10.604097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7342081069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6203603744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.717945098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5065135955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.587833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4577217102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3764019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.571569442749</t>
+    <t xml:space="preserve">10.7342090606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.620361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7179460525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5065126419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5878343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4577207565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3764009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5715684890747</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089288711548</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8968486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0594892501831</t>
+    <t xml:space="preserve">10.8968477249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0594882965088</t>
   </si>
   <si>
     <t xml:space="preserve">10.9944324493408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.669153213501</t>
+    <t xml:space="preserve">10.6691522598267</t>
   </si>
   <si>
     <t xml:space="preserve">10.7829999923706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9619035720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9456396102905</t>
+    <t xml:space="preserve">10.9619045257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9456405639648</t>
   </si>
   <si>
     <t xml:space="preserve">11.2709188461304</t>
@@ -2126,10 +2126,10 @@
     <t xml:space="preserve">11.5799341201782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4172945022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3034467697144</t>
+    <t xml:space="preserve">11.4172954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3034477233887</t>
   </si>
   <si>
     <t xml:space="preserve">9.9860668182373</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">10.0836505889893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4414567947388</t>
+    <t xml:space="preserve">10.4414577484131</t>
   </si>
   <si>
     <t xml:space="preserve">10.7504730224609</t>
@@ -2147,22 +2147,22 @@
     <t xml:space="preserve">11.1570711135864</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1082782745361</t>
+    <t xml:space="preserve">11.1082801818848</t>
   </si>
   <si>
     <t xml:space="preserve">11.0269594192505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9131126403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2546558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3522396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4010305404663</t>
+    <t xml:space="preserve">10.9131116867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2546548843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3522386550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4010314941406</t>
   </si>
   <si>
     <t xml:space="preserve">11.3197107315063</t>
@@ -2171,19 +2171,19 @@
     <t xml:space="preserve">11.1733350753784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0106954574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5311412811279</t>
+    <t xml:space="preserve">11.0106964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5311422348022</t>
   </si>
   <si>
     <t xml:space="preserve">11.7751016616821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7100458145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7425737380981</t>
+    <t xml:space="preserve">11.7100448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7425727844238</t>
   </si>
   <si>
     <t xml:space="preserve">12.0190601348877</t>
@@ -2192,52 +2192,52 @@
     <t xml:space="preserve">12.3118124008179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5882978439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1979627609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8726844787598</t>
+    <t xml:space="preserve">12.5882997512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1979637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8726863861084</t>
   </si>
   <si>
     <t xml:space="preserve">12.00279712677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8076295852661</t>
+    <t xml:space="preserve">11.8076305389404</t>
   </si>
   <si>
     <t xml:space="preserve">11.8564214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5961990356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.954005241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9865322113037</t>
+    <t xml:space="preserve">11.5961971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9540033340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9865312576294</t>
   </si>
   <si>
     <t xml:space="preserve">12.100380897522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1816997528076</t>
+    <t xml:space="preserve">12.1817007064819</t>
   </si>
   <si>
     <t xml:space="preserve">12.1166439056396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2792835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4093952178955</t>
+    <t xml:space="preserve">12.2792854309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4093961715698</t>
   </si>
   <si>
     <t xml:space="preserve">12.5069789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4581880569458</t>
+    <t xml:space="preserve">12.4581871032715</t>
   </si>
   <si>
     <t xml:space="preserve">12.4907150268555</t>
@@ -2255,19 +2255,19 @@
     <t xml:space="preserve">12.8647861480713</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7997303009033</t>
+    <t xml:space="preserve">12.799729347229</t>
   </si>
   <si>
     <t xml:space="preserve">12.6370916366577</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8810501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1738023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2713842391968</t>
+    <t xml:space="preserve">12.8810510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1738014221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2713851928711</t>
   </si>
   <si>
     <t xml:space="preserve">13.3527050018311</t>
@@ -2282,40 +2282,40 @@
     <t xml:space="preserve">14.052056312561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2309579849243</t>
+    <t xml:space="preserve">14.2309598922729</t>
   </si>
   <si>
     <t xml:space="preserve">14.2634878158569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2146949768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9056787490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6129283905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8080940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8894157409668</t>
+    <t xml:space="preserve">14.2146940231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9056797027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6129274368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8080959320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8894147872925</t>
   </si>
   <si>
     <t xml:space="preserve">13.6454563140869</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8406229019165</t>
+    <t xml:space="preserve">13.8406248092651</t>
   </si>
   <si>
     <t xml:space="preserve">13.7918310165405</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0032615661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9544696807861</t>
+    <t xml:space="preserve">14.0032625198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9544706344604</t>
   </si>
   <si>
     <t xml:space="preserve">14.3448057174683</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">14.1496391296387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2472229003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4749174118042</t>
+    <t xml:space="preserve">14.2472219467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4749164581299</t>
   </si>
   <si>
     <t xml:space="preserve">14.557915687561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1927223205566</t>
+    <t xml:space="preserve">14.192723274231</t>
   </si>
   <si>
     <t xml:space="preserve">14.1595239639282</t>
@@ -2342,16 +2342,16 @@
     <t xml:space="preserve">14.1429243087769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2757225036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2923212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.375319480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1097240447998</t>
+    <t xml:space="preserve">14.2757215499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2923192977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3753185272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1097249984741</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425212860107</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">13.8109292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3089189529419</t>
+    <t xml:space="preserve">14.3089208602905</t>
   </si>
   <si>
     <t xml:space="preserve">14.05992603302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0101251602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9769258499146</t>
+    <t xml:space="preserve">14.0101261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9769268035889</t>
   </si>
   <si>
     <t xml:space="preserve">14.0433263778687</t>
@@ -2387,13 +2387,13 @@
     <t xml:space="preserve">14.3255205154419</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2259216308594</t>
+    <t xml:space="preserve">14.2259206771851</t>
   </si>
   <si>
     <t xml:space="preserve">14.3421211242676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1761236190796</t>
+    <t xml:space="preserve">14.1761226654053</t>
   </si>
   <si>
     <t xml:space="preserve">13.9437265396118</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">13.9603271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3587188720703</t>
+    <t xml:space="preserve">14.358717918396</t>
   </si>
   <si>
     <t xml:space="preserve">14.2591228485107</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">14.5081157684326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.524715423584</t>
+    <t xml:space="preserve">14.5247173309326</t>
   </si>
   <si>
     <t xml:space="preserve">14.0267248153687</t>
@@ -2426,34 +2426,34 @@
     <t xml:space="preserve">14.7737102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6907119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7405118942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9397077560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1057062149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3214998245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1721048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8899097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.371298789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7032918930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5372953414917</t>
+    <t xml:space="preserve">14.6907138824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7405128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9397087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1057052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3214988708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1721029281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.889910697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3712997436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.703293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.537296295166</t>
   </si>
   <si>
     <t xml:space="preserve">15.387900352478</t>
@@ -2462,22 +2462,22 @@
     <t xml:space="preserve">15.2883014678955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2717008590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0725059509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2219018936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1223020553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9895076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.85671043396</t>
+    <t xml:space="preserve">15.2717018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0725049972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2219038009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1223030090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9895067214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567085266113</t>
   </si>
   <si>
     <t xml:space="preserve">14.8235101699829</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">14.7903108596802</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1389045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9729099273682</t>
+    <t xml:space="preserve">15.1389055252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9729089736938</t>
   </si>
   <si>
     <t xml:space="preserve">14.873309135437</t>
@@ -2498,46 +2498,46 @@
     <t xml:space="preserve">14.8069105148315</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8607292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6947317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7113332748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4417171478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5745134353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.541316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4251194000244</t>
+    <t xml:space="preserve">13.8607301712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.711332321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4417181015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5745153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5413160324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4251165390015</t>
   </si>
   <si>
     <t xml:space="preserve">14.4085187911987</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3919191360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4708976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2053022384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0227079391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4915151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8275299072266</t>
+    <t xml:space="preserve">14.3919200897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4708986282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.205304145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4915161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8275308609009</t>
   </si>
   <si>
     <t xml:space="preserve">13.7777318954468</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">13.6449337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445316314697</t>
+    <t xml:space="preserve">13.7445306777954</t>
   </si>
   <si>
     <t xml:space="preserve">13.5287351608276</t>
@@ -2555,10 +2555,10 @@
     <t xml:space="preserve">13.5619354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4125385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1137437820435</t>
+    <t xml:space="preserve">13.4125375747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1137447357178</t>
   </si>
   <si>
     <t xml:space="preserve">13.2797403335571</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">13.6117334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1303434371948</t>
+    <t xml:space="preserve">13.1303424835205</t>
   </si>
   <si>
     <t xml:space="preserve">13.3295392990112</t>
@@ -2585,16 +2585,16 @@
     <t xml:space="preserve">13.4955368041992</t>
   </si>
   <si>
-    <t xml:space="preserve">13.080545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3129396438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.196741104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7983503341675</t>
+    <t xml:space="preserve">13.0805444717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3129405975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1967420578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7983493804932</t>
   </si>
   <si>
     <t xml:space="preserve">12.4497566223145</t>
@@ -2603,13 +2603,13 @@
     <t xml:space="preserve">12.3003597259521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7153511047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4331560134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5991544723511</t>
+    <t xml:space="preserve">12.7153520584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4331569671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5991535186768</t>
   </si>
   <si>
     <t xml:space="preserve">12.3335590362549</t>
@@ -2618,19 +2618,19 @@
     <t xml:space="preserve">12.3501586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0679636001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8521680831909</t>
+    <t xml:space="preserve">12.067964553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8521671295166</t>
   </si>
   <si>
     <t xml:space="preserve">11.6695728302002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0845651626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8189687728882</t>
+    <t xml:space="preserve">12.0845642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8189697265625</t>
   </si>
   <si>
     <t xml:space="preserve">11.6031723022461</t>
@@ -2642,28 +2642,28 @@
     <t xml:space="preserve">11.7857694625854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5367746353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3209800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1715822219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.221381187439</t>
+    <t xml:space="preserve">11.5367755889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3209781646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1715812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2213821411133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8395881652832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2088003158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6735906600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6237926483154</t>
+    <t xml:space="preserve">10.2088012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6735916137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6237936019897</t>
   </si>
   <si>
     <t xml:space="preserve">10.258599281311</t>
@@ -2675,25 +2675,25 @@
     <t xml:space="preserve">9.97640514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54481315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56141376495361</t>
+    <t xml:space="preserve">9.54481410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5614128112793</t>
   </si>
   <si>
     <t xml:space="preserve">9.36221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6278133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32901763916016</t>
+    <t xml:space="preserve">9.62781143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32901859283447</t>
   </si>
   <si>
     <t xml:space="preserve">9.52821445465088</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0096054077148</t>
+    <t xml:space="preserve">10.0096044540405</t>
   </si>
   <si>
     <t xml:space="preserve">9.39541625976562</t>
@@ -2717,34 +2717,34 @@
     <t xml:space="preserve">10.1092023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1424007415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0594024658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86020755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89340591430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69421195983887</t>
+    <t xml:space="preserve">10.1424026489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0594034194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86020851135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89340686798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69421005249023</t>
   </si>
   <si>
     <t xml:space="preserve">9.61121273040771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17962074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27921962738037</t>
+    <t xml:space="preserve">9.17962169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27921867370605</t>
   </si>
   <si>
     <t xml:space="preserve">9.37881660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19622039794922</t>
+    <t xml:space="preserve">9.19622135162354</t>
   </si>
   <si>
     <t xml:space="preserve">9.29581737518311</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">9.12982177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42861461639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77720928192139</t>
+    <t xml:space="preserve">9.42861557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77720832824707</t>
   </si>
   <si>
     <t xml:space="preserve">9.64441108703613</t>
@@ -2765,13 +2765,13 @@
     <t xml:space="preserve">10.0262041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5407943725586</t>
+    <t xml:space="preserve">10.5407934188843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4577960968018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.076003074646</t>
+    <t xml:space="preserve">10.0760040283203</t>
   </si>
   <si>
     <t xml:space="preserve">9.92660617828369</t>
@@ -2780,37 +2780,37 @@
     <t xml:space="preserve">9.66899490356445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70334434509277</t>
+    <t xml:space="preserve">9.70334339141846</t>
   </si>
   <si>
     <t xml:space="preserve">9.7205171585083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0639991760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0983476638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2529134750366</t>
+    <t xml:space="preserve">10.0639982223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0983467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2529125213623</t>
   </si>
   <si>
     <t xml:space="preserve">9.85791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0811719894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3559579849243</t>
+    <t xml:space="preserve">10.0811729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.35595703125</t>
   </si>
   <si>
     <t xml:space="preserve">10.2700872421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6479158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7681350708008</t>
+    <t xml:space="preserve">10.6479167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7681341171265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9570503234863</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">11.0600938796997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1803121566772</t>
+    <t xml:space="preserve">11.1803131103516</t>
   </si>
   <si>
     <t xml:space="preserve">11.0944423675537</t>
@@ -2834,16 +2834,16 @@
     <t xml:space="preserve">10.9742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.991397857666</t>
+    <t xml:space="preserve">10.9913988113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.0296506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0124769210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.390305519104</t>
+    <t xml:space="preserve">10.0124759674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3903064727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1498689651489</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">10.1326951980591</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97812747955322</t>
+    <t xml:space="preserve">9.97812843322754</t>
   </si>
   <si>
     <t xml:space="preserve">9.87508392333984</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">10.2872610092163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2013921737671</t>
+    <t xml:space="preserve">10.2013912200928</t>
   </si>
   <si>
     <t xml:space="preserve">10.3044357299805</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">10.1842164993286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0468254089355</t>
+    <t xml:space="preserve">10.0468244552612</t>
   </si>
   <si>
     <t xml:space="preserve">10.5620460510254</t>
@@ -2885,16 +2885,16 @@
     <t xml:space="preserve">10.424654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7166128158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.459002494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5105237960815</t>
+    <t xml:space="preserve">10.4418287277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5105228424072</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509613037109</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">10.6822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4933500289917</t>
+    <t xml:space="preserve">10.493350982666</t>
   </si>
   <si>
     <t xml:space="preserve">10.1155204772949</t>
@@ -2915,10 +2915,10 @@
     <t xml:space="preserve">9.61747264862061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37703704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51442813873291</t>
+    <t xml:space="preserve">9.37703609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51442909240723</t>
   </si>
   <si>
     <t xml:space="preserve">9.63464736938477</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">9.25681781768799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46290683746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0850772857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54877758026123</t>
+    <t xml:space="preserve">9.4629077911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08507633209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54877662658691</t>
   </si>
   <si>
     <t xml:space="preserve">9.56595039367676</t>
@@ -2966,19 +2966,19 @@
     <t xml:space="preserve">9.65182113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82356071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3387832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5963945388794</t>
+    <t xml:space="preserve">9.823561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3387842178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5963954925537</t>
   </si>
   <si>
     <t xml:space="preserve">10.8540058135986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4550981521606</t>
+    <t xml:space="preserve">11.4550971984863</t>
   </si>
   <si>
     <t xml:space="preserve">11.2661828994751</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">11.0429201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8883533477783</t>
+    <t xml:space="preserve">10.8883543014526</t>
   </si>
   <si>
     <t xml:space="preserve">10.9398756027222</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">10.8196573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8024835586548</t>
+    <t xml:space="preserve">10.8024826049805</t>
   </si>
   <si>
     <t xml:space="preserve">11.3692274093628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4379224777222</t>
+    <t xml:space="preserve">11.4379234313965</t>
   </si>
   <si>
     <t xml:space="preserve">12.0733642578125</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">12.5027151107788</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2966260910034</t>
+    <t xml:space="preserve">12.2966251373291</t>
   </si>
   <si>
     <t xml:space="preserve">12.0561895370483</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">11.7470560073853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7127094268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9703197479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9359703063965</t>
+    <t xml:space="preserve">11.7127084732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9703187942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9359712600708</t>
   </si>
   <si>
     <t xml:space="preserve">12.0046663284302</t>
@@ -3041,28 +3041,28 @@
     <t xml:space="preserve">11.8157529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2279300689697</t>
+    <t xml:space="preserve">12.227931022644</t>
   </si>
   <si>
     <t xml:space="preserve">12.3653221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4340190887451</t>
+    <t xml:space="preserve">12.4340181350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.3996696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3137998580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5198888778687</t>
+    <t xml:space="preserve">12.3138008117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.519889831543</t>
   </si>
   <si>
     <t xml:space="preserve">12.485541343689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6401071548462</t>
+    <t xml:space="preserve">12.6401081085205</t>
   </si>
   <si>
     <t xml:space="preserve">12.2451038360596</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">12.1764087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1592330932617</t>
+    <t xml:space="preserve">12.159234046936</t>
   </si>
   <si>
     <t xml:space="preserve">12.1077117919922</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">12.9148921966553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0694589614868</t>
+    <t xml:space="preserve">13.0694599151611</t>
   </si>
   <si>
     <t xml:space="preserve">13.1038074493408</t>
@@ -3107,58 +3107,58 @@
     <t xml:space="preserve">13.1896772384644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6705513000488</t>
+    <t xml:space="preserve">13.6705503463745</t>
   </si>
   <si>
     <t xml:space="preserve">13.3442440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6362037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6018543243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.550332069397</t>
+    <t xml:space="preserve">13.6362028121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6018552780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5503330230713</t>
   </si>
   <si>
     <t xml:space="preserve">13.5675067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4644632339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3957653045654</t>
+    <t xml:space="preserve">13.4644622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3957672119141</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.619029045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0827283859253</t>
+    <t xml:space="preserve">13.6190280914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.082727432251</t>
   </si>
   <si>
     <t xml:space="preserve">13.6877250671387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7048988342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7220735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8766403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6151237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7353429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6494722366333</t>
+    <t xml:space="preserve">13.7048997879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7220726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8766393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6151247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7353420257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6494731903076</t>
   </si>
   <si>
     <t xml:space="preserve">14.8040390014648</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">14.6838207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7868642807007</t>
+    <t xml:space="preserve">14.7868633270264</t>
   </si>
   <si>
     <t xml:space="preserve">14.7181673049927</t>
@@ -3179,28 +3179,28 @@
     <t xml:space="preserve">15.0616502761841</t>
   </si>
   <si>
-    <t xml:space="preserve">15.387957572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1990423202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2505664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818685531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.216215133667</t>
+    <t xml:space="preserve">15.3879566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2505645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2162160873413</t>
   </si>
   <si>
     <t xml:space="preserve">14.9757795333862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9242553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4262094497681</t>
+    <t xml:space="preserve">14.9242563247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4262084960938</t>
   </si>
   <si>
     <t xml:space="preserve">14.3918619155884</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">14.9586057662964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5464296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1131706237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1303462982178</t>
+    <t xml:space="preserve">14.5464286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1131715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1303472518921</t>
   </si>
   <si>
     <t xml:space="preserve">14.9929523468018</t>
@@ -3224,34 +3224,34 @@
     <t xml:space="preserve">15.2677392959595</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4223041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9031801223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9375267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1436138153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.851655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547004699707</t>
+    <t xml:space="preserve">15.4223051071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9031782150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9375276565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1436157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8516550064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9546995162964</t>
   </si>
   <si>
     <t xml:space="preserve">15.7829599380493</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7142629623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5253486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5596990585327</t>
+    <t xml:space="preserve">15.7142639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5253496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5596981048584</t>
   </si>
   <si>
     <t xml:space="preserve">14.8383884429932</t>
@@ -3260,34 +3260,34 @@
     <t xml:space="preserve">14.4605579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3059902191162</t>
+    <t xml:space="preserve">14.3059921264648</t>
   </si>
   <si>
     <t xml:space="preserve">14.2888164520264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5120782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6323003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7009954452515</t>
+    <t xml:space="preserve">14.5120792388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6322994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7009963989258</t>
   </si>
   <si>
     <t xml:space="preserve">14.5807752609253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5292549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3746871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1431255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2678136825562</t>
+    <t xml:space="preserve">14.5292539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3746862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1431245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2678127288818</t>
   </si>
   <si>
     <t xml:space="preserve">14.321249961853</t>
@@ -3299,10 +3299,10 @@
     <t xml:space="preserve">14.6774997711182</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6062498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0540618896484</t>
+    <t xml:space="preserve">14.6062488555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0540628433228</t>
   </si>
   <si>
     <t xml:space="preserve">14.0362501144409</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">14.0184373855591</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0006256103516</t>
+    <t xml:space="preserve">14.0006246566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.733437538147</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">13.875937461853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2856254577637</t>
+    <t xml:space="preserve">14.285626411438</t>
   </si>
   <si>
     <t xml:space="preserve">14.0896873474121</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">14.1609373092651</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1253118515015</t>
+    <t xml:space="preserve">14.1253128051758</t>
   </si>
   <si>
     <t xml:space="preserve">14.4459371566772</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">14.178750038147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9828119277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9293756484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6978130340576</t>
+    <t xml:space="preserve">13.9828128814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9293746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6978120803833</t>
   </si>
   <si>
     <t xml:space="preserve">13.6799993515015</t>
@@ -3365,16 +3365,16 @@
     <t xml:space="preserve">13.5731248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8403129577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8581247329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9115629196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4840621948242</t>
+    <t xml:space="preserve">13.8403120040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8581256866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9115619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4840631484985</t>
   </si>
   <si>
     <t xml:space="preserve">13.1278123855591</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">13.8046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7690629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8225002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3034372329712</t>
+    <t xml:space="preserve">13.7690620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8225011825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3034362792969</t>
   </si>
   <si>
     <t xml:space="preserve">14.3924999237061</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">14.624062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4993753433228</t>
+    <t xml:space="preserve">14.4993762969971</t>
   </si>
   <si>
     <t xml:space="preserve">14.5349998474121</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">14.25</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0718755722046</t>
+    <t xml:space="preserve">14.0718746185303</t>
   </si>
   <si>
     <t xml:space="preserve">13.359375</t>
@@ -3428,22 +3428,22 @@
     <t xml:space="preserve">13.5018749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5196876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2321863174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6265630722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812496185303</t>
+    <t xml:space="preserve">13.5196886062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2321872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6265621185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812505722046</t>
   </si>
   <si>
     <t xml:space="preserve">13.0565624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1099996566772</t>
+    <t xml:space="preserve">13.1100006103516</t>
   </si>
   <si>
     <t xml:space="preserve">12.842812538147</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">12.8249998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7181253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221881866455</t>
+    <t xml:space="preserve">12.7181243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221872329712</t>
   </si>
   <si>
     <t xml:space="preserve">12.397500038147</t>
@@ -3476,25 +3476,25 @@
     <t xml:space="preserve">12.4865627288818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2906255722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2193756103516</t>
+    <t xml:space="preserve">12.2906246185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2193746566772</t>
   </si>
   <si>
     <t xml:space="preserve">12.2550001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1481256484985</t>
+    <t xml:space="preserve">12.1481246948242</t>
   </si>
   <si>
     <t xml:space="preserve">12.1659374237061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1303119659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165630340576</t>
+    <t xml:space="preserve">12.1303129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165620803833</t>
   </si>
   <si>
     <t xml:space="preserve">11.578125</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">11.3287506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2931261062622</t>
+    <t xml:space="preserve">11.2931251525879</t>
   </si>
   <si>
     <t xml:space="preserve">11.1328125</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">10.9012498855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9190635681152</t>
+    <t xml:space="preserve">10.9190626144409</t>
   </si>
   <si>
     <t xml:space="preserve">11.061562538147</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">11.0971879959106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1684379577637</t>
+    <t xml:space="preserve">11.1684370040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.204062461853</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">11.4534368515015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8631238937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0768756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453130722046</t>
+    <t xml:space="preserve">11.8631248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0768747329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453121185303</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809375762939</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">11.9878120422363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2015619277954</t>
+    <t xml:space="preserve">12.2015628814697</t>
   </si>
   <si>
     <t xml:space="preserve">12.6468753814697</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">12.7003126144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3618745803833</t>
+    <t xml:space="preserve">12.3618755340576</t>
   </si>
   <si>
     <t xml:space="preserve">12.3440628051758</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">12.094687461853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0590620040894</t>
+    <t xml:space="preserve">12.0590629577637</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056247711182</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">11.4178123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4356250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7384376525879</t>
+    <t xml:space="preserve">11.4356260299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7384386062622</t>
   </si>
   <si>
     <t xml:space="preserve">11.7562494277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5959386825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274993896484</t>
+    <t xml:space="preserve">11.5959377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8275003433228</t>
   </si>
   <si>
     <t xml:space="preserve">11.7206249237061</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">11.2396869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5425004959106</t>
+    <t xml:space="preserve">11.5424995422363</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028131484985</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">11.9700002670288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5246877670288</t>
+    <t xml:space="preserve">11.5246868133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.9724998474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1149988174438</t>
+    <t xml:space="preserve">11.1149997711182</t>
   </si>
   <si>
     <t xml:space="preserve">11.3382139205933</t>
@@ -4356,6 +4356,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.80000019073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51000022888184</t>
   </si>
 </sst>
 </file>
@@ -69356,7 +69359,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6496180556</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>65088</v>
@@ -69377,6 +69380,32 @@
         <v>1447</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6523611111</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>234954</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>7.84999990463257</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>7.46000003814697</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>7.84999990463257</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>7.51000022888184</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="1454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="1455">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,328 +44,328 @@
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93978953361511</t>
+    <t xml:space="preserve">4.02447938919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93978881835938</t>
   </si>
   <si>
     <t xml:space="preserve">3.82799816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78057098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75685811042786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74330735206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80089640617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040886878967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571853637695</t>
+    <t xml:space="preserve">3.78057193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943188667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7568576335907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74330830574036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80089712142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040815353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571782112122</t>
   </si>
   <si>
     <t xml:space="preserve">3.66539263725281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56376481056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65184235572815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72636985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70265650749207</t>
+    <t xml:space="preserve">3.56376457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65184211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72636938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70265626907349</t>
   </si>
   <si>
     <t xml:space="preserve">3.65861749649048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69249320030212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74669551849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5976402759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59086537361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5840904712677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49601197242737</t>
+    <t xml:space="preserve">3.6924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74669599533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59764075279236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59086513519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58408999443054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49601221084595</t>
   </si>
   <si>
     <t xml:space="preserve">3.46213626861572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51633787155151</t>
+    <t xml:space="preserve">3.51633810997009</t>
   </si>
   <si>
     <t xml:space="preserve">3.38760900497437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40793490409851</t>
+    <t xml:space="preserve">3.40793418884277</t>
   </si>
   <si>
     <t xml:space="preserve">3.50956273078918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55698943138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56715202331543</t>
+    <t xml:space="preserve">3.55698871612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56715178489685</t>
   </si>
   <si>
     <t xml:space="preserve">3.61119103431702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57731509208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54682683944702</t>
+    <t xml:space="preserve">3.57731556892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54682636260986</t>
   </si>
   <si>
     <t xml:space="preserve">3.52650094032288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50278735160828</t>
+    <t xml:space="preserve">3.50278759002686</t>
   </si>
   <si>
     <t xml:space="preserve">3.5603768825531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58070230484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60102844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54343867301941</t>
+    <t xml:space="preserve">3.58070254325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60102820396423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54343938827515</t>
   </si>
   <si>
     <t xml:space="preserve">3.57053995132446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6450674533844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78734707832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84154844284058</t>
+    <t xml:space="preserve">3.64506721496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78734660148621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.841548204422</t>
   </si>
   <si>
     <t xml:space="preserve">3.8652617931366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8517107963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92962622642517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93640089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607642173767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9025251865387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89575052261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285108566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90930032730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97027730941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87881207466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85848665237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94317698478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89913749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94656419754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95672726631165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9635021686554</t>
+    <t xml:space="preserve">3.85171127319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92962646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9364013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607570648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90252590179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89574980735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285084724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90930080413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9702775478363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87881231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85848617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94317650794983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89913773536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94656443595886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95672702789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96350193023682</t>
   </si>
   <si>
     <t xml:space="preserve">3.91268825531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9736647605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91946339607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87203645706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8870484828949</t>
+    <t xml:space="preserve">3.97366452217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91946291923523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8720371723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88704752922058</t>
   </si>
   <si>
     <t xml:space="preserve">3.87291359901428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85877895355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83757615089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86231255531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87644648551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89411592483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90118193626404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058184623718</t>
+    <t xml:space="preserve">3.85877871513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83757638931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86231231689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87644720077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89411568641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90118336677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89058208465576</t>
   </si>
   <si>
     <t xml:space="preserve">3.94358730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95418763160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96125555038452</t>
+    <t xml:space="preserve">3.95418810844421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96125483512878</t>
   </si>
   <si>
     <t xml:space="preserve">4.01426029205322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02486181259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08846807479858</t>
+    <t xml:space="preserve">4.02486085891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08846712112427</t>
   </si>
   <si>
     <t xml:space="preserve">4.05666446685791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03899574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9930579662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00719261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97539043426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97185659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80224013328552</t>
+    <t xml:space="preserve">4.03899669647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305844306946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00719308853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97538995742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97185707092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80223989486694</t>
   </si>
   <si>
     <t xml:space="preserve">3.78103709220886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75630211830139</t>
+    <t xml:space="preserve">3.75630164146423</t>
   </si>
   <si>
     <t xml:space="preserve">3.74923419952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90471649169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92238473892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065474510193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03546237945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75983595848083</t>
+    <t xml:space="preserve">3.90471601486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92238521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065450668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03546333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75983548164368</t>
   </si>
   <si>
     <t xml:space="preserve">3.80930709838867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83050894737244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86937952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82344150543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80577349662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84111022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8163743019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8658459186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89764881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93651914596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9082498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91531825065613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.978924036026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00012588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02132749557495</t>
+    <t xml:space="preserve">3.83050918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86937999725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82344198226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80577397346497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84110999107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81637477874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86584544181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89764833450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93651962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90825057029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91531753540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97892379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00012540817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02132797241211</t>
   </si>
   <si>
     <t xml:space="preserve">3.95772123336792</t>
@@ -377,28 +377,28 @@
     <t xml:space="preserve">3.81284022331238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77043676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690292358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76336860656738</t>
+    <t xml:space="preserve">3.77043604850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690268516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76336884498596</t>
   </si>
   <si>
     <t xml:space="preserve">3.74570083618164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72449851036072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77397012710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78810501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81990766525269</t>
+    <t xml:space="preserve">3.72449898719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77397084236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78810477256775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81990790367126</t>
   </si>
   <si>
     <t xml:space="preserve">3.72803211212158</t>
@@ -407,70 +407,70 @@
     <t xml:space="preserve">3.73863363265991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73156571388245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73509955406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65382480621338</t>
+    <t xml:space="preserve">3.73156666755676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73509979248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65382528305054</t>
   </si>
   <si>
     <t xml:space="preserve">3.63969039916992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66089224815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61848783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61142086982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62555575370789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61495471000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64675784111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74216723442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91885137557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98599100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99659252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87998008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88351392745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79517197608948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82697606086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79163837432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8481776714325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71036410331726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85524463653564</t>
+    <t xml:space="preserve">3.66089200973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.618488073349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61142110824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62555599212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61495423316956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64675760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7421669960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9188506603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98599123954773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99659204483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87998080253601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88351440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79517269134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82697558403015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79163861274719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84817695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71036386489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85524415969849</t>
   </si>
   <si>
     <t xml:space="preserve">4.03192901611328</t>
@@ -479,31 +479,31 @@
     <t xml:space="preserve">4.04253005981445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08493423461914</t>
+    <t xml:space="preserve">4.08493375778198</t>
   </si>
   <si>
     <t xml:space="preserve">4.09906911849976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05313110351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04959678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09200191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10966968536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07786655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07433271408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04606294631958</t>
+    <t xml:space="preserve">4.05313062667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04959774017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09200143814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10967016220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07786703109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07433319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04606342315674</t>
   </si>
   <si>
     <t xml:space="preserve">4.0637321472168</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">4.10613632202148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10260200500488</t>
+    <t xml:space="preserve">4.10260248184204</t>
   </si>
   <si>
     <t xml:space="preserve">4.13440561294556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12733793258667</t>
+    <t xml:space="preserve">4.12733840942383</t>
   </si>
   <si>
     <t xml:space="preserve">4.16974258422852</t>
@@ -527,28 +527,28 @@
     <t xml:space="preserve">4.18387699127197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15914106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24041509628296</t>
+    <t xml:space="preserve">4.15914154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24041557312012</t>
   </si>
   <si>
     <t xml:space="preserve">4.21568059921265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27575302124023</t>
+    <t xml:space="preserve">4.27575349807739</t>
   </si>
   <si>
     <t xml:space="preserve">4.34642648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36762809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35349416732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31108856201172</t>
+    <t xml:space="preserve">4.36762762069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35349369049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31108903884888</t>
   </si>
   <si>
     <t xml:space="preserve">4.30402183532715</t>
@@ -557,28 +557,28 @@
     <t xml:space="preserve">4.38176298141479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50897550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72806358337402</t>
+    <t xml:space="preserve">4.50897598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72806406021118</t>
   </si>
   <si>
     <t xml:space="preserve">4.91181516647339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94715213775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19450950622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2227783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22984600067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22631216049194</t>
+    <t xml:space="preserve">4.94715166091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19450902938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22277927398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22984647750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22631311416626</t>
   </si>
   <si>
     <t xml:space="preserve">5.09203243255615</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.08496570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11676836013794</t>
+    <t xml:space="preserve">5.1167688369751</t>
   </si>
   <si>
     <t xml:space="preserve">5.10616731643677</t>
@@ -599,34 +599,34 @@
     <t xml:space="preserve">5.15210580825806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15917253494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17330741882324</t>
+    <t xml:space="preserve">5.15917301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1733078956604</t>
   </si>
   <si>
     <t xml:space="preserve">5.19097566604614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14503812789917</t>
+    <t xml:space="preserve">5.14503860473633</t>
   </si>
   <si>
     <t xml:space="preserve">5.13090324401855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24751424789429</t>
+    <t xml:space="preserve">5.24751472473145</t>
   </si>
   <si>
     <t xml:space="preserve">5.26871633529663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59734869003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5125412940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35705852508545</t>
+    <t xml:space="preserve">5.59734916687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51254081726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35705900192261</t>
   </si>
   <si>
     <t xml:space="preserve">5.47720384597778</t>
@@ -641,25 +641,25 @@
     <t xml:space="preserve">5.53020906448364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61199808120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65216159820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6886739730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62295150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.619300365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59739208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42213106155396</t>
+    <t xml:space="preserve">5.61199760437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65216112136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68867349624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62295055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61930084228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5973916053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42213153839111</t>
   </si>
   <si>
     <t xml:space="preserve">5.41848039627075</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">5.55722808837891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45499277114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36736297607422</t>
+    <t xml:space="preserve">5.45499229431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3673620223999</t>
   </si>
   <si>
     <t xml:space="preserve">5.37466526031494</t>
@@ -695,55 +695,55 @@
     <t xml:space="preserve">5.40387535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47690105438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4476900100708</t>
+    <t xml:space="preserve">5.47690057754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44769048690796</t>
   </si>
   <si>
     <t xml:space="preserve">5.48055171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49515724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54627466201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60104322433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41117763519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51341342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54992532730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45134210586548</t>
+    <t xml:space="preserve">5.49515676498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54627418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60104370117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41117715835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5134129524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54992580413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45134162902832</t>
   </si>
   <si>
     <t xml:space="preserve">5.61564826965332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50611019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34545564651489</t>
+    <t xml:space="preserve">5.50611066818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34545516967773</t>
   </si>
   <si>
     <t xml:space="preserve">5.37101411819458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31259346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.287034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15558958053589</t>
+    <t xml:space="preserve">5.31259298324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28703451156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15558910369873</t>
   </si>
   <si>
     <t xml:space="preserve">5.12637901306152</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">5.31989574432373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14098310470581</t>
+    <t xml:space="preserve">5.14098405838013</t>
   </si>
   <si>
     <t xml:space="preserve">5.40752649307251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38926982879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37831544876099</t>
+    <t xml:space="preserve">5.38927030563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37831592559814</t>
   </si>
   <si>
     <t xml:space="preserve">5.24321937561035</t>
@@ -776,22 +776,22 @@
     <t xml:space="preserve">5.41482877731323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42578220367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44038724899292</t>
+    <t xml:space="preserve">5.42578268051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44038820266724</t>
   </si>
   <si>
     <t xml:space="preserve">5.48420333862305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3527569770813</t>
+    <t xml:space="preserve">5.35275745391846</t>
   </si>
   <si>
     <t xml:space="preserve">5.48785448074341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50245952606201</t>
+    <t xml:space="preserve">5.50245904922485</t>
   </si>
   <si>
     <t xml:space="preserve">5.57183361053467</t>
@@ -800,61 +800,61 @@
     <t xml:space="preserve">5.57913541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56453084945679</t>
+    <t xml:space="preserve">5.56453037261963</t>
   </si>
   <si>
     <t xml:space="preserve">5.52071523666382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53897190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65581274032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58643865585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57548475265503</t>
+    <t xml:space="preserve">5.5389723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65581226348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58643817901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57548522949219</t>
   </si>
   <si>
     <t xml:space="preserve">5.50976228713989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5316686630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60469532012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59008979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75804805755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79456043243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92965745925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94426345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99903154373169</t>
+    <t xml:space="preserve">5.53166961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60469436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59009027481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75804758071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79456090927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92965698242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94426298141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99903202056885</t>
   </si>
   <si>
     <t xml:space="preserve">5.93696022033691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98807716369629</t>
+    <t xml:space="preserve">5.98807764053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.83107328414917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88584232330322</t>
+    <t xml:space="preserve">5.88584280014038</t>
   </si>
   <si>
     <t xml:space="preserve">5.83472394943237</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">5.91140127182007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83837556838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84202766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87123775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78360748291016</t>
+    <t xml:space="preserve">5.83837604522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84202671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87123680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.783607006073</t>
   </si>
   <si>
     <t xml:space="preserve">5.8529806137085</t>
@@ -887,28 +887,28 @@
     <t xml:space="preserve">5.7032790184021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82742214202881</t>
+    <t xml:space="preserve">5.82742166519165</t>
   </si>
   <si>
     <t xml:space="preserve">5.86393451690674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75439739227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72883796691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68502187728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66676664352417</t>
+    <t xml:space="preserve">5.75439691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72883749008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68502283096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66676616668701</t>
   </si>
   <si>
     <t xml:space="preserve">5.88949346542358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78725814819336</t>
+    <t xml:space="preserve">5.78725862503052</t>
   </si>
   <si>
     <t xml:space="preserve">5.77995586395264</t>
@@ -917,16 +917,16 @@
     <t xml:space="preserve">5.73614025115967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6083459854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63025379180908</t>
+    <t xml:space="preserve">5.60834550857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63025331497192</t>
   </si>
   <si>
     <t xml:space="preserve">5.53532123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76169967651367</t>
+    <t xml:space="preserve">5.76169919967651</t>
   </si>
   <si>
     <t xml:space="preserve">5.62660217285156</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">5.68137168884277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73979187011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76535129547119</t>
+    <t xml:space="preserve">5.73979139328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76535081863403</t>
   </si>
   <si>
     <t xml:space="preserve">5.80916595458984</t>
@@ -950,73 +950,73 @@
     <t xml:space="preserve">5.82377147674561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87853956222534</t>
+    <t xml:space="preserve">5.8785400390625</t>
   </si>
   <si>
     <t xml:space="preserve">5.82011938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90409851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92235517501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95156478881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02459096908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06110429763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00998449325562</t>
+    <t xml:space="preserve">5.90409898757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600679397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92235422134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95156526565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02459049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06110382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00998497009277</t>
   </si>
   <si>
     <t xml:space="preserve">6.09031343460083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22906112670898</t>
+    <t xml:space="preserve">6.22906160354614</t>
   </si>
   <si>
     <t xml:space="preserve">6.18524646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03189325332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03919553756714</t>
+    <t xml:space="preserve">6.03189373016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0391960144043</t>
   </si>
   <si>
     <t xml:space="preserve">6.04649782180786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2509708404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20715427398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14143085479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12682628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7982120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72518634796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96617078781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00268363952637</t>
+    <t xml:space="preserve">6.25096893310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20715379714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14143037796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12682580947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79821157455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72518682479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96617031097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00268268585205</t>
   </si>
   <si>
     <t xml:space="preserve">5.89314460754395</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">6.15603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10491800308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98077583312988</t>
+    <t xml:space="preserve">6.10491895675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98077487945557</t>
   </si>
   <si>
     <t xml:space="preserve">5.90044736862183</t>
@@ -1052,31 +1052,31 @@
     <t xml:space="preserve">6.09761619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05380010604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07570838928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08301115036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17794322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17063999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2436671257019</t>
+    <t xml:space="preserve">6.05380058288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07570743560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08300971984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17794370651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17064094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24366664886475</t>
   </si>
   <si>
     <t xml:space="preserve">6.28017950057983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38636541366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31810331344604</t>
+    <t xml:space="preserve">6.38636589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31810188293457</t>
   </si>
   <si>
     <t xml:space="preserve">6.23467016220093</t>
@@ -1085,22 +1085,22 @@
     <t xml:space="preserve">6.28017902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15882253646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27259492874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26500940322876</t>
+    <t xml:space="preserve">6.15882301330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2725944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26501035690308</t>
   </si>
   <si>
     <t xml:space="preserve">6.21191596984863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1815767288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15123796463013</t>
+    <t xml:space="preserve">6.18157720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15123748779297</t>
   </si>
   <si>
     <t xml:space="preserve">6.02988195419312</t>
@@ -1112,22 +1112,22 @@
     <t xml:space="preserve">6.25742435455322</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22708606719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24983930587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29534864425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37119579315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1891622543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1664080619812</t>
+    <t xml:space="preserve">6.22708559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24983978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29534912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37119626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18916130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16640758514404</t>
   </si>
   <si>
     <t xml:space="preserve">6.20433187484741</t>
@@ -1136,31 +1136,31 @@
     <t xml:space="preserve">6.0147123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04505109786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00712776184082</t>
+    <t xml:space="preserve">6.04505157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00712823867798</t>
   </si>
   <si>
     <t xml:space="preserve">5.98437356948853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12089824676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13606834411621</t>
+    <t xml:space="preserve">6.12089872360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13606882095337</t>
   </si>
   <si>
     <t xml:space="preserve">6.11331510543823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09056043624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96161937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08297538757324</t>
+    <t xml:space="preserve">6.09055995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96161890029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0829758644104</t>
   </si>
   <si>
     <t xml:space="preserve">6.14365386962891</t>
@@ -1169,13 +1169,13 @@
     <t xml:space="preserve">6.10572957992554</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06022119522095</t>
+    <t xml:space="preserve">6.06022071838379</t>
   </si>
   <si>
     <t xml:space="preserve">5.99954271316528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95403385162354</t>
+    <t xml:space="preserve">5.95403432846069</t>
   </si>
   <si>
     <t xml:space="preserve">5.93886470794678</t>
@@ -1187,19 +1187,19 @@
     <t xml:space="preserve">5.91611051559448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94644975662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818670272827</t>
+    <t xml:space="preserve">5.94645023345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818717956543</t>
   </si>
   <si>
     <t xml:space="preserve">6.03746700286865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02229738235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9919581413269</t>
+    <t xml:space="preserve">6.02229642868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99195861816406</t>
   </si>
   <si>
     <t xml:space="preserve">5.86301755905151</t>
@@ -1208,103 +1208,103 @@
     <t xml:space="preserve">6.07539129257202</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24225473403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63666343688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46221303939819</t>
+    <t xml:space="preserve">6.24225521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738313674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63666200637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46221399307251</t>
   </si>
   <si>
     <t xml:space="preserve">6.57598400115967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56081485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60632371902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55323028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65183258056641</t>
+    <t xml:space="preserve">6.56081533432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6063232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55323076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65183305740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.53806066513062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48496723175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61390829086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66700124740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59873867034912</t>
+    <t xml:space="preserve">6.48496770858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6139087677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66700172424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59873914718628</t>
   </si>
   <si>
     <t xml:space="preserve">6.34085702896118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39395141601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4167046546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42428970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53047609329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59115362167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54564666748047</t>
+    <t xml:space="preserve">6.39395046234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41670417785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42428922653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59115314483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54564523696899</t>
   </si>
   <si>
     <t xml:space="preserve">6.56839990615845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44704389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3484411239624</t>
+    <t xml:space="preserve">6.44704341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34844160079956</t>
   </si>
   <si>
     <t xml:space="preserve">6.21950101852417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40912055969238</t>
+    <t xml:space="preserve">6.40911960601807</t>
   </si>
   <si>
     <t xml:space="preserve">6.32568788528442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28776407241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6897554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67458629608154</t>
+    <t xml:space="preserve">6.28776359558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68975591659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67458581924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.74284934997559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75043296813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62149333953857</t>
+    <t xml:space="preserve">6.75043392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62149286270142</t>
   </si>
   <si>
     <t xml:space="preserve">6.37878036499023</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">6.46979808807373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51530694961548</t>
+    <t xml:space="preserve">6.51530742645264</t>
   </si>
   <si>
     <t xml:space="preserve">6.31051778793335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35602712631226</t>
+    <t xml:space="preserve">6.35602617263794</t>
   </si>
   <si>
     <t xml:space="preserve">6.19674682617188</t>
@@ -1331,67 +1331,67 @@
     <t xml:space="preserve">6.40153455734253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72009515762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75801944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80352735519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78835773468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73526525497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84903621673584</t>
+    <t xml:space="preserve">6.72009468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75801849365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80352687835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78835821151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73526430130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84903573989868</t>
   </si>
   <si>
     <t xml:space="preserve">6.8642053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81111192703247</t>
+    <t xml:space="preserve">6.81111097335815</t>
   </si>
   <si>
     <t xml:space="preserve">6.8414511680603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81869697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90212821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99314546585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89454412460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9400520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05382394790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10691738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15242719650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11450242996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01590013504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08416271209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04623937606812</t>
+    <t xml:space="preserve">6.81869554519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90212869644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99314594268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89454507827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94005298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05382490158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10691785812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15242624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.114501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01590061187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04623889923096</t>
   </si>
   <si>
     <t xml:space="preserve">7.09174728393555</t>
@@ -1400,88 +1400,88 @@
     <t xml:space="preserve">7.39513778686523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35721397399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34204578399658</t>
+    <t xml:space="preserve">7.35721492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34204530715942</t>
   </si>
   <si>
     <t xml:space="preserve">7.1220874786377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13725709915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1296706199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25102853775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22827386856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20551872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1979341506958</t>
+    <t xml:space="preserve">7.13725662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12967157363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25102806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22827291488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20552015304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19793462753296</t>
   </si>
   <si>
     <t xml:space="preserve">7.16759538650513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37996959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43306112289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49374103546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5392484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54683256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75162172317505</t>
+    <t xml:space="preserve">7.37996864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43306159973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49374055862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53924751281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54683303833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75162267684937</t>
   </si>
   <si>
     <t xml:space="preserve">7.79713010787964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64543581008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6909441947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57717227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45581674575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5164942741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59992647171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50890874862671</t>
+    <t xml:space="preserve">7.64543628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69094371795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57717275619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45581579208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51649522781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59992694854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50890970230103</t>
   </si>
   <si>
     <t xml:space="preserve">7.56200313568115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58475637435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55441856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47857093811035</t>
+    <t xml:space="preserve">7.58475732803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55441951751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47857046127319</t>
   </si>
   <si>
     <t xml:space="preserve">7.47098588943481</t>
@@ -1490,64 +1490,64 @@
     <t xml:space="preserve">7.4482307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70611429214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331792831421</t>
+    <t xml:space="preserve">7.70611238479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331649780273</t>
   </si>
   <si>
     <t xml:space="preserve">7.88814640045166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2522144317627</t>
+    <t xml:space="preserve">8.25221633911133</t>
   </si>
   <si>
     <t xml:space="preserve">8.61628341674805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49492645263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17636680603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41907978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11876964569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08742141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93068838119507</t>
+    <t xml:space="preserve">8.49492740631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17636775970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41908168792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1187686920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08742332458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93068885803223</t>
   </si>
   <si>
     <t xml:space="preserve">8.04040336608887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9620361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25982856750488</t>
+    <t xml:space="preserve">7.96203565597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2598295211792</t>
   </si>
   <si>
     <t xml:space="preserve">8.02472972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.867995262146</t>
+    <t xml:space="preserve">7.86799573898315</t>
   </si>
   <si>
     <t xml:space="preserve">7.7347731590271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83664894104004</t>
+    <t xml:space="preserve">7.83664989471436</t>
   </si>
   <si>
     <t xml:space="preserve">7.82097625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91501522064209</t>
+    <t xml:space="preserve">7.91501760482788</t>
   </si>
   <si>
     <t xml:space="preserve">7.97770929336548</t>
@@ -1565,19 +1565,19 @@
     <t xml:space="preserve">8.40088844299316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46358108520508</t>
+    <t xml:space="preserve">8.46358203887939</t>
   </si>
   <si>
     <t xml:space="preserve">8.6203145980835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30684757232666</t>
+    <t xml:space="preserve">8.30684852600098</t>
   </si>
   <si>
     <t xml:space="preserve">8.1657886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33819580078125</t>
+    <t xml:space="preserve">8.33819484710693</t>
   </si>
   <si>
     <t xml:space="preserve">8.21280860900879</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">8.27550315856934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36954116821289</t>
+    <t xml:space="preserve">8.36954402923584</t>
   </si>
   <si>
     <t xml:space="preserve">8.15011501312256</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">8.18146228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13444232940674</t>
+    <t xml:space="preserve">8.13444328308105</t>
   </si>
   <si>
     <t xml:space="preserve">8.22848129272461</t>
@@ -1604,55 +1604,55 @@
     <t xml:space="preserve">8.43223571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9933819770813</t>
+    <t xml:space="preserve">7.99338340759277</t>
   </si>
   <si>
     <t xml:space="preserve">8.19713592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75828218460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89934301376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82881307601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88366937637329</t>
+    <t xml:space="preserve">7.7582836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89934396743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82881259918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88366889953613</t>
   </si>
   <si>
     <t xml:space="preserve">7.81313991546631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67991542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79746532440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41656112670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80530309677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68775415420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74261093139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00905609130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94636297225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75044727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71909999847412</t>
+    <t xml:space="preserve">7.67991781234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79746580123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4165620803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8053035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68775367736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74261045455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00905704498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94636344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75044631958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71909952163696</t>
   </si>
   <si>
     <t xml:space="preserve">8.10309600830078</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">8.82406711578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37263298034668</t>
+    <t xml:space="preserve">9.372633934021</t>
   </si>
   <si>
     <t xml:space="preserve">9.60773277282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48234748840332</t>
+    <t xml:space="preserve">9.482346534729</t>
   </si>
   <si>
     <t xml:space="preserve">9.79581260681152</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">9.87417888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9995641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1562986373901</t>
+    <t xml:space="preserve">9.99956512451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1562976837158</t>
   </si>
   <si>
     <t xml:space="preserve">10.5011100769043</t>
@@ -1691,34 +1691,34 @@
     <t xml:space="preserve">10.3757238388062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5481300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2189903259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.171971321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95254516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90552425384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88985252380371</t>
+    <t xml:space="preserve">10.5481309890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2189912796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1719722747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95254421234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90552520751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88985061645508</t>
   </si>
   <si>
     <t xml:space="preserve">9.92119789123535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73311996459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76446437835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57638645172119</t>
+    <t xml:space="preserve">9.73311901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76446533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57638549804688</t>
   </si>
   <si>
     <t xml:space="preserve">9.96821784973145</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">10.0309114456177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4854373931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2503385543823</t>
+    <t xml:space="preserve">10.4854364395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2503366470337</t>
   </si>
   <si>
     <t xml:space="preserve">10.0152378082275</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">10.3600511550903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2973575592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3130302429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4384174346924</t>
+    <t xml:space="preserve">10.2973585128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3130311965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4384164810181</t>
   </si>
   <si>
     <t xml:space="preserve">10.6264963150024</t>
@@ -1757,37 +1757,37 @@
     <t xml:space="preserve">10.6578435897827</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6108236312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5951499938965</t>
+    <t xml:space="preserve">10.6108226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5951509475708</t>
   </si>
   <si>
     <t xml:space="preserve">10.5794763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6421699523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7518835067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9869823455811</t>
+    <t xml:space="preserve">10.6421709060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7518844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9869832992554</t>
   </si>
   <si>
     <t xml:space="preserve">10.9556360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1280422210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0183305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2377557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593894958496</t>
+    <t xml:space="preserve">11.1280431747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0183296203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2377548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593885421753</t>
   </si>
   <si>
     <t xml:space="preserve">11.0966958999634</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">11.1750621795654</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1123695373535</t>
+    <t xml:space="preserve">11.1123704910278</t>
   </si>
   <si>
     <t xml:space="preserve">11.0810222625732</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">10.9713096618652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7989044189453</t>
+    <t xml:space="preserve">10.7989025115967</t>
   </si>
   <si>
     <t xml:space="preserve">10.0622577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0936050415039</t>
+    <t xml:space="preserve">10.0936059951782</t>
   </si>
   <si>
     <t xml:space="preserve">9.68609809875488</t>
@@ -1823,31 +1823,31 @@
     <t xml:space="preserve">9.54503917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98079967498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54194641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31942987442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50751113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5388560295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49183797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66733360290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44790649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38521480560303</t>
+    <t xml:space="preserve">8.98080062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54194736480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31943130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50750970840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53885746002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49183702468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66733551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44790840148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38521575927734</t>
   </si>
   <si>
     <t xml:space="preserve">8.52627372741699</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">9.01214694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45099925994873</t>
+    <t xml:space="preserve">9.45100021362305</t>
   </si>
   <si>
     <t xml:space="preserve">9.10618686676025</t>
@@ -1868,16 +1868,16 @@
     <t xml:space="preserve">9.38830661773682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88676166534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87108707427979</t>
+    <t xml:space="preserve">8.88676071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87108612060547</t>
   </si>
   <si>
     <t xml:space="preserve">9.12186050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91810703277588</t>
+    <t xml:space="preserve">8.9181079864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.15320682525635</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">9.04349422454834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21589851379395</t>
+    <t xml:space="preserve">9.21590042114258</t>
   </si>
   <si>
     <t xml:space="preserve">8.96512699127197</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">9.01022911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68494987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50604724884033</t>
+    <t xml:space="preserve">8.68495178222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50604820251465</t>
   </si>
   <si>
     <t xml:space="preserve">8.70121383666992</t>
@@ -1919,28 +1919,28 @@
     <t xml:space="preserve">9.18913269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9289083480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76626873016357</t>
+    <t xml:space="preserve">8.92890930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76627063751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.71747875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97770118713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3355073928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48188304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61199569702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2625541687012</t>
+    <t xml:space="preserve">8.97770214080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33550834655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48188400268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6119966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2625532150269</t>
   </si>
   <si>
     <t xml:space="preserve">10.0673866271973</t>
@@ -1955,28 +1955,28 @@
     <t xml:space="preserve">10.2137622833252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2788171768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2300252914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95353889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88848209381104</t>
+    <t xml:space="preserve">10.2788181304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2300262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.953537940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88848304748535</t>
   </si>
   <si>
     <t xml:space="preserve">9.69331550598145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1324415206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1974973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3276100158691</t>
+    <t xml:space="preserve">10.1324424743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1974983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3276090621948</t>
   </si>
   <si>
     <t xml:space="preserve">10.2462902069092</t>
@@ -1985,13 +1985,13 @@
     <t xml:space="preserve">10.555305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8480558395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8805847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8317918777466</t>
+    <t xml:space="preserve">10.8480577468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8805837631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8317909240723</t>
   </si>
   <si>
     <t xml:space="preserve">10.7992639541626</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">10.9293746948242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6854162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.636625289917</t>
+    <t xml:space="preserve">10.685417175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6366243362427</t>
   </si>
   <si>
     <t xml:space="preserve">10.7667360305786</t>
@@ -2012,13 +2012,13 @@
     <t xml:space="preserve">10.9781675338745</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1245441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1408061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2871837615967</t>
+    <t xml:space="preserve">11.1245431900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1408081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2871828079224</t>
   </si>
   <si>
     <t xml:space="preserve">11.3847665786743</t>
@@ -2030,52 +2030,52 @@
     <t xml:space="preserve">11.4335594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498233795166</t>
+    <t xml:space="preserve">11.4498224258423</t>
   </si>
   <si>
     <t xml:space="preserve">11.4660873413086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.482349395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3359746932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2058639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2221279144287</t>
+    <t xml:space="preserve">11.4823503494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3359756469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2058629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2221269607544</t>
   </si>
   <si>
     <t xml:space="preserve">10.8643198013306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.539041519165</t>
+    <t xml:space="preserve">10.5390405654907</t>
   </si>
   <si>
     <t xml:space="preserve">10.5227766036987</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7016801834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8155288696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6040964126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7342090606689</t>
+    <t xml:space="preserve">10.701681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8155279159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.604097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7342071533203</t>
   </si>
   <si>
     <t xml:space="preserve">10.620361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.717945098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5065135955811</t>
+    <t xml:space="preserve">10.7179441452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5065126419067</t>
   </si>
   <si>
     <t xml:space="preserve">10.587833404541</t>
@@ -2084,25 +2084,25 @@
     <t xml:space="preserve">10.4577207565308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3764009475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.571569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4089298248291</t>
+    <t xml:space="preserve">10.3764019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5715684890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4089288711548</t>
   </si>
   <si>
     <t xml:space="preserve">10.8968477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0594873428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9944314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.669153213501</t>
+    <t xml:space="preserve">11.0594882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9944324493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6691522598267</t>
   </si>
   <si>
     <t xml:space="preserve">10.7830009460449</t>
@@ -2111,19 +2111,19 @@
     <t xml:space="preserve">10.9619035720825</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9456396102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2709188461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1895999908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5799341201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4172945022583</t>
+    <t xml:space="preserve">10.9456415176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2709178924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1895990371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5799331665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4172954559326</t>
   </si>
   <si>
     <t xml:space="preserve">11.3034467697144</t>
@@ -2138,28 +2138,28 @@
     <t xml:space="preserve">10.4414567947388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7504730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1570711135864</t>
+    <t xml:space="preserve">10.7504739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1570720672607</t>
   </si>
   <si>
     <t xml:space="preserve">11.1082792282104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0269594192505</t>
+    <t xml:space="preserve">11.0269584655762</t>
   </si>
   <si>
     <t xml:space="preserve">10.9131116867065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2546548843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3522396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4010305404663</t>
+    <t xml:space="preserve">11.2546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3522386550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4010314941406</t>
   </si>
   <si>
     <t xml:space="preserve">11.3197107315063</t>
@@ -2168,16 +2168,16 @@
     <t xml:space="preserve">11.1733350753784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0106954574585</t>
+    <t xml:space="preserve">11.0106964111328</t>
   </si>
   <si>
     <t xml:space="preserve">11.5311422348022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7751007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7100448608398</t>
+    <t xml:space="preserve">11.7751016616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7100458145142</t>
   </si>
   <si>
     <t xml:space="preserve">11.7425727844238</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">12.3118124008179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5882987976074</t>
+    <t xml:space="preserve">12.5882997512817</t>
   </si>
   <si>
     <t xml:space="preserve">12.1979637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8726854324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0027980804443</t>
+    <t xml:space="preserve">11.8726863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.00279712677</t>
   </si>
   <si>
     <t xml:space="preserve">11.8076295852661</t>
@@ -2207,34 +2207,34 @@
     <t xml:space="preserve">11.8564205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5961980819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.954005241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.986533164978</t>
+    <t xml:space="preserve">11.5961971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9540042877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9865322113037</t>
   </si>
   <si>
     <t xml:space="preserve">12.100380897522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1816997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1166439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2792835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4093952178955</t>
+    <t xml:space="preserve">12.1817007064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.116644859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2792844772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4093961715698</t>
   </si>
   <si>
     <t xml:space="preserve">12.5069789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4581871032715</t>
+    <t xml:space="preserve">12.4581880569458</t>
   </si>
   <si>
     <t xml:space="preserve">12.4907150268555</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">12.8973140716553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0111618041992</t>
+    <t xml:space="preserve">13.0111608505249</t>
   </si>
   <si>
     <t xml:space="preserve">12.9786338806152</t>
@@ -2252,43 +2252,43 @@
     <t xml:space="preserve">12.8647861480713</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7997312545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6370916366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8810501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1738023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2713851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3527059555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7267751693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8243598937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0520544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2309598922729</t>
+    <t xml:space="preserve">12.7997303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6370906829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8810510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1738014221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2713842391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3527050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7267742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8243589401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.052056312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.23095703125</t>
   </si>
   <si>
     <t xml:space="preserve">14.2634878158569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2146949768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9056797027588</t>
+    <t xml:space="preserve">14.2146940231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9056806564331</t>
   </si>
   <si>
     <t xml:space="preserve">13.6129274368286</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">13.8080959320068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8894147872925</t>
+    <t xml:space="preserve">13.8894157409668</t>
   </si>
   <si>
     <t xml:space="preserve">13.6454563140869</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">13.8406229019165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7918319702148</t>
+    <t xml:space="preserve">13.7918310165405</t>
   </si>
   <si>
     <t xml:space="preserve">14.0032625198364</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">13.9544715881348</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3448047637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1496391296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2472238540649</t>
+    <t xml:space="preserve">14.3448066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1496381759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2472229003906</t>
   </si>
   <si>
     <t xml:space="preserve">14.4749164581299</t>
@@ -2330,40 +2330,40 @@
     <t xml:space="preserve">14.5579166412354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1927223205566</t>
+    <t xml:space="preserve">14.192723274231</t>
   </si>
   <si>
     <t xml:space="preserve">14.1595230102539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1429233551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2757225036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.375319480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1097249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2425212860107</t>
+    <t xml:space="preserve">14.1429243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2757205963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2923192977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3753185272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1097240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2425222396851</t>
   </si>
   <si>
     <t xml:space="preserve">14.0765237808228</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2093238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9935283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8109292984009</t>
+    <t xml:space="preserve">14.209321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9935274124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8109283447266</t>
   </si>
   <si>
     <t xml:space="preserve">14.3089199066162</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">14.05992603302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0101261138916</t>
+    <t xml:space="preserve">14.0101251602173</t>
   </si>
   <si>
     <t xml:space="preserve">13.9769268035889</t>
@@ -2381,25 +2381,25 @@
     <t xml:space="preserve">14.0433263778687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3255205154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2259216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3421201705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1761226654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9437265396118</t>
+    <t xml:space="preserve">14.3255195617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2259206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3421211242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1761236190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9437274932861</t>
   </si>
   <si>
     <t xml:space="preserve">14.0931243896484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9603261947632</t>
+    <t xml:space="preserve">13.9603271484375</t>
   </si>
   <si>
     <t xml:space="preserve">14.3587188720703</t>
@@ -2408,43 +2408,43 @@
     <t xml:space="preserve">14.2591228485107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5081167221069</t>
+    <t xml:space="preserve">14.5081157684326</t>
   </si>
   <si>
     <t xml:space="preserve">14.524715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.026725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.707311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7737112045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.690712928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7405109405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9397077560425</t>
+    <t xml:space="preserve">14.0267248153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7073125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7737102508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6907138824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7405128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9397087097168</t>
   </si>
   <si>
     <t xml:space="preserve">15.1057052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3215007781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1721038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8899097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3713006973267</t>
+    <t xml:space="preserve">15.3214988708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1721048355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8899087905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3712997436523</t>
   </si>
   <si>
     <t xml:space="preserve">15.7032918930054</t>
@@ -2453,37 +2453,37 @@
     <t xml:space="preserve">15.537296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3878993988037</t>
+    <t xml:space="preserve">15.387900352478</t>
   </si>
   <si>
     <t xml:space="preserve">15.2883014678955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2717008590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0725059509277</t>
+    <t xml:space="preserve">15.2717018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0725049972534</t>
   </si>
   <si>
     <t xml:space="preserve">15.2219018936157</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1223039627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9895057678223</t>
+    <t xml:space="preserve">15.1223030090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9895067214966</t>
   </si>
   <si>
     <t xml:space="preserve">14.85671043396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8235111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7903099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1389045715332</t>
+    <t xml:space="preserve">14.8235101699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7903108596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1389055252075</t>
   </si>
   <si>
     <t xml:space="preserve">14.9729089736938</t>
@@ -2492,49 +2492,52 @@
     <t xml:space="preserve">14.873309135437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8069124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8607292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6947317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.711332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4417171478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5745143890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.541316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4251174926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4085187911987</t>
+    <t xml:space="preserve">14.8069105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8607301712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7113332748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4417181015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4749174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5745153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5413160324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4251165390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4085178375244</t>
   </si>
   <si>
     <t xml:space="preserve">14.3919191360474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4708976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2053031921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0227079391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4915170669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8275308609009</t>
+    <t xml:space="preserve">15.4708986282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2053022384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4915161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8275289535522</t>
   </si>
   <si>
     <t xml:space="preserve">13.7777318954468</t>
@@ -2543,19 +2546,19 @@
     <t xml:space="preserve">13.6449337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445316314697</t>
+    <t xml:space="preserve">13.7445306777954</t>
   </si>
   <si>
     <t xml:space="preserve">13.5287351608276</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5619344711304</t>
+    <t xml:space="preserve">13.5619354248047</t>
   </si>
   <si>
     <t xml:space="preserve">13.4125375747681</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1137437820435</t>
+    <t xml:space="preserve">13.1137447357178</t>
   </si>
   <si>
     <t xml:space="preserve">13.2797403335571</t>
@@ -2567,40 +2570,40 @@
     <t xml:space="preserve">13.5121374130249</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5951347351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6117334365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1303434371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3295402526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4955368041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0805444717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3129405975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1967420578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7983503341675</t>
+    <t xml:space="preserve">13.5951337814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6117343902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1303424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3295392990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4955358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.080545425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3129415512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.196741104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7983493804932</t>
   </si>
   <si>
     <t xml:space="preserve">12.4497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3003597259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7153511047363</t>
+    <t xml:space="preserve">12.3003587722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7153520584106</t>
   </si>
   <si>
     <t xml:space="preserve">12.4331569671631</t>
@@ -2609,13 +2612,13 @@
     <t xml:space="preserve">12.5991535186768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3335580825806</t>
+    <t xml:space="preserve">12.3335590362549</t>
   </si>
   <si>
     <t xml:space="preserve">12.3501586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0679636001587</t>
+    <t xml:space="preserve">12.067964553833</t>
   </si>
   <si>
     <t xml:space="preserve">11.8521671295166</t>
@@ -2645,10 +2648,10 @@
     <t xml:space="preserve">11.3209791183472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1715812683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.221381187439</t>
+    <t xml:space="preserve">11.1715822219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2213821411133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8395881652832</t>
@@ -2669,10 +2672,10 @@
     <t xml:space="preserve">10.1922006607056</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97640514373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54481220245361</t>
+    <t xml:space="preserve">9.97640609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54481410980225</t>
   </si>
   <si>
     <t xml:space="preserve">9.56141376495361</t>
@@ -2702,13 +2705,13 @@
     <t xml:space="preserve">10.6071929931641</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3083982467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4909944534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1756019592285</t>
+    <t xml:space="preserve">10.3083972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4909954071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1756010055542</t>
   </si>
   <si>
     <t xml:space="preserve">10.1092023849487</t>
@@ -2717,16 +2720,16 @@
     <t xml:space="preserve">10.1424016952515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0594024658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86020755767822</t>
+    <t xml:space="preserve">10.0594034194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86020851135254</t>
   </si>
   <si>
     <t xml:space="preserve">9.89340686798096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69421195983887</t>
+    <t xml:space="preserve">9.69421005249023</t>
   </si>
   <si>
     <t xml:space="preserve">9.61121273040771</t>
@@ -2744,13 +2747,13 @@
     <t xml:space="preserve">9.19622039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29581832885742</t>
+    <t xml:space="preserve">9.29581737518311</t>
   </si>
   <si>
     <t xml:space="preserve">9.12982177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42861652374268</t>
+    <t xml:space="preserve">9.42861461639404</t>
   </si>
   <si>
     <t xml:space="preserve">9.77720832824707</t>
@@ -2759,7 +2762,7 @@
     <t xml:space="preserve">9.64441108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0262031555176</t>
+    <t xml:space="preserve">10.0262041091919</t>
   </si>
   <si>
     <t xml:space="preserve">10.5407934188843</t>
@@ -2798,10 +2801,10 @@
     <t xml:space="preserve">10.0811729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3559579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2700881958008</t>
+    <t xml:space="preserve">10.35595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2700872421265</t>
   </si>
   <si>
     <t xml:space="preserve">10.6479167938232</t>
@@ -2810,16 +2813,16 @@
     <t xml:space="preserve">10.7681341171265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.957049369812</t>
+    <t xml:space="preserve">10.9570503234863</t>
   </si>
   <si>
     <t xml:space="preserve">11.1631383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0600938796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1803131103516</t>
+    <t xml:space="preserve">11.060094833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1803121566772</t>
   </si>
   <si>
     <t xml:space="preserve">11.0944423675537</t>
@@ -2831,7 +2834,7 @@
     <t xml:space="preserve">10.9742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9913988113403</t>
+    <t xml:space="preserve">10.991397857666</t>
   </si>
   <si>
     <t xml:space="preserve">10.0296506881714</t>
@@ -2840,7 +2843,7 @@
     <t xml:space="preserve">10.0124759674072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.390305519104</t>
+    <t xml:space="preserve">10.3903064727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1498689651489</t>
@@ -2873,7 +2876,7 @@
     <t xml:space="preserve">10.0468244552612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5620470046997</t>
+    <t xml:space="preserve">10.5620460510254</t>
   </si>
   <si>
     <t xml:space="preserve">10.6307430267334</t>
@@ -2885,13 +2888,13 @@
     <t xml:space="preserve">10.4418277740479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7166128158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.459002494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5105237960815</t>
+    <t xml:space="preserve">10.7166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5105228424072</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509613037109</t>
@@ -2900,25 +2903,25 @@
     <t xml:space="preserve">10.6822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.493350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1155214309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7548656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61747360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37703609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51442909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63464641571045</t>
+    <t xml:space="preserve">10.4933500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1155204772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75486469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61747264862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37703704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51442813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63464832305908</t>
   </si>
   <si>
     <t xml:space="preserve">9.80638790130615</t>
@@ -2933,19 +2936,19 @@
     <t xml:space="preserve">9.49725532531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39421081542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22246932983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32551383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25681686401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4629077911377</t>
+    <t xml:space="preserve">9.39420986175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2224702835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.325514793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25681781768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46290683746338</t>
   </si>
   <si>
     <t xml:space="preserve">9.0850772857666</t>
@@ -2954,10 +2957,10 @@
     <t xml:space="preserve">9.54877662658691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56595039367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58312511444092</t>
+    <t xml:space="preserve">9.56595134735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58312606811523</t>
   </si>
   <si>
     <t xml:space="preserve">9.65182113647461</t>
@@ -2966,7 +2969,7 @@
     <t xml:space="preserve">9.823561668396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3387842178345</t>
+    <t xml:space="preserve">10.3387832641602</t>
   </si>
   <si>
     <t xml:space="preserve">10.5963945388794</t>
@@ -2975,16 +2978,16 @@
     <t xml:space="preserve">10.8540058135986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4550971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2661819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0429191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8883533477783</t>
+    <t xml:space="preserve">11.4550981521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2661828994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0429201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8883543014526</t>
   </si>
   <si>
     <t xml:space="preserve">10.9398756027222</t>
@@ -2999,16 +3002,16 @@
     <t xml:space="preserve">11.3692274093628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4379234313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0733633041382</t>
+    <t xml:space="preserve">11.4379224777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0733642578125</t>
   </si>
   <si>
     <t xml:space="preserve">12.4683666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5027160644531</t>
+    <t xml:space="preserve">12.5027151107788</t>
   </si>
   <si>
     <t xml:space="preserve">12.2966260910034</t>
@@ -3017,22 +3020,22 @@
     <t xml:space="preserve">12.0561895370483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7470569610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7127075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9703187942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9359712600708</t>
+    <t xml:space="preserve">11.7470560073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7127094268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9703197479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9359703063965</t>
   </si>
   <si>
     <t xml:space="preserve">12.0046663284302</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0218410491943</t>
+    <t xml:space="preserve">12.0218420028687</t>
   </si>
   <si>
     <t xml:space="preserve">11.8157529830933</t>
@@ -3044,13 +3047,13 @@
     <t xml:space="preserve">12.3653221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4340181350708</t>
+    <t xml:space="preserve">12.4340190887451</t>
   </si>
   <si>
     <t xml:space="preserve">12.3996696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3138008117676</t>
+    <t xml:space="preserve">12.3137998580933</t>
   </si>
   <si>
     <t xml:space="preserve">12.5198888778687</t>
@@ -3065,49 +3068,49 @@
     <t xml:space="preserve">12.2451038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2794523239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1420602798462</t>
+    <t xml:space="preserve">12.2794532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1420593261719</t>
   </si>
   <si>
     <t xml:space="preserve">12.1248865127563</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1764078140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.159234046936</t>
+    <t xml:space="preserve">12.1764087677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1592330932617</t>
   </si>
   <si>
     <t xml:space="preserve">12.1077117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3481492996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6572818756104</t>
+    <t xml:space="preserve">12.3481483459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.657280921936</t>
   </si>
   <si>
     <t xml:space="preserve">12.9148921966553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0694599151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1038084030151</t>
+    <t xml:space="preserve">13.0694589614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1038074493408</t>
   </si>
   <si>
     <t xml:space="preserve">13.0866327285767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.18967628479</t>
+    <t xml:space="preserve">13.1896772384644</t>
   </si>
   <si>
     <t xml:space="preserve">13.6705513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3442430496216</t>
+    <t xml:space="preserve">13.3442440032959</t>
   </si>
   <si>
     <t xml:space="preserve">13.6362028121948</t>
@@ -3116,31 +3119,31 @@
     <t xml:space="preserve">13.6018552780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5503330230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5675058364868</t>
+    <t xml:space="preserve">13.550332069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5675067901611</t>
   </si>
   <si>
     <t xml:space="preserve">13.4644622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3957672119141</t>
+    <t xml:space="preserve">13.3957662582397</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.619029045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.082727432251</t>
+    <t xml:space="preserve">13.6190280914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0827283859253</t>
   </si>
   <si>
     <t xml:space="preserve">13.6877250671387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7048997879028</t>
+    <t xml:space="preserve">13.7048988342285</t>
   </si>
   <si>
     <t xml:space="preserve">13.7220726013184</t>
@@ -3149,16 +3152,16 @@
     <t xml:space="preserve">13.8766393661499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6151247024536</t>
+    <t xml:space="preserve">14.6151237487793</t>
   </si>
   <si>
     <t xml:space="preserve">14.7353429794312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6494731903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8040390014648</t>
+    <t xml:space="preserve">14.6494722366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8040380477905</t>
   </si>
   <si>
     <t xml:space="preserve">14.6838207244873</t>
@@ -3173,25 +3176,25 @@
     <t xml:space="preserve">15.0101270675659</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0616502761841</t>
+    <t xml:space="preserve">15.0616512298584</t>
   </si>
   <si>
     <t xml:space="preserve">15.3879566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1990423202515</t>
+    <t xml:space="preserve">15.1990432739258</t>
   </si>
   <si>
     <t xml:space="preserve">15.2505645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1818685531616</t>
+    <t xml:space="preserve">15.1818695068359</t>
   </si>
   <si>
     <t xml:space="preserve">15.2162160873413</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9757785797119</t>
+    <t xml:space="preserve">14.9757804870605</t>
   </si>
   <si>
     <t xml:space="preserve">14.9242563247681</t>
@@ -3200,16 +3203,16 @@
     <t xml:space="preserve">14.4262094497681</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3918619155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9586067199707</t>
+    <t xml:space="preserve">14.3918609619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9586057662964</t>
   </si>
   <si>
     <t xml:space="preserve">14.5464286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1131725311279</t>
+    <t xml:space="preserve">15.1131715774536</t>
   </si>
   <si>
     <t xml:space="preserve">15.1303462982178</t>
@@ -3218,37 +3221,37 @@
     <t xml:space="preserve">14.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2677383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4223041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9031791687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9375276565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1436157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.851655960083</t>
+    <t xml:space="preserve">15.2677392959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4223031997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9031782150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9375257492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1436138153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8516550064087</t>
   </si>
   <si>
     <t xml:space="preserve">15.9546995162964</t>
   </si>
   <si>
-    <t xml:space="preserve">15.782958984375</t>
+    <t xml:space="preserve">15.7829599380493</t>
   </si>
   <si>
     <t xml:space="preserve">15.7142639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5253505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5596971511841</t>
+    <t xml:space="preserve">15.5253496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5596981048584</t>
   </si>
   <si>
     <t xml:space="preserve">14.8383884429932</t>
@@ -3257,10 +3260,10 @@
     <t xml:space="preserve">14.4605579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3059911727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2888164520264</t>
+    <t xml:space="preserve">14.3059902191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2888154983521</t>
   </si>
   <si>
     <t xml:space="preserve">14.5120792388916</t>
@@ -3269,16 +3272,16 @@
     <t xml:space="preserve">14.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7009954452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5807762145996</t>
+    <t xml:space="preserve">14.7009944915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5807752609253</t>
   </si>
   <si>
     <t xml:space="preserve">14.5292539596558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3746871948242</t>
+    <t xml:space="preserve">14.3746862411499</t>
   </si>
   <si>
     <t xml:space="preserve">14.1431245803833</t>
@@ -3290,9 +3293,6 @@
     <t xml:space="preserve">14.321249961853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3746862411499</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.6596870422363</t>
   </si>
   <si>
@@ -4374,6 +4374,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.73000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73999977111816</t>
   </si>
 </sst>
 </file>
@@ -43080,7 +43083,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1476" t="s">
-        <v>770</v>
+        <v>831</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -43106,7 +43109,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1477" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -43132,7 +43135,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1478" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -43158,7 +43161,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1479" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -43184,7 +43187,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1480" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -43210,7 +43213,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1481" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -43236,7 +43239,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1482" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -43262,7 +43265,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1483" t="s">
-        <v>770</v>
+        <v>831</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -43314,7 +43317,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1485" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -43340,7 +43343,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1486" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -43366,7 +43369,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1487" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -43418,7 +43421,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1489" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -43470,7 +43473,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1491" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -43522,7 +43525,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43600,7 +43603,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1496" t="s">
-        <v>770</v>
+        <v>831</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43626,7 +43629,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1497" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43652,7 +43655,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1498" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43834,7 +43837,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1505" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43886,7 +43889,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1507" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43912,7 +43915,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1508" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43938,7 +43941,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1509" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -44068,7 +44071,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1514" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -44094,7 +44097,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1515" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -44120,7 +44123,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1516" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -44172,7 +44175,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1518" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -44198,7 +44201,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -44224,7 +44227,7 @@
         <v>16</v>
       </c>
       <c r="G1520" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -44250,7 +44253,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1521" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -44276,7 +44279,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1522" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -44484,7 +44487,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1530" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -44510,7 +44513,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44536,7 +44539,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1532" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44562,7 +44565,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1533" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44588,7 +44591,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1534" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44614,7 +44617,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1535" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44640,7 +44643,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1536" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44666,7 +44669,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1537" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44692,7 +44695,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1538" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44718,7 +44721,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G1539" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44744,7 +44747,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44770,7 +44773,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1541" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44796,7 +44799,7 @@
         <v>15</v>
       </c>
       <c r="G1542" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44822,7 +44825,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1543" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44848,7 +44851,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1544" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44874,7 +44877,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1545" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44900,7 +44903,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1546" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44926,7 +44929,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1547" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44952,7 +44955,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1548" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44978,7 +44981,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1549" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -45004,7 +45007,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1550" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -45030,7 +45033,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1551" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -45056,7 +45059,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1552" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -45082,7 +45085,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1553" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -45108,7 +45111,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1554" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -45134,7 +45137,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1555" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -45160,7 +45163,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1556" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -45186,7 +45189,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1557" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -45212,7 +45215,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -45238,7 +45241,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1559" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -45264,7 +45267,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1560" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -45290,7 +45293,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1561" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -45316,7 +45319,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1562" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -45342,7 +45345,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1563" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -45368,7 +45371,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1564" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -45394,7 +45397,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1565" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -45420,7 +45423,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1566" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -45446,7 +45449,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1567" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -45472,7 +45475,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1568" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -45498,7 +45501,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1569" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -45524,7 +45527,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1570" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45550,7 +45553,7 @@
         <v>11.5</v>
       </c>
       <c r="G1571" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45576,7 +45579,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1572" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45602,7 +45605,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1573" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45628,7 +45631,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1574" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45654,7 +45657,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1575" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45680,7 +45683,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1576" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45706,7 +45709,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1577" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45732,7 +45735,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1578" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45758,7 +45761,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1579" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45784,7 +45787,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1580" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45810,7 +45813,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1581" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45836,7 +45839,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1582" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45862,7 +45865,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1583" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45888,7 +45891,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1584" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45914,7 +45917,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1585" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45940,7 +45943,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1586" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45966,7 +45969,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1587" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45992,7 +45995,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1588" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -46018,7 +46021,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1589" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -46044,7 +46047,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1590" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -46070,7 +46073,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1591" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -46096,7 +46099,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1592" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -46122,7 +46125,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1593" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -46148,7 +46151,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1594" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -46174,7 +46177,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1595" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -46200,7 +46203,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -46226,7 +46229,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1597" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -46252,7 +46255,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1598" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -46278,7 +46281,7 @@
         <v>11</v>
       </c>
       <c r="G1599" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -46304,7 +46307,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1600" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -46330,7 +46333,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1601" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -46356,7 +46359,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1602" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -46382,7 +46385,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1603" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -46408,7 +46411,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1604" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -46434,7 +46437,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1605" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -46460,7 +46463,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1606" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -46486,7 +46489,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1607" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -46512,7 +46515,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1608" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46538,7 +46541,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1609" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -46564,7 +46567,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1610" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46590,7 +46593,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1611" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -46616,7 +46619,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1612" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46642,7 +46645,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1613" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -46668,7 +46671,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1614" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -46694,7 +46697,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1615" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46720,7 +46723,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1616" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -46746,7 +46749,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1617" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46772,7 +46775,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1618" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46798,7 +46801,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1619" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46824,7 +46827,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1620" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46850,7 +46853,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1621" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46876,7 +46879,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1622" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46902,7 +46905,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1623" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46928,7 +46931,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1624" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46954,7 +46957,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1625" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46980,7 +46983,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1626" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -47006,7 +47009,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1627" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -47032,7 +47035,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1628" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -47058,7 +47061,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1629" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47084,7 +47087,7 @@
         <v>13</v>
       </c>
       <c r="G1630" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47110,7 +47113,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1631" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47136,7 +47139,7 @@
         <v>13</v>
       </c>
       <c r="G1632" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47162,7 +47165,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1633" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47188,7 +47191,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1634" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47214,7 +47217,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1635" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47240,7 +47243,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1636" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47266,7 +47269,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1637" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47292,7 +47295,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1638" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47318,7 +47321,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1639" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47344,7 +47347,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1640" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47370,7 +47373,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1641" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47396,7 +47399,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1642" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47422,7 +47425,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1643" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47448,7 +47451,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1644" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47474,7 +47477,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1645" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47500,7 +47503,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1646" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47526,7 +47529,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1647" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47552,7 +47555,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1648" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47578,7 +47581,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1649" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47604,7 +47607,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1650" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47630,7 +47633,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1651" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47656,7 +47659,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1652" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47682,7 +47685,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1653" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47708,7 +47711,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1654" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47734,7 +47737,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1655" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47760,7 +47763,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1656" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47786,7 +47789,7 @@
         <v>11.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47812,7 +47815,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1658" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47838,7 +47841,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1659" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47864,7 +47867,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1660" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47890,7 +47893,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1661" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47916,7 +47919,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1662" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47942,7 +47945,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1663" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47968,7 +47971,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1664" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47994,7 +47997,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1665" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -48020,7 +48023,7 @@
         <v>12</v>
       </c>
       <c r="G1666" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48046,7 +48049,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1667" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -48072,7 +48075,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1668" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48098,7 +48101,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1669" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48124,7 +48127,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1670" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48150,7 +48153,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1671" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48176,7 +48179,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1672" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48202,7 +48205,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1673" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48228,7 +48231,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1674" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48254,7 +48257,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1675" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48280,7 +48283,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1676" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48306,7 +48309,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1677" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48332,7 +48335,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1678" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48358,7 +48361,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1679" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48384,7 +48387,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1680" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48410,7 +48413,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1681" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48436,7 +48439,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1682" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48462,7 +48465,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1683" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48488,7 +48491,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1684" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48514,7 +48517,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1685" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48540,7 +48543,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1686" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48566,7 +48569,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1687" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48592,7 +48595,7 @@
         <v>12</v>
       </c>
       <c r="G1688" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48618,7 +48621,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1689" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48644,7 +48647,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1690" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48670,7 +48673,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1691" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48696,7 +48699,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1692" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -48722,7 +48725,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1693" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -48748,7 +48751,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1694" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48774,7 +48777,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1695" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48800,7 +48803,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1696" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48826,7 +48829,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48852,7 +48855,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1698" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48878,7 +48881,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1699" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48904,7 +48907,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1700" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48930,7 +48933,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1701" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48956,7 +48959,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1702" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -48982,7 +48985,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1703" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -49008,7 +49011,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1704" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -49034,7 +49037,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1705" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -49060,7 +49063,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1706" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -49086,7 +49089,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1707" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -49112,7 +49115,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1708" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -49138,7 +49141,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1709" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -49164,7 +49167,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1710" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49190,7 +49193,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1711" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49216,7 +49219,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1712" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -49242,7 +49245,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1713" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49268,7 +49271,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1714" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -49294,7 +49297,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1715" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -49320,7 +49323,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1716" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -49346,7 +49349,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1717" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49372,7 +49375,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1718" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -49398,7 +49401,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1719" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49424,7 +49427,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1720" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -49450,7 +49453,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1721" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49476,7 +49479,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1722" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49502,7 +49505,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1723" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49528,7 +49531,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1724" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49554,7 +49557,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1725" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49580,7 +49583,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1726" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49606,7 +49609,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1727" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49632,7 +49635,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1728" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49658,7 +49661,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1729" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49684,7 +49687,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1730" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -49710,7 +49713,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -49736,7 +49739,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1732" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -49762,7 +49765,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G1733" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -49788,7 +49791,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1734" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -49814,7 +49817,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1735" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49840,7 +49843,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1736" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49866,7 +49869,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1737" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49892,7 +49895,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1738" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49918,7 +49921,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1739" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -49944,7 +49947,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1740" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49970,7 +49973,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1741" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -49996,7 +49999,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1742" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -50022,7 +50025,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1743" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -50048,7 +50051,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1744" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -50074,7 +50077,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1745" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -50100,7 +50103,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1746" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -50126,7 +50129,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1747" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -50152,7 +50155,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1748" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -50178,7 +50181,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1749" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50204,7 +50207,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1750" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -50230,7 +50233,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1751" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -50256,7 +50259,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1752" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -50282,7 +50285,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1753" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -50308,7 +50311,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -50334,7 +50337,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1755" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -50360,7 +50363,7 @@
         <v>14</v>
       </c>
       <c r="G1756" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -50386,7 +50389,7 @@
         <v>14</v>
       </c>
       <c r="G1757" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50412,7 +50415,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1758" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -50438,7 +50441,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1759" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -50464,7 +50467,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1760" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50490,7 +50493,7 @@
         <v>14</v>
       </c>
       <c r="G1761" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50516,7 +50519,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1762" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50542,7 +50545,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -50568,7 +50571,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1764" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -50594,7 +50597,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1765" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50620,7 +50623,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1766" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -50646,7 +50649,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1767" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50672,7 +50675,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1768" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -50698,7 +50701,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1769" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -50724,7 +50727,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1770" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50750,7 +50753,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1771" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50776,7 +50779,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1772" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -50802,7 +50805,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1773" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50828,7 +50831,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1774" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50854,7 +50857,7 @@
         <v>14</v>
       </c>
       <c r="G1775" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50880,7 +50883,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1776" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50906,7 +50909,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1777" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50932,7 +50935,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1778" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50958,7 +50961,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1779" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50984,7 +50987,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1780" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -51010,7 +51013,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1781" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -51036,7 +51039,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -51062,7 +51065,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1783" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -51088,7 +51091,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1784" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -51114,7 +51117,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1785" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -51140,7 +51143,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1786" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -51166,7 +51169,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1787" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -51192,7 +51195,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1788" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -51218,7 +51221,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1789" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51244,7 +51247,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1790" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51270,7 +51273,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1791" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -51296,7 +51299,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1792" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -51322,7 +51325,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1793" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -51348,7 +51351,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1794" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51374,7 +51377,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1795" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -51400,7 +51403,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1796" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -51426,7 +51429,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1797" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51452,7 +51455,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1798" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51478,7 +51481,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1799" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51504,7 +51507,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1800" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -51530,7 +51533,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1801" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -51556,7 +51559,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1802" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -51582,7 +51585,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1803" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51608,7 +51611,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1804" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -51634,7 +51637,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1805" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -51660,7 +51663,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1806" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51686,7 +51689,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1807" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -51712,7 +51715,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51738,7 +51741,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1809" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51764,7 +51767,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1810" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51790,7 +51793,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1811" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51816,7 +51819,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1812" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51842,7 +51845,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1813" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51868,7 +51871,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1814" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51894,7 +51897,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1815" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51920,7 +51923,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1816" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51946,7 +51949,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1817" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51972,7 +51975,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1818" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51998,7 +52001,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1819" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -52024,7 +52027,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1820" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -52050,7 +52053,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1821" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -52076,7 +52079,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1822" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -52102,7 +52105,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1823" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -52128,7 +52131,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1824" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -52154,7 +52157,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1825" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -52180,7 +52183,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1826" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -52206,7 +52209,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1827" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52232,7 +52235,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1828" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -52258,7 +52261,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1829" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -52284,7 +52287,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1830" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -52310,7 +52313,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1831" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -52336,7 +52339,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1832" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -52362,7 +52365,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1833" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52388,7 +52391,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1834" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -52414,7 +52417,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1835" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52440,7 +52443,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1836" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52466,7 +52469,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1837" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52492,7 +52495,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1838" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -52518,7 +52521,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1839" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -52544,7 +52547,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52570,7 +52573,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1841" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52596,7 +52599,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1842" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52622,7 +52625,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1843" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52648,7 +52651,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1844" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52674,7 +52677,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1845" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52700,7 +52703,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1846" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52726,7 +52729,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1847" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52752,7 +52755,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1848" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52778,7 +52781,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1849" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52804,7 +52807,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1850" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52830,7 +52833,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1851" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52856,7 +52859,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1852" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52882,7 +52885,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1853" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52908,7 +52911,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1854" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52934,7 +52937,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1855" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52960,7 +52963,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1856" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52986,7 +52989,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1857" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -53012,7 +53015,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G1858" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -53038,7 +53041,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1859" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -53064,7 +53067,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1860" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -53090,7 +53093,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1861" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -53116,7 +53119,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1862" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -53142,7 +53145,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1863" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -53168,7 +53171,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1864" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -53194,7 +53197,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1865" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -53220,7 +53223,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1866" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -53246,7 +53249,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -53272,7 +53275,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1868" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -53298,7 +53301,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1869" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53324,7 +53327,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1870" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53350,7 +53353,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1871" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53376,7 +53379,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1872" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53402,7 +53405,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1873" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53428,7 +53431,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1874" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53454,7 +53457,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1875" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53480,7 +53483,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1876" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53506,7 +53509,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1877" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53532,7 +53535,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1878" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -55092,7 +55095,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1938" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -69634,7 +69637,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912268518</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>53045</v>
@@ -69655,6 +69658,32 @@
         <v>1453</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6919444444</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>52257</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>7.76999998092651</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>7.67999982833862</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>7.73999977111816</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>7.73999977111816</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1454</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="1458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="1459">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,73 +38,73 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04141759872437</t>
+    <t xml:space="preserve">4.04141712188721</t>
   </si>
   <si>
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447938919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93978929519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82799816131592</t>
+    <t xml:space="preserve">4.02447891235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93978905677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8279983997345</t>
   </si>
   <si>
     <t xml:space="preserve">3.78057146072388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70943188667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75685834884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74330806732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8008975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571877479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66539239883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56376504898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65184259414673</t>
+    <t xml:space="preserve">3.70943164825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75685858726501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74330830574036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80089688301086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040886878967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571829795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66539263725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56376481056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65184211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.72636961936951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70265603065491</t>
+    <t xml:space="preserve">3.70265674591064</t>
   </si>
   <si>
     <t xml:space="preserve">3.65861773490906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69249367713928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74669575691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5976402759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59086561203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58408999443054</t>
+    <t xml:space="preserve">3.69249296188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74669551849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59764051437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59086513519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58408975601196</t>
   </si>
   <si>
     <t xml:space="preserve">3.49601244926453</t>
@@ -113,43 +113,43 @@
     <t xml:space="preserve">3.46213626861572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51633763313293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38760900497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40793466567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50956273078918</t>
+    <t xml:space="preserve">3.51633787155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38760876655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40793442726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50956225395203</t>
   </si>
   <si>
     <t xml:space="preserve">3.55698919296265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56715202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57731533050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54682660102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52650046348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50278759002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56037759780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58070278167725</t>
+    <t xml:space="preserve">3.56715250015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61119055747986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57731509208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54682612419128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52650022506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50278735160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56037664413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58070230484009</t>
   </si>
   <si>
     <t xml:space="preserve">3.60102868080139</t>
@@ -158,100 +158,100 @@
     <t xml:space="preserve">3.54343867301941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57053923606873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64506721496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78734683990479</t>
+    <t xml:space="preserve">3.57053971290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6450674533844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78734636306763</t>
   </si>
   <si>
     <t xml:space="preserve">3.841548204422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8652617931366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85171151161194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92962622642517</t>
+    <t xml:space="preserve">3.86526203155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85171127319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92962670326233</t>
   </si>
   <si>
     <t xml:space="preserve">3.9364013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91607594490051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90252494812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89575004577637</t>
+    <t xml:space="preserve">3.91607618331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90252614021301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89574980735779</t>
   </si>
   <si>
     <t xml:space="preserve">3.92285084724426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90930008888245</t>
+    <t xml:space="preserve">3.90930104255676</t>
   </si>
   <si>
     <t xml:space="preserve">3.9702775478363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87881183624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85848689079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94317674636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89913749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94656372070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95672702789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96350264549255</t>
+    <t xml:space="preserve">3.87881112098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85848665237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94317722320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8991379737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94656467437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95672750473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96350240707397</t>
   </si>
   <si>
     <t xml:space="preserve">3.91268801689148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97366452217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91946339607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87203621864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88704776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87291312217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8587794303894</t>
+    <t xml:space="preserve">3.97366523742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91946387290955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8720371723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88704824447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8729133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85877847671509</t>
   </si>
   <si>
     <t xml:space="preserve">3.83757638931274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86231207847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87644648551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89411592483521</t>
+    <t xml:space="preserve">3.86231279373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8764476776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89411497116089</t>
   </si>
   <si>
     <t xml:space="preserve">3.9011824131012</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">3.8905816078186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94358706474304</t>
+    <t xml:space="preserve">3.94358730316162</t>
   </si>
   <si>
     <t xml:space="preserve">3.95418787002563</t>
@@ -269,100 +269,100 @@
     <t xml:space="preserve">3.96125555038452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01425981521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02486133575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08846807479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05666446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03899574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305868148804</t>
+    <t xml:space="preserve">4.01426029205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02486228942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08846759796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05666399002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03899669647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305844306946</t>
   </si>
   <si>
     <t xml:space="preserve">4.00719356536865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97539019584656</t>
+    <t xml:space="preserve">3.9753897190094</t>
   </si>
   <si>
     <t xml:space="preserve">3.97185587882996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80223989486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7810378074646</t>
+    <t xml:space="preserve">3.8022403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78103733062744</t>
   </si>
   <si>
     <t xml:space="preserve">3.75630187988281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74923372268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90471625328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92238473892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065498352051</t>
+    <t xml:space="preserve">3.74923419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9047167301178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92238521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065450668335</t>
   </si>
   <si>
     <t xml:space="preserve">4.03546237945557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75983619689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80930709838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83050918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86937975883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82344126701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80577421188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84110951423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85171127319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81637454032898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8658459186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89764928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93651986122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90825057029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91531753540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97892379760742</t>
+    <t xml:space="preserve">3.7598352432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80930662155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83050870895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86937952041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82344150543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80577373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84111022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85171055793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8163743019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86584568023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89764857292175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93651962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9082498550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91531705856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97892355918884</t>
   </si>
   <si>
     <t xml:space="preserve">4.00012540817261</t>
@@ -371,124 +371,124 @@
     <t xml:space="preserve">4.02132797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95772123336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84464430809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81284070014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77043676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690268516541</t>
+    <t xml:space="preserve">3.95772171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84464406967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81284046173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77043628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690220832825</t>
   </si>
   <si>
     <t xml:space="preserve">3.76336884498596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74570107460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72449827194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77397036552429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78810477256775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81990838050842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72803258895874</t>
+    <t xml:space="preserve">3.74570035934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7244987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77396965026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78810524940491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81990814208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7280330657959</t>
   </si>
   <si>
     <t xml:space="preserve">3.73863339424133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73156642913818</t>
+    <t xml:space="preserve">3.7315661907196</t>
   </si>
   <si>
     <t xml:space="preserve">3.73510003089905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65382480621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63968968391418</t>
+    <t xml:space="preserve">3.65382504463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63969039916992</t>
   </si>
   <si>
     <t xml:space="preserve">3.66089224815369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61848735809326</t>
+    <t xml:space="preserve">3.61848759651184</t>
   </si>
   <si>
     <t xml:space="preserve">3.61142110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62555575370789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61495423316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64675736427307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74216723442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91885089874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98599100112915</t>
+    <t xml:space="preserve">3.62555551528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61495471000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64675784111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7421669960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91885137557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98599123954773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9965922832489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87998032569885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8835141658783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79517245292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82697534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79163813591003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84817790985107</t>
+    <t xml:space="preserve">3.87998104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88351488113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79517292976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82697486877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79163861274719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84817719459534</t>
   </si>
   <si>
     <t xml:space="preserve">3.71036386489868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85524415969849</t>
+    <t xml:space="preserve">3.85524463653564</t>
   </si>
   <si>
     <t xml:space="preserve">4.03192901611328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04253005981445</t>
+    <t xml:space="preserve">4.04252958297729</t>
   </si>
   <si>
     <t xml:space="preserve">4.08493423461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0990686416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05313062667847</t>
+    <t xml:space="preserve">4.09906911849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05313110351562</t>
   </si>
   <si>
     <t xml:space="preserve">4.04959726333618</t>
@@ -503,67 +503,67 @@
     <t xml:space="preserve">4.07786655426025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07433271408081</t>
+    <t xml:space="preserve">4.07433319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.04606342315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0637321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10613584518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10260200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1344051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12733840942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16974210739136</t>
+    <t xml:space="preserve">4.06373167037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10613632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10260248184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13440561294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12733793258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16974258422852</t>
   </si>
   <si>
     <t xml:space="preserve">4.18387699127197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1591420173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24041557312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21568059921265</t>
+    <t xml:space="preserve">4.15914154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24041604995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21568012237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.27575254440308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34642648696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36762809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35349369049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31108951568604</t>
+    <t xml:space="preserve">4.34642601013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36762762069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35349321365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31108999252319</t>
   </si>
   <si>
     <t xml:space="preserve">4.30402231216431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38176345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50897598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72806406021118</t>
+    <t xml:space="preserve">4.38176298141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5089750289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72806358337402</t>
   </si>
   <si>
     <t xml:space="preserve">4.91181516647339</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">4.94715213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19450902938843</t>
+    <t xml:space="preserve">5.19450950622559</t>
   </si>
   <si>
     <t xml:space="preserve">5.22277879714966</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.07436418533325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08496570587158</t>
+    <t xml:space="preserve">5.08496522903442</t>
   </si>
   <si>
     <t xml:space="preserve">5.11676836013794</t>
@@ -599,22 +599,22 @@
     <t xml:space="preserve">5.10616731643677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1521053314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15917301177979</t>
+    <t xml:space="preserve">5.15210580825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15917348861694</t>
   </si>
   <si>
     <t xml:space="preserve">5.1733078956604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19097518920898</t>
+    <t xml:space="preserve">5.19097566604614</t>
   </si>
   <si>
     <t xml:space="preserve">5.14503812789917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13090324401855</t>
+    <t xml:space="preserve">5.13090372085571</t>
   </si>
   <si>
     <t xml:space="preserve">5.24751472473145</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">5.26871681213379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59734964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5125412940979</t>
+    <t xml:space="preserve">5.59734869003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51254081726074</t>
   </si>
   <si>
     <t xml:space="preserve">5.35705852508545</t>
@@ -638,13 +638,13 @@
     <t xml:space="preserve">5.37119340896606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44186592102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53020858764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61199712753296</t>
+    <t xml:space="preserve">5.44186735153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53020906448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61199760437012</t>
   </si>
   <si>
     <t xml:space="preserve">5.65216159820557</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">5.6886739730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6229510307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.619300365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59739255905151</t>
+    <t xml:space="preserve">5.62295150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61929988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59739208221436</t>
   </si>
   <si>
     <t xml:space="preserve">5.42213153839111</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">5.41847991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55357694625854</t>
+    <t xml:space="preserve">5.5535774230957</t>
   </si>
   <si>
     <t xml:space="preserve">5.56087970733643</t>
@@ -680,49 +680,49 @@
     <t xml:space="preserve">5.46229600906372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55722808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45499277114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3673620223999</t>
+    <t xml:space="preserve">5.55722856521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45499324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36736249923706</t>
   </si>
   <si>
     <t xml:space="preserve">5.37466526031494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43308544158936</t>
+    <t xml:space="preserve">5.4330849647522</t>
   </si>
   <si>
     <t xml:space="preserve">5.40387487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47690010070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44769048690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48055219650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49515724182129</t>
+    <t xml:space="preserve">5.47690057754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44769096374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48055171966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49515628814697</t>
   </si>
   <si>
     <t xml:space="preserve">5.54627466201782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60104322433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41117763519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5134129524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54992628097534</t>
+    <t xml:space="preserve">5.60104417800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41117715835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51341390609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54992580413818</t>
   </si>
   <si>
     <t xml:space="preserve">5.45134210586548</t>
@@ -731,28 +731,28 @@
     <t xml:space="preserve">5.61564922332764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50611066818237</t>
+    <t xml:space="preserve">5.50611114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.34545469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37101364135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31259393692017</t>
+    <t xml:space="preserve">5.37101411819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31259346008301</t>
   </si>
   <si>
     <t xml:space="preserve">5.28703451156616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15558910369873</t>
+    <t xml:space="preserve">5.15558958053589</t>
   </si>
   <si>
     <t xml:space="preserve">5.12637853622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2724289894104</t>
+    <t xml:space="preserve">5.27242946624756</t>
   </si>
   <si>
     <t xml:space="preserve">5.31989574432373</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">5.14098405838013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40752601623535</t>
+    <t xml:space="preserve">5.40752649307251</t>
   </si>
   <si>
     <t xml:space="preserve">5.38927030563354</t>
@@ -773,37 +773,37 @@
     <t xml:space="preserve">5.24321889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46959733963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41482973098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42578268051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44038772583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48420286178589</t>
+    <t xml:space="preserve">5.46959781646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41482877731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42578220367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44038820266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48420381546021</t>
   </si>
   <si>
     <t xml:space="preserve">5.35275745391846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48785448074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50245952606201</t>
+    <t xml:space="preserve">5.48785400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50245904922485</t>
   </si>
   <si>
     <t xml:space="preserve">5.57183408737183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57913589477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56453037261963</t>
+    <t xml:space="preserve">5.57913541793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56453084945679</t>
   </si>
   <si>
     <t xml:space="preserve">5.52071523666382</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">5.53897190093994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65581274032593</t>
+    <t xml:space="preserve">5.65581226348877</t>
   </si>
   <si>
     <t xml:space="preserve">5.58643817901611</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">5.53166961669922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60469436645508</t>
+    <t xml:space="preserve">5.60469484329224</t>
   </si>
   <si>
     <t xml:space="preserve">5.59009027481079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75804758071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79456090927124</t>
+    <t xml:space="preserve">5.75804805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79456043243408</t>
   </si>
   <si>
     <t xml:space="preserve">5.92965745925903</t>
@@ -845,19 +845,19 @@
     <t xml:space="preserve">5.94426298141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99903154373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93696069717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98807716369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83107280731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88584280014038</t>
+    <t xml:space="preserve">5.99903202056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93695974349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98807764053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83107328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88584232330322</t>
   </si>
   <si>
     <t xml:space="preserve">5.83472490310669</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">5.95886754989624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76900148391724</t>
+    <t xml:space="preserve">5.76900243759155</t>
   </si>
   <si>
     <t xml:space="preserve">5.91140174865723</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83837556838989</t>
+    <t xml:space="preserve">5.83837652206421</t>
   </si>
   <si>
     <t xml:space="preserve">5.84202718734741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87123727798462</t>
+    <t xml:space="preserve">5.87123680114746</t>
   </si>
   <si>
     <t xml:space="preserve">5.78360652923584</t>
@@ -887,22 +887,22 @@
     <t xml:space="preserve">5.85298109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7032790184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82742214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8639349937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75439739227295</t>
+    <t xml:space="preserve">5.70327854156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82742166519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86393404006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75439643859863</t>
   </si>
   <si>
     <t xml:space="preserve">5.72883796691895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68502235412598</t>
+    <t xml:space="preserve">5.68502330780029</t>
   </si>
   <si>
     <t xml:space="preserve">5.66676664352417</t>
@@ -911,25 +911,25 @@
     <t xml:space="preserve">5.88949346542358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78725814819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77995586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73614025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6083459854126</t>
+    <t xml:space="preserve">5.7872576713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77995491027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73614072799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60834646224976</t>
   </si>
   <si>
     <t xml:space="preserve">5.63025379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53532075881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76169872283936</t>
+    <t xml:space="preserve">5.53532028198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76169919967651</t>
   </si>
   <si>
     <t xml:space="preserve">5.62660217285156</t>
@@ -938,16 +938,16 @@
     <t xml:space="preserve">5.68137168884277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73979187011719</t>
+    <t xml:space="preserve">5.73979139328003</t>
   </si>
   <si>
     <t xml:space="preserve">5.76535081863403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80916547775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80551338195801</t>
+    <t xml:space="preserve">5.80916595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80551433563232</t>
   </si>
   <si>
     <t xml:space="preserve">5.82377052307129</t>
@@ -956,124 +956,124 @@
     <t xml:space="preserve">5.87853956222534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82011985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90409851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92235469818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9515643119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02459049224854</t>
+    <t xml:space="preserve">5.82011890411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90409898757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92235517501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95156478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02459001541138</t>
   </si>
   <si>
     <t xml:space="preserve">6.06110334396362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00998544692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09031343460083</t>
+    <t xml:space="preserve">6.00998497009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09031391143799</t>
   </si>
   <si>
     <t xml:space="preserve">6.22906160354614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18524694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03189373016357</t>
+    <t xml:space="preserve">6.18524599075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03189325332642</t>
   </si>
   <si>
     <t xml:space="preserve">6.0391960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04649829864502</t>
+    <t xml:space="preserve">6.0464973449707</t>
   </si>
   <si>
     <t xml:space="preserve">6.25096940994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2071533203125</t>
+    <t xml:space="preserve">6.20715379714966</t>
   </si>
   <si>
     <t xml:space="preserve">6.14143133163452</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12682580947876</t>
+    <t xml:space="preserve">6.12682628631592</t>
   </si>
   <si>
     <t xml:space="preserve">5.7982120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72518682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96616983413696</t>
+    <t xml:space="preserve">5.72518634796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96617078781128</t>
   </si>
   <si>
     <t xml:space="preserve">6.00268268585205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8931450843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84932947158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97347354888916</t>
+    <t xml:space="preserve">5.89314413070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84932994842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.973473072052</t>
   </si>
   <si>
     <t xml:space="preserve">5.99538040161133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11952352523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15603590011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10491847991943</t>
+    <t xml:space="preserve">6.11952304840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15603637695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10491800308228</t>
   </si>
   <si>
     <t xml:space="preserve">5.98077487945557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90044784545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14873361587524</t>
+    <t xml:space="preserve">5.90044736862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1487340927124</t>
   </si>
   <si>
     <t xml:space="preserve">6.09761619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05380058288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07570743560791</t>
+    <t xml:space="preserve">6.05380010604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07570791244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.08301067352295</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17794418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17064046859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24366617202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28017902374268</t>
+    <t xml:space="preserve">6.17794322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17063999176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24366664886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28017997741699</t>
   </si>
   <si>
     <t xml:space="preserve">6.38636589050293</t>
@@ -1088,16 +1088,16 @@
     <t xml:space="preserve">6.28017854690552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15882253646851</t>
+    <t xml:space="preserve">6.15882301330566</t>
   </si>
   <si>
     <t xml:space="preserve">6.27259492874146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26501035690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21191549301147</t>
+    <t xml:space="preserve">6.26500988006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21191596984863</t>
   </si>
   <si>
     <t xml:space="preserve">6.1815767288208</t>
@@ -1106,37 +1106,37 @@
     <t xml:space="preserve">6.15123796463013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02988147735596</t>
+    <t xml:space="preserve">6.02988195419312</t>
   </si>
   <si>
     <t xml:space="preserve">6.05263614654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25742435455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22708511352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24983930587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29534912109375</t>
+    <t xml:space="preserve">6.25742483139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22708559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24983978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29534864425659</t>
   </si>
   <si>
     <t xml:space="preserve">6.37119579315186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18916130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16640758514404</t>
+    <t xml:space="preserve">6.18916177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1664080619812</t>
   </si>
   <si>
     <t xml:space="preserve">6.20433187484741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0147123336792</t>
+    <t xml:space="preserve">6.01471185684204</t>
   </si>
   <si>
     <t xml:space="preserve">6.04505157470703</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">6.12089920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13606834411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11331462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09056043624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96161890029907</t>
+    <t xml:space="preserve">6.13606882095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11331510543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09055948257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96161937713623</t>
   </si>
   <si>
     <t xml:space="preserve">6.0829758644104</t>
@@ -1169,76 +1169,76 @@
     <t xml:space="preserve">6.14365339279175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10572957992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06022167205811</t>
+    <t xml:space="preserve">6.10572910308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06022119522095</t>
   </si>
   <si>
     <t xml:space="preserve">5.99954271316528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95403385162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93886518478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06780624389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91611051559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94645071029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818670272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746747970581</t>
+    <t xml:space="preserve">5.95403432846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93886470794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06780576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91611099243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94644975662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818765640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746652603149</t>
   </si>
   <si>
     <t xml:space="preserve">6.02229738235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9919581413269</t>
+    <t xml:space="preserve">5.99195861816406</t>
   </si>
   <si>
     <t xml:space="preserve">5.86301755905151</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07539033889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24225568771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738265991211</t>
+    <t xml:space="preserve">6.07539129257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24225473403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738313674927</t>
   </si>
   <si>
     <t xml:space="preserve">6.63666200637817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46221399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57598447799683</t>
+    <t xml:space="preserve">6.46221351623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57598400115967</t>
   </si>
   <si>
     <t xml:space="preserve">6.56081533432007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6063232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55323076248169</t>
+    <t xml:space="preserve">6.60632419586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55323123931885</t>
   </si>
   <si>
     <t xml:space="preserve">6.65183258056641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53806114196777</t>
+    <t xml:space="preserve">6.53806066513062</t>
   </si>
   <si>
     <t xml:space="preserve">6.48496723175049</t>
@@ -1250,22 +1250,22 @@
     <t xml:space="preserve">6.66700124740601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59873867034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34085702896118</t>
+    <t xml:space="preserve">6.59873962402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34085655212402</t>
   </si>
   <si>
     <t xml:space="preserve">6.39395046234131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41670513153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42428922653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53047561645508</t>
+    <t xml:space="preserve">6.4167046546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42428970336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53047609329224</t>
   </si>
   <si>
     <t xml:space="preserve">6.59115362167358</t>
@@ -1274,19 +1274,19 @@
     <t xml:space="preserve">6.54564523696899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56840038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44704389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34844207763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21950054168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40911912918091</t>
+    <t xml:space="preserve">6.56839942932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44704341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3484411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21950101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40911960601807</t>
   </si>
   <si>
     <t xml:space="preserve">6.32568788528442</t>
@@ -1298,49 +1298,49 @@
     <t xml:space="preserve">6.68975591659546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67458581924438</t>
+    <t xml:space="preserve">6.67458629608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.7428503036499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75043296813965</t>
+    <t xml:space="preserve">6.75043344497681</t>
   </si>
   <si>
     <t xml:space="preserve">6.62149238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37878084182739</t>
+    <t xml:space="preserve">6.37878036499023</t>
   </si>
   <si>
     <t xml:space="preserve">6.36361169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46979808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51530647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31051731109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35602712631226</t>
+    <t xml:space="preserve">6.46979761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51530742645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31051826477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35602617263794</t>
   </si>
   <si>
     <t xml:space="preserve">6.19674682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40153408050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72009468078613</t>
+    <t xml:space="preserve">6.40153503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72009515762329</t>
   </si>
   <si>
     <t xml:space="preserve">6.7580189704895</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80352735519409</t>
+    <t xml:space="preserve">6.80352783203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.78835773468018</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">6.73526525497437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84903621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8642053604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81111097335815</t>
+    <t xml:space="preserve">6.84903526306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86420488357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81111192703247</t>
   </si>
   <si>
     <t xml:space="preserve">6.8414511680603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81869649887085</t>
+    <t xml:space="preserve">6.81869602203369</t>
   </si>
   <si>
     <t xml:space="preserve">6.90212869644165</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">6.99314641952515</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89454507827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94005298614502</t>
+    <t xml:space="preserve">6.89454412460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94005250930786</t>
   </si>
   <si>
     <t xml:space="preserve">7.05382442474365</t>
@@ -1382,58 +1382,58 @@
     <t xml:space="preserve">7.10691738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15242576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11450290679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01589965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08416318893433</t>
+    <t xml:space="preserve">7.15242624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11450338363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01590061187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08416271209717</t>
   </si>
   <si>
     <t xml:space="preserve">7.04623889923096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09174776077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39513921737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35721445083618</t>
+    <t xml:space="preserve">7.09174823760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39513826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35721397399902</t>
   </si>
   <si>
     <t xml:space="preserve">7.34204530715942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12208700180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13725614547729</t>
+    <t xml:space="preserve">7.12208795547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13725662231445</t>
   </si>
   <si>
     <t xml:space="preserve">7.12967157363892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25102806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22827291488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20551872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19793510437012</t>
+    <t xml:space="preserve">7.2510290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22827386856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20551919937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1979341506958</t>
   </si>
   <si>
     <t xml:space="preserve">7.16759490966797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37996816635132</t>
+    <t xml:space="preserve">7.37996864318848</t>
   </si>
   <si>
     <t xml:space="preserve">7.4330620765686</t>
@@ -1442,49 +1442,49 @@
     <t xml:space="preserve">7.49374055862427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53924894332886</t>
+    <t xml:space="preserve">7.5392484664917</t>
   </si>
   <si>
     <t xml:space="preserve">7.54683303833008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75162267684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7971305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64543485641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69094514846802</t>
+    <t xml:space="preserve">7.75162172317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79713106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64543628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6909441947937</t>
   </si>
   <si>
     <t xml:space="preserve">7.57717180252075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4558162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51649379730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59992837905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50890970230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56200265884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58475732803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55441904067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47857046127319</t>
+    <t xml:space="preserve">7.45581579208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51649570465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59992742538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50890922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56200408935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58475637435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55441856384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47856998443604</t>
   </si>
   <si>
     <t xml:space="preserve">7.47098588943481</t>
@@ -1493,28 +1493,28 @@
     <t xml:space="preserve">7.44823122024536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70611333847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88814783096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25221538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61628341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49492835998535</t>
+    <t xml:space="preserve">7.7061128616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331697463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88814640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25221633911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61628437042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49492740631104</t>
   </si>
   <si>
     <t xml:space="preserve">8.17636775970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41908073425293</t>
+    <t xml:space="preserve">8.41908168792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.1187686920166</t>
@@ -1523,25 +1523,25 @@
     <t xml:space="preserve">8.08742237091064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93068838119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04040241241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9620361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2598295211792</t>
+    <t xml:space="preserve">7.93068981170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04040336608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96203565597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25982856750488</t>
   </si>
   <si>
     <t xml:space="preserve">8.02472877502441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86799669265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7347731590271</t>
+    <t xml:space="preserve">7.86799621582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73477268218994</t>
   </si>
   <si>
     <t xml:space="preserve">7.83664989471436</t>
@@ -1550,19 +1550,19 @@
     <t xml:space="preserve">7.82097578048706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91501569747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97770929336548</t>
+    <t xml:space="preserve">7.91501760482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97771024703979</t>
   </si>
   <si>
     <t xml:space="preserve">8.07174873352051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05607604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85232448577881</t>
+    <t xml:space="preserve">8.056077003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85232400894165</t>
   </si>
   <si>
     <t xml:space="preserve">8.40088844299316</t>
@@ -1571,61 +1571,61 @@
     <t xml:space="preserve">8.46358203887939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62031555175781</t>
+    <t xml:space="preserve">8.6203145980835</t>
   </si>
   <si>
     <t xml:space="preserve">8.30684947967529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16578960418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33819484710693</t>
+    <t xml:space="preserve">8.1657886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33819580078125</t>
   </si>
   <si>
     <t xml:space="preserve">8.21280860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27550220489502</t>
+    <t xml:space="preserve">8.27550315856934</t>
   </si>
   <si>
     <t xml:space="preserve">8.36954307556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15011596679688</t>
+    <t xml:space="preserve">8.15011501312256</t>
   </si>
   <si>
     <t xml:space="preserve">8.18146324157715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13444232940674</t>
+    <t xml:space="preserve">8.13444328308105</t>
   </si>
   <si>
     <t xml:space="preserve">8.22848224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43223476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99338293075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19713592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75828313827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89934253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82881259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88366937637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313943862915</t>
+    <t xml:space="preserve">8.43223571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99338340759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19713497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7582836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89934301376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82881307601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88366985321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313991546631</t>
   </si>
   <si>
     <t xml:space="preserve">7.6799168586731</t>
@@ -1637,52 +1637,52 @@
     <t xml:space="preserve">8.4165620803833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80530405044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68775415420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74261045455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00905704498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94636392593384</t>
+    <t xml:space="preserve">7.80530309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68775367736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74260902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00905609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94636344909668</t>
   </si>
   <si>
     <t xml:space="preserve">7.75044679641724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71909999847412</t>
+    <t xml:space="preserve">7.71910047531128</t>
   </si>
   <si>
     <t xml:space="preserve">8.10309600830078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82406806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37263202667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60773372650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48234558105469</t>
+    <t xml:space="preserve">8.82406711578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37263298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60773277282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.482346534729</t>
   </si>
   <si>
     <t xml:space="preserve">9.79581260681152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93687152862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87417793273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99956512451172</t>
+    <t xml:space="preserve">9.9368724822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87417984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99956607818604</t>
   </si>
   <si>
     <t xml:space="preserve">10.1562976837158</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">10.5011100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3757238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5481300354004</t>
+    <t xml:space="preserve">10.3757247924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5481309890747</t>
   </si>
   <si>
     <t xml:space="preserve">10.2189922332764</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">9.88985157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92119884490967</t>
+    <t xml:space="preserve">9.92119789123535</t>
   </si>
   <si>
     <t xml:space="preserve">9.73311805725098</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">9.57638549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96821784973145</t>
+    <t xml:space="preserve">9.96821880340576</t>
   </si>
   <si>
     <t xml:space="preserve">10.0309114456177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4854373931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.250337600708</t>
+    <t xml:space="preserve">10.4854364395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2503385543823</t>
   </si>
   <si>
     <t xml:space="preserve">10.0152378082275</t>
@@ -1751,19 +1751,19 @@
     <t xml:space="preserve">10.3130311965942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4384164810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6264972686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.657844543457</t>
+    <t xml:space="preserve">10.4384174346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6264963150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6578435897827</t>
   </si>
   <si>
     <t xml:space="preserve">10.6108236312866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5951509475708</t>
+    <t xml:space="preserve">10.5951519012451</t>
   </si>
   <si>
     <t xml:space="preserve">10.5794763565063</t>
@@ -1778,16 +1778,16 @@
     <t xml:space="preserve">10.9869832992554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9556350708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1280431747437</t>
+    <t xml:space="preserve">10.9556360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1280422210693</t>
   </si>
   <si>
     <t xml:space="preserve">11.0183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2377557754517</t>
+    <t xml:space="preserve">11.2377548217773</t>
   </si>
   <si>
     <t xml:space="preserve">11.1593885421753</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">11.0966958999634</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1750621795654</t>
+    <t xml:space="preserve">11.1750631332397</t>
   </si>
   <si>
     <t xml:space="preserve">11.1123695373535</t>
@@ -1805,43 +1805,43 @@
     <t xml:space="preserve">11.0810232162476</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9713096618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7989025115967</t>
+    <t xml:space="preserve">10.9713106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.798903465271</t>
   </si>
   <si>
     <t xml:space="preserve">10.0622587203979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0936040878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6860990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29426670074463</t>
+    <t xml:space="preserve">10.0936059951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68609809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29426574707031</t>
   </si>
   <si>
     <t xml:space="preserve">9.54503917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98080158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54194736480713</t>
+    <t xml:space="preserve">8.98080062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54194831848145</t>
   </si>
   <si>
     <t xml:space="preserve">7.31943082809448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50750923156738</t>
+    <t xml:space="preserve">7.5075101852417</t>
   </si>
   <si>
     <t xml:space="preserve">7.53885746002197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49183702468872</t>
+    <t xml:space="preserve">7.49183750152588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66733551025391</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">8.52627468109131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01214694976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45100021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10618591308594</t>
+    <t xml:space="preserve">9.01214790344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45099925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10618686676025</t>
   </si>
   <si>
     <t xml:space="preserve">8.93378067016602</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">9.38830661773682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88676071166992</t>
+    <t xml:space="preserve">8.88676166534424</t>
   </si>
   <si>
     <t xml:space="preserve">8.87108707427979</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">9.12186050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91810703277588</t>
+    <t xml:space="preserve">8.9181079864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.15320682525635</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">9.04349422454834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21590137481689</t>
+    <t xml:space="preserve">9.21590042114258</t>
   </si>
   <si>
     <t xml:space="preserve">8.96512699127197</t>
@@ -1904,25 +1904,25 @@
     <t xml:space="preserve">9.30298042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12407875061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01022911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68495082855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50604629516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70121479034424</t>
+    <t xml:space="preserve">9.12407779693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01023006439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68495178222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50604724884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70121383666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.18913269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92890930175781</t>
+    <t xml:space="preserve">8.92891025543213</t>
   </si>
   <si>
     <t xml:space="preserve">8.76626968383789</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">9.48188495635986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61199569702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2625532150269</t>
+    <t xml:space="preserve">9.6119966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2625541687012</t>
   </si>
   <si>
     <t xml:space="preserve">10.0673875808716</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">10.3113460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1812334060669</t>
+    <t xml:space="preserve">10.1812343597412</t>
   </si>
   <si>
     <t xml:space="preserve">10.2137622833252</t>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">10.2300252914429</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95353889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88848304748535</t>
+    <t xml:space="preserve">9.953537940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88848209381104</t>
   </si>
   <si>
     <t xml:space="preserve">9.69331550598145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1324434280396</t>
+    <t xml:space="preserve">10.1324424743652</t>
   </si>
   <si>
     <t xml:space="preserve">10.1974973678589</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">10.3276090621948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2462892532349</t>
+    <t xml:space="preserve">10.2462902069092</t>
   </si>
   <si>
     <t xml:space="preserve">10.555305480957</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">10.8480567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8805837631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8317909240723</t>
+    <t xml:space="preserve">10.8805828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8317918777466</t>
   </si>
   <si>
     <t xml:space="preserve">10.7992639541626</t>
@@ -2015,10 +2015,10 @@
     <t xml:space="preserve">10.9781675338745</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1245431900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1408081054688</t>
+    <t xml:space="preserve">11.1245441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1408071517944</t>
   </si>
   <si>
     <t xml:space="preserve">11.2871828079224</t>
@@ -2036,22 +2036,22 @@
     <t xml:space="preserve">11.4498224258423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4660863876343</t>
+    <t xml:space="preserve">11.4660873413086</t>
   </si>
   <si>
     <t xml:space="preserve">11.4823503494263</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3359746932983</t>
+    <t xml:space="preserve">11.3359756469727</t>
   </si>
   <si>
     <t xml:space="preserve">11.2058629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2221269607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8643198013306</t>
+    <t xml:space="preserve">11.2221260070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8643207550049</t>
   </si>
   <si>
     <t xml:space="preserve">10.539041519165</t>
@@ -2060,19 +2060,19 @@
     <t xml:space="preserve">10.522777557373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.701681137085</t>
+    <t xml:space="preserve">10.7016801834106</t>
   </si>
   <si>
     <t xml:space="preserve">10.8155279159546</t>
   </si>
   <si>
-    <t xml:space="preserve">10.604097366333</t>
+    <t xml:space="preserve">10.6040983200073</t>
   </si>
   <si>
     <t xml:space="preserve">10.7342081069946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.620361328125</t>
+    <t xml:space="preserve">10.6203603744507</t>
   </si>
   <si>
     <t xml:space="preserve">10.7179441452026</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">10.4577217102051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3764028549194</t>
+    <t xml:space="preserve">10.3764019012451</t>
   </si>
   <si>
     <t xml:space="preserve">10.571569442749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089288711548</t>
+    <t xml:space="preserve">10.4089298248291</t>
   </si>
   <si>
     <t xml:space="preserve">10.8968477249146</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">10.9944334030151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.669153213501</t>
+    <t xml:space="preserve">10.6691522598267</t>
   </si>
   <si>
     <t xml:space="preserve">10.7830009460449</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">10.9619035720825</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9456396102905</t>
+    <t xml:space="preserve">10.9456405639648</t>
   </si>
   <si>
     <t xml:space="preserve">11.2709178924561</t>
@@ -2126,25 +2126,25 @@
     <t xml:space="preserve">11.5799341201782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4172954559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.30344581604</t>
+    <t xml:space="preserve">11.4172945022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3034467697144</t>
   </si>
   <si>
     <t xml:space="preserve">9.9860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0836496353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4414567947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7504730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1570720672607</t>
+    <t xml:space="preserve">10.0836505889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4414577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7504720687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1570711135864</t>
   </si>
   <si>
     <t xml:space="preserve">11.1082792282104</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">10.9131126403809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2546548843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3522386550903</t>
+    <t xml:space="preserve">11.2546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.352237701416</t>
   </si>
   <si>
     <t xml:space="preserve">11.4010314941406</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">11.3197107315063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1733360290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0106964111328</t>
+    <t xml:space="preserve">11.1733350753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0106954574585</t>
   </si>
   <si>
     <t xml:space="preserve">11.5311431884766</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">11.7100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7425727844238</t>
+    <t xml:space="preserve">11.7425718307495</t>
   </si>
   <si>
     <t xml:space="preserve">12.019061088562</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">12.3118124008179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5882987976074</t>
+    <t xml:space="preserve">12.5882997512817</t>
   </si>
   <si>
     <t xml:space="preserve">12.1979637145996</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">11.8726854324341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.00279712677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8076295852661</t>
+    <t xml:space="preserve">12.0027961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8076286315918</t>
   </si>
   <si>
     <t xml:space="preserve">11.8564214706421</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">11.954005241394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9865322113037</t>
+    <t xml:space="preserve">11.986533164978</t>
   </si>
   <si>
     <t xml:space="preserve">12.100380897522</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">12.1816997528076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.116644859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2792844772339</t>
+    <t xml:space="preserve">12.1166458129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2792835235596</t>
   </si>
   <si>
     <t xml:space="preserve">12.4093961715698</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">12.4907150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8973150253296</t>
+    <t xml:space="preserve">12.8973140716553</t>
   </si>
   <si>
     <t xml:space="preserve">13.0111618041992</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">12.9786338806152</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8647861480713</t>
+    <t xml:space="preserve">12.864785194397</t>
   </si>
   <si>
     <t xml:space="preserve">12.7997303009033</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">12.8810501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1738014221191</t>
+    <t xml:space="preserve">13.1738023757935</t>
   </si>
   <si>
     <t xml:space="preserve">13.2713842391968</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">13.3527050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7267742156982</t>
+    <t xml:space="preserve">13.7267751693726</t>
   </si>
   <si>
     <t xml:space="preserve">13.8243589401245</t>
@@ -2282,22 +2282,22 @@
     <t xml:space="preserve">14.052056312561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.23095703125</t>
+    <t xml:space="preserve">14.2309579849243</t>
   </si>
   <si>
     <t xml:space="preserve">14.2634868621826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.214693069458</t>
+    <t xml:space="preserve">14.2146940231323</t>
   </si>
   <si>
     <t xml:space="preserve">13.9056797027588</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6129283905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8080940246582</t>
+    <t xml:space="preserve">13.6129274368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8080949783325</t>
   </si>
   <si>
     <t xml:space="preserve">13.8894157409668</t>
@@ -2312,10 +2312,10 @@
     <t xml:space="preserve">13.7918300628662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0032625198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9544706344604</t>
+    <t xml:space="preserve">14.0032615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9544715881348</t>
   </si>
   <si>
     <t xml:space="preserve">14.3448057174683</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">14.1496391296387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2472229003906</t>
+    <t xml:space="preserve">14.2472219467163</t>
   </si>
   <si>
     <t xml:space="preserve">14.4749164581299</t>
@@ -2333,58 +2333,58 @@
     <t xml:space="preserve">14.5579166412354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1927223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1595220565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1429252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2757215499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.375319480896</t>
+    <t xml:space="preserve">14.192723274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1595230102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1429243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2757205963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2923192977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3753185272217</t>
   </si>
   <si>
     <t xml:space="preserve">14.1097240447998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425212860107</t>
+    <t xml:space="preserve">14.2425222396851</t>
   </si>
   <si>
     <t xml:space="preserve">14.0765237808228</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2093229293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9935264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8109292984009</t>
+    <t xml:space="preserve">14.209321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9935274124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8109283447266</t>
   </si>
   <si>
     <t xml:space="preserve">14.3089199066162</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0599269866943</t>
+    <t xml:space="preserve">14.05992603302</t>
   </si>
   <si>
     <t xml:space="preserve">14.0101251602173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9769277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.043327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3255186080933</t>
+    <t xml:space="preserve">13.9769268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0433263778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3255195617676</t>
   </si>
   <si>
     <t xml:space="preserve">14.2259206771851</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">14.3421211242676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1761226654053</t>
+    <t xml:space="preserve">14.1761236190796</t>
   </si>
   <si>
     <t xml:space="preserve">13.9437274932861</t>
@@ -2402,13 +2402,13 @@
     <t xml:space="preserve">14.0931243896484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9603281021118</t>
+    <t xml:space="preserve">13.9603271484375</t>
   </si>
   <si>
     <t xml:space="preserve">14.3587188720703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2591218948364</t>
+    <t xml:space="preserve">14.2591228485107</t>
   </si>
   <si>
     <t xml:space="preserve">14.5081157684326</t>
@@ -2426,34 +2426,34 @@
     <t xml:space="preserve">14.7737102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">14.690712928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7405138015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9397077560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1057043075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3214998245239</t>
+    <t xml:space="preserve">14.6907138824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7405128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9397087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1057052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3214988708496</t>
   </si>
   <si>
     <t xml:space="preserve">15.1721048355103</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8899097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3713006973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.703293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5372972488403</t>
+    <t xml:space="preserve">14.8899087905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3712997436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7032918930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.537296295166</t>
   </si>
   <si>
     <t xml:space="preserve">15.387900352478</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">15.2883014678955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2717008590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0725059509277</t>
+    <t xml:space="preserve">15.2717018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0725049972534</t>
   </si>
   <si>
     <t xml:space="preserve">15.2219018936157</t>
@@ -2477,22 +2477,22 @@
     <t xml:space="preserve">14.9895067214966</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8567094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8235111236572</t>
+    <t xml:space="preserve">14.85671043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8235101699829</t>
   </si>
   <si>
     <t xml:space="preserve">14.7903108596802</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1389045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9729080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8733100891113</t>
+    <t xml:space="preserve">15.1389055252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9729089736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.873309135437</t>
   </si>
   <si>
     <t xml:space="preserve">14.8069105148315</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">13.8607301712036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6947317123413</t>
+    <t xml:space="preserve">13.6947326660156</t>
   </si>
   <si>
     <t xml:space="preserve">13.7113332748413</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">14.5745153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.541316986084</t>
+    <t xml:space="preserve">14.5413160324097</t>
   </si>
   <si>
     <t xml:space="preserve">14.4251165390015</t>
@@ -2528,64 +2528,64 @@
     <t xml:space="preserve">14.3919191360474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4708976745605</t>
+    <t xml:space="preserve">15.4708986282349</t>
   </si>
   <si>
     <t xml:space="preserve">15.2053022384644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.022705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4915151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8275299072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7777309417725</t>
+    <t xml:space="preserve">15.0227069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4915161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8275289535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7777318954468</t>
   </si>
   <si>
     <t xml:space="preserve">13.6449337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5287342071533</t>
+    <t xml:space="preserve">13.7445306777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5287351608276</t>
   </si>
   <si>
     <t xml:space="preserve">13.5619354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4125385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1137437820435</t>
+    <t xml:space="preserve">13.4125375747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1137447357178</t>
   </si>
   <si>
     <t xml:space="preserve">13.2797403335571</t>
   </si>
   <si>
-    <t xml:space="preserve">13.362738609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5121364593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5951328277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6117334365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1303434371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3295402526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4955368041992</t>
+    <t xml:space="preserve">13.3627395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5121374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5951337814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6117343902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1303424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3295392990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4955358505249</t>
   </si>
   <si>
     <t xml:space="preserve">13.080545425415</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">12.7983493804932</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4497575759888</t>
+    <t xml:space="preserve">12.4497566223145</t>
   </si>
   <si>
     <t xml:space="preserve">12.3003587722778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7153511047363</t>
+    <t xml:space="preserve">12.7153520584106</t>
   </si>
   <si>
     <t xml:space="preserve">12.4331569671631</t>
@@ -2621,10 +2621,10 @@
     <t xml:space="preserve">12.3501586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0679636001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8521680831909</t>
+    <t xml:space="preserve">12.067964553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8521671295166</t>
   </si>
   <si>
     <t xml:space="preserve">11.6695728302002</t>
@@ -2642,25 +2642,25 @@
     <t xml:space="preserve">11.7027721405029</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7857704162598</t>
+    <t xml:space="preserve">11.7857694625854</t>
   </si>
   <si>
     <t xml:space="preserve">11.5367746353149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3209800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1715812683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.221381187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8395891189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2088003158569</t>
+    <t xml:space="preserve">11.3209791183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1715822219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2213821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8395881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2088012695312</t>
   </si>
   <si>
     <t xml:space="preserve">10.6735916137695</t>
@@ -2672,106 +2672,106 @@
     <t xml:space="preserve">10.258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1922016143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97640514373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54481315612793</t>
+    <t xml:space="preserve">10.1922006607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97640609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54481410980225</t>
   </si>
   <si>
     <t xml:space="preserve">9.56141376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36221790313721</t>
+    <t xml:space="preserve">9.36221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">9.62781238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32901763916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52821445465088</t>
+    <t xml:space="preserve">9.32901859283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52821350097656</t>
   </si>
   <si>
     <t xml:space="preserve">10.0096044540405</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39541721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.391396522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6071920394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3083982467651</t>
+    <t xml:space="preserve">9.39541625976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3913974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6071929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3083972930908</t>
   </si>
   <si>
     <t xml:space="preserve">10.4909954071045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1756019592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.109203338623</t>
+    <t xml:space="preserve">10.1756010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1092023849487</t>
   </si>
   <si>
     <t xml:space="preserve">10.1424016952515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0594024658203</t>
+    <t xml:space="preserve">10.0594034194946</t>
   </si>
   <si>
     <t xml:space="preserve">9.86020851135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89340591430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69421100616455</t>
+    <t xml:space="preserve">9.89340686798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69421005249023</t>
   </si>
   <si>
     <t xml:space="preserve">9.61121273040771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17962074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27921962738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37881755828857</t>
+    <t xml:space="preserve">9.17962169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27921867370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37881660461426</t>
   </si>
   <si>
     <t xml:space="preserve">9.19622039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29581832885742</t>
+    <t xml:space="preserve">9.29581737518311</t>
   </si>
   <si>
     <t xml:space="preserve">9.12982177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42861557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77720928192139</t>
+    <t xml:space="preserve">9.42861461639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77720832824707</t>
   </si>
   <si>
     <t xml:space="preserve">9.64441108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0262050628662</t>
+    <t xml:space="preserve">10.0262041091919</t>
   </si>
   <si>
     <t xml:space="preserve">10.5407934188843</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4577951431274</t>
+    <t xml:space="preserve">10.4577960968018</t>
   </si>
   <si>
     <t xml:space="preserve">10.0760040283203</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">9.66899490356445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70334434509277</t>
+    <t xml:space="preserve">9.70334339141846</t>
   </si>
   <si>
     <t xml:space="preserve">9.7205171585083</t>
@@ -2792,28 +2792,28 @@
     <t xml:space="preserve">10.0639991760254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0983476638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2529134750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0811719894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3559579849243</t>
+    <t xml:space="preserve">10.0983467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2529125213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85790920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0811729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.35595703125</t>
   </si>
   <si>
     <t xml:space="preserve">10.2700872421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6479158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7681350708008</t>
+    <t xml:space="preserve">10.6479167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7681341171265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9570503234863</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">11.1631383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0600938796997</t>
+    <t xml:space="preserve">11.060094833374</t>
   </si>
   <si>
     <t xml:space="preserve">11.1803121566772</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">10.0296506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0124769210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.390305519104</t>
+    <t xml:space="preserve">10.0124759674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3903064727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1498689651489</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">10.1326951980591</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97812747955322</t>
+    <t xml:space="preserve">9.97812843322754</t>
   </si>
   <si>
     <t xml:space="preserve">9.87508392333984</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">10.2872610092163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2013921737671</t>
+    <t xml:space="preserve">10.2013912200928</t>
   </si>
   <si>
     <t xml:space="preserve">10.3044357299805</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">10.1842164993286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0468254089355</t>
+    <t xml:space="preserve">10.0468244552612</t>
   </si>
   <si>
     <t xml:space="preserve">10.5620460510254</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">10.4418277740479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7166128158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.459002494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5105237960815</t>
+    <t xml:space="preserve">10.7166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5105228424072</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509613037109</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">10.1155204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7548656463623</t>
+    <t xml:space="preserve">9.75486469268799</t>
   </si>
   <si>
     <t xml:space="preserve">9.61747264862061</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">9.51442813873291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63464736938477</t>
+    <t xml:space="preserve">9.63464832305908</t>
   </si>
   <si>
     <t xml:space="preserve">9.80638790130615</t>
@@ -2942,10 +2942,10 @@
     <t xml:space="preserve">9.39420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22246932983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32551383972168</t>
+    <t xml:space="preserve">9.2224702835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.325514793396</t>
   </si>
   <si>
     <t xml:space="preserve">9.25681781768799</t>
@@ -2957,19 +2957,19 @@
     <t xml:space="preserve">9.0850772857666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54877758026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56595039367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58312511444092</t>
+    <t xml:space="preserve">9.54877662658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56595134735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58312606811523</t>
   </si>
   <si>
     <t xml:space="preserve">9.65182113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82356071472168</t>
+    <t xml:space="preserve">9.823561668396</t>
   </si>
   <si>
     <t xml:space="preserve">10.3387832641602</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">11.0429201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8883533477783</t>
+    <t xml:space="preserve">10.8883543014526</t>
   </si>
   <si>
     <t xml:space="preserve">10.9398756027222</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">12.0733642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4683675765991</t>
+    <t xml:space="preserve">12.4683666229248</t>
   </si>
   <si>
     <t xml:space="preserve">12.5027151107788</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">12.485541343689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6401071548462</t>
+    <t xml:space="preserve">12.6401081085205</t>
   </si>
   <si>
     <t xml:space="preserve">12.2451038360596</t>
@@ -3116,10 +3116,10 @@
     <t xml:space="preserve">13.3442440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6362037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6018543243408</t>
+    <t xml:space="preserve">13.6362028121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6018552780151</t>
   </si>
   <si>
     <t xml:space="preserve">13.550332069397</t>
@@ -3128,16 +3128,16 @@
     <t xml:space="preserve">13.5675067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4644632339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3957653045654</t>
+    <t xml:space="preserve">13.4644622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3957662582397</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.619029045105</t>
+    <t xml:space="preserve">13.6190280914307</t>
   </si>
   <si>
     <t xml:space="preserve">14.0827283859253</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">13.7048988342285</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7220735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8766403198242</t>
+    <t xml:space="preserve">13.7220726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8766393661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.6151237487793</t>
@@ -3164,13 +3164,13 @@
     <t xml:space="preserve">14.6494722366333</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8040390014648</t>
+    <t xml:space="preserve">14.8040380477905</t>
   </si>
   <si>
     <t xml:space="preserve">14.6838207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7868642807007</t>
+    <t xml:space="preserve">14.7868633270264</t>
   </si>
   <si>
     <t xml:space="preserve">14.7181673049927</t>
@@ -3179,43 +3179,43 @@
     <t xml:space="preserve">15.0101270675659</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0616502761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.387957572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1990423202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2505664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818685531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.216215133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9757795333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9242553710938</t>
+    <t xml:space="preserve">15.0616512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3879566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2505645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2162160873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9757804870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9242563247681</t>
   </si>
   <si>
     <t xml:space="preserve">14.4262094497681</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3918619155884</t>
+    <t xml:space="preserve">14.3918609619141</t>
   </si>
   <si>
     <t xml:space="preserve">14.9586057662964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5464296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1131706237793</t>
+    <t xml:space="preserve">14.5464286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1131715774536</t>
   </si>
   <si>
     <t xml:space="preserve">15.1303462982178</t>
@@ -3227,34 +3227,34 @@
     <t xml:space="preserve">15.2677392959595</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4223041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9031801223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9375267028809</t>
+    <t xml:space="preserve">15.4223031997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9031782150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9375257492065</t>
   </si>
   <si>
     <t xml:space="preserve">16.1436138153076</t>
   </si>
   <si>
-    <t xml:space="preserve">15.851655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547004699707</t>
+    <t xml:space="preserve">15.8516550064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9546995162964</t>
   </si>
   <si>
     <t xml:space="preserve">15.7829599380493</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7142629623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5253486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5596990585327</t>
+    <t xml:space="preserve">15.7142639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5253496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5596981048584</t>
   </si>
   <si>
     <t xml:space="preserve">14.8383884429932</t>
@@ -3266,31 +3266,31 @@
     <t xml:space="preserve">14.3059902191162</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2888164520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5120782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6323003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7009954452515</t>
+    <t xml:space="preserve">14.2888154983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5120792388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6322994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7009944915771</t>
   </si>
   <si>
     <t xml:space="preserve">14.5807752609253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5292549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3746871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1431255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2678136825562</t>
+    <t xml:space="preserve">14.5292539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3746862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1431245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2678127288818</t>
   </si>
   <si>
     <t xml:space="preserve">14.321249961853</t>
@@ -3302,10 +3302,10 @@
     <t xml:space="preserve">14.6774997711182</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6062498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0540618896484</t>
+    <t xml:space="preserve">14.6062488555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0540628433228</t>
   </si>
   <si>
     <t xml:space="preserve">14.0362501144409</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">14.0184373855591</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0006256103516</t>
+    <t xml:space="preserve">14.0006246566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.733437538147</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">13.875937461853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2856254577637</t>
+    <t xml:space="preserve">14.285626411438</t>
   </si>
   <si>
     <t xml:space="preserve">14.0896873474121</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">14.1609373092651</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1253118515015</t>
+    <t xml:space="preserve">14.1253128051758</t>
   </si>
   <si>
     <t xml:space="preserve">14.4459371566772</t>
@@ -3347,13 +3347,13 @@
     <t xml:space="preserve">14.178750038147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9828119277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9293756484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6978130340576</t>
+    <t xml:space="preserve">13.9828128814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9293746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6978120803833</t>
   </si>
   <si>
     <t xml:space="preserve">13.6799993515015</t>
@@ -3368,16 +3368,16 @@
     <t xml:space="preserve">13.5731248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8403129577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8581247329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9115629196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4840621948242</t>
+    <t xml:space="preserve">13.8403120040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8581256866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9115619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4840631484985</t>
   </si>
   <si>
     <t xml:space="preserve">13.1278123855591</t>
@@ -3392,13 +3392,13 @@
     <t xml:space="preserve">13.8046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7690629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8225002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3034372329712</t>
+    <t xml:space="preserve">13.7690620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8225011825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3034362792969</t>
   </si>
   <si>
     <t xml:space="preserve">14.3924999237061</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">14.624062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4993753433228</t>
+    <t xml:space="preserve">14.4993762969971</t>
   </si>
   <si>
     <t xml:space="preserve">14.5349998474121</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">14.25</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0718755722046</t>
+    <t xml:space="preserve">14.0718746185303</t>
   </si>
   <si>
     <t xml:space="preserve">13.359375</t>
@@ -3431,22 +3431,22 @@
     <t xml:space="preserve">13.5018749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5196876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2321863174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6265630722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812496185303</t>
+    <t xml:space="preserve">13.5196886062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2321872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6265621185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812505722046</t>
   </si>
   <si>
     <t xml:space="preserve">13.0565624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1099996566772</t>
+    <t xml:space="preserve">13.1100006103516</t>
   </si>
   <si>
     <t xml:space="preserve">12.842812538147</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">12.8249998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7181253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221881866455</t>
+    <t xml:space="preserve">12.7181243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221872329712</t>
   </si>
   <si>
     <t xml:space="preserve">12.397500038147</t>
@@ -3479,25 +3479,25 @@
     <t xml:space="preserve">12.4865627288818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2906255722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2193756103516</t>
+    <t xml:space="preserve">12.2906246185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2193746566772</t>
   </si>
   <si>
     <t xml:space="preserve">12.2550001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1481256484985</t>
+    <t xml:space="preserve">12.1481246948242</t>
   </si>
   <si>
     <t xml:space="preserve">12.1659374237061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1303119659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165630340576</t>
+    <t xml:space="preserve">12.1303129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165620803833</t>
   </si>
   <si>
     <t xml:space="preserve">11.578125</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">11.3287506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2931261062622</t>
+    <t xml:space="preserve">11.2931251525879</t>
   </si>
   <si>
     <t xml:space="preserve">11.1328125</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">10.9012498855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9190635681152</t>
+    <t xml:space="preserve">10.9190626144409</t>
   </si>
   <si>
     <t xml:space="preserve">11.061562538147</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">11.0971879959106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1684379577637</t>
+    <t xml:space="preserve">11.1684370040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.204062461853</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">11.4534368515015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8631238937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0768756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453130722046</t>
+    <t xml:space="preserve">11.8631248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0768747329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453121185303</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809375762939</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">11.9878120422363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2015619277954</t>
+    <t xml:space="preserve">12.2015628814697</t>
   </si>
   <si>
     <t xml:space="preserve">12.6468753814697</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">12.7003126144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3618745803833</t>
+    <t xml:space="preserve">12.3618755340576</t>
   </si>
   <si>
     <t xml:space="preserve">12.3440628051758</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">12.094687461853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0590620040894</t>
+    <t xml:space="preserve">12.0590629577637</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056247711182</t>
@@ -3644,19 +3644,19 @@
     <t xml:space="preserve">11.4178123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4356250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7384376525879</t>
+    <t xml:space="preserve">11.4356260299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7384386062622</t>
   </si>
   <si>
     <t xml:space="preserve">11.7562494277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5959386825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274993896484</t>
+    <t xml:space="preserve">11.5959377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8275003433228</t>
   </si>
   <si>
     <t xml:space="preserve">11.7206249237061</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">11.2396869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5425004959106</t>
+    <t xml:space="preserve">11.5424995422363</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028131484985</t>
@@ -3686,13 +3686,13 @@
     <t xml:space="preserve">11.9700002670288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5246877670288</t>
+    <t xml:space="preserve">11.5246868133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.9724998474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1149988174438</t>
+    <t xml:space="preserve">11.1149997711182</t>
   </si>
   <si>
     <t xml:space="preserve">11.3382139205933</t>
@@ -4386,6 +4386,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.51999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40000009536743</t>
   </si>
 </sst>
 </file>
@@ -69750,7 +69753,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6912268518</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>63864</v>
@@ -69771,6 +69774,32 @@
         <v>1449</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6912847222</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>96708</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>7.55999994277954</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>7.40999984741211</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="1464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="1465">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04141712188721</t>
+    <t xml:space="preserve">4.04141759872437</t>
   </si>
   <si>
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447891235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93978953361511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8279972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78057193756104</t>
+    <t xml:space="preserve">4.02447938919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93978929519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82799816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7805712223053</t>
   </si>
   <si>
     <t xml:space="preserve">3.70943164825439</t>
@@ -62,85 +62,85 @@
     <t xml:space="preserve">3.75685834884644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74330806732178</t>
+    <t xml:space="preserve">3.74330759048462</t>
   </si>
   <si>
     <t xml:space="preserve">3.80089664459229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77040839195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571853637695</t>
+    <t xml:space="preserve">3.77040863037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571877479553</t>
   </si>
   <si>
     <t xml:space="preserve">3.66539239883423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56376481056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65184235572815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72636985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70265698432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65861797332764</t>
+    <t xml:space="preserve">3.56376457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65184211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72636938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70265674591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6586172580719</t>
   </si>
   <si>
     <t xml:space="preserve">3.6924934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74669599533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5976402759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59086561203003</t>
+    <t xml:space="preserve">3.74669623374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59764051437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59086537361145</t>
   </si>
   <si>
     <t xml:space="preserve">3.58408999443054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49601221084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46213674545288</t>
+    <t xml:space="preserve">3.49601173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4621365070343</t>
   </si>
   <si>
     <t xml:space="preserve">3.51633787155151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38760900497437</t>
+    <t xml:space="preserve">3.38760852813721</t>
   </si>
   <si>
     <t xml:space="preserve">3.40793490409851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50956273078918</t>
+    <t xml:space="preserve">3.50956296920776</t>
   </si>
   <si>
     <t xml:space="preserve">3.55698943138123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56715202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61119055747986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57731509208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54682660102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52650117874146</t>
+    <t xml:space="preserve">3.56715226173401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6111912727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57731485366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54682636260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52650046348572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50278782844543</t>
@@ -149,88 +149,88 @@
     <t xml:space="preserve">3.56037664413452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58070230484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60102891921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54343843460083</t>
+    <t xml:space="preserve">3.58070206642151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60102844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54343914985657</t>
   </si>
   <si>
     <t xml:space="preserve">3.57053995132446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64506649971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78734707832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84154868125916</t>
+    <t xml:space="preserve">3.64506697654724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78734683990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84154891967773</t>
   </si>
   <si>
     <t xml:space="preserve">3.86526131629944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85171175003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92962551116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93640112876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607594490051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90252494812012</t>
+    <t xml:space="preserve">3.85171103477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92962574958801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93640065193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607570648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90252542495728</t>
   </si>
   <si>
     <t xml:space="preserve">3.89575052261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92285060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9093005657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9702775478363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87881135940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85848641395569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94317650794983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89913749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94656443595886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95672655105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96350264549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91268849372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97366523742676</t>
+    <t xml:space="preserve">3.92285132408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90930080413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97027730941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87881231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85848689079285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94317698478699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89913821220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94656419754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95672702789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96350288391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91268801689148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97366547584534</t>
   </si>
   <si>
     <t xml:space="preserve">3.91946339607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87203621864319</t>
+    <t xml:space="preserve">3.87203645706177</t>
   </si>
   <si>
     <t xml:space="preserve">3.88704800605774</t>
@@ -239,34 +239,34 @@
     <t xml:space="preserve">3.8729133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85877871513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83757710456848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86231279373169</t>
+    <t xml:space="preserve">3.85877847671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83757591247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86231207847595</t>
   </si>
   <si>
     <t xml:space="preserve">3.87644696235657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89411544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90118288993835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058184623718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94358706474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95418763160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96125602722168</t>
+    <t xml:space="preserve">3.89411568641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90118217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8905816078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9435863494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95418834686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96125555038452</t>
   </si>
   <si>
     <t xml:space="preserve">4.01426029205322</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">4.08846759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05666446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03899574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305772781372</t>
+    <t xml:space="preserve">4.05666399002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03899621963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305844306946</t>
   </si>
   <si>
     <t xml:space="preserve">4.00719356536865</t>
@@ -296,43 +296,43 @@
     <t xml:space="preserve">3.97185611724854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80223917961121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78103756904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75630259513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74923396110535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90471649169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92238450050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065450668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03546285629272</t>
+    <t xml:space="preserve">3.80223989486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78103733062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75630187988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74923467636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9047167301178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9223849773407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065474510193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03546237945557</t>
   </si>
   <si>
     <t xml:space="preserve">3.75983572006226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80930709838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83050918579102</t>
+    <t xml:space="preserve">3.80930614471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83050847053528</t>
   </si>
   <si>
     <t xml:space="preserve">3.86937975883484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82344126701355</t>
+    <t xml:space="preserve">3.82344102859497</t>
   </si>
   <si>
     <t xml:space="preserve">3.80577349662781</t>
@@ -341,73 +341,70 @@
     <t xml:space="preserve">3.84110975265503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8517107963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81637477874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86584520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89764833450317</t>
+    <t xml:space="preserve">3.81637382507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86584568023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89764904975891</t>
   </si>
   <si>
     <t xml:space="preserve">3.93651914596558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90825057029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91531753540039</t>
+    <t xml:space="preserve">3.90825080871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91531777381897</t>
   </si>
   <si>
     <t xml:space="preserve">3.97892379760742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00012540817261</t>
+    <t xml:space="preserve">4.00012588500977</t>
   </si>
   <si>
     <t xml:space="preserve">4.02132749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95772171020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84464383125305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81284070014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77043652534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76336884498596</t>
+    <t xml:space="preserve">3.9577214717865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84464406967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81284046173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77043676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690316200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76336932182312</t>
   </si>
   <si>
     <t xml:space="preserve">3.74570107460022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72449898719788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77397012710571</t>
+    <t xml:space="preserve">3.7244987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77397036552429</t>
   </si>
   <si>
     <t xml:space="preserve">3.78810501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81990814208984</t>
+    <t xml:space="preserve">3.81990790367126</t>
   </si>
   <si>
     <t xml:space="preserve">3.72803211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73863339424133</t>
+    <t xml:space="preserve">3.73863315582275</t>
   </si>
   <si>
     <t xml:space="preserve">3.73156595230103</t>
@@ -416,55 +413,55 @@
     <t xml:space="preserve">3.73509979248047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65382528305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63968992233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66089224815369</t>
+    <t xml:space="preserve">3.65382480621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63969039916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66089200973511</t>
   </si>
   <si>
     <t xml:space="preserve">3.618488073349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61142134666443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62555575370789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6149537563324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64675760269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74216675758362</t>
+    <t xml:space="preserve">3.61142086982727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62555599212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61495447158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64675712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74216771125793</t>
   </si>
   <si>
     <t xml:space="preserve">3.91885137557983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98599123954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99659180641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87997984886169</t>
+    <t xml:space="preserve">3.98599147796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99659204483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87998080253601</t>
   </si>
   <si>
     <t xml:space="preserve">3.88351440429688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79517245292664</t>
+    <t xml:space="preserve">3.79517149925232</t>
   </si>
   <si>
     <t xml:space="preserve">3.82697510719299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79163813591003</t>
+    <t xml:space="preserve">3.79163837432861</t>
   </si>
   <si>
     <t xml:space="preserve">3.84817719459534</t>
@@ -473,22 +470,22 @@
     <t xml:space="preserve">3.71036410331726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85524487495422</t>
+    <t xml:space="preserve">3.85524463653564</t>
   </si>
   <si>
     <t xml:space="preserve">4.03192853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04253005981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08493375778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09906816482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05313062667847</t>
+    <t xml:space="preserve">4.04252958297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08493423461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09906911849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05313110351562</t>
   </si>
   <si>
     <t xml:space="preserve">4.04959678649902</t>
@@ -497,16 +494,16 @@
     <t xml:space="preserve">4.09200143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10967016220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07786655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07433319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04606294631958</t>
+    <t xml:space="preserve">4.10966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07786703109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07433271408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04606342315674</t>
   </si>
   <si>
     <t xml:space="preserve">4.0637321472168</t>
@@ -515,31 +512,31 @@
     <t xml:space="preserve">4.10613584518433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1026029586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13440608978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12733793258667</t>
+    <t xml:space="preserve">4.10260248184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1344051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12733840942383</t>
   </si>
   <si>
     <t xml:space="preserve">4.16974210739136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18387651443481</t>
+    <t xml:space="preserve">4.18387699127197</t>
   </si>
   <si>
     <t xml:space="preserve">4.15914154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24041557312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21567964553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27575302124023</t>
+    <t xml:space="preserve">4.24041604995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21568059921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27575254440308</t>
   </si>
   <si>
     <t xml:space="preserve">4.34642601013184</t>
@@ -548,55 +545,55 @@
     <t xml:space="preserve">4.36762809753418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35349369049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31108903884888</t>
+    <t xml:space="preserve">4.35349321365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31108951568604</t>
   </si>
   <si>
     <t xml:space="preserve">4.30402231216431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38176345825195</t>
+    <t xml:space="preserve">4.38176298141479</t>
   </si>
   <si>
     <t xml:space="preserve">4.50897550582886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72806358337402</t>
+    <t xml:space="preserve">4.72806406021118</t>
   </si>
   <si>
     <t xml:space="preserve">4.91181468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94715166091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19450902938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22277927398682</t>
+    <t xml:space="preserve">4.94715213775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19450950622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22277879714966</t>
   </si>
   <si>
     <t xml:space="preserve">5.2298469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22631311416626</t>
+    <t xml:space="preserve">5.2263126373291</t>
   </si>
   <si>
     <t xml:space="preserve">5.09203243255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07436370849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08496618270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11676788330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10616779327393</t>
+    <t xml:space="preserve">5.07436466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08496522903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11676836013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10616683959961</t>
   </si>
   <si>
     <t xml:space="preserve">5.15210580825806</t>
@@ -605,52 +602,52 @@
     <t xml:space="preserve">5.15917253494263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1733078956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19097566604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14503812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13090372085571</t>
+    <t xml:space="preserve">5.17330741882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1909761428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14503765106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13090324401855</t>
   </si>
   <si>
     <t xml:space="preserve">5.24751472473145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26871633529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59734869003296</t>
+    <t xml:space="preserve">5.26871681213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59734916687012</t>
   </si>
   <si>
     <t xml:space="preserve">5.51254081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35705900192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47720384597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37119293212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44186687469482</t>
+    <t xml:space="preserve">5.35705852508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47720432281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37119388580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44186735153198</t>
   </si>
   <si>
     <t xml:space="preserve">5.53020906448364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61199712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65216064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6886739730835</t>
+    <t xml:space="preserve">5.61199760437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65216112136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68867349624634</t>
   </si>
   <si>
     <t xml:space="preserve">5.6229510307312</t>
@@ -659,10 +656,10 @@
     <t xml:space="preserve">5.619300365448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59739255905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42213153839111</t>
+    <t xml:space="preserve">5.59739208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42213201522827</t>
   </si>
   <si>
     <t xml:space="preserve">5.41848039627075</t>
@@ -671,43 +668,43 @@
     <t xml:space="preserve">5.55357694625854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56087923049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49880886077881</t>
+    <t xml:space="preserve">5.56087970733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49880838394165</t>
   </si>
   <si>
     <t xml:space="preserve">5.4622950553894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55722904205322</t>
+    <t xml:space="preserve">5.55722856521606</t>
   </si>
   <si>
     <t xml:space="preserve">5.45499324798584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36736297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37466526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43308591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40387535095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47690010070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4476900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48055171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49515676498413</t>
+    <t xml:space="preserve">5.36736249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37466478347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43308544158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40387487411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47690057754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44769096374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48055219650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49515628814697</t>
   </si>
   <si>
     <t xml:space="preserve">5.54627418518066</t>
@@ -716,7 +713,7 @@
     <t xml:space="preserve">5.60104370117188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41117763519287</t>
+    <t xml:space="preserve">5.41117811203003</t>
   </si>
   <si>
     <t xml:space="preserve">5.51341342926025</t>
@@ -728,7 +725,7 @@
     <t xml:space="preserve">5.45134210586548</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61564922332764</t>
+    <t xml:space="preserve">5.61564874649048</t>
   </si>
   <si>
     <t xml:space="preserve">5.50611114501953</t>
@@ -737,19 +734,19 @@
     <t xml:space="preserve">5.34545516967773</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37101364135742</t>
+    <t xml:space="preserve">5.37101411819458</t>
   </si>
   <si>
     <t xml:space="preserve">5.31259346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28703451156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15558958053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12637901306152</t>
+    <t xml:space="preserve">5.28703498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15558862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12637853622437</t>
   </si>
   <si>
     <t xml:space="preserve">5.27242946624756</t>
@@ -785,37 +782,37 @@
     <t xml:space="preserve">5.44038772583008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48420333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35275793075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48785448074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50245904922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57183313369751</t>
+    <t xml:space="preserve">5.48420286178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35275745391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48785400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50245952606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57183361053467</t>
   </si>
   <si>
     <t xml:space="preserve">5.57913589477539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56453084945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52071571350098</t>
+    <t xml:space="preserve">5.5645318031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52071523666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.5389723777771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65581274032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58643913269043</t>
+    <t xml:space="preserve">5.65581178665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58643817901611</t>
   </si>
   <si>
     <t xml:space="preserve">5.57548475265503</t>
@@ -827,7 +824,7 @@
     <t xml:space="preserve">5.53166961669922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60469532012939</t>
+    <t xml:space="preserve">5.60469484329224</t>
   </si>
   <si>
     <t xml:space="preserve">5.59008979797363</t>
@@ -836,61 +833,61 @@
     <t xml:space="preserve">5.75804805755615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79456090927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92965841293335</t>
+    <t xml:space="preserve">5.79456043243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92965745925903</t>
   </si>
   <si>
     <t xml:space="preserve">5.94426298141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99903202056885</t>
+    <t xml:space="preserve">5.99903154373169</t>
   </si>
   <si>
     <t xml:space="preserve">5.93696069717407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98807764053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83107376098633</t>
+    <t xml:space="preserve">5.98807811737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83107280731201</t>
   </si>
   <si>
     <t xml:space="preserve">5.88584280014038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83472442626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9588680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76900243759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91140174865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83837556838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84202718734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87123727798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78360748291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85298109054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7032790184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82742214202881</t>
+    <t xml:space="preserve">5.83472490310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95886850357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76900196075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140127182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83837604522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84202766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8712363243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.783607006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85298156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70327854156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82742261886597</t>
   </si>
   <si>
     <t xml:space="preserve">5.86393451690674</t>
@@ -902,55 +899,55 @@
     <t xml:space="preserve">5.72883796691895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68502283096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66676712036133</t>
+    <t xml:space="preserve">5.68502330780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66676664352417</t>
   </si>
   <si>
     <t xml:space="preserve">5.88949298858643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78725862503052</t>
+    <t xml:space="preserve">5.78725814819336</t>
   </si>
   <si>
     <t xml:space="preserve">5.77995586395264</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73614072799683</t>
+    <t xml:space="preserve">5.73613977432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.6083459854126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63025426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53532123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76169967651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62660217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68137216567993</t>
+    <t xml:space="preserve">5.63025379180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53532075881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76169872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62660264968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68137168884277</t>
   </si>
   <si>
     <t xml:space="preserve">5.73979139328003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76535081863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80916500091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80551481246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82377004623413</t>
+    <t xml:space="preserve">5.76535034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80916595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80551433563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82377099990845</t>
   </si>
   <si>
     <t xml:space="preserve">5.87854051589966</t>
@@ -959,10 +956,10 @@
     <t xml:space="preserve">5.82011938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90409851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600584030151</t>
+    <t xml:space="preserve">5.90409898757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600631713867</t>
   </si>
   <si>
     <t xml:space="preserve">5.92235469818115</t>
@@ -971,34 +968,34 @@
     <t xml:space="preserve">5.95156478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02459049224854</t>
+    <t xml:space="preserve">6.02459001541138</t>
   </si>
   <si>
     <t xml:space="preserve">6.06110429763794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00998544692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09031391143799</t>
+    <t xml:space="preserve">6.00998449325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09031343460083</t>
   </si>
   <si>
     <t xml:space="preserve">6.2290620803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18524694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03189325332642</t>
+    <t xml:space="preserve">6.18524646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03189277648926</t>
   </si>
   <si>
     <t xml:space="preserve">6.0391960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04649877548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25096988677979</t>
+    <t xml:space="preserve">6.04649829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25096940994263</t>
   </si>
   <si>
     <t xml:space="preserve">6.20715427398682</t>
@@ -1010,43 +1007,43 @@
     <t xml:space="preserve">6.12682628631592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79821252822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72518682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96617078781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00268268585205</t>
+    <t xml:space="preserve">5.7982120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72518730163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96617031097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00268316268921</t>
   </si>
   <si>
     <t xml:space="preserve">5.89314460754395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84932994842529</t>
+    <t xml:space="preserve">5.84932947158813</t>
   </si>
   <si>
     <t xml:space="preserve">5.97347259521484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99537992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11952304840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15603590011597</t>
+    <t xml:space="preserve">5.99538040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15603685379028</t>
   </si>
   <si>
     <t xml:space="preserve">6.10491800308228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98077535629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90044736862183</t>
+    <t xml:space="preserve">5.98077440261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90044784545898</t>
   </si>
   <si>
     <t xml:space="preserve">6.14873361587524</t>
@@ -1055,43 +1052,46 @@
     <t xml:space="preserve">6.09761619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0538010597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07570838928223</t>
+    <t xml:space="preserve">6.05380058288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07570791244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.08301115036011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17794418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17064046859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2436671257019</t>
+    <t xml:space="preserve">6.17794370651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17064094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24366617202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28017997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38636541366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31810331344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23467063903809</t>
   </si>
   <si>
     <t xml:space="preserve">6.28017902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38636541366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31810331344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23467016220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15882301330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27259492874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26500988006592</t>
+    <t xml:space="preserve">6.15882253646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2725944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26500940322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.21191549301147</t>
@@ -1103,28 +1103,28 @@
     <t xml:space="preserve">6.15123796463013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02988147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05263614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25742483139038</t>
+    <t xml:space="preserve">6.02988195419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05263662338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25742435455322</t>
   </si>
   <si>
     <t xml:space="preserve">6.22708559036255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.249840259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29534912109375</t>
+    <t xml:space="preserve">6.24984073638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29534959793091</t>
   </si>
   <si>
     <t xml:space="preserve">6.3711953163147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1891622543335</t>
+    <t xml:space="preserve">6.18916273117065</t>
   </si>
   <si>
     <t xml:space="preserve">6.1664080619812</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">6.20433139801025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01471281051636</t>
+    <t xml:space="preserve">6.0147123336792</t>
   </si>
   <si>
     <t xml:space="preserve">6.04505157470703</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">6.00712776184082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98437356948853</t>
+    <t xml:space="preserve">5.98437309265137</t>
   </si>
   <si>
     <t xml:space="preserve">6.12089872360229</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">5.96161890029907</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08297634124756</t>
+    <t xml:space="preserve">6.08297538757324</t>
   </si>
   <si>
     <t xml:space="preserve">6.14365339279175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10573053359985</t>
+    <t xml:space="preserve">6.1057300567627</t>
   </si>
   <si>
     <t xml:space="preserve">6.06022119522095</t>
@@ -1175,19 +1175,19 @@
     <t xml:space="preserve">5.99954319000244</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95403432846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93886470794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06780576705933</t>
+    <t xml:space="preserve">5.95403480529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93886518478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06780624389648</t>
   </si>
   <si>
     <t xml:space="preserve">5.91611099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94644975662231</t>
+    <t xml:space="preserve">5.94645023345947</t>
   </si>
   <si>
     <t xml:space="preserve">5.87818717956543</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">6.03746700286865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02229785919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99195861816406</t>
+    <t xml:space="preserve">6.02229738235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9919581413269</t>
   </si>
   <si>
     <t xml:space="preserve">5.86301708221436</t>
@@ -1208,40 +1208,40 @@
     <t xml:space="preserve">6.07539033889771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24225473403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738218307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63666296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46221399307251</t>
+    <t xml:space="preserve">6.24225425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63666248321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46221351623535</t>
   </si>
   <si>
     <t xml:space="preserve">6.57598447799683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56081485748291</t>
+    <t xml:space="preserve">6.56081438064575</t>
   </si>
   <si>
     <t xml:space="preserve">6.6063232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55323028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65183258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53806114196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48496770858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6139087677002</t>
+    <t xml:space="preserve">6.55323076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65183210372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53806018829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48496723175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61390829086304</t>
   </si>
   <si>
     <t xml:space="preserve">6.66700172424316</t>
@@ -1253,55 +1253,55 @@
     <t xml:space="preserve">6.34085655212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39395046234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41670417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4242901802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53047513961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59115409851074</t>
+    <t xml:space="preserve">6.39395093917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4167046546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42428970336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53047609329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5911545753479</t>
   </si>
   <si>
     <t xml:space="preserve">6.54564571380615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56839942932129</t>
+    <t xml:space="preserve">6.56839990615845</t>
   </si>
   <si>
     <t xml:space="preserve">6.44704389572144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3484411239624</t>
+    <t xml:space="preserve">6.34844160079956</t>
   </si>
   <si>
     <t xml:space="preserve">6.21950101852417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40911912918091</t>
+    <t xml:space="preserve">6.40911960601807</t>
   </si>
   <si>
     <t xml:space="preserve">6.32568788528442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28776407241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68975591659546</t>
+    <t xml:space="preserve">6.28776359558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68975639343262</t>
   </si>
   <si>
     <t xml:space="preserve">6.6745867729187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74284887313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75043392181396</t>
+    <t xml:space="preserve">6.74284934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75043296813965</t>
   </si>
   <si>
     <t xml:space="preserve">6.62149238586426</t>
@@ -1313,22 +1313,22 @@
     <t xml:space="preserve">6.36361169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46979808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51530599594116</t>
+    <t xml:space="preserve">6.46979856491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51530647277832</t>
   </si>
   <si>
     <t xml:space="preserve">6.31051778793335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3560266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19674730300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40153503417969</t>
+    <t xml:space="preserve">6.35602712631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19674682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40153455734253</t>
   </si>
   <si>
     <t xml:space="preserve">6.72009515762329</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">6.75801849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80352783203125</t>
+    <t xml:space="preserve">6.80352735519409</t>
   </si>
   <si>
     <t xml:space="preserve">6.78835821151733</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">6.86420631408691</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81111145019531</t>
+    <t xml:space="preserve">6.81111097335815</t>
   </si>
   <si>
     <t xml:space="preserve">6.84145164489746</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">6.81869649887085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90212917327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99314594268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89454412460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94005155563354</t>
+    <t xml:space="preserve">6.90213012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99314737319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89454507827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9400520324707</t>
   </si>
   <si>
     <t xml:space="preserve">7.05382394790649</t>
@@ -1379,16 +1379,16 @@
     <t xml:space="preserve">7.10691738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15242576599121</t>
+    <t xml:space="preserve">7.15242671966553</t>
   </si>
   <si>
     <t xml:space="preserve">7.11450242996216</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0159010887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08416366577148</t>
+    <t xml:space="preserve">7.01590061187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08416318893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.04623985290527</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">7.09174823760986</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39513921737671</t>
+    <t xml:space="preserve">7.39513874053955</t>
   </si>
   <si>
     <t xml:space="preserve">7.35721397399902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34204435348511</t>
+    <t xml:space="preserve">7.34204530715942</t>
   </si>
   <si>
     <t xml:space="preserve">7.12208700180054</t>
@@ -1415,13 +1415,13 @@
     <t xml:space="preserve">7.12967157363892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25102806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22827386856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20552015304565</t>
+    <t xml:space="preserve">7.2510290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22827291488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20551824569702</t>
   </si>
   <si>
     <t xml:space="preserve">7.1979341506958</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">7.16759586334229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37996864318848</t>
+    <t xml:space="preserve">7.37996768951416</t>
   </si>
   <si>
     <t xml:space="preserve">7.43306255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49373960494995</t>
+    <t xml:space="preserve">7.49374008178711</t>
   </si>
   <si>
     <t xml:space="preserve">7.53924894332886</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">7.54683399200439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75162267684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79713010787964</t>
+    <t xml:space="preserve">7.75162172317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79713106155396</t>
   </si>
   <si>
     <t xml:space="preserve">7.64543533325195</t>
@@ -1457,10 +1457,10 @@
     <t xml:space="preserve">7.69094371795654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57717275619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4558162689209</t>
+    <t xml:space="preserve">7.57717132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45581483840942</t>
   </si>
   <si>
     <t xml:space="preserve">7.5164942741394</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">7.50890922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56200408935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58475732803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55441808700562</t>
+    <t xml:space="preserve">7.56200361251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58475828170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5544171333313</t>
   </si>
   <si>
     <t xml:space="preserve">7.47857093811035</t>
@@ -1487,28 +1487,28 @@
     <t xml:space="preserve">7.47098588943481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44823026657104</t>
+    <t xml:space="preserve">7.44823122024536</t>
   </si>
   <si>
     <t xml:space="preserve">7.7061128616333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90331649780273</t>
+    <t xml:space="preserve">7.90331745147705</t>
   </si>
   <si>
     <t xml:space="preserve">7.88814687728882</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25221538543701</t>
+    <t xml:space="preserve">8.25221633911133</t>
   </si>
   <si>
     <t xml:space="preserve">8.61628437042236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49492835998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17636775970459</t>
+    <t xml:space="preserve">8.49492740631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17636680603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.41908168792725</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">7.93068933486938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04040241241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96203517913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25982761383057</t>
+    <t xml:space="preserve">8.04040336608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9620361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25982856750488</t>
   </si>
   <si>
     <t xml:space="preserve">8.02472972869873</t>
@@ -1544,16 +1544,16 @@
     <t xml:space="preserve">7.83664989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82097768783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91501569747925</t>
+    <t xml:space="preserve">7.82097578048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91501617431641</t>
   </si>
   <si>
     <t xml:space="preserve">7.97770929336548</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07175064086914</t>
+    <t xml:space="preserve">8.07174968719482</t>
   </si>
   <si>
     <t xml:space="preserve">8.05607604980469</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">8.46358108520508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6203145980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30684852600098</t>
+    <t xml:space="preserve">8.62031555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30684947967529</t>
   </si>
   <si>
     <t xml:space="preserve">8.16578960418701</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">8.21280765533447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27550315856934</t>
+    <t xml:space="preserve">8.27550220489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.36954212188721</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">8.22848129272461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43223476409912</t>
+    <t xml:space="preserve">8.43223571777344</t>
   </si>
   <si>
     <t xml:space="preserve">7.99338388442993</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">8.19713592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75828218460083</t>
+    <t xml:space="preserve">7.75828313827515</t>
   </si>
   <si>
     <t xml:space="preserve">7.89934253692627</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">7.82881259918213</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88367033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313943862915</t>
+    <t xml:space="preserve">7.88366937637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81314039230347</t>
   </si>
   <si>
     <t xml:space="preserve">7.67991781234741</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">7.79746675491333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4165620803833</t>
+    <t xml:space="preserve">8.41656112670898</t>
   </si>
   <si>
     <t xml:space="preserve">7.80530214309692</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">8.00905609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94636297225952</t>
+    <t xml:space="preserve">7.94636249542236</t>
   </si>
   <si>
     <t xml:space="preserve">7.75044679641724</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">7.71909999847412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10309505462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37263202667236</t>
+    <t xml:space="preserve">8.10309600830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82406806945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37263298034668</t>
   </si>
   <si>
     <t xml:space="preserve">9.60773277282715</t>
@@ -1682,19 +1682,19 @@
     <t xml:space="preserve">9.99956512451172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1562986373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5011110305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3757228851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5481290817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2189912796021</t>
+    <t xml:space="preserve">10.1562976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5011100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3757238388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5481300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2189922332764</t>
   </si>
   <si>
     <t xml:space="preserve">10.1719703674316</t>
@@ -1703,16 +1703,16 @@
     <t xml:space="preserve">9.95254516601562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90552616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88985157012939</t>
+    <t xml:space="preserve">9.90552520751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88985252380371</t>
   </si>
   <si>
     <t xml:space="preserve">9.92119884490967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73311901092529</t>
+    <t xml:space="preserve">9.73311996459961</t>
   </si>
   <si>
     <t xml:space="preserve">9.76446628570557</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">9.96821784973145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0309114456177</t>
+    <t xml:space="preserve">10.0309104919434</t>
   </si>
   <si>
     <t xml:space="preserve">10.4854373931885</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">10.2503385543823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0152378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1249513626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3600521087646</t>
+    <t xml:space="preserve">10.0152387619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1249523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3600511550903</t>
   </si>
   <si>
     <t xml:space="preserve">10.2973585128784</t>
@@ -1751,19 +1751,19 @@
     <t xml:space="preserve">10.4384174346924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6264972686768</t>
+    <t xml:space="preserve">10.6264963150024</t>
   </si>
   <si>
     <t xml:space="preserve">10.657844543457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6108245849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5951499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5794773101807</t>
+    <t xml:space="preserve">10.6108236312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5951509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.579478263855</t>
   </si>
   <si>
     <t xml:space="preserve">10.6421699523926</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">10.9869832992554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9556369781494</t>
+    <t xml:space="preserve">10.9556360244751</t>
   </si>
   <si>
     <t xml:space="preserve">11.1280431747437</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">11.1593894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0966958999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1750631332397</t>
+    <t xml:space="preserve">11.0966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1750621795654</t>
   </si>
   <si>
     <t xml:space="preserve">11.1123695373535</t>
@@ -1805,28 +1805,28 @@
     <t xml:space="preserve">10.9713096618652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7989015579224</t>
+    <t xml:space="preserve">10.7989025115967</t>
   </si>
   <si>
     <t xml:space="preserve">10.0622587203979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0936040878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68609809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29426670074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54504013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98080062866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54194831848145</t>
+    <t xml:space="preserve">10.0936050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6860990524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29426574707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54503917694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98079967498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54194736480713</t>
   </si>
   <si>
     <t xml:space="preserve">7.31943130493164</t>
@@ -1838,13 +1838,13 @@
     <t xml:space="preserve">7.53885746002197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49183702468872</t>
+    <t xml:space="preserve">7.49183750152588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66733551025391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44790840148926</t>
+    <t xml:space="preserve">8.44790744781494</t>
   </si>
   <si>
     <t xml:space="preserve">8.38521480560303</t>
@@ -1853,19 +1853,19 @@
     <t xml:space="preserve">8.52627563476562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01214790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45100021362305</t>
+    <t xml:space="preserve">9.01214694976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45100116729736</t>
   </si>
   <si>
     <t xml:space="preserve">9.10618686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93378067016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38830757141113</t>
+    <t xml:space="preserve">8.9337797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38830661773682</t>
   </si>
   <si>
     <t xml:space="preserve">8.88676166534424</t>
@@ -1874,13 +1874,13 @@
     <t xml:space="preserve">8.87108707427979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12185955047607</t>
+    <t xml:space="preserve">9.12186050415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.91810703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15320682525635</t>
+    <t xml:space="preserve">9.15320777893066</t>
   </si>
   <si>
     <t xml:space="preserve">8.90243434906006</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">9.04349422454834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21590137481689</t>
+    <t xml:space="preserve">9.21590042114258</t>
   </si>
   <si>
     <t xml:space="preserve">8.96512794494629</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">9.01022911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68495082855225</t>
+    <t xml:space="preserve">8.68494987487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.50604724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70121479034424</t>
+    <t xml:space="preserve">8.70121383666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.18913269042969</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">8.92890930175781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76627063751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71747779846191</t>
+    <t xml:space="preserve">8.76626968383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71747875213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.97770214080811</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">9.33550834655762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48188495635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61199569702148</t>
+    <t xml:space="preserve">9.48188400268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61199474334717</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625541687012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0673875808716</t>
+    <t xml:space="preserve">10.0673866271973</t>
   </si>
   <si>
     <t xml:space="preserve">10.3113470077515</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">10.2300252914429</t>
   </si>
   <si>
-    <t xml:space="preserve">9.953537940979</t>
+    <t xml:space="preserve">9.95353889465332</t>
   </si>
   <si>
     <t xml:space="preserve">9.88848304748535</t>
@@ -1997,28 +1997,28 @@
     <t xml:space="preserve">10.7992639541626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9293746948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6854162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.636625289917</t>
+    <t xml:space="preserve">10.9293756484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.685417175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6366262435913</t>
   </si>
   <si>
     <t xml:space="preserve">10.7667360305786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9781675338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1245422363281</t>
+    <t xml:space="preserve">10.9781684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1245431900024</t>
   </si>
   <si>
     <t xml:space="preserve">11.1408081054688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2871828079224</t>
+    <t xml:space="preserve">11.287181854248</t>
   </si>
   <si>
     <t xml:space="preserve">11.3847675323486</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">11.4498224258423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4660863876343</t>
+    <t xml:space="preserve">11.4660873413086</t>
   </si>
   <si>
     <t xml:space="preserve">11.4823503494263</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">11.2058629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2221269607544</t>
+    <t xml:space="preserve">11.2221279144287</t>
   </si>
   <si>
     <t xml:space="preserve">10.8643188476562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5390396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.522777557373</t>
+    <t xml:space="preserve">10.5390405654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5227766036987</t>
   </si>
   <si>
     <t xml:space="preserve">10.701681137085</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">10.8155288696289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6040964126587</t>
+    <t xml:space="preserve">10.604097366333</t>
   </si>
   <si>
     <t xml:space="preserve">10.7342081069946</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">10.587833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4577217102051</t>
+    <t xml:space="preserve">10.4577207565308</t>
   </si>
   <si>
     <t xml:space="preserve">10.3764019012451</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">10.8968486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0594882965088</t>
+    <t xml:space="preserve">11.0594892501831</t>
   </si>
   <si>
     <t xml:space="preserve">10.9944324493408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6691522598267</t>
+    <t xml:space="preserve">10.669153213501</t>
   </si>
   <si>
     <t xml:space="preserve">10.7829999923706</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">11.2709188461304</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1895990371704</t>
+    <t xml:space="preserve">11.1895999908447</t>
   </si>
   <si>
     <t xml:space="preserve">11.5799341201782</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">9.9860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0836496353149</t>
+    <t xml:space="preserve">10.0836505889893</t>
   </si>
   <si>
     <t xml:space="preserve">10.4414567947388</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">11.1570711135864</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1082792282104</t>
+    <t xml:space="preserve">11.1082782745361</t>
   </si>
   <si>
     <t xml:space="preserve">11.0269594192505</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">10.9131126403809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2546548843384</t>
+    <t xml:space="preserve">11.2546558380127</t>
   </si>
   <si>
     <t xml:space="preserve">11.3522386550903</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">11.5311422348022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7751007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7100448608398</t>
+    <t xml:space="preserve">11.7751016616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7100458145142</t>
   </si>
   <si>
     <t xml:space="preserve">11.7425737380981</t>
@@ -2195,16 +2195,16 @@
     <t xml:space="preserve">12.1979637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8726854324341</t>
+    <t xml:space="preserve">11.8726844787598</t>
   </si>
   <si>
     <t xml:space="preserve">12.00279712677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8076295852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8564205169678</t>
+    <t xml:space="preserve">11.8076305389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8564214706421</t>
   </si>
   <si>
     <t xml:space="preserve">11.5961980819702</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">11.9865322113037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1003799438477</t>
+    <t xml:space="preserve">12.100380897522</t>
   </si>
   <si>
     <t xml:space="preserve">12.1816997528076</t>
@@ -2225,19 +2225,19 @@
     <t xml:space="preserve">12.1166439056396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2792844772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4093961715698</t>
+    <t xml:space="preserve">12.2792835235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4093952178955</t>
   </si>
   <si>
     <t xml:space="preserve">12.5069799423218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4581880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4907159805298</t>
+    <t xml:space="preserve">12.4581871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4907150268555</t>
   </si>
   <si>
     <t xml:space="preserve">12.8973140716553</t>
@@ -2246,16 +2246,16 @@
     <t xml:space="preserve">13.0111618041992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9786338806152</t>
+    <t xml:space="preserve">12.9786348342896</t>
   </si>
   <si>
     <t xml:space="preserve">12.8647861480713</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7997312545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6370906829834</t>
+    <t xml:space="preserve">12.7997303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6370916366577</t>
   </si>
   <si>
     <t xml:space="preserve">12.8810501098633</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">13.7267751693726</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8243589401245</t>
+    <t xml:space="preserve">13.8243598937988</t>
   </si>
   <si>
     <t xml:space="preserve">14.0520553588867</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">14.2309579849243</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634878158569</t>
+    <t xml:space="preserve">14.2634859085083</t>
   </si>
   <si>
     <t xml:space="preserve">14.2146940231323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9056797027588</t>
+    <t xml:space="preserve">13.9056787490845</t>
   </si>
   <si>
     <t xml:space="preserve">13.6129283905029</t>
@@ -2303,22 +2303,22 @@
     <t xml:space="preserve">13.6454563140869</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8406229019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918319702148</t>
+    <t xml:space="preserve">13.8406238555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918310165405</t>
   </si>
   <si>
     <t xml:space="preserve">14.0032625198364</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9544715881348</t>
+    <t xml:space="preserve">13.9544706344604</t>
   </si>
   <si>
     <t xml:space="preserve">14.3448057174683</t>
   </si>
   <si>
-    <t xml:space="preserve">14.149640083313</t>
+    <t xml:space="preserve">14.1496381759644</t>
   </si>
   <si>
     <t xml:space="preserve">14.2472229003906</t>
@@ -2327,13 +2327,13 @@
     <t xml:space="preserve">14.4749174118042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5579175949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.192723274231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1595230102539</t>
+    <t xml:space="preserve">14.557915687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1927223205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1595239639282</t>
   </si>
   <si>
     <t xml:space="preserve">14.1429243087769</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">14.1097240447998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425222396851</t>
+    <t xml:space="preserve">14.2425212860107</t>
   </si>
   <si>
     <t xml:space="preserve">14.0765237808228</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">14.2093238830566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9935264587402</t>
+    <t xml:space="preserve">13.9935274124146</t>
   </si>
   <si>
     <t xml:space="preserve">13.8109292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3089208602905</t>
+    <t xml:space="preserve">14.3089189529419</t>
   </si>
   <si>
     <t xml:space="preserve">14.05992603302</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">14.0101251602173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9769268035889</t>
+    <t xml:space="preserve">13.9769258499146</t>
   </si>
   <si>
     <t xml:space="preserve">14.0433263778687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3255186080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2259206771851</t>
+    <t xml:space="preserve">14.3255205154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2259216308594</t>
   </si>
   <si>
     <t xml:space="preserve">14.3421211242676</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">14.1761236190796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9437274932861</t>
+    <t xml:space="preserve">13.9437265396118</t>
   </si>
   <si>
     <t xml:space="preserve">14.0931243896484</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">14.524715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0267238616943</t>
+    <t xml:space="preserve">14.0267248153687</t>
   </si>
   <si>
     <t xml:space="preserve">14.7073125839233</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">14.7737102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6907138824463</t>
+    <t xml:space="preserve">14.6907119750977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7405118942261</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9397096633911</t>
+    <t xml:space="preserve">14.9397077560425</t>
   </si>
   <si>
     <t xml:space="preserve">15.1057062149048</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">14.8899097442627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3713006973267</t>
+    <t xml:space="preserve">15.371298789978</t>
   </si>
   <si>
     <t xml:space="preserve">15.7032918930054</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">15.1223020553589</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9895057678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567094802856</t>
+    <t xml:space="preserve">14.9895076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.85671043396</t>
   </si>
   <si>
     <t xml:space="preserve">14.8235101699829</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">14.8069105148315</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8607301712036</t>
+    <t xml:space="preserve">13.8607292175293</t>
   </si>
   <si>
     <t xml:space="preserve">13.6947317123413</t>
@@ -2504,16 +2504,16 @@
     <t xml:space="preserve">13.7113332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4417190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5745153427124</t>
+    <t xml:space="preserve">14.4417171478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5745134353638</t>
   </si>
   <si>
     <t xml:space="preserve">14.541316986084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4251174926758</t>
+    <t xml:space="preserve">14.4251194000244</t>
   </si>
   <si>
     <t xml:space="preserve">14.4085187911987</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">15.2053022384644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0227060317993</t>
+    <t xml:space="preserve">15.0227079391479</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915151596069</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8275289535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7777309417725</t>
+    <t xml:space="preserve">13.8275299072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7777318954468</t>
   </si>
   <si>
     <t xml:space="preserve">13.6449337005615</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">13.5951337814331</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6117343902588</t>
+    <t xml:space="preserve">13.6117334365845</t>
   </si>
   <si>
     <t xml:space="preserve">13.1303434371948</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">13.4955368041992</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0805444717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3129405975342</t>
+    <t xml:space="preserve">13.080545425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3129396438599</t>
   </si>
   <si>
     <t xml:space="preserve">13.196741104126</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">12.4497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3003587722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7153520584106</t>
+    <t xml:space="preserve">12.3003597259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7153511047363</t>
   </si>
   <si>
     <t xml:space="preserve">12.4331560134888</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">12.3335590362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3501577377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.067964553833</t>
+    <t xml:space="preserve">12.3501586914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0679636001587</t>
   </si>
   <si>
     <t xml:space="preserve">11.8521680831909</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">11.6695728302002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0845642089844</t>
+    <t xml:space="preserve">12.0845651626587</t>
   </si>
   <si>
     <t xml:space="preserve">11.8189687728882</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">11.6031723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7027711868286</t>
+    <t xml:space="preserve">11.7027721405029</t>
   </si>
   <si>
     <t xml:space="preserve">11.7857694625854</t>
@@ -2657,13 +2657,13 @@
     <t xml:space="preserve">10.2088003158569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6735916137695</t>
+    <t xml:space="preserve">10.6735906600952</t>
   </si>
   <si>
     <t xml:space="preserve">10.6237926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2585983276367</t>
+    <t xml:space="preserve">10.258599281311</t>
   </si>
   <si>
     <t xml:space="preserve">10.1922006607056</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">9.97640514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54481410980225</t>
+    <t xml:space="preserve">9.54481315612793</t>
   </si>
   <si>
     <t xml:space="preserve">9.56141376495361</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">9.36221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62781238555908</t>
+    <t xml:space="preserve">9.6278133392334</t>
   </si>
   <si>
     <t xml:space="preserve">9.32901763916016</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">9.52821445465088</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0096044540405</t>
+    <t xml:space="preserve">10.0096054077148</t>
   </si>
   <si>
     <t xml:space="preserve">9.39541625976562</t>
@@ -2714,22 +2714,22 @@
     <t xml:space="preserve">10.1092023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1424016952515</t>
+    <t xml:space="preserve">10.1424007415771</t>
   </si>
   <si>
     <t xml:space="preserve">10.0594024658203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86020851135254</t>
+    <t xml:space="preserve">9.86020755767822</t>
   </si>
   <si>
     <t xml:space="preserve">9.89340591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69421100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61121368408203</t>
+    <t xml:space="preserve">9.69421195983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61121273040771</t>
   </si>
   <si>
     <t xml:space="preserve">9.17962074279785</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">10.4577960968018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0760040283203</t>
+    <t xml:space="preserve">10.076003074646</t>
   </si>
   <si>
     <t xml:space="preserve">9.92660617828369</t>
@@ -4404,6 +4404,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.96000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90000009536743</t>
   </si>
 </sst>
 </file>
@@ -8218,7 +8221,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G134" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8244,7 +8247,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G135" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -8270,7 +8273,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G136" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -8348,7 +8351,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G139" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8374,7 +8377,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G140" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8400,7 +8403,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G141" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8478,7 +8481,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G144" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8504,7 +8507,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G145" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8556,7 +8559,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G147" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8582,7 +8585,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G148" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8608,7 +8611,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G149" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8634,7 +8637,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G150" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8660,7 +8663,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G151" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -8686,7 +8689,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G152" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8738,7 +8741,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G154" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -8816,7 +8819,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G157" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -8842,7 +8845,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G158" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -8946,7 +8949,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G162" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -8972,7 +8975,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G163" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -8998,7 +9001,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G164" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9024,7 +9027,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G165" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9050,7 +9053,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G166" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9076,7 +9079,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G167" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9102,7 +9105,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G168" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9128,7 +9131,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G169" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9154,7 +9157,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G170" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9180,7 +9183,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G171" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9206,7 +9209,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G172" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9258,7 +9261,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G174" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9310,7 +9313,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G176" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9336,7 +9339,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G177" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9362,7 +9365,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G178" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9388,7 +9391,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G179" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9414,7 +9417,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G180" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9440,7 +9443,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G181" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9466,7 +9469,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G182" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9518,7 +9521,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G184" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9544,7 +9547,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G185" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9570,7 +9573,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G186" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9648,7 +9651,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G189" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9674,7 +9677,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G190" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9700,7 +9703,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G191" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9726,7 +9729,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G192" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -9752,7 +9755,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G193" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -9778,7 +9781,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G194" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -9804,7 +9807,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G195" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -9830,7 +9833,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G196" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -9856,7 +9859,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G197" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -9882,7 +9885,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G198" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -9908,7 +9911,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G199" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -9960,7 +9963,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G201" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10090,7 +10093,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G206" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10142,7 +10145,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G208" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10168,7 +10171,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G209" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10194,7 +10197,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G210" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10298,7 +10301,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G214" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10324,7 +10327,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G215" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10350,7 +10353,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G216" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10376,7 +10379,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G217" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10402,7 +10405,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G218" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10428,7 +10431,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G219" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10454,7 +10457,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G220" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10480,7 +10483,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G221" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10506,7 +10509,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G222" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10558,7 +10561,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G224" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10610,7 +10613,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G226" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10636,7 +10639,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G227" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10662,7 +10665,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G228" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10688,7 +10691,7 @@
         <v>5.25</v>
       </c>
       <c r="G229" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10740,7 +10743,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G231" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10792,7 +10795,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G233" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -10870,7 +10873,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G236" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -10896,7 +10899,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G237" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -10922,7 +10925,7 @@
         <v>5.25</v>
       </c>
       <c r="G238" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -10948,7 +10951,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G239" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11000,7 +11003,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G241" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11026,7 +11029,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G242" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11052,7 +11055,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G243" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11182,7 +11185,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G248" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11208,7 +11211,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G249" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11234,7 +11237,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G250" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11260,7 +11263,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G251" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11338,7 +11341,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G254" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11364,7 +11367,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G255" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11442,7 +11445,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G258" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11468,7 +11471,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G259" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11494,7 +11497,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G260" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11520,7 +11523,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G261" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11572,7 +11575,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G263" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11598,7 +11601,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G264" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11624,7 +11627,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G265" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11650,7 +11653,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G266" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11676,7 +11679,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G267" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11702,7 +11705,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G268" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11728,7 +11731,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G269" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -11754,7 +11757,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G270" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11780,7 +11783,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G271" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -11806,7 +11809,7 @@
         <v>5.7649998664856</v>
       </c>
       <c r="G272" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -11832,7 +11835,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G273" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -11858,7 +11861,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G274" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -11910,7 +11913,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G276" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12040,7 +12043,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G281" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12092,7 +12095,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G283" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12144,7 +12147,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G285" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12170,7 +12173,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G286" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12196,7 +12199,7 @@
         <v>5.75</v>
       </c>
       <c r="G287" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12222,7 +12225,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G288" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12248,7 +12251,7 @@
         <v>5.80499982833862</v>
       </c>
       <c r="G289" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12274,7 +12277,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G290" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12300,7 +12303,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G291" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12326,7 +12329,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G292" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12352,7 +12355,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G293" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12378,7 +12381,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G294" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12404,7 +12407,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G295" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12430,7 +12433,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G296" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12456,7 +12459,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G297" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12482,7 +12485,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G298" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12508,7 +12511,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G299" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12534,7 +12537,7 @@
         <v>6</v>
       </c>
       <c r="G300" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12560,7 +12563,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G301" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12586,7 +12589,7 @@
         <v>6</v>
       </c>
       <c r="G302" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12612,7 +12615,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G303" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12638,7 +12641,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G304" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12664,7 +12667,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G305" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12690,7 +12693,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G306" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12716,7 +12719,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G307" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12742,7 +12745,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G308" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12768,7 +12771,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G309" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -12794,7 +12797,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G310" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -12820,7 +12823,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G311" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -12846,7 +12849,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G312" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -12872,7 +12875,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G313" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -12898,7 +12901,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G314" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -12924,7 +12927,7 @@
         <v>7</v>
       </c>
       <c r="G315" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -12950,7 +12953,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G316" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -12976,7 +12979,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G317" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13002,7 +13005,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G318" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13028,7 +13031,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G319" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13054,7 +13057,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G320" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13080,7 +13083,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G321" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13106,7 +13109,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G322" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13132,7 +13135,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G323" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13158,7 +13161,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G324" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13184,7 +13187,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G325" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13210,7 +13213,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G326" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13236,7 +13239,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G327" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13262,7 +13265,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G328" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13288,7 +13291,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G329" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13314,7 +13317,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G330" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13340,7 +13343,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G331" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13366,7 +13369,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G332" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13392,7 +13395,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G333" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13418,7 +13421,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G334" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13444,7 +13447,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G335" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13470,7 +13473,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G336" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13496,7 +13499,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G337" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13522,7 +13525,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G338" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13548,7 +13551,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G339" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13574,7 +13577,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G340" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13600,7 +13603,7 @@
         <v>7.75</v>
       </c>
       <c r="G341" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13626,7 +13629,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G342" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13652,7 +13655,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G343" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13678,7 +13681,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G344" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13704,7 +13707,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G345" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13730,7 +13733,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13756,7 +13759,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G347" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13782,7 +13785,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G348" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -13808,7 +13811,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G349" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -13834,7 +13837,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G350" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -13860,7 +13863,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G351" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -13886,7 +13889,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G352" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -13912,7 +13915,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G353" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -13938,7 +13941,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G354" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -13964,7 +13967,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G355" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -13990,7 +13993,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G356" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14016,7 +14019,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G357" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14042,7 +14045,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G358" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14068,7 +14071,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G359" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14094,7 +14097,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G360" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14120,7 +14123,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G361" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14146,7 +14149,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G362" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14172,7 +14175,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G363" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14198,7 +14201,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G364" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14224,7 +14227,7 @@
         <v>7.5</v>
       </c>
       <c r="G365" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14250,7 +14253,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G366" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14276,7 +14279,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G367" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14302,7 +14305,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G368" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14328,7 +14331,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G369" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14354,7 +14357,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G370" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14380,7 +14383,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G371" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14406,7 +14409,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G372" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14432,7 +14435,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G373" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14458,7 +14461,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G374" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14484,7 +14487,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G375" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14510,7 +14513,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G376" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14536,7 +14539,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G377" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14562,7 +14565,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G378" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14588,7 +14591,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G379" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14614,7 +14617,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G380" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14640,7 +14643,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G381" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14666,7 +14669,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G382" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14692,7 +14695,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G383" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14718,7 +14721,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G384" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14744,7 +14747,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G385" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -14770,7 +14773,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G386" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -14796,7 +14799,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G387" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -14822,7 +14825,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G388" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -14848,7 +14851,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G389" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -14874,7 +14877,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G390" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -14900,7 +14903,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G391" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -14926,7 +14929,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G392" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -14952,7 +14955,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G393" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -14978,7 +14981,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G394" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15004,7 +15007,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G395" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15030,7 +15033,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G396" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15056,7 +15059,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G397" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15082,7 +15085,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G398" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15108,7 +15111,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15134,7 +15137,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G400" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15160,7 +15163,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G401" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15186,7 +15189,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G402" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15212,7 +15215,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G403" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15238,7 +15241,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G404" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15264,7 +15267,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G405" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15290,7 +15293,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G406" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15316,7 +15319,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G407" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15342,7 +15345,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G408" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15368,7 +15371,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G409" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15394,7 +15397,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G410" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15420,7 +15423,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G411" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15446,7 +15449,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G412" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15472,7 +15475,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G413" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15498,7 +15501,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G414" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15524,7 +15527,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G415" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15550,7 +15553,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G416" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15576,7 +15579,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G417" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15602,7 +15605,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G418" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -15628,7 +15631,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G419" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15654,7 +15657,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G420" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15680,7 +15683,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G421" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15706,7 +15709,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G422" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15732,7 +15735,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G423" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -15758,7 +15761,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G424" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -15784,7 +15787,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G425" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -15810,7 +15813,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G426" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -15836,7 +15839,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G427" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -15862,7 +15865,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G428" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -15888,7 +15891,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G429" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -15914,7 +15917,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G430" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -15940,7 +15943,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G431" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -15966,7 +15969,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G432" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -15992,7 +15995,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G433" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16018,7 +16021,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G434" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16044,7 +16047,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G435" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16070,7 +16073,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G436" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16096,7 +16099,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G437" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16122,7 +16125,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G438" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16148,7 +16151,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G439" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16174,7 +16177,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G440" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16200,7 +16203,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G441" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16226,7 +16229,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G442" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16252,7 +16255,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G443" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16278,7 +16281,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G444" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16304,7 +16307,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G445" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16330,7 +16333,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G446" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16356,7 +16359,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G447" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16382,7 +16385,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G448" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16408,7 +16411,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G449" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16434,7 +16437,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G450" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16460,7 +16463,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G451" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16486,7 +16489,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G452" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16512,7 +16515,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G453" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16538,7 +16541,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G454" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16564,7 +16567,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G455" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16590,7 +16593,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G456" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16616,7 +16619,7 @@
         <v>8</v>
       </c>
       <c r="G457" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16642,7 +16645,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G458" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -16668,7 +16671,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G459" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -16694,7 +16697,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G460" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -16720,7 +16723,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G461" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -16746,7 +16749,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G462" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -16772,7 +16775,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G463" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -16798,7 +16801,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G464" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -16824,7 +16827,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G465" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -16850,7 +16853,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G466" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -16876,7 +16879,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G467" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -16902,7 +16905,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G468" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -16928,7 +16931,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G469" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -16954,7 +16957,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G470" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -16980,7 +16983,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G471" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17006,7 +17009,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G472" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17032,7 +17035,7 @@
         <v>8</v>
       </c>
       <c r="G473" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17058,7 +17061,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G474" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17084,7 +17087,7 @@
         <v>7.85500001907349</v>
       </c>
       <c r="G475" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17110,7 +17113,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G476" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17136,7 +17139,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G477" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17162,7 +17165,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G478" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17188,7 +17191,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G479" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17214,7 +17217,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G480" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17240,7 +17243,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G481" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17266,7 +17269,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G482" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17292,7 +17295,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G483" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17318,7 +17321,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G484" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17344,7 +17347,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G485" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17370,7 +17373,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G486" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17396,7 +17399,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G487" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17422,7 +17425,7 @@
         <v>8</v>
       </c>
       <c r="G488" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17448,7 +17451,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G489" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17474,7 +17477,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G490" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17500,7 +17503,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G491" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17526,7 +17529,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G492" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17552,7 +17555,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G493" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17578,7 +17581,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G494" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17604,7 +17607,7 @@
         <v>8</v>
       </c>
       <c r="G495" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17630,7 +17633,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G496" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17656,7 +17659,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G497" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -17682,7 +17685,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G498" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -17708,7 +17711,7 @@
         <v>8.08500003814697</v>
       </c>
       <c r="G499" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -17734,7 +17737,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G500" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -17760,7 +17763,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G501" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -17786,7 +17789,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G502" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -17812,7 +17815,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G503" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -17838,7 +17841,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -17864,7 +17867,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G505" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -17890,7 +17893,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G506" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -17916,7 +17919,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G507" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -17942,7 +17945,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G508" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -17968,7 +17971,7 @@
         <v>8.25</v>
       </c>
       <c r="G509" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -17994,7 +17997,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G510" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18020,7 +18023,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G511" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18046,7 +18049,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G512" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18072,7 +18075,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G513" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18098,7 +18101,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G514" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18124,7 +18127,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G515" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18150,7 +18153,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G516" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18176,7 +18179,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G517" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18202,7 +18205,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G518" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18228,7 +18231,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G519" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18254,7 +18257,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G520" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18280,7 +18283,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G521" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18306,7 +18309,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G522" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18332,7 +18335,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G523" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18358,7 +18361,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G524" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18384,7 +18387,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G525" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18410,7 +18413,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G526" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18436,7 +18439,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G527" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18462,7 +18465,7 @@
         <v>8.5</v>
       </c>
       <c r="G528" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18488,7 +18491,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G529" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18514,7 +18517,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G530" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18540,7 +18543,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G531" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18566,7 +18569,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G532" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18592,7 +18595,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G533" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18618,7 +18621,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G534" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18644,7 +18647,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G535" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -18670,7 +18673,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G536" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -18696,7 +18699,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G537" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -18722,7 +18725,7 @@
         <v>8</v>
       </c>
       <c r="G538" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -18748,7 +18751,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G539" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -18774,7 +18777,7 @@
         <v>8</v>
       </c>
       <c r="G540" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -18800,7 +18803,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G541" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -18826,7 +18829,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G542" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -18852,7 +18855,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G543" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -18878,7 +18881,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G544" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -18904,7 +18907,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G545" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -18930,7 +18933,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G546" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -18956,7 +18959,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G547" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -18982,7 +18985,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G548" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19008,7 +19011,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G549" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19034,7 +19037,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G550" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19060,7 +19063,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G551" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19086,7 +19089,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G552" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19112,7 +19115,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G553" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19138,7 +19141,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G554" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19164,7 +19167,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G555" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19190,7 +19193,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G556" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19216,7 +19219,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G557" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19242,7 +19245,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G558" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19268,7 +19271,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G559" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19294,7 +19297,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G560" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19320,7 +19323,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G561" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19346,7 +19349,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G562" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19372,7 +19375,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G563" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19398,7 +19401,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G564" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19424,7 +19427,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G565" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19450,7 +19453,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G566" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19476,7 +19479,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G567" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19502,7 +19505,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G568" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19528,7 +19531,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G569" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19554,7 +19557,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G570" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19580,7 +19583,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G571" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19606,7 +19609,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G572" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19632,7 +19635,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G573" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19658,7 +19661,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G574" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -19684,7 +19687,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G575" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -19710,7 +19713,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G576" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -19736,7 +19739,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G577" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -19762,7 +19765,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G578" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -19788,7 +19791,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G579" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -19814,7 +19817,7 @@
         <v>8.25</v>
       </c>
       <c r="G580" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -19840,7 +19843,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -19866,7 +19869,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -19892,7 +19895,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G583" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -19918,7 +19921,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G584" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -19944,7 +19947,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G585" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -19970,7 +19973,7 @@
         <v>8.25</v>
       </c>
       <c r="G586" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -19996,7 +19999,7 @@
         <v>8.25</v>
       </c>
       <c r="G587" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20022,7 +20025,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G588" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20048,7 +20051,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G589" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20074,7 +20077,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G590" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20100,7 +20103,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G591" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20126,7 +20129,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G592" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20152,7 +20155,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G593" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20178,7 +20181,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G594" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20204,7 +20207,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20230,7 +20233,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G596" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20256,7 +20259,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G597" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20282,7 +20285,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G598" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20308,7 +20311,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G599" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20334,7 +20337,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G600" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20360,7 +20363,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G601" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20386,7 +20389,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G602" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20412,7 +20415,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G603" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20438,7 +20441,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G604" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20464,7 +20467,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G605" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20490,7 +20493,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G606" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20932,7 +20935,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -20984,7 +20987,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G625" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21036,7 +21039,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G627" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -23532,7 +23535,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G723" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -24052,7 +24055,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G743" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24520,7 +24523,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G761" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -70028,7 +70031,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.691087963</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>245672</v>
@@ -70049,6 +70052,32 @@
         <v>1463</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6912152778</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>92046</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>6.96999979019165</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>6.8899998664856</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>6.94999980926514</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>1464</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="1470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="1471">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,52 +44,52 @@
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447986602783</t>
+    <t xml:space="preserve">4.02447938919067</t>
   </si>
   <si>
     <t xml:space="preserve">3.93978929519653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82799792289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78057146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943140983582</t>
+    <t xml:space="preserve">3.82799816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78057193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943164825439</t>
   </si>
   <si>
     <t xml:space="preserve">3.75685834884644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74330759048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80089735984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040815353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66539216041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56376481056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65184283256531</t>
+    <t xml:space="preserve">3.74330806732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80089640617371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040839195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571805953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66539192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56376504898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65184235572815</t>
   </si>
   <si>
     <t xml:space="preserve">3.72636961936951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70265698432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6586172580719</t>
+    <t xml:space="preserve">3.70265626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65861749649048</t>
   </si>
   <si>
     <t xml:space="preserve">3.69249391555786</t>
@@ -107,67 +107,67 @@
     <t xml:space="preserve">3.58408975601196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49601244926453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4621365070343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51633739471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38760876655579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40793442726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50956273078918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55698919296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56715226173401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6111912727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57731556892395</t>
+    <t xml:space="preserve">3.49601221084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46213626861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51633763313293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38760900497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40793466567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50956249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55698871612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56715178489685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61119031906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57731485366821</t>
   </si>
   <si>
     <t xml:space="preserve">3.54682612419128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52650022506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50278782844543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56037735939026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58070278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60102796554565</t>
+    <t xml:space="preserve">3.52650141716003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50278759002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56037712097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58070230484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60102820396423</t>
   </si>
   <si>
     <t xml:space="preserve">3.54343867301941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5705394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64506697654724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78734683990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84154844284058</t>
+    <t xml:space="preserve">3.57053995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64506721496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78734660148621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84154868125916</t>
   </si>
   <si>
     <t xml:space="preserve">3.86526131629944</t>
@@ -176,34 +176,34 @@
     <t xml:space="preserve">3.85171103477478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92962622642517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93640160560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607618331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90252494812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89575004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285084724426</t>
+    <t xml:space="preserve">3.92962646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93640089035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607570648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90252542495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89574980735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285132408142</t>
   </si>
   <si>
     <t xml:space="preserve">3.90930080413818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97027826309204</t>
+    <t xml:space="preserve">3.97027707099915</t>
   </si>
   <si>
     <t xml:space="preserve">3.87881231307983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85848641395569</t>
+    <t xml:space="preserve">3.85848617553711</t>
   </si>
   <si>
     <t xml:space="preserve">3.94317698478699</t>
@@ -212,61 +212,61 @@
     <t xml:space="preserve">3.89913821220398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94656419754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95672655105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96350240707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91268849372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97366499900818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91946244239807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87203693389893</t>
+    <t xml:space="preserve">3.94656443595886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95672750473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96350193023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91268825531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97366452217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91946291923523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8720371723175</t>
   </si>
   <si>
     <t xml:space="preserve">3.88704800605774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87291240692139</t>
+    <t xml:space="preserve">3.87291264533997</t>
   </si>
   <si>
     <t xml:space="preserve">3.85877871513367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83757591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86231255531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87644672393799</t>
+    <t xml:space="preserve">3.83757638931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86231279373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87644720077515</t>
   </si>
   <si>
     <t xml:space="preserve">3.89411568641663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90118312835693</t>
+    <t xml:space="preserve">3.9011824131012</t>
   </si>
   <si>
     <t xml:space="preserve">3.8905816078186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94358730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95418787002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96125555038452</t>
+    <t xml:space="preserve">3.94358682632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9541871547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9612557888031</t>
   </si>
   <si>
     <t xml:space="preserve">4.01426029205322</t>
@@ -275,142 +275,142 @@
     <t xml:space="preserve">4.02486181259155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08846807479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05666446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03899574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305844306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00719356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97539067268372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97185659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80223894119263</t>
+    <t xml:space="preserve">4.08846759796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05666494369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03899621963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9930579662323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00719308853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97538948059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97185611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80223989486694</t>
   </si>
   <si>
     <t xml:space="preserve">3.78103709220886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75630140304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74923419952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90471625328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9223849773407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065474510193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03546285629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75983548164368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80930757522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83050918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86937975883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82344126701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80577373504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84110999107361</t>
+    <t xml:space="preserve">3.75630164146423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74923491477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90471696853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92238545417786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065355300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03546237945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7598352432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80930709838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83050870895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86937999725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82344198226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80577254295349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84111046791077</t>
   </si>
   <si>
     <t xml:space="preserve">3.81637477874756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86584568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89764904975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93651962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9082498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91531729698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97892379760742</t>
+    <t xml:space="preserve">3.8658459186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89764881134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93651914596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90825009346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91531753540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97892355918884</t>
   </si>
   <si>
     <t xml:space="preserve">4.00012540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02132749557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95772099494934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84464359283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81284022331238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77043676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690316200256</t>
+    <t xml:space="preserve">4.02132797241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95772123336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84464406967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81284070014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77043652534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690292358398</t>
   </si>
   <si>
     <t xml:space="preserve">3.76336860656738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7457001209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72449851036072</t>
+    <t xml:space="preserve">3.74570107460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7244987487793</t>
   </si>
   <si>
     <t xml:space="preserve">3.77397084236145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78810548782349</t>
+    <t xml:space="preserve">3.78810524940491</t>
   </si>
   <si>
     <t xml:space="preserve">3.81990838050842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72803211212158</t>
+    <t xml:space="preserve">3.72803235054016</t>
   </si>
   <si>
     <t xml:space="preserve">3.73863315582275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7315661907196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73510003089905</t>
+    <t xml:space="preserve">3.73156595230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73509931564331</t>
   </si>
   <si>
     <t xml:space="preserve">3.65382504463196</t>
@@ -422,19 +422,19 @@
     <t xml:space="preserve">3.66089248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61848783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61142086982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62555551528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61495423316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64675784111023</t>
+    <t xml:space="preserve">3.61848855018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61142063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62555599212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61495471000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64675760269165</t>
   </si>
   <si>
     <t xml:space="preserve">3.7421669960022</t>
@@ -443,40 +443,40 @@
     <t xml:space="preserve">3.91885137557983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98599076271057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99659252166748</t>
+    <t xml:space="preserve">3.98599123954773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99659204483032</t>
   </si>
   <si>
     <t xml:space="preserve">3.87998032569885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88351392745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79517197608948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82697606086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79163837432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84817814826965</t>
+    <t xml:space="preserve">3.88351440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79517221450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82697510719299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79163861274719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84817719459534</t>
   </si>
   <si>
     <t xml:space="preserve">3.7103636264801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85524463653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03192901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04252958297729</t>
+    <t xml:space="preserve">3.8552451133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03192853927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04253005981445</t>
   </si>
   <si>
     <t xml:space="preserve">4.08493423461914</t>
@@ -485,37 +485,37 @@
     <t xml:space="preserve">4.0990686416626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05313110351562</t>
+    <t xml:space="preserve">4.05313062667847</t>
   </si>
   <si>
     <t xml:space="preserve">4.04959726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09200096130371</t>
+    <t xml:space="preserve">4.09200143814087</t>
   </si>
   <si>
     <t xml:space="preserve">4.10966968536377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0778660774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07433319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04606294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0637321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10613679885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10260200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1344051361084</t>
+    <t xml:space="preserve">4.07786703109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07433271408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04606342315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06373167037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10613632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10260248184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13440608978271</t>
   </si>
   <si>
     <t xml:space="preserve">4.12733840942383</t>
@@ -524,43 +524,43 @@
     <t xml:space="preserve">4.16974210739136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18387746810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15914154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24041652679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21568012237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27575302124023</t>
+    <t xml:space="preserve">4.18387699127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15914106369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24041604995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21568059921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27575254440308</t>
   </si>
   <si>
     <t xml:space="preserve">4.34642601013184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36762857437134</t>
+    <t xml:space="preserve">4.36762762069702</t>
   </si>
   <si>
     <t xml:space="preserve">4.35349369049072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31108951568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30402231216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38176250457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50897550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72806406021118</t>
+    <t xml:space="preserve">4.31108999252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30402183532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38176298141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50897645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72806358337402</t>
   </si>
   <si>
     <t xml:space="preserve">4.91181564331055</t>
@@ -572,52 +572,52 @@
     <t xml:space="preserve">5.19450950622559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22277879714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22984600067139</t>
+    <t xml:space="preserve">5.2227783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22984552383423</t>
   </si>
   <si>
     <t xml:space="preserve">5.2263126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09203243255615</t>
+    <t xml:space="preserve">5.09203290939331</t>
   </si>
   <si>
     <t xml:space="preserve">5.07436418533325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08496475219727</t>
+    <t xml:space="preserve">5.08496570587158</t>
   </si>
   <si>
     <t xml:space="preserve">5.11676836013794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10616731643677</t>
+    <t xml:space="preserve">5.10616683959961</t>
   </si>
   <si>
     <t xml:space="preserve">5.15210580825806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1591739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17330741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1909761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14503717422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13090324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24751567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26871681213379</t>
+    <t xml:space="preserve">5.15917301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1733078956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19097661972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14503812789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13090372085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24751424789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26871633529663</t>
   </si>
   <si>
     <t xml:space="preserve">5.59734869003296</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">5.47720336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37119340896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44186735153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53020906448364</t>
+    <t xml:space="preserve">5.37119388580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44186687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53020858764648</t>
   </si>
   <si>
     <t xml:space="preserve">5.61199712753296</t>
@@ -647,40 +647,40 @@
     <t xml:space="preserve">5.65216112136841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6886739730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6229510307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.619300365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59739208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42213201522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41848039627075</t>
+    <t xml:space="preserve">5.68867349624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62295055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61929941177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5973916053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42213153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41847991943359</t>
   </si>
   <si>
     <t xml:space="preserve">5.55357694625854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56087970733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49880838394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46229600906372</t>
+    <t xml:space="preserve">5.56088018417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49880886077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4622950553894</t>
   </si>
   <si>
     <t xml:space="preserve">5.55722904205322</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45499324798584</t>
+    <t xml:space="preserve">5.45499277114868</t>
   </si>
   <si>
     <t xml:space="preserve">5.36736249923706</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">5.37466526031494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4330849647522</t>
+    <t xml:space="preserve">5.43308544158936</t>
   </si>
   <si>
     <t xml:space="preserve">5.40387487411499</t>
@@ -701,61 +701,61 @@
     <t xml:space="preserve">5.44769048690796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48055219650269</t>
+    <t xml:space="preserve">5.48055171966553</t>
   </si>
   <si>
     <t xml:space="preserve">5.49515676498413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54627418518066</t>
+    <t xml:space="preserve">5.54627466201782</t>
   </si>
   <si>
     <t xml:space="preserve">5.60104370117188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41117763519287</t>
+    <t xml:space="preserve">5.41117715835571</t>
   </si>
   <si>
     <t xml:space="preserve">5.51341390609741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54992580413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45134210586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61564874649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50611066818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34545516967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37101316452026</t>
+    <t xml:space="preserve">5.54992532730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45134162902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61564826965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50611019134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34545564651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37101364135742</t>
   </si>
   <si>
     <t xml:space="preserve">5.31259346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28703451156616</t>
+    <t xml:space="preserve">5.287034034729</t>
   </si>
   <si>
     <t xml:space="preserve">5.15558910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12637853622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2724289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31989622116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14098358154297</t>
+    <t xml:space="preserve">5.12637901306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27242946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31989669799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14098405838013</t>
   </si>
   <si>
     <t xml:space="preserve">5.40752649307251</t>
@@ -764,34 +764,34 @@
     <t xml:space="preserve">5.38927030563354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37831592559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24321937561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46959829330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41482877731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42578220367432</t>
+    <t xml:space="preserve">5.3783164024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24321889877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46959781646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41482925415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42578268051147</t>
   </si>
   <si>
     <t xml:space="preserve">5.44038772583008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48420286178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35275745391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48785352706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50246000289917</t>
+    <t xml:space="preserve">5.48420381546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3527569770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48785448074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50245952606201</t>
   </si>
   <si>
     <t xml:space="preserve">5.57183361053467</t>
@@ -800,67 +800,67 @@
     <t xml:space="preserve">5.57913589477539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56453037261963</t>
+    <t xml:space="preserve">5.56453084945679</t>
   </si>
   <si>
     <t xml:space="preserve">5.52071523666382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53897190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65581226348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58643865585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57548475265503</t>
+    <t xml:space="preserve">5.5389723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65581178665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58643913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57548522949219</t>
   </si>
   <si>
     <t xml:space="preserve">5.50976228713989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53166913986206</t>
+    <t xml:space="preserve">5.53166961669922</t>
   </si>
   <si>
     <t xml:space="preserve">5.60469484329224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59008979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75804853439331</t>
+    <t xml:space="preserve">5.59009027481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75804805755615</t>
   </si>
   <si>
     <t xml:space="preserve">5.79456090927124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92965793609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94426345825195</t>
+    <t xml:space="preserve">5.92965745925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94426298141479</t>
   </si>
   <si>
     <t xml:space="preserve">5.99903154373169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93696069717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98807811737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83107328414917</t>
+    <t xml:space="preserve">5.93696022033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98807764053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83107376098633</t>
   </si>
   <si>
     <t xml:space="preserve">5.88584280014038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83472490310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95886707305908</t>
+    <t xml:space="preserve">5.83472442626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9588680267334</t>
   </si>
   <si>
     <t xml:space="preserve">5.76900196075439</t>
@@ -875,79 +875,79 @@
     <t xml:space="preserve">5.84202718734741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87123680114746</t>
+    <t xml:space="preserve">5.87123727798462</t>
   </si>
   <si>
     <t xml:space="preserve">5.78360652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85298109054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70327854156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82742214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86393451690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75439643859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72883749008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68502283096313</t>
+    <t xml:space="preserve">5.8529806137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7032790184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82742166519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8639349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75439691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72883796691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68502235412598</t>
   </si>
   <si>
     <t xml:space="preserve">5.66676616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88949394226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78725814819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77995586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73614072799683</t>
+    <t xml:space="preserve">5.88949346542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78725862503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77995538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73614025115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.6083459854126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63025379180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53532028198242</t>
+    <t xml:space="preserve">5.63025331497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53532075881958</t>
   </si>
   <si>
     <t xml:space="preserve">5.76169919967651</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62660264968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68137216567993</t>
+    <t xml:space="preserve">5.62660217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68137168884277</t>
   </si>
   <si>
     <t xml:space="preserve">5.73979187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76535034179688</t>
+    <t xml:space="preserve">5.76535081863403</t>
   </si>
   <si>
     <t xml:space="preserve">5.80916547775269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80551433563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82377099990845</t>
+    <t xml:space="preserve">5.80551481246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82377052307129</t>
   </si>
   <si>
     <t xml:space="preserve">5.8785400390625</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">5.82011938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90409851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600584030151</t>
+    <t xml:space="preserve">5.90409898757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600679397583</t>
   </si>
   <si>
     <t xml:space="preserve">5.92235469818115</t>
@@ -968,52 +968,52 @@
     <t xml:space="preserve">5.95156526565552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02459096908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06110382080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00998449325562</t>
+    <t xml:space="preserve">6.02459049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06110334396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00998544692993</t>
   </si>
   <si>
     <t xml:space="preserve">6.09031295776367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22906112670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18524694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03189277648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0391960144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04649829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25096893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20715427398682</t>
+    <t xml:space="preserve">6.2290620803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18524599075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03189325332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03919553756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0464973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25096940994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20715379714966</t>
   </si>
   <si>
     <t xml:space="preserve">6.14143037796021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12682580947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79821157455444</t>
+    <t xml:space="preserve">6.12682628631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7982120513916</t>
   </si>
   <si>
     <t xml:space="preserve">5.72518682479858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96617031097412</t>
+    <t xml:space="preserve">5.96617078781128</t>
   </si>
   <si>
     <t xml:space="preserve">6.00268316268921</t>
@@ -1028,31 +1028,31 @@
     <t xml:space="preserve">5.973473072052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99538087844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1195240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15603685379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10491800308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98077487945557</t>
+    <t xml:space="preserve">5.99538040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11952352523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15603590011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10491847991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98077535629272</t>
   </si>
   <si>
     <t xml:space="preserve">5.90044736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1487340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09761619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05380010604858</t>
+    <t xml:space="preserve">6.14873361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09761571884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05380058288574</t>
   </si>
   <si>
     <t xml:space="preserve">6.07570791244507</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">6.17064094543457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24366664886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28017997741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38636589050293</t>
+    <t xml:space="preserve">6.2436671257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28017950057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38636636734009</t>
   </si>
   <si>
     <t xml:space="preserve">6.31810283660889</t>
@@ -1082,64 +1082,64 @@
     <t xml:space="preserve">6.23467063903809</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28017902374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15882349014282</t>
+    <t xml:space="preserve">6.28017854690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15882301330566</t>
   </si>
   <si>
     <t xml:space="preserve">6.2725944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26500940322876</t>
+    <t xml:space="preserve">6.26501035690308</t>
   </si>
   <si>
     <t xml:space="preserve">6.21191596984863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18157720565796</t>
+    <t xml:space="preserve">6.1815767288208</t>
   </si>
   <si>
     <t xml:space="preserve">6.15123796463013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02988195419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05263614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25742530822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22708606719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24983978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29534912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37119483947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18916130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1664080619812</t>
+    <t xml:space="preserve">6.02988243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05263662338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25742483139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22708559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24983930587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29534864425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37119626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18916177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16640758514404</t>
   </si>
   <si>
     <t xml:space="preserve">6.20433187484741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01471185684204</t>
+    <t xml:space="preserve">6.01471281051636</t>
   </si>
   <si>
     <t xml:space="preserve">6.04505157470703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00712728500366</t>
+    <t xml:space="preserve">6.00712776184082</t>
   </si>
   <si>
     <t xml:space="preserve">5.98437356948853</t>
@@ -1154,43 +1154,43 @@
     <t xml:space="preserve">6.11331462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09055995941162</t>
+    <t xml:space="preserve">6.09055948257446</t>
   </si>
   <si>
     <t xml:space="preserve">5.96161937713623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08297634124756</t>
+    <t xml:space="preserve">6.08297538757324</t>
   </si>
   <si>
     <t xml:space="preserve">6.14365339279175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10572957992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06022119522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99954319000244</t>
+    <t xml:space="preserve">6.10572910308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06022071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99954271316528</t>
   </si>
   <si>
     <t xml:space="preserve">5.95403432846069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93886518478394</t>
+    <t xml:space="preserve">5.93886470794678</t>
   </si>
   <si>
     <t xml:space="preserve">6.06780576705933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91611099243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94644975662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818622589111</t>
+    <t xml:space="preserve">5.91611051559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94645023345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818670272827</t>
   </si>
   <si>
     <t xml:space="preserve">6.03746700286865</t>
@@ -1208,100 +1208,100 @@
     <t xml:space="preserve">6.07539081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24225425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63666248321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46221303939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57598447799683</t>
+    <t xml:space="preserve">6.24225521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738313674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63666296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46221399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57598495483398</t>
   </si>
   <si>
     <t xml:space="preserve">6.56081438064575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6063232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55323028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65183210372925</t>
+    <t xml:space="preserve">6.60632371902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55323076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65183258056641</t>
   </si>
   <si>
     <t xml:space="preserve">6.53806066513062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48496770858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6139087677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66700220108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59873819351196</t>
+    <t xml:space="preserve">6.4849681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61390781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66700172424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59873867034912</t>
   </si>
   <si>
     <t xml:space="preserve">6.34085655212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39395093917847</t>
+    <t xml:space="preserve">6.39395046234131</t>
   </si>
   <si>
     <t xml:space="preserve">6.4167046546936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4242901802063</t>
+    <t xml:space="preserve">6.42428922653198</t>
   </si>
   <si>
     <t xml:space="preserve">6.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59115409851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54564619064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56839990615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44704389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34844207763672</t>
+    <t xml:space="preserve">6.59115314483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54564523696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56839942932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44704341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3484411239624</t>
   </si>
   <si>
     <t xml:space="preserve">6.21950101852417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40911960601807</t>
+    <t xml:space="preserve">6.40912008285522</t>
   </si>
   <si>
     <t xml:space="preserve">6.32568740844727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2877631187439</t>
+    <t xml:space="preserve">6.28776407241821</t>
   </si>
   <si>
     <t xml:space="preserve">6.6897554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6745867729187</t>
+    <t xml:space="preserve">6.67458629608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.74284934997559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75043344497681</t>
+    <t xml:space="preserve">6.75043392181396</t>
   </si>
   <si>
     <t xml:space="preserve">6.62149286270142</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">6.37878036499023</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36361122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46979761123657</t>
+    <t xml:space="preserve">6.36361169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46979856491089</t>
   </si>
   <si>
     <t xml:space="preserve">6.51530647277832</t>
@@ -1322,76 +1322,76 @@
     <t xml:space="preserve">6.31051778793335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35602712631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19674682617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40153551101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72009420394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75801849365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80352735519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78835725784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73526430130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84903621673584</t>
+    <t xml:space="preserve">6.35602617263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19674730300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40153455734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72009468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75801753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80352783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78835773468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73526382446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84903526306152</t>
   </si>
   <si>
     <t xml:space="preserve">6.8642053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81111192703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8414511680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81869697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90213012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99314594268799</t>
+    <t xml:space="preserve">6.81111240386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84145164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81869602203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90212917327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9931468963623</t>
   </si>
   <si>
     <t xml:space="preserve">6.89454507827759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94005346298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05382394790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10691785812378</t>
+    <t xml:space="preserve">6.94005298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05382490158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10691690444946</t>
   </si>
   <si>
     <t xml:space="preserve">7.15242624282837</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11450242996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01590061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08416366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04623937606812</t>
+    <t xml:space="preserve">7.11450147628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01590013504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08416318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04623985290527</t>
   </si>
   <si>
     <t xml:space="preserve">7.09174776077271</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">7.39513826370239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35721445083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34204626083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12208700180054</t>
+    <t xml:space="preserve">7.3572154045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34204578399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1220874786377</t>
   </si>
   <si>
     <t xml:space="preserve">7.13725614547729</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">7.12967205047607</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25102853775024</t>
+    <t xml:space="preserve">7.25102806091309</t>
   </si>
   <si>
     <t xml:space="preserve">7.22827386856079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20552015304565</t>
+    <t xml:space="preserve">7.2055196762085</t>
   </si>
   <si>
     <t xml:space="preserve">7.19793462753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16759538650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37996864318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43306255340576</t>
+    <t xml:space="preserve">7.16759490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37996959686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43306303024292</t>
   </si>
   <si>
     <t xml:space="preserve">7.49374008178711</t>
@@ -1445,58 +1445,58 @@
     <t xml:space="preserve">7.54683303833008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75162172317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79712963104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64543533325195</t>
+    <t xml:space="preserve">7.75162267684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79713010787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64543437957764</t>
   </si>
   <si>
     <t xml:space="preserve">7.69094467163086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57717323303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45581722259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5164942741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59992694854736</t>
+    <t xml:space="preserve">7.57717275619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45581579208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51649522781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59992599487305</t>
   </si>
   <si>
     <t xml:space="preserve">7.50890970230103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56200313568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58475780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55441808700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47856950759888</t>
+    <t xml:space="preserve">7.56200265884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58475732803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55441856384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47857046127319</t>
   </si>
   <si>
     <t xml:space="preserve">7.47098636627197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44823122024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7061128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331792831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88814735412598</t>
+    <t xml:space="preserve">7.4482307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70611333847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331840515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88814830780029</t>
   </si>
   <si>
     <t xml:space="preserve">8.25221538543701</t>
@@ -1505,106 +1505,106 @@
     <t xml:space="preserve">8.61628437042236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49492740631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17636966705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41908073425293</t>
+    <t xml:space="preserve">8.49492645263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17636871337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41908168792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.1187686920166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08742141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93068933486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04040336608887</t>
+    <t xml:space="preserve">8.08742237091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93068981170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04040241241455</t>
   </si>
   <si>
     <t xml:space="preserve">7.96203565597534</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25982856750488</t>
+    <t xml:space="preserve">8.25982761383057</t>
   </si>
   <si>
     <t xml:space="preserve">8.02472972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86799669265747</t>
+    <t xml:space="preserve">7.86799573898315</t>
   </si>
   <si>
     <t xml:space="preserve">7.7347731590271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83665084838867</t>
+    <t xml:space="preserve">7.83664989471436</t>
   </si>
   <si>
     <t xml:space="preserve">7.82097625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91501665115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97770929336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07175064086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05607604980469</t>
+    <t xml:space="preserve">7.91501569747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97771024703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07174968719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05607509613037</t>
   </si>
   <si>
     <t xml:space="preserve">7.85232305526733</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40088939666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46358203887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62031555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30684852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1657886505127</t>
+    <t xml:space="preserve">8.40088844299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46358108520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6203145980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30684947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16578960418701</t>
   </si>
   <si>
     <t xml:space="preserve">8.33819580078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21280765533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27550315856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36954307556152</t>
+    <t xml:space="preserve">8.21280860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27550220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36954212188721</t>
   </si>
   <si>
     <t xml:space="preserve">8.15011596679688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18146133422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13444232940674</t>
+    <t xml:space="preserve">8.18146228790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13444423675537</t>
   </si>
   <si>
     <t xml:space="preserve">8.22848224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43223476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99338293075562</t>
+    <t xml:space="preserve">8.43223571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99338245391846</t>
   </si>
   <si>
     <t xml:space="preserve">8.19713592529297</t>
@@ -1616,46 +1616,46 @@
     <t xml:space="preserve">7.89934206008911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82881307601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88367033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313943862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67991733551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79746675491333</t>
+    <t xml:space="preserve">7.82881355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88366985321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67991781234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79746580123901</t>
   </si>
   <si>
     <t xml:space="preserve">8.41656112670898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80530261993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68775367736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74261093139648</t>
+    <t xml:space="preserve">7.80530309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68775463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74261045455933</t>
   </si>
   <si>
     <t xml:space="preserve">8.00905609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94636392593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75044679641724</t>
+    <t xml:space="preserve">7.94636344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75044727325439</t>
   </si>
   <si>
     <t xml:space="preserve">7.71910047531128</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10309505462646</t>
+    <t xml:space="preserve">8.10309600830078</t>
   </si>
   <si>
     <t xml:space="preserve">8.82406711578369</t>
@@ -1667,13 +1667,13 @@
     <t xml:space="preserve">9.60773277282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.482346534729</t>
+    <t xml:space="preserve">9.48234558105469</t>
   </si>
   <si>
     <t xml:space="preserve">9.79581260681152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93687152862549</t>
+    <t xml:space="preserve">9.9368724822998</t>
   </si>
   <si>
     <t xml:space="preserve">9.87417984008789</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">9.99956512451172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1562986373901</t>
+    <t xml:space="preserve">10.1562976837158</t>
   </si>
   <si>
     <t xml:space="preserve">10.5011100769043</t>
@@ -1691,25 +1691,25 @@
     <t xml:space="preserve">10.3757238388062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5481300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2189893722534</t>
+    <t xml:space="preserve">10.5481309890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2189912796021</t>
   </si>
   <si>
     <t xml:space="preserve">10.1719703674316</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95254611968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90552520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88985157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92119789123535</t>
+    <t xml:space="preserve">9.95254516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90552616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88985061645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92119884490967</t>
   </si>
   <si>
     <t xml:space="preserve">9.73311901092529</t>
@@ -1718,16 +1718,16 @@
     <t xml:space="preserve">9.76446533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57638549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96821975708008</t>
+    <t xml:space="preserve">9.57638645172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96821880340576</t>
   </si>
   <si>
     <t xml:space="preserve">10.030912399292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4854383468628</t>
+    <t xml:space="preserve">10.4854364395142</t>
   </si>
   <si>
     <t xml:space="preserve">10.250337600708</t>
@@ -1739,61 +1739,61 @@
     <t xml:space="preserve">10.1249513626099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.360053062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2973575592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3130321502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4384183883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6264972686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6578454971313</t>
+    <t xml:space="preserve">10.3600511550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2973585128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3130302429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4384174346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6264963150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6578435897827</t>
   </si>
   <si>
     <t xml:space="preserve">10.6108236312866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5951499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5794773101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6421709060669</t>
+    <t xml:space="preserve">10.5951509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.579478263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6421699523926</t>
   </si>
   <si>
     <t xml:space="preserve">10.7518835067749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9869842529297</t>
+    <t xml:space="preserve">10.9869832992554</t>
   </si>
   <si>
     <t xml:space="preserve">10.9556360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.128041267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0183305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2377548217773</t>
+    <t xml:space="preserve">11.1280431747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0183296203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.237756729126</t>
   </si>
   <si>
     <t xml:space="preserve">11.1593885421753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0966968536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1750621795654</t>
+    <t xml:space="preserve">11.0966958999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1750631332397</t>
   </si>
   <si>
     <t xml:space="preserve">11.1123695373535</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">11.0810222625732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9713106155396</t>
+    <t xml:space="preserve">10.9713096618652</t>
   </si>
   <si>
     <t xml:space="preserve">10.7989025115967</t>
@@ -1814,40 +1814,40 @@
     <t xml:space="preserve">10.0936050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6860990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29426670074463</t>
+    <t xml:space="preserve">9.68609809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29426574707031</t>
   </si>
   <si>
     <t xml:space="preserve">9.54504013061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98080158233643</t>
+    <t xml:space="preserve">8.98080062866211</t>
   </si>
   <si>
     <t xml:space="preserve">8.54194831848145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31943035125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50751113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53885746002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49183750152588</t>
+    <t xml:space="preserve">7.31943082809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5075101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53885698318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49183702468872</t>
   </si>
   <si>
     <t xml:space="preserve">8.66733551025391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44790935516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38521480560303</t>
+    <t xml:space="preserve">8.44790840148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38521575927734</t>
   </si>
   <si>
     <t xml:space="preserve">8.52627468109131</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">9.10618686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93378067016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3883056640625</t>
+    <t xml:space="preserve">8.9337797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38830661773682</t>
   </si>
   <si>
     <t xml:space="preserve">8.88676071166992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87108612060547</t>
+    <t xml:space="preserve">8.87108707427979</t>
   </si>
   <si>
     <t xml:space="preserve">9.12185955047607</t>
@@ -1880,25 +1880,25 @@
     <t xml:space="preserve">8.91810703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15320777893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90243339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05916786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04349327087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21589946746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96512794494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30298137664795</t>
+    <t xml:space="preserve">9.15320873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90243434906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05916690826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04349422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21590042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96512699127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30298042297363</t>
   </si>
   <si>
     <t xml:space="preserve">9.12407779693604</t>
@@ -1913,31 +1913,31 @@
     <t xml:space="preserve">8.50604724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70121383666992</t>
+    <t xml:space="preserve">8.70121479034424</t>
   </si>
   <si>
     <t xml:space="preserve">9.18913269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9289083480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76626968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71747875213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97770118713379</t>
+    <t xml:space="preserve">8.92890930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76627063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71747970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97770214080811</t>
   </si>
   <si>
     <t xml:space="preserve">9.33550834655762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48188400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6119966506958</t>
+    <t xml:space="preserve">9.48188591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61199569702148</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625532150269</t>
@@ -1955,16 +1955,16 @@
     <t xml:space="preserve">10.2137622833252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2788181304932</t>
+    <t xml:space="preserve">10.2788190841675</t>
   </si>
   <si>
     <t xml:space="preserve">10.2300262451172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.953537940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88848304748535</t>
+    <t xml:space="preserve">9.95353889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88848400115967</t>
   </si>
   <si>
     <t xml:space="preserve">9.69331550598145</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">10.1324424743652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1974973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3276090621948</t>
+    <t xml:space="preserve">10.1974983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3276100158691</t>
   </si>
   <si>
     <t xml:space="preserve">10.2462911605835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.555305480957</t>
+    <t xml:space="preserve">10.5553045272827</t>
   </si>
   <si>
     <t xml:space="preserve">10.8480567932129</t>
@@ -2003,25 +2003,25 @@
     <t xml:space="preserve">10.685417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6366243362427</t>
+    <t xml:space="preserve">10.636625289917</t>
   </si>
   <si>
     <t xml:space="preserve">10.7667360305786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9781675338745</t>
+    <t xml:space="preserve">10.9781684875488</t>
   </si>
   <si>
     <t xml:space="preserve">11.1245431900024</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1408061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2871837615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3847665786743</t>
+    <t xml:space="preserve">11.1408071517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2871828079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3847675323486</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474061965942</t>
@@ -2033,16 +2033,16 @@
     <t xml:space="preserve">11.4498233795166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4660863876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4823503494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3359746932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.205864906311</t>
+    <t xml:space="preserve">11.4660873413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4823513031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.335973739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2058629989624</t>
   </si>
   <si>
     <t xml:space="preserve">11.2221269607544</t>
@@ -2051,43 +2051,43 @@
     <t xml:space="preserve">10.8643198013306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.539041519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5227766036987</t>
+    <t xml:space="preserve">10.5390405654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5227756500244</t>
   </si>
   <si>
     <t xml:space="preserve">10.701681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8155288696289</t>
+    <t xml:space="preserve">10.8155279159546</t>
   </si>
   <si>
     <t xml:space="preserve">10.604097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7342090606689</t>
+    <t xml:space="preserve">10.7342081069946</t>
   </si>
   <si>
     <t xml:space="preserve">10.620361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7179460525513</t>
+    <t xml:space="preserve">10.717945098877</t>
   </si>
   <si>
     <t xml:space="preserve">10.5065126419067</t>
   </si>
   <si>
-    <t xml:space="preserve">10.587833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4577217102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3764009475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.571569442749</t>
+    <t xml:space="preserve">10.5878343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4577207565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3764028549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5715684890747</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089298248291</t>
@@ -2096,10 +2096,10 @@
     <t xml:space="preserve">10.8968477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0594873428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9944314956665</t>
+    <t xml:space="preserve">11.0594882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9944324493408</t>
   </si>
   <si>
     <t xml:space="preserve">10.6691522598267</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">10.9456396102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2709197998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1895999908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5799350738525</t>
+    <t xml:space="preserve">11.2709188461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1895990371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5799331665039</t>
   </si>
   <si>
     <t xml:space="preserve">11.4172954559326</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">9.9860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0836505889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4414577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7504720687866</t>
+    <t xml:space="preserve">10.0836496353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4414587020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7504730224609</t>
   </si>
   <si>
     <t xml:space="preserve">11.1570711135864</t>
@@ -2156,31 +2156,31 @@
     <t xml:space="preserve">11.2546548843384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3522386550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4010305404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3197116851807</t>
+    <t xml:space="preserve">11.3522396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4010314941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3197107315063</t>
   </si>
   <si>
     <t xml:space="preserve">11.1733350753784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0106954574585</t>
+    <t xml:space="preserve">11.0106964111328</t>
   </si>
   <si>
     <t xml:space="preserve">11.5311422348022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7751007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7100439071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7425727844238</t>
+    <t xml:space="preserve">11.7751016616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7100448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7425737380981</t>
   </si>
   <si>
     <t xml:space="preserve">12.0190601348877</t>
@@ -2189,43 +2189,43 @@
     <t xml:space="preserve">12.3118124008179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5882987976074</t>
+    <t xml:space="preserve">12.5882997512817</t>
   </si>
   <si>
     <t xml:space="preserve">12.1979637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8726844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0027980804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8076295852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8564205169678</t>
+    <t xml:space="preserve">11.8726863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.00279712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8076305389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8564224243164</t>
   </si>
   <si>
     <t xml:space="preserve">11.5961980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9540042877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.986533164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.100380897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1816997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1166439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2792844772339</t>
+    <t xml:space="preserve">11.954005241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9865322113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1003799438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1817007064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.116644859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2792854309082</t>
   </si>
   <si>
     <t xml:space="preserve">12.4093961715698</t>
@@ -2237,19 +2237,19 @@
     <t xml:space="preserve">12.4581871032715</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907140731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8973140716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0111627578735</t>
+    <t xml:space="preserve">12.4907150268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8973150253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0111618041992</t>
   </si>
   <si>
     <t xml:space="preserve">12.9786338806152</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8647871017456</t>
+    <t xml:space="preserve">12.8647861480713</t>
   </si>
   <si>
     <t xml:space="preserve">12.7997303009033</t>
@@ -2258,16 +2258,16 @@
     <t xml:space="preserve">12.6370916366577</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8810501098633</t>
+    <t xml:space="preserve">12.8810510635376</t>
   </si>
   <si>
     <t xml:space="preserve">13.1738023757935</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2713851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3527059555054</t>
+    <t xml:space="preserve">13.2713861465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3527050018311</t>
   </si>
   <si>
     <t xml:space="preserve">13.7267751693726</t>
@@ -2285,16 +2285,16 @@
     <t xml:space="preserve">14.2634878158569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2146940231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9056797027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6129274368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8080949783325</t>
+    <t xml:space="preserve">14.2146949768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9056806564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6129264831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8080959320068</t>
   </si>
   <si>
     <t xml:space="preserve">13.8894147872925</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">13.8406238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7918310165405</t>
+    <t xml:space="preserve">13.7918319702148</t>
   </si>
   <si>
     <t xml:space="preserve">14.0032615661621</t>
@@ -2315,198 +2315,201 @@
     <t xml:space="preserve">13.9544706344604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3448057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1496391296387</t>
+    <t xml:space="preserve">14.3448047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1496381759644</t>
   </si>
   <si>
     <t xml:space="preserve">14.2472219467163</t>
   </si>
   <si>
+    <t xml:space="preserve">14.4749174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5579166412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1927242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1595239639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1429252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2757215499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2923192977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3753185272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1097249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2425212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0765247344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2093229293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9935274124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8109292984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3089199066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.05992603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0101251602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9769277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0433263778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3255205154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2259206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3421201705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1761226654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9437265396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0931243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9603261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.358717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591218948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5081167221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5247173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.026725769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.707311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7737112045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.690712928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7405118942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9397087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1057052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3215007781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1721029281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8899097442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3712997436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7032918930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.537296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.387900352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2883033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2717018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0725059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2219038009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1223039627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9895067214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8235101699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7903099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1389045715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9729089736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.873309135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8069105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8607301712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7113332748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4417171478271</t>
+  </si>
+  <si>
     <t xml:space="preserve">14.4749164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5579166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.192723274231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1595239639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1429252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2757225036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2923192977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3753185272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1097249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2425212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0765247344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2093229293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9935274124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8109292984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3089199066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.05992603302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0101261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9769277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0433263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3255205154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2259216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3421211242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1761226654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9437265396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0931243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9603261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3587188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591218948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5081167221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5247173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.026725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.707311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7737112045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.690712928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7405109405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9397077560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1057052612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3215007781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1721038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8899097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3713006973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7032918930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.537296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2883033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2717018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0725059509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2219038009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1223039627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9895057678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567085266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8235111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7903099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1389045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9729089736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.873309135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8069105148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8607292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6947326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.711332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4417171478271</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.5745153427124</t>
   </si>
   <si>
@@ -2522,16 +2525,16 @@
     <t xml:space="preserve">14.3919191360474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4708976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2053031921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0227079391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4915161132812</t>
+    <t xml:space="preserve">15.4708967208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.205304145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4915151596069</t>
   </si>
   <si>
     <t xml:space="preserve">13.8275299072266</t>
@@ -2540,10 +2543,10 @@
     <t xml:space="preserve">13.7777309417725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6449337005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445306777954</t>
+    <t xml:space="preserve">13.6449346542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445297241211</t>
   </si>
   <si>
     <t xml:space="preserve">13.5287351608276</t>
@@ -2555,7 +2558,7 @@
     <t xml:space="preserve">13.4125375747681</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1137437820435</t>
+    <t xml:space="preserve">13.1137447357178</t>
   </si>
   <si>
     <t xml:space="preserve">13.2797403335571</t>
@@ -2588,16 +2591,16 @@
     <t xml:space="preserve">13.3129405975342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1967430114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7983503341675</t>
+    <t xml:space="preserve">13.1967420578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7983493804932</t>
   </si>
   <si>
     <t xml:space="preserve">12.4497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3003597259521</t>
+    <t xml:space="preserve">12.3003587722778</t>
   </si>
   <si>
     <t xml:space="preserve">12.7153520584106</t>
@@ -2645,7 +2648,7 @@
     <t xml:space="preserve">11.3209781646729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1715822219849</t>
+    <t xml:space="preserve">11.1715812683105</t>
   </si>
   <si>
     <t xml:space="preserve">11.221381187439</t>
@@ -2654,7 +2657,7 @@
     <t xml:space="preserve">10.8395881652832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2088022232056</t>
+    <t xml:space="preserve">10.2088012695312</t>
   </si>
   <si>
     <t xml:space="preserve">10.6735916137695</t>
@@ -2672,10 +2675,10 @@
     <t xml:space="preserve">9.97640514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54481315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56141376495361</t>
+    <t xml:space="preserve">9.54481410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5614128112793</t>
   </si>
   <si>
     <t xml:space="preserve">9.36221694946289</t>
@@ -2687,10 +2690,10 @@
     <t xml:space="preserve">9.32901763916016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52821350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0096044540405</t>
+    <t xml:space="preserve">9.52821445465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0096054077148</t>
   </si>
   <si>
     <t xml:space="preserve">9.39541625976562</t>
@@ -2717,7 +2720,7 @@
     <t xml:space="preserve">10.1424026489258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0594034194946</t>
+    <t xml:space="preserve">10.0594043731689</t>
   </si>
   <si>
     <t xml:space="preserve">9.86020755767822</t>
@@ -2726,7 +2729,7 @@
     <t xml:space="preserve">9.89340686798096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69421195983887</t>
+    <t xml:space="preserve">9.69421100616455</t>
   </si>
   <si>
     <t xml:space="preserve">9.61121273040771</t>
@@ -2735,22 +2738,22 @@
     <t xml:space="preserve">9.17962169647217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27921772003174</t>
+    <t xml:space="preserve">9.27921867370605</t>
   </si>
   <si>
     <t xml:space="preserve">9.37881660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19622039794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29581832885742</t>
+    <t xml:space="preserve">9.19622135162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29581737518311</t>
   </si>
   <si>
     <t xml:space="preserve">9.12982177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42861652374268</t>
+    <t xml:space="preserve">9.42861557006836</t>
   </si>
   <si>
     <t xml:space="preserve">9.77720832824707</t>
@@ -2762,7 +2765,7 @@
     <t xml:space="preserve">10.0262041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5407934188843</t>
+    <t xml:space="preserve">10.5407943725586</t>
   </si>
   <si>
     <t xml:space="preserve">10.4577960968018</t>
@@ -2783,7 +2786,7 @@
     <t xml:space="preserve">9.7205171585083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0639991760254</t>
+    <t xml:space="preserve">10.0639982223511</t>
   </si>
   <si>
     <t xml:space="preserve">10.0983467102051</t>
@@ -2792,16 +2795,16 @@
     <t xml:space="preserve">10.2529125213623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85790920257568</t>
+    <t xml:space="preserve">9.85791015625</t>
   </si>
   <si>
     <t xml:space="preserve">10.0811729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3559579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2700881958008</t>
+    <t xml:space="preserve">10.35595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2700872421265</t>
   </si>
   <si>
     <t xml:space="preserve">10.6479167938232</t>
@@ -2810,7 +2813,7 @@
     <t xml:space="preserve">10.7681341171265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.957049369812</t>
+    <t xml:space="preserve">10.9570503234863</t>
   </si>
   <si>
     <t xml:space="preserve">11.1631383895874</t>
@@ -2840,7 +2843,7 @@
     <t xml:space="preserve">10.0124759674072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.390305519104</t>
+    <t xml:space="preserve">10.3903064727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1498689651489</t>
@@ -2873,7 +2876,7 @@
     <t xml:space="preserve">10.0468244552612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5620470046997</t>
+    <t xml:space="preserve">10.5620460510254</t>
   </si>
   <si>
     <t xml:space="preserve">10.6307430267334</t>
@@ -2882,16 +2885,16 @@
     <t xml:space="preserve">10.424654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7166128158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.459002494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5105237960815</t>
+    <t xml:space="preserve">10.4418287277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5105228424072</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509613037109</t>
@@ -2903,13 +2906,13 @@
     <t xml:space="preserve">10.493350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1155214309692</t>
+    <t xml:space="preserve">10.1155204772949</t>
   </si>
   <si>
     <t xml:space="preserve">9.7548656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61747360229492</t>
+    <t xml:space="preserve">9.61747264862061</t>
   </si>
   <si>
     <t xml:space="preserve">9.37703609466553</t>
@@ -2918,7 +2921,7 @@
     <t xml:space="preserve">9.51442909240723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63464641571045</t>
+    <t xml:space="preserve">9.63464736938477</t>
   </si>
   <si>
     <t xml:space="preserve">9.80638790130615</t>
@@ -2933,7 +2936,7 @@
     <t xml:space="preserve">9.49725532531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39421081542969</t>
+    <t xml:space="preserve">9.39420986175537</t>
   </si>
   <si>
     <t xml:space="preserve">9.22246932983398</t>
@@ -2942,13 +2945,13 @@
     <t xml:space="preserve">9.32551383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25681686401367</t>
+    <t xml:space="preserve">9.25681781768799</t>
   </si>
   <si>
     <t xml:space="preserve">9.4629077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0850772857666</t>
+    <t xml:space="preserve">9.08507633209229</t>
   </si>
   <si>
     <t xml:space="preserve">9.54877662658691</t>
@@ -2969,7 +2972,7 @@
     <t xml:space="preserve">10.3387842178345</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5963945388794</t>
+    <t xml:space="preserve">10.5963954925537</t>
   </si>
   <si>
     <t xml:space="preserve">10.8540058135986</t>
@@ -2978,13 +2981,13 @@
     <t xml:space="preserve">11.4550971984863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2661819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0429191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8883533477783</t>
+    <t xml:space="preserve">11.2661828994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0429201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8883543014526</t>
   </si>
   <si>
     <t xml:space="preserve">10.9398756027222</t>
@@ -2993,7 +2996,7 @@
     <t xml:space="preserve">10.8196573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8024835586548</t>
+    <t xml:space="preserve">10.8024826049805</t>
   </si>
   <si>
     <t xml:space="preserve">11.3692274093628</t>
@@ -3002,25 +3005,25 @@
     <t xml:space="preserve">11.4379234313965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0733633041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4683666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5027160644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2966260910034</t>
+    <t xml:space="preserve">12.0733642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4683675765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5027151107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2966251373291</t>
   </si>
   <si>
     <t xml:space="preserve">12.0561895370483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7470569610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7127075195312</t>
+    <t xml:space="preserve">11.7470560073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7127084732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.9703187942505</t>
@@ -3032,13 +3035,13 @@
     <t xml:space="preserve">12.0046663284302</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0218410491943</t>
+    <t xml:space="preserve">12.0218420028687</t>
   </si>
   <si>
     <t xml:space="preserve">11.8157529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2279300689697</t>
+    <t xml:space="preserve">12.227931022644</t>
   </si>
   <si>
     <t xml:space="preserve">12.3653221130371</t>
@@ -3053,7 +3056,7 @@
     <t xml:space="preserve">12.3138008117676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5198888778687</t>
+    <t xml:space="preserve">12.519889831543</t>
   </si>
   <si>
     <t xml:space="preserve">12.485541343689</t>
@@ -3065,16 +3068,16 @@
     <t xml:space="preserve">12.2451038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2794523239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1420602798462</t>
+    <t xml:space="preserve">12.2794532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1420593261719</t>
   </si>
   <si>
     <t xml:space="preserve">12.1248865127563</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1764078140259</t>
+    <t xml:space="preserve">12.1764087677002</t>
   </si>
   <si>
     <t xml:space="preserve">12.159234046936</t>
@@ -3083,10 +3086,10 @@
     <t xml:space="preserve">12.1077117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3481492996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6572818756104</t>
+    <t xml:space="preserve">12.3481483459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.657280921936</t>
   </si>
   <si>
     <t xml:space="preserve">12.9148921966553</t>
@@ -3095,19 +3098,19 @@
     <t xml:space="preserve">13.0694599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1038084030151</t>
+    <t xml:space="preserve">13.1038074493408</t>
   </si>
   <si>
     <t xml:space="preserve">13.0866327285767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.18967628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6705513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3442430496216</t>
+    <t xml:space="preserve">13.1896772384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6705503463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3442440032959</t>
   </si>
   <si>
     <t xml:space="preserve">13.6362028121948</t>
@@ -3119,7 +3122,7 @@
     <t xml:space="preserve">13.5503330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5675058364868</t>
+    <t xml:space="preserve">13.5675067901611</t>
   </si>
   <si>
     <t xml:space="preserve">13.4644622802734</t>
@@ -3131,7 +3134,7 @@
     <t xml:space="preserve">13.5159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.619029045105</t>
+    <t xml:space="preserve">13.6190280914307</t>
   </si>
   <si>
     <t xml:space="preserve">14.082727432251</t>
@@ -3152,7 +3155,7 @@
     <t xml:space="preserve">14.6151247024536</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7353429794312</t>
+    <t xml:space="preserve">14.7353420257568</t>
   </si>
   <si>
     <t xml:space="preserve">14.6494731903076</t>
@@ -3179,52 +3182,52 @@
     <t xml:space="preserve">15.3879566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1990423202515</t>
+    <t xml:space="preserve">15.1990432739258</t>
   </si>
   <si>
     <t xml:space="preserve">15.2505645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1818685531616</t>
+    <t xml:space="preserve">15.1818675994873</t>
   </si>
   <si>
     <t xml:space="preserve">15.2162160873413</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9757785797119</t>
+    <t xml:space="preserve">14.9757795333862</t>
   </si>
   <si>
     <t xml:space="preserve">14.9242563247681</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4262094497681</t>
+    <t xml:space="preserve">14.4262084960938</t>
   </si>
   <si>
     <t xml:space="preserve">14.3918619155884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9586067199707</t>
+    <t xml:space="preserve">14.9586057662964</t>
   </si>
   <si>
     <t xml:space="preserve">14.5464286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1131725311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1303462982178</t>
+    <t xml:space="preserve">15.1131715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1303472518921</t>
   </si>
   <si>
     <t xml:space="preserve">14.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2677383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4223041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9031791687012</t>
+    <t xml:space="preserve">15.2677392959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4223051071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9031782150269</t>
   </si>
   <si>
     <t xml:space="preserve">15.9375276565552</t>
@@ -3233,22 +3236,22 @@
     <t xml:space="preserve">16.1436157226562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.851655960083</t>
+    <t xml:space="preserve">15.8516550064087</t>
   </si>
   <si>
     <t xml:space="preserve">15.9546995162964</t>
   </si>
   <si>
-    <t xml:space="preserve">15.782958984375</t>
+    <t xml:space="preserve">15.7829599380493</t>
   </si>
   <si>
     <t xml:space="preserve">15.7142639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5253505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5596971511841</t>
+    <t xml:space="preserve">15.5253496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5596981048584</t>
   </si>
   <si>
     <t xml:space="preserve">14.8383884429932</t>
@@ -3257,7 +3260,7 @@
     <t xml:space="preserve">14.4605579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3059911727905</t>
+    <t xml:space="preserve">14.3059921264648</t>
   </si>
   <si>
     <t xml:space="preserve">14.2888164520264</t>
@@ -3269,16 +3272,16 @@
     <t xml:space="preserve">14.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7009954452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5807762145996</t>
+    <t xml:space="preserve">14.7009963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5807752609253</t>
   </si>
   <si>
     <t xml:space="preserve">14.5292539596558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3746871948242</t>
+    <t xml:space="preserve">14.3746862411499</t>
   </si>
   <si>
     <t xml:space="preserve">14.1431245803833</t>
@@ -3290,9 +3293,6 @@
     <t xml:space="preserve">14.321249961853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3746862411499</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.6596870422363</t>
   </si>
   <si>
@@ -4422,6 +4422,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.96999979019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15000009536743</t>
   </si>
 </sst>
 </file>
@@ -43128,7 +43131,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1476" t="s">
-        <v>770</v>
+        <v>831</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -43154,7 +43157,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1477" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -43180,7 +43183,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1478" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -43206,7 +43209,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1479" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -43232,7 +43235,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1480" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -43258,7 +43261,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1481" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -43284,7 +43287,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1482" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -43310,7 +43313,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1483" t="s">
-        <v>770</v>
+        <v>831</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -43362,7 +43365,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1485" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -43388,7 +43391,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1486" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -43414,7 +43417,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1487" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -43466,7 +43469,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1489" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -43518,7 +43521,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1491" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -43570,7 +43573,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43648,7 +43651,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1496" t="s">
-        <v>770</v>
+        <v>831</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43674,7 +43677,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1497" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43700,7 +43703,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1498" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43882,7 +43885,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1505" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43934,7 +43937,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1507" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43960,7 +43963,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1508" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43986,7 +43989,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1509" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -44116,7 +44119,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1514" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -44142,7 +44145,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1515" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -44168,7 +44171,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1516" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -44220,7 +44223,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1518" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -44246,7 +44249,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -44272,7 +44275,7 @@
         <v>16</v>
       </c>
       <c r="G1520" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -44298,7 +44301,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1521" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -44324,7 +44327,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1522" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -44532,7 +44535,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1530" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -44558,7 +44561,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44584,7 +44587,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1532" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44610,7 +44613,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1533" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44636,7 +44639,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1534" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44662,7 +44665,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1535" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44688,7 +44691,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1536" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44714,7 +44717,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1537" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44740,7 +44743,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1538" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44766,7 +44769,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G1539" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44792,7 +44795,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44818,7 +44821,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1541" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44844,7 +44847,7 @@
         <v>15</v>
       </c>
       <c r="G1542" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44870,7 +44873,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1543" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44896,7 +44899,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1544" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44922,7 +44925,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1545" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44948,7 +44951,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1546" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44974,7 +44977,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1547" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -45000,7 +45003,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1548" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -45026,7 +45029,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1549" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -45052,7 +45055,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1550" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -45078,7 +45081,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1551" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -45104,7 +45107,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1552" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -45130,7 +45133,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1553" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -45156,7 +45159,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1554" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -45182,7 +45185,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1555" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -45208,7 +45211,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1556" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -45234,7 +45237,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1557" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -45260,7 +45263,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -45286,7 +45289,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1559" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -45312,7 +45315,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1560" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -45338,7 +45341,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1561" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -45364,7 +45367,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1562" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -45390,7 +45393,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1563" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -45416,7 +45419,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1564" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -45442,7 +45445,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1565" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -45468,7 +45471,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1566" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -45494,7 +45497,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1567" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -45520,7 +45523,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1568" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -45546,7 +45549,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1569" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -45572,7 +45575,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1570" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45598,7 +45601,7 @@
         <v>11.5</v>
       </c>
       <c r="G1571" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45624,7 +45627,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1572" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45650,7 +45653,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1573" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45676,7 +45679,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1574" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45702,7 +45705,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1575" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45728,7 +45731,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1576" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45754,7 +45757,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1577" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45780,7 +45783,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1578" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45806,7 +45809,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1579" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45832,7 +45835,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1580" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45858,7 +45861,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1581" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45884,7 +45887,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1582" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45910,7 +45913,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1583" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45936,7 +45939,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1584" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45962,7 +45965,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1585" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45988,7 +45991,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1586" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -46014,7 +46017,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1587" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -46040,7 +46043,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1588" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -46066,7 +46069,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1589" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -46092,7 +46095,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1590" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -46118,7 +46121,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1591" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -46144,7 +46147,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1592" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -46170,7 +46173,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1593" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -46196,7 +46199,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1594" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -46222,7 +46225,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1595" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -46248,7 +46251,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -46274,7 +46277,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1597" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -46300,7 +46303,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1598" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -46326,7 +46329,7 @@
         <v>11</v>
       </c>
       <c r="G1599" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -46352,7 +46355,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1600" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -46378,7 +46381,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1601" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -46404,7 +46407,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1602" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -46430,7 +46433,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1603" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -46456,7 +46459,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1604" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -46482,7 +46485,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1605" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -46508,7 +46511,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1606" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -46534,7 +46537,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1607" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -46560,7 +46563,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1608" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46586,7 +46589,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1609" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -46612,7 +46615,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1610" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46638,7 +46641,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1611" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -46664,7 +46667,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1612" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46690,7 +46693,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1613" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -46716,7 +46719,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1614" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -46742,7 +46745,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1615" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46768,7 +46771,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1616" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -46794,7 +46797,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1617" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46820,7 +46823,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1618" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46846,7 +46849,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1619" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46872,7 +46875,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1620" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46898,7 +46901,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1621" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46924,7 +46927,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1622" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46950,7 +46953,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1623" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46976,7 +46979,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1624" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -47002,7 +47005,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1625" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -47028,7 +47031,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1626" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -47054,7 +47057,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1627" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -47080,7 +47083,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1628" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -47106,7 +47109,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1629" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47132,7 +47135,7 @@
         <v>13</v>
       </c>
       <c r="G1630" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47158,7 +47161,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1631" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47184,7 +47187,7 @@
         <v>13</v>
       </c>
       <c r="G1632" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47210,7 +47213,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1633" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47236,7 +47239,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1634" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47262,7 +47265,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1635" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47288,7 +47291,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1636" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47314,7 +47317,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1637" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47340,7 +47343,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1638" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47366,7 +47369,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1639" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47392,7 +47395,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1640" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47418,7 +47421,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1641" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47444,7 +47447,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1642" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47470,7 +47473,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1643" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47496,7 +47499,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1644" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47522,7 +47525,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1645" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47548,7 +47551,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1646" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47574,7 +47577,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1647" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47600,7 +47603,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1648" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47626,7 +47629,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1649" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47652,7 +47655,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1650" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47678,7 +47681,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1651" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47704,7 +47707,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1652" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47730,7 +47733,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1653" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47756,7 +47759,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1654" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47782,7 +47785,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1655" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47808,7 +47811,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1656" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47834,7 +47837,7 @@
         <v>11.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47860,7 +47863,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1658" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47886,7 +47889,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1659" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47912,7 +47915,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1660" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47938,7 +47941,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1661" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47964,7 +47967,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1662" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47990,7 +47993,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1663" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -48016,7 +48019,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1664" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -48042,7 +48045,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1665" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -48068,7 +48071,7 @@
         <v>12</v>
       </c>
       <c r="G1666" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48094,7 +48097,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1667" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -48120,7 +48123,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1668" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48146,7 +48149,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1669" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48172,7 +48175,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1670" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48198,7 +48201,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1671" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48224,7 +48227,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1672" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48250,7 +48253,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1673" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48276,7 +48279,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1674" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48302,7 +48305,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1675" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48328,7 +48331,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1676" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48354,7 +48357,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1677" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48380,7 +48383,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1678" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48406,7 +48409,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1679" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48432,7 +48435,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1680" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48458,7 +48461,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1681" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48484,7 +48487,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1682" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48510,7 +48513,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1683" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48536,7 +48539,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1684" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48562,7 +48565,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1685" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48588,7 +48591,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1686" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48614,7 +48617,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1687" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48640,7 +48643,7 @@
         <v>12</v>
       </c>
       <c r="G1688" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48666,7 +48669,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1689" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48692,7 +48695,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1690" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48718,7 +48721,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1691" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48744,7 +48747,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1692" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -48770,7 +48773,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1693" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -48796,7 +48799,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1694" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48822,7 +48825,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1695" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48848,7 +48851,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1696" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48874,7 +48877,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48900,7 +48903,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1698" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48926,7 +48929,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1699" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48952,7 +48955,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1700" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48978,7 +48981,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1701" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -49004,7 +49007,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1702" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -49030,7 +49033,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1703" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -49056,7 +49059,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1704" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -49082,7 +49085,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1705" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -49108,7 +49111,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1706" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -49134,7 +49137,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1707" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -49160,7 +49163,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1708" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -49186,7 +49189,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1709" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -49212,7 +49215,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1710" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49238,7 +49241,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1711" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49264,7 +49267,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1712" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -49290,7 +49293,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1713" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49316,7 +49319,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1714" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -49342,7 +49345,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1715" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -49368,7 +49371,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1716" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -49394,7 +49397,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1717" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49420,7 +49423,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1718" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -49446,7 +49449,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1719" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49472,7 +49475,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1720" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -49498,7 +49501,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1721" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49524,7 +49527,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1722" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49550,7 +49553,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1723" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49576,7 +49579,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1724" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49602,7 +49605,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1725" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49628,7 +49631,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1726" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49654,7 +49657,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1727" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49680,7 +49683,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1728" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49706,7 +49709,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1729" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49732,7 +49735,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1730" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -49758,7 +49761,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -49784,7 +49787,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1732" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -49810,7 +49813,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G1733" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -49836,7 +49839,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1734" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -49862,7 +49865,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1735" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49888,7 +49891,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1736" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49914,7 +49917,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1737" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49940,7 +49943,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1738" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49966,7 +49969,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1739" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -49992,7 +49995,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1740" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -50018,7 +50021,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1741" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -50044,7 +50047,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1742" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -50070,7 +50073,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1743" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -50096,7 +50099,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1744" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -50122,7 +50125,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1745" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -50148,7 +50151,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1746" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -50174,7 +50177,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1747" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -50200,7 +50203,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1748" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -50226,7 +50229,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1749" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50252,7 +50255,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1750" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -50278,7 +50281,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1751" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -50304,7 +50307,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1752" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -50330,7 +50333,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1753" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -50356,7 +50359,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -50382,7 +50385,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1755" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -50408,7 +50411,7 @@
         <v>14</v>
       </c>
       <c r="G1756" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -50434,7 +50437,7 @@
         <v>14</v>
       </c>
       <c r="G1757" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50460,7 +50463,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1758" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -50486,7 +50489,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1759" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -50512,7 +50515,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1760" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50538,7 +50541,7 @@
         <v>14</v>
       </c>
       <c r="G1761" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50564,7 +50567,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1762" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50590,7 +50593,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -50616,7 +50619,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1764" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -50642,7 +50645,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1765" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50668,7 +50671,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1766" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -50694,7 +50697,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1767" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50720,7 +50723,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1768" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -50746,7 +50749,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1769" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -50772,7 +50775,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1770" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50798,7 +50801,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1771" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50824,7 +50827,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1772" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -50850,7 +50853,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1773" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50876,7 +50879,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1774" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50902,7 +50905,7 @@
         <v>14</v>
       </c>
       <c r="G1775" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50928,7 +50931,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1776" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50954,7 +50957,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1777" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50980,7 +50983,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1778" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -51006,7 +51009,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1779" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -51032,7 +51035,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1780" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -51058,7 +51061,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1781" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -51084,7 +51087,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -51110,7 +51113,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1783" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -51136,7 +51139,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1784" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -51162,7 +51165,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1785" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -51188,7 +51191,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1786" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -51214,7 +51217,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1787" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -51240,7 +51243,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1788" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -51266,7 +51269,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1789" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51292,7 +51295,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1790" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51318,7 +51321,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1791" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -51344,7 +51347,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1792" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -51370,7 +51373,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1793" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -51396,7 +51399,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1794" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51422,7 +51425,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1795" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -51448,7 +51451,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1796" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -51474,7 +51477,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1797" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51500,7 +51503,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1798" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51526,7 +51529,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1799" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51552,7 +51555,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1800" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -51578,7 +51581,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1801" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -51604,7 +51607,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1802" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -51630,7 +51633,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1803" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51656,7 +51659,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1804" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -51682,7 +51685,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1805" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -51708,7 +51711,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1806" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51734,7 +51737,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1807" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -51760,7 +51763,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51786,7 +51789,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1809" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51812,7 +51815,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1810" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51838,7 +51841,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1811" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51864,7 +51867,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1812" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51890,7 +51893,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1813" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51916,7 +51919,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1814" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51942,7 +51945,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1815" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51968,7 +51971,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1816" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51994,7 +51997,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1817" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -52020,7 +52023,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1818" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -52046,7 +52049,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1819" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -52072,7 +52075,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1820" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -52098,7 +52101,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1821" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -52124,7 +52127,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1822" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -52150,7 +52153,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1823" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -52176,7 +52179,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1824" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -52202,7 +52205,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1825" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -52228,7 +52231,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1826" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -52254,7 +52257,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1827" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52280,7 +52283,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1828" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -52306,7 +52309,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1829" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -52332,7 +52335,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1830" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -52358,7 +52361,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1831" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -52384,7 +52387,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1832" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -52410,7 +52413,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1833" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52436,7 +52439,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1834" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -52462,7 +52465,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1835" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52488,7 +52491,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1836" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52514,7 +52517,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1837" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52540,7 +52543,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1838" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -52566,7 +52569,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1839" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -52592,7 +52595,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52618,7 +52621,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1841" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52644,7 +52647,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1842" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52670,7 +52673,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1843" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52696,7 +52699,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1844" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52722,7 +52725,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1845" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52748,7 +52751,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1846" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52774,7 +52777,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1847" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52800,7 +52803,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1848" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52826,7 +52829,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1849" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52852,7 +52855,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1850" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52878,7 +52881,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1851" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52904,7 +52907,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1852" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52930,7 +52933,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1853" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52956,7 +52959,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1854" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52982,7 +52985,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1855" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -53008,7 +53011,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1856" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -53034,7 +53037,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1857" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -53060,7 +53063,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G1858" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -53086,7 +53089,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1859" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -53112,7 +53115,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1860" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -53138,7 +53141,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1861" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -53164,7 +53167,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1862" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -53190,7 +53193,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1863" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -53216,7 +53219,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1864" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -53242,7 +53245,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1865" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -53268,7 +53271,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1866" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -53294,7 +53297,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -53320,7 +53323,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1868" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -53346,7 +53349,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1869" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53372,7 +53375,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1870" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53398,7 +53401,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1871" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53424,7 +53427,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1872" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53450,7 +53453,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1873" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53476,7 +53479,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1874" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53502,7 +53505,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1875" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53528,7 +53531,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1876" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53554,7 +53557,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1877" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53580,7 +53583,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1878" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -55140,7 +55143,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1938" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -70202,7 +70205,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6910648148</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>90583</v>
@@ -70223,6 +70226,32 @@
         <v>1459</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6912962963</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>81444</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>7.19000005722046</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>7.01000022888184</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>7.15000009536743</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04141759872437</t>
+    <t xml:space="preserve">4.04141807556152</t>
   </si>
   <si>
     <t xml:space="preserve">ZV.MI</t>
@@ -50,55 +50,55 @@
     <t xml:space="preserve">3.93978929519653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82799816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78057193756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75685834884644</t>
+    <t xml:space="preserve">3.82799768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78057074546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943236351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75685858726501</t>
   </si>
   <si>
     <t xml:space="preserve">3.74330806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80089640617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040839195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571805953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66539192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56376504898071</t>
+    <t xml:space="preserve">3.80089735984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040863037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571782112122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66539263725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56376481056213</t>
   </si>
   <si>
     <t xml:space="preserve">3.65184235572815</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72636961936951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70265626907349</t>
+    <t xml:space="preserve">3.72636914253235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70265674591064</t>
   </si>
   <si>
     <t xml:space="preserve">3.65861749649048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69249391555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74669504165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59764099121094</t>
+    <t xml:space="preserve">3.6924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74669528007507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5976402759552</t>
   </si>
   <si>
     <t xml:space="preserve">3.59086537361145</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">3.58408975601196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49601221084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46213626861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51633763313293</t>
+    <t xml:space="preserve">3.49601197242737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46213579177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51633810997009</t>
   </si>
   <si>
     <t xml:space="preserve">3.38760900497437</t>
@@ -122,25 +122,25 @@
     <t xml:space="preserve">3.40793466567993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50956249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55698871612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56715178489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61119031906128</t>
+    <t xml:space="preserve">3.50956273078918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55698919296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56715226173401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61119103431702</t>
   </si>
   <si>
     <t xml:space="preserve">3.57731485366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54682612419128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52650141716003</t>
+    <t xml:space="preserve">3.54682636260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52650046348572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50278759002686</t>
@@ -149,28 +149,28 @@
     <t xml:space="preserve">3.56037712097168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58070230484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60102820396423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54343867301941</t>
+    <t xml:space="preserve">3.58070206642151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60102796554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54343891143799</t>
   </si>
   <si>
     <t xml:space="preserve">3.57053995132446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64506721496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78734660148621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84154868125916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86526131629944</t>
+    <t xml:space="preserve">3.64506793022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78734683990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84154796600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86526203155518</t>
   </si>
   <si>
     <t xml:space="preserve">3.85171103477478</t>
@@ -179,79 +179,79 @@
     <t xml:space="preserve">3.92962646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93640089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607570648193</t>
+    <t xml:space="preserve">3.9364013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607546806335</t>
   </si>
   <si>
     <t xml:space="preserve">3.90252542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89574980735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285132408142</t>
+    <t xml:space="preserve">3.89575004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285084724426</t>
   </si>
   <si>
     <t xml:space="preserve">3.90930080413818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97027707099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87881231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85848617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94317698478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89913821220398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94656443595886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95672750473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96350193023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91268825531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97366452217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91946291923523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8720371723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88704800605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87291264533997</t>
+    <t xml:space="preserve">3.97027730941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87881183624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85848689079285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94317674636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8991379737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94656348228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9567277431488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96350288391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91268849372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97366428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91946387290955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87203693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88704705238342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87291359901428</t>
   </si>
   <si>
     <t xml:space="preserve">3.85877871513367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83757638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86231279373169</t>
+    <t xml:space="preserve">3.83757662773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86231231689453</t>
   </si>
   <si>
     <t xml:space="preserve">3.87644720077515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89411568641663</t>
+    <t xml:space="preserve">3.89411520957947</t>
   </si>
   <si>
     <t xml:space="preserve">3.9011824131012</t>
@@ -260,67 +260,67 @@
     <t xml:space="preserve">3.8905816078186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94358682632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9541871547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9612557888031</t>
+    <t xml:space="preserve">3.9435863494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95418763160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96125531196594</t>
   </si>
   <si>
     <t xml:space="preserve">4.01426029205322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02486181259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08846759796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05666494369507</t>
+    <t xml:space="preserve">4.02486228942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08846807479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05666446685791</t>
   </si>
   <si>
     <t xml:space="preserve">4.03899621963501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9930579662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00719308853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97538948059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97185611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80223989486694</t>
+    <t xml:space="preserve">3.99305820465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00719261169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97539019584656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97185659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80224084854126</t>
   </si>
   <si>
     <t xml:space="preserve">3.78103709220886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75630164146423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74923491477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90471696853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92238545417786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065355300903</t>
+    <t xml:space="preserve">3.75630187988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74923419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90471649169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9223849773407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065402984619</t>
   </si>
   <si>
     <t xml:space="preserve">4.03546237945557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7598352432251</t>
+    <t xml:space="preserve">3.75983619689941</t>
   </si>
   <si>
     <t xml:space="preserve">3.80930709838867</t>
@@ -332,16 +332,16 @@
     <t xml:space="preserve">3.86937999725342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82344198226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80577254295349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84111046791077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81637477874756</t>
+    <t xml:space="preserve">3.82344150543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80577349662781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84111022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8163743019104</t>
   </si>
   <si>
     <t xml:space="preserve">3.8658459186554</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">3.90825009346008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91531753540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97892355918884</t>
+    <t xml:space="preserve">3.91531729698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97892379760742</t>
   </si>
   <si>
     <t xml:space="preserve">4.00012540817261</t>
@@ -368,136 +368,136 @@
     <t xml:space="preserve">4.02132797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95772123336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84464406967163</t>
+    <t xml:space="preserve">3.95772171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84464335441589</t>
   </si>
   <si>
     <t xml:space="preserve">3.81284070014954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77043652534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690292358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76336860656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74570107460022</t>
+    <t xml:space="preserve">3.77043676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690316200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76336908340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74570059776306</t>
   </si>
   <si>
     <t xml:space="preserve">3.7244987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77397084236145</t>
+    <t xml:space="preserve">3.77397036552429</t>
   </si>
   <si>
     <t xml:space="preserve">3.78810524940491</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81990838050842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72803235054016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73863315582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73156595230103</t>
+    <t xml:space="preserve">3.81990790367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72803258895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73863291740417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73156571388245</t>
   </si>
   <si>
     <t xml:space="preserve">3.73509931564331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65382504463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63969087600708</t>
+    <t xml:space="preserve">3.65382528305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63969111442566</t>
   </si>
   <si>
     <t xml:space="preserve">3.66089248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61848855018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61142063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62555599212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61495471000671</t>
+    <t xml:space="preserve">3.618488073349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61142086982727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62555551528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61495494842529</t>
   </si>
   <si>
     <t xml:space="preserve">3.64675760269165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7421669960022</t>
+    <t xml:space="preserve">3.74216628074646</t>
   </si>
   <si>
     <t xml:space="preserve">3.91885137557983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98599123954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99659204483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87998032569885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88351440429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79517221450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82697510719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79163861274719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84817719459534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7103636264801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8552451133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03192853927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04253005981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08493423461914</t>
+    <t xml:space="preserve">3.98599100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9965922832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87998080253601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88351345062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79517269134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82697558403015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79163837432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84817695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71036386489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85524463653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03192949295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04252910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08493375778198</t>
   </si>
   <si>
     <t xml:space="preserve">4.0990686416626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05313062667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04959726333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09200143814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10966968536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07786703109741</t>
+    <t xml:space="preserve">4.05313158035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04959678649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09200096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10967016220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07786655426025</t>
   </si>
   <si>
     <t xml:space="preserve">4.07433271408081</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">4.04606342315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06373167037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10613632202148</t>
+    <t xml:space="preserve">4.0637321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10613584518433</t>
   </si>
   <si>
     <t xml:space="preserve">4.10260248184204</t>
@@ -521,43 +521,43 @@
     <t xml:space="preserve">4.12733840942383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16974210739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18387699127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15914106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24041604995728</t>
+    <t xml:space="preserve">4.16974258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18387746810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15914154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24041652679443</t>
   </si>
   <si>
     <t xml:space="preserve">4.21568059921265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27575254440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34642601013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36762762069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35349369049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31108999252319</t>
+    <t xml:space="preserve">4.27575302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34642648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36762809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35349273681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31108903884888</t>
   </si>
   <si>
     <t xml:space="preserve">4.30402183532715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38176298141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50897645950317</t>
+    <t xml:space="preserve">4.38176250457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50897550582886</t>
   </si>
   <si>
     <t xml:space="preserve">4.72806358337402</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">4.94715213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19450950622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2227783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22984552383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2263126373291</t>
+    <t xml:space="preserve">5.19450902938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22277927398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2298469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22631216049194</t>
   </si>
   <si>
     <t xml:space="preserve">5.09203290939331</t>
@@ -593,34 +593,34 @@
     <t xml:space="preserve">5.11676836013794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10616683959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15210580825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15917301177979</t>
+    <t xml:space="preserve">5.10616731643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1521053314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15917253494263</t>
   </si>
   <si>
     <t xml:space="preserve">5.1733078956604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19097661972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14503812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13090372085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24751424789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26871633529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59734869003296</t>
+    <t xml:space="preserve">5.19097566604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14503765106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13090324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24751472473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26871681213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59734964370728</t>
   </si>
   <si>
     <t xml:space="preserve">5.51254081726074</t>
@@ -629,52 +629,52 @@
     <t xml:space="preserve">5.35705852508545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47720336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37119388580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44186687469482</t>
+    <t xml:space="preserve">5.47720384597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37119340896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44186735153198</t>
   </si>
   <si>
     <t xml:space="preserve">5.53020858764648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61199712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65216112136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68867349624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62295055389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61929941177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5973916053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42213153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41847991943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55357694625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56088018417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49880886077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4622950553894</t>
+    <t xml:space="preserve">5.61199760437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65216159820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6886739730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6229510307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61929988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59739255905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42213201522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41848087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5535774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56087875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49880838394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46229553222656</t>
   </si>
   <si>
     <t xml:space="preserve">5.55722904205322</t>
@@ -683,55 +683,55 @@
     <t xml:space="preserve">5.45499277114868</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36736249923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37466526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43308544158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40387487411499</t>
+    <t xml:space="preserve">5.3673620223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37466478347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4330849647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40387535095215</t>
   </si>
   <si>
     <t xml:space="preserve">5.47690010070801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44769048690796</t>
+    <t xml:space="preserve">5.4476900100708</t>
   </si>
   <si>
     <t xml:space="preserve">5.48055171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49515676498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54627466201782</t>
+    <t xml:space="preserve">5.49515724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54627418518066</t>
   </si>
   <si>
     <t xml:space="preserve">5.60104370117188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41117715835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51341390609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54992532730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45134162902832</t>
+    <t xml:space="preserve">5.41117763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51341342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54992580413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45134210586548</t>
   </si>
   <si>
     <t xml:space="preserve">5.61564826965332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50611019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34545564651489</t>
+    <t xml:space="preserve">5.50610971450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34545516967773</t>
   </si>
   <si>
     <t xml:space="preserve">5.37101364135742</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">5.31259346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.287034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15558910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12637901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27242946624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31989669799805</t>
+    <t xml:space="preserve">5.28703451156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15558958053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12637853622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2724289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31989574432373</t>
   </si>
   <si>
     <t xml:space="preserve">5.14098405838013</t>
@@ -761,28 +761,28 @@
     <t xml:space="preserve">5.40752649307251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38927030563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3783164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24321889877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46959781646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41482925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42578268051147</t>
+    <t xml:space="preserve">5.3892707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37831592559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24321937561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46959733963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41482830047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42578220367432</t>
   </si>
   <si>
     <t xml:space="preserve">5.44038772583008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48420381546021</t>
+    <t xml:space="preserve">5.48420333862305</t>
   </si>
   <si>
     <t xml:space="preserve">5.3527569770813</t>
@@ -791,34 +791,34 @@
     <t xml:space="preserve">5.48785448074341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50245952606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57183361053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57913589477539</t>
+    <t xml:space="preserve">5.50245904922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57183408737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57913637161255</t>
   </si>
   <si>
     <t xml:space="preserve">5.56453084945679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52071523666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5389723777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65581178665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58643913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57548522949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50976228713989</t>
+    <t xml:space="preserve">5.52071571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53897190093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65581226348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58643770217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57548475265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50976181030273</t>
   </si>
   <si>
     <t xml:space="preserve">5.53166961669922</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">5.75804805755615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79456090927124</t>
+    <t xml:space="preserve">5.79456043243408</t>
   </si>
   <si>
     <t xml:space="preserve">5.92965745925903</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">5.94426298141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99903154373169</t>
+    <t xml:space="preserve">5.99903202056885</t>
   </si>
   <si>
     <t xml:space="preserve">5.93696022033691</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">5.98807764053345</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83107376098633</t>
+    <t xml:space="preserve">5.83107328414917</t>
   </si>
   <si>
     <t xml:space="preserve">5.88584280014038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83472442626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9588680267334</t>
+    <t xml:space="preserve">5.83472490310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95886754989624</t>
   </si>
   <si>
     <t xml:space="preserve">5.76900196075439</t>
@@ -872,40 +872,40 @@
     <t xml:space="preserve">5.83837556838989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84202718734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87123727798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78360652923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8529806137085</t>
+    <t xml:space="preserve">5.84202671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87123680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.783607006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85298109054565</t>
   </si>
   <si>
     <t xml:space="preserve">5.7032790184021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82742166519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8639349937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75439691543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72883796691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68502235412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66676616668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88949346542358</t>
+    <t xml:space="preserve">5.82742214202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86393451690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75439643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72883749008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68502283096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66676712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88949298858643</t>
   </si>
   <si>
     <t xml:space="preserve">5.78725862503052</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.6083459854126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63025331497192</t>
+    <t xml:space="preserve">5.63025379180908</t>
   </si>
   <si>
     <t xml:space="preserve">5.53532075881958</t>
@@ -932,40 +932,40 @@
     <t xml:space="preserve">5.62660217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68137168884277</t>
+    <t xml:space="preserve">5.68137121200562</t>
   </si>
   <si>
     <t xml:space="preserve">5.73979187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76535081863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80916547775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80551481246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82377052307129</t>
+    <t xml:space="preserve">5.76535129547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80916500091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80551433563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82377099990845</t>
   </si>
   <si>
     <t xml:space="preserve">5.8785400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82011938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90409898757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600679397583</t>
+    <t xml:space="preserve">5.82011985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90409851074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600584030151</t>
   </si>
   <si>
     <t xml:space="preserve">5.92235469818115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95156526565552</t>
+    <t xml:space="preserve">5.95156478881836</t>
   </si>
   <si>
     <t xml:space="preserve">6.02459049224854</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">6.00998544692993</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09031295776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2290620803833</t>
+    <t xml:space="preserve">6.09031343460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22906160354614</t>
   </si>
   <si>
     <t xml:space="preserve">6.18524599075317</t>
@@ -989,31 +989,31 @@
     <t xml:space="preserve">6.03189325332642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03919553756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0464973449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25096940994263</t>
+    <t xml:space="preserve">6.0391960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04649829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25096988677979</t>
   </si>
   <si>
     <t xml:space="preserve">6.20715379714966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14143037796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12682628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7982120513916</t>
+    <t xml:space="preserve">6.14143085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12682580947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79821252822876</t>
   </si>
   <si>
     <t xml:space="preserve">5.72518682479858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96617078781128</t>
+    <t xml:space="preserve">5.96617031097412</t>
   </si>
   <si>
     <t xml:space="preserve">6.00268316268921</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">5.89314460754395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84932994842529</t>
+    <t xml:space="preserve">5.84932947158813</t>
   </si>
   <si>
     <t xml:space="preserve">5.973473072052</t>
@@ -1034,19 +1034,19 @@
     <t xml:space="preserve">6.11952352523804</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15603590011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10491847991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98077535629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90044736862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14873361587524</t>
+    <t xml:space="preserve">6.15603685379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10491800308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98077487945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90044784545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14873313903809</t>
   </si>
   <si>
     <t xml:space="preserve">6.09761571884155</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">6.08301067352295</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17794370651245</t>
+    <t xml:space="preserve">6.17794418334961</t>
   </si>
   <si>
     <t xml:space="preserve">6.17064094543457</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">6.2436671257019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28017950057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38636636734009</t>
+    <t xml:space="preserve">6.28018045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38636541366577</t>
   </si>
   <si>
     <t xml:space="preserve">6.31810283660889</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">6.23467063903809</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28017854690552</t>
+    <t xml:space="preserve">6.28017902374268</t>
   </si>
   <si>
     <t xml:space="preserve">6.15882301330566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2725944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26501035690308</t>
+    <t xml:space="preserve">6.27259492874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26500940322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.21191596984863</t>
@@ -1100,22 +1100,22 @@
     <t xml:space="preserve">6.1815767288208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15123796463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02988243103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05263662338257</t>
+    <t xml:space="preserve">6.15123748779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02988195419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05263614654541</t>
   </si>
   <si>
     <t xml:space="preserve">6.25742483139038</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22708559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24983930587769</t>
+    <t xml:space="preserve">6.22708606719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24983978271484</t>
   </si>
   <si>
     <t xml:space="preserve">6.29534864425659</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">6.18916177749634</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16640758514404</t>
+    <t xml:space="preserve">6.1664080619812</t>
   </si>
   <si>
     <t xml:space="preserve">6.20433187484741</t>
@@ -1136,25 +1136,25 @@
     <t xml:space="preserve">6.01471281051636</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04505157470703</t>
+    <t xml:space="preserve">6.04505109786987</t>
   </si>
   <si>
     <t xml:space="preserve">6.00712776184082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98437356948853</t>
+    <t xml:space="preserve">5.98437309265137</t>
   </si>
   <si>
     <t xml:space="preserve">6.12089872360229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13606882095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11331462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09055948257446</t>
+    <t xml:space="preserve">6.13606929779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11331510543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09055995941162</t>
   </si>
   <si>
     <t xml:space="preserve">5.96161937713623</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">6.14365339279175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10572910308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06022071838379</t>
+    <t xml:space="preserve">6.10572957992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06022167205811</t>
   </si>
   <si>
     <t xml:space="preserve">5.99954271316528</t>
@@ -1178,40 +1178,40 @@
     <t xml:space="preserve">5.95403432846069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93886470794678</t>
+    <t xml:space="preserve">5.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">6.06780576705933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91611051559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94645023345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818670272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746700286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02229690551758</t>
+    <t xml:space="preserve">5.91611099243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94644975662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818622589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746652603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02229738235474</t>
   </si>
   <si>
     <t xml:space="preserve">5.99195861816406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86301755905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07539081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24225521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738313674927</t>
+    <t xml:space="preserve">5.86301708221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07539033889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24225473403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738218307495</t>
   </si>
   <si>
     <t xml:space="preserve">6.63666296005249</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">6.57598495483398</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56081438064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60632371902466</t>
+    <t xml:space="preserve">6.56081485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6063232421875</t>
   </si>
   <si>
     <t xml:space="preserve">6.55323076248169</t>
@@ -1235,16 +1235,16 @@
     <t xml:space="preserve">6.65183258056641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53806066513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4849681854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61390781402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66700172424316</t>
+    <t xml:space="preserve">6.53806018829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48496770858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61390829086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66700220108032</t>
   </si>
   <si>
     <t xml:space="preserve">6.59873867034912</t>
@@ -1256,94 +1256,94 @@
     <t xml:space="preserve">6.39395046234131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4167046546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42428922653198</t>
+    <t xml:space="preserve">6.41670513153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42428970336914</t>
   </si>
   <si>
     <t xml:space="preserve">6.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59115314483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54564523696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56839942932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44704341888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3484411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21950101852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40912008285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32568740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28776407241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6897554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67458629608154</t>
+    <t xml:space="preserve">6.59115362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54564571380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56839990615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44704389572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34844160079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21950054168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40911960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32568788528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28776359558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68975639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67458581924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.74284934997559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75043392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62149286270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37878036499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36361169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46979856491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51530647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31051778793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35602617263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19674730300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40153455734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72009468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75801753997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80352783203125</t>
+    <t xml:space="preserve">6.75043344497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62149238586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37878084182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36361122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46979808807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51530694961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31051731109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3560266494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19674682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40153503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72009515762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75801849365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80352735519409</t>
   </si>
   <si>
     <t xml:space="preserve">6.78835773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73526382446289</t>
+    <t xml:space="preserve">6.73526430130005</t>
   </si>
   <si>
     <t xml:space="preserve">6.84903526306152</t>
@@ -1352,151 +1352,151 @@
     <t xml:space="preserve">6.8642053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81111240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84145164489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81869602203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90212917327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9931468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89454507827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94005298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05382490158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10691690444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15242624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11450147628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01590013504028</t>
+    <t xml:space="preserve">6.81111192703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84145212173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81869554519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90212869644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99314641952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89454555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94005250930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05382442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10691785812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15242671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.114501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01589965820312</t>
   </si>
   <si>
     <t xml:space="preserve">7.08416318893433</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04623985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09174776077271</t>
+    <t xml:space="preserve">7.04623889923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09174871444702</t>
   </si>
   <si>
     <t xml:space="preserve">7.39513826370239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3572154045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34204578399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1220874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13725614547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12967205047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25102806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22827386856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2055196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19793462753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16759490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37996959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43306303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49374008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53924798965454</t>
+    <t xml:space="preserve">7.35721492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34204435348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12208795547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13725566864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12967109680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2510290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22827339172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20551919937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1979341506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16759538650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37996864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4330620765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49374055862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">7.54683303833008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75162267684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79713010787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64543437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69094467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57717275619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45581579208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51649522781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59992599487305</t>
+    <t xml:space="preserve">7.75162076950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79713106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64543533325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6909441947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57717323303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45581769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5164942741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59992837905884</t>
   </si>
   <si>
     <t xml:space="preserve">7.50890970230103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56200265884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58475732803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55441856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47857046127319</t>
+    <t xml:space="preserve">7.56200313568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58475828170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55441808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47856998443604</t>
   </si>
   <si>
     <t xml:space="preserve">7.47098636627197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4482307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70611333847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331840515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88814830780029</t>
+    <t xml:space="preserve">7.44823122024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7061128616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331792831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88814735412598</t>
   </si>
   <si>
     <t xml:space="preserve">8.25221538543701</t>
@@ -1505,49 +1505,49 @@
     <t xml:space="preserve">8.61628437042236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49492645263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17636871337891</t>
+    <t xml:space="preserve">8.49492740631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17636775970459</t>
   </si>
   <si>
     <t xml:space="preserve">8.41908168792725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1187686920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08742237091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93068981170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04040241241455</t>
+    <t xml:space="preserve">8.11876964569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08742141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93068933486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04040336608887</t>
   </si>
   <si>
     <t xml:space="preserve">7.96203565597534</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25982761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02472972869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86799573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7347731590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83664989471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82097625732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91501569747925</t>
+    <t xml:space="preserve">8.25982856750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02472877502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86799669265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73477220535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83665037155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82097578048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91501665115356</t>
   </si>
   <si>
     <t xml:space="preserve">7.97771024703979</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">8.07174968719482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05607509613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85232305526733</t>
+    <t xml:space="preserve">8.05607604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85232448577881</t>
   </si>
   <si>
     <t xml:space="preserve">8.40088844299316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46358108520508</t>
+    <t xml:space="preserve">8.46358203887939</t>
   </si>
   <si>
     <t xml:space="preserve">8.6203145980835</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">8.30684947967529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16578960418701</t>
+    <t xml:space="preserve">8.1657886505127</t>
   </si>
   <si>
     <t xml:space="preserve">8.33819580078125</t>
@@ -1583,22 +1583,22 @@
     <t xml:space="preserve">8.21280860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27550220489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36954212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15011596679688</t>
+    <t xml:space="preserve">8.27550315856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36954307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15011501312256</t>
   </si>
   <si>
     <t xml:space="preserve">8.18146228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13444423675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22848224639893</t>
+    <t xml:space="preserve">8.13444232940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22848129272461</t>
   </si>
   <si>
     <t xml:space="preserve">8.43223571777344</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">8.19713592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7582836151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89934206008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82881355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88366985321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67991781234741</t>
+    <t xml:space="preserve">7.75828266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89934301376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82881307601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88367033004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313943862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6799168586731</t>
   </si>
   <si>
     <t xml:space="preserve">7.79746580123901</t>
@@ -1634,46 +1634,46 @@
     <t xml:space="preserve">8.41656112670898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80530309677124</t>
+    <t xml:space="preserve">7.80530261993408</t>
   </si>
   <si>
     <t xml:space="preserve">7.68775463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74261045455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00905609130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94636344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75044727325439</t>
+    <t xml:space="preserve">7.74260997772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00905513763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94636297225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75044679641724</t>
   </si>
   <si>
     <t xml:space="preserve">7.71910047531128</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10309600830078</t>
+    <t xml:space="preserve">8.1030969619751</t>
   </si>
   <si>
     <t xml:space="preserve">8.82406711578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37263298034668</t>
+    <t xml:space="preserve">9.372633934021</t>
   </si>
   <si>
     <t xml:space="preserve">9.60773277282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48234558105469</t>
+    <t xml:space="preserve">9.482346534729</t>
   </si>
   <si>
     <t xml:space="preserve">9.79581260681152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9368724822998</t>
+    <t xml:space="preserve">9.93687152862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.87417984008789</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">10.5011100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3757238388062</t>
+    <t xml:space="preserve">10.3757247924805</t>
   </si>
   <si>
     <t xml:space="preserve">10.5481309890747</t>
@@ -1700,37 +1700,37 @@
     <t xml:space="preserve">10.1719703674316</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95254516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90552616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88985061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92119884490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73311901092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76446533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57638645172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96821880340576</t>
+    <t xml:space="preserve">9.95254611968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90552425384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88985157012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92119693756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73311996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76446437835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57638549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96821975708008</t>
   </si>
   <si>
     <t xml:space="preserve">10.030912399292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4854364395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.250337600708</t>
+    <t xml:space="preserve">10.4854373931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2503366470337</t>
   </si>
   <si>
     <t xml:space="preserve">10.0152378082275</t>
@@ -1739,19 +1739,19 @@
     <t xml:space="preserve">10.1249513626099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3600511550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2973585128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3130302429199</t>
+    <t xml:space="preserve">10.360050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2973594665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3130311965942</t>
   </si>
   <si>
     <t xml:space="preserve">10.4384174346924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6264963150024</t>
+    <t xml:space="preserve">10.6264982223511</t>
   </si>
   <si>
     <t xml:space="preserve">10.6578435897827</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">10.6108236312866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5951509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.579478263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6421699523926</t>
+    <t xml:space="preserve">10.5951499938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5794763565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6421709060669</t>
   </si>
   <si>
     <t xml:space="preserve">10.7518835067749</t>
@@ -1784,16 +1784,16 @@
     <t xml:space="preserve">11.0183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">11.237756729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593885421753</t>
+    <t xml:space="preserve">11.2377557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593894958496</t>
   </si>
   <si>
     <t xml:space="preserve">11.0966958999634</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1750631332397</t>
+    <t xml:space="preserve">11.1750621795654</t>
   </si>
   <si>
     <t xml:space="preserve">11.1123695373535</t>
@@ -1802,10 +1802,10 @@
     <t xml:space="preserve">11.0810222625732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9713096618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7989025115967</t>
+    <t xml:space="preserve">10.9713106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.798903465271</t>
   </si>
   <si>
     <t xml:space="preserve">10.0622587203979</t>
@@ -1814,31 +1814,31 @@
     <t xml:space="preserve">10.0936050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68609809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29426574707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54504013061523</t>
+    <t xml:space="preserve">9.6860990524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29426670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54503917694092</t>
   </si>
   <si>
     <t xml:space="preserve">8.98080062866211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54194831848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31943082809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5075101852417</t>
+    <t xml:space="preserve">8.54194736480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31943035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50751113891602</t>
   </si>
   <si>
     <t xml:space="preserve">7.53885698318481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49183702468872</t>
+    <t xml:space="preserve">7.49183750152588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66733551025391</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">8.44790840148926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38521575927734</t>
+    <t xml:space="preserve">8.38521480560303</t>
   </si>
   <si>
     <t xml:space="preserve">8.52627468109131</t>
@@ -1862,28 +1862,28 @@
     <t xml:space="preserve">9.10618686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9337797164917</t>
+    <t xml:space="preserve">8.93378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">9.38830661773682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88676071166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87108707427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12185955047607</t>
+    <t xml:space="preserve">8.88675975799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8710880279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12186050415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.91810703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15320873260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90243434906006</t>
+    <t xml:space="preserve">9.15320682525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90243339538574</t>
   </si>
   <si>
     <t xml:space="preserve">9.05916690826416</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">8.50604724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70121479034424</t>
+    <t xml:space="preserve">8.70121383666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.18913269042969</t>
@@ -1922,25 +1922,25 @@
     <t xml:space="preserve">8.92890930175781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76627063751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71747970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97770214080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33550834655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48188591003418</t>
+    <t xml:space="preserve">8.76626968383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71747875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97770118713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33550930023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48188400268555</t>
   </si>
   <si>
     <t xml:space="preserve">9.61199569702148</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2625532150269</t>
+    <t xml:space="preserve">10.2625522613525</t>
   </si>
   <si>
     <t xml:space="preserve">10.0673866271973</t>
@@ -1949,22 +1949,22 @@
     <t xml:space="preserve">10.3113460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1812343597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2137622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2788190841675</t>
+    <t xml:space="preserve">10.1812353134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2137632369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2788171768188</t>
   </si>
   <si>
     <t xml:space="preserve">10.2300262451172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95353889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88848400115967</t>
+    <t xml:space="preserve">9.953537940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88848304748535</t>
   </si>
   <si>
     <t xml:space="preserve">9.69331550598145</t>
@@ -1976,13 +1976,13 @@
     <t xml:space="preserve">10.1974983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3276100158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2462911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5553045272827</t>
+    <t xml:space="preserve">10.3276090621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2462902069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.555305480957</t>
   </si>
   <si>
     <t xml:space="preserve">10.8480567932129</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">10.8805837631226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8317918777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7992649078369</t>
+    <t xml:space="preserve">10.8317928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7992639541626</t>
   </si>
   <si>
     <t xml:space="preserve">10.9293756484985</t>
@@ -2009,16 +2009,16 @@
     <t xml:space="preserve">10.7667360305786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9781684875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1245431900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1408071517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2871828079224</t>
+    <t xml:space="preserve">10.9781675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1245422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1408061981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2871837615967</t>
   </si>
   <si>
     <t xml:space="preserve">11.3847675323486</t>
@@ -2030,19 +2030,19 @@
     <t xml:space="preserve">11.4335594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4660873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4823513031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.335973739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2058629989624</t>
+    <t xml:space="preserve">11.4498224258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.46608543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4823503494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3359746932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2058639526367</t>
   </si>
   <si>
     <t xml:space="preserve">11.2221269607544</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">10.8643198013306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5390405654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5227756500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.701681137085</t>
+    <t xml:space="preserve">10.539041519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.522777557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7016801834106</t>
   </si>
   <si>
     <t xml:space="preserve">10.8155279159546</t>
@@ -2066,28 +2066,28 @@
     <t xml:space="preserve">10.604097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7342081069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.620361328125</t>
+    <t xml:space="preserve">10.7342090606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6203622817993</t>
   </si>
   <si>
     <t xml:space="preserve">10.717945098877</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5065126419067</t>
+    <t xml:space="preserve">10.5065135955811</t>
   </si>
   <si>
     <t xml:space="preserve">10.5878343582153</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4577207565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3764028549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5715684890747</t>
+    <t xml:space="preserve">10.4577217102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3764009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.571569442749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089298248291</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">10.8968477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0594882965088</t>
+    <t xml:space="preserve">11.0594873428345</t>
   </si>
   <si>
     <t xml:space="preserve">10.9944324493408</t>
@@ -2111,40 +2111,40 @@
     <t xml:space="preserve">10.9619045257568</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9456396102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2709188461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1895990371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5799331665039</t>
+    <t xml:space="preserve">10.9456405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2709197998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1895999908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5799341201782</t>
   </si>
   <si>
     <t xml:space="preserve">11.4172954559326</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3034467697144</t>
+    <t xml:space="preserve">11.3034477233887</t>
   </si>
   <si>
     <t xml:space="preserve">9.9860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0836496353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4414587020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7504730224609</t>
+    <t xml:space="preserve">10.0836505889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4414577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7504720687866</t>
   </si>
   <si>
     <t xml:space="preserve">11.1570711135864</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1082792282104</t>
+    <t xml:space="preserve">11.1082782745361</t>
   </si>
   <si>
     <t xml:space="preserve">11.0269594192505</t>
@@ -2153,49 +2153,49 @@
     <t xml:space="preserve">10.9131116867065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2546548843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3522396087646</t>
+    <t xml:space="preserve">11.2546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3522386550903</t>
   </si>
   <si>
     <t xml:space="preserve">11.4010314941406</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3197107315063</t>
+    <t xml:space="preserve">11.3197116851807</t>
   </si>
   <si>
     <t xml:space="preserve">11.1733350753784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0106964111328</t>
+    <t xml:space="preserve">11.0106954574585</t>
   </si>
   <si>
     <t xml:space="preserve">11.5311422348022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7751016616821</t>
+    <t xml:space="preserve">11.7751007080078</t>
   </si>
   <si>
     <t xml:space="preserve">11.7100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7425737380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0190601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3118124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5882997512817</t>
+    <t xml:space="preserve">11.7425727844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.019061088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3118114471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5882987976074</t>
   </si>
   <si>
     <t xml:space="preserve">12.1979637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8726863861084</t>
+    <t xml:space="preserve">11.8726844787598</t>
   </si>
   <si>
     <t xml:space="preserve">12.00279712677</t>
@@ -2204,19 +2204,19 @@
     <t xml:space="preserve">11.8076305389404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8564224243164</t>
+    <t xml:space="preserve">11.8564205169678</t>
   </si>
   <si>
     <t xml:space="preserve">11.5961980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">11.954005241394</t>
+    <t xml:space="preserve">11.9540042877197</t>
   </si>
   <si>
     <t xml:space="preserve">11.9865322113037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1003799438477</t>
+    <t xml:space="preserve">12.100380897522</t>
   </si>
   <si>
     <t xml:space="preserve">12.1817007064819</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">12.116644859314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2792854309082</t>
+    <t xml:space="preserve">12.2792844772339</t>
   </si>
   <si>
     <t xml:space="preserve">12.4093961715698</t>
@@ -2243,10 +2243,10 @@
     <t xml:space="preserve">12.8973150253296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0111618041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9786338806152</t>
+    <t xml:space="preserve">13.0111627578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9786348342896</t>
   </si>
   <si>
     <t xml:space="preserve">12.8647861480713</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">12.8810510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1738023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2713861465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3527050018311</t>
+    <t xml:space="preserve">13.1738014221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2713851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3527059555054</t>
   </si>
   <si>
     <t xml:space="preserve">13.7267751693726</t>
@@ -2276,28 +2276,28 @@
     <t xml:space="preserve">13.8243598937988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.052056312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2309589385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2634878158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2146949768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9056806564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6129264831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8080959320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8894147872925</t>
+    <t xml:space="preserve">14.0520553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2309598922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634868621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2146940231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9056787490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6129274368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8080949783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8894138336182</t>
   </si>
   <si>
     <t xml:space="preserve">13.6454563140869</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">13.8406238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7918319702148</t>
+    <t xml:space="preserve">13.7918310165405</t>
   </si>
   <si>
     <t xml:space="preserve">14.0032615661621</t>
@@ -2315,31 +2315,31 @@
     <t xml:space="preserve">13.9544706344604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3448047637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1496381759644</t>
+    <t xml:space="preserve">14.3448057174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1496391296387</t>
   </si>
   <si>
     <t xml:space="preserve">14.2472219467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4749174118042</t>
+    <t xml:space="preserve">14.4749164581299</t>
   </si>
   <si>
     <t xml:space="preserve">14.5579166412354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1927242279053</t>
+    <t xml:space="preserve">14.1927223205566</t>
   </si>
   <si>
     <t xml:space="preserve">14.1595239639282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1429252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2757215499878</t>
+    <t xml:space="preserve">14.1429243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2757225036621</t>
   </si>
   <si>
     <t xml:space="preserve">14.2923192977905</t>
@@ -2357,28 +2357,28 @@
     <t xml:space="preserve">14.0765247344971</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2093229293823</t>
+    <t xml:space="preserve">14.2093238830566</t>
   </si>
   <si>
     <t xml:space="preserve">13.9935274124146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8109292984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3089199066162</t>
+    <t xml:space="preserve">13.8109302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3089208602905</t>
   </si>
   <si>
     <t xml:space="preserve">14.05992603302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0101251602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9769277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0433263778687</t>
+    <t xml:space="preserve">14.0101261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9769268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0433254241943</t>
   </si>
   <si>
     <t xml:space="preserve">14.3255205154419</t>
@@ -2387,22 +2387,22 @@
     <t xml:space="preserve">14.2259206771851</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3421201705933</t>
+    <t xml:space="preserve">14.3421211242676</t>
   </si>
   <si>
     <t xml:space="preserve">14.1761226654053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9437265396118</t>
+    <t xml:space="preserve">13.9437274932861</t>
   </si>
   <si>
     <t xml:space="preserve">14.0931243896484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9603261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.358717918396</t>
+    <t xml:space="preserve">13.9603271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3587188720703</t>
   </si>
   <si>
     <t xml:space="preserve">14.2591218948364</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">14.026725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.707311630249</t>
+    <t xml:space="preserve">14.7073125839233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7737112045288</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">14.7405118942261</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9397087097168</t>
+    <t xml:space="preserve">14.9397077560425</t>
   </si>
   <si>
     <t xml:space="preserve">15.1057052612305</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">14.8899097442627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3712997436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7032918930054</t>
+    <t xml:space="preserve">15.3713006973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.703293800354</t>
   </si>
   <si>
     <t xml:space="preserve">15.537296295166</t>
@@ -2456,60 +2456,57 @@
     <t xml:space="preserve">15.387900352478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2883033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2717018127441</t>
+    <t xml:space="preserve">15.2883024215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2717027664185</t>
   </si>
   <si>
     <t xml:space="preserve">15.0725059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2219038009644</t>
+    <t xml:space="preserve">15.22190284729</t>
   </si>
   <si>
     <t xml:space="preserve">15.1223039627075</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9895067214966</t>
+    <t xml:space="preserve">14.9895057678223</t>
   </si>
   <si>
     <t xml:space="preserve">14.8567085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8235101699829</t>
+    <t xml:space="preserve">14.8235120773315</t>
   </si>
   <si>
     <t xml:space="preserve">14.7903099060059</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1389045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9729089736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.873309135437</t>
+    <t xml:space="preserve">15.1389055252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9729099273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8733100891113</t>
   </si>
   <si>
     <t xml:space="preserve">14.8069105148315</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8607301712036</t>
+    <t xml:space="preserve">13.8607292175293</t>
   </si>
   <si>
     <t xml:space="preserve">13.6947326660156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7113332748413</t>
+    <t xml:space="preserve">13.711332321167</t>
   </si>
   <si>
     <t xml:space="preserve">14.4417171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4749164581299</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.5745153427124</t>
   </si>
   <si>
@@ -2525,13 +2522,13 @@
     <t xml:space="preserve">14.3919191360474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4708967208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.205304145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0227069854736</t>
+    <t xml:space="preserve">15.4708976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2053022384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227079391479</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915151596069</t>
@@ -2543,10 +2540,10 @@
     <t xml:space="preserve">13.7777309417725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6449346542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445297241211</t>
+    <t xml:space="preserve">13.6449337005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445316314697</t>
   </si>
   <si>
     <t xml:space="preserve">13.5287351608276</t>
@@ -2558,10 +2555,10 @@
     <t xml:space="preserve">13.4125375747681</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1137447357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2797403335571</t>
+    <t xml:space="preserve">13.1137428283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2797412872314</t>
   </si>
   <si>
     <t xml:space="preserve">13.362738609314</t>
@@ -2573,7 +2570,7 @@
     <t xml:space="preserve">13.5951347351074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6117334365845</t>
+    <t xml:space="preserve">13.6117324829102</t>
   </si>
   <si>
     <t xml:space="preserve">13.1303434371948</t>
@@ -2588,22 +2585,22 @@
     <t xml:space="preserve">13.0805444717407</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3129405975342</t>
+    <t xml:space="preserve">13.3129415512085</t>
   </si>
   <si>
     <t xml:space="preserve">13.1967420578003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7983493804932</t>
+    <t xml:space="preserve">12.7983503341675</t>
   </si>
   <si>
     <t xml:space="preserve">12.4497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3003587722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7153520584106</t>
+    <t xml:space="preserve">12.3003597259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7153511047363</t>
   </si>
   <si>
     <t xml:space="preserve">12.4331569671631</t>
@@ -2621,10 +2618,10 @@
     <t xml:space="preserve">12.067964553833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8521671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6695728302002</t>
+    <t xml:space="preserve">11.8521680831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6695718765259</t>
   </si>
   <si>
     <t xml:space="preserve">12.0845642089844</t>
@@ -2642,7 +2639,7 @@
     <t xml:space="preserve">11.7857694625854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5367746353149</t>
+    <t xml:space="preserve">11.5367736816406</t>
   </si>
   <si>
     <t xml:space="preserve">11.3209781646729</t>
@@ -2651,19 +2648,19 @@
     <t xml:space="preserve">11.1715812683105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.221381187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8395881652832</t>
+    <t xml:space="preserve">11.2213821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8395891189575</t>
   </si>
   <si>
     <t xml:space="preserve">10.2088012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6735916137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6237936019897</t>
+    <t xml:space="preserve">10.6735906600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6237926483154</t>
   </si>
   <si>
     <t xml:space="preserve">10.2585983276367</t>
@@ -2675,13 +2672,13 @@
     <t xml:space="preserve">9.97640514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54481410980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5614128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36221694946289</t>
+    <t xml:space="preserve">9.54481315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56141376495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36221790313721</t>
   </si>
   <si>
     <t xml:space="preserve">9.62781238555908</t>
@@ -2690,10 +2687,10 @@
     <t xml:space="preserve">9.32901763916016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52821445465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0096054077148</t>
+    <t xml:space="preserve">9.52821350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0096044540405</t>
   </si>
   <si>
     <t xml:space="preserve">9.39541625976562</t>
@@ -2702,7 +2699,7 @@
     <t xml:space="preserve">10.3913974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6071929931641</t>
+    <t xml:space="preserve">10.6071920394897</t>
   </si>
   <si>
     <t xml:space="preserve">10.3083982467651</t>
@@ -2714,13 +2711,13 @@
     <t xml:space="preserve">10.1756019592285</t>
   </si>
   <si>
-    <t xml:space="preserve">10.109203338623</t>
+    <t xml:space="preserve">10.1092023849487</t>
   </si>
   <si>
     <t xml:space="preserve">10.1424026489258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0594043731689</t>
+    <t xml:space="preserve">10.0594034194946</t>
   </si>
   <si>
     <t xml:space="preserve">9.86020755767822</t>
@@ -2744,19 +2741,19 @@
     <t xml:space="preserve">9.37881660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19622135162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29581737518311</t>
+    <t xml:space="preserve">9.19622039794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29581832885742</t>
   </si>
   <si>
     <t xml:space="preserve">9.12982177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42861557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77720832824707</t>
+    <t xml:space="preserve">9.42861652374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77720928192139</t>
   </si>
   <si>
     <t xml:space="preserve">9.64441204071045</t>
@@ -2765,7 +2762,7 @@
     <t xml:space="preserve">10.0262041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5407943725586</t>
+    <t xml:space="preserve">10.5407934188843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4577960968018</t>
@@ -2774,7 +2771,7 @@
     <t xml:space="preserve">10.0760040283203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92660617828369</t>
+    <t xml:space="preserve">9.92660713195801</t>
   </si>
   <si>
     <t xml:space="preserve">9.66899490356445</t>
@@ -2786,7 +2783,7 @@
     <t xml:space="preserve">9.7205171585083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0639982223511</t>
+    <t xml:space="preserve">10.0639991760254</t>
   </si>
   <si>
     <t xml:space="preserve">10.0983467102051</t>
@@ -2795,16 +2792,16 @@
     <t xml:space="preserve">10.2529125213623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85791015625</t>
+    <t xml:space="preserve">9.85790920257568</t>
   </si>
   <si>
     <t xml:space="preserve">10.0811729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.35595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2700872421265</t>
+    <t xml:space="preserve">10.3559579849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2700881958008</t>
   </si>
   <si>
     <t xml:space="preserve">10.6479167938232</t>
@@ -2813,7 +2810,7 @@
     <t xml:space="preserve">10.7681341171265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9570503234863</t>
+    <t xml:space="preserve">10.957049369812</t>
   </si>
   <si>
     <t xml:space="preserve">11.1631383895874</t>
@@ -2843,7 +2840,7 @@
     <t xml:space="preserve">10.0124759674072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3903064727783</t>
+    <t xml:space="preserve">10.390305519104</t>
   </si>
   <si>
     <t xml:space="preserve">10.1498689651489</t>
@@ -2876,7 +2873,7 @@
     <t xml:space="preserve">10.0468244552612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5620460510254</t>
+    <t xml:space="preserve">10.5620470046997</t>
   </si>
   <si>
     <t xml:space="preserve">10.6307430267334</t>
@@ -2885,16 +2882,16 @@
     <t xml:space="preserve">10.424654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4418287277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7166118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4590015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5105228424072</t>
+    <t xml:space="preserve">10.4418277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7166128158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.459002494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5105237960815</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509613037109</t>
@@ -2906,13 +2903,13 @@
     <t xml:space="preserve">10.493350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1155204772949</t>
+    <t xml:space="preserve">10.1155214309692</t>
   </si>
   <si>
     <t xml:space="preserve">9.7548656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61747264862061</t>
+    <t xml:space="preserve">9.61747360229492</t>
   </si>
   <si>
     <t xml:space="preserve">9.37703609466553</t>
@@ -2921,7 +2918,7 @@
     <t xml:space="preserve">9.51442909240723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63464736938477</t>
+    <t xml:space="preserve">9.63464641571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.80638790130615</t>
@@ -2936,7 +2933,7 @@
     <t xml:space="preserve">9.49725532531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39420986175537</t>
+    <t xml:space="preserve">9.39421081542969</t>
   </si>
   <si>
     <t xml:space="preserve">9.22246932983398</t>
@@ -2945,13 +2942,13 @@
     <t xml:space="preserve">9.32551383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25681781768799</t>
+    <t xml:space="preserve">9.25681686401367</t>
   </si>
   <si>
     <t xml:space="preserve">9.4629077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08507633209229</t>
+    <t xml:space="preserve">9.0850772857666</t>
   </si>
   <si>
     <t xml:space="preserve">9.54877662658691</t>
@@ -2972,7 +2969,7 @@
     <t xml:space="preserve">10.3387842178345</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5963954925537</t>
+    <t xml:space="preserve">10.5963945388794</t>
   </si>
   <si>
     <t xml:space="preserve">10.8540058135986</t>
@@ -2981,13 +2978,13 @@
     <t xml:space="preserve">11.4550971984863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2661828994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0429201126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8883543014526</t>
+    <t xml:space="preserve">11.2661819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0429191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8883533477783</t>
   </si>
   <si>
     <t xml:space="preserve">10.9398756027222</t>
@@ -2996,7 +2993,7 @@
     <t xml:space="preserve">10.8196573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8024826049805</t>
+    <t xml:space="preserve">10.8024835586548</t>
   </si>
   <si>
     <t xml:space="preserve">11.3692274093628</t>
@@ -3005,25 +3002,25 @@
     <t xml:space="preserve">11.4379234313965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0733642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4683675765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5027151107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2966251373291</t>
+    <t xml:space="preserve">12.0733633041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4683666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5027160644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2966260910034</t>
   </si>
   <si>
     <t xml:space="preserve">12.0561895370483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7470560073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7127084732056</t>
+    <t xml:space="preserve">11.7470569610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7127075195312</t>
   </si>
   <si>
     <t xml:space="preserve">11.9703187942505</t>
@@ -3035,13 +3032,13 @@
     <t xml:space="preserve">12.0046663284302</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0218420028687</t>
+    <t xml:space="preserve">12.0218410491943</t>
   </si>
   <si>
     <t xml:space="preserve">11.8157529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.227931022644</t>
+    <t xml:space="preserve">12.2279300689697</t>
   </si>
   <si>
     <t xml:space="preserve">12.3653221130371</t>
@@ -3056,7 +3053,7 @@
     <t xml:space="preserve">12.3138008117676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.519889831543</t>
+    <t xml:space="preserve">12.5198888778687</t>
   </si>
   <si>
     <t xml:space="preserve">12.485541343689</t>
@@ -3068,16 +3065,16 @@
     <t xml:space="preserve">12.2451038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2794532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1420593261719</t>
+    <t xml:space="preserve">12.2794523239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1420602798462</t>
   </si>
   <si>
     <t xml:space="preserve">12.1248865127563</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1764087677002</t>
+    <t xml:space="preserve">12.1764078140259</t>
   </si>
   <si>
     <t xml:space="preserve">12.159234046936</t>
@@ -3086,10 +3083,10 @@
     <t xml:space="preserve">12.1077117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3481483459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.657280921936</t>
+    <t xml:space="preserve">12.3481492996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6572818756104</t>
   </si>
   <si>
     <t xml:space="preserve">12.9148921966553</t>
@@ -3098,19 +3095,19 @@
     <t xml:space="preserve">13.0694599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1038074493408</t>
+    <t xml:space="preserve">13.1038084030151</t>
   </si>
   <si>
     <t xml:space="preserve">13.0866327285767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1896772384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6705503463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3442440032959</t>
+    <t xml:space="preserve">13.18967628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6705513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3442430496216</t>
   </si>
   <si>
     <t xml:space="preserve">13.6362028121948</t>
@@ -3122,7 +3119,7 @@
     <t xml:space="preserve">13.5503330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5675067901611</t>
+    <t xml:space="preserve">13.5675058364868</t>
   </si>
   <si>
     <t xml:space="preserve">13.4644622802734</t>
@@ -3134,7 +3131,7 @@
     <t xml:space="preserve">13.5159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6190280914307</t>
+    <t xml:space="preserve">13.619029045105</t>
   </si>
   <si>
     <t xml:space="preserve">14.082727432251</t>
@@ -3155,7 +3152,7 @@
     <t xml:space="preserve">14.6151247024536</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7353420257568</t>
+    <t xml:space="preserve">14.7353429794312</t>
   </si>
   <si>
     <t xml:space="preserve">14.6494731903076</t>
@@ -3182,52 +3179,52 @@
     <t xml:space="preserve">15.3879566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1990432739258</t>
+    <t xml:space="preserve">15.1990423202515</t>
   </si>
   <si>
     <t xml:space="preserve">15.2505645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1818675994873</t>
+    <t xml:space="preserve">15.1818685531616</t>
   </si>
   <si>
     <t xml:space="preserve">15.2162160873413</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9757795333862</t>
+    <t xml:space="preserve">14.9757785797119</t>
   </si>
   <si>
     <t xml:space="preserve">14.9242563247681</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4262084960938</t>
+    <t xml:space="preserve">14.4262094497681</t>
   </si>
   <si>
     <t xml:space="preserve">14.3918619155884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9586057662964</t>
+    <t xml:space="preserve">14.9586067199707</t>
   </si>
   <si>
     <t xml:space="preserve">14.5464286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1131715774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1303472518921</t>
+    <t xml:space="preserve">15.1131725311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1303462982178</t>
   </si>
   <si>
     <t xml:space="preserve">14.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2677392959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4223051071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9031782150269</t>
+    <t xml:space="preserve">15.2677383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4223041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9031791687012</t>
   </si>
   <si>
     <t xml:space="preserve">15.9375276565552</t>
@@ -3236,22 +3233,22 @@
     <t xml:space="preserve">16.1436157226562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8516550064087</t>
+    <t xml:space="preserve">15.851655960083</t>
   </si>
   <si>
     <t xml:space="preserve">15.9546995162964</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7829599380493</t>
+    <t xml:space="preserve">15.782958984375</t>
   </si>
   <si>
     <t xml:space="preserve">15.7142639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5253496170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5596981048584</t>
+    <t xml:space="preserve">15.5253505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5596971511841</t>
   </si>
   <si>
     <t xml:space="preserve">14.8383884429932</t>
@@ -3260,7 +3257,7 @@
     <t xml:space="preserve">14.4605579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3059921264648</t>
+    <t xml:space="preserve">14.3059911727905</t>
   </si>
   <si>
     <t xml:space="preserve">14.2888164520264</t>
@@ -3272,25 +3269,28 @@
     <t xml:space="preserve">14.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7009963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5807752609253</t>
+    <t xml:space="preserve">14.7009954452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5807762145996</t>
   </si>
   <si>
     <t xml:space="preserve">14.5292539596558</t>
   </si>
   <si>
+    <t xml:space="preserve">14.3746871948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1431245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2678127288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.321249961853</t>
+  </si>
+  <si>
     <t xml:space="preserve">14.3746862411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1431245803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2678127288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.321249961853</t>
   </si>
   <si>
     <t xml:space="preserve">14.6596870422363</t>
@@ -43131,7 +43131,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1476" t="s">
-        <v>831</v>
+        <v>770</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -43157,7 +43157,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1477" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -43183,7 +43183,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1478" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -43209,7 +43209,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1479" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -43235,7 +43235,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1480" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -43261,7 +43261,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1481" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -43287,7 +43287,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1482" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -43313,7 +43313,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1483" t="s">
-        <v>831</v>
+        <v>770</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -43365,7 +43365,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1485" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -43391,7 +43391,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1486" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -43417,7 +43417,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1487" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -43469,7 +43469,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1489" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -43521,7 +43521,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1491" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -43573,7 +43573,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43651,7 +43651,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1496" t="s">
-        <v>831</v>
+        <v>770</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43677,7 +43677,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1497" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43703,7 +43703,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1498" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43885,7 +43885,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1505" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43937,7 +43937,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1507" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43963,7 +43963,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1508" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43989,7 +43989,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1509" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -44119,7 +44119,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1514" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -44145,7 +44145,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1515" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -44171,7 +44171,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1516" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -44223,7 +44223,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1518" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -44249,7 +44249,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -44275,7 +44275,7 @@
         <v>16</v>
       </c>
       <c r="G1520" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -44301,7 +44301,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1521" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -44327,7 +44327,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1522" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -44535,7 +44535,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1530" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -44561,7 +44561,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44587,7 +44587,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1532" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44613,7 +44613,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1533" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44639,7 +44639,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1534" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44665,7 +44665,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1535" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44691,7 +44691,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1536" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44717,7 +44717,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1537" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44743,7 +44743,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1538" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44769,7 +44769,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G1539" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44795,7 +44795,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44821,7 +44821,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1541" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44847,7 +44847,7 @@
         <v>15</v>
       </c>
       <c r="G1542" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44873,7 +44873,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1543" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44899,7 +44899,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1544" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44925,7 +44925,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1545" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44951,7 +44951,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1546" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44977,7 +44977,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1547" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -45003,7 +45003,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1548" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -45029,7 +45029,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1549" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -45055,7 +45055,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1550" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -45081,7 +45081,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1551" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -45107,7 +45107,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1552" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -45133,7 +45133,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1553" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -45159,7 +45159,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1554" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -45185,7 +45185,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1555" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -45211,7 +45211,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1556" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -45237,7 +45237,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1557" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -45263,7 +45263,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -45289,7 +45289,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1559" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -45315,7 +45315,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1560" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -45341,7 +45341,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1561" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -45367,7 +45367,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1562" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -45393,7 +45393,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1563" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -45419,7 +45419,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1564" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -45445,7 +45445,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1565" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -45471,7 +45471,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1566" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -45497,7 +45497,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1567" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -45523,7 +45523,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1568" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -45549,7 +45549,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1569" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -45575,7 +45575,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1570" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45601,7 +45601,7 @@
         <v>11.5</v>
       </c>
       <c r="G1571" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45627,7 +45627,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1572" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45653,7 +45653,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1573" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45679,7 +45679,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1574" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45705,7 +45705,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1575" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45731,7 +45731,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1576" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45757,7 +45757,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1577" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45783,7 +45783,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1578" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45809,7 +45809,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1579" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45835,7 +45835,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1580" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45861,7 +45861,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1581" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45887,7 +45887,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1582" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45913,7 +45913,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1583" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45939,7 +45939,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1584" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45965,7 +45965,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1585" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45991,7 +45991,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1586" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -46017,7 +46017,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1587" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -46043,7 +46043,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1588" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -46069,7 +46069,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1589" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -46095,7 +46095,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1590" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -46121,7 +46121,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1591" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -46147,7 +46147,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1592" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -46173,7 +46173,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1593" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -46199,7 +46199,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1594" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -46225,7 +46225,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1595" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -46251,7 +46251,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -46277,7 +46277,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1597" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -46303,7 +46303,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1598" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -46329,7 +46329,7 @@
         <v>11</v>
       </c>
       <c r="G1599" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -46355,7 +46355,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1600" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -46381,7 +46381,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1601" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -46407,7 +46407,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1602" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -46433,7 +46433,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1603" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -46459,7 +46459,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1604" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -46485,7 +46485,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1605" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -46511,7 +46511,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1606" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -46537,7 +46537,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1607" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -46563,7 +46563,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1608" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46589,7 +46589,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1609" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -46615,7 +46615,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1610" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46641,7 +46641,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1611" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -46667,7 +46667,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1612" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46693,7 +46693,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1613" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -46719,7 +46719,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1614" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -46745,7 +46745,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1615" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46771,7 +46771,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1616" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -46797,7 +46797,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1617" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46823,7 +46823,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1618" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46849,7 +46849,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1619" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46875,7 +46875,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1620" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46901,7 +46901,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1621" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46927,7 +46927,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1622" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46953,7 +46953,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1623" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46979,7 +46979,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1624" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -47005,7 +47005,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1625" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -47031,7 +47031,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1626" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -47057,7 +47057,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1627" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -47083,7 +47083,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1628" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -47109,7 +47109,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1629" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47135,7 +47135,7 @@
         <v>13</v>
       </c>
       <c r="G1630" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47161,7 +47161,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1631" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47187,7 +47187,7 @@
         <v>13</v>
       </c>
       <c r="G1632" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47213,7 +47213,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1633" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47239,7 +47239,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1634" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47265,7 +47265,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1635" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47291,7 +47291,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1636" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47317,7 +47317,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1637" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47343,7 +47343,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1638" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47369,7 +47369,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1639" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47395,7 +47395,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1640" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47421,7 +47421,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1641" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47447,7 +47447,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1642" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47473,7 +47473,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1643" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47499,7 +47499,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1644" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47525,7 +47525,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1645" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47551,7 +47551,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1646" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47577,7 +47577,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1647" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47603,7 +47603,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1648" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47629,7 +47629,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1649" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47655,7 +47655,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1650" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47681,7 +47681,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1651" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47707,7 +47707,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1652" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47733,7 +47733,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1653" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47759,7 +47759,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1654" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47785,7 +47785,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1655" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47811,7 +47811,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1656" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47837,7 +47837,7 @@
         <v>11.5</v>
       </c>
       <c r="G1657" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47863,7 +47863,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1658" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47889,7 +47889,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1659" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47915,7 +47915,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1660" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47941,7 +47941,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1661" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47967,7 +47967,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1662" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47993,7 +47993,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1663" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -48019,7 +48019,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1664" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -48045,7 +48045,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1665" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -48071,7 +48071,7 @@
         <v>12</v>
       </c>
       <c r="G1666" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48097,7 +48097,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1667" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -48123,7 +48123,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1668" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48149,7 +48149,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1669" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48175,7 +48175,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1670" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48201,7 +48201,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1671" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48227,7 +48227,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1672" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48253,7 +48253,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1673" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48279,7 +48279,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1674" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48305,7 +48305,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1675" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48331,7 +48331,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1676" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48357,7 +48357,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1677" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48383,7 +48383,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1678" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48409,7 +48409,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1679" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48435,7 +48435,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1680" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48461,7 +48461,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1681" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48487,7 +48487,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1682" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48513,7 +48513,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1683" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48539,7 +48539,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1684" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48565,7 +48565,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1685" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48591,7 +48591,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1686" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48617,7 +48617,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1687" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48643,7 +48643,7 @@
         <v>12</v>
       </c>
       <c r="G1688" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48669,7 +48669,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1689" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48695,7 +48695,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1690" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48721,7 +48721,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1691" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48747,7 +48747,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1692" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -48773,7 +48773,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1693" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -48799,7 +48799,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1694" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48825,7 +48825,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1695" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48851,7 +48851,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1696" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48877,7 +48877,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48903,7 +48903,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1698" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48929,7 +48929,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1699" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48955,7 +48955,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1700" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48981,7 +48981,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1701" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -49007,7 +49007,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1702" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -49033,7 +49033,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1703" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -49059,7 +49059,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1704" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -49085,7 +49085,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1705" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -49111,7 +49111,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1706" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -49137,7 +49137,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1707" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -49163,7 +49163,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1708" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -49189,7 +49189,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1709" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -49215,7 +49215,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1710" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49241,7 +49241,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1711" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49267,7 +49267,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1712" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -49293,7 +49293,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1713" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49319,7 +49319,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1714" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -49345,7 +49345,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1715" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -49371,7 +49371,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1716" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -49397,7 +49397,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1717" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49423,7 +49423,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1718" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -49449,7 +49449,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1719" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49475,7 +49475,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1720" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -49501,7 +49501,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1721" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49527,7 +49527,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1722" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49553,7 +49553,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1723" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49579,7 +49579,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1724" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49605,7 +49605,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1725" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49631,7 +49631,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1726" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49657,7 +49657,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1727" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49683,7 +49683,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1728" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49709,7 +49709,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1729" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49735,7 +49735,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1730" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -49761,7 +49761,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -49787,7 +49787,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1732" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -49813,7 +49813,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G1733" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -49839,7 +49839,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1734" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -49865,7 +49865,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1735" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49891,7 +49891,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1736" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49917,7 +49917,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1737" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49943,7 +49943,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1738" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49969,7 +49969,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1739" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -49995,7 +49995,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1740" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -50021,7 +50021,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1741" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -50047,7 +50047,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1742" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -50073,7 +50073,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1743" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -50099,7 +50099,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1744" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -50125,7 +50125,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1745" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -50151,7 +50151,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1746" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -50177,7 +50177,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1747" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -50203,7 +50203,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1748" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -50229,7 +50229,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1749" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50255,7 +50255,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1750" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -50281,7 +50281,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1751" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -50307,7 +50307,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1752" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -50333,7 +50333,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1753" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -50359,7 +50359,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -50385,7 +50385,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1755" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -50411,7 +50411,7 @@
         <v>14</v>
       </c>
       <c r="G1756" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -50437,7 +50437,7 @@
         <v>14</v>
       </c>
       <c r="G1757" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50463,7 +50463,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1758" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -50489,7 +50489,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1759" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -50515,7 +50515,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1760" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50541,7 +50541,7 @@
         <v>14</v>
       </c>
       <c r="G1761" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50567,7 +50567,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1762" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50593,7 +50593,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -50619,7 +50619,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1764" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -50645,7 +50645,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1765" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50671,7 +50671,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1766" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -50697,7 +50697,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1767" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50723,7 +50723,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1768" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -50749,7 +50749,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1769" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -50775,7 +50775,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1770" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50801,7 +50801,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1771" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50827,7 +50827,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1772" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -50853,7 +50853,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1773" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50879,7 +50879,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1774" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50905,7 +50905,7 @@
         <v>14</v>
       </c>
       <c r="G1775" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50931,7 +50931,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1776" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50957,7 +50957,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1777" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50983,7 +50983,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1778" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -51009,7 +51009,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1779" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -51035,7 +51035,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1780" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -51061,7 +51061,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1781" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -51087,7 +51087,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -51113,7 +51113,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1783" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -51139,7 +51139,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1784" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -51165,7 +51165,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1785" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -51191,7 +51191,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1786" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -51217,7 +51217,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1787" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -51243,7 +51243,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1788" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -51269,7 +51269,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1789" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51295,7 +51295,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1790" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51321,7 +51321,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1791" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -51347,7 +51347,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1792" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -51373,7 +51373,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1793" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -51399,7 +51399,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1794" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51425,7 +51425,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1795" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -51451,7 +51451,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1796" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -51477,7 +51477,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1797" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51503,7 +51503,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1798" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51529,7 +51529,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1799" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51555,7 +51555,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1800" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -51581,7 +51581,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1801" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -51607,7 +51607,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1802" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -51633,7 +51633,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1803" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51659,7 +51659,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1804" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -51685,7 +51685,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1805" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -51711,7 +51711,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1806" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51737,7 +51737,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1807" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -51763,7 +51763,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51789,7 +51789,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1809" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51815,7 +51815,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1810" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51841,7 +51841,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1811" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51867,7 +51867,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1812" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51893,7 +51893,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1813" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51919,7 +51919,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1814" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51945,7 +51945,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1815" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51971,7 +51971,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1816" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51997,7 +51997,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1817" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -52023,7 +52023,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1818" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -52049,7 +52049,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1819" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -52075,7 +52075,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1820" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -52101,7 +52101,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1821" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -52127,7 +52127,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1822" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -52153,7 +52153,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1823" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -52179,7 +52179,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1824" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -52205,7 +52205,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1825" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -52231,7 +52231,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1826" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -52257,7 +52257,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1827" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52283,7 +52283,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1828" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -52309,7 +52309,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1829" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -52335,7 +52335,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1830" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -52361,7 +52361,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1831" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -52387,7 +52387,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1832" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -52413,7 +52413,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1833" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52439,7 +52439,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1834" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -52465,7 +52465,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1835" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52491,7 +52491,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1836" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52517,7 +52517,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1837" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52543,7 +52543,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1838" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -52569,7 +52569,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1839" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -52595,7 +52595,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52621,7 +52621,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1841" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52647,7 +52647,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1842" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52673,7 +52673,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1843" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52699,7 +52699,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1844" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52725,7 +52725,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1845" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52751,7 +52751,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1846" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52777,7 +52777,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1847" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52803,7 +52803,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1848" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52829,7 +52829,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1849" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52855,7 +52855,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1850" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52881,7 +52881,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1851" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52907,7 +52907,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1852" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52933,7 +52933,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1853" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52959,7 +52959,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1854" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52985,7 +52985,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1855" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -53011,7 +53011,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1856" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -53037,7 +53037,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1857" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -53063,7 +53063,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G1858" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -53089,7 +53089,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1859" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -53115,7 +53115,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1860" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -53141,7 +53141,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1861" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -53167,7 +53167,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1862" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -53193,7 +53193,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1863" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -53219,7 +53219,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1864" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -53245,7 +53245,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1865" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -53271,7 +53271,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1866" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -53297,7 +53297,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -53323,7 +53323,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1868" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -53349,7 +53349,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1869" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53375,7 +53375,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1870" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53401,7 +53401,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1871" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53427,7 +53427,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1872" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53453,7 +53453,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1873" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53479,7 +53479,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1874" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53505,7 +53505,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1875" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53531,7 +53531,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1876" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53557,7 +53557,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1877" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53583,7 +53583,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1878" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -55143,7 +55143,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1938" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -70231,7 +70231,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6912962963</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>81444</v>
@@ -70252,6 +70252,32 @@
         <v>1470</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6911458333</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>57113</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>7.21000003814697</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>7.1399998664856</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1462</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="1472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="1473">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">4.02447938919067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93978905677795</t>
+    <t xml:space="preserve">3.93978881835938</t>
   </si>
   <si>
     <t xml:space="preserve">3.82799792289734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78057217597961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943164825439</t>
+    <t xml:space="preserve">3.78057169914246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943188667297</t>
   </si>
   <si>
     <t xml:space="preserve">3.75685834884644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74330830574036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80089735984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040839195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571782112122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66539263725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56376481056213</t>
+    <t xml:space="preserve">3.74330806732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80089688301086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040863037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66539287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56376457214355</t>
   </si>
   <si>
     <t xml:space="preserve">3.65184259414673</t>
@@ -86,70 +86,70 @@
     <t xml:space="preserve">3.72636938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70265650749207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65861773490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6924934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74669599533081</t>
+    <t xml:space="preserve">3.70265698432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65861749649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69249367713928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74669551849365</t>
   </si>
   <si>
     <t xml:space="preserve">3.59764051437378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086561203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58408951759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49601244926453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4621365070343</t>
+    <t xml:space="preserve">3.59086585044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58408975601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49601197242737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46213626861572</t>
   </si>
   <si>
     <t xml:space="preserve">3.51633810997009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38760900497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40793514251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50956249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55698895454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56715178489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6111912727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57731556892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54682612419128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5265007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50278806686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56037640571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58070278167725</t>
+    <t xml:space="preserve">3.38760876655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40793418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50956225395203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55698943138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56715226173401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61119151115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57731533050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54682683944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52650094032288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50278759002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56037664413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58070230484009</t>
   </si>
   <si>
     <t xml:space="preserve">3.60102844238281</t>
@@ -158,25 +158,25 @@
     <t xml:space="preserve">3.54343867301941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5705394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64506697654724</t>
+    <t xml:space="preserve">3.57053971290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64506769180298</t>
   </si>
   <si>
     <t xml:space="preserve">3.78734636306763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84154844284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8652617931366</t>
+    <t xml:space="preserve">3.84154891967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86526131629944</t>
   </si>
   <si>
     <t xml:space="preserve">3.85171151161194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92962670326233</t>
+    <t xml:space="preserve">3.92962646484375</t>
   </si>
   <si>
     <t xml:space="preserve">3.93640184402466</t>
@@ -185,52 +185,52 @@
     <t xml:space="preserve">3.91607642173767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9025251865387</t>
+    <t xml:space="preserve">3.90252542495728</t>
   </si>
   <si>
     <t xml:space="preserve">3.89575004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90930128097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97027778625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87881207466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85848665237427</t>
+    <t xml:space="preserve">3.92285180091858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90930151939392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97027730941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87881231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85848689079285</t>
   </si>
   <si>
     <t xml:space="preserve">3.94317698478699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89913749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94656467437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9567277431488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96350264549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91268825531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9736647605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91946339607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87203693389893</t>
+    <t xml:space="preserve">3.89913773536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94656419754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95672726631165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96350240707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91268873214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97366499900818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91946363449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87203741073608</t>
   </si>
   <si>
     <t xml:space="preserve">3.88704752922058</t>
@@ -239,46 +239,46 @@
     <t xml:space="preserve">3.87291264533997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85877799987793</t>
+    <t xml:space="preserve">3.85877823829651</t>
   </si>
   <si>
     <t xml:space="preserve">3.83757615089417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86231207847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87644648551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89411497116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90118193626404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058184623718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94358730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95418763160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96125507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01426029205322</t>
+    <t xml:space="preserve">3.86231231689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87644720077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89411544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90118265151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89058136940002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94358682632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95418787002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9612557888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01426076889038</t>
   </si>
   <si>
     <t xml:space="preserve">4.02486133575439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08846807479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05666446685791</t>
+    <t xml:space="preserve">4.08846759796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05666494369507</t>
   </si>
   <si>
     <t xml:space="preserve">4.03899669647217</t>
@@ -290,34 +290,34 @@
     <t xml:space="preserve">4.00719308853149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97538948059082</t>
+    <t xml:space="preserve">3.97539067268372</t>
   </si>
   <si>
     <t xml:space="preserve">3.97185659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80223917961121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78103804588318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75630211830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74923467636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90471649169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92238473892212</t>
+    <t xml:space="preserve">3.8022403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78103756904602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75630164146423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7492344379425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9047167301178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92238545417786</t>
   </si>
   <si>
     <t xml:space="preserve">3.95065426826477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03546142578125</t>
+    <t xml:space="preserve">4.03546285629272</t>
   </si>
   <si>
     <t xml:space="preserve">3.75983572006226</t>
@@ -329,16 +329,16 @@
     <t xml:space="preserve">3.83050966262817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86937952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82344150543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80577349662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84110999107361</t>
+    <t xml:space="preserve">3.86937999725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82344174385071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80577301979065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84111070632935</t>
   </si>
   <si>
     <t xml:space="preserve">3.85171103477478</t>
@@ -347,91 +347,91 @@
     <t xml:space="preserve">3.8163743019104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86584615707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89764928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93651962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90825080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91531729698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97892355918884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00012540817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02132749557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95772123336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84464335441589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81284022331238</t>
+    <t xml:space="preserve">3.86584544181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89764904975891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93651866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90825009346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91531777381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97892379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00012588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02132797241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95772099494934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84464383125305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81284070014954</t>
   </si>
   <si>
     <t xml:space="preserve">3.77043652534485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76690316200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76336932182312</t>
+    <t xml:space="preserve">3.76690268516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76336884498596</t>
   </si>
   <si>
     <t xml:space="preserve">3.74570083618164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72449803352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77397084236145</t>
+    <t xml:space="preserve">3.7244987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77397012710571</t>
   </si>
   <si>
     <t xml:space="preserve">3.78810501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81990838050842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72803258895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73863291740417</t>
+    <t xml:space="preserve">3.81990814208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.728031873703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73863315582275</t>
   </si>
   <si>
     <t xml:space="preserve">3.73156666755676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73510003089905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65382552146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63969039916992</t>
+    <t xml:space="preserve">3.73509979248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65382528305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63969016075134</t>
   </si>
   <si>
     <t xml:space="preserve">3.66089224815369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61848855018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61142134666443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62555551528931</t>
+    <t xml:space="preserve">3.618488073349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61142063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62555599212646</t>
   </si>
   <si>
     <t xml:space="preserve">3.61495447158813</t>
@@ -440,55 +440,55 @@
     <t xml:space="preserve">3.64675760269165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74216771125793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91885089874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98599100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99659204483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87997961044312</t>
+    <t xml:space="preserve">3.7421669960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91885137557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98599028587341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9965922832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87997984886169</t>
   </si>
   <si>
     <t xml:space="preserve">3.88351392745972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79517245292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82697486877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79163837432861</t>
+    <t xml:space="preserve">3.79517221450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82697534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79163813591003</t>
   </si>
   <si>
     <t xml:space="preserve">3.84817743301392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7103636264801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8552451133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03192901611328</t>
+    <t xml:space="preserve">3.71036386489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85524487495422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03192853927612</t>
   </si>
   <si>
     <t xml:space="preserve">4.04252958297729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08493423461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09906911849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05313110351562</t>
+    <t xml:space="preserve">4.0849347114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09906816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05313062667847</t>
   </si>
   <si>
     <t xml:space="preserve">4.04959678649902</t>
@@ -500,22 +500,22 @@
     <t xml:space="preserve">4.10966968536377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07786750793457</t>
+    <t xml:space="preserve">4.07786655426025</t>
   </si>
   <si>
     <t xml:space="preserve">4.07433271408081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04606294631958</t>
+    <t xml:space="preserve">4.04606342315674</t>
   </si>
   <si>
     <t xml:space="preserve">4.06373167037964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10613679885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10260248184204</t>
+    <t xml:space="preserve">4.10613584518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10260200500488</t>
   </si>
   <si>
     <t xml:space="preserve">4.13440561294556</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.18387699127197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15914154052734</t>
+    <t xml:space="preserve">4.15914106369019</t>
   </si>
   <si>
     <t xml:space="preserve">4.24041604995728</t>
@@ -539,40 +539,40 @@
     <t xml:space="preserve">4.21568059921265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27575349807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34642601013184</t>
+    <t xml:space="preserve">4.27575254440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34642696380615</t>
   </si>
   <si>
     <t xml:space="preserve">4.36762809753418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35349416732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31108951568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30402135848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38176250457764</t>
+    <t xml:space="preserve">4.35349321365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31108999252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30402183532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38176298141479</t>
   </si>
   <si>
     <t xml:space="preserve">4.50897550582886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72806406021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91181421279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94715261459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19450998306274</t>
+    <t xml:space="preserve">4.72806358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91181516647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94715166091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19450950622559</t>
   </si>
   <si>
     <t xml:space="preserve">5.2227783203125</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">5.22984647750854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2263126373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09203243255615</t>
+    <t xml:space="preserve">5.22631359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09203195571899</t>
   </si>
   <si>
     <t xml:space="preserve">5.07436370849609</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">5.08496570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11676836013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10616779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1521053314209</t>
+    <t xml:space="preserve">5.11676788330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10616731643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15210580825806</t>
   </si>
   <si>
     <t xml:space="preserve">5.15917301177979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17330741882324</t>
+    <t xml:space="preserve">5.17330837249756</t>
   </si>
   <si>
     <t xml:space="preserve">5.19097566604614</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">5.14503812789917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13090324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24751472473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26871728897095</t>
+    <t xml:space="preserve">5.13090372085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2475152015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26871681213379</t>
   </si>
   <si>
     <t xml:space="preserve">5.59734869003296</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5125412940979</t>
+    <t xml:space="preserve">5.51254034042358</t>
   </si>
   <si>
     <t xml:space="preserve">5.35705900192261</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">5.37119340896606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44186639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5302095413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61199760437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65216159820557</t>
+    <t xml:space="preserve">5.44186687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53020906448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6119966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65216112136841</t>
   </si>
   <si>
     <t xml:space="preserve">5.6886739730835</t>
@@ -656,31 +656,31 @@
     <t xml:space="preserve">5.6229510307312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61930084228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59739255905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42213153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41848039627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55357646942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56087970733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49880790710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46229553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55722808837891</t>
+    <t xml:space="preserve">5.61929988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59739208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42213201522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41847991943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55357694625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56087923049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49880838394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4622950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55722856521606</t>
   </si>
   <si>
     <t xml:space="preserve">5.45499277114868</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">5.36736249923706</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37466478347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43308544158936</t>
+    <t xml:space="preserve">5.37466526031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4330849647522</t>
   </si>
   <si>
     <t xml:space="preserve">5.40387535095215</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">5.44769048690796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48055171966553</t>
+    <t xml:space="preserve">5.48055267333984</t>
   </si>
   <si>
     <t xml:space="preserve">5.49515724182129</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">5.54627418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60104322433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41117763519287</t>
+    <t xml:space="preserve">5.60104370117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41117715835571</t>
   </si>
   <si>
     <t xml:space="preserve">5.51341342926025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54992532730103</t>
+    <t xml:space="preserve">5.54992580413818</t>
   </si>
   <si>
     <t xml:space="preserve">5.45134210586548</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">5.50611066818237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34545516967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37101316452026</t>
+    <t xml:space="preserve">5.34545564651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37101364135742</t>
   </si>
   <si>
     <t xml:space="preserve">5.31259346008301</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">5.287034034729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15558910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12637901306152</t>
+    <t xml:space="preserve">5.15558958053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12637853622437</t>
   </si>
   <si>
     <t xml:space="preserve">5.27242946624756</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">5.14098358154297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40752601623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38926982879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37831592559814</t>
+    <t xml:space="preserve">5.40752553939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38927030563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3783164024353</t>
   </si>
   <si>
     <t xml:space="preserve">5.24321889877319</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">5.44038772583008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48420381546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35275745391846</t>
+    <t xml:space="preserve">5.48420286178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3527569770813</t>
   </si>
   <si>
     <t xml:space="preserve">5.48785400390625</t>
@@ -800,25 +800,25 @@
     <t xml:space="preserve">5.57183361053467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57913541793823</t>
+    <t xml:space="preserve">5.57913589477539</t>
   </si>
   <si>
     <t xml:space="preserve">5.56453084945679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52071523666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5389723777771</t>
+    <t xml:space="preserve">5.52071571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53897190093994</t>
   </si>
   <si>
     <t xml:space="preserve">5.65581226348877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58643913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57548427581787</t>
+    <t xml:space="preserve">5.58643817901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57548522949219</t>
   </si>
   <si>
     <t xml:space="preserve">5.50976228713989</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">5.60469532012939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59008932113647</t>
+    <t xml:space="preserve">5.59008979797363</t>
   </si>
   <si>
     <t xml:space="preserve">5.75804805755615</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">5.79456090927124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92965745925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94426298141479</t>
+    <t xml:space="preserve">5.92965793609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94426345825195</t>
   </si>
   <si>
     <t xml:space="preserve">5.99903202056885</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">5.93696022033691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98807764053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83107376098633</t>
+    <t xml:space="preserve">5.98807716369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83107328414917</t>
   </si>
   <si>
     <t xml:space="preserve">5.88584232330322</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">5.83472442626953</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9588680267334</t>
+    <t xml:space="preserve">5.95886754989624</t>
   </si>
   <si>
     <t xml:space="preserve">5.76900196075439</t>
@@ -872,22 +872,22 @@
     <t xml:space="preserve">5.91140079498291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83837556838989</t>
+    <t xml:space="preserve">5.83837604522705</t>
   </si>
   <si>
     <t xml:space="preserve">5.84202671051025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87123775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.783607006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85298109054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7032790184021</t>
+    <t xml:space="preserve">5.87123680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78360652923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85298156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70327949523926</t>
   </si>
   <si>
     <t xml:space="preserve">5.82742214202881</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">5.86393451690674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75439739227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72883749008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68502235412598</t>
+    <t xml:space="preserve">5.75439643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72883796691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68502283096313</t>
   </si>
   <si>
     <t xml:space="preserve">5.66676616668701</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">5.88949346542358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78725910186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77995586395264</t>
+    <t xml:space="preserve">5.78725814819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77995634078979</t>
   </si>
   <si>
     <t xml:space="preserve">5.73614025115967</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">5.6083459854126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63025379180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53532123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76169919967651</t>
+    <t xml:space="preserve">5.63025426864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53532075881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76169872283936</t>
   </si>
   <si>
     <t xml:space="preserve">5.62660264968872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68137121200562</t>
+    <t xml:space="preserve">5.68137168884277</t>
   </si>
   <si>
     <t xml:space="preserve">5.73979187011719</t>
@@ -947,52 +947,52 @@
     <t xml:space="preserve">5.80916595458984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80551433563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82377099990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87853956222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82011938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90409851074219</t>
+    <t xml:space="preserve">5.80551481246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82377052307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8785400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82011985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9040994644165</t>
   </si>
   <si>
     <t xml:space="preserve">5.92600631713867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92235517501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95156526565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02459049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06110334396362</t>
+    <t xml:space="preserve">5.92235469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95156478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02459096908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06110286712646</t>
   </si>
   <si>
     <t xml:space="preserve">6.00998497009277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09031438827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22906112670898</t>
+    <t xml:space="preserve">6.09031343460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22906160354614</t>
   </si>
   <si>
     <t xml:space="preserve">6.18524646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03189373016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0391960144043</t>
+    <t xml:space="preserve">6.03189325332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03919649124146</t>
   </si>
   <si>
     <t xml:space="preserve">6.0464973449707</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">6.25096988677979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20715379714966</t>
+    <t xml:space="preserve">6.20715427398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.14143085479736</t>
@@ -1010,28 +1010,28 @@
     <t xml:space="preserve">6.12682580947876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79821252822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72518634796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96617078781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00268268585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89314413070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84932994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.973473072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99537992477417</t>
+    <t xml:space="preserve">5.7982120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72518682479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96617031097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00268316268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89314460754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84933042526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97347354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99538087844849</t>
   </si>
   <si>
     <t xml:space="preserve">6.11952352523804</t>
@@ -1040,43 +1040,43 @@
     <t xml:space="preserve">6.15603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10491752624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98077535629272</t>
+    <t xml:space="preserve">6.10491800308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98077487945557</t>
   </si>
   <si>
     <t xml:space="preserve">5.90044736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14873361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09761571884155</t>
+    <t xml:space="preserve">6.1487340927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09761619567871</t>
   </si>
   <si>
     <t xml:space="preserve">6.0538010597229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07570838928223</t>
+    <t xml:space="preserve">6.07570743560791</t>
   </si>
   <si>
     <t xml:space="preserve">6.08301115036011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17794370651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17064046859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2436671257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28017902374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38636589050293</t>
+    <t xml:space="preserve">6.17794418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17064094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24366664886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28017950057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38636541366577</t>
   </si>
   <si>
     <t xml:space="preserve">6.31810283660889</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">6.27259492874146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26500988006592</t>
+    <t xml:space="preserve">6.26500940322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.21191596984863</t>
@@ -1103,19 +1103,19 @@
     <t xml:space="preserve">6.18157720565796</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15123796463013</t>
+    <t xml:space="preserve">6.15123748779297</t>
   </si>
   <si>
     <t xml:space="preserve">6.02988195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05263614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25742435455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22708559036255</t>
+    <t xml:space="preserve">6.05263662338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25742483139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22708606719971</t>
   </si>
   <si>
     <t xml:space="preserve">6.24983978271484</t>
@@ -1130,28 +1130,28 @@
     <t xml:space="preserve">6.1891622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1664080619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20433139801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0147123336792</t>
+    <t xml:space="preserve">6.16640758514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20433187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01471185684204</t>
   </si>
   <si>
     <t xml:space="preserve">6.04505157470703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00712823867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98437309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12089872360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13606834411621</t>
+    <t xml:space="preserve">6.00712776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98437356948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12089920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13606882095337</t>
   </si>
   <si>
     <t xml:space="preserve">6.11331462860107</t>
@@ -1160,49 +1160,49 @@
     <t xml:space="preserve">6.09055948257446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96161937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0829758644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14365386962891</t>
+    <t xml:space="preserve">5.96161890029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08297538757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14365434646606</t>
   </si>
   <si>
     <t xml:space="preserve">6.10572957992554</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06022119522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99954319000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95403432846069</t>
+    <t xml:space="preserve">6.06022071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99954271316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95403385162354</t>
   </si>
   <si>
     <t xml:space="preserve">5.93886470794678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06780529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91611099243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94644927978516</t>
+    <t xml:space="preserve">6.06780624389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9161114692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94644975662231</t>
   </si>
   <si>
     <t xml:space="preserve">5.87818670272827</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03746700286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02229738235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99195861816406</t>
+    <t xml:space="preserve">6.03746652603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02229690551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9919581413269</t>
   </si>
   <si>
     <t xml:space="preserve">5.86301708221436</t>
@@ -1211,49 +1211,49 @@
     <t xml:space="preserve">6.07539081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24225425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738313674927</t>
+    <t xml:space="preserve">6.24225521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738265991211</t>
   </si>
   <si>
     <t xml:space="preserve">6.63666296005249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46221399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57598447799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56081485748291</t>
+    <t xml:space="preserve">6.46221351623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57598495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56081438064575</t>
   </si>
   <si>
     <t xml:space="preserve">6.60632371902466</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55322980880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65183305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53806018829346</t>
+    <t xml:space="preserve">6.55323076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65183210372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53806066513062</t>
   </si>
   <si>
     <t xml:space="preserve">6.48496770858765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6139087677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66700172424316</t>
+    <t xml:space="preserve">6.61390829086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66700220108032</t>
   </si>
   <si>
     <t xml:space="preserve">6.59873867034912</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34085655212402</t>
+    <t xml:space="preserve">6.34085702896118</t>
   </si>
   <si>
     <t xml:space="preserve">6.39395046234131</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">6.44704389572144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34844160079956</t>
+    <t xml:space="preserve">6.3484411239624</t>
   </si>
   <si>
     <t xml:space="preserve">6.21950101852417</t>
@@ -1289,16 +1289,16 @@
     <t xml:space="preserve">6.40911960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32568788528442</t>
+    <t xml:space="preserve">6.32568740844727</t>
   </si>
   <si>
     <t xml:space="preserve">6.28776407241821</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68975639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67458724975586</t>
+    <t xml:space="preserve">6.6897554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67458581924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.74284934997559</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">6.62149286270142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37878036499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36361074447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46979761123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51530647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31051826477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3560266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19674730300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40153408050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72009515762329</t>
+    <t xml:space="preserve">6.37878084182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36361122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46979856491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51530694961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31051731109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35602712631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19674682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40153455734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72009468078613</t>
   </si>
   <si>
     <t xml:space="preserve">6.75801849365234</t>
@@ -1346,31 +1346,31 @@
     <t xml:space="preserve">6.78835725784302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73526382446289</t>
+    <t xml:space="preserve">6.73526430130005</t>
   </si>
   <si>
     <t xml:space="preserve">6.84903573989868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86420631408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81111145019531</t>
+    <t xml:space="preserve">6.8642053604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81111192703247</t>
   </si>
   <si>
     <t xml:space="preserve">6.84145164489746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81869697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90212869644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9931468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89454412460327</t>
+    <t xml:space="preserve">6.81869602203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90212917327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99314594268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89454507827759</t>
   </si>
   <si>
     <t xml:space="preserve">6.94005298614502</t>
@@ -1379,40 +1379,40 @@
     <t xml:space="preserve">7.05382442474365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10691738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15242624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11450147628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01590061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08416271209717</t>
+    <t xml:space="preserve">7.10691785812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15242671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.114501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01590013504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08416366577148</t>
   </si>
   <si>
     <t xml:space="preserve">7.04623937606812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09174823760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39513874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35721397399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34204530715942</t>
+    <t xml:space="preserve">7.09174919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39513826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35721492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34204578399658</t>
   </si>
   <si>
     <t xml:space="preserve">7.1220874786377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13725614547729</t>
+    <t xml:space="preserve">7.13725662231445</t>
   </si>
   <si>
     <t xml:space="preserve">7.12967205047607</t>
@@ -1424,40 +1424,40 @@
     <t xml:space="preserve">7.22827339172363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2055196762085</t>
+    <t xml:space="preserve">7.20552015304565</t>
   </si>
   <si>
     <t xml:space="preserve">7.19793462753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16759490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37996912002563</t>
+    <t xml:space="preserve">7.16759538650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37996816635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.43306255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49373912811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53924894332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54683256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75162267684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79713106155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64543533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69094371795654</t>
+    <t xml:space="preserve">7.49374055862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53924798965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54683351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75162172317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79713010787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64543581008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6909441947937</t>
   </si>
   <si>
     <t xml:space="preserve">7.57717227935791</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">7.4558162689209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51649379730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59992742538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50890970230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56200313568115</t>
+    <t xml:space="preserve">7.5164942741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59992694854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50890922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56200265884399</t>
   </si>
   <si>
     <t xml:space="preserve">7.58475732803345</t>
@@ -1484,79 +1484,79 @@
     <t xml:space="preserve">7.55441856384277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47857093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47098636627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44823217391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70611333847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331697463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88814783096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25221538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61628341674805</t>
+    <t xml:space="preserve">7.47857046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47098684310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44823169708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7061128616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331792831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88814640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25221633911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61628437042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.49492740631104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17636775970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41908073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11876964569092</t>
+    <t xml:space="preserve">8.17636871337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41908168792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1187686920166</t>
   </si>
   <si>
     <t xml:space="preserve">8.08742237091064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93068933486938</t>
+    <t xml:space="preserve">7.93068885803223</t>
   </si>
   <si>
     <t xml:space="preserve">8.04040241241455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96203517913818</t>
+    <t xml:space="preserve">7.96203565597534</t>
   </si>
   <si>
     <t xml:space="preserve">8.25982856750488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0247278213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.867995262146</t>
+    <t xml:space="preserve">8.02472877502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86799621582031</t>
   </si>
   <si>
     <t xml:space="preserve">7.7347731590271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8366494178772</t>
+    <t xml:space="preserve">7.83664894104004</t>
   </si>
   <si>
     <t xml:space="preserve">7.82097625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91501617431641</t>
+    <t xml:space="preserve">7.91501665115356</t>
   </si>
   <si>
     <t xml:space="preserve">7.97770929336548</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07174968719482</t>
+    <t xml:space="preserve">8.07174873352051</t>
   </si>
   <si>
     <t xml:space="preserve">8.05607509613037</t>
@@ -1565,22 +1565,22 @@
     <t xml:space="preserve">7.85232305526733</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40088844299316</t>
+    <t xml:space="preserve">8.4008903503418</t>
   </si>
   <si>
     <t xml:space="preserve">8.46358203887939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6203145980835</t>
+    <t xml:space="preserve">8.62031364440918</t>
   </si>
   <si>
     <t xml:space="preserve">8.30684852600098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1657886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33819580078125</t>
+    <t xml:space="preserve">8.16578960418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33819675445557</t>
   </si>
   <si>
     <t xml:space="preserve">8.21280860900879</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">8.36954212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15011692047119</t>
+    <t xml:space="preserve">8.15011501312256</t>
   </si>
   <si>
     <t xml:space="preserve">8.18146228790283</t>
@@ -1601,46 +1601,46 @@
     <t xml:space="preserve">8.13444328308105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22848129272461</t>
+    <t xml:space="preserve">8.22848224639893</t>
   </si>
   <si>
     <t xml:space="preserve">8.43223571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9933819770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19713592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75828313827515</t>
+    <t xml:space="preserve">7.99338245391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19713497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7582836151123</t>
   </si>
   <si>
     <t xml:space="preserve">7.89934301376343</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82881307601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88366937637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313991546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6799168586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79746532440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41656303405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80530214309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68775320053101</t>
+    <t xml:space="preserve">7.82881259918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88366985321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67991733551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79746675491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41656112670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80530309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68775367736816</t>
   </si>
   <si>
     <t xml:space="preserve">7.74260997772217</t>
@@ -1649,28 +1649,28 @@
     <t xml:space="preserve">8.00905609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94636297225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75044631958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71909999847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1030969619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82406806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37263298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60773372650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.482346534729</t>
+    <t xml:space="preserve">7.94636344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75044727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71910047531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10309600830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82406711578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37263202667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60773277282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48234748840332</t>
   </si>
   <si>
     <t xml:space="preserve">9.79581260681152</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">9.87417984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99956512451172</t>
+    <t xml:space="preserve">9.99956607818604</t>
   </si>
   <si>
     <t xml:space="preserve">10.1562976837158</t>
@@ -1691,19 +1691,19 @@
     <t xml:space="preserve">10.5011100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3757238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5481300354004</t>
+    <t xml:space="preserve">10.3757247924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5481309890747</t>
   </si>
   <si>
     <t xml:space="preserve">10.2189903259277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1719703674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95254421234131</t>
+    <t xml:space="preserve">10.171971321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95254516601562</t>
   </si>
   <si>
     <t xml:space="preserve">9.90552520751953</t>
@@ -1721,25 +1721,25 @@
     <t xml:space="preserve">9.76446628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57638549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96821975708008</t>
+    <t xml:space="preserve">9.57638645172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96821880340576</t>
   </si>
   <si>
     <t xml:space="preserve">10.0309114456177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4854373931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.250337600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0152378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1249513626099</t>
+    <t xml:space="preserve">10.4854383468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2503385543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0152387619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1249523162842</t>
   </si>
   <si>
     <t xml:space="preserve">10.3600511550903</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.2973585128784</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3130302429199</t>
+    <t xml:space="preserve">10.3130311965942</t>
   </si>
   <si>
     <t xml:space="preserve">10.4384174346924</t>
@@ -1760,40 +1760,40 @@
     <t xml:space="preserve">10.657844543457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6108236312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5951509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.579475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6421689987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7518835067749</t>
+    <t xml:space="preserve">10.6108245849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5951519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5794763565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6421699523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7518844604492</t>
   </si>
   <si>
     <t xml:space="preserve">10.9869823455811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9556350708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1280422210693</t>
+    <t xml:space="preserve">10.9556360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1280431747437</t>
   </si>
   <si>
     <t xml:space="preserve">11.0183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2377548217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0966949462891</t>
+    <t xml:space="preserve">11.2377557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0966958999634</t>
   </si>
   <si>
     <t xml:space="preserve">11.1750621795654</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">11.1123695373535</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0810222625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9713096618652</t>
+    <t xml:space="preserve">11.0810232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9713087081909</t>
   </si>
   <si>
     <t xml:space="preserve">10.798903465271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0622577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0936050415039</t>
+    <t xml:space="preserve">10.0622587203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0936040878296</t>
   </si>
   <si>
     <t xml:space="preserve">9.68609809875488</t>
@@ -1823,25 +1823,25 @@
     <t xml:space="preserve">9.29426670074463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5450382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98080158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54194736480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31943130493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50751066207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53885650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49183797836304</t>
+    <t xml:space="preserve">9.54504013061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98080062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54194831848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31943082809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50751113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53885746002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49183702468872</t>
   </si>
   <si>
     <t xml:space="preserve">8.66733551025391</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">8.44790840148926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38521575927734</t>
+    <t xml:space="preserve">8.38521480560303</t>
   </si>
   <si>
     <t xml:space="preserve">8.52627563476562</t>
@@ -1859,25 +1859,25 @@
     <t xml:space="preserve">9.01214790344238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45100021362305</t>
+    <t xml:space="preserve">9.45099925994873</t>
   </si>
   <si>
     <t xml:space="preserve">9.10618782043457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93378162384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38830661773682</t>
+    <t xml:space="preserve">8.93378067016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38830471038818</t>
   </si>
   <si>
     <t xml:space="preserve">8.88676071166992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8710880279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12185955047607</t>
+    <t xml:space="preserve">8.87108707427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12186050415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.91810703277588</t>
@@ -1886,16 +1886,16 @@
     <t xml:space="preserve">9.15320682525635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90243339538574</t>
+    <t xml:space="preserve">8.90243434906006</t>
   </si>
   <si>
     <t xml:space="preserve">9.05916690826416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04349422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21589946746826</t>
+    <t xml:space="preserve">9.04349517822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21590042114258</t>
   </si>
   <si>
     <t xml:space="preserve">8.96512699127197</t>
@@ -1904,19 +1904,19 @@
     <t xml:space="preserve">9.30298042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12407779693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01023006439209</t>
+    <t xml:space="preserve">9.12407684326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01023101806641</t>
   </si>
   <si>
     <t xml:space="preserve">8.68495082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50604724884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70121479034424</t>
+    <t xml:space="preserve">8.50604629516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70121383666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.18913269042969</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">8.92891025543213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76627063751221</t>
+    <t xml:space="preserve">8.76626968383789</t>
   </si>
   <si>
     <t xml:space="preserve">8.71747875213623</t>
@@ -1934,22 +1934,22 @@
     <t xml:space="preserve">8.97770118713379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33550834655762</t>
+    <t xml:space="preserve">9.33550930023193</t>
   </si>
   <si>
     <t xml:space="preserve">9.48188495635986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61199569702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2625532150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0673866271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3113470077515</t>
+    <t xml:space="preserve">9.6119966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2625541687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0673875808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3113460540771</t>
   </si>
   <si>
     <t xml:space="preserve">10.1812343597412</t>
@@ -1961,34 +1961,34 @@
     <t xml:space="preserve">10.2788181304932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2300252914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95353889465332</t>
+    <t xml:space="preserve">10.2300243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.953537940979</t>
   </si>
   <si>
     <t xml:space="preserve">9.88848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69331645965576</t>
+    <t xml:space="preserve">9.69331550598145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1324434280396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1974983215332</t>
+    <t xml:space="preserve">10.1974973678589</t>
   </si>
   <si>
     <t xml:space="preserve">10.3276090621948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2462911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5553045272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8480567932129</t>
+    <t xml:space="preserve">10.2462902069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.555305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8480558395386</t>
   </si>
   <si>
     <t xml:space="preserve">10.8805837631226</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">10.8317918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7992630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9293756484985</t>
+    <t xml:space="preserve">10.7992639541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9293766021729</t>
   </si>
   <si>
     <t xml:space="preserve">10.685417175293</t>
@@ -2012,49 +2012,49 @@
     <t xml:space="preserve">10.7667360305786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9781665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1245431900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1408061981201</t>
+    <t xml:space="preserve">10.9781675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1245441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1408071517944</t>
   </si>
   <si>
     <t xml:space="preserve">11.2871828079224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3847665786743</t>
+    <t xml:space="preserve">11.3847675323486</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474061965942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4335584640503</t>
+    <t xml:space="preserve">11.4335594177246</t>
   </si>
   <si>
     <t xml:space="preserve">11.4498224258423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4660863876343</t>
+    <t xml:space="preserve">11.4660873413086</t>
   </si>
   <si>
     <t xml:space="preserve">11.4823503494263</t>
   </si>
   <si>
-    <t xml:space="preserve">11.335973739624</t>
+    <t xml:space="preserve">11.3359746932983</t>
   </si>
   <si>
     <t xml:space="preserve">11.2058629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2221269607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8643198013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5390405654907</t>
+    <t xml:space="preserve">11.2221260070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8643207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.539041519165</t>
   </si>
   <si>
     <t xml:space="preserve">10.522777557373</t>
@@ -2066,25 +2066,25 @@
     <t xml:space="preserve">10.8155279159546</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6040964126587</t>
+    <t xml:space="preserve">10.604097366333</t>
   </si>
   <si>
     <t xml:space="preserve">10.7342090606689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.620361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7179441452026</t>
+    <t xml:space="preserve">10.6203603744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.717945098877</t>
   </si>
   <si>
     <t xml:space="preserve">10.5065135955811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.587833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4577207565308</t>
+    <t xml:space="preserve">10.5878343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4577217102051</t>
   </si>
   <si>
     <t xml:space="preserve">10.3764019012451</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">10.571569442749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089298248291</t>
+    <t xml:space="preserve">10.4089307785034</t>
   </si>
   <si>
     <t xml:space="preserve">10.8968477249146</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">11.0594882965088</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9944324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.669153213501</t>
+    <t xml:space="preserve">10.9944334030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6691522598267</t>
   </si>
   <si>
     <t xml:space="preserve">10.7830009460449</t>
@@ -2123,43 +2123,43 @@
     <t xml:space="preserve">11.1895990371704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5799331665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.417293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.30344581604</t>
+    <t xml:space="preserve">11.5799350738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4172945022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3034477233887</t>
   </si>
   <si>
     <t xml:space="preserve">9.9860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0836496353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4414567947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7504730224609</t>
+    <t xml:space="preserve">10.0836505889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4414577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7504711151123</t>
   </si>
   <si>
     <t xml:space="preserve">11.1570711135864</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1082792282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0269603729248</t>
+    <t xml:space="preserve">11.1082801818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0269594192505</t>
   </si>
   <si>
     <t xml:space="preserve">10.9131126403809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2546539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3522386550903</t>
+    <t xml:space="preserve">11.2546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.352237701416</t>
   </si>
   <si>
     <t xml:space="preserve">11.4010305404663</t>
@@ -2168,22 +2168,22 @@
     <t xml:space="preserve">11.3197107315063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1733360290527</t>
+    <t xml:space="preserve">11.1733350753784</t>
   </si>
   <si>
     <t xml:space="preserve">11.0106954574585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5311422348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7751016616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7100458145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7425737380981</t>
+    <t xml:space="preserve">11.5311431884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7751007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7100448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7425718307495</t>
   </si>
   <si>
     <t xml:space="preserve">12.0190601348877</t>
@@ -2192,25 +2192,25 @@
     <t xml:space="preserve">12.3118124008179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5882987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1979646682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8726863861084</t>
+    <t xml:space="preserve">12.5882997512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1979637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8726844787598</t>
   </si>
   <si>
     <t xml:space="preserve">12.00279712677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8076305389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8564214706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5961980819702</t>
+    <t xml:space="preserve">11.8076295852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8564224243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5961990356445</t>
   </si>
   <si>
     <t xml:space="preserve">11.954005241394</t>
@@ -2219,19 +2219,19 @@
     <t xml:space="preserve">11.986533164978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1003818511963</t>
+    <t xml:space="preserve">12.100380897522</t>
   </si>
   <si>
     <t xml:space="preserve">12.1816997528076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1166439056396</t>
+    <t xml:space="preserve">12.116644859314</t>
   </si>
   <si>
     <t xml:space="preserve">12.2792844772339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4093971252441</t>
+    <t xml:space="preserve">12.4093961715698</t>
   </si>
   <si>
     <t xml:space="preserve">12.5069799423218</t>
@@ -2240,19 +2240,19 @@
     <t xml:space="preserve">12.4581880569458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907159805298</t>
+    <t xml:space="preserve">12.4907150268555</t>
   </si>
   <si>
     <t xml:space="preserve">12.8973140716553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0111627578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9786338806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8647861480713</t>
+    <t xml:space="preserve">13.0111618041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9786348342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.864785194397</t>
   </si>
   <si>
     <t xml:space="preserve">12.7997303009033</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">12.8810501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1738023757935</t>
+    <t xml:space="preserve">13.1738033294678</t>
   </si>
   <si>
     <t xml:space="preserve">13.2713842391968</t>
@@ -2273,19 +2273,19 @@
     <t xml:space="preserve">13.3527050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7267751693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8243608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0520544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.23095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2634868621826</t>
+    <t xml:space="preserve">13.7267761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8243598937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.052056312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2309598922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634859085083</t>
   </si>
   <si>
     <t xml:space="preserve">14.2146940231323</t>
@@ -2297,10 +2297,10 @@
     <t xml:space="preserve">13.6129274368286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8080940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8894166946411</t>
+    <t xml:space="preserve">13.8080949783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8894147872925</t>
   </si>
   <si>
     <t xml:space="preserve">13.6454563140869</t>
@@ -2312,13 +2312,13 @@
     <t xml:space="preserve">13.7918300628662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0032634735107</t>
+    <t xml:space="preserve">14.0032615661621</t>
   </si>
   <si>
     <t xml:space="preserve">13.9544706344604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3448047637939</t>
+    <t xml:space="preserve">14.3448057174683</t>
   </si>
   <si>
     <t xml:space="preserve">14.1496391296387</t>
@@ -2327,16 +2327,16 @@
     <t xml:space="preserve">14.2472219467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4749174118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5579166412354</t>
+    <t xml:space="preserve">14.4749164581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.557915687561</t>
   </si>
   <si>
     <t xml:space="preserve">14.192723274231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1595220565796</t>
+    <t xml:space="preserve">14.1595239639282</t>
   </si>
   <si>
     <t xml:space="preserve">14.1429243087769</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">14.2757215499878</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2923212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.375319480896</t>
+    <t xml:space="preserve">14.2923192977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3753185272217</t>
   </si>
   <si>
     <t xml:space="preserve">14.1097249984741</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">14.0765237808228</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2093229293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9935264587402</t>
+    <t xml:space="preserve">14.2093238830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9935274124146</t>
   </si>
   <si>
     <t xml:space="preserve">13.8109292984009</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">14.0433263778687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3255195617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2259225845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3421201705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1761245727539</t>
+    <t xml:space="preserve">14.3255205154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2259206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3421211242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1761226654053</t>
   </si>
   <si>
     <t xml:space="preserve">13.9437265396118</t>
@@ -2402,109 +2402,109 @@
     <t xml:space="preserve">14.0931243896484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9603281021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3587198257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591218948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5081167221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.524715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.026725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.707311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7737112045288</t>
+    <t xml:space="preserve">13.9603271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.358717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5081157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5247173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0267248153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7073125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7737102508545</t>
   </si>
   <si>
     <t xml:space="preserve">14.6907138824463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7405118942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9397096633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1057043075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3214998245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1721048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8899097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3713006973267</t>
+    <t xml:space="preserve">14.7405128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9397087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1057052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3214988708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1721029281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.889910697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3712997436523</t>
   </si>
   <si>
     <t xml:space="preserve">15.703293800354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5372953414917</t>
+    <t xml:space="preserve">15.537296295166</t>
   </si>
   <si>
     <t xml:space="preserve">15.387900352478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2882995605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2717008590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0725040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2219018936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1223049163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9895076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.85671043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8235111236572</t>
+    <t xml:space="preserve">15.2883014678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2717018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0725049972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2219038009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1223030090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9895067214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8235101699829</t>
   </si>
   <si>
     <t xml:space="preserve">14.7903108596802</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1389045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9729080200195</t>
+    <t xml:space="preserve">15.1389055252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9729089736938</t>
   </si>
   <si>
     <t xml:space="preserve">14.873309135437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8069124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8607292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6947317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7113332748413</t>
+    <t xml:space="preserve">14.8069105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8607301712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.711332321167</t>
   </si>
   <si>
     <t xml:space="preserve">14.4417181015015</t>
@@ -2513,22 +2513,22 @@
     <t xml:space="preserve">14.5745153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5413150787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4251184463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4085178375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3919191360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4708976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2053022384644</t>
+    <t xml:space="preserve">14.5413160324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4251165390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4085187911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3919200897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4708986282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.205304145813</t>
   </si>
   <si>
     <t xml:space="preserve">15.0227069854736</t>
@@ -2537,28 +2537,28 @@
     <t xml:space="preserve">14.4915161132812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8275299072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7777309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6449346542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5287342071533</t>
+    <t xml:space="preserve">13.8275308609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7777318954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6449337005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445306777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5287351608276</t>
   </si>
   <si>
     <t xml:space="preserve">13.5619354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4125385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1137437820435</t>
+    <t xml:space="preserve">13.4125375747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1137447357178</t>
   </si>
   <si>
     <t xml:space="preserve">13.2797403335571</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">13.362738609314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5121364593506</t>
+    <t xml:space="preserve">13.5121374130249</t>
   </si>
   <si>
     <t xml:space="preserve">13.5951337814331</t>
@@ -2576,37 +2576,37 @@
     <t xml:space="preserve">13.6117334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1303434371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3295402526855</t>
+    <t xml:space="preserve">13.1303424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3295392990112</t>
   </si>
   <si>
     <t xml:space="preserve">13.4955368041992</t>
   </si>
   <si>
-    <t xml:space="preserve">13.080545425415</t>
+    <t xml:space="preserve">13.0805444717407</t>
   </si>
   <si>
     <t xml:space="preserve">13.3129405975342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.196741104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7983503341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4497575759888</t>
+    <t xml:space="preserve">13.1967420578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7983493804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4497566223145</t>
   </si>
   <si>
     <t xml:space="preserve">12.3003597259521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7153511047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4331560134888</t>
+    <t xml:space="preserve">12.7153520584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4331569671631</t>
   </si>
   <si>
     <t xml:space="preserve">12.5991535186768</t>
@@ -2621,46 +2621,46 @@
     <t xml:space="preserve">12.067964553833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8521690368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6695718765259</t>
+    <t xml:space="preserve">11.8521671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6695728302002</t>
   </si>
   <si>
     <t xml:space="preserve">12.0845642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8189687728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6031732559204</t>
+    <t xml:space="preserve">11.8189697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6031723022461</t>
   </si>
   <si>
     <t xml:space="preserve">11.7027721405029</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7857704162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5367746353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3209800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1715822219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.221381187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8395891189575</t>
+    <t xml:space="preserve">11.7857694625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5367755889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3209781646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1715812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2213821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8395881652832</t>
   </si>
   <si>
     <t xml:space="preserve">10.2088012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6735906600952</t>
+    <t xml:space="preserve">10.6735916137695</t>
   </si>
   <si>
     <t xml:space="preserve">10.6237936019897</t>
@@ -2678,16 +2678,16 @@
     <t xml:space="preserve">9.54481410980225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56141376495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36221790313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62781238555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32901763916016</t>
+    <t xml:space="preserve">9.5614128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62781143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32901859283447</t>
   </si>
   <si>
     <t xml:space="preserve">9.52821445465088</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">9.39541625976562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.391396522522</t>
+    <t xml:space="preserve">10.3913974761963</t>
   </si>
   <si>
     <t xml:space="preserve">10.6071929931641</t>
@@ -2711,34 +2711,34 @@
     <t xml:space="preserve">10.4909954071045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1756019592285</t>
+    <t xml:space="preserve">10.1756010055542</t>
   </si>
   <si>
     <t xml:space="preserve">10.1092023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1424016952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0594024658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86020755767822</t>
+    <t xml:space="preserve">10.1424026489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0594034194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86020851135254</t>
   </si>
   <si>
     <t xml:space="preserve">9.89340686798096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69421100616455</t>
+    <t xml:space="preserve">9.69421005249023</t>
   </si>
   <si>
     <t xml:space="preserve">9.61121273040771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17962074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27921962738037</t>
+    <t xml:space="preserve">9.17962169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27921867370605</t>
   </si>
   <si>
     <t xml:space="preserve">9.37881660461426</t>
@@ -2747,16 +2747,16 @@
     <t xml:space="preserve">9.19622135162354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29581832885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12982082366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42861461639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77720928192139</t>
+    <t xml:space="preserve">9.29581737518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12982177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42861557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77720832824707</t>
   </si>
   <si>
     <t xml:space="preserve">9.64441108703613</t>
@@ -2765,10 +2765,10 @@
     <t xml:space="preserve">10.0262041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5407943725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4577970504761</t>
+    <t xml:space="preserve">10.5407934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4577960968018</t>
   </si>
   <si>
     <t xml:space="preserve">10.0760040283203</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">9.7205171585083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0639991760254</t>
+    <t xml:space="preserve">10.0639982223511</t>
   </si>
   <si>
     <t xml:space="preserve">10.0983467102051</t>
@@ -2798,19 +2798,19 @@
     <t xml:space="preserve">9.85791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0811719894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3559579849243</t>
+    <t xml:space="preserve">10.0811729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.35595703125</t>
   </si>
   <si>
     <t xml:space="preserve">10.2700872421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6479158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7681350708008</t>
+    <t xml:space="preserve">10.6479167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7681341171265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9570503234863</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">11.1631383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.060094833374</t>
+    <t xml:space="preserve">11.0600938796997</t>
   </si>
   <si>
     <t xml:space="preserve">11.1803131103516</t>
@@ -2834,22 +2834,22 @@
     <t xml:space="preserve">10.9742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.991397857666</t>
+    <t xml:space="preserve">10.9913988113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.0296506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0124769210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.390305519104</t>
+    <t xml:space="preserve">10.0124759674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3903064727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1498689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1326942443848</t>
+    <t xml:space="preserve">10.1326951980591</t>
   </si>
   <si>
     <t xml:space="preserve">9.97812843322754</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">10.2872610092163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2013921737671</t>
+    <t xml:space="preserve">10.2013912200928</t>
   </si>
   <si>
     <t xml:space="preserve">10.3044357299805</t>
@@ -2876,31 +2876,31 @@
     <t xml:space="preserve">10.0468244552612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5620470046997</t>
+    <t xml:space="preserve">10.5620460510254</t>
   </si>
   <si>
     <t xml:space="preserve">10.6307430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4246530532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7166128158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.459002494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5105237960815</t>
+    <t xml:space="preserve">10.424654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4418287277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5105228424072</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509613037109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6822633743286</t>
+    <t xml:space="preserve">10.6822643280029</t>
   </si>
   <si>
     <t xml:space="preserve">10.493350982666</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">9.25681781768799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46290683746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0850772857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54877758026123</t>
+    <t xml:space="preserve">9.4629077911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08507633209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54877662658691</t>
   </si>
   <si>
     <t xml:space="preserve">9.56595039367676</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">9.65182113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82356071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3387832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5963945388794</t>
+    <t xml:space="preserve">9.823561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3387842178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5963954925537</t>
   </si>
   <si>
     <t xml:space="preserve">10.8540058135986</t>
@@ -2984,25 +2984,25 @@
     <t xml:space="preserve">11.2661828994751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0429191589355</t>
+    <t xml:space="preserve">11.0429201126099</t>
   </si>
   <si>
     <t xml:space="preserve">10.8883543014526</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9398746490479</t>
+    <t xml:space="preserve">10.9398756027222</t>
   </si>
   <si>
     <t xml:space="preserve">10.8196573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8024835586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3692264556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4379224777222</t>
+    <t xml:space="preserve">10.8024826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3692274093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4379234313965</t>
   </si>
   <si>
     <t xml:space="preserve">12.0733642578125</t>
@@ -3014,13 +3014,13 @@
     <t xml:space="preserve">12.5027151107788</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2966260910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.056188583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7470569610596</t>
+    <t xml:space="preserve">12.2966251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0561895370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7470560073853</t>
   </si>
   <si>
     <t xml:space="preserve">11.7127084732056</t>
@@ -3029,31 +3029,31 @@
     <t xml:space="preserve">11.9703187942505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9359703063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0046672821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0218410491943</t>
+    <t xml:space="preserve">11.9359712600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0046663284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0218420028687</t>
   </si>
   <si>
     <t xml:space="preserve">11.8157529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2279300689697</t>
+    <t xml:space="preserve">12.227931022644</t>
   </si>
   <si>
     <t xml:space="preserve">12.3653221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4340190887451</t>
+    <t xml:space="preserve">12.4340181350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.3996696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3137998580933</t>
+    <t xml:space="preserve">12.3138008117676</t>
   </si>
   <si>
     <t xml:space="preserve">12.519889831543</t>
@@ -3062,13 +3062,13 @@
     <t xml:space="preserve">12.485541343689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6401071548462</t>
+    <t xml:space="preserve">12.6401081085205</t>
   </si>
   <si>
     <t xml:space="preserve">12.2451038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2794523239136</t>
+    <t xml:space="preserve">12.2794532775879</t>
   </si>
   <si>
     <t xml:space="preserve">12.1420593261719</t>
@@ -3095,40 +3095,40 @@
     <t xml:space="preserve">12.9148921966553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0694589614868</t>
+    <t xml:space="preserve">13.0694599151611</t>
   </si>
   <si>
     <t xml:space="preserve">13.1038074493408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.086633682251</t>
+    <t xml:space="preserve">13.0866327285767</t>
   </si>
   <si>
     <t xml:space="preserve">13.1896772384644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6705513000488</t>
+    <t xml:space="preserve">13.6705503463745</t>
   </si>
   <si>
     <t xml:space="preserve">13.3442440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6362037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6018543243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.550332069397</t>
+    <t xml:space="preserve">13.6362028121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6018552780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5503330230713</t>
   </si>
   <si>
     <t xml:space="preserve">13.5675067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4644632339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3957653045654</t>
+    <t xml:space="preserve">13.4644622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3957672119141</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159845352173</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">13.6190280914307</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0827283859253</t>
+    <t xml:space="preserve">14.082727432251</t>
   </si>
   <si>
     <t xml:space="preserve">13.6877250671387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7048988342285</t>
+    <t xml:space="preserve">13.7048997879028</t>
   </si>
   <si>
     <t xml:space="preserve">13.7220726013184</t>
@@ -3155,22 +3155,22 @@
     <t xml:space="preserve">14.6151247024536</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7353429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.649471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8040399551392</t>
+    <t xml:space="preserve">14.7353420257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6494731903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8040390014648</t>
   </si>
   <si>
     <t xml:space="preserve">14.6838207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.786865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7181692123413</t>
+    <t xml:space="preserve">14.7868633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7181673049927</t>
   </si>
   <si>
     <t xml:space="preserve">15.0101270675659</t>
@@ -3179,25 +3179,25 @@
     <t xml:space="preserve">15.0616502761841</t>
   </si>
   <si>
-    <t xml:space="preserve">15.387957572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1990442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2505664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818685531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.216215133667</t>
+    <t xml:space="preserve">15.3879566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2505645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2162160873413</t>
   </si>
   <si>
     <t xml:space="preserve">14.9757795333862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9242572784424</t>
+    <t xml:space="preserve">14.9242563247681</t>
   </si>
   <si>
     <t xml:space="preserve">14.4262084960938</t>
@@ -3212,34 +3212,34 @@
     <t xml:space="preserve">14.5464286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1131725311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1303462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9929533004761</t>
+    <t xml:space="preserve">15.1131715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1303472518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9929523468018</t>
   </si>
   <si>
     <t xml:space="preserve">15.2677392959595</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4223041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9031801223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9375267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1436138153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.851655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547004699707</t>
+    <t xml:space="preserve">15.4223051071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9031782150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9375276565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1436157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8516550064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9546995162964</t>
   </si>
   <si>
     <t xml:space="preserve">15.7829599380493</t>
@@ -3248,22 +3248,22 @@
     <t xml:space="preserve">15.7142639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5253486633301</t>
+    <t xml:space="preserve">15.5253496170044</t>
   </si>
   <si>
     <t xml:space="preserve">15.5596981048584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8383874893188</t>
+    <t xml:space="preserve">14.8383884429932</t>
   </si>
   <si>
     <t xml:space="preserve">14.4605579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3059902191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2888174057007</t>
+    <t xml:space="preserve">14.3059921264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2888164520264</t>
   </si>
   <si>
     <t xml:space="preserve">14.5120792388916</t>
@@ -3272,22 +3272,22 @@
     <t xml:space="preserve">14.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7009954452515</t>
+    <t xml:space="preserve">14.7009963989258</t>
   </si>
   <si>
     <t xml:space="preserve">14.5807752609253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5292549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3746871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1431255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2678136825562</t>
+    <t xml:space="preserve">14.5292539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3746862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1431245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2678127288818</t>
   </si>
   <si>
     <t xml:space="preserve">14.321249961853</t>
@@ -3299,10 +3299,10 @@
     <t xml:space="preserve">14.6774997711182</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6062498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0540618896484</t>
+    <t xml:space="preserve">14.6062488555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0540628433228</t>
   </si>
   <si>
     <t xml:space="preserve">14.0362501144409</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">14.0184373855591</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0006256103516</t>
+    <t xml:space="preserve">14.0006246566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.733437538147</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">13.875937461853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2856254577637</t>
+    <t xml:space="preserve">14.285626411438</t>
   </si>
   <si>
     <t xml:space="preserve">14.0896873474121</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">14.1609373092651</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1253118515015</t>
+    <t xml:space="preserve">14.1253128051758</t>
   </si>
   <si>
     <t xml:space="preserve">14.4459371566772</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">14.178750038147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9828119277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9293756484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6978130340576</t>
+    <t xml:space="preserve">13.9828128814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9293746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6978120803833</t>
   </si>
   <si>
     <t xml:space="preserve">13.6799993515015</t>
@@ -3365,16 +3365,16 @@
     <t xml:space="preserve">13.5731248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8403129577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8581247329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9115629196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4840621948242</t>
+    <t xml:space="preserve">13.8403120040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8581256866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9115619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4840631484985</t>
   </si>
   <si>
     <t xml:space="preserve">13.1278123855591</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">13.8046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7690629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8225002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3034372329712</t>
+    <t xml:space="preserve">13.7690620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8225011825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3034362792969</t>
   </si>
   <si>
     <t xml:space="preserve">14.3924999237061</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">14.624062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4993753433228</t>
+    <t xml:space="preserve">14.4993762969971</t>
   </si>
   <si>
     <t xml:space="preserve">14.5349998474121</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">14.25</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0718755722046</t>
+    <t xml:space="preserve">14.0718746185303</t>
   </si>
   <si>
     <t xml:space="preserve">13.359375</t>
@@ -3428,22 +3428,22 @@
     <t xml:space="preserve">13.5018749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5196876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2321863174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6265630722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812496185303</t>
+    <t xml:space="preserve">13.5196886062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2321872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6265621185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812505722046</t>
   </si>
   <si>
     <t xml:space="preserve">13.0565624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1099996566772</t>
+    <t xml:space="preserve">13.1100006103516</t>
   </si>
   <si>
     <t xml:space="preserve">12.842812538147</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">12.8249998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7181253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221881866455</t>
+    <t xml:space="preserve">12.7181243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221872329712</t>
   </si>
   <si>
     <t xml:space="preserve">12.397500038147</t>
@@ -3476,25 +3476,25 @@
     <t xml:space="preserve">12.4865627288818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2906255722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2193756103516</t>
+    <t xml:space="preserve">12.2906246185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2193746566772</t>
   </si>
   <si>
     <t xml:space="preserve">12.2550001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1481256484985</t>
+    <t xml:space="preserve">12.1481246948242</t>
   </si>
   <si>
     <t xml:space="preserve">12.1659374237061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1303119659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165630340576</t>
+    <t xml:space="preserve">12.1303129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165620803833</t>
   </si>
   <si>
     <t xml:space="preserve">11.578125</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">11.3287506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2931261062622</t>
+    <t xml:space="preserve">11.2931251525879</t>
   </si>
   <si>
     <t xml:space="preserve">11.1328125</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">10.9012498855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9190635681152</t>
+    <t xml:space="preserve">10.9190626144409</t>
   </si>
   <si>
     <t xml:space="preserve">11.061562538147</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">11.0971879959106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1684379577637</t>
+    <t xml:space="preserve">11.1684370040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.204062461853</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">11.4534368515015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8631238937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0768756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453130722046</t>
+    <t xml:space="preserve">11.8631248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0768747329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453121185303</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809375762939</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">11.9878120422363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2015619277954</t>
+    <t xml:space="preserve">12.2015628814697</t>
   </si>
   <si>
     <t xml:space="preserve">12.6468753814697</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">12.7003126144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3618745803833</t>
+    <t xml:space="preserve">12.3618755340576</t>
   </si>
   <si>
     <t xml:space="preserve">12.3440628051758</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">12.094687461853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0590620040894</t>
+    <t xml:space="preserve">12.0590629577637</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056247711182</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">11.4178123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4356250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7384376525879</t>
+    <t xml:space="preserve">11.4356260299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7384386062622</t>
   </si>
   <si>
     <t xml:space="preserve">11.7562494277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5959386825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274993896484</t>
+    <t xml:space="preserve">11.5959377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8275003433228</t>
   </si>
   <si>
     <t xml:space="preserve">11.7206249237061</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">11.2396869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5425004959106</t>
+    <t xml:space="preserve">11.5424995422363</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028131484985</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">11.9700002670288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5246877670288</t>
+    <t xml:space="preserve">11.5246868133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.9724998474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1149988174438</t>
+    <t xml:space="preserve">11.1149997711182</t>
   </si>
   <si>
     <t xml:space="preserve">11.3382139205933</t>
@@ -4428,6 +4428,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.21999979019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23000001907349</t>
   </si>
 </sst>
 </file>
@@ -70286,7 +70289,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6911689815</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>52716</v>
@@ -70307,6 +70310,32 @@
         <v>1471</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.6910300926</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>35280</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>7.28999996185303</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>7.17000007629395</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>7.28999996185303</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>7.23000001907349</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>1472</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="1476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="1477">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,100 +47,100 @@
     <t xml:space="preserve">4.02447938919067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93978953361511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82799816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78057146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943212509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75685834884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74330806732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8008975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040839195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571829795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66539263725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5637640953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65184259414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72637033462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70265698432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65861773490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69249320030212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74669575691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5976414680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59086537361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58408975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49601197242737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46213674545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51633810997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38760924339294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40793442726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50956225395203</t>
+    <t xml:space="preserve">3.93978977203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82799768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7805712223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943117141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7568576335907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74330759048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80089688301086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040910720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66539239883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56376433372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65184235572815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72636985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70265626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6586172580719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74669551849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5976402759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59086585044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5840904712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49601149559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4621365070343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51633763313293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38760948181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40793490409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50956296920776</t>
   </si>
   <si>
     <t xml:space="preserve">3.55698943138123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56715178489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57731556892395</t>
+    <t xml:space="preserve">3.56715250015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61119103431702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57731509208679</t>
   </si>
   <si>
     <t xml:space="preserve">3.54682660102844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52650117874146</t>
+    <t xml:space="preserve">3.52650046348572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50278782844543</t>
@@ -149,238 +149,238 @@
     <t xml:space="preserve">3.5603768825531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58070254325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60102868080139</t>
+    <t xml:space="preserve">3.58070302009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60102796554565</t>
   </si>
   <si>
     <t xml:space="preserve">3.54343891143799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57053971290588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64506673812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78734660148621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84154868125916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8652617931366</t>
+    <t xml:space="preserve">3.57053923606873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64506697654724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78734636306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84154796600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86526083946228</t>
   </si>
   <si>
     <t xml:space="preserve">3.85171127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92962646484375</t>
+    <t xml:space="preserve">3.92962622642517</t>
   </si>
   <si>
     <t xml:space="preserve">3.93640160560608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91607546806335</t>
+    <t xml:space="preserve">3.9160749912262</t>
   </si>
   <si>
     <t xml:space="preserve">3.90252542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89575052261353</t>
+    <t xml:space="preserve">3.8957507610321</t>
   </si>
   <si>
     <t xml:space="preserve">3.92285108566284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9093005657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97027802467346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87881135940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85848641395569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94317746162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89913749694824</t>
+    <t xml:space="preserve">3.90930080413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9702775478363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8788115978241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85848665237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94317626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8991379737854</t>
   </si>
   <si>
     <t xml:space="preserve">3.94656443595886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95672702789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96350264549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91268801689148</t>
+    <t xml:space="preserve">3.9567277431488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96350240707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91268873214722</t>
   </si>
   <si>
     <t xml:space="preserve">3.9736647605896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91946291923523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87203669548035</t>
+    <t xml:space="preserve">3.91946339607239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87203741073608</t>
   </si>
   <si>
     <t xml:space="preserve">3.88704800605774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87291288375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85877871513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83757662773132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86231231689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87644672393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89411497116089</t>
+    <t xml:space="preserve">3.87291312217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85877799987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8375768661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86231207847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87644791603088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89411544799805</t>
   </si>
   <si>
     <t xml:space="preserve">3.9011824131012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89058184623718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94358706474304</t>
+    <t xml:space="preserve">3.89058232307434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94358658790588</t>
   </si>
   <si>
     <t xml:space="preserve">3.95418763160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96125555038452</t>
+    <t xml:space="preserve">3.96125507354736</t>
   </si>
   <si>
     <t xml:space="preserve">4.01426076889038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02486133575439</t>
+    <t xml:space="preserve">4.02486181259155</t>
   </si>
   <si>
     <t xml:space="preserve">4.08846759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05666446685791</t>
+    <t xml:space="preserve">4.05666399002075</t>
   </si>
   <si>
     <t xml:space="preserve">4.03899669647217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99305820465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00719308853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9753897190094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97185611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80223965644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78103756904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75630187988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74923372268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90471696853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9223849773407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065450668335</t>
+    <t xml:space="preserve">3.9930579662323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00719261169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97539043426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97185659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80223941802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78103709220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75630164146423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7492344379425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90471625328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92238569259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065379142761</t>
   </si>
   <si>
     <t xml:space="preserve">4.03546237945557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75983548164368</t>
+    <t xml:space="preserve">3.75983595848083</t>
   </si>
   <si>
     <t xml:space="preserve">3.80930709838867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83050918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86937975883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82344174385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80577301979065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84111022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8517107963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81637454032898</t>
+    <t xml:space="preserve">3.83050870895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8693790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82344126701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80577325820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84110975265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85171103477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81637406349182</t>
   </si>
   <si>
     <t xml:space="preserve">3.8658459186554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89764881134033</t>
+    <t xml:space="preserve">3.89764928817749</t>
   </si>
   <si>
     <t xml:space="preserve">3.93651962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90825057029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91531705856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97892355918884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00012588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02132701873779</t>
+    <t xml:space="preserve">3.90825033187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91531777381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97892451286316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00012540817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02132749557495</t>
   </si>
   <si>
     <t xml:space="preserve">3.95772123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84464335441589</t>
+    <t xml:space="preserve">3.84464383125305</t>
   </si>
   <si>
     <t xml:space="preserve">3.81284070014954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77043652534485</t>
+    <t xml:space="preserve">3.77043628692627</t>
   </si>
   <si>
     <t xml:space="preserve">3.76690292358398</t>
@@ -389,31 +389,31 @@
     <t xml:space="preserve">3.76336884498596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74570107460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7244987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77396988868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78810453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81990766525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72803235054016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73863339424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73156666755676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73510003089905</t>
+    <t xml:space="preserve">3.7457013130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72449827194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77397036552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78810524940491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81990790367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72803258895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73863363265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7315661907196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73510026931763</t>
   </si>
   <si>
     <t xml:space="preserve">3.65382528305054</t>
@@ -422,73 +422,73 @@
     <t xml:space="preserve">3.63969039916992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66089224815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.618488073349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61142086982727</t>
+    <t xml:space="preserve">3.66089272499084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61848783493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61142110824585</t>
   </si>
   <si>
     <t xml:space="preserve">3.62555575370789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61495471000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64675807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74216651916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91885137557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98599171638489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99659180641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87998080253601</t>
+    <t xml:space="preserve">3.61495447158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64675688743591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74216675758362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91885042190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98599052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99659204483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87998008728027</t>
   </si>
   <si>
     <t xml:space="preserve">3.88351392745972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79517245292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82697582244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79163861274719</t>
+    <t xml:space="preserve">3.79517197608948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82697606086731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79163813591003</t>
   </si>
   <si>
     <t xml:space="preserve">3.8481776714325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71036386489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85524487495422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03192949295044</t>
+    <t xml:space="preserve">3.71036410331726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85524463653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03192806243896</t>
   </si>
   <si>
     <t xml:space="preserve">4.04253005981445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08493375778198</t>
+    <t xml:space="preserve">4.08493328094482</t>
   </si>
   <si>
     <t xml:space="preserve">4.0990686416626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05313014984131</t>
+    <t xml:space="preserve">4.05313158035278</t>
   </si>
   <si>
     <t xml:space="preserve">4.04959726333618</t>
@@ -497,58 +497,58 @@
     <t xml:space="preserve">4.09200143814087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10966968536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07786655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07433319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04606342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0637321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10613584518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1026029586792</t>
+    <t xml:space="preserve">4.10967063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07786703109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07433271408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04606294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06373262405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10613632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10260200500488</t>
   </si>
   <si>
     <t xml:space="preserve">4.13440561294556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12733793258667</t>
+    <t xml:space="preserve">4.12733888626099</t>
   </si>
   <si>
     <t xml:space="preserve">4.16974258422852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18387699127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15914154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24041604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21568012237549</t>
+    <t xml:space="preserve">4.18387746810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1591420173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24041557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21568059921265</t>
   </si>
   <si>
     <t xml:space="preserve">4.27575302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34642601013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36762857437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35349369049072</t>
+    <t xml:space="preserve">4.34642696380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36762809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35349321365356</t>
   </si>
   <si>
     <t xml:space="preserve">4.31108951568604</t>
@@ -560,37 +560,37 @@
     <t xml:space="preserve">4.38176298141479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5089750289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72806406021118</t>
+    <t xml:space="preserve">4.50897598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72806358337402</t>
   </si>
   <si>
     <t xml:space="preserve">4.91181516647339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94715213775635</t>
+    <t xml:space="preserve">4.94715166091919</t>
   </si>
   <si>
     <t xml:space="preserve">5.19450950622559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22277975082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22984600067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22631216049194</t>
+    <t xml:space="preserve">5.2227783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22984647750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2263126373291</t>
   </si>
   <si>
     <t xml:space="preserve">5.09203243255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07436466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08496570587158</t>
+    <t xml:space="preserve">5.07436418533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08496522903442</t>
   </si>
   <si>
     <t xml:space="preserve">5.1167688369751</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">5.13090324401855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24751472473145</t>
+    <t xml:space="preserve">5.24751424789429</t>
   </si>
   <si>
     <t xml:space="preserve">5.26871728897095</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">5.59734869003296</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51254081726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35705900192261</t>
+    <t xml:space="preserve">5.51254034042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35705852508545</t>
   </si>
   <si>
     <t xml:space="preserve">5.47720384597778</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">5.44186735153198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53020906448364</t>
+    <t xml:space="preserve">5.5302095413208</t>
   </si>
   <si>
     <t xml:space="preserve">5.61199760437012</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">5.65216159820557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68867349624634</t>
+    <t xml:space="preserve">5.68867444992065</t>
   </si>
   <si>
     <t xml:space="preserve">5.6229510307312</t>
@@ -665,16 +665,16 @@
     <t xml:space="preserve">5.42213153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41847991943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5535774230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56087875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49880838394165</t>
+    <t xml:space="preserve">5.41848039627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55357789993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56087923049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49880790710449</t>
   </si>
   <si>
     <t xml:space="preserve">5.46229553222656</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">5.55722856521606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45499277114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3673620223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37466526031494</t>
+    <t xml:space="preserve">5.45499324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36736249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37466478347778</t>
   </si>
   <si>
     <t xml:space="preserve">5.43308544158936</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">5.40387535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47690057754517</t>
+    <t xml:space="preserve">5.47690010070801</t>
   </si>
   <si>
     <t xml:space="preserve">5.44769048690796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48055171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49515676498413</t>
+    <t xml:space="preserve">5.48055124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49515724182129</t>
   </si>
   <si>
     <t xml:space="preserve">5.54627466201782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60104370117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41117715835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5134129524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54992628097534</t>
+    <t xml:space="preserve">5.60104274749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41117763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51341342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54992532730103</t>
   </si>
   <si>
     <t xml:space="preserve">5.45134162902832</t>
@@ -734,46 +734,46 @@
     <t xml:space="preserve">5.50611066818237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34545421600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37101459503174</t>
+    <t xml:space="preserve">5.34545516967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37101364135742</t>
   </si>
   <si>
     <t xml:space="preserve">5.31259346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28703451156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15558958053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12637901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27242946624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31989622116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14098358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40752601623535</t>
+    <t xml:space="preserve">5.287034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15558910369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12637853622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2724289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31989526748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14098453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40752649307251</t>
   </si>
   <si>
     <t xml:space="preserve">5.38926982879639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37831544876099</t>
+    <t xml:space="preserve">5.37831592559814</t>
   </si>
   <si>
     <t xml:space="preserve">5.24321937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46959829330444</t>
+    <t xml:space="preserve">5.46959781646729</t>
   </si>
   <si>
     <t xml:space="preserve">5.41482925415039</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">5.42578268051147</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44038772583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48420333862305</t>
+    <t xml:space="preserve">5.44038724899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48420381546021</t>
   </si>
   <si>
     <t xml:space="preserve">5.35275745391846</t>
@@ -797,94 +797,94 @@
     <t xml:space="preserve">5.50245904922485</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57183408737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57913589477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56453037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52071523666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53897190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65581274032593</t>
+    <t xml:space="preserve">5.57183313369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57913637161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56453084945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52071571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5389723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65581226348877</t>
   </si>
   <si>
     <t xml:space="preserve">5.58643817901611</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57548522949219</t>
+    <t xml:space="preserve">5.57548427581787</t>
   </si>
   <si>
     <t xml:space="preserve">5.50976181030273</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53166961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60469484329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59009027481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75804805755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79456090927124</t>
+    <t xml:space="preserve">5.5316686630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60469532012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59008979797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75804853439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79455995559692</t>
   </si>
   <si>
     <t xml:space="preserve">5.92965745925903</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94426345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99903154373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9369592666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98807764053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83107328414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88584280014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83472490310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95886707305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76900196075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91140127182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83837604522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84202671051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87123727798462</t>
+    <t xml:space="preserve">5.94426298141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99903202056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93695974349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98807716369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83107376098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88584232330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83472442626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9588680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76900148391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83837556838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84202766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87123775482178</t>
   </si>
   <si>
     <t xml:space="preserve">5.78360652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85298109054565</t>
+    <t xml:space="preserve">5.8529806137085</t>
   </si>
   <si>
     <t xml:space="preserve">5.70327949523926</t>
@@ -896,82 +896,82 @@
     <t xml:space="preserve">5.86393451690674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75439691543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72883796691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68502283096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66676664352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88949298858643</t>
+    <t xml:space="preserve">5.75439643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72883749008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68502187728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66676616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88949346542358</t>
   </si>
   <si>
     <t xml:space="preserve">5.78725862503052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77995586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73614025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60834550857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63025379180908</t>
+    <t xml:space="preserve">5.77995538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73614072799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60834646224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63025331497192</t>
   </si>
   <si>
     <t xml:space="preserve">5.53532075881958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76169872283936</t>
+    <t xml:space="preserve">5.76169967651367</t>
   </si>
   <si>
     <t xml:space="preserve">5.62660217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68137216567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73979139328003</t>
+    <t xml:space="preserve">5.68137168884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73979187011719</t>
   </si>
   <si>
     <t xml:space="preserve">5.76535129547119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80916595458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80551433563232</t>
+    <t xml:space="preserve">5.80916547775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80551481246948</t>
   </si>
   <si>
     <t xml:space="preserve">5.82377004623413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87854051589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82011890411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90409803390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92235517501831</t>
+    <t xml:space="preserve">5.87853956222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82011938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90409851074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92235469818115</t>
   </si>
   <si>
     <t xml:space="preserve">5.95156478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02459049224854</t>
+    <t xml:space="preserve">6.02459096908569</t>
   </si>
   <si>
     <t xml:space="preserve">6.06110334396362</t>
@@ -980,64 +980,64 @@
     <t xml:space="preserve">6.00998544692993</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09031391143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22906160354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18524599075317</t>
+    <t xml:space="preserve">6.09031343460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22906112670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18524646759033</t>
   </si>
   <si>
     <t xml:space="preserve">6.03189325332642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03919506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04649829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25096893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2071533203125</t>
+    <t xml:space="preserve">6.0391960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04649782180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25096988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20715427398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.14143085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12682628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79821157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72518682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96617078781128</t>
+    <t xml:space="preserve">6.1268253326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79821252822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72518587112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96617031097412</t>
   </si>
   <si>
     <t xml:space="preserve">6.00268316268921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8931450843811</t>
+    <t xml:space="preserve">5.89314460754395</t>
   </si>
   <si>
     <t xml:space="preserve">5.84932994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.973473072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99538087844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11952304840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15603590011597</t>
+    <t xml:space="preserve">5.97347259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99538040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11952352523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15603637695312</t>
   </si>
   <si>
     <t xml:space="preserve">6.10491800308228</t>
@@ -1049,22 +1049,22 @@
     <t xml:space="preserve">5.90044784545898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14873361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09761619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0538010597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07570886611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08301019668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17794466018677</t>
+    <t xml:space="preserve">6.1487340927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09761571884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05380153656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07570743560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08301115036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17794418334961</t>
   </si>
   <si>
     <t xml:space="preserve">6.17064046859741</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">6.28017950057983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38636541366577</t>
+    <t xml:space="preserve">6.38636589050293</t>
   </si>
   <si>
     <t xml:space="preserve">6.31810283660889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23467063903809</t>
+    <t xml:space="preserve">6.23467111587524</t>
   </si>
   <si>
     <t xml:space="preserve">6.28017854690552</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">6.27259492874146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26500988006592</t>
+    <t xml:space="preserve">6.26500940322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.21191549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1815767288208</t>
+    <t xml:space="preserve">6.18157720565796</t>
   </si>
   <si>
     <t xml:space="preserve">6.15123796463013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02988147735596</t>
+    <t xml:space="preserve">6.02988195419312</t>
   </si>
   <si>
     <t xml:space="preserve">6.05263614654541</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">6.249840259552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29534912109375</t>
+    <t xml:space="preserve">6.29534864425659</t>
   </si>
   <si>
     <t xml:space="preserve">6.37119579315186</t>
@@ -1133,43 +1133,43 @@
     <t xml:space="preserve">6.16640758514404</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2043309211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0147123336792</t>
+    <t xml:space="preserve">6.20433187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01471281051636</t>
   </si>
   <si>
     <t xml:space="preserve">6.04505157470703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0071268081665</t>
+    <t xml:space="preserve">6.00712776184082</t>
   </si>
   <si>
     <t xml:space="preserve">5.98437309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12089872360229</t>
+    <t xml:space="preserve">6.12089824676514</t>
   </si>
   <si>
     <t xml:space="preserve">6.13606834411621</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11331462860107</t>
+    <t xml:space="preserve">6.11331510543823</t>
   </si>
   <si>
     <t xml:space="preserve">6.09055948257446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96161890029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0829758644104</t>
+    <t xml:space="preserve">5.96161937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08297538757324</t>
   </si>
   <si>
     <t xml:space="preserve">6.14365339279175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10572957992554</t>
+    <t xml:space="preserve">6.1057300567627</t>
   </si>
   <si>
     <t xml:space="preserve">6.06022119522095</t>
@@ -1178,28 +1178,28 @@
     <t xml:space="preserve">5.99954271316528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95403480529785</t>
+    <t xml:space="preserve">5.95403432846069</t>
   </si>
   <si>
     <t xml:space="preserve">5.93886470794678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06780576705933</t>
+    <t xml:space="preserve">6.06780624389648</t>
   </si>
   <si>
     <t xml:space="preserve">5.91611099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94645023345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818670272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746700286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02229690551758</t>
+    <t xml:space="preserve">5.94644927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818717956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746652603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02229785919189</t>
   </si>
   <si>
     <t xml:space="preserve">5.9919581413269</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">5.86301708221436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07539033889771</t>
+    <t xml:space="preserve">6.07539081573486</t>
   </si>
   <si>
     <t xml:space="preserve">6.24225521087646</t>
@@ -1220,34 +1220,34 @@
     <t xml:space="preserve">6.63666296005249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46221399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57598400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56081485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60632419586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55323123931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65183305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53806066513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48496770858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6139087677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66700124740601</t>
+    <t xml:space="preserve">6.46221446990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57598495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56081438064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60632371902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55323028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65183258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53806018829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48496723175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61390924453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66700220108032</t>
   </si>
   <si>
     <t xml:space="preserve">6.59873914718628</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">6.34085702896118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39395046234131</t>
+    <t xml:space="preserve">6.39395093917847</t>
   </si>
   <si>
     <t xml:space="preserve">6.4167046546936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42429065704346</t>
+    <t xml:space="preserve">6.42428970336914</t>
   </si>
   <si>
     <t xml:space="preserve">6.53047609329224</t>
@@ -1271,34 +1271,34 @@
     <t xml:space="preserve">6.59115314483643</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54564523696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56840038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44704341888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34844160079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21950101852417</t>
+    <t xml:space="preserve">6.54564571380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56839990615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44704389572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3484411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21950054168701</t>
   </si>
   <si>
     <t xml:space="preserve">6.40911960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32568836212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28776407241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6897554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67458629608154</t>
+    <t xml:space="preserve">6.32568788528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28776454925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68975591659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67458581924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.74284934997559</t>
@@ -1310,28 +1310,28 @@
     <t xml:space="preserve">6.62149286270142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37878084182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36361169815063</t>
+    <t xml:space="preserve">6.37878036499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36361074447632</t>
   </si>
   <si>
     <t xml:space="preserve">6.46979808807373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51530647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31051778793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35602712631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19674682617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40153455734253</t>
+    <t xml:space="preserve">6.51530694961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31051731109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3560266494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19674634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40153503417969</t>
   </si>
   <si>
     <t xml:space="preserve">6.72009468078613</t>
@@ -1340,43 +1340,43 @@
     <t xml:space="preserve">6.7580189704895</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80352735519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78835725784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73526525497437</t>
+    <t xml:space="preserve">6.80352783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78835773468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73526382446289</t>
   </si>
   <si>
     <t xml:space="preserve">6.84903526306152</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8642053604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81111192703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84145164489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81869649887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90212917327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9931468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89454507827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94005250930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05382490158081</t>
+    <t xml:space="preserve">6.86420583724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81111240386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84145212173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81869602203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90212869644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99314594268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8945460319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9400520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05382537841797</t>
   </si>
   <si>
     <t xml:space="preserve">7.10691785812378</t>
@@ -1388,25 +1388,25 @@
     <t xml:space="preserve">7.114501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01590061187744</t>
+    <t xml:space="preserve">7.01589918136597</t>
   </si>
   <si>
     <t xml:space="preserve">7.08416366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04623937606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09174728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39513874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35721397399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34204530715942</t>
+    <t xml:space="preserve">7.04623889923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09174823760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39513778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35721492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34204578399658</t>
   </si>
   <si>
     <t xml:space="preserve">7.12208843231201</t>
@@ -1415,28 +1415,28 @@
     <t xml:space="preserve">7.13725614547729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12967157363892</t>
+    <t xml:space="preserve">7.12967205047607</t>
   </si>
   <si>
     <t xml:space="preserve">7.25102806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22827243804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2055196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19793510437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16759586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37996912002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43306255340576</t>
+    <t xml:space="preserve">7.22827386856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20551919937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19793462753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16759538650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37996816635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4330620765686</t>
   </si>
   <si>
     <t xml:space="preserve">7.49374008178711</t>
@@ -1445,22 +1445,22 @@
     <t xml:space="preserve">7.53924798965454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54683303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75162267684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79713010787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64543581008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69094467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57717275619507</t>
+    <t xml:space="preserve">7.54683351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75162172317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79713106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64543533325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69094371795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57717227935791</t>
   </si>
   <si>
     <t xml:space="preserve">7.45581579208374</t>
@@ -1472,34 +1472,34 @@
     <t xml:space="preserve">7.59992647171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50890970230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56200361251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58475637435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55441904067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47857093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47098588943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4482307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7061128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88814783096313</t>
+    <t xml:space="preserve">7.50890922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56200265884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58475732803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55441808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47857046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47098636627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44823169708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70611238479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331697463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88814735412598</t>
   </si>
   <si>
     <t xml:space="preserve">8.25221538543701</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">8.61628437042236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49492645263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17636680603027</t>
+    <t xml:space="preserve">8.49492835998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17636775970459</t>
   </si>
   <si>
     <t xml:space="preserve">8.41908073425293</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">8.1187686920166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08742237091064</t>
+    <t xml:space="preserve">8.08742332458496</t>
   </si>
   <si>
     <t xml:space="preserve">7.93068933486938</t>
@@ -1529,43 +1529,43 @@
     <t xml:space="preserve">8.04040336608887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9620361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25982856750488</t>
+    <t xml:space="preserve">7.96203517913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25982761383057</t>
   </si>
   <si>
     <t xml:space="preserve">8.02472877502441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86799573898315</t>
+    <t xml:space="preserve">7.86799716949463</t>
   </si>
   <si>
     <t xml:space="preserve">7.7347731590271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83664989471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82097578048706</t>
+    <t xml:space="preserve">7.8366494178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8209753036499</t>
   </si>
   <si>
     <t xml:space="preserve">7.91501617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97770929336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07174873352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.056077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85232353210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40088748931885</t>
+    <t xml:space="preserve">7.97771024703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07175064086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05607604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85232305526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40088844299316</t>
   </si>
   <si>
     <t xml:space="preserve">8.46358203887939</t>
@@ -1574,85 +1574,85 @@
     <t xml:space="preserve">8.6203145980835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30684947967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16578960418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33819580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21280765533447</t>
+    <t xml:space="preserve">8.30684852600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1657886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33819675445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21280860900879</t>
   </si>
   <si>
     <t xml:space="preserve">8.27550220489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36954402923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15011596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18146228790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13444328308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22848129272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43223476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9933819770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19713497161865</t>
+    <t xml:space="preserve">8.36954307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15011501312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18146133422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13444137573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22848224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43223667144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99338293075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19713592529297</t>
   </si>
   <si>
     <t xml:space="preserve">7.75828313827515</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89934349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82881355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88366937637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81314039230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6799168586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79746580123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4165620803833</t>
+    <t xml:space="preserve">7.89934301376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82881307601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88367033004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313991546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67991638183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79746627807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41656112670898</t>
   </si>
   <si>
     <t xml:space="preserve">7.80530309677124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68775320053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74261140823364</t>
+    <t xml:space="preserve">7.68775415420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74260997772217</t>
   </si>
   <si>
     <t xml:space="preserve">8.00905609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94636392593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75044679641724</t>
+    <t xml:space="preserve">7.94636297225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75044727325439</t>
   </si>
   <si>
     <t xml:space="preserve">7.71910095214844</t>
@@ -1661,16 +1661,16 @@
     <t xml:space="preserve">8.10309600830078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.372633934021</t>
+    <t xml:space="preserve">8.82406902313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37263298034668</t>
   </si>
   <si>
     <t xml:space="preserve">9.60773277282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48234558105469</t>
+    <t xml:space="preserve">9.482346534729</t>
   </si>
   <si>
     <t xml:space="preserve">9.79581260681152</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">9.9368724822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87417888641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99956607818604</t>
+    <t xml:space="preserve">9.87417984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99956512451172</t>
   </si>
   <si>
     <t xml:space="preserve">10.1562976837158</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">10.5011100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3757238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5481309890747</t>
+    <t xml:space="preserve">10.3757228851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5481300354004</t>
   </si>
   <si>
     <t xml:space="preserve">10.2189903259277</t>
@@ -1706,31 +1706,31 @@
     <t xml:space="preserve">9.95254516601562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90552520751953</t>
+    <t xml:space="preserve">9.90552616119385</t>
   </si>
   <si>
     <t xml:space="preserve">9.88985252380371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92119884490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73311805725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76446533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57638740539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96821784973145</t>
+    <t xml:space="preserve">9.92119789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73311996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76446437835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57638645172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96821975708008</t>
   </si>
   <si>
     <t xml:space="preserve">10.0309114456177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4854364395142</t>
+    <t xml:space="preserve">10.4854373931885</t>
   </si>
   <si>
     <t xml:space="preserve">10.250337600708</t>
@@ -1739,19 +1739,19 @@
     <t xml:space="preserve">10.0152378082275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1249523162842</t>
+    <t xml:space="preserve">10.1249504089355</t>
   </si>
   <si>
     <t xml:space="preserve">10.3600511550903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2973575592041</t>
+    <t xml:space="preserve">10.2973594665527</t>
   </si>
   <si>
     <t xml:space="preserve">10.3130311965942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4384164810181</t>
+    <t xml:space="preserve">10.4384174346924</t>
   </si>
   <si>
     <t xml:space="preserve">10.6264972686768</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">10.5794763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6421699523926</t>
+    <t xml:space="preserve">10.6421709060669</t>
   </si>
   <si>
     <t xml:space="preserve">10.7518835067749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9869832992554</t>
+    <t xml:space="preserve">10.9869823455811</t>
   </si>
   <si>
     <t xml:space="preserve">10.9556360244751</t>
@@ -1787,58 +1787,58 @@
     <t xml:space="preserve">11.0183305740356</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2377548217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593904495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0966949462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1750631332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1123685836792</t>
+    <t xml:space="preserve">11.2377557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1750612258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1123704910278</t>
   </si>
   <si>
     <t xml:space="preserve">11.0810232162476</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9713106155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7989025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622568130493</t>
+    <t xml:space="preserve">10.9713096618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7989044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622587203979</t>
   </si>
   <si>
     <t xml:space="preserve">10.0936040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6860990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29426574707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5450382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98080158233643</t>
+    <t xml:space="preserve">9.68609809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29426670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54503917694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98080062866211</t>
   </si>
   <si>
     <t xml:space="preserve">8.54194831848145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31943130493164</t>
+    <t xml:space="preserve">7.31943082809448</t>
   </si>
   <si>
     <t xml:space="preserve">7.50751066207886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53885746002197</t>
+    <t xml:space="preserve">7.53885698318481</t>
   </si>
   <si>
     <t xml:space="preserve">7.49183750152588</t>
@@ -1847,31 +1847,31 @@
     <t xml:space="preserve">8.66733551025391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44790744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38521480560303</t>
+    <t xml:space="preserve">8.44790840148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38521575927734</t>
   </si>
   <si>
     <t xml:space="preserve">8.52627468109131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01214599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45099925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10618686676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93378067016602</t>
+    <t xml:space="preserve">9.01214694976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45100021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10618782043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">9.38830661773682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88676166534424</t>
+    <t xml:space="preserve">8.88676071166992</t>
   </si>
   <si>
     <t xml:space="preserve">8.87108707427979</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">9.15320777893066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90243434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05916786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04349327087402</t>
+    <t xml:space="preserve">8.90243339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05916690826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04349422454834</t>
   </si>
   <si>
     <t xml:space="preserve">9.21590042114258</t>
@@ -1904,16 +1904,16 @@
     <t xml:space="preserve">9.30298042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12407875061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01022911071777</t>
+    <t xml:space="preserve">9.12407779693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01023006439209</t>
   </si>
   <si>
     <t xml:space="preserve">8.68495178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50604629516602</t>
+    <t xml:space="preserve">8.50604724884033</t>
   </si>
   <si>
     <t xml:space="preserve">8.70121479034424</t>
@@ -1925,16 +1925,16 @@
     <t xml:space="preserve">8.92890930175781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76626968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71747779846191</t>
+    <t xml:space="preserve">8.76627063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71747875213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.97770214080811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33550834655762</t>
+    <t xml:space="preserve">9.33550930023193</t>
   </si>
   <si>
     <t xml:space="preserve">9.48188495635986</t>
@@ -1949,19 +1949,19 @@
     <t xml:space="preserve">10.0673866271973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3113470077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1812334060669</t>
+    <t xml:space="preserve">10.3113460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812343597412</t>
   </si>
   <si>
     <t xml:space="preserve">10.2137632369995</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2788181304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2300252914429</t>
+    <t xml:space="preserve">10.2788190841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2300262451172</t>
   </si>
   <si>
     <t xml:space="preserve">9.95353889465332</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">9.69331550598145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1324424743652</t>
+    <t xml:space="preserve">10.1324415206909</t>
   </si>
   <si>
     <t xml:space="preserve">10.1974973678589</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">10.3276100158691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2462902069092</t>
+    <t xml:space="preserve">10.2462911605835</t>
   </si>
   <si>
     <t xml:space="preserve">10.555305480957</t>
@@ -1994,22 +1994,22 @@
     <t xml:space="preserve">10.8805837631226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8317909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7992649078369</t>
+    <t xml:space="preserve">10.8317918777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7992639541626</t>
   </si>
   <si>
     <t xml:space="preserve">10.9293756484985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6854162216187</t>
+    <t xml:space="preserve">10.6854181289673</t>
   </si>
   <si>
     <t xml:space="preserve">10.6366243362427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7667360305786</t>
+    <t xml:space="preserve">10.7667350769043</t>
   </si>
   <si>
     <t xml:space="preserve">10.9781675338745</t>
@@ -2024,28 +2024,28 @@
     <t xml:space="preserve">11.2871828079224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3847675323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5474052429199</t>
+    <t xml:space="preserve">11.3847665786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5474061965942</t>
   </si>
   <si>
     <t xml:space="preserve">11.4335594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498224258423</t>
+    <t xml:space="preserve">11.4498233795166</t>
   </si>
   <si>
     <t xml:space="preserve">11.4660863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.482349395752</t>
+    <t xml:space="preserve">11.4823503494263</t>
   </si>
   <si>
     <t xml:space="preserve">11.3359746932983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2058629989624</t>
+    <t xml:space="preserve">11.2058639526367</t>
   </si>
   <si>
     <t xml:space="preserve">11.2221269607544</t>
@@ -2054,46 +2054,46 @@
     <t xml:space="preserve">10.8643198013306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.539041519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.522777557373</t>
+    <t xml:space="preserve">10.5390405654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5227766036987</t>
   </si>
   <si>
     <t xml:space="preserve">10.701681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8155288696289</t>
+    <t xml:space="preserve">10.8155279159546</t>
   </si>
   <si>
     <t xml:space="preserve">10.6040964126587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7342081069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6203603744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7179441452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5065135955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.587833404541</t>
+    <t xml:space="preserve">10.7342100143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.620361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7179460525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5065126419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5878343582153</t>
   </si>
   <si>
     <t xml:space="preserve">10.4577207565308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3764028549194</t>
+    <t xml:space="preserve">10.3764019012451</t>
   </si>
   <si>
     <t xml:space="preserve">10.571569442749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089288711548</t>
+    <t xml:space="preserve">10.4089298248291</t>
   </si>
   <si>
     <t xml:space="preserve">10.8968477249146</t>
@@ -2105,10 +2105,10 @@
     <t xml:space="preserve">10.9944324493408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6691522598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7830009460449</t>
+    <t xml:space="preserve">10.669153213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7829990386963</t>
   </si>
   <si>
     <t xml:space="preserve">10.9619035720825</t>
@@ -2117,28 +2117,28 @@
     <t xml:space="preserve">10.9456396102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2709178924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1895999908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5799350738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4172954559326</t>
+    <t xml:space="preserve">11.2709188461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1895990371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5799341201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4172945022583</t>
   </si>
   <si>
     <t xml:space="preserve">11.3034467697144</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9860668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0836496353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4414558410645</t>
+    <t xml:space="preserve">9.98606586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0836505889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4414577484131</t>
   </si>
   <si>
     <t xml:space="preserve">10.7504730224609</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">11.2546548843384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3522396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4010314941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3197107315063</t>
+    <t xml:space="preserve">11.3522386550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4010305404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3197116851807</t>
   </si>
   <si>
     <t xml:space="preserve">11.1733350753784</t>
@@ -2174,25 +2174,25 @@
     <t xml:space="preserve">11.0106954574585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5311422348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7751016616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7100448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7425737380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.019061088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3118124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5882978439331</t>
+    <t xml:space="preserve">11.5311431884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7751007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7100439071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7425727844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0190601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3118133544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5882987976074</t>
   </si>
   <si>
     <t xml:space="preserve">12.1979637145996</t>
@@ -2204,49 +2204,49 @@
     <t xml:space="preserve">12.00279712677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8076295852661</t>
+    <t xml:space="preserve">11.8076305389404</t>
   </si>
   <si>
     <t xml:space="preserve">11.8564214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5961990356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.954005241394</t>
+    <t xml:space="preserve">11.5961971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9540042877197</t>
   </si>
   <si>
     <t xml:space="preserve">11.9865322113037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1003799438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1817007064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.116644859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2792844772339</t>
+    <t xml:space="preserve">12.100380897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1816997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1166439056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2792854309082</t>
   </si>
   <si>
     <t xml:space="preserve">12.4093961715698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5069799423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4581880569458</t>
+    <t xml:space="preserve">12.5069789886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4581871032715</t>
   </si>
   <si>
     <t xml:space="preserve">12.4907150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8973140716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0111618041992</t>
+    <t xml:space="preserve">12.8973150253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0111627578735</t>
   </si>
   <si>
     <t xml:space="preserve">12.9786338806152</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">12.7997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6370906829834</t>
+    <t xml:space="preserve">12.6370916366577</t>
   </si>
   <si>
     <t xml:space="preserve">12.8810501098633</t>
@@ -2273,25 +2273,25 @@
     <t xml:space="preserve">13.3527050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7267742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8243579864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.052056312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2309579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2634878158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.214693069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9056797027588</t>
+    <t xml:space="preserve">13.7267761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8243598937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0520553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2309589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634868621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2146940231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9056787490845</t>
   </si>
   <si>
     <t xml:space="preserve">13.6129274368286</t>
@@ -2300,22 +2300,22 @@
     <t xml:space="preserve">13.8080949783325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8894166946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6454563140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406229019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918300628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0032615661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9544715881348</t>
+    <t xml:space="preserve">13.8894157409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6454553604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406248092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918310165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0032625198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9544706344604</t>
   </si>
   <si>
     <t xml:space="preserve">14.3448057174683</t>
@@ -2324,43 +2324,43 @@
     <t xml:space="preserve">14.1496391296387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2472229003906</t>
+    <t xml:space="preserve">14.2472219467163</t>
   </si>
   <si>
     <t xml:space="preserve">14.4749174118042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5579166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1927223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1595220565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1429252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2757215499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2923202514648</t>
+    <t xml:space="preserve">14.557915687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.192723274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1595239639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1429243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2757225036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2923192977905</t>
   </si>
   <si>
     <t xml:space="preserve">14.375319480896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1097240447998</t>
+    <t xml:space="preserve">14.1097249984741</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425212860107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0765237808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2093229293823</t>
+    <t xml:space="preserve">14.0765247344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2093238830566</t>
   </si>
   <si>
     <t xml:space="preserve">13.9935264587402</t>
@@ -2369,22 +2369,22 @@
     <t xml:space="preserve">13.8109292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3089199066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0599269866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0101251602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9769277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.043327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3255186080933</t>
+    <t xml:space="preserve">14.3089208602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.05992603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0101261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9769268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0433254241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3255205154419</t>
   </si>
   <si>
     <t xml:space="preserve">14.2259206771851</t>
@@ -2396,67 +2396,67 @@
     <t xml:space="preserve">14.1761226654053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9437274932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0931243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9603281021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3587188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591218948364</t>
+    <t xml:space="preserve">13.9437265396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0931234359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9603271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.358717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591228485107</t>
   </si>
   <si>
     <t xml:space="preserve">14.5081157684326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.524715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0267248153687</t>
+    <t xml:space="preserve">14.5247173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.026725769043</t>
   </si>
   <si>
     <t xml:space="preserve">14.7073125839233</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7737102508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.690712928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7405138015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9397077560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1057043075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3214998245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1721048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8899097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3713006973267</t>
+    <t xml:space="preserve">14.7737112045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6907138824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7405118942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9397087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1057052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3214988708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1721029281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.889910697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.371298789978</t>
   </si>
   <si>
     <t xml:space="preserve">15.703293800354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5372972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.387900352478</t>
+    <t xml:space="preserve">15.537296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3878993988037</t>
   </si>
   <si>
     <t xml:space="preserve">15.2883014678955</t>
@@ -2468,22 +2468,22 @@
     <t xml:space="preserve">15.0725059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2219018936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1223030090332</t>
+    <t xml:space="preserve">15.22190284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1223039627075</t>
   </si>
   <si>
     <t xml:space="preserve">14.9895067214966</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8567094802856</t>
+    <t xml:space="preserve">14.8567085266113</t>
   </si>
   <si>
     <t xml:space="preserve">14.8235111236572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7903108596802</t>
+    <t xml:space="preserve">14.7903099060059</t>
   </si>
   <si>
     <t xml:space="preserve">15.1389045715332</t>
@@ -2492,70 +2492,70 @@
     <t xml:space="preserve">14.9729080200195</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8733100891113</t>
+    <t xml:space="preserve">14.873309135437</t>
   </si>
   <si>
     <t xml:space="preserve">14.8069105148315</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8607301712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6947317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7113332748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4417181015015</t>
+    <t xml:space="preserve">13.8607292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.711332321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4417171478271</t>
   </si>
   <si>
     <t xml:space="preserve">14.5745153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.541316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4251165390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4085178375244</t>
+    <t xml:space="preserve">14.5413160324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4251174926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.408519744873</t>
   </si>
   <si>
     <t xml:space="preserve">14.3919191360474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4708976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2053022384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.022705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4915151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8275299072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7777309417725</t>
+    <t xml:space="preserve">15.4708986282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2053031921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227060317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4915161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8275308609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7777318954468</t>
   </si>
   <si>
     <t xml:space="preserve">13.6449337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5287342071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5619354248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4125385284424</t>
+    <t xml:space="preserve">13.7445306777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5287351608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5619344711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4125375747681</t>
   </si>
   <si>
     <t xml:space="preserve">13.1137437820435</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">13.5121364593506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5951328277588</t>
+    <t xml:space="preserve">13.5951337814331</t>
   </si>
   <si>
     <t xml:space="preserve">13.6117334365845</t>
@@ -2579,28 +2579,28 @@
     <t xml:space="preserve">13.1303434371948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3295402526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4955368041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.080545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3129415512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.196741104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7983493804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4497575759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3003587722778</t>
+    <t xml:space="preserve">13.3295392990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4955377578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0805444717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3129405975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1967430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7983503341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4497566223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3003597259521</t>
   </si>
   <si>
     <t xml:space="preserve">12.7153511047363</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">12.4331569671631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5991535186768</t>
+    <t xml:space="preserve">12.5991544723511</t>
   </si>
   <si>
     <t xml:space="preserve">12.3335590362549</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">12.3501586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0679636001587</t>
+    <t xml:space="preserve">12.067964553833</t>
   </si>
   <si>
     <t xml:space="preserve">11.8521680831909</t>
@@ -2630,28 +2630,28 @@
     <t xml:space="preserve">12.0845642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8189687728882</t>
+    <t xml:space="preserve">11.8189697265625</t>
   </si>
   <si>
     <t xml:space="preserve">11.6031723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7027721405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7857704162598</t>
+    <t xml:space="preserve">11.7027711868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7857694625854</t>
   </si>
   <si>
     <t xml:space="preserve">11.5367746353149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3209800720215</t>
+    <t xml:space="preserve">11.3209791183472</t>
   </si>
   <si>
     <t xml:space="preserve">11.1715812683105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.221381187439</t>
+    <t xml:space="preserve">11.2213821411133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8395891189575</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">10.6735916137695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6237926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.258599281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1922016143799</t>
+    <t xml:space="preserve">10.6237936019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2585983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1922006607056</t>
   </si>
   <si>
     <t xml:space="preserve">9.97640514373779</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">9.56141376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36221790313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62781238555908</t>
+    <t xml:space="preserve">9.36221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62781143188477</t>
   </si>
   <si>
     <t xml:space="preserve">9.32901763916016</t>
@@ -2693,13 +2693,13 @@
     <t xml:space="preserve">9.52821445465088</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0096044540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39541721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.391396522522</t>
+    <t xml:space="preserve">10.0096035003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39541625976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3913974761963</t>
   </si>
   <si>
     <t xml:space="preserve">10.6071920394897</t>
@@ -2714,19 +2714,19 @@
     <t xml:space="preserve">10.1756019592285</t>
   </si>
   <si>
-    <t xml:space="preserve">10.109203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1424016952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0594024658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86020851135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89340591430664</t>
+    <t xml:space="preserve">10.1092023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1424026489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0594034194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86020755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89340686798096</t>
   </si>
   <si>
     <t xml:space="preserve">9.69421100616455</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">9.61121273040771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17962074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27921962738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37881755828857</t>
+    <t xml:space="preserve">9.17962169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27921867370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37881660461426</t>
   </si>
   <si>
     <t xml:space="preserve">9.19622039794922</t>
@@ -2750,28 +2750,28 @@
     <t xml:space="preserve">9.29581832885742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12982177734375</t>
+    <t xml:space="preserve">9.12982082366943</t>
   </si>
   <si>
     <t xml:space="preserve">9.42861557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77720928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64441108703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0262050628662</t>
+    <t xml:space="preserve">9.77720832824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64441204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0262041091919</t>
   </si>
   <si>
     <t xml:space="preserve">10.5407934188843</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4577951431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0760040283203</t>
+    <t xml:space="preserve">10.4577960968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.076003074646</t>
   </si>
   <si>
     <t xml:space="preserve">9.92660617828369</t>
@@ -2780,37 +2780,37 @@
     <t xml:space="preserve">9.66899490356445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70334434509277</t>
+    <t xml:space="preserve">9.70334339141846</t>
   </si>
   <si>
     <t xml:space="preserve">9.7205171585083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0639991760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0983476638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2529134750366</t>
+    <t xml:space="preserve">10.0639982223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0983467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2529125213623</t>
   </si>
   <si>
     <t xml:space="preserve">9.85791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0811719894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3559579849243</t>
+    <t xml:space="preserve">10.0811729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.35595703125</t>
   </si>
   <si>
     <t xml:space="preserve">10.2700872421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6479158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7681350708008</t>
+    <t xml:space="preserve">10.6479167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7681341171265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9570503234863</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">11.0600938796997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1803121566772</t>
+    <t xml:space="preserve">11.1803131103516</t>
   </si>
   <si>
     <t xml:space="preserve">11.0944423675537</t>
@@ -2834,16 +2834,16 @@
     <t xml:space="preserve">10.9742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.991397857666</t>
+    <t xml:space="preserve">10.9913988113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.0296506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0124769210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.390305519104</t>
+    <t xml:space="preserve">10.0124759674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3903064727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1498689651489</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">10.1326951980591</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97812747955322</t>
+    <t xml:space="preserve">9.97812843322754</t>
   </si>
   <si>
     <t xml:space="preserve">9.87508392333984</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">10.2872610092163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2013921737671</t>
+    <t xml:space="preserve">10.2013912200928</t>
   </si>
   <si>
     <t xml:space="preserve">10.3044357299805</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">10.1842164993286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0468254089355</t>
+    <t xml:space="preserve">10.0468244552612</t>
   </si>
   <si>
     <t xml:space="preserve">10.5620460510254</t>
@@ -2885,16 +2885,16 @@
     <t xml:space="preserve">10.424654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7166128158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.459002494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5105237960815</t>
+    <t xml:space="preserve">10.4418287277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5105228424072</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509613037109</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">10.6822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4933500289917</t>
+    <t xml:space="preserve">10.493350982666</t>
   </si>
   <si>
     <t xml:space="preserve">10.1155204772949</t>
@@ -2915,10 +2915,10 @@
     <t xml:space="preserve">9.61747264862061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37703704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51442813873291</t>
+    <t xml:space="preserve">9.37703609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51442909240723</t>
   </si>
   <si>
     <t xml:space="preserve">9.63464736938477</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">9.25681781768799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46290683746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0850772857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54877758026123</t>
+    <t xml:space="preserve">9.4629077911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08507633209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54877662658691</t>
   </si>
   <si>
     <t xml:space="preserve">9.56595039367676</t>
@@ -2966,19 +2966,19 @@
     <t xml:space="preserve">9.65182113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82356071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3387832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5963945388794</t>
+    <t xml:space="preserve">9.823561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3387842178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5963954925537</t>
   </si>
   <si>
     <t xml:space="preserve">10.8540058135986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4550981521606</t>
+    <t xml:space="preserve">11.4550971984863</t>
   </si>
   <si>
     <t xml:space="preserve">11.2661828994751</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">11.0429201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8883533477783</t>
+    <t xml:space="preserve">10.8883543014526</t>
   </si>
   <si>
     <t xml:space="preserve">10.9398756027222</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">10.8196573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8024835586548</t>
+    <t xml:space="preserve">10.8024826049805</t>
   </si>
   <si>
     <t xml:space="preserve">11.3692274093628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4379224777222</t>
+    <t xml:space="preserve">11.4379234313965</t>
   </si>
   <si>
     <t xml:space="preserve">12.0733642578125</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">12.5027151107788</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2966260910034</t>
+    <t xml:space="preserve">12.2966251373291</t>
   </si>
   <si>
     <t xml:space="preserve">12.0561895370483</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">11.7470560073853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7127094268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9703197479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9359703063965</t>
+    <t xml:space="preserve">11.7127084732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9703187942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9359712600708</t>
   </si>
   <si>
     <t xml:space="preserve">12.0046663284302</t>
@@ -3041,28 +3041,28 @@
     <t xml:space="preserve">11.8157529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2279300689697</t>
+    <t xml:space="preserve">12.227931022644</t>
   </si>
   <si>
     <t xml:space="preserve">12.3653221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4340190887451</t>
+    <t xml:space="preserve">12.4340181350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.3996696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3137998580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5198888778687</t>
+    <t xml:space="preserve">12.3138008117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.519889831543</t>
   </si>
   <si>
     <t xml:space="preserve">12.485541343689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6401071548462</t>
+    <t xml:space="preserve">12.6401081085205</t>
   </si>
   <si>
     <t xml:space="preserve">12.2451038360596</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">12.1764087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1592330932617</t>
+    <t xml:space="preserve">12.159234046936</t>
   </si>
   <si>
     <t xml:space="preserve">12.1077117919922</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">12.9148921966553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0694589614868</t>
+    <t xml:space="preserve">13.0694599151611</t>
   </si>
   <si>
     <t xml:space="preserve">13.1038074493408</t>
@@ -3107,58 +3107,58 @@
     <t xml:space="preserve">13.1896772384644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6705513000488</t>
+    <t xml:space="preserve">13.6705503463745</t>
   </si>
   <si>
     <t xml:space="preserve">13.3442440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6362037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6018543243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.550332069397</t>
+    <t xml:space="preserve">13.6362028121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6018552780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5503330230713</t>
   </si>
   <si>
     <t xml:space="preserve">13.5675067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4644632339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3957653045654</t>
+    <t xml:space="preserve">13.4644622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3957672119141</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.619029045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0827283859253</t>
+    <t xml:space="preserve">13.6190280914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.082727432251</t>
   </si>
   <si>
     <t xml:space="preserve">13.6877250671387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7048988342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7220735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8766403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6151237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7353429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6494722366333</t>
+    <t xml:space="preserve">13.7048997879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7220726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8766393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6151247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7353420257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6494731903076</t>
   </si>
   <si>
     <t xml:space="preserve">14.8040390014648</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">14.6838207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7868642807007</t>
+    <t xml:space="preserve">14.7868633270264</t>
   </si>
   <si>
     <t xml:space="preserve">14.7181673049927</t>
@@ -3179,28 +3179,28 @@
     <t xml:space="preserve">15.0616502761841</t>
   </si>
   <si>
-    <t xml:space="preserve">15.387957572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1990423202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2505664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818685531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.216215133667</t>
+    <t xml:space="preserve">15.3879566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2505645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2162160873413</t>
   </si>
   <si>
     <t xml:space="preserve">14.9757795333862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9242553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4262094497681</t>
+    <t xml:space="preserve">14.9242563247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4262084960938</t>
   </si>
   <si>
     <t xml:space="preserve">14.3918619155884</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">14.9586057662964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5464296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1131706237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1303462982178</t>
+    <t xml:space="preserve">14.5464286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1131715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1303472518921</t>
   </si>
   <si>
     <t xml:space="preserve">14.9929523468018</t>
@@ -3224,34 +3224,34 @@
     <t xml:space="preserve">15.2677392959595</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4223041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9031801223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9375267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1436138153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.851655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547004699707</t>
+    <t xml:space="preserve">15.4223051071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9031782150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9375276565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1436157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8516550064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9546995162964</t>
   </si>
   <si>
     <t xml:space="preserve">15.7829599380493</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7142629623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5253486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5596990585327</t>
+    <t xml:space="preserve">15.7142639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5253496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5596981048584</t>
   </si>
   <si>
     <t xml:space="preserve">14.8383884429932</t>
@@ -3260,34 +3260,34 @@
     <t xml:space="preserve">14.4605579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3059902191162</t>
+    <t xml:space="preserve">14.3059921264648</t>
   </si>
   <si>
     <t xml:space="preserve">14.2888164520264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5120782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6323003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7009954452515</t>
+    <t xml:space="preserve">14.5120792388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6322994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7009963989258</t>
   </si>
   <si>
     <t xml:space="preserve">14.5807752609253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5292549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3746871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1431255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2678136825562</t>
+    <t xml:space="preserve">14.5292539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3746862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1431245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2678127288818</t>
   </si>
   <si>
     <t xml:space="preserve">14.321249961853</t>
@@ -3299,10 +3299,10 @@
     <t xml:space="preserve">14.6774997711182</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6062498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0540618896484</t>
+    <t xml:space="preserve">14.6062488555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0540628433228</t>
   </si>
   <si>
     <t xml:space="preserve">14.0362501144409</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">14.0184373855591</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0006256103516</t>
+    <t xml:space="preserve">14.0006246566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.733437538147</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">13.875937461853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2856254577637</t>
+    <t xml:space="preserve">14.285626411438</t>
   </si>
   <si>
     <t xml:space="preserve">14.0896873474121</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">14.1609373092651</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1253118515015</t>
+    <t xml:space="preserve">14.1253128051758</t>
   </si>
   <si>
     <t xml:space="preserve">14.4459371566772</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">14.178750038147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9828119277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9293756484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6978130340576</t>
+    <t xml:space="preserve">13.9828128814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9293746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6978120803833</t>
   </si>
   <si>
     <t xml:space="preserve">13.6799993515015</t>
@@ -3365,16 +3365,16 @@
     <t xml:space="preserve">13.5731248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8403129577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8581247329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9115629196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4840621948242</t>
+    <t xml:space="preserve">13.8403120040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8581256866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9115619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4840631484985</t>
   </si>
   <si>
     <t xml:space="preserve">13.1278123855591</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">13.8046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7690629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8225002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3034372329712</t>
+    <t xml:space="preserve">13.7690620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8225011825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3034362792969</t>
   </si>
   <si>
     <t xml:space="preserve">14.3924999237061</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">14.624062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4993753433228</t>
+    <t xml:space="preserve">14.4993762969971</t>
   </si>
   <si>
     <t xml:space="preserve">14.5349998474121</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">14.25</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0718755722046</t>
+    <t xml:space="preserve">14.0718746185303</t>
   </si>
   <si>
     <t xml:space="preserve">13.359375</t>
@@ -3428,22 +3428,22 @@
     <t xml:space="preserve">13.5018749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5196876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2321863174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6265630722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812496185303</t>
+    <t xml:space="preserve">13.5196886062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2321872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6265621185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812505722046</t>
   </si>
   <si>
     <t xml:space="preserve">13.0565624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1099996566772</t>
+    <t xml:space="preserve">13.1100006103516</t>
   </si>
   <si>
     <t xml:space="preserve">12.842812538147</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">12.8249998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7181253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221881866455</t>
+    <t xml:space="preserve">12.7181243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221872329712</t>
   </si>
   <si>
     <t xml:space="preserve">12.397500038147</t>
@@ -3476,25 +3476,25 @@
     <t xml:space="preserve">12.4865627288818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2906255722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2193756103516</t>
+    <t xml:space="preserve">12.2906246185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2193746566772</t>
   </si>
   <si>
     <t xml:space="preserve">12.2550001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1481256484985</t>
+    <t xml:space="preserve">12.1481246948242</t>
   </si>
   <si>
     <t xml:space="preserve">12.1659374237061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1303119659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165630340576</t>
+    <t xml:space="preserve">12.1303129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165620803833</t>
   </si>
   <si>
     <t xml:space="preserve">11.578125</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">11.3287506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2931261062622</t>
+    <t xml:space="preserve">11.2931251525879</t>
   </si>
   <si>
     <t xml:space="preserve">11.1328125</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">10.9012498855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9190635681152</t>
+    <t xml:space="preserve">10.9190626144409</t>
   </si>
   <si>
     <t xml:space="preserve">11.061562538147</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">11.0971879959106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1684379577637</t>
+    <t xml:space="preserve">11.1684370040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.204062461853</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">11.4534368515015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8631238937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0768756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453130722046</t>
+    <t xml:space="preserve">11.8631248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0768747329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453121185303</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809375762939</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">11.9878120422363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2015619277954</t>
+    <t xml:space="preserve">12.2015628814697</t>
   </si>
   <si>
     <t xml:space="preserve">12.6468753814697</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">12.7003126144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3618745803833</t>
+    <t xml:space="preserve">12.3618755340576</t>
   </si>
   <si>
     <t xml:space="preserve">12.3440628051758</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">12.094687461853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0590620040894</t>
+    <t xml:space="preserve">12.0590629577637</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056247711182</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">11.4178123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4356250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7384376525879</t>
+    <t xml:space="preserve">11.4356260299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7384386062622</t>
   </si>
   <si>
     <t xml:space="preserve">11.7562494277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5959386825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274993896484</t>
+    <t xml:space="preserve">11.5959377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8275003433228</t>
   </si>
   <si>
     <t xml:space="preserve">11.7206249237061</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">11.2396869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5425004959106</t>
+    <t xml:space="preserve">11.5424995422363</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028131484985</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">11.9700002670288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5246877670288</t>
+    <t xml:space="preserve">11.5246868133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.9724998474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1149988174438</t>
+    <t xml:space="preserve">11.1149997711182</t>
   </si>
   <si>
     <t xml:space="preserve">11.3382139205933</t>
@@ -4440,6 +4440,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.61999988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44000005722046</t>
   </si>
 </sst>
 </file>
@@ -70428,7 +70431,7 @@
     </row>
     <row r="2526">
       <c r="A2526" s="1" t="n">
-        <v>45995.6925925926</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2526" t="n">
         <v>214514</v>
@@ -70449,6 +70452,32 @@
         <v>1475</v>
       </c>
       <c r="H2526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>45996.6910763889</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>84214</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>7.65000009536743</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>7.42000007629395</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>7.57999992370605</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>7.44000005722046</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H2527" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -44,70 +44,70 @@
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447938919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9397885799408</t>
+    <t xml:space="preserve">4.02447986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93978929519653</t>
   </si>
   <si>
     <t xml:space="preserve">3.82799816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78057146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943140983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7568576335907</t>
+    <t xml:space="preserve">3.78057098388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943212509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75685834884644</t>
   </si>
   <si>
     <t xml:space="preserve">3.74330806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80089712142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040910720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571805953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66539311408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56376528739929</t>
+    <t xml:space="preserve">3.80089664459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040839195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66539263725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56376481056213</t>
   </si>
   <si>
     <t xml:space="preserve">3.65184211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72636961936951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70265674591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65861749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69249320030212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74669551849365</t>
+    <t xml:space="preserve">3.72636985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70265698432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65861797332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69249367713928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74669575691223</t>
   </si>
   <si>
     <t xml:space="preserve">3.59764075279236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086537361145</t>
+    <t xml:space="preserve">3.59086561203003</t>
   </si>
   <si>
     <t xml:space="preserve">3.5840904712677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49601244926453</t>
+    <t xml:space="preserve">3.49601173400879</t>
   </si>
   <si>
     <t xml:space="preserve">3.4621365070343</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">3.51633810997009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38760852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40793490409851</t>
+    <t xml:space="preserve">3.38760924339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40793466567993</t>
   </si>
   <si>
     <t xml:space="preserve">3.50956249237061</t>
@@ -134,118 +134,118 @@
     <t xml:space="preserve">3.61119079589844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57731485366821</t>
+    <t xml:space="preserve">3.57731509208679</t>
   </si>
   <si>
     <t xml:space="preserve">3.54682636260986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52650094032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50278759002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5603768825531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58070278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60102844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54343914985657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57053995132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64506721496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78734636306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84154891967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86526107788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85171151161194</t>
+    <t xml:space="preserve">3.5265007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5027871131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56037640571594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58070254325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60102796554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54343867301941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57053971290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64506697654724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78734683990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84154844284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8652617931366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8517107963562</t>
   </si>
   <si>
     <t xml:space="preserve">3.92962622642517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93640089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607570648193</t>
+    <t xml:space="preserve">3.93640112876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607546806335</t>
   </si>
   <si>
     <t xml:space="preserve">3.90252542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89575028419495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285132408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90930008888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9702775478363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87881183624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85848617553711</t>
+    <t xml:space="preserve">3.89574980735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9093005657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97027778625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8788115978241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85848665237427</t>
   </si>
   <si>
     <t xml:space="preserve">3.94317674636841</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89913749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94656419754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95672702789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96350288391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9126877784729</t>
+    <t xml:space="preserve">3.89913773536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9465639591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95672726631165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96350193023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91268825531006</t>
   </si>
   <si>
     <t xml:space="preserve">3.97366523742676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91946291923523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87203741073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88704776763916</t>
+    <t xml:space="preserve">3.91946339607239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87203693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88704800605774</t>
   </si>
   <si>
     <t xml:space="preserve">3.87291312217712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85877919197083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83757615089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86231255531311</t>
+    <t xml:space="preserve">3.85877847671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83757638931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86231279373169</t>
   </si>
   <si>
     <t xml:space="preserve">3.87644720077515</t>
@@ -254,40 +254,40 @@
     <t xml:space="preserve">3.89411544799805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9011824131012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058113098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94358682632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95418787002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96125507354736</t>
+    <t xml:space="preserve">3.90118360519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89058184623718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9435863494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95418739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96125531196594</t>
   </si>
   <si>
     <t xml:space="preserve">4.01426076889038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02486133575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08846712112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05666494369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03899669647217</t>
+    <t xml:space="preserve">4.02486181259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08846759796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05666446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03899621963501</t>
   </si>
   <si>
     <t xml:space="preserve">3.99305844306946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00719356536865</t>
+    <t xml:space="preserve">4.00719308853149</t>
   </si>
   <si>
     <t xml:space="preserve">3.97539019584656</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">3.97185611724854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80223965644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78103756904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75630187988281</t>
+    <t xml:space="preserve">3.80223941802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78103733062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75630164146423</t>
   </si>
   <si>
     <t xml:space="preserve">3.74923396110535</t>
@@ -311,115 +311,115 @@
     <t xml:space="preserve">3.9047167301178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92238521575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065402984619</t>
+    <t xml:space="preserve">3.9223849773407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065426826477</t>
   </si>
   <si>
     <t xml:space="preserve">4.03546285629272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7598352432251</t>
+    <t xml:space="preserve">3.75983572006226</t>
   </si>
   <si>
     <t xml:space="preserve">3.80930685997009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83050870895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86937928199768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82344198226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80577349662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84110999107361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8517107963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8163743019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86584544181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89764809608459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93651962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90825009346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91531753540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.978924036026</t>
+    <t xml:space="preserve">3.83050918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86937999725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82344150543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80577373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84111022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85171127319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81637477874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86584568023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89764857292175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93651866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90825057029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91531729698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97892379760742</t>
   </si>
   <si>
     <t xml:space="preserve">4.00012540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02132797241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95772171020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84464359283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81284046173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77043676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76336860656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74570059776306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72449922561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77397012710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78810453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.819908618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72803258895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73863387107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73156595230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73510003089905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65382504463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6396906375885</t>
+    <t xml:space="preserve">4.02132749557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9577214717865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84464406967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81284117698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77043652534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690268516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76336884498596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74570107460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7244987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77397036552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78810477256775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81990814208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72803235054016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73863363265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7315661907196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73509979248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6538245677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63969039916992</t>
   </si>
   <si>
     <t xml:space="preserve">3.66089224815369</t>
@@ -431,40 +431,40 @@
     <t xml:space="preserve">3.61142134666443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62555575370789</t>
+    <t xml:space="preserve">3.62555503845215</t>
   </si>
   <si>
     <t xml:space="preserve">3.61495471000671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64675784111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74216723442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9188506603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98599123954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99659180641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87998056411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88351440429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79517197608948</t>
+    <t xml:space="preserve">3.64675712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7421669960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91885137557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98599076271057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99659204483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87998080253601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88351488113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79517245292664</t>
   </si>
   <si>
     <t xml:space="preserve">3.82697534561157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79163837432861</t>
+    <t xml:space="preserve">3.79163861274719</t>
   </si>
   <si>
     <t xml:space="preserve">3.84817743301392</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">3.71036386489868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85524487495422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03192853927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04252910614014</t>
+    <t xml:space="preserve">3.85524439811707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03192901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04252958297729</t>
   </si>
   <si>
     <t xml:space="preserve">4.08493375778198</t>
@@ -494,37 +494,37 @@
     <t xml:space="preserve">4.04959774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09200191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10966920852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0778660774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07433271408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04606342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0637321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10613536834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10260200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13440608978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12733793258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16974306106567</t>
+    <t xml:space="preserve">4.09200096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10967016220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07786655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07433319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04606294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06373167037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10613584518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1026029586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1344051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12733840942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16974210739136</t>
   </si>
   <si>
     <t xml:space="preserve">4.18387699127197</t>
@@ -533,37 +533,37 @@
     <t xml:space="preserve">4.15914154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24041509628296</t>
+    <t xml:space="preserve">4.24041557312012</t>
   </si>
   <si>
     <t xml:space="preserve">4.21568059921265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27575302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34642601013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36762809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35349273681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31108999252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30402231216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38176298141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50897550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72806310653687</t>
+    <t xml:space="preserve">4.27575349807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34642648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36762762069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35349321365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31108951568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30402278900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38176345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50897598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72806406021118</t>
   </si>
   <si>
     <t xml:space="preserve">4.91181516647339</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">5.19450902938843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22277927398682</t>
+    <t xml:space="preserve">5.22277879714966</t>
   </si>
   <si>
     <t xml:space="preserve">5.22984647750854</t>
@@ -587,22 +587,22 @@
     <t xml:space="preserve">5.09203290939331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07436418533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08496522903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11676836013794</t>
+    <t xml:space="preserve">5.07436370849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08496570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11676788330078</t>
   </si>
   <si>
     <t xml:space="preserve">5.10616731643677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1521053314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15917348861694</t>
+    <t xml:space="preserve">5.15210485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15917301177979</t>
   </si>
   <si>
     <t xml:space="preserve">5.17330741882324</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">5.19097566604614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14503765106201</t>
+    <t xml:space="preserve">5.14503812789917</t>
   </si>
   <si>
     <t xml:space="preserve">5.13090324401855</t>
@@ -626,52 +626,52 @@
     <t xml:space="preserve">5.59734916687012</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51254034042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35705900192261</t>
+    <t xml:space="preserve">5.5125412940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35705947875977</t>
   </si>
   <si>
     <t xml:space="preserve">5.47720336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37119293212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44186735153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53020858764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61199760437012</t>
+    <t xml:space="preserve">5.37119388580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44186639785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53020906448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61199712753296</t>
   </si>
   <si>
     <t xml:space="preserve">5.65216112136841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6886739730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6229510307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61929988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59739208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42213201522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41848087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5535774230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56087923049927</t>
+    <t xml:space="preserve">5.68867444992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62295055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.619300365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59739255905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42213153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41847991943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55357694625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56087970733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.49880886077881</t>
@@ -683,61 +683,61 @@
     <t xml:space="preserve">5.55722856521606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45499277114868</t>
+    <t xml:space="preserve">5.45499229431152</t>
   </si>
   <si>
     <t xml:space="preserve">5.3673620223999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37466478347778</t>
+    <t xml:space="preserve">5.37466526031494</t>
   </si>
   <si>
     <t xml:space="preserve">5.4330849647522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40387487411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47690105438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44769048690796</t>
+    <t xml:space="preserve">5.40387535095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47690010070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44769096374512</t>
   </si>
   <si>
     <t xml:space="preserve">5.48055219650269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49515724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54627418518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60104322433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41117668151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51341390609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54992532730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45134210586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61564922332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50611114501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34545421600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37101411819458</t>
+    <t xml:space="preserve">5.49515676498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54627370834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60104370117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41117715835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51341342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54992628097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45134115219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61564826965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50611066818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34545469284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37101364135742</t>
   </si>
   <si>
     <t xml:space="preserve">5.31259346008301</t>
@@ -746,28 +746,28 @@
     <t xml:space="preserve">5.287034034729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15558958053589</t>
+    <t xml:space="preserve">5.15558910369873</t>
   </si>
   <si>
     <t xml:space="preserve">5.12637901306152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2724289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31989622116089</t>
+    <t xml:space="preserve">5.27242946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31989574432373</t>
   </si>
   <si>
     <t xml:space="preserve">5.14098405838013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40752649307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38927030563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3783164024353</t>
+    <t xml:space="preserve">5.40752696990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3892707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37831592559814</t>
   </si>
   <si>
     <t xml:space="preserve">5.24321889877319</t>
@@ -779,13 +779,13 @@
     <t xml:space="preserve">5.41482877731323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42578220367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44038820266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48420286178589</t>
+    <t xml:space="preserve">5.42578268051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44038772583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48420333862305</t>
   </si>
   <si>
     <t xml:space="preserve">5.3527569770813</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">5.48785448074341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50245952606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57183361053467</t>
+    <t xml:space="preserve">5.50245904922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57183313369751</t>
   </si>
   <si>
     <t xml:space="preserve">5.57913589477539</t>
@@ -806,73 +806,73 @@
     <t xml:space="preserve">5.56453037261963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52071523666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53897190093994</t>
+    <t xml:space="preserve">5.52071619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5389723777771</t>
   </si>
   <si>
     <t xml:space="preserve">5.65581226348877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58643817901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57548475265503</t>
+    <t xml:space="preserve">5.58643865585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57548522949219</t>
   </si>
   <si>
     <t xml:space="preserve">5.50976228713989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53166961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60469436645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59008979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75804758071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79456043243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92965698242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94426298141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99903154373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93695974349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98807716369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83107376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88584280014038</t>
+    <t xml:space="preserve">5.5316686630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60469484329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59009027481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75804805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79455995559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92965745925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94426345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99903106689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93696069717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98807764053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83107328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88584232330322</t>
   </si>
   <si>
     <t xml:space="preserve">5.83472490310669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95886754989624</t>
+    <t xml:space="preserve">5.9588680267334</t>
   </si>
   <si>
     <t xml:space="preserve">5.76900196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91140174865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83837604522705</t>
+    <t xml:space="preserve">5.91140127182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83837556838989</t>
   </si>
   <si>
     <t xml:space="preserve">5.84202718734741</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">5.87123727798462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78360652923584</t>
+    <t xml:space="preserve">5.783607006073</t>
   </si>
   <si>
     <t xml:space="preserve">5.85298109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70327854156494</t>
+    <t xml:space="preserve">5.7032790184021</t>
   </si>
   <si>
     <t xml:space="preserve">5.82742214202881</t>
@@ -896,31 +896,31 @@
     <t xml:space="preserve">5.8639349937439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75439691543579</t>
+    <t xml:space="preserve">5.75439643859863</t>
   </si>
   <si>
     <t xml:space="preserve">5.72883796691895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68502235412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66676616668701</t>
+    <t xml:space="preserve">5.68502187728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66676664352417</t>
   </si>
   <si>
     <t xml:space="preserve">5.88949346542358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78725814819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77995586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73614025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60834550857544</t>
+    <t xml:space="preserve">5.78725862503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77995538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73614072799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6083459854126</t>
   </si>
   <si>
     <t xml:space="preserve">5.63025331497192</t>
@@ -932,25 +932,25 @@
     <t xml:space="preserve">5.76169919967651</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62660217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68137168884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73979187011719</t>
+    <t xml:space="preserve">5.62660264968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68137121200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73979139328003</t>
   </si>
   <si>
     <t xml:space="preserve">5.76535081863403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.809166431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80551433563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82377052307129</t>
+    <t xml:space="preserve">5.80916500091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80551481246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82377099990845</t>
   </si>
   <si>
     <t xml:space="preserve">5.87853956222534</t>
@@ -959,100 +959,100 @@
     <t xml:space="preserve">5.82011938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90409851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92235517501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9515643119812</t>
+    <t xml:space="preserve">5.90409898757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600679397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92235469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95156526565552</t>
   </si>
   <si>
     <t xml:space="preserve">6.02459049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06110382080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00998497009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09031391143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22906064987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18524646759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03189373016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03919649124146</t>
+    <t xml:space="preserve">6.06110334396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00998544692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09031343460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22906160354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18524599075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03189277648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03919506072998</t>
   </si>
   <si>
     <t xml:space="preserve">6.0464973449707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25096893310547</t>
+    <t xml:space="preserve">6.25096988677979</t>
   </si>
   <si>
     <t xml:space="preserve">6.20715379714966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14143180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1268253326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79821252822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72518682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96617031097412</t>
+    <t xml:space="preserve">6.14143085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12682628631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7982120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72518587112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96617078781128</t>
   </si>
   <si>
     <t xml:space="preserve">6.00268316268921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89314413070679</t>
+    <t xml:space="preserve">5.89314460754395</t>
   </si>
   <si>
     <t xml:space="preserve">5.84932994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97347354888916</t>
+    <t xml:space="preserve">5.973473072052</t>
   </si>
   <si>
     <t xml:space="preserve">5.99538040161133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1195240020752</t>
+    <t xml:space="preserve">6.11952352523804</t>
   </si>
   <si>
     <t xml:space="preserve">6.15603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10491800308228</t>
+    <t xml:space="preserve">6.10491895675659</t>
   </si>
   <si>
     <t xml:space="preserve">5.98077487945557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90044736862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1487340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09761667251587</t>
+    <t xml:space="preserve">5.90044784545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14873361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09761571884155</t>
   </si>
   <si>
     <t xml:space="preserve">6.05380058288574</t>
@@ -1064,31 +1064,31 @@
     <t xml:space="preserve">6.08301115036011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17794418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17064046859741</t>
+    <t xml:space="preserve">6.17794370651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17064094543457</t>
   </si>
   <si>
     <t xml:space="preserve">6.24366664886475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28017950057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38636636734009</t>
+    <t xml:space="preserve">6.28017997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38636541366577</t>
   </si>
   <si>
     <t xml:space="preserve">6.31810283660889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23467111587524</t>
+    <t xml:space="preserve">6.23467063903809</t>
   </si>
   <si>
     <t xml:space="preserve">6.28017854690552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15882253646851</t>
+    <t xml:space="preserve">6.15882349014282</t>
   </si>
   <si>
     <t xml:space="preserve">6.27259492874146</t>
@@ -1097,28 +1097,28 @@
     <t xml:space="preserve">6.26500988006592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21191596984863</t>
+    <t xml:space="preserve">6.21191549301147</t>
   </si>
   <si>
     <t xml:space="preserve">6.1815767288208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15123748779297</t>
+    <t xml:space="preserve">6.15123796463013</t>
   </si>
   <si>
     <t xml:space="preserve">6.02988195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05263614654541</t>
+    <t xml:space="preserve">6.05263662338257</t>
   </si>
   <si>
     <t xml:space="preserve">6.25742483139038</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22708606719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24983978271484</t>
+    <t xml:space="preserve">6.22708559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24983930587769</t>
   </si>
   <si>
     <t xml:space="preserve">6.29534864425659</t>
@@ -1127,22 +1127,22 @@
     <t xml:space="preserve">6.37119626998901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18916130065918</t>
+    <t xml:space="preserve">6.1891622543335</t>
   </si>
   <si>
     <t xml:space="preserve">6.16640758514404</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20433187484741</t>
+    <t xml:space="preserve">6.20433139801025</t>
   </si>
   <si>
     <t xml:space="preserve">6.0147123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04505109786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00712776184082</t>
+    <t xml:space="preserve">6.04505157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00712728500366</t>
   </si>
   <si>
     <t xml:space="preserve">5.98437356948853</t>
@@ -1157,22 +1157,22 @@
     <t xml:space="preserve">6.11331462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09056043624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96161937713623</t>
+    <t xml:space="preserve">6.09055948257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96161890029907</t>
   </si>
   <si>
     <t xml:space="preserve">6.0829758644104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14365386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10572957992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06022119522095</t>
+    <t xml:space="preserve">6.14365291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1057300567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06022071838379</t>
   </si>
   <si>
     <t xml:space="preserve">5.99954319000244</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">6.06780576705933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91611051559448</t>
+    <t xml:space="preserve">5.91611099243164</t>
   </si>
   <si>
     <t xml:space="preserve">5.94645023345947</t>
@@ -1205,43 +1205,43 @@
     <t xml:space="preserve">5.9919581413269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86301708221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07539033889771</t>
+    <t xml:space="preserve">5.86301803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07539081573486</t>
   </si>
   <si>
     <t xml:space="preserve">6.24225521087646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47738265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63666248321533</t>
+    <t xml:space="preserve">6.47738313674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63666296005249</t>
   </si>
   <si>
     <t xml:space="preserve">6.46221351623535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57598447799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56081485748291</t>
+    <t xml:space="preserve">6.57598495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56081438064575</t>
   </si>
   <si>
     <t xml:space="preserve">6.60632371902466</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55323076248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65183258056641</t>
+    <t xml:space="preserve">6.55323123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65183210372925</t>
   </si>
   <si>
     <t xml:space="preserve">6.53806018829346</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48496770858765</t>
+    <t xml:space="preserve">6.4849681854248</t>
   </si>
   <si>
     <t xml:space="preserve">6.61390829086304</t>
@@ -1253,34 +1253,34 @@
     <t xml:space="preserve">6.59873867034912</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34085702896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39394998550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41670513153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4242901802063</t>
+    <t xml:space="preserve">6.34085655212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39395046234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4167046546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42428970336914</t>
   </si>
   <si>
     <t xml:space="preserve">6.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59115266799927</t>
+    <t xml:space="preserve">6.59115314483643</t>
   </si>
   <si>
     <t xml:space="preserve">6.54564523696899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56839942932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44704341888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34844207763672</t>
+    <t xml:space="preserve">6.56839990615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44704389572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34844160079956</t>
   </si>
   <si>
     <t xml:space="preserve">6.21950054168701</t>
@@ -1289,103 +1289,103 @@
     <t xml:space="preserve">6.40911960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32568740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28776359558105</t>
+    <t xml:space="preserve">6.32568788528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28776454925537</t>
   </si>
   <si>
     <t xml:space="preserve">6.68975591659546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67458629608154</t>
+    <t xml:space="preserve">6.6745867729187</t>
   </si>
   <si>
     <t xml:space="preserve">6.74284982681274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75043344497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62149238586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37878131866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36361122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46979713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51530694961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31051731109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35602712631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19674634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40153455734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72009468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7580189704895</t>
+    <t xml:space="preserve">6.75043392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62149286270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37878084182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36361169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46979761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51530647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31051826477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3560266494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19674682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40153503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72009515762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75801801681519</t>
   </si>
   <si>
     <t xml:space="preserve">6.80352783203125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78835773468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73526525497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84903573989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86420440673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81111240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8414511680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81869649887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90212869644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99314594268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89454460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9400520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05382490158081</t>
+    <t xml:space="preserve">6.78835725784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73526382446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84903526306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86420488357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81111288070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84145164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81869602203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90212965011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9931468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89454507827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94005298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05382394790649</t>
   </si>
   <si>
     <t xml:space="preserve">7.10691738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15242624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.114501953125</t>
+    <t xml:space="preserve">7.15242671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11450242996216</t>
   </si>
   <si>
     <t xml:space="preserve">7.01590061187744</t>
@@ -1394,118 +1394,118 @@
     <t xml:space="preserve">7.08416318893433</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04623937606812</t>
+    <t xml:space="preserve">7.04623889923096</t>
   </si>
   <si>
     <t xml:space="preserve">7.09174823760986</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39513778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35721349716187</t>
+    <t xml:space="preserve">7.39513826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35721397399902</t>
   </si>
   <si>
     <t xml:space="preserve">7.34204530715942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1220874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13725662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12967109680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2510290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22827339172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2055196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19793510437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16759586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37996768951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43306159973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49373960494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53924798965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54683256149292</t>
+    <t xml:space="preserve">7.12208795547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13725614547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12967157363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25102806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22827291488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20552015304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1979341506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16759634017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37996864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43306303024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49374008178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53924894332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54683303833008</t>
   </si>
   <si>
     <t xml:space="preserve">7.75162267684937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7971305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64543581008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69094562530518</t>
+    <t xml:space="preserve">7.79713106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64543533325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69094467163086</t>
   </si>
   <si>
     <t xml:space="preserve">7.57717275619507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45581531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51649475097656</t>
+    <t xml:space="preserve">7.45581579208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5164942741394</t>
   </si>
   <si>
     <t xml:space="preserve">7.59992694854736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50890970230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56200313568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58475685119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55441761016846</t>
+    <t xml:space="preserve">7.50890922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56200265884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58475732803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55441856384277</t>
   </si>
   <si>
     <t xml:space="preserve">7.47857046127319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47098588943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44823169708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7061128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331697463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88814830780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25221633911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61628437042236</t>
+    <t xml:space="preserve">7.47098731994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44823026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70611429214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331840515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88814735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25221538543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61628341674805</t>
   </si>
   <si>
     <t xml:space="preserve">8.49492835998535</t>
@@ -1514,16 +1514,16 @@
     <t xml:space="preserve">8.17636775970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41908073425293</t>
+    <t xml:space="preserve">8.41908168792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.1187686920166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08742332458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93068885803223</t>
+    <t xml:space="preserve">8.08742237091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93068981170654</t>
   </si>
   <si>
     <t xml:space="preserve">8.04040241241455</t>
@@ -1532,61 +1532,61 @@
     <t xml:space="preserve">7.96203565597534</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2598295211792</t>
+    <t xml:space="preserve">8.25982761383057</t>
   </si>
   <si>
     <t xml:space="preserve">8.02472972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86799621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73477268218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8366494178772</t>
+    <t xml:space="preserve">7.86799573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7347731590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83664989471436</t>
   </si>
   <si>
     <t xml:space="preserve">7.82097625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91501665115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97770929336548</t>
+    <t xml:space="preserve">7.91501569747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97771024703979</t>
   </si>
   <si>
     <t xml:space="preserve">8.07174968719482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05607604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85232400894165</t>
+    <t xml:space="preserve">8.05607509613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85232305526733</t>
   </si>
   <si>
     <t xml:space="preserve">8.40088844299316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46358203887939</t>
+    <t xml:space="preserve">8.46358108520508</t>
   </si>
   <si>
     <t xml:space="preserve">8.6203145980835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30684852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1657886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33819484710693</t>
+    <t xml:space="preserve">8.30684947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16578960418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33819580078125</t>
   </si>
   <si>
     <t xml:space="preserve">8.21280860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27550315856934</t>
+    <t xml:space="preserve">8.27550220489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.36954212188721</t>
@@ -1595,19 +1595,19 @@
     <t xml:space="preserve">8.15011596679688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18146324157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13444328308105</t>
+    <t xml:space="preserve">8.18146228790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13444423675537</t>
   </si>
   <si>
     <t xml:space="preserve">8.22848224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43223476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99338340759277</t>
+    <t xml:space="preserve">8.43223571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99338245391846</t>
   </si>
   <si>
     <t xml:space="preserve">8.19713592529297</t>
@@ -1616,43 +1616,43 @@
     <t xml:space="preserve">7.7582836151123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89934301376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82881307601929</t>
+    <t xml:space="preserve">7.89934206008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82881355285645</t>
   </si>
   <si>
     <t xml:space="preserve">7.88366985321045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81313991546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67991638183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79746532440186</t>
+    <t xml:space="preserve">7.81313896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67991781234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79746580123901</t>
   </si>
   <si>
     <t xml:space="preserve">8.41656112670898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80530261993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68775367736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74260902404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00905704498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.946364402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75044631958008</t>
+    <t xml:space="preserve">7.80530309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68775463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74261045455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00905609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94636344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75044727325439</t>
   </si>
   <si>
     <t xml:space="preserve">7.71910047531128</t>
@@ -1667,19 +1667,19 @@
     <t xml:space="preserve">9.37263298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60773372650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.482346534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79581165313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93687152862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87417793273926</t>
+    <t xml:space="preserve">9.60773277282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48234558105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79581260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9368724822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87417984008789</t>
   </si>
   <si>
     <t xml:space="preserve">9.99956512451172</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">10.1562976837158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5011110305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3757247924805</t>
+    <t xml:space="preserve">10.5011100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3757238388062</t>
   </si>
   <si>
     <t xml:space="preserve">10.5481309890747</t>
@@ -1700,43 +1700,43 @@
     <t xml:space="preserve">10.2189912796021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.171971321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95254421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90552520751953</t>
+    <t xml:space="preserve">10.1719703674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95254516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90552616119385</t>
   </si>
   <si>
     <t xml:space="preserve">9.88985061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92119789123535</t>
+    <t xml:space="preserve">9.92119884490967</t>
   </si>
   <si>
     <t xml:space="preserve">9.73311901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76446437835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57638549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96821784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0309114456177</t>
+    <t xml:space="preserve">9.76446533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57638645172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96821880340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.030912399292</t>
   </si>
   <si>
     <t xml:space="preserve">10.4854364395142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2503385543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0152368545532</t>
+    <t xml:space="preserve">10.250337600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0152378082275</t>
   </si>
   <si>
     <t xml:space="preserve">10.1249513626099</t>
@@ -1748,34 +1748,34 @@
     <t xml:space="preserve">10.2973585128784</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3130321502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4384183883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6264972686768</t>
+    <t xml:space="preserve">10.3130302429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4384174346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6264963150024</t>
   </si>
   <si>
     <t xml:space="preserve">10.6578435897827</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6108245849609</t>
+    <t xml:space="preserve">10.6108236312866</t>
   </si>
   <si>
     <t xml:space="preserve">10.5951509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5794763565063</t>
+    <t xml:space="preserve">10.579478263855</t>
   </si>
   <si>
     <t xml:space="preserve">10.6421699523926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7518844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9869842529297</t>
+    <t xml:space="preserve">10.7518835067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9869832992554</t>
   </si>
   <si>
     <t xml:space="preserve">10.9556360244751</t>
@@ -1787,10 +1787,10 @@
     <t xml:space="preserve">11.0183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2377548217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593894958496</t>
+    <t xml:space="preserve">11.237756729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593885421753</t>
   </si>
   <si>
     <t xml:space="preserve">11.0966958999634</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">11.1750631332397</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1123704910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0810232162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9713106155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.798903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0936040878296</t>
+    <t xml:space="preserve">11.1123695373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0810222625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9713096618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7989025115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622587203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0936050415039</t>
   </si>
   <si>
     <t xml:space="preserve">9.68609809875488</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">9.54504013061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98080158233643</t>
+    <t xml:space="preserve">8.98080062866211</t>
   </si>
   <si>
     <t xml:space="preserve">8.54194831848145</t>
@@ -1838,40 +1838,40 @@
     <t xml:space="preserve">7.5075101852417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53885793685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4918384552002</t>
+    <t xml:space="preserve">7.53885698318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49183702468872</t>
   </si>
   <si>
     <t xml:space="preserve">8.66733551025391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44790744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38521480560303</t>
+    <t xml:space="preserve">8.44790840148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38521575927734</t>
   </si>
   <si>
     <t xml:space="preserve">8.52627468109131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01214694976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45099925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10618591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93378067016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3883056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88676166534424</t>
+    <t xml:space="preserve">9.01214790344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45100021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10618686676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9337797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38830661773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88676071166992</t>
   </si>
   <si>
     <t xml:space="preserve">8.87108707427979</t>
@@ -1880,19 +1880,19 @@
     <t xml:space="preserve">9.12185955047607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9181079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15320682525635</t>
+    <t xml:space="preserve">8.91810703277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15320873260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.90243434906006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05916595458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04349327087402</t>
+    <t xml:space="preserve">9.05916690826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04349422454834</t>
   </si>
   <si>
     <t xml:space="preserve">9.21590042114258</t>
@@ -1916,49 +1916,49 @@
     <t xml:space="preserve">8.50604724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70121383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.189133644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92891025543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76626968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71747875213623</t>
+    <t xml:space="preserve">8.70121479034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18913269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92890930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76627063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71747970581055</t>
   </si>
   <si>
     <t xml:space="preserve">8.97770214080811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33550930023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48188400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61199474334717</t>
+    <t xml:space="preserve">9.33550834655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48188591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61199569702148</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625532150269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0673885345459</t>
+    <t xml:space="preserve">10.0673866271973</t>
   </si>
   <si>
     <t xml:space="preserve">10.3113460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1812334060669</t>
+    <t xml:space="preserve">10.1812343597412</t>
   </si>
   <si>
     <t xml:space="preserve">10.2137622833252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2788181304932</t>
+    <t xml:space="preserve">10.2788190841675</t>
   </si>
   <si>
     <t xml:space="preserve">10.2300262451172</t>
@@ -1967,37 +1967,37 @@
     <t xml:space="preserve">9.95353889465332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88848304748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69331455230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1324415206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1974973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3276090621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2462892532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.555305480957</t>
+    <t xml:space="preserve">9.88848400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69331550598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1324424743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1974983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3276100158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2462911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5553045272827</t>
   </si>
   <si>
     <t xml:space="preserve">10.8480567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8805828094482</t>
+    <t xml:space="preserve">10.8805837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.8317918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7992639541626</t>
+    <t xml:space="preserve">10.7992649078369</t>
   </si>
   <si>
     <t xml:space="preserve">10.9293756484985</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">10.685417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6366233825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7667369842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9781675338745</t>
+    <t xml:space="preserve">10.636625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7667360305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9781684875488</t>
   </si>
   <si>
     <t xml:space="preserve">11.1245431900024</t>
@@ -2027,13 +2027,13 @@
     <t xml:space="preserve">11.3847675323486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474071502686</t>
+    <t xml:space="preserve">11.5474061965942</t>
   </si>
   <si>
     <t xml:space="preserve">11.4335594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498224258423</t>
+    <t xml:space="preserve">11.4498233795166</t>
   </si>
   <si>
     <t xml:space="preserve">11.4660873413086</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">11.4823513031006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3359746932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2058620452881</t>
+    <t xml:space="preserve">11.335973739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2058629989624</t>
   </si>
   <si>
     <t xml:space="preserve">11.2221269607544</t>
@@ -2054,19 +2054,19 @@
     <t xml:space="preserve">10.8643198013306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.539041519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.522777557373</t>
+    <t xml:space="preserve">10.5390405654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5227756500244</t>
   </si>
   <si>
     <t xml:space="preserve">10.701681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8155288696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6040983200073</t>
+    <t xml:space="preserve">10.8155279159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.604097366333</t>
   </si>
   <si>
     <t xml:space="preserve">10.7342081069946</t>
@@ -2075,22 +2075,22 @@
     <t xml:space="preserve">10.620361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7179441452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5065135955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.587833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4577217102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3764019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.571569442749</t>
+    <t xml:space="preserve">10.717945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5065126419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5878343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4577207565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3764028549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5715684890747</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089298248291</t>
@@ -2108,37 +2108,37 @@
     <t xml:space="preserve">10.6691522598267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7830009460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9619026184082</t>
+    <t xml:space="preserve">10.7829999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9619045257568</t>
   </si>
   <si>
     <t xml:space="preserve">10.9456396102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2709178924561</t>
+    <t xml:space="preserve">11.2709188461304</t>
   </si>
   <si>
     <t xml:space="preserve">11.1895990371704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5799341201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4172945022583</t>
+    <t xml:space="preserve">11.5799331665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4172954559326</t>
   </si>
   <si>
     <t xml:space="preserve">11.3034467697144</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98606777191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0836505889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4414577484131</t>
+    <t xml:space="preserve">9.9860668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0836496353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4414587020874</t>
   </si>
   <si>
     <t xml:space="preserve">10.7504730224609</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">11.2546548843384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3522386550903</t>
+    <t xml:space="preserve">11.3522396087646</t>
   </si>
   <si>
     <t xml:space="preserve">11.4010314941406</t>
@@ -2174,28 +2174,28 @@
     <t xml:space="preserve">11.0106964111328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5311431884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7751007080078</t>
+    <t xml:space="preserve">11.5311422348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7751016616821</t>
   </si>
   <si>
     <t xml:space="preserve">11.7100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7425727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.019061088562</t>
+    <t xml:space="preserve">11.7425737380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0190601348877</t>
   </si>
   <si>
     <t xml:space="preserve">12.3118124008179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5882987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1979646682739</t>
+    <t xml:space="preserve">12.5882997512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1979637145996</t>
   </si>
   <si>
     <t xml:space="preserve">11.8726863861084</t>
@@ -2204,13 +2204,13 @@
     <t xml:space="preserve">12.00279712677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8076295852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8564205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5961990356445</t>
+    <t xml:space="preserve">11.8076305389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8564224243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5961980819702</t>
   </si>
   <si>
     <t xml:space="preserve">11.954005241394</t>
@@ -2219,22 +2219,22 @@
     <t xml:space="preserve">11.9865322113037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.100380897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1816997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1166458129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2792844772339</t>
+    <t xml:space="preserve">12.1003799438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1817007064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.116644859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2792854309082</t>
   </si>
   <si>
     <t xml:space="preserve">12.4093961715698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5069799423218</t>
+    <t xml:space="preserve">12.5069789886475</t>
   </si>
   <si>
     <t xml:space="preserve">12.4581871032715</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">13.0111618041992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9786348342896</t>
+    <t xml:space="preserve">12.9786338806152</t>
   </si>
   <si>
     <t xml:space="preserve">12.8647861480713</t>
@@ -2258,16 +2258,16 @@
     <t xml:space="preserve">12.7997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6370906829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8810501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1738014221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2713842391968</t>
+    <t xml:space="preserve">12.6370916366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8810510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1738023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2713861465454</t>
   </si>
   <si>
     <t xml:space="preserve">13.3527050018311</t>
@@ -2276,28 +2276,28 @@
     <t xml:space="preserve">13.7267751693726</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8243589401245</t>
+    <t xml:space="preserve">13.8243598937988</t>
   </si>
   <si>
     <t xml:space="preserve">14.052056312561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2309579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2634868621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2146940231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9056787490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6129283905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8080949783325</t>
+    <t xml:space="preserve">14.2309589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634878158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2146949768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9056806564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6129264831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8080959320068</t>
   </si>
   <si>
     <t xml:space="preserve">13.8894147872925</t>
@@ -2309,232 +2309,232 @@
     <t xml:space="preserve">13.8406238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7918300628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0032625198364</t>
+    <t xml:space="preserve">13.7918319702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0032615661621</t>
   </si>
   <si>
     <t xml:space="preserve">13.9544706344604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3448057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1496391296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2472229003906</t>
+    <t xml:space="preserve">14.3448047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1496381759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2472219467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4749174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5579166412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1927242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1595239639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1429252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2757215499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2923192977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3753185272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1097249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2425212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0765247344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2093229293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9935274124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8109292984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3089199066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.05992603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0101251602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9769277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0433263778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3255205154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2259206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3421201705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1761226654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9437265396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0931243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9603261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.358717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591218948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5081167221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5247173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.026725769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.707311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7737112045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.690712928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7405118942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9397087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1057052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3215007781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1721029281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8899097442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3712997436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7032918930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.537296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.387900352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2883033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2717018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0725059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2219038009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1223039627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9895067214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8235101699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7903099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1389045715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9729089736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.873309135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8069105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8607301712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7113332748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4417171478271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4749164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5579166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1927223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1595220565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1429252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2757215499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.375319480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1097240447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2425212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0765237808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2093229293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9935264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8109292984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3089199066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0599269866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0101251602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9769277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.043327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3255186080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2259206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3421211242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1761226654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9437274932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0931243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9603281021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3587188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591218948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5081157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.524715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0267248153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7073125839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7737102508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.690712928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7405138015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9397077560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1057043075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3214998245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1721048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8899097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3713006973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.703293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5372972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.387900352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2883014678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2717008590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0725059509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2219018936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1223030090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9895067214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8235111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7903108596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1389045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9729080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8733100891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8069105148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8607301712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6947317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7113332748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4417181015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4749174118042</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.5745153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.541316986084</t>
+    <t xml:space="preserve">14.5413160324097</t>
   </si>
   <si>
     <t xml:space="preserve">14.4251165390015</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4085178375244</t>
+    <t xml:space="preserve">14.408519744873</t>
   </si>
   <si>
     <t xml:space="preserve">14.3919191360474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4708976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2053022384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.022705078125</t>
+    <t xml:space="preserve">15.4708967208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.205304145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227069854736</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915151596069</t>
@@ -2546,22 +2546,22 @@
     <t xml:space="preserve">13.7777309417725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6449337005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5287342071533</t>
+    <t xml:space="preserve">13.6449346542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445297241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5287351608276</t>
   </si>
   <si>
     <t xml:space="preserve">13.5619354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4125385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1137437820435</t>
+    <t xml:space="preserve">13.4125375747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1137447357178</t>
   </si>
   <si>
     <t xml:space="preserve">13.2797403335571</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">13.362738609314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5121364593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5951328277588</t>
+    <t xml:space="preserve">13.5121374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5951347351074</t>
   </si>
   <si>
     <t xml:space="preserve">13.6117334365845</t>
@@ -2582,49 +2582,49 @@
     <t xml:space="preserve">13.1303434371948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3295402526855</t>
+    <t xml:space="preserve">13.3295392990112</t>
   </si>
   <si>
     <t xml:space="preserve">13.4955368041992</t>
   </si>
   <si>
-    <t xml:space="preserve">13.080545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3129415512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.196741104126</t>
+    <t xml:space="preserve">13.0805444717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3129405975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1967420578003</t>
   </si>
   <si>
     <t xml:space="preserve">12.7983493804932</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4497575759888</t>
+    <t xml:space="preserve">12.4497566223145</t>
   </si>
   <si>
     <t xml:space="preserve">12.3003587722778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7153511047363</t>
+    <t xml:space="preserve">12.7153520584106</t>
   </si>
   <si>
     <t xml:space="preserve">12.4331569671631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5991535186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3335590362549</t>
+    <t xml:space="preserve">12.5991544723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3335580825806</t>
   </si>
   <si>
     <t xml:space="preserve">12.3501586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0679636001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8521680831909</t>
+    <t xml:space="preserve">12.067964553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8521671295166</t>
   </si>
   <si>
     <t xml:space="preserve">11.6695728302002</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">11.7027721405029</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7857704162598</t>
+    <t xml:space="preserve">11.7857694625854</t>
   </si>
   <si>
     <t xml:space="preserve">11.5367746353149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3209800720215</t>
+    <t xml:space="preserve">11.3209781646729</t>
   </si>
   <si>
     <t xml:space="preserve">11.1715812683105</t>
@@ -2657,34 +2657,34 @@
     <t xml:space="preserve">11.221381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8395891189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2088003158569</t>
+    <t xml:space="preserve">10.8395881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2088012695312</t>
   </si>
   <si>
     <t xml:space="preserve">10.6735916137695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6237926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.258599281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1922016143799</t>
+    <t xml:space="preserve">10.6237936019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2585983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1922006607056</t>
   </si>
   <si>
     <t xml:space="preserve">9.97640514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54481315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56141376495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36221790313721</t>
+    <t xml:space="preserve">9.54481410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5614128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">9.62781238555908</t>
@@ -2696,16 +2696,16 @@
     <t xml:space="preserve">9.52821445465088</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0096044540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39541721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.391396522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6071920394897</t>
+    <t xml:space="preserve">10.0096054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39541625976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3913974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6071929931641</t>
   </si>
   <si>
     <t xml:space="preserve">10.3083982467651</t>
@@ -2720,16 +2720,16 @@
     <t xml:space="preserve">10.109203338623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1424016952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0594024658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86020851135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89340591430664</t>
+    <t xml:space="preserve">10.1424026489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0594043731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86020755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89340686798096</t>
   </si>
   <si>
     <t xml:space="preserve">9.69421100616455</t>
@@ -2738,19 +2738,19 @@
     <t xml:space="preserve">9.61121273040771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17962074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27921962738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37881755828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19622039794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29581832885742</t>
+    <t xml:space="preserve">9.17962169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27921867370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37881660461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19622135162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29581737518311</t>
   </si>
   <si>
     <t xml:space="preserve">9.12982177734375</t>
@@ -2759,19 +2759,19 @@
     <t xml:space="preserve">9.42861557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77720928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64441108703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0262050628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5407934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4577951431274</t>
+    <t xml:space="preserve">9.77720832824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64441204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0262041091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5407943725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4577960968018</t>
   </si>
   <si>
     <t xml:space="preserve">10.0760040283203</t>
@@ -2783,37 +2783,37 @@
     <t xml:space="preserve">9.66899490356445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70334434509277</t>
+    <t xml:space="preserve">9.70334339141846</t>
   </si>
   <si>
     <t xml:space="preserve">9.7205171585083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0639991760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0983476638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2529134750366</t>
+    <t xml:space="preserve">10.0639982223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0983467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2529125213623</t>
   </si>
   <si>
     <t xml:space="preserve">9.85791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0811719894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3559579849243</t>
+    <t xml:space="preserve">10.0811729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.35595703125</t>
   </si>
   <si>
     <t xml:space="preserve">10.2700872421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6479158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7681350708008</t>
+    <t xml:space="preserve">10.6479167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7681341171265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9570503234863</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">11.0600938796997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1803121566772</t>
+    <t xml:space="preserve">11.1803131103516</t>
   </si>
   <si>
     <t xml:space="preserve">11.0944423675537</t>
@@ -2837,16 +2837,16 @@
     <t xml:space="preserve">10.9742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.991397857666</t>
+    <t xml:space="preserve">10.9913988113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.0296506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0124769210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.390305519104</t>
+    <t xml:space="preserve">10.0124759674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3903064727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1498689651489</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">10.1326951980591</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97812747955322</t>
+    <t xml:space="preserve">9.97812843322754</t>
   </si>
   <si>
     <t xml:space="preserve">9.87508392333984</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">10.2872610092163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2013921737671</t>
+    <t xml:space="preserve">10.2013912200928</t>
   </si>
   <si>
     <t xml:space="preserve">10.3044357299805</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">10.1842164993286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0468254089355</t>
+    <t xml:space="preserve">10.0468244552612</t>
   </si>
   <si>
     <t xml:space="preserve">10.5620460510254</t>
@@ -2888,16 +2888,16 @@
     <t xml:space="preserve">10.424654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7166128158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.459002494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5105237960815</t>
+    <t xml:space="preserve">10.4418287277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5105228424072</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509613037109</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">10.6822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4933500289917</t>
+    <t xml:space="preserve">10.493350982666</t>
   </si>
   <si>
     <t xml:space="preserve">10.1155204772949</t>
@@ -2918,10 +2918,10 @@
     <t xml:space="preserve">9.61747264862061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37703704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51442813873291</t>
+    <t xml:space="preserve">9.37703609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51442909240723</t>
   </si>
   <si>
     <t xml:space="preserve">9.63464736938477</t>
@@ -2951,13 +2951,13 @@
     <t xml:space="preserve">9.25681781768799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46290683746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0850772857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54877758026123</t>
+    <t xml:space="preserve">9.4629077911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08507633209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54877662658691</t>
   </si>
   <si>
     <t xml:space="preserve">9.56595039367676</t>
@@ -2969,19 +2969,19 @@
     <t xml:space="preserve">9.65182113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82356071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3387832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5963945388794</t>
+    <t xml:space="preserve">9.823561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3387842178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5963954925537</t>
   </si>
   <si>
     <t xml:space="preserve">10.8540058135986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4550981521606</t>
+    <t xml:space="preserve">11.4550971984863</t>
   </si>
   <si>
     <t xml:space="preserve">11.2661828994751</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">11.0429201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8883533477783</t>
+    <t xml:space="preserve">10.8883543014526</t>
   </si>
   <si>
     <t xml:space="preserve">10.9398756027222</t>
@@ -2999,13 +2999,13 @@
     <t xml:space="preserve">10.8196573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8024835586548</t>
+    <t xml:space="preserve">10.8024826049805</t>
   </si>
   <si>
     <t xml:space="preserve">11.3692274093628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4379224777222</t>
+    <t xml:space="preserve">11.4379234313965</t>
   </si>
   <si>
     <t xml:space="preserve">12.0733642578125</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">12.5027151107788</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2966260910034</t>
+    <t xml:space="preserve">12.2966251373291</t>
   </si>
   <si>
     <t xml:space="preserve">12.0561895370483</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">11.7470560073853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7127094268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9703197479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9359703063965</t>
+    <t xml:space="preserve">11.7127084732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9703187942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9359712600708</t>
   </si>
   <si>
     <t xml:space="preserve">12.0046663284302</t>
@@ -3044,28 +3044,28 @@
     <t xml:space="preserve">11.8157529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2279300689697</t>
+    <t xml:space="preserve">12.227931022644</t>
   </si>
   <si>
     <t xml:space="preserve">12.3653221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4340190887451</t>
+    <t xml:space="preserve">12.4340181350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.3996696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3137998580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5198888778687</t>
+    <t xml:space="preserve">12.3138008117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.519889831543</t>
   </si>
   <si>
     <t xml:space="preserve">12.485541343689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6401071548462</t>
+    <t xml:space="preserve">12.6401081085205</t>
   </si>
   <si>
     <t xml:space="preserve">12.2451038360596</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">12.1764087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1592330932617</t>
+    <t xml:space="preserve">12.159234046936</t>
   </si>
   <si>
     <t xml:space="preserve">12.1077117919922</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">12.9148921966553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0694589614868</t>
+    <t xml:space="preserve">13.0694599151611</t>
   </si>
   <si>
     <t xml:space="preserve">13.1038074493408</t>
@@ -3110,58 +3110,58 @@
     <t xml:space="preserve">13.1896772384644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6705513000488</t>
+    <t xml:space="preserve">13.6705503463745</t>
   </si>
   <si>
     <t xml:space="preserve">13.3442440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6362037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6018543243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.550332069397</t>
+    <t xml:space="preserve">13.6362028121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6018552780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5503330230713</t>
   </si>
   <si>
     <t xml:space="preserve">13.5675067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4644632339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3957653045654</t>
+    <t xml:space="preserve">13.4644622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3957672119141</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.619029045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0827283859253</t>
+    <t xml:space="preserve">13.6190280914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.082727432251</t>
   </si>
   <si>
     <t xml:space="preserve">13.6877250671387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7048988342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7220735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8766403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6151237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7353429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6494722366333</t>
+    <t xml:space="preserve">13.7048997879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7220726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8766393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6151247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7353420257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6494731903076</t>
   </si>
   <si>
     <t xml:space="preserve">14.8040390014648</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">14.6838207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7868642807007</t>
+    <t xml:space="preserve">14.7868633270264</t>
   </si>
   <si>
     <t xml:space="preserve">14.7181673049927</t>
@@ -3182,28 +3182,28 @@
     <t xml:space="preserve">15.0616502761841</t>
   </si>
   <si>
-    <t xml:space="preserve">15.387957572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1990423202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2505664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818685531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.216215133667</t>
+    <t xml:space="preserve">15.3879566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2505645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2162160873413</t>
   </si>
   <si>
     <t xml:space="preserve">14.9757795333862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9242553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4262094497681</t>
+    <t xml:space="preserve">14.9242563247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4262084960938</t>
   </si>
   <si>
     <t xml:space="preserve">14.3918619155884</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">14.9586057662964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5464296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1131706237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1303462982178</t>
+    <t xml:space="preserve">14.5464286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1131715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1303472518921</t>
   </si>
   <si>
     <t xml:space="preserve">14.9929523468018</t>
@@ -3227,34 +3227,34 @@
     <t xml:space="preserve">15.2677392959595</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4223041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9031801223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9375267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1436138153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.851655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547004699707</t>
+    <t xml:space="preserve">15.4223051071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9031782150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9375276565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1436157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8516550064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9546995162964</t>
   </si>
   <si>
     <t xml:space="preserve">15.7829599380493</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7142629623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5253486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5596990585327</t>
+    <t xml:space="preserve">15.7142639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5253496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5596981048584</t>
   </si>
   <si>
     <t xml:space="preserve">14.8383884429932</t>
@@ -3263,34 +3263,34 @@
     <t xml:space="preserve">14.4605579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3059902191162</t>
+    <t xml:space="preserve">14.3059921264648</t>
   </si>
   <si>
     <t xml:space="preserve">14.2888164520264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5120782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6323003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7009954452515</t>
+    <t xml:space="preserve">14.5120792388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6322994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7009963989258</t>
   </si>
   <si>
     <t xml:space="preserve">14.5807752609253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5292549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3746871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1431255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2678136825562</t>
+    <t xml:space="preserve">14.5292539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3746862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1431245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2678127288818</t>
   </si>
   <si>
     <t xml:space="preserve">14.321249961853</t>
@@ -3302,10 +3302,10 @@
     <t xml:space="preserve">14.6774997711182</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6062498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0540618896484</t>
+    <t xml:space="preserve">14.6062488555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0540628433228</t>
   </si>
   <si>
     <t xml:space="preserve">14.0362501144409</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">14.0184373855591</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0006256103516</t>
+    <t xml:space="preserve">14.0006246566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.733437538147</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">13.875937461853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2856254577637</t>
+    <t xml:space="preserve">14.285626411438</t>
   </si>
   <si>
     <t xml:space="preserve">14.0896873474121</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">14.1609373092651</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1253118515015</t>
+    <t xml:space="preserve">14.1253128051758</t>
   </si>
   <si>
     <t xml:space="preserve">14.4459371566772</t>
@@ -3347,13 +3347,13 @@
     <t xml:space="preserve">14.178750038147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9828119277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9293756484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6978130340576</t>
+    <t xml:space="preserve">13.9828128814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9293746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6978120803833</t>
   </si>
   <si>
     <t xml:space="preserve">13.6799993515015</t>
@@ -3368,16 +3368,16 @@
     <t xml:space="preserve">13.5731248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8403129577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8581247329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9115629196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4840621948242</t>
+    <t xml:space="preserve">13.8403120040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8581256866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9115619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4840631484985</t>
   </si>
   <si>
     <t xml:space="preserve">13.1278123855591</t>
@@ -3392,13 +3392,13 @@
     <t xml:space="preserve">13.8046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7690629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8225002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3034372329712</t>
+    <t xml:space="preserve">13.7690620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8225011825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3034362792969</t>
   </si>
   <si>
     <t xml:space="preserve">14.3924999237061</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">14.624062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4993753433228</t>
+    <t xml:space="preserve">14.4993762969971</t>
   </si>
   <si>
     <t xml:space="preserve">14.5349998474121</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">14.25</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0718755722046</t>
+    <t xml:space="preserve">14.0718746185303</t>
   </si>
   <si>
     <t xml:space="preserve">13.359375</t>
@@ -3431,22 +3431,22 @@
     <t xml:space="preserve">13.5018749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5196876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2321863174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6265630722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812496185303</t>
+    <t xml:space="preserve">13.5196886062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2321872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6265621185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812505722046</t>
   </si>
   <si>
     <t xml:space="preserve">13.0565624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1099996566772</t>
+    <t xml:space="preserve">13.1100006103516</t>
   </si>
   <si>
     <t xml:space="preserve">12.842812538147</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">12.8249998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7181253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221881866455</t>
+    <t xml:space="preserve">12.7181243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221872329712</t>
   </si>
   <si>
     <t xml:space="preserve">12.397500038147</t>
@@ -3479,25 +3479,25 @@
     <t xml:space="preserve">12.4865627288818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2906255722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2193756103516</t>
+    <t xml:space="preserve">12.2906246185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2193746566772</t>
   </si>
   <si>
     <t xml:space="preserve">12.2550001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1481256484985</t>
+    <t xml:space="preserve">12.1481246948242</t>
   </si>
   <si>
     <t xml:space="preserve">12.1659374237061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1303119659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165630340576</t>
+    <t xml:space="preserve">12.1303129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165620803833</t>
   </si>
   <si>
     <t xml:space="preserve">11.578125</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">11.3287506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2931261062622</t>
+    <t xml:space="preserve">11.2931251525879</t>
   </si>
   <si>
     <t xml:space="preserve">11.1328125</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">10.9012498855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9190635681152</t>
+    <t xml:space="preserve">10.9190626144409</t>
   </si>
   <si>
     <t xml:space="preserve">11.061562538147</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">11.0971879959106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1684379577637</t>
+    <t xml:space="preserve">11.1684370040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.204062461853</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">11.4534368515015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8631238937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0768756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453130722046</t>
+    <t xml:space="preserve">11.8631248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0768747329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453121185303</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809375762939</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">11.9878120422363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2015619277954</t>
+    <t xml:space="preserve">12.2015628814697</t>
   </si>
   <si>
     <t xml:space="preserve">12.6468753814697</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">12.7003126144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3618745803833</t>
+    <t xml:space="preserve">12.3618755340576</t>
   </si>
   <si>
     <t xml:space="preserve">12.3440628051758</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">12.094687461853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0590620040894</t>
+    <t xml:space="preserve">12.0590629577637</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056247711182</t>
@@ -3644,19 +3644,19 @@
     <t xml:space="preserve">11.4178123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4356250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7384376525879</t>
+    <t xml:space="preserve">11.4356260299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7384386062622</t>
   </si>
   <si>
     <t xml:space="preserve">11.7562494277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5959386825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274993896484</t>
+    <t xml:space="preserve">11.5959377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8275003433228</t>
   </si>
   <si>
     <t xml:space="preserve">11.7206249237061</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">11.2396869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5425004959106</t>
+    <t xml:space="preserve">11.5424995422363</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028131484985</t>
@@ -3686,13 +3686,13 @@
     <t xml:space="preserve">11.9700002670288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5246877670288</t>
+    <t xml:space="preserve">11.5246868133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.9724998474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1149988174438</t>
+    <t xml:space="preserve">11.1149997711182</t>
   </si>
   <si>
     <t xml:space="preserve">11.3382139205933</t>
@@ -70489,7 +70489,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6910763889</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>49753</v>
@@ -70498,7 +70498,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="D2528" t="n">
-        <v>7.26999998092651</v>
+        <v>7.26000022888184</v>
       </c>
       <c r="E2528" t="n">
         <v>7.44999980926514</v>
@@ -70510,6 +70510,32 @@
         <v>1478</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6910532407</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>189212</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>7.48999977111816</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>7.26999998092651</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>7.28999996185303</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>7.46000003814697</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="1482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="1483">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04141759872437</t>
+    <t xml:space="preserve">4.04141712188721</t>
   </si>
   <si>
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447843551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9397885799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82799816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78057146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943140983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75685811042786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74330830574036</t>
+    <t xml:space="preserve">4.02447891235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93978881835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82799744606018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78057098388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943164825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75685858726501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74330806732178</t>
   </si>
   <si>
     <t xml:space="preserve">3.80089712142944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77040863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571805953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66539287567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56376433372498</t>
+    <t xml:space="preserve">3.77040839195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66539263725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56376457214355</t>
   </si>
   <si>
     <t xml:space="preserve">3.65184211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72636985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70265674591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65861773490906</t>
+    <t xml:space="preserve">3.72637009620667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70265650749207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65861749649048</t>
   </si>
   <si>
     <t xml:space="preserve">3.6924934387207</t>
@@ -107,16 +107,16 @@
     <t xml:space="preserve">3.58408999443054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49601197242737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46213626861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51633739471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38760924339294</t>
+    <t xml:space="preserve">3.49601173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46213603019714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51633787155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38760852813721</t>
   </si>
   <si>
     <t xml:space="preserve">3.40793442726135</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">3.50956249237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55698871612549</t>
+    <t xml:space="preserve">3.55698943138123</t>
   </si>
   <si>
     <t xml:space="preserve">3.56715226173401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61119174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57731533050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54682660102844</t>
+    <t xml:space="preserve">3.61119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57731485366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54682612419128</t>
   </si>
   <si>
     <t xml:space="preserve">3.52650094032288</t>
@@ -146,40 +146,40 @@
     <t xml:space="preserve">3.50278759002686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56037712097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58070230484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60102796554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54343843460083</t>
+    <t xml:space="preserve">3.5603768825531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58070206642151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60102772712708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54343867301941</t>
   </si>
   <si>
     <t xml:space="preserve">3.57053971290588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64506721496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78734707832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.841548204422</t>
+    <t xml:space="preserve">3.64506769180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78734636306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84154891967773</t>
   </si>
   <si>
     <t xml:space="preserve">3.8652617931366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85171127319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92962694168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93640160560608</t>
+    <t xml:space="preserve">3.85171103477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92962670326233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93640184402466</t>
   </si>
   <si>
     <t xml:space="preserve">3.91607546806335</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">3.90252542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89575052261353</t>
+    <t xml:space="preserve">3.89575028419495</t>
   </si>
   <si>
     <t xml:space="preserve">3.92285108566284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90930032730103</t>
+    <t xml:space="preserve">3.9093005657196</t>
   </si>
   <si>
     <t xml:space="preserve">3.97027802467346</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">3.87881183624268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85848689079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94317650794983</t>
+    <t xml:space="preserve">3.85848641395569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94317674636841</t>
   </si>
   <si>
     <t xml:space="preserve">3.8991379737854</t>
@@ -215,64 +215,64 @@
     <t xml:space="preserve">3.94656443595886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95672750473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9635021686554</t>
+    <t xml:space="preserve">3.95672702789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96350145339966</t>
   </si>
   <si>
     <t xml:space="preserve">3.91268849372864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9736647605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91946339607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87203669548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88704776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87291288375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85877919197083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83757567405701</t>
+    <t xml:space="preserve">3.97366452217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91946315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8720371723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88704824447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8729133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85877799987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8375768661499</t>
   </si>
   <si>
     <t xml:space="preserve">3.86231231689453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87644672393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89411497116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9011824131012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058184623718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94358611106873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95418810844421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96125555038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01426029205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02486228942871</t>
+    <t xml:space="preserve">3.87644696235657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89411568641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90118288993835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89058232307434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94358658790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95418739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96125507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01426124572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02486181259155</t>
   </si>
   <si>
     <t xml:space="preserve">4.08846759796143</t>
@@ -281,10 +281,10 @@
     <t xml:space="preserve">4.05666446685791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03899574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305820465088</t>
+    <t xml:space="preserve">4.03899669647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9930579662323</t>
   </si>
   <si>
     <t xml:space="preserve">4.00719356536865</t>
@@ -296,94 +296,91 @@
     <t xml:space="preserve">3.97185659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80223965644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78103709220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75630187988281</t>
+    <t xml:space="preserve">3.8022403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7810378074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75630140304565</t>
   </si>
   <si>
     <t xml:space="preserve">3.74923396110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90471696853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9223849773407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065450668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03546190261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7598352432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80930709838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83050870895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86937928199768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82344174385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80577349662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84111070632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8517107963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81637477874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8658459186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89764904975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93651962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90825057029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91531753540039</t>
+    <t xml:space="preserve">3.90471649169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92238473892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065379142761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03546237945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75983595848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80930685997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83050894737244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86937975883484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82344150543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80577325820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84110927581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8163743019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86584568023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89764881134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93651914596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90825009346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91531705856323</t>
   </si>
   <si>
     <t xml:space="preserve">3.97892379760742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00012588500977</t>
+    <t xml:space="preserve">4.00012540817261</t>
   </si>
   <si>
     <t xml:space="preserve">4.02132749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95772171020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84464335441589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81284070014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77043652534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690340042114</t>
+    <t xml:space="preserve">3.95772099494934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84464383125305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81284022331238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77043676376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690244674683</t>
   </si>
   <si>
     <t xml:space="preserve">3.76336884498596</t>
@@ -392,139 +389,139 @@
     <t xml:space="preserve">3.74570059776306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7244987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77397060394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78810548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81990814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72803258895874</t>
+    <t xml:space="preserve">3.72449851036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77397012710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78810477256775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.819908618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72803235054016</t>
   </si>
   <si>
     <t xml:space="preserve">3.73863339424133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73156642913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73509955406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65382528305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6396906375885</t>
+    <t xml:space="preserve">3.7315661907196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73509931564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65382504463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63969016075134</t>
   </si>
   <si>
     <t xml:space="preserve">3.66089224815369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61848783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61142110824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62555575370789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61495423316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64675760269165</t>
+    <t xml:space="preserve">3.61848855018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61142086982727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62555551528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61495471000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64675712585449</t>
   </si>
   <si>
     <t xml:space="preserve">3.74216747283936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91885042190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98599076271057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9965922832489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87998032569885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88351440429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79517245292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82697510719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79163813591003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8481776714325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71036338806152</t>
+    <t xml:space="preserve">3.91885161399841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98599123954773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99659299850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87998056411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8835141658783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7951717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82697534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79163837432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84817743301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71036434173584</t>
   </si>
   <si>
     <t xml:space="preserve">3.85524487495422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03192853927612</t>
+    <t xml:space="preserve">4.03192901611328</t>
   </si>
   <si>
     <t xml:space="preserve">4.04252958297729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08493328094482</t>
+    <t xml:space="preserve">4.08493375778198</t>
   </si>
   <si>
     <t xml:space="preserve">4.09906911849976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05313062667847</t>
+    <t xml:space="preserve">4.05313110351562</t>
   </si>
   <si>
     <t xml:space="preserve">4.04959726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09200143814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10966968536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0778660774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07433319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04606342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06373262405396</t>
+    <t xml:space="preserve">4.09200191497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10966920852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07786655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07433366775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04606294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0637321472168</t>
   </si>
   <si>
     <t xml:space="preserve">4.10613632202148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10260200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13440561294556</t>
+    <t xml:space="preserve">4.10260248184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13440465927124</t>
   </si>
   <si>
     <t xml:space="preserve">4.12733793258667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16974258422852</t>
+    <t xml:space="preserve">4.16974210739136</t>
   </si>
   <si>
     <t xml:space="preserve">4.18387746810913</t>
@@ -533,40 +530,40 @@
     <t xml:space="preserve">4.15914154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24041604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21568059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27575302124023</t>
+    <t xml:space="preserve">4.24041652679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21568012237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27575254440308</t>
   </si>
   <si>
     <t xml:space="preserve">4.34642648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36762809753418</t>
+    <t xml:space="preserve">4.36762857437134</t>
   </si>
   <si>
     <t xml:space="preserve">4.35349321365356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31108951568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30402231216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38176250457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50897598266602</t>
+    <t xml:space="preserve">4.31108903884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30402183532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38176345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5089750289917</t>
   </si>
   <si>
     <t xml:space="preserve">4.72806406021118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91181516647339</t>
+    <t xml:space="preserve">4.91181468963623</t>
   </si>
   <si>
     <t xml:space="preserve">4.94715213775635</t>
@@ -575,31 +572,31 @@
     <t xml:space="preserve">5.19450950622559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22277927398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22984600067139</t>
+    <t xml:space="preserve">5.22277879714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22984552383423</t>
   </si>
   <si>
     <t xml:space="preserve">5.2263126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09203195571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07436418533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08496570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1167688369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10616779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1521053314209</t>
+    <t xml:space="preserve">5.09203338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07436466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08496522903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11676788330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10616731643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15210580825806</t>
   </si>
   <si>
     <t xml:space="preserve">5.15917301177979</t>
@@ -608,34 +605,34 @@
     <t xml:space="preserve">5.1733078956604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1909761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14503812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13090324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2475152015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26871728897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59734916687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51254034042358</t>
+    <t xml:space="preserve">5.19097566604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14503860473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13090372085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24751472473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26871633529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59734964370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51254081726074</t>
   </si>
   <si>
     <t xml:space="preserve">5.35705900192261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47720384597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37119293212891</t>
+    <t xml:space="preserve">5.47720336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37119340896606</t>
   </si>
   <si>
     <t xml:space="preserve">5.44186687469482</t>
@@ -644,28 +641,28 @@
     <t xml:space="preserve">5.53020906448364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61199712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65216064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6886739730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6229510307312</t>
+    <t xml:space="preserve">5.61199808120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65216159820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68867349624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62295150756836</t>
   </si>
   <si>
     <t xml:space="preserve">5.619300365448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59739255905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42213201522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41848087310791</t>
+    <t xml:space="preserve">5.59739208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42213153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41848039627075</t>
   </si>
   <si>
     <t xml:space="preserve">5.55357694625854</t>
@@ -674,16 +671,16 @@
     <t xml:space="preserve">5.56087923049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49880886077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46229553222656</t>
+    <t xml:space="preserve">5.49880790710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4622950553894</t>
   </si>
   <si>
     <t xml:space="preserve">5.55722856521606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45499324798584</t>
+    <t xml:space="preserve">5.45499277114868</t>
   </si>
   <si>
     <t xml:space="preserve">5.36736249923706</t>
@@ -692,16 +689,16 @@
     <t xml:space="preserve">5.37466478347778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43308544158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40387487411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47690057754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4476900100708</t>
+    <t xml:space="preserve">5.43308591842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40387439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47690010070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44769048690796</t>
   </si>
   <si>
     <t xml:space="preserve">5.48055219650269</t>
@@ -710,40 +707,40 @@
     <t xml:space="preserve">5.49515676498413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54627370834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60104370117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41117715835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51341342926025</t>
+    <t xml:space="preserve">5.54627466201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60104322433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41117763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5134129524231</t>
   </si>
   <si>
     <t xml:space="preserve">5.54992580413818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45134115219116</t>
+    <t xml:space="preserve">5.45134210586548</t>
   </si>
   <si>
     <t xml:space="preserve">5.61564874649048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50611019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34545516967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37101364135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31259298324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28703451156616</t>
+    <t xml:space="preserve">5.50611066818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34545469284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37101411819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31259346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.287034034729</t>
   </si>
   <si>
     <t xml:space="preserve">5.15558862686157</t>
@@ -752,7 +749,7 @@
     <t xml:space="preserve">5.12637853622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2724289894104</t>
+    <t xml:space="preserve">5.27242946624756</t>
   </si>
   <si>
     <t xml:space="preserve">5.31989622116089</t>
@@ -761,34 +758,34 @@
     <t xml:space="preserve">5.14098358154297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40752649307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38926982879639</t>
+    <t xml:space="preserve">5.40752601623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38927030563354</t>
   </si>
   <si>
     <t xml:space="preserve">5.37831592559814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24321985244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46959781646729</t>
+    <t xml:space="preserve">5.24321889877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46959733963013</t>
   </si>
   <si>
     <t xml:space="preserve">5.41482877731323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42578220367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44038724899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48420381546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35275745391846</t>
+    <t xml:space="preserve">5.42578315734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44038772583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48420238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3527569770813</t>
   </si>
   <si>
     <t xml:space="preserve">5.48785400390625</t>
@@ -797,16 +794,16 @@
     <t xml:space="preserve">5.50245904922485</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57183408737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57913589477539</t>
+    <t xml:space="preserve">5.57183265686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57913494110107</t>
   </si>
   <si>
     <t xml:space="preserve">5.56453132629395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52071571350098</t>
+    <t xml:space="preserve">5.52071619033813</t>
   </si>
   <si>
     <t xml:space="preserve">5.53897190093994</t>
@@ -818,7 +815,7 @@
     <t xml:space="preserve">5.58643817901611</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57548522949219</t>
+    <t xml:space="preserve">5.57548475265503</t>
   </si>
   <si>
     <t xml:space="preserve">5.50976181030273</t>
@@ -839,64 +836,64 @@
     <t xml:space="preserve">5.79456090927124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92965793609619</t>
+    <t xml:space="preserve">5.92965745925903</t>
   </si>
   <si>
     <t xml:space="preserve">5.94426298141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99903249740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93695974349976</t>
+    <t xml:space="preserve">5.99903154373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93696069717407</t>
   </si>
   <si>
     <t xml:space="preserve">5.98807716369629</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83107376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88584232330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83472442626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95886754989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76900148391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91140174865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83837556838989</t>
+    <t xml:space="preserve">5.83107328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88584327697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83472394943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9588680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76900243759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140079498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83837604522705</t>
   </si>
   <si>
     <t xml:space="preserve">5.84202671051025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87123727798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.783607006073</t>
+    <t xml:space="preserve">5.87123775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78360748291016</t>
   </si>
   <si>
     <t xml:space="preserve">5.85298109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7032790184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82742214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86393451690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75439643859863</t>
+    <t xml:space="preserve">5.70327854156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82742261886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8639349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75439691543579</t>
   </si>
   <si>
     <t xml:space="preserve">5.72883796691895</t>
@@ -905,25 +902,25 @@
     <t xml:space="preserve">5.68502235412598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66676664352417</t>
+    <t xml:space="preserve">5.66676616668701</t>
   </si>
   <si>
     <t xml:space="preserve">5.88949346542358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78725862503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77995634078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73614025115967</t>
+    <t xml:space="preserve">5.78725814819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77995538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73614072799683</t>
   </si>
   <si>
     <t xml:space="preserve">5.60834550857544</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63025426864624</t>
+    <t xml:space="preserve">5.63025331497192</t>
   </si>
   <si>
     <t xml:space="preserve">5.53532075881958</t>
@@ -932,22 +929,22 @@
     <t xml:space="preserve">5.76169919967651</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6266016960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68137264251709</t>
+    <t xml:space="preserve">5.62660217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68137168884277</t>
   </si>
   <si>
     <t xml:space="preserve">5.73979187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76535034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80916547775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80551433563232</t>
+    <t xml:space="preserve">5.76535081863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80916595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80551385879517</t>
   </si>
   <si>
     <t xml:space="preserve">5.82377099990845</t>
@@ -959,46 +956,46 @@
     <t xml:space="preserve">5.82011938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90409898757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92235469818115</t>
+    <t xml:space="preserve">5.90409803390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600679397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92235422134399</t>
   </si>
   <si>
     <t xml:space="preserve">5.95156478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02459049224854</t>
+    <t xml:space="preserve">6.02459096908569</t>
   </si>
   <si>
     <t xml:space="preserve">6.06110334396362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00998544692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09031295776367</t>
+    <t xml:space="preserve">6.00998449325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09031343460083</t>
   </si>
   <si>
     <t xml:space="preserve">6.2290620803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18524646759033</t>
+    <t xml:space="preserve">6.18524599075317</t>
   </si>
   <si>
     <t xml:space="preserve">6.03189325332642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03919553756714</t>
+    <t xml:space="preserve">6.0391960144043</t>
   </si>
   <si>
     <t xml:space="preserve">6.04649829864502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25096893310547</t>
+    <t xml:space="preserve">6.25096988677979</t>
   </si>
   <si>
     <t xml:space="preserve">6.20715379714966</t>
@@ -1010,10 +1007,10 @@
     <t xml:space="preserve">6.12682628631592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79821252822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72518634796143</t>
+    <t xml:space="preserve">5.79821157455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72518682479858</t>
   </si>
   <si>
     <t xml:space="preserve">5.96617031097412</t>
@@ -1022,31 +1019,31 @@
     <t xml:space="preserve">6.00268316268921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8931450843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84932994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97347259521484</t>
+    <t xml:space="preserve">5.89314413070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84933042526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.973473072052</t>
   </si>
   <si>
     <t xml:space="preserve">5.99538087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11952352523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15603685379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10491752624512</t>
+    <t xml:space="preserve">6.1195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15603590011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10491800308228</t>
   </si>
   <si>
     <t xml:space="preserve">5.98077487945557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90044736862183</t>
+    <t xml:space="preserve">5.90044689178467</t>
   </si>
   <si>
     <t xml:space="preserve">6.14873361587524</t>
@@ -1058,13 +1055,13 @@
     <t xml:space="preserve">6.05380058288574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07570838928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08301067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17794370651245</t>
+    <t xml:space="preserve">6.07570791244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08301019668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17794322967529</t>
   </si>
   <si>
     <t xml:space="preserve">6.17064046859741</t>
@@ -1073,22 +1070,25 @@
     <t xml:space="preserve">6.2436671257019</t>
   </si>
   <si>
+    <t xml:space="preserve">6.28017997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38636541366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31810283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23467063903809</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.28017902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38636589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31810283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23467111587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15882301330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2725944519043</t>
+    <t xml:space="preserve">6.15882349014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27259397506714</t>
   </si>
   <si>
     <t xml:space="preserve">6.26500988006592</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">6.21191596984863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18157625198364</t>
+    <t xml:space="preserve">6.18157720565796</t>
   </si>
   <si>
     <t xml:space="preserve">6.15123748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0298810005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05263614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25742530822754</t>
+    <t xml:space="preserve">6.02988243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05263566970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25742435455322</t>
   </si>
   <si>
     <t xml:space="preserve">6.22708606719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.249840259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29534816741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3711953163147</t>
+    <t xml:space="preserve">6.24983978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29534864425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37119579315186</t>
   </si>
   <si>
     <t xml:space="preserve">6.18916177749634</t>
@@ -1130,22 +1130,22 @@
     <t xml:space="preserve">6.1664080619812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2043309211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0147123336792</t>
+    <t xml:space="preserve">6.20433187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01471138000488</t>
   </si>
   <si>
     <t xml:space="preserve">6.04505157470703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00712728500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98437356948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12089872360229</t>
+    <t xml:space="preserve">6.00712823867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98437309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12089920043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.13606882095337</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">6.09055995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96161985397339</t>
+    <t xml:space="preserve">5.96161937713623</t>
   </si>
   <si>
     <t xml:space="preserve">6.08297634124756</t>
@@ -1166,28 +1166,28 @@
     <t xml:space="preserve">6.14365386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1057300567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06022167205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99954319000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95403480529785</t>
+    <t xml:space="preserve">6.10572957992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06022071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99954271316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95403528213501</t>
   </si>
   <si>
     <t xml:space="preserve">5.93886470794678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06780576705933</t>
+    <t xml:space="preserve">6.06780624389648</t>
   </si>
   <si>
     <t xml:space="preserve">5.91611099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94644975662231</t>
+    <t xml:space="preserve">5.94644927978516</t>
   </si>
   <si>
     <t xml:space="preserve">5.87818717956543</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">6.02229738235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9919581413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86301708221436</t>
+    <t xml:space="preserve">5.99195861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86301755905151</t>
   </si>
   <si>
     <t xml:space="preserve">6.07539033889771</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">6.24225521087646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47738265991211</t>
+    <t xml:space="preserve">6.47738218307495</t>
   </si>
   <si>
     <t xml:space="preserve">6.63666248321533</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">6.56081438064575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6063232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55323028564453</t>
+    <t xml:space="preserve">6.60632371902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55323076248169</t>
   </si>
   <si>
     <t xml:space="preserve">6.65183258056641</t>
@@ -1241,22 +1241,22 @@
     <t xml:space="preserve">6.48496770858765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6139087677002</t>
+    <t xml:space="preserve">6.61390829086304</t>
   </si>
   <si>
     <t xml:space="preserve">6.66700172424316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59873867034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34085655212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39395046234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41670417785645</t>
+    <t xml:space="preserve">6.59873914718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34085702896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39395141601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41670513153076</t>
   </si>
   <si>
     <t xml:space="preserve">6.4242901802063</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">6.54564619064331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56839942932129</t>
+    <t xml:space="preserve">6.56839990615845</t>
   </si>
   <si>
     <t xml:space="preserve">6.44704341888428</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">6.21950101852417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40912008285522</t>
+    <t xml:space="preserve">6.40911912918091</t>
   </si>
   <si>
     <t xml:space="preserve">6.32568740844727</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">6.6745867729187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74284982681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75043439865112</t>
+    <t xml:space="preserve">6.7428503036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75043392181396</t>
   </si>
   <si>
     <t xml:space="preserve">6.62149333953857</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">6.37878084182739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36361169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46979761123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51530694961548</t>
+    <t xml:space="preserve">6.36361122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46979856491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51530599594116</t>
   </si>
   <si>
     <t xml:space="preserve">6.31051778793335</t>
@@ -1325,76 +1325,76 @@
     <t xml:space="preserve">6.35602712631226</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19674634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40153503417969</t>
+    <t xml:space="preserve">6.19674682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40153408050537</t>
   </si>
   <si>
     <t xml:space="preserve">6.72009468078613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7580189704895</t>
+    <t xml:space="preserve">6.75801849365234</t>
   </si>
   <si>
     <t xml:space="preserve">6.80352735519409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78835868835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73526430130005</t>
+    <t xml:space="preserve">6.78835725784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73526382446289</t>
   </si>
   <si>
     <t xml:space="preserve">6.84903526306152</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86420583724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81111097335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8414511680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81869649887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90212965011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9931468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89454460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94005346298218</t>
+    <t xml:space="preserve">6.86420488357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81111145019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84145164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81869745254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90213012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99314641952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89454364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94005250930786</t>
   </si>
   <si>
     <t xml:space="preserve">7.05382394790649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10691738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15242624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.114501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01589965820312</t>
+    <t xml:space="preserve">7.10691785812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15242671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11450242996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01590013504028</t>
   </si>
   <si>
     <t xml:space="preserve">7.08416318893433</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04623889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09174776077271</t>
+    <t xml:space="preserve">7.0462384223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09174728393555</t>
   </si>
   <si>
     <t xml:space="preserve">7.39513826370239</t>
@@ -1403,46 +1403,46 @@
     <t xml:space="preserve">7.35721445083618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34204578399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1220874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13725709915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12967109680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25102710723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22827434539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2055196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19793462753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16759490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37996816635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43306255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49374008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53924798965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54683399200439</t>
+    <t xml:space="preserve">7.34204483032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12208652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13725662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12967157363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25102806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22827339172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20551872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1979341506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16759538650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37996912002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43306159973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49374103546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53924894332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54683351516724</t>
   </si>
   <si>
     <t xml:space="preserve">7.75162172317505</t>
@@ -1454,49 +1454,49 @@
     <t xml:space="preserve">7.64543533325195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69094562530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57717275619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45581531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51649522781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59992599487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50890874862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56200361251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58475637435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5544171333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47857093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47098541259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44823122024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7061128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88814783096313</t>
+    <t xml:space="preserve">7.69094371795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57717227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45581674575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5164942741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59992694854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50890970230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56200265884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58475780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55441761016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47857046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47098636627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44823169708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70611333847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331602096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88814735412598</t>
   </si>
   <si>
     <t xml:space="preserve">8.25221633911133</t>
@@ -1514,16 +1514,16 @@
     <t xml:space="preserve">8.41908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11876964569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08742237091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9306902885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04040241241455</t>
+    <t xml:space="preserve">8.1187686920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08742332458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93068933486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04040336608887</t>
   </si>
   <si>
     <t xml:space="preserve">7.9620361328125</t>
@@ -1532,31 +1532,31 @@
     <t xml:space="preserve">8.25982856750488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02472972869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86799669265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7347731590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83664989471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82097673416138</t>
+    <t xml:space="preserve">8.0247278213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86799621582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73477268218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83665037155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82097625732422</t>
   </si>
   <si>
     <t xml:space="preserve">7.91501617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97771024703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07175064086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05607604980469</t>
+    <t xml:space="preserve">7.97770833969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07174873352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05607509613037</t>
   </si>
   <si>
     <t xml:space="preserve">7.85232257843018</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">8.40088844299316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46358108520508</t>
+    <t xml:space="preserve">8.46358203887939</t>
   </si>
   <si>
     <t xml:space="preserve">8.6203145980835</t>
@@ -1577,40 +1577,40 @@
     <t xml:space="preserve">8.1657886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33819484710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21280765533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27550220489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36954212188721</t>
+    <t xml:space="preserve">8.33819580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21280860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27550315856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36954307556152</t>
   </si>
   <si>
     <t xml:space="preserve">8.15011596679688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18146228790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13444232940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22848129272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43223476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99338388442993</t>
+    <t xml:space="preserve">8.18146324157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13444328308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22848320007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43223571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99338245391846</t>
   </si>
   <si>
     <t xml:space="preserve">8.19713592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75828218460083</t>
+    <t xml:space="preserve">7.75828266143799</t>
   </si>
   <si>
     <t xml:space="preserve">7.89934253692627</t>
@@ -1622,22 +1622,22 @@
     <t xml:space="preserve">7.88366937637329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81313943862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67991781234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79746675491333</t>
+    <t xml:space="preserve">7.81314039230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6799168586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79746627807617</t>
   </si>
   <si>
     <t xml:space="preserve">8.4165620803833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80530309677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68775320053101</t>
+    <t xml:space="preserve">7.80530261993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68775415420532</t>
   </si>
   <si>
     <t xml:space="preserve">7.74261045455933</t>
@@ -1646,34 +1646,34 @@
     <t xml:space="preserve">8.00905609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94636392593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75044679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71909999847412</t>
+    <t xml:space="preserve">7.94636344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75044727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71910095214844</t>
   </si>
   <si>
     <t xml:space="preserve">8.10309505462646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37263202667236</t>
+    <t xml:space="preserve">8.82406806945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.372633934021</t>
   </si>
   <si>
     <t xml:space="preserve">9.60773277282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48234558105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79581260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93687152862549</t>
+    <t xml:space="preserve">9.482346534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79581165313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93687057495117</t>
   </si>
   <si>
     <t xml:space="preserve">9.87417888641357</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">10.1562986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5011110305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3757238388062</t>
+    <t xml:space="preserve">10.5011100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3757247924805</t>
   </si>
   <si>
     <t xml:space="preserve">10.5481300354004</t>
@@ -1697,19 +1697,19 @@
     <t xml:space="preserve">10.2189903259277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.171971321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95254516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90552520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88985157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92119884490967</t>
+    <t xml:space="preserve">10.1719703674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95254611968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90552711486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88985061645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92119789123535</t>
   </si>
   <si>
     <t xml:space="preserve">9.73311901092529</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">10.4854383468628</t>
   </si>
   <si>
-    <t xml:space="preserve">10.250337600708</t>
+    <t xml:space="preserve">10.2503385543823</t>
   </si>
   <si>
     <t xml:space="preserve">10.0152378082275</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">10.1249513626099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3600521087646</t>
+    <t xml:space="preserve">10.3600511550903</t>
   </si>
   <si>
     <t xml:space="preserve">10.2973585128784</t>
@@ -1751,49 +1751,49 @@
     <t xml:space="preserve">10.4384174346924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6264972686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.657844543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6108245849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5951499938965</t>
+    <t xml:space="preserve">10.6264982223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6578435897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6108226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5951509475708</t>
   </si>
   <si>
     <t xml:space="preserve">10.5794773101807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6421699523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7518835067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9869823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9556369781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1280431747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0183296203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2377548217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593894958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0966958999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1750631332397</t>
+    <t xml:space="preserve">10.6421709060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7518825531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9869832992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9556360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.128041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0183305740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2377557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593885421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1750621795654</t>
   </si>
   <si>
     <t xml:space="preserve">11.1123695373535</t>
@@ -1805,73 +1805,73 @@
     <t xml:space="preserve">10.9713096618652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7989025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0936040878296</t>
+    <t xml:space="preserve">10.7989015579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0936050415039</t>
   </si>
   <si>
     <t xml:space="preserve">9.6860990524292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29426670074463</t>
+    <t xml:space="preserve">9.29426765441895</t>
   </si>
   <si>
     <t xml:space="preserve">9.54504013061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98080158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54194831848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31943082809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50750970840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53885650634766</t>
+    <t xml:space="preserve">8.98079967498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54194736480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31943130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50751066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53885746002197</t>
   </si>
   <si>
     <t xml:space="preserve">7.49183654785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66733551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44790840148926</t>
+    <t xml:space="preserve">8.66733455657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44790744781494</t>
   </si>
   <si>
     <t xml:space="preserve">8.38521480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52627468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01214790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45100021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10618686676025</t>
+    <t xml:space="preserve">8.52627563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01214694976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45099925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10618591308594</t>
   </si>
   <si>
     <t xml:space="preserve">8.9337797164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38830757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88676166534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87108612060547</t>
+    <t xml:space="preserve">9.38830661773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88675975799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87108707427979</t>
   </si>
   <si>
     <t xml:space="preserve">9.12185955047607</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">8.91810703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15320682525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90243339538574</t>
+    <t xml:space="preserve">9.15320777893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90243434906006</t>
   </si>
   <si>
     <t xml:space="preserve">9.05916690826416</t>
@@ -1895,16 +1895,16 @@
     <t xml:space="preserve">9.21590042114258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96512699127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30297946929932</t>
+    <t xml:space="preserve">8.96512603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30298042297363</t>
   </si>
   <si>
     <t xml:space="preserve">9.12407779693604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01022911071777</t>
+    <t xml:space="preserve">9.01023006439209</t>
   </si>
   <si>
     <t xml:space="preserve">8.68495178222656</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">8.50604724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70121574401855</t>
+    <t xml:space="preserve">8.70121479034424</t>
   </si>
   <si>
     <t xml:space="preserve">9.18913269042969</t>
@@ -1928,55 +1928,55 @@
     <t xml:space="preserve">8.71747875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97770214080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33550834655762</t>
+    <t xml:space="preserve">8.97770118713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33550930023193</t>
   </si>
   <si>
     <t xml:space="preserve">9.48188495635986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6119966506958</t>
+    <t xml:space="preserve">9.61199569702148</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625541687012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0673866271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3113470077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1812353134155</t>
+    <t xml:space="preserve">10.0673875808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3113460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812343597412</t>
   </si>
   <si>
     <t xml:space="preserve">10.2137622833252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2788181304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2300252914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.953537940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88848209381104</t>
+    <t xml:space="preserve">10.2788190841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2300262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95353889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88848304748535</t>
   </si>
   <si>
     <t xml:space="preserve">9.69331550598145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1324434280396</t>
+    <t xml:space="preserve">10.1324424743652</t>
   </si>
   <si>
     <t xml:space="preserve">10.1974983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3276100158691</t>
+    <t xml:space="preserve">10.3276090621948</t>
   </si>
   <si>
     <t xml:space="preserve">10.2462902069092</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">10.555305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8480567932129</t>
+    <t xml:space="preserve">10.8480558395386</t>
   </si>
   <si>
     <t xml:space="preserve">10.8805847167969</t>
@@ -1994,10 +1994,10 @@
     <t xml:space="preserve">10.8317918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7992630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9293756484985</t>
+    <t xml:space="preserve">10.7992639541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9293746948242</t>
   </si>
   <si>
     <t xml:space="preserve">10.6854162216187</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">10.6366243362427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7667360305786</t>
+    <t xml:space="preserve">10.7667350769043</t>
   </si>
   <si>
     <t xml:space="preserve">10.9781675338745</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1245422363281</t>
+    <t xml:space="preserve">11.1245441436768</t>
   </si>
   <si>
     <t xml:space="preserve">11.1408071517944</t>
@@ -2030,25 +2030,25 @@
     <t xml:space="preserve">11.4335594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498224258423</t>
+    <t xml:space="preserve">11.449821472168</t>
   </si>
   <si>
     <t xml:space="preserve">11.4660863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4823503494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.335973739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2058629989624</t>
+    <t xml:space="preserve">11.4823513031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3359746932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2058639526367</t>
   </si>
   <si>
     <t xml:space="preserve">11.2221269607544</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8643198013306</t>
+    <t xml:space="preserve">10.8643207550049</t>
   </si>
   <si>
     <t xml:space="preserve">10.5390405654907</t>
@@ -2057,10 +2057,10 @@
     <t xml:space="preserve">10.522777557373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.701681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8155279159546</t>
+    <t xml:space="preserve">10.7016801834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8155288696289</t>
   </si>
   <si>
     <t xml:space="preserve">10.6040964126587</t>
@@ -2069,28 +2069,28 @@
     <t xml:space="preserve">10.7342081069946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6203603744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.717945098877</t>
+    <t xml:space="preserve">10.620361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7179460525513</t>
   </si>
   <si>
     <t xml:space="preserve">10.5065135955811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5878324508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4577217102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3764028549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5715684890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4089288711548</t>
+    <t xml:space="preserve">10.5878343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4577198028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3764019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.571569442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4089298248291</t>
   </si>
   <si>
     <t xml:space="preserve">10.8968486785889</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">10.9944324493408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6691522598267</t>
+    <t xml:space="preserve">10.669153213501</t>
   </si>
   <si>
     <t xml:space="preserve">10.7829999923706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9619035720825</t>
+    <t xml:space="preserve">10.9619045257568</t>
   </si>
   <si>
     <t xml:space="preserve">10.9456396102905</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">11.2709188461304</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1895990371704</t>
+    <t xml:space="preserve">11.1895999908447</t>
   </si>
   <si>
     <t xml:space="preserve">11.5799341201782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4172945022583</t>
+    <t xml:space="preserve">11.417293548584</t>
   </si>
   <si>
     <t xml:space="preserve">11.30344581604</t>
@@ -2135,16 +2135,16 @@
     <t xml:space="preserve">10.0836496353149</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4414567947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7504720687866</t>
+    <t xml:space="preserve">10.4414577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7504739761353</t>
   </si>
   <si>
     <t xml:space="preserve">11.1570711135864</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1082801818848</t>
+    <t xml:space="preserve">11.1082792282104</t>
   </si>
   <si>
     <t xml:space="preserve">11.0269603729248</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">10.9131126403809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2546548843384</t>
+    <t xml:space="preserve">11.2546539306641</t>
   </si>
   <si>
     <t xml:space="preserve">11.3522386550903</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">11.4010305404663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.319709777832</t>
+    <t xml:space="preserve">11.3197107315063</t>
   </si>
   <si>
     <t xml:space="preserve">11.1733350753784</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">11.0106954574585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5311422348022</t>
+    <t xml:space="preserve">11.5311431884766</t>
   </si>
   <si>
     <t xml:space="preserve">11.7751016616821</t>
@@ -2180,34 +2180,34 @@
     <t xml:space="preserve">11.7100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7425737380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.019061088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3118124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5882987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1979637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8726854324341</t>
+    <t xml:space="preserve">11.7425727844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0190601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3118114471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5882997512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1979646682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8726844787598</t>
   </si>
   <si>
     <t xml:space="preserve">12.00279712677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8076295852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8564205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5961990356445</t>
+    <t xml:space="preserve">11.8076305389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8564214706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5961980819702</t>
   </si>
   <si>
     <t xml:space="preserve">11.954005241394</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">11.9865322113037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1003799438477</t>
+    <t xml:space="preserve">12.1003818511963</t>
   </si>
   <si>
     <t xml:space="preserve">12.1816997528076</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">12.5069799423218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4581880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4907159805298</t>
+    <t xml:space="preserve">12.4581871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4907150268555</t>
   </si>
   <si>
     <t xml:space="preserve">12.8973140716553</t>
@@ -2255,40 +2255,40 @@
     <t xml:space="preserve">12.7997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6370906829834</t>
+    <t xml:space="preserve">12.6370916366577</t>
   </si>
   <si>
     <t xml:space="preserve">12.8810501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1738023757935</t>
+    <t xml:space="preserve">13.1738014221191</t>
   </si>
   <si>
     <t xml:space="preserve">13.2713851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3527050018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7267742156982</t>
+    <t xml:space="preserve">13.3527059555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7267761230469</t>
   </si>
   <si>
     <t xml:space="preserve">13.8243598937988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.052056312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2309579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2634878158569</t>
+    <t xml:space="preserve">14.0520553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.23095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634868621826</t>
   </si>
   <si>
     <t xml:space="preserve">14.2146940231323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9056797027588</t>
+    <t xml:space="preserve">13.9056787490845</t>
   </si>
   <si>
     <t xml:space="preserve">13.6129274368286</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">13.8080949783325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8894157409668</t>
+    <t xml:space="preserve">13.8894166946411</t>
   </si>
   <si>
     <t xml:space="preserve">13.6454563140869</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">13.8406238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7918310165405</t>
+    <t xml:space="preserve">13.7918300628662</t>
   </si>
   <si>
     <t xml:space="preserve">14.0032634735107</t>
@@ -2315,31 +2315,31 @@
     <t xml:space="preserve">13.9544715881348</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3448057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.149640083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2472229003906</t>
+    <t xml:space="preserve">14.3448066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1496381759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2472219467163</t>
   </si>
   <si>
     <t xml:space="preserve">14.4749164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5579175949097</t>
+    <t xml:space="preserve">14.557915687561</t>
   </si>
   <si>
     <t xml:space="preserve">14.192723274231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1595230102539</t>
+    <t xml:space="preserve">14.1595220565796</t>
   </si>
   <si>
     <t xml:space="preserve">14.1429243087769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2757225036621</t>
+    <t xml:space="preserve">14.2757205963135</t>
   </si>
   <si>
     <t xml:space="preserve">14.2923212051392</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">14.375319480896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1097240447998</t>
+    <t xml:space="preserve">14.1097249984741</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425222396851</t>
@@ -2357,22 +2357,22 @@
     <t xml:space="preserve">14.0765237808228</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2093238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9935264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8109292984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3089208602905</t>
+    <t xml:space="preserve">14.2093229293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9935274124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8109302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3089218139648</t>
   </si>
   <si>
     <t xml:space="preserve">14.05992603302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0101251602173</t>
+    <t xml:space="preserve">14.0101261138916</t>
   </si>
   <si>
     <t xml:space="preserve">13.9769268035889</t>
@@ -2381,28 +2381,28 @@
     <t xml:space="preserve">14.0433263778687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3255186080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2259206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3421211242676</t>
+    <t xml:space="preserve">14.3255195617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2259225845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3421201705933</t>
   </si>
   <si>
     <t xml:space="preserve">14.1761236190796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9437274932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0931243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9603271484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3587188720703</t>
+    <t xml:space="preserve">13.9437265396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0931234359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9603281021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">14.2591228485107</t>
@@ -2414,31 +2414,31 @@
     <t xml:space="preserve">14.524715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0267238616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7073125839233</t>
+    <t xml:space="preserve">14.026725769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.707311630249</t>
   </si>
   <si>
     <t xml:space="preserve">14.7737102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6907138824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7405118942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9397096633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1057062149048</t>
+    <t xml:space="preserve">14.6907148361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7405138015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9397087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1057043075562</t>
   </si>
   <si>
     <t xml:space="preserve">15.3214998245239</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1721048355103</t>
+    <t xml:space="preserve">15.1721029281616</t>
   </si>
   <si>
     <t xml:space="preserve">14.8899097442627</t>
@@ -2447,55 +2447,55 @@
     <t xml:space="preserve">15.3713006973267</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7032918930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5372953414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.387900352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2883014678955</t>
+    <t xml:space="preserve">15.703293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.537296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3878993988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2883005142212</t>
   </si>
   <si>
     <t xml:space="preserve">15.2717008590698</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0725059509277</t>
+    <t xml:space="preserve">15.0725069046021</t>
   </si>
   <si>
     <t xml:space="preserve">15.2219018936157</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1223020553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9895057678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8235101699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7903108596802</t>
+    <t xml:space="preserve">15.1223039627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9895076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.85671043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8235111236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7903089523315</t>
   </si>
   <si>
     <t xml:space="preserve">15.1389045715332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9729099273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.873309135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8069105148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8607301712036</t>
+    <t xml:space="preserve">14.9729080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8733100891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8069114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8607292175293</t>
   </si>
   <si>
     <t xml:space="preserve">13.6947317123413</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">13.7113332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4417190551758</t>
+    <t xml:space="preserve">14.4417171478271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4749174118042</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">14.5745153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.541316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4251174926758</t>
+    <t xml:space="preserve">14.5413160324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4251184463501</t>
   </si>
   <si>
     <t xml:space="preserve">14.4085187911987</t>
@@ -2525,16 +2525,16 @@
     <t xml:space="preserve">14.3919191360474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4708976745605</t>
+    <t xml:space="preserve">15.4708967208862</t>
   </si>
   <si>
     <t xml:space="preserve">15.2053022384644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0227060317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4915151596069</t>
+    <t xml:space="preserve">15.0227069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4915170669556</t>
   </si>
   <si>
     <t xml:space="preserve">13.8275289535522</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">13.6449337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445316314697</t>
+    <t xml:space="preserve">13.7445306777954</t>
   </si>
   <si>
     <t xml:space="preserve">13.5287351608276</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">13.5619354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4125385284424</t>
+    <t xml:space="preserve">13.4125375747681</t>
   </si>
   <si>
     <t xml:space="preserve">13.1137437820435</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">13.2797403335571</t>
   </si>
   <si>
-    <t xml:space="preserve">13.362738609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5121374130249</t>
+    <t xml:space="preserve">13.3627395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5121364593506</t>
   </si>
   <si>
     <t xml:space="preserve">13.5951337814331</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">13.4955368041992</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0805444717407</t>
+    <t xml:space="preserve">13.080545425415</t>
   </si>
   <si>
     <t xml:space="preserve">13.3129405975342</t>
@@ -2594,19 +2594,19 @@
     <t xml:space="preserve">13.196741104126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7983503341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4497566223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3003587722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7153520584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4331560134888</t>
+    <t xml:space="preserve">12.7983512878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4497575759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3003597259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7153511047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4331569671631</t>
   </si>
   <si>
     <t xml:space="preserve">12.5991544723511</t>
@@ -2615,13 +2615,13 @@
     <t xml:space="preserve">12.3335590362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3501577377319</t>
+    <t xml:space="preserve">12.3501596450806</t>
   </si>
   <si>
     <t xml:space="preserve">12.067964553833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8521680831909</t>
+    <t xml:space="preserve">11.8521690368652</t>
   </si>
   <si>
     <t xml:space="preserve">11.6695728302002</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">11.8189687728882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6031723022461</t>
+    <t xml:space="preserve">11.6031732559204</t>
   </si>
   <si>
     <t xml:space="preserve">11.7027711868286</t>
@@ -2642,31 +2642,31 @@
     <t xml:space="preserve">11.7857694625854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5367746353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3209800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1715822219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.221381187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8395881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2088003158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6735916137695</t>
+    <t xml:space="preserve">11.5367736816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3209791183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1715812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2213821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8395891189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2088012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6735906600952</t>
   </si>
   <si>
     <t xml:space="preserve">10.6237926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2585983276367</t>
+    <t xml:space="preserve">10.258599281311</t>
   </si>
   <si>
     <t xml:space="preserve">10.1922006607056</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">9.97640514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54481410980225</t>
+    <t xml:space="preserve">9.54481315612793</t>
   </si>
   <si>
     <t xml:space="preserve">9.56141376495361</t>
@@ -2702,40 +2702,40 @@
     <t xml:space="preserve">10.3913974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3083982467651</t>
+    <t xml:space="preserve">10.6071920394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3083992004395</t>
   </si>
   <si>
     <t xml:space="preserve">10.4909954071045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1756010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1092023849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1424016952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0594024658203</t>
+    <t xml:space="preserve">10.1756019592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.109203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1424026489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0594043731689</t>
   </si>
   <si>
     <t xml:space="preserve">9.86020851135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89340591430664</t>
+    <t xml:space="preserve">9.89340686798096</t>
   </si>
   <si>
     <t xml:space="preserve">9.69421100616455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61121368408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17962074279785</t>
+    <t xml:space="preserve">9.61121273040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17962169647217</t>
   </si>
   <si>
     <t xml:space="preserve">9.27921962738037</t>
@@ -2747,31 +2747,31 @@
     <t xml:space="preserve">9.19622039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29581737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12982177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42861461639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77720928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64441108703613</t>
+    <t xml:space="preserve">9.29581832885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12982082366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42861557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77720832824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64441204071045</t>
   </si>
   <si>
     <t xml:space="preserve">10.0262041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5407943725586</t>
+    <t xml:space="preserve">10.5407934188843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4577960968018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0760040283203</t>
+    <t xml:space="preserve">10.0760021209717</t>
   </si>
   <si>
     <t xml:space="preserve">9.92660617828369</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">9.66899490356445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70334434509277</t>
+    <t xml:space="preserve">9.70334339141846</t>
   </si>
   <si>
     <t xml:space="preserve">9.7205171585083</t>
@@ -2789,10 +2789,10 @@
     <t xml:space="preserve">10.0639991760254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0983476638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2529134750366</t>
+    <t xml:space="preserve">10.0983467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2529125213623</t>
   </si>
   <si>
     <t xml:space="preserve">9.85791015625</t>
@@ -2819,10 +2819,10 @@
     <t xml:space="preserve">11.1631383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0600938796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1803121566772</t>
+    <t xml:space="preserve">11.060094833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1803131103516</t>
   </si>
   <si>
     <t xml:space="preserve">11.0944423675537</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">10.1498689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1326951980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97812747955322</t>
+    <t xml:space="preserve">10.1326942443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97812843322754</t>
   </si>
   <si>
     <t xml:space="preserve">9.87508392333984</t>
@@ -2873,16 +2873,16 @@
     <t xml:space="preserve">10.1842164993286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0468254089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5620460510254</t>
+    <t xml:space="preserve">10.0468244552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5620470046997</t>
   </si>
   <si>
     <t xml:space="preserve">10.6307430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.424654006958</t>
+    <t xml:space="preserve">10.4246530532837</t>
   </si>
   <si>
     <t xml:space="preserve">10.4418277740479</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">10.7509613037109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6822643280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4933500289917</t>
+    <t xml:space="preserve">10.6822633743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.493350982666</t>
   </si>
   <si>
     <t xml:space="preserve">10.1155204772949</t>
@@ -2915,10 +2915,10 @@
     <t xml:space="preserve">9.61747264862061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37703704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51442813873291</t>
+    <t xml:space="preserve">9.37703609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51442909240723</t>
   </si>
   <si>
     <t xml:space="preserve">9.63464736938477</t>
@@ -2978,19 +2978,19 @@
     <t xml:space="preserve">10.8540058135986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4550981521606</t>
+    <t xml:space="preserve">11.4550971984863</t>
   </si>
   <si>
     <t xml:space="preserve">11.2661828994751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0429201126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8883533477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9398756027222</t>
+    <t xml:space="preserve">11.0429191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8883543014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9398746490479</t>
   </si>
   <si>
     <t xml:space="preserve">10.8196573257446</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">10.8024835586548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3692274093628</t>
+    <t xml:space="preserve">11.3692264556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.4379224777222</t>
@@ -3017,25 +3017,25 @@
     <t xml:space="preserve">12.2966260910034</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0561895370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7470560073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7127094268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9703197479248</t>
+    <t xml:space="preserve">12.056188583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7470569610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7127084732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9703187942505</t>
   </si>
   <si>
     <t xml:space="preserve">11.9359703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0046663284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0218420028687</t>
+    <t xml:space="preserve">12.0046672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0218410491943</t>
   </si>
   <si>
     <t xml:space="preserve">11.8157529830933</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">12.3137998580933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5198888778687</t>
+    <t xml:space="preserve">12.519889831543</t>
   </si>
   <si>
     <t xml:space="preserve">12.485541343689</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">12.2451038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2794532775879</t>
+    <t xml:space="preserve">12.2794523239136</t>
   </si>
   <si>
     <t xml:space="preserve">12.1420593261719</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">12.1764087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1592330932617</t>
+    <t xml:space="preserve">12.159234046936</t>
   </si>
   <si>
     <t xml:space="preserve">12.1077117919922</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">13.1038074493408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0866327285767</t>
+    <t xml:space="preserve">13.086633682251</t>
   </si>
   <si>
     <t xml:space="preserve">13.1896772384644</t>
@@ -3134,7 +3134,7 @@
     <t xml:space="preserve">13.5159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.619029045105</t>
+    <t xml:space="preserve">13.6190280914307</t>
   </si>
   <si>
     <t xml:space="preserve">14.0827283859253</t>
@@ -3146,31 +3146,31 @@
     <t xml:space="preserve">13.7048988342285</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7220735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8766403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6151237487793</t>
+    <t xml:space="preserve">13.7220726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8766393661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6151247024536</t>
   </si>
   <si>
     <t xml:space="preserve">14.7353429794312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6494722366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8040390014648</t>
+    <t xml:space="preserve">14.649471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8040399551392</t>
   </si>
   <si>
     <t xml:space="preserve">14.6838207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7868642807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7181673049927</t>
+    <t xml:space="preserve">14.786865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7181692123413</t>
   </si>
   <si>
     <t xml:space="preserve">15.0101270675659</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">15.387957572937</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1990423202515</t>
+    <t xml:space="preserve">15.1990442276001</t>
   </si>
   <si>
     <t xml:space="preserve">15.2505664825439</t>
@@ -3197,10 +3197,10 @@
     <t xml:space="preserve">14.9757795333862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9242553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4262094497681</t>
+    <t xml:space="preserve">14.9242572784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4262084960938</t>
   </si>
   <si>
     <t xml:space="preserve">14.3918619155884</t>
@@ -3209,16 +3209,16 @@
     <t xml:space="preserve">14.9586057662964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5464296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1131706237793</t>
+    <t xml:space="preserve">14.5464286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1131725311279</t>
   </si>
   <si>
     <t xml:space="preserve">15.1303462982178</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9929523468018</t>
+    <t xml:space="preserve">14.9929533004761</t>
   </si>
   <si>
     <t xml:space="preserve">15.2677392959595</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">15.7829599380493</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7142629623413</t>
+    <t xml:space="preserve">15.7142639160156</t>
   </si>
   <si>
     <t xml:space="preserve">15.5253486633301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5596990585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8383884429932</t>
+    <t xml:space="preserve">15.5596981048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8383874893188</t>
   </si>
   <si>
     <t xml:space="preserve">14.4605579376221</t>
@@ -3263,13 +3263,13 @@
     <t xml:space="preserve">14.3059902191162</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2888164520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5120782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6323003768921</t>
+    <t xml:space="preserve">14.2888174057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5120792388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6322994232178</t>
   </si>
   <si>
     <t xml:space="preserve">14.7009954452515</t>
@@ -4458,6 +4458,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.40999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55000019073486</t>
   </si>
 </sst>
 </file>
@@ -8272,7 +8275,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G134" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8298,7 +8301,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G135" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -8324,7 +8327,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G136" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -8402,7 +8405,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G139" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8428,7 +8431,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G140" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8454,7 +8457,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G141" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8532,7 +8535,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G144" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8558,7 +8561,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G145" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8610,7 +8613,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G147" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8636,7 +8639,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G148" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8662,7 +8665,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G149" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8688,7 +8691,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G150" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8714,7 +8717,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G151" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -8740,7 +8743,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G152" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8792,7 +8795,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G154" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -8870,7 +8873,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G157" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -8896,7 +8899,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G158" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9000,7 +9003,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G162" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9026,7 +9029,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G163" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9052,7 +9055,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G164" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9078,7 +9081,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G165" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9104,7 +9107,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G166" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9130,7 +9133,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G167" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9156,7 +9159,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G168" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9182,7 +9185,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G169" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9208,7 +9211,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G170" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9234,7 +9237,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G171" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9260,7 +9263,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G172" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9312,7 +9315,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G174" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9364,7 +9367,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G176" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9390,7 +9393,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G177" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9416,7 +9419,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G178" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9442,7 +9445,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G179" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9468,7 +9471,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G180" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9494,7 +9497,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G181" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9520,7 +9523,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G182" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9572,7 +9575,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G184" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9598,7 +9601,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G185" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9624,7 +9627,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G186" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9702,7 +9705,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G189" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9728,7 +9731,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G190" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9754,7 +9757,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G191" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9780,7 +9783,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G192" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -9806,7 +9809,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G193" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -9832,7 +9835,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G194" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -9858,7 +9861,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G195" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -9884,7 +9887,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G196" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -9910,7 +9913,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G197" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -9936,7 +9939,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G198" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -9962,7 +9965,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G199" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10014,7 +10017,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G201" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10144,7 +10147,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G206" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10196,7 +10199,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G208" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10222,7 +10225,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G209" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10248,7 +10251,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G210" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10352,7 +10355,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G214" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10378,7 +10381,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G215" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10404,7 +10407,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G216" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10430,7 +10433,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G217" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10456,7 +10459,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G218" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10482,7 +10485,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G219" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10508,7 +10511,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G220" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10534,7 +10537,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G221" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10560,7 +10563,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G222" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10612,7 +10615,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G224" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10664,7 +10667,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G226" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10690,7 +10693,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G227" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10716,7 +10719,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G228" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10742,7 +10745,7 @@
         <v>5.25</v>
       </c>
       <c r="G229" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10794,7 +10797,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G231" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10846,7 +10849,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G233" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -10924,7 +10927,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G236" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -10950,7 +10953,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G237" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -10976,7 +10979,7 @@
         <v>5.25</v>
       </c>
       <c r="G238" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11002,7 +11005,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G239" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11054,7 +11057,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G241" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11080,7 +11083,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G242" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11106,7 +11109,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G243" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11236,7 +11239,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G248" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11262,7 +11265,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G249" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11288,7 +11291,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G250" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11314,7 +11317,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G251" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11392,7 +11395,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G254" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11418,7 +11421,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G255" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11496,7 +11499,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G258" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11522,7 +11525,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G259" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11548,7 +11551,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G260" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11574,7 +11577,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G261" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11626,7 +11629,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G263" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11652,7 +11655,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G264" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11678,7 +11681,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G265" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11704,7 +11707,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G266" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11730,7 +11733,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G267" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11756,7 +11759,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G268" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11782,7 +11785,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G269" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -11808,7 +11811,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G270" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11834,7 +11837,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G271" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -11860,7 +11863,7 @@
         <v>5.7649998664856</v>
       </c>
       <c r="G272" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -11886,7 +11889,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G273" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -11912,7 +11915,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G274" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -11964,7 +11967,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G276" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12094,7 +12097,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G281" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12146,7 +12149,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G283" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12198,7 +12201,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G285" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12224,7 +12227,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G286" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12250,7 +12253,7 @@
         <v>5.75</v>
       </c>
       <c r="G287" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12276,7 +12279,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G288" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12302,7 +12305,7 @@
         <v>5.80499982833862</v>
       </c>
       <c r="G289" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12328,7 +12331,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G290" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12354,7 +12357,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G291" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12380,7 +12383,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G292" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12406,7 +12409,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G293" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12432,7 +12435,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G294" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12458,7 +12461,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G295" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12484,7 +12487,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G296" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12510,7 +12513,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G297" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12536,7 +12539,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G298" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12562,7 +12565,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G299" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12588,7 +12591,7 @@
         <v>6</v>
       </c>
       <c r="G300" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12614,7 +12617,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G301" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12640,7 +12643,7 @@
         <v>6</v>
       </c>
       <c r="G302" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12666,7 +12669,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G303" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12692,7 +12695,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G304" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12718,7 +12721,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G305" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12744,7 +12747,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G306" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12770,7 +12773,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G307" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12796,7 +12799,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G308" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12822,7 +12825,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G309" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -12848,7 +12851,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G310" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -12874,7 +12877,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G311" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -12900,7 +12903,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G312" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -12926,7 +12929,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G313" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -12952,7 +12955,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G314" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -12978,7 +12981,7 @@
         <v>7</v>
       </c>
       <c r="G315" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13004,7 +13007,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G316" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13030,7 +13033,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G317" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13056,7 +13059,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G318" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13082,7 +13085,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G319" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13108,7 +13111,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G320" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13134,7 +13137,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G321" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13160,7 +13163,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G322" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13186,7 +13189,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G323" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13212,7 +13215,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G324" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13238,7 +13241,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G325" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13264,7 +13267,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G326" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13290,7 +13293,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G327" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13316,7 +13319,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G328" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13342,7 +13345,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G329" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13368,7 +13371,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G330" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13394,7 +13397,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G331" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13420,7 +13423,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G332" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13446,7 +13449,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G333" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13472,7 +13475,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G334" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13498,7 +13501,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G335" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13524,7 +13527,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G336" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13550,7 +13553,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G337" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13576,7 +13579,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G338" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13602,7 +13605,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G339" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13628,7 +13631,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G340" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13654,7 +13657,7 @@
         <v>7.75</v>
       </c>
       <c r="G341" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13680,7 +13683,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G342" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13706,7 +13709,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G343" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13732,7 +13735,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G344" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13758,7 +13761,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G345" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13784,7 +13787,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G346" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13810,7 +13813,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G347" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13836,7 +13839,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G348" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -13862,7 +13865,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G349" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -13888,7 +13891,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G350" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -13914,7 +13917,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G351" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -13940,7 +13943,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G352" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -13966,7 +13969,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G353" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -13992,7 +13995,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G354" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14018,7 +14021,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G355" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14044,7 +14047,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G356" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14070,7 +14073,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G357" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14096,7 +14099,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G358" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14122,7 +14125,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G359" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14148,7 +14151,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G360" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14174,7 +14177,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G361" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14200,7 +14203,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G362" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14226,7 +14229,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G363" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14252,7 +14255,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G364" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14278,7 +14281,7 @@
         <v>7.5</v>
       </c>
       <c r="G365" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14304,7 +14307,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G366" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14330,7 +14333,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G367" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14356,7 +14359,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G368" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14382,7 +14385,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G369" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14408,7 +14411,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G370" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14434,7 +14437,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G371" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14460,7 +14463,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G372" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14486,7 +14489,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G373" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14512,7 +14515,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G374" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14538,7 +14541,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G375" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14564,7 +14567,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G376" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14590,7 +14593,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G377" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14616,7 +14619,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G378" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14642,7 +14645,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G379" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14668,7 +14671,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G380" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14694,7 +14697,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G381" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14720,7 +14723,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G382" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14746,7 +14749,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G383" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14772,7 +14775,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G384" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14798,7 +14801,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G385" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -14824,7 +14827,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G386" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -14850,7 +14853,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G387" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -14876,7 +14879,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G388" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -14902,7 +14905,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G389" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -14928,7 +14931,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G390" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -14954,7 +14957,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G391" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -14980,7 +14983,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G392" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15006,7 +15009,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G393" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15032,7 +15035,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G394" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15058,7 +15061,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G395" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15084,7 +15087,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G396" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15110,7 +15113,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G397" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15136,7 +15139,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G398" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15162,7 +15165,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15188,7 +15191,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G400" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15214,7 +15217,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G401" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15240,7 +15243,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G402" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15266,7 +15269,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G403" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15292,7 +15295,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G404" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15318,7 +15321,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G405" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15344,7 +15347,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G406" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15370,7 +15373,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G407" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15396,7 +15399,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G408" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15422,7 +15425,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G409" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15448,7 +15451,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G410" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15474,7 +15477,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G411" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15500,7 +15503,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G412" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15526,7 +15529,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G413" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15552,7 +15555,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G414" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15578,7 +15581,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G415" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15604,7 +15607,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G416" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15630,7 +15633,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G417" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15656,7 +15659,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G418" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -15682,7 +15685,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G419" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15708,7 +15711,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G420" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15734,7 +15737,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G421" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15760,7 +15763,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G422" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15786,7 +15789,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G423" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -15812,7 +15815,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G424" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -15838,7 +15841,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G425" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -15864,7 +15867,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G426" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -15890,7 +15893,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G427" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -15916,7 +15919,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G428" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -15942,7 +15945,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G429" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -15968,7 +15971,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G430" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -15994,7 +15997,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G431" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16020,7 +16023,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G432" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16046,7 +16049,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G433" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16072,7 +16075,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G434" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16098,7 +16101,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G435" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16124,7 +16127,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G436" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16150,7 +16153,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G437" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16176,7 +16179,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G438" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16202,7 +16205,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G439" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16228,7 +16231,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G440" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16254,7 +16257,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G441" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16280,7 +16283,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G442" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16306,7 +16309,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G443" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16332,7 +16335,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G444" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16358,7 +16361,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G445" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16384,7 +16387,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G446" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16410,7 +16413,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G447" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16436,7 +16439,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G448" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16462,7 +16465,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G449" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16488,7 +16491,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G450" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16514,7 +16517,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G451" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16540,7 +16543,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G452" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16566,7 +16569,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G453" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16592,7 +16595,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G454" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16618,7 +16621,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G455" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16644,7 +16647,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G456" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16670,7 +16673,7 @@
         <v>8</v>
       </c>
       <c r="G457" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16696,7 +16699,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G458" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -16722,7 +16725,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G459" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -16748,7 +16751,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G460" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -16774,7 +16777,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G461" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -16800,7 +16803,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G462" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -16826,7 +16829,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G463" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -16852,7 +16855,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G464" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -16878,7 +16881,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G465" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -16904,7 +16907,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G466" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -16930,7 +16933,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G467" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -16956,7 +16959,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G468" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -16982,7 +16985,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G469" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17008,7 +17011,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G470" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17034,7 +17037,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G471" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17060,7 +17063,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G472" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17086,7 +17089,7 @@
         <v>8</v>
       </c>
       <c r="G473" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17112,7 +17115,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G474" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17138,7 +17141,7 @@
         <v>7.85500001907349</v>
       </c>
       <c r="G475" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17164,7 +17167,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G476" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17190,7 +17193,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G477" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17216,7 +17219,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G478" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17242,7 +17245,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G479" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17268,7 +17271,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G480" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17294,7 +17297,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G481" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17320,7 +17323,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G482" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17346,7 +17349,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G483" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17372,7 +17375,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G484" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17398,7 +17401,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G485" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17424,7 +17427,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G486" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17450,7 +17453,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G487" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17476,7 +17479,7 @@
         <v>8</v>
       </c>
       <c r="G488" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17502,7 +17505,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G489" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17528,7 +17531,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G490" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17554,7 +17557,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G491" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17580,7 +17583,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G492" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17606,7 +17609,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G493" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17632,7 +17635,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G494" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17658,7 +17661,7 @@
         <v>8</v>
       </c>
       <c r="G495" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17684,7 +17687,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G496" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17710,7 +17713,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G497" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -17736,7 +17739,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G498" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -17762,7 +17765,7 @@
         <v>8.08500003814697</v>
       </c>
       <c r="G499" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -17788,7 +17791,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G500" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -17814,7 +17817,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G501" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -17840,7 +17843,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G502" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -17866,7 +17869,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G503" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -17892,7 +17895,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -17918,7 +17921,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G505" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -17944,7 +17947,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G506" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -17970,7 +17973,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G507" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -17996,7 +17999,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G508" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18022,7 +18025,7 @@
         <v>8.25</v>
       </c>
       <c r="G509" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18048,7 +18051,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G510" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18074,7 +18077,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G511" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18100,7 +18103,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G512" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18126,7 +18129,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G513" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18152,7 +18155,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G514" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18178,7 +18181,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G515" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18204,7 +18207,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G516" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18230,7 +18233,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G517" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18256,7 +18259,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G518" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18282,7 +18285,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G519" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18308,7 +18311,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G520" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18334,7 +18337,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G521" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18360,7 +18363,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G522" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18386,7 +18389,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G523" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18412,7 +18415,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G524" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18438,7 +18441,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G525" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18464,7 +18467,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G526" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18490,7 +18493,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G527" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18516,7 +18519,7 @@
         <v>8.5</v>
       </c>
       <c r="G528" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18542,7 +18545,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G529" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18568,7 +18571,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G530" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18594,7 +18597,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G531" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18620,7 +18623,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G532" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18646,7 +18649,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G533" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18672,7 +18675,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G534" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18698,7 +18701,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G535" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -18724,7 +18727,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G536" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -18750,7 +18753,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G537" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -18776,7 +18779,7 @@
         <v>8</v>
       </c>
       <c r="G538" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -18802,7 +18805,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G539" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -18828,7 +18831,7 @@
         <v>8</v>
       </c>
       <c r="G540" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -18854,7 +18857,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G541" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -18880,7 +18883,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G542" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -18906,7 +18909,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G543" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -18932,7 +18935,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G544" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -18958,7 +18961,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G545" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -18984,7 +18987,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G546" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19010,7 +19013,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G547" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19036,7 +19039,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G548" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19062,7 +19065,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G549" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19088,7 +19091,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G550" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19114,7 +19117,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G551" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19140,7 +19143,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G552" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19166,7 +19169,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G553" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19192,7 +19195,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G554" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19218,7 +19221,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G555" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19244,7 +19247,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G556" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19270,7 +19273,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G557" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19296,7 +19299,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G558" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19322,7 +19325,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G559" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19348,7 +19351,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G560" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19374,7 +19377,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G561" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19400,7 +19403,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G562" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19426,7 +19429,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G563" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19452,7 +19455,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G564" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19478,7 +19481,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G565" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19504,7 +19507,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G566" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19530,7 +19533,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G567" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19556,7 +19559,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G568" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19582,7 +19585,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G569" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19608,7 +19611,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G570" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19634,7 +19637,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G571" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19660,7 +19663,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G572" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19686,7 +19689,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G573" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19712,7 +19715,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G574" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -19738,7 +19741,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G575" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -19764,7 +19767,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G576" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -19790,7 +19793,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G577" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -19816,7 +19819,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G578" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -19842,7 +19845,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G579" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -19868,7 +19871,7 @@
         <v>8.25</v>
       </c>
       <c r="G580" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -19894,7 +19897,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -19920,7 +19923,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -19946,7 +19949,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G583" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -19972,7 +19975,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G584" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -19998,7 +20001,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G585" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20024,7 +20027,7 @@
         <v>8.25</v>
       </c>
       <c r="G586" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20050,7 +20053,7 @@
         <v>8.25</v>
       </c>
       <c r="G587" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20076,7 +20079,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G588" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20102,7 +20105,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G589" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20128,7 +20131,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G590" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20154,7 +20157,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G591" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20180,7 +20183,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G592" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20206,7 +20209,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G593" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20232,7 +20235,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G594" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20258,7 +20261,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20284,7 +20287,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G596" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20310,7 +20313,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G597" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20336,7 +20339,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G598" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20362,7 +20365,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G599" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20388,7 +20391,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G600" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20414,7 +20417,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G601" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20440,7 +20443,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G602" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20466,7 +20469,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G603" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20492,7 +20495,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G604" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20518,7 +20521,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G605" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20544,7 +20547,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G606" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20986,7 +20989,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21038,7 +21041,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G625" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21090,7 +21093,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G627" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -23586,7 +23589,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G723" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -24106,7 +24109,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G743" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24574,7 +24577,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G761" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -70654,7 +70657,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.69125</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>33542</v>
@@ -70675,6 +70678,32 @@
         <v>1481</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.6910416667</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>61843</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>7.34999990463257</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>7.42999982833862</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>7.55000019073486</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>1482</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="1485">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,157 +38,157 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04141712188721</t>
+    <t xml:space="preserve">4.04141759872437</t>
   </si>
   <si>
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447938919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9397885799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82799816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78057098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943140983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75685787200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7433078289032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80089712142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040839195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571877479553</t>
+    <t xml:space="preserve">4.02447891235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93978905677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82799768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78057050704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943164825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7568576335907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74330735206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80089664459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040910720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571829795837</t>
   </si>
   <si>
     <t xml:space="preserve">3.66539263725281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56376528739929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65184259414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72636938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70265650749207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65861749649048</t>
+    <t xml:space="preserve">3.56376481056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65184235572815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72636985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70265603065491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65861701965332</t>
   </si>
   <si>
     <t xml:space="preserve">3.69249391555786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74669504165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59764099121094</t>
+    <t xml:space="preserve">3.74669528007507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59764051437378</t>
   </si>
   <si>
     <t xml:space="preserve">3.59086585044861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58408975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49601221084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4621365070343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51633834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38760900497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40793418884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50956225395203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55698895454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56715202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61119103431702</t>
+    <t xml:space="preserve">3.58409023284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49601244926453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46213674545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51633810997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38760876655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40793442726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50956296920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55698919296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56715250015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6111912727356</t>
   </si>
   <si>
     <t xml:space="preserve">3.57731509208679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54682588577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52650141716003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50278782844543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56037664413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58070230484009</t>
+    <t xml:space="preserve">3.5468270778656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52650094032288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50278759002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56037640571594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58070278167725</t>
   </si>
   <si>
     <t xml:space="preserve">3.60102820396423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54343867301941</t>
+    <t xml:space="preserve">3.54343914985657</t>
   </si>
   <si>
     <t xml:space="preserve">3.57053971290588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64506697654724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78734660148621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.841548204422</t>
+    <t xml:space="preserve">3.64506721496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78734707832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84154844284058</t>
   </si>
   <si>
     <t xml:space="preserve">3.86526226997375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85171175003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92962646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93640112876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607546806335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90252542495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89575052261353</t>
+    <t xml:space="preserve">3.85171151161194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92962574958801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9364013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9160749912262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90252566337585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89574956893921</t>
   </si>
   <si>
     <t xml:space="preserve">3.92285108566284</t>
@@ -197,37 +197,37 @@
     <t xml:space="preserve">3.90930032730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97027826309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87881231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85848689079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94317698478699</t>
+    <t xml:space="preserve">3.97027778625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8788115978241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85848569869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94317603111267</t>
   </si>
   <si>
     <t xml:space="preserve">3.89913749694824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9465639591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95672750473022</t>
+    <t xml:space="preserve">3.94656467437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95672702789307</t>
   </si>
   <si>
     <t xml:space="preserve">3.9635021686554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91268801689148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9736647605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91946291923523</t>
+    <t xml:space="preserve">3.91268825531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97366523742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91946387290955</t>
   </si>
   <si>
     <t xml:space="preserve">3.87203693389893</t>
@@ -236,133 +236,133 @@
     <t xml:space="preserve">3.88704800605774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87291288375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85877871513367</t>
+    <t xml:space="preserve">3.87291264533997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85877799987793</t>
   </si>
   <si>
     <t xml:space="preserve">3.83757662773132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86231231689453</t>
+    <t xml:space="preserve">3.86231160163879</t>
   </si>
   <si>
     <t xml:space="preserve">3.87644696235657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89411592483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9011824131012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058136940002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94358658790588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95418763160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96125555038452</t>
+    <t xml:space="preserve">3.89411497116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90118288993835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89058184623718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94358611106873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95418810844421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96125507354736</t>
   </si>
   <si>
     <t xml:space="preserve">4.01426029205322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02486181259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08846712112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05666399002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03899669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305772781372</t>
+    <t xml:space="preserve">4.02486085891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08846807479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05666446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03899621963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9930579662323</t>
   </si>
   <si>
     <t xml:space="preserve">4.00719308853149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97539019584656</t>
+    <t xml:space="preserve">3.97539043426514</t>
   </si>
   <si>
     <t xml:space="preserve">3.97185611724854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80224013328552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78103756904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75630235671997</t>
+    <t xml:space="preserve">3.80223965644836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78103804588318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75630164146423</t>
   </si>
   <si>
     <t xml:space="preserve">3.7492344379425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90471649169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9223849773407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03546237945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75983572006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80930757522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83050966262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86937975883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82344174385071</t>
+    <t xml:space="preserve">3.90471625328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92238426208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065474510193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03546285629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7598352432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80930685997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83050918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86937952041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82344150543213</t>
   </si>
   <si>
     <t xml:space="preserve">3.80577349662781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84110975265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81637454032898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8658459186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89764881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93651962280273</t>
+    <t xml:space="preserve">3.84110999107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81637382507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86584615707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89764928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93651914596558</t>
   </si>
   <si>
     <t xml:space="preserve">3.9082498550415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91531705856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97892379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00012493133545</t>
+    <t xml:space="preserve">3.91531729698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97892308235168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00012588500977</t>
   </si>
   <si>
     <t xml:space="preserve">4.02132749557495</t>
@@ -377,118 +377,118 @@
     <t xml:space="preserve">3.81284070014954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77043700218201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76336884498596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74570107460022</t>
+    <t xml:space="preserve">3.77043652534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690316200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76336932182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7457013130188</t>
   </si>
   <si>
     <t xml:space="preserve">3.72449851036072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77397012710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78810548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81990766525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72803282737732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73863315582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73156571388245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73509979248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6538245677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63969016075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66089224815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61848783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61142086982727</t>
+    <t xml:space="preserve">3.77397036552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78810477256775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.819908618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72803258895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73863339424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7315661907196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73510003089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65382504463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63969039916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66089272499084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61848831176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61142158508301</t>
   </si>
   <si>
     <t xml:space="preserve">3.62555575370789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61495399475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64675760269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74216794967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91885161399841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98599076271057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99659276008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87998032569885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88351345062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79517269134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82697510719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79163861274719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8481776714325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7103636264801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85524415969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03192853927612</t>
+    <t xml:space="preserve">3.61495494842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64675784111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74216723442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91885042190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98599100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99659204483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87998008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88351440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79517245292664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82697534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79163837432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84817790985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71036410331726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8552451133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03192901611328</t>
   </si>
   <si>
     <t xml:space="preserve">4.04252958297729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08493375778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0990686416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05313062667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04959774017334</t>
+    <t xml:space="preserve">4.08493328094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09906816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05313110351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04959678649902</t>
   </si>
   <si>
     <t xml:space="preserve">4.09200143814087</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">4.07786655426025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07433223724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04606342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06373167037964</t>
+    <t xml:space="preserve">4.07433271408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04606294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06373119354248</t>
   </si>
   <si>
     <t xml:space="preserve">4.10613632202148</t>
@@ -518,94 +518,94 @@
     <t xml:space="preserve">4.13440561294556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12733840942383</t>
+    <t xml:space="preserve">4.12733793258667</t>
   </si>
   <si>
     <t xml:space="preserve">4.16974258422852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18387746810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1591420173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24041557312012</t>
+    <t xml:space="preserve">4.18387699127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15914154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24041604995728</t>
   </si>
   <si>
     <t xml:space="preserve">4.21568059921265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27575397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34642696380615</t>
+    <t xml:space="preserve">4.27575302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34642648696899</t>
   </si>
   <si>
     <t xml:space="preserve">4.36762809753418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35349369049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31108999252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30402231216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38176250457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50897598266602</t>
+    <t xml:space="preserve">4.35349416732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31108951568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30402135848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38176298141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50897550582886</t>
   </si>
   <si>
     <t xml:space="preserve">4.72806358337402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91181516647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94715166091919</t>
+    <t xml:space="preserve">4.91181468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94715261459351</t>
   </si>
   <si>
     <t xml:space="preserve">5.19450998306274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2227783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22984600067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22631311416626</t>
+    <t xml:space="preserve">5.22277879714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22984647750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2263126373291</t>
   </si>
   <si>
     <t xml:space="preserve">5.09203243255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07436513900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08496570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1167688369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10616683959961</t>
+    <t xml:space="preserve">5.07436466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08496522903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11676836013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10616731643677</t>
   </si>
   <si>
     <t xml:space="preserve">5.1521053314209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15917301177979</t>
+    <t xml:space="preserve">5.15917253494263</t>
   </si>
   <si>
     <t xml:space="preserve">5.17330741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1909761428833</t>
+    <t xml:space="preserve">5.19097566604614</t>
   </si>
   <si>
     <t xml:space="preserve">5.14503765106201</t>
@@ -614,52 +614,52 @@
     <t xml:space="preserve">5.13090324401855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24751567840576</t>
+    <t xml:space="preserve">5.24751424789429</t>
   </si>
   <si>
     <t xml:space="preserve">5.26871681213379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59734869003296</t>
+    <t xml:space="preserve">5.59734916687012</t>
   </si>
   <si>
     <t xml:space="preserve">5.51254081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35705900192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47720336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37119388580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44186687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53020858764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61199712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65216064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68867444992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62295055389404</t>
+    <t xml:space="preserve">5.35705852508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47720384597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37119340896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44186639785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5302095413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61199760437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65216112136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6886739730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6229510307312</t>
   </si>
   <si>
     <t xml:space="preserve">5.619300365448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59739208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42213249206543</t>
+    <t xml:space="preserve">5.59739255905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42213106155396</t>
   </si>
   <si>
     <t xml:space="preserve">5.41847991943359</t>
@@ -668,28 +668,28 @@
     <t xml:space="preserve">5.55357694625854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56087923049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49880838394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4622950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55722761154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45499324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36736297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37466526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43308591842651</t>
+    <t xml:space="preserve">5.56087970733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49880790710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46229553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55722808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45499277114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36736249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37466478347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43308544158936</t>
   </si>
   <si>
     <t xml:space="preserve">5.40387535095215</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">5.47690010070801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44769096374512</t>
+    <t xml:space="preserve">5.4476900100708</t>
   </si>
   <si>
     <t xml:space="preserve">5.48055171966553</t>
@@ -707,31 +707,31 @@
     <t xml:space="preserve">5.49515676498413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54627466201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60104417800903</t>
+    <t xml:space="preserve">5.54627418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60104322433472</t>
   </si>
   <si>
     <t xml:space="preserve">5.41117763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51341342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54992580413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45134162902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61564874649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50611114501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34545421600342</t>
+    <t xml:space="preserve">5.51341390609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54992532730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45134115219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61564922332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50611019134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34545469284058</t>
   </si>
   <si>
     <t xml:space="preserve">5.37101316452026</t>
@@ -740,49 +740,49 @@
     <t xml:space="preserve">5.31259298324585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28703451156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15558910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12637853622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2724289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31989574432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14098453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40752696990967</t>
+    <t xml:space="preserve">5.287034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15558862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12637901306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27242946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31989622116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14098405838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40752649307251</t>
   </si>
   <si>
     <t xml:space="preserve">5.38926982879639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37831544876099</t>
+    <t xml:space="preserve">5.3783164024353</t>
   </si>
   <si>
     <t xml:space="preserve">5.24321937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46959733963013</t>
+    <t xml:space="preserve">5.46959781646729</t>
   </si>
   <si>
     <t xml:space="preserve">5.41482877731323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42578220367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44038772583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48420286178589</t>
+    <t xml:space="preserve">5.42578268051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44038724899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48420381546021</t>
   </si>
   <si>
     <t xml:space="preserve">5.35275745391846</t>
@@ -791,13 +791,13 @@
     <t xml:space="preserve">5.48785400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50245952606201</t>
+    <t xml:space="preserve">5.50245904922485</t>
   </si>
   <si>
     <t xml:space="preserve">5.57183361053467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57913541793823</t>
+    <t xml:space="preserve">5.57913589477539</t>
   </si>
   <si>
     <t xml:space="preserve">5.56453084945679</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">5.52071571350098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53897190093994</t>
+    <t xml:space="preserve">5.5389723777771</t>
   </si>
   <si>
     <t xml:space="preserve">5.65581226348877</t>
@@ -818,22 +818,22 @@
     <t xml:space="preserve">5.57548427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50976181030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53166961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60469532012939</t>
+    <t xml:space="preserve">5.50976276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53166913986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60469436645508</t>
   </si>
   <si>
     <t xml:space="preserve">5.59009027481079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75804758071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79456090927124</t>
+    <t xml:space="preserve">5.75804805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79456043243408</t>
   </si>
   <si>
     <t xml:space="preserve">5.92965745925903</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">5.94426298141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99903154373169</t>
+    <t xml:space="preserve">5.99903202056885</t>
   </si>
   <si>
     <t xml:space="preserve">5.93695974349976</t>
@@ -854,37 +854,37 @@
     <t xml:space="preserve">5.83107328414917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88584327697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83472394943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95886754989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76900243759155</t>
+    <t xml:space="preserve">5.88584232330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83472490310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9588680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76900196075439</t>
   </si>
   <si>
     <t xml:space="preserve">5.91140127182007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83837556838989</t>
+    <t xml:space="preserve">5.83837604522705</t>
   </si>
   <si>
     <t xml:space="preserve">5.84202671051025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87123727798462</t>
+    <t xml:space="preserve">5.87123775482178</t>
   </si>
   <si>
     <t xml:space="preserve">5.783607006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85298156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7032790184021</t>
+    <t xml:space="preserve">5.8529806137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70327949523926</t>
   </si>
   <si>
     <t xml:space="preserve">5.82742214202881</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">5.8639349937439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75439643859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72883796691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68502235412598</t>
+    <t xml:space="preserve">5.75439691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72883749008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68502187728882</t>
   </si>
   <si>
     <t xml:space="preserve">5.66676616668701</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">5.88949298858643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78725862503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77995634078979</t>
+    <t xml:space="preserve">5.78725814819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77995586395264</t>
   </si>
   <si>
     <t xml:space="preserve">5.73614025115967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6083459854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63025426864624</t>
+    <t xml:space="preserve">5.60834550857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63025379180908</t>
   </si>
   <si>
     <t xml:space="preserve">5.53532123565674</t>
@@ -932,79 +932,79 @@
     <t xml:space="preserve">5.62660217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68137216567993</t>
+    <t xml:space="preserve">5.68137121200562</t>
   </si>
   <si>
     <t xml:space="preserve">5.73979187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76535081863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80916547775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80551433563232</t>
+    <t xml:space="preserve">5.76535034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80916595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80551528930664</t>
   </si>
   <si>
     <t xml:space="preserve">5.82377052307129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87854051589966</t>
+    <t xml:space="preserve">5.8785400390625</t>
   </si>
   <si>
     <t xml:space="preserve">5.82011938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90409851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92235469818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95156526565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02459001541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06110382080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00998544692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09031295776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22906112670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18524694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03189325332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0391960144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04649877548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25096893310547</t>
+    <t xml:space="preserve">5.90409803390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92235565185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95156478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02459049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06110334396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00998497009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09031343460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22906064987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18524646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03189373016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03919553756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04649782180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25096988677979</t>
   </si>
   <si>
     <t xml:space="preserve">6.20715379714966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14143180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12682676315308</t>
+    <t xml:space="preserve">6.14143085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12682580947876</t>
   </si>
   <si>
     <t xml:space="preserve">5.7982120513916</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">5.72518682479858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96617078781128</t>
+    <t xml:space="preserve">5.96617031097412</t>
   </si>
   <si>
     <t xml:space="preserve">6.00268363952637</t>
@@ -1022,13 +1022,13 @@
     <t xml:space="preserve">5.8931450843811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84932994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97347259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99538040161133</t>
+    <t xml:space="preserve">5.84933042526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.973473072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99537992477417</t>
   </si>
   <si>
     <t xml:space="preserve">6.11952352523804</t>
@@ -1037,28 +1037,28 @@
     <t xml:space="preserve">6.15603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10491800308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98077487945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90044689178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14873313903809</t>
+    <t xml:space="preserve">6.10491847991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98077535629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90044736862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14873361587524</t>
   </si>
   <si>
     <t xml:space="preserve">6.09761571884155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05380058288574</t>
+    <t xml:space="preserve">6.0538010597229</t>
   </si>
   <si>
     <t xml:space="preserve">6.07570838928223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08301019668579</t>
+    <t xml:space="preserve">6.08301067352295</t>
   </si>
   <si>
     <t xml:space="preserve">6.17794370651245</t>
@@ -1079,115 +1079,115 @@
     <t xml:space="preserve">6.31810283660889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2346715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28017902374268</t>
+    <t xml:space="preserve">6.23467063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28017854690552</t>
   </si>
   <si>
     <t xml:space="preserve">6.15882253646851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2725944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26500940322876</t>
+    <t xml:space="preserve">6.27259492874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26500988006592</t>
   </si>
   <si>
     <t xml:space="preserve">6.21191549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1815767288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15123796463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02988147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05263662338257</t>
+    <t xml:space="preserve">6.18157720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15123844146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02988195419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05263614654541</t>
   </si>
   <si>
     <t xml:space="preserve">6.25742483139038</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22708559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.249840259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29534912109375</t>
+    <t xml:space="preserve">6.22708606719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24983978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29534864425659</t>
   </si>
   <si>
     <t xml:space="preserve">6.3711953163147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1891622543335</t>
+    <t xml:space="preserve">6.18916177749634</t>
   </si>
   <si>
     <t xml:space="preserve">6.1664080619812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2043309211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0147123336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04505157470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00712776184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98437356948853</t>
+    <t xml:space="preserve">6.20433139801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01471185684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04505205154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00712871551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98437309265137</t>
   </si>
   <si>
     <t xml:space="preserve">6.12089872360229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13606882095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11331510543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09055995941162</t>
+    <t xml:space="preserve">6.13606834411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11331415176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09055948257446</t>
   </si>
   <si>
     <t xml:space="preserve">5.96161937713623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08297538757324</t>
+    <t xml:space="preserve">6.0829758644104</t>
   </si>
   <si>
     <t xml:space="preserve">6.14365386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10573053359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06022119522095</t>
+    <t xml:space="preserve">6.1057300567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06022071838379</t>
   </si>
   <si>
     <t xml:space="preserve">5.99954271316528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95403480529785</t>
+    <t xml:space="preserve">5.95403432846069</t>
   </si>
   <si>
     <t xml:space="preserve">5.93886470794678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06780576705933</t>
+    <t xml:space="preserve">6.06780624389648</t>
   </si>
   <si>
     <t xml:space="preserve">5.91611099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94645023345947</t>
+    <t xml:space="preserve">5.94644975662231</t>
   </si>
   <si>
     <t xml:space="preserve">5.87818670272827</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">5.99195861816406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86301755905151</t>
+    <t xml:space="preserve">5.86301708221436</t>
   </si>
   <si>
     <t xml:space="preserve">6.07539081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24225521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47738265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63666248321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46221351623535</t>
+    <t xml:space="preserve">6.24225473403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47738361358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63666296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46221399307251</t>
   </si>
   <si>
     <t xml:space="preserve">6.57598447799683</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">6.6063232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55322980880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65183258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53806066513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4849681854248</t>
+    <t xml:space="preserve">6.55323028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65183305740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53806018829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48496723175049</t>
   </si>
   <si>
     <t xml:space="preserve">6.6139087677002</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">6.66700172424316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59873867034912</t>
+    <t xml:space="preserve">6.59873819351196</t>
   </si>
   <si>
     <t xml:space="preserve">6.34085655212402</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">6.39395093917847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41670417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4242901802063</t>
+    <t xml:space="preserve">6.41670513153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42428970336914</t>
   </si>
   <si>
     <t xml:space="preserve">6.53047609329224</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">6.59115362167358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54564619064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56840038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44704389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3484411239624</t>
+    <t xml:space="preserve">6.54564476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56839942932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44704437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34844160079956</t>
   </si>
   <si>
     <t xml:space="preserve">6.21950054168701</t>
@@ -1286,34 +1286,34 @@
     <t xml:space="preserve">6.40911960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32568740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2877631187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6897554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67458724975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7428503036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75043344497681</t>
+    <t xml:space="preserve">6.32568788528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28776407241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68975591659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6745867729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74284982681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75043296813965</t>
   </si>
   <si>
     <t xml:space="preserve">6.62149286270142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37878131866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36361169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46979761123657</t>
+    <t xml:space="preserve">6.37878036499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36361122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46979808807373</t>
   </si>
   <si>
     <t xml:space="preserve">6.51530647277832</t>
@@ -1322,82 +1322,82 @@
     <t xml:space="preserve">6.31051778793335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35602712631226</t>
+    <t xml:space="preserve">6.3560266494751</t>
   </si>
   <si>
     <t xml:space="preserve">6.19674682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40153503417969</t>
+    <t xml:space="preserve">6.40153408050537</t>
   </si>
   <si>
     <t xml:space="preserve">6.72009468078613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7580189704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80352735519409</t>
+    <t xml:space="preserve">6.75801849365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80352783203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.78835773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73526477813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84903621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86420583724976</t>
+    <t xml:space="preserve">6.73526430130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84903526306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86420631408691</t>
   </si>
   <si>
     <t xml:space="preserve">6.81111192703247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84145069122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81869649887085</t>
+    <t xml:space="preserve">6.84145164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81869697570801</t>
   </si>
   <si>
     <t xml:space="preserve">6.90212869644165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99314737319946</t>
+    <t xml:space="preserve">6.99314641952515</t>
   </si>
   <si>
     <t xml:space="preserve">6.89454412460327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94005298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05382490158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10691785812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15242719650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11450242996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01590013504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08416366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0462384223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09174823760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39513826370239</t>
+    <t xml:space="preserve">6.94005250930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05382394790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10691738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15242624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.114501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01590061187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08416271209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04623937606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09174776077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39513969421387</t>
   </si>
   <si>
     <t xml:space="preserve">7.35721397399902</t>
@@ -1406,34 +1406,34 @@
     <t xml:space="preserve">7.34204530715942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1220874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13725709915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12967109680176</t>
+    <t xml:space="preserve">7.12208843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13725614547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12967157363892</t>
   </si>
   <si>
     <t xml:space="preserve">7.25102806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22827386856079</t>
+    <t xml:space="preserve">7.22827339172363</t>
   </si>
   <si>
     <t xml:space="preserve">7.2055196762085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1979341506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16759586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37996768951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43306255340576</t>
+    <t xml:space="preserve">7.19793510437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16759490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37996816635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43306159973145</t>
   </si>
   <si>
     <t xml:space="preserve">7.49374008178711</t>
@@ -1442,34 +1442,34 @@
     <t xml:space="preserve">7.53924894332886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54683303833008</t>
+    <t xml:space="preserve">7.54683446884155</t>
   </si>
   <si>
     <t xml:space="preserve">7.75162267684937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79713106155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64543437957764</t>
+    <t xml:space="preserve">7.79713010787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64543533325195</t>
   </si>
   <si>
     <t xml:space="preserve">7.69094467163086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57717180252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45581674575806</t>
+    <t xml:space="preserve">7.57717227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45581531524658</t>
   </si>
   <si>
     <t xml:space="preserve">7.51649475097656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59992742538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50890922546387</t>
+    <t xml:space="preserve">7.59992599487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50890970230103</t>
   </si>
   <si>
     <t xml:space="preserve">7.56200361251831</t>
@@ -1478,55 +1478,55 @@
     <t xml:space="preserve">7.58475732803345</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55441904067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47857093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47098588943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4482307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7061128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88814783096313</t>
+    <t xml:space="preserve">7.55441761016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47856998443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47098636627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44823217391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70611333847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331792831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88814735412598</t>
   </si>
   <si>
     <t xml:space="preserve">8.25221538543701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61628437042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49492740631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17636871337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41908168792725</t>
+    <t xml:space="preserve">8.61628532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49492835998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17636680603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41908073425293</t>
   </si>
   <si>
     <t xml:space="preserve">8.11876964569092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08742237091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93068933486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04040336608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9620361328125</t>
+    <t xml:space="preserve">8.08742141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9306902885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04040241241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96203708648682</t>
   </si>
   <si>
     <t xml:space="preserve">8.25982856750488</t>
@@ -1535,16 +1535,16 @@
     <t xml:space="preserve">8.02472877502441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86799573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73477363586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83664989471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82097578048706</t>
+    <t xml:space="preserve">7.86799621582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7347731590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8366494178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82097625732422</t>
   </si>
   <si>
     <t xml:space="preserve">7.91501617431641</t>
@@ -1553,106 +1553,106 @@
     <t xml:space="preserve">7.97770929336548</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07174873352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.056077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85232353210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40088939666748</t>
+    <t xml:space="preserve">8.07175064086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05607604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85232305526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40088844299316</t>
   </si>
   <si>
     <t xml:space="preserve">8.46358203887939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62031555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30685043334961</t>
+    <t xml:space="preserve">8.6203145980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30684852600098</t>
   </si>
   <si>
     <t xml:space="preserve">8.1657886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33819484710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21280956268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2755012512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36954307556152</t>
+    <t xml:space="preserve">8.33819580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21280860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27550315856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36954212188721</t>
   </si>
   <si>
     <t xml:space="preserve">8.15011596679688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18146133422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13444232940674</t>
+    <t xml:space="preserve">8.18146324157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13444328308105</t>
   </si>
   <si>
     <t xml:space="preserve">8.22848129272461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43223476409912</t>
+    <t xml:space="preserve">8.43223571777344</t>
   </si>
   <si>
     <t xml:space="preserve">7.9933819770813</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19713592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75828218460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89934253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82881355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88367033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313943862915</t>
+    <t xml:space="preserve">8.19713497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75828313827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89934301376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82881307601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88366937637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81314039230347</t>
   </si>
   <si>
     <t xml:space="preserve">7.6799168586731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79746675491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41656303405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80530405044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68775415420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74261045455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00905704498291</t>
+    <t xml:space="preserve">7.79746627807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41656112670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80530309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68775320053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74261093139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00905609130859</t>
   </si>
   <si>
     <t xml:space="preserve">7.94636392593384</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75044679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7190990447998</t>
+    <t xml:space="preserve">7.75044727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71910095214844</t>
   </si>
   <si>
     <t xml:space="preserve">8.10309600830078</t>
@@ -1661,31 +1661,31 @@
     <t xml:space="preserve">8.82406806945801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37263202667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60773372650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48234558105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79581165313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9368724822998</t>
+    <t xml:space="preserve">9.37263298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60773277282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48234748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79581356048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93687343597412</t>
   </si>
   <si>
     <t xml:space="preserve">9.87417888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99956607818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1562976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5011110305786</t>
+    <t xml:space="preserve">9.99956512451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1562986373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5011100769043</t>
   </si>
   <si>
     <t xml:space="preserve">10.3757238388062</t>
@@ -1694,25 +1694,25 @@
     <t xml:space="preserve">10.5481300354004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2189912796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1719722747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95254421234131</t>
+    <t xml:space="preserve">10.2189903259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.171971321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95254516601562</t>
   </si>
   <si>
     <t xml:space="preserve">9.90552616119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88985157012939</t>
+    <t xml:space="preserve">9.88985252380371</t>
   </si>
   <si>
     <t xml:space="preserve">9.92119884490967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73311901092529</t>
+    <t xml:space="preserve">9.73311996459961</t>
   </si>
   <si>
     <t xml:space="preserve">9.76446628570557</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">9.57638645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96821880340576</t>
+    <t xml:space="preserve">9.96821975708008</t>
   </si>
   <si>
     <t xml:space="preserve">10.0309114456177</t>
@@ -1733,16 +1733,16 @@
     <t xml:space="preserve">10.250337600708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0152387619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1249523162842</t>
+    <t xml:space="preserve">10.0152378082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1249504089355</t>
   </si>
   <si>
     <t xml:space="preserve">10.3600511550903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2973585128784</t>
+    <t xml:space="preserve">10.2973575592041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3130302429199</t>
@@ -1751,13 +1751,13 @@
     <t xml:space="preserve">10.4384164810181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6264972686768</t>
+    <t xml:space="preserve">10.6264963150024</t>
   </si>
   <si>
     <t xml:space="preserve">10.657844543457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6108236312866</t>
+    <t xml:space="preserve">10.6108245849609</t>
   </si>
   <si>
     <t xml:space="preserve">10.5951519012451</t>
@@ -1778,40 +1778,40 @@
     <t xml:space="preserve">10.9556360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1280431747437</t>
+    <t xml:space="preserve">11.1280422210693</t>
   </si>
   <si>
     <t xml:space="preserve">11.0183305740356</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2377548217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0966968536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1750621795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1123695373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0810232162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9713087081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.798903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0936050415039</t>
+    <t xml:space="preserve">11.2377557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593904495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0966958999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1750631332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1123704910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0810222625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9713106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7989044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0936040878296</t>
   </si>
   <si>
     <t xml:space="preserve">9.68609809875488</t>
@@ -1823,34 +1823,34 @@
     <t xml:space="preserve">9.54503917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98080158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54194831848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3194317817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5075101852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53885746002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49183702468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66733551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44790744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38521480560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52627468109131</t>
+    <t xml:space="preserve">8.98080062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54194736480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31943130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50751066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53885650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49183797836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66733360290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44790840148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38521671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52627563476562</t>
   </si>
   <si>
     <t xml:space="preserve">9.01214694976807</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">8.93378067016602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38830661773682</t>
+    <t xml:space="preserve">9.38830757141113</t>
   </si>
   <si>
     <t xml:space="preserve">8.88676071166992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87108707427979</t>
+    <t xml:space="preserve">8.87108612060547</t>
   </si>
   <si>
     <t xml:space="preserve">9.12185955047607</t>
@@ -1880,19 +1880,19 @@
     <t xml:space="preserve">8.91810703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15320682525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90243434906006</t>
+    <t xml:space="preserve">9.15320777893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90243339538574</t>
   </si>
   <si>
     <t xml:space="preserve">9.05916690826416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04349422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21590042114258</t>
+    <t xml:space="preserve">9.04349327087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21589946746826</t>
   </si>
   <si>
     <t xml:space="preserve">8.96512699127197</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">9.12407779693604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01022911071777</t>
+    <t xml:space="preserve">9.01022815704346</t>
   </si>
   <si>
     <t xml:space="preserve">8.68495082855225</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">9.48188495635986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61199474334717</t>
+    <t xml:space="preserve">9.61199569702148</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625541687012</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">10.1812343597412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2137622833252</t>
+    <t xml:space="preserve">10.2137632369995</t>
   </si>
   <si>
     <t xml:space="preserve">10.2788190841675</t>
@@ -1973,19 +1973,19 @@
     <t xml:space="preserve">10.1324434280396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1974983215332</t>
+    <t xml:space="preserve">10.1974992752075</t>
   </si>
   <si>
     <t xml:space="preserve">10.3276100158691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2462911605835</t>
+    <t xml:space="preserve">10.2462902069092</t>
   </si>
   <si>
     <t xml:space="preserve">10.555305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8480558395386</t>
+    <t xml:space="preserve">10.8480567932129</t>
   </si>
   <si>
     <t xml:space="preserve">10.8805847167969</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">10.9293756484985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.685417175293</t>
+    <t xml:space="preserve">10.6854162216187</t>
   </si>
   <si>
     <t xml:space="preserve">10.6366243362427</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">10.9781675338745</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1245431900024</t>
+    <t xml:space="preserve">11.1245441436768</t>
   </si>
   <si>
     <t xml:space="preserve">11.1408071517944</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">11.4498224258423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4660863876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4823503494263</t>
+    <t xml:space="preserve">11.4660873413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.482349395752</t>
   </si>
   <si>
     <t xml:space="preserve">11.3359746932983</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">10.8643198013306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5390405654907</t>
+    <t xml:space="preserve">10.539041519165</t>
   </si>
   <si>
     <t xml:space="preserve">10.522777557373</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">10.6040964126587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7342081069946</t>
+    <t xml:space="preserve">10.7342090606689</t>
   </si>
   <si>
     <t xml:space="preserve">10.6203603744507</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">10.4577207565308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3764028549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.571569442749</t>
+    <t xml:space="preserve">10.3764019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5715684890747</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089288711548</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">10.9944334030151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6691522598267</t>
+    <t xml:space="preserve">10.669153213501</t>
   </si>
   <si>
     <t xml:space="preserve">10.7830009460449</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9619045257568</t>
+    <t xml:space="preserve">10.9619035720825</t>
   </si>
   <si>
     <t xml:space="preserve">10.9456396102905</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">11.4172954559326</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3034467697144</t>
+    <t xml:space="preserve">11.30344581604</t>
   </si>
   <si>
     <t xml:space="preserve">9.9860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0836496353149</t>
+    <t xml:space="preserve">10.0836505889893</t>
   </si>
   <si>
     <t xml:space="preserve">10.4414567947388</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">11.1082792282104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0269603729248</t>
+    <t xml:space="preserve">11.0269594192505</t>
   </si>
   <si>
     <t xml:space="preserve">10.9131126403809</t>
@@ -2156,19 +2156,19 @@
     <t xml:space="preserve">11.2546548843384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3522386550903</t>
+    <t xml:space="preserve">11.3522396087646</t>
   </si>
   <si>
     <t xml:space="preserve">11.4010314941406</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3197107315063</t>
+    <t xml:space="preserve">11.3197116851807</t>
   </si>
   <si>
     <t xml:space="preserve">11.1733360290527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0106954574585</t>
+    <t xml:space="preserve">11.0106964111328</t>
   </si>
   <si>
     <t xml:space="preserve">11.5311431884766</t>
@@ -2189,10 +2189,10 @@
     <t xml:space="preserve">12.3118124008179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5882978439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1979646682739</t>
+    <t xml:space="preserve">12.5882987976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1979637145996</t>
   </si>
   <si>
     <t xml:space="preserve">11.8726844787598</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">11.5961990356445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.954005241394</t>
+    <t xml:space="preserve">11.9540042877197</t>
   </si>
   <si>
     <t xml:space="preserve">11.9865322113037</t>
@@ -2228,19 +2228,19 @@
     <t xml:space="preserve">12.2792844772339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4093961715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5069799423218</t>
+    <t xml:space="preserve">12.4093952178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5069789886475</t>
   </si>
   <si>
     <t xml:space="preserve">12.4581880569458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4907150268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8973140716553</t>
+    <t xml:space="preserve">12.4907159805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8973150253296</t>
   </si>
   <si>
     <t xml:space="preserve">13.0111627578735</t>
@@ -2261,25 +2261,25 @@
     <t xml:space="preserve">12.8810510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1738014221191</t>
+    <t xml:space="preserve">13.1738023757935</t>
   </si>
   <si>
     <t xml:space="preserve">13.2713842391968</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3527050018311</t>
+    <t xml:space="preserve">13.3527059555054</t>
   </si>
   <si>
     <t xml:space="preserve">13.7267751693726</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8243598937988</t>
+    <t xml:space="preserve">13.8243589401245</t>
   </si>
   <si>
     <t xml:space="preserve">14.0520544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.23095703125</t>
+    <t xml:space="preserve">14.2309589385986</t>
   </si>
   <si>
     <t xml:space="preserve">14.2634878158569</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">13.6129274368286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8080940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8894166946411</t>
+    <t xml:space="preserve">13.8080959320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8894157409668</t>
   </si>
   <si>
     <t xml:space="preserve">13.6454563140869</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8406238555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918300628662</t>
+    <t xml:space="preserve">13.8406229019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918310165405</t>
   </si>
   <si>
     <t xml:space="preserve">14.0032634735107</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">13.9544706344604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3448066711426</t>
+    <t xml:space="preserve">14.3448047637939</t>
   </si>
   <si>
     <t xml:space="preserve">14.1496391296387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2472229003906</t>
+    <t xml:space="preserve">14.2472238540649</t>
   </si>
   <si>
     <t xml:space="preserve">14.4749174118042</t>
@@ -4464,6 +4464,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.57999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63000011444092</t>
   </si>
 </sst>
 </file>
@@ -70738,7 +70741,7 @@
     </row>
     <row r="2537">
       <c r="A2537" s="1" t="n">
-        <v>46010.6910532407</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2537" t="n">
         <v>53794</v>
@@ -70759,6 +70762,32 @@
         <v>1483</v>
       </c>
       <c r="H2537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="1" t="n">
+        <v>46013.6911226852</v>
+      </c>
+      <c r="B2538" t="n">
+        <v>91637</v>
+      </c>
+      <c r="C2538" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>7.48000001907349</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>7.57000017166138</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>7.63000011444092</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H2538" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="1487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="1486">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04141759872437</t>
+    <t xml:space="preserve">4.04141712188721</t>
   </si>
   <si>
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447938919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93978953361511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8279983997345</t>
+    <t xml:space="preserve">4.02447986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93978905677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82799768447876</t>
   </si>
   <si>
     <t xml:space="preserve">3.7805712223053</t>
@@ -59,28 +59,28 @@
     <t xml:space="preserve">3.70943188667297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75685834884644</t>
+    <t xml:space="preserve">3.75685858726501</t>
   </si>
   <si>
     <t xml:space="preserve">3.74330735206604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80089712142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040863037109</t>
+    <t xml:space="preserve">3.8008975982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040886878967</t>
   </si>
   <si>
     <t xml:space="preserve">3.68571805953979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66539216041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5637640953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65184211730957</t>
+    <t xml:space="preserve">3.66539287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56376457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65184283256531</t>
   </si>
   <si>
     <t xml:space="preserve">3.72636961936951</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">3.70265626907349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65861701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69249391555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74669623374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5976402759552</t>
+    <t xml:space="preserve">3.65861749649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69249367713928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74669551849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59764099121094</t>
   </si>
   <si>
     <t xml:space="preserve">3.59086537361145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58408975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49601244926453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46213626861572</t>
+    <t xml:space="preserve">3.5840904712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49601221084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4621365070343</t>
   </si>
   <si>
     <t xml:space="preserve">3.51633810997009</t>
@@ -119,31 +119,31 @@
     <t xml:space="preserve">3.38760852813721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40793466567993</t>
+    <t xml:space="preserve">3.40793395042419</t>
   </si>
   <si>
     <t xml:space="preserve">3.50956296920776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5569896697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56715202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57731509208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54682636260986</t>
+    <t xml:space="preserve">3.55698943138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56715226173401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61119031906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57731485366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54682660102844</t>
   </si>
   <si>
     <t xml:space="preserve">3.52650046348572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50278782844543</t>
+    <t xml:space="preserve">3.50278735160828</t>
   </si>
   <si>
     <t xml:space="preserve">3.56037664413452</t>
@@ -152,34 +152,34 @@
     <t xml:space="preserve">3.58070230484009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60102772712708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54343867301941</t>
+    <t xml:space="preserve">3.60102820396423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54343891143799</t>
   </si>
   <si>
     <t xml:space="preserve">3.57053995132446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6450674533844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78734636306763</t>
+    <t xml:space="preserve">3.64506793022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78734683990479</t>
   </si>
   <si>
     <t xml:space="preserve">3.84154844284058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86526155471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85171103477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92962598800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93640089035034</t>
+    <t xml:space="preserve">3.8652617931366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85171127319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92962622642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93640112876892</t>
   </si>
   <si>
     <t xml:space="preserve">3.91607546806335</t>
@@ -188,34 +188,34 @@
     <t xml:space="preserve">3.90252494812012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89575052261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285060882568</t>
+    <t xml:space="preserve">3.89575028419495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285108566284</t>
   </si>
   <si>
     <t xml:space="preserve">3.9093005657196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97027778625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87881231307983</t>
+    <t xml:space="preserve">3.9702775478363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87881207466125</t>
   </si>
   <si>
     <t xml:space="preserve">3.85848665237427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94317698478699</t>
+    <t xml:space="preserve">3.94317626953125</t>
   </si>
   <si>
     <t xml:space="preserve">3.89913773536682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94656372070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95672702789307</t>
+    <t xml:space="preserve">3.94656443595886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95672678947449</t>
   </si>
   <si>
     <t xml:space="preserve">3.96350288391113</t>
@@ -224,49 +224,49 @@
     <t xml:space="preserve">3.91268825531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97366499900818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91946315765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87203693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88704800605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87291264533997</t>
+    <t xml:space="preserve">3.97366523742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91946363449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87203741073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88704776763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8729133605957</t>
   </si>
   <si>
     <t xml:space="preserve">3.85877823829651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83757567405701</t>
+    <t xml:space="preserve">3.83757638931274</t>
   </si>
   <si>
     <t xml:space="preserve">3.86231207847595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8764476776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89411544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90118217468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058184623718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9435863494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95418691635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96125507354736</t>
+    <t xml:space="preserve">3.87644648551941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89411520957947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90118288993835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89058136940002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94358658790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95418739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96125555038452</t>
   </si>
   <si>
     <t xml:space="preserve">4.01426076889038</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">4.02486181259155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08846759796143</t>
+    <t xml:space="preserve">4.08846807479858</t>
   </si>
   <si>
     <t xml:space="preserve">4.05666446685791</t>
@@ -287,148 +287,148 @@
     <t xml:space="preserve">3.9930579662323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00719356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97539019584656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97185611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80223989486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78103709220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75630164146423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7492344379425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90471625328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9223849773407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065379142761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03546190261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75983548164368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80930662155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83050894737244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.869380235672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82344126701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80577325820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84111094474792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81637382507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8658459186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89764857292175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93651914596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90825057029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91531777381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97892379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00012540817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02132844924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95772194862366</t>
+    <t xml:space="preserve">4.00719308853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97539067268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97185659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80224061012268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78103733062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75630187988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74923372268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90471601486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92238521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065426826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03546237945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75983572006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80930757522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83050847053528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86937975883484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82344198226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80577349662781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84111022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8163743019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86584520339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89764881134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93651962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90825009346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91531753540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97892332077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00012588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02132749557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95772099494934</t>
   </si>
   <si>
     <t xml:space="preserve">3.84464335441589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81284141540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77043676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76336908340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74570035934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72449851036072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77397012710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78810453414917</t>
+    <t xml:space="preserve">3.81284093856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77043652534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690220832825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7633683681488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74570083618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72449898719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77397060394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78810501098633</t>
   </si>
   <si>
     <t xml:space="preserve">3.81990838050842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72803235054016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73863339424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7315661907196</t>
+    <t xml:space="preserve">3.72803282737732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73863387107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73156595230103</t>
   </si>
   <si>
     <t xml:space="preserve">3.73509955406189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65382528305054</t>
+    <t xml:space="preserve">3.65382480621338</t>
   </si>
   <si>
     <t xml:space="preserve">3.6396906375885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66089248657227</t>
+    <t xml:space="preserve">3.66089272499084</t>
   </si>
   <si>
     <t xml:space="preserve">3.61848783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61142063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62555575370789</t>
+    <t xml:space="preserve">3.61142134666443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62555646896362</t>
   </si>
   <si>
     <t xml:space="preserve">3.61495471000671</t>
@@ -440,31 +440,31 @@
     <t xml:space="preserve">3.74216723442078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91885137557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98599076271057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99659276008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87997984886169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88351440429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79517221450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82697558403015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79163885116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8481776714325</t>
+    <t xml:space="preserve">3.91885161399841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98599123954773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99659204483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87998008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8835141658783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79517197608948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82697534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79163765907288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84817790985107</t>
   </si>
   <si>
     <t xml:space="preserve">3.71036410331726</t>
@@ -482,19 +482,19 @@
     <t xml:space="preserve">4.08493375778198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09906816482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05313158035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04959678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09200096130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10967016220093</t>
+    <t xml:space="preserve">4.0990686416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05313110351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04959774017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09200143814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10966968536377</t>
   </si>
   <si>
     <t xml:space="preserve">4.07786655426025</t>
@@ -506,19 +506,19 @@
     <t xml:space="preserve">4.04606342315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06373167037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10613536834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1026029586792</t>
+    <t xml:space="preserve">4.0637321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10613584518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10260152816772</t>
   </si>
   <si>
     <t xml:space="preserve">4.13440608978271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12733840942383</t>
+    <t xml:space="preserve">4.12733793258667</t>
   </si>
   <si>
     <t xml:space="preserve">4.16974210739136</t>
@@ -527,25 +527,25 @@
     <t xml:space="preserve">4.18387699127197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1591420173645</t>
+    <t xml:space="preserve">4.15914106369019</t>
   </si>
   <si>
     <t xml:space="preserve">4.24041604995728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21568059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27575302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34642696380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36762762069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35349273681641</t>
+    <t xml:space="preserve">4.21568012237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27575254440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34642648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36762809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35349321365356</t>
   </si>
   <si>
     <t xml:space="preserve">4.31108951568604</t>
@@ -557,31 +557,31 @@
     <t xml:space="preserve">4.38176298141479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50897550582886</t>
+    <t xml:space="preserve">4.5089750289917</t>
   </si>
   <si>
     <t xml:space="preserve">4.72806310653687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91181516647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94715166091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19450950622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2227783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2298469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2263126373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09203290939331</t>
+    <t xml:space="preserve">4.91181564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94715213775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19450902938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22277879714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22984743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22631216049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09203243255615</t>
   </si>
   <si>
     <t xml:space="preserve">5.07436418533325</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">5.08496570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11676836013794</t>
+    <t xml:space="preserve">5.1167688369751</t>
   </si>
   <si>
     <t xml:space="preserve">5.10616779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15210485458374</t>
+    <t xml:space="preserve">5.15210580825806</t>
   </si>
   <si>
     <t xml:space="preserve">5.15917253494263</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">5.14503812789917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13090372085571</t>
+    <t xml:space="preserve">5.13090324401855</t>
   </si>
   <si>
     <t xml:space="preserve">5.24751472473145</t>
@@ -620,67 +620,67 @@
     <t xml:space="preserve">5.26871681213379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59734916687012</t>
+    <t xml:space="preserve">5.59734869003296</t>
   </si>
   <si>
     <t xml:space="preserve">5.51254081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35705852508545</t>
+    <t xml:space="preserve">5.35705900192261</t>
   </si>
   <si>
     <t xml:space="preserve">5.47720384597778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37119293212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44186735153198</t>
+    <t xml:space="preserve">5.37119340896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44186639785767</t>
   </si>
   <si>
     <t xml:space="preserve">5.53020906448364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61199712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65216159820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68867444992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62295150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61929941177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5973916053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42213153839111</t>
+    <t xml:space="preserve">5.61199760437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65216112136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68867349624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62295055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61930084228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59739208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42213201522827</t>
   </si>
   <si>
     <t xml:space="preserve">5.41848039627075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5535774230957</t>
+    <t xml:space="preserve">5.55357694625854</t>
   </si>
   <si>
     <t xml:space="preserve">5.56087923049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49880838394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46229553222656</t>
+    <t xml:space="preserve">5.49880790710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4622950553894</t>
   </si>
   <si>
     <t xml:space="preserve">5.55722856521606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45499229431152</t>
+    <t xml:space="preserve">5.45499181747437</t>
   </si>
   <si>
     <t xml:space="preserve">5.36736249923706</t>
@@ -689,16 +689,16 @@
     <t xml:space="preserve">5.37466526031494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43308544158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40387582778931</t>
+    <t xml:space="preserve">5.4330849647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40387487411499</t>
   </si>
   <si>
     <t xml:space="preserve">5.47690010070801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4476900100708</t>
+    <t xml:space="preserve">5.44769096374512</t>
   </si>
   <si>
     <t xml:space="preserve">5.48055171966553</t>
@@ -710,28 +710,28 @@
     <t xml:space="preserve">5.54627418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60104322433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41117811203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51341342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54992532730103</t>
+    <t xml:space="preserve">5.60104417800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41117715835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51341390609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54992580413818</t>
   </si>
   <si>
     <t xml:space="preserve">5.45134162902832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61564826965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50611019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34545516967773</t>
+    <t xml:space="preserve">5.61564874649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50611066818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34545564651489</t>
   </si>
   <si>
     <t xml:space="preserve">5.37101364135742</t>
@@ -740,46 +740,46 @@
     <t xml:space="preserve">5.31259298324585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28703451156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15558910369873</t>
+    <t xml:space="preserve">5.287034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15558862686157</t>
   </si>
   <si>
     <t xml:space="preserve">5.12637901306152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2724289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31989622116089</t>
+    <t xml:space="preserve">5.27242946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31989574432373</t>
   </si>
   <si>
     <t xml:space="preserve">5.14098358154297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40752601623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38927030563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37831592559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24321937561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46959781646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41482877731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42578268051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44038724899292</t>
+    <t xml:space="preserve">5.40752649307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38926982879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3783164024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24321889877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46959829330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41482830047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42578315734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44038772583008</t>
   </si>
   <si>
     <t xml:space="preserve">5.48420286178589</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">5.57183408737183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57913589477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56453084945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52071571350098</t>
+    <t xml:space="preserve">5.57913541793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56453037261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52071523666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.53897190093994</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">5.65581178665161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58643865585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57548427581787</t>
+    <t xml:space="preserve">5.58643817901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57548475265503</t>
   </si>
   <si>
     <t xml:space="preserve">5.50976228713989</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">5.60469484329224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59008932113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75804758071899</t>
+    <t xml:space="preserve">5.59009027481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75804805755615</t>
   </si>
   <si>
     <t xml:space="preserve">5.79456043243408</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">5.92965745925903</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94426345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99903154373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93696069717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98807764053345</t>
+    <t xml:space="preserve">5.94426298141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99903202056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93696117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98807716369629</t>
   </si>
   <si>
     <t xml:space="preserve">5.83107376098633</t>
@@ -857,97 +857,97 @@
     <t xml:space="preserve">5.88584280014038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83472442626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9588680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76900100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91140079498291</t>
+    <t xml:space="preserve">5.83472394943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95886754989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76900196075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140127182007</t>
   </si>
   <si>
     <t xml:space="preserve">5.83837556838989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84202766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87123775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.783607006073</t>
+    <t xml:space="preserve">5.84202671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87123727798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78360748291016</t>
   </si>
   <si>
     <t xml:space="preserve">5.85298109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70327949523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82742166519165</t>
+    <t xml:space="preserve">5.7032790184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82742214202881</t>
   </si>
   <si>
     <t xml:space="preserve">5.86393451690674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75439691543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72883749008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68502187728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66676664352417</t>
+    <t xml:space="preserve">5.75439643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72883701324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68502235412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66676616668701</t>
   </si>
   <si>
     <t xml:space="preserve">5.88949346542358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78725814819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77995491027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73614025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60834550857544</t>
+    <t xml:space="preserve">5.78725862503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77995538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73614072799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6083459854126</t>
   </si>
   <si>
     <t xml:space="preserve">5.63025379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53532028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76169919967651</t>
+    <t xml:space="preserve">5.53532075881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76169967651367</t>
   </si>
   <si>
     <t xml:space="preserve">5.62660217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68137216567993</t>
+    <t xml:space="preserve">5.68137264251709</t>
   </si>
   <si>
     <t xml:space="preserve">5.73979139328003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76535129547119</t>
+    <t xml:space="preserve">5.76535081863403</t>
   </si>
   <si>
     <t xml:space="preserve">5.80916547775269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80551433563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82377099990845</t>
+    <t xml:space="preserve">5.80551481246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82377052307129</t>
   </si>
   <si>
     <t xml:space="preserve">5.87853956222534</t>
@@ -956,40 +956,40 @@
     <t xml:space="preserve">5.82011938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90409851074219</t>
+    <t xml:space="preserve">5.90409898757935</t>
   </si>
   <si>
     <t xml:space="preserve">5.92600631713867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92235469818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95156478881836</t>
+    <t xml:space="preserve">5.92235374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95156526565552</t>
   </si>
   <si>
     <t xml:space="preserve">6.02459049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06110334396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00998544692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09031343460083</t>
+    <t xml:space="preserve">6.06110382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00998497009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09031295776367</t>
   </si>
   <si>
     <t xml:space="preserve">6.2290620803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18524646759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03189373016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03919553756714</t>
+    <t xml:space="preserve">6.18524599075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03189325332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03919696807861</t>
   </si>
   <si>
     <t xml:space="preserve">6.04649782180786</t>
@@ -998,31 +998,31 @@
     <t xml:space="preserve">6.25096988677979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20715379714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14143085479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12682628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7982120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72518682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96617078781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00268316268921</t>
+    <t xml:space="preserve">6.20715427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14143037796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12682580947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79821157455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72518730163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96617031097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00268220901489</t>
   </si>
   <si>
     <t xml:space="preserve">5.89314460754395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84932994842529</t>
+    <t xml:space="preserve">5.84933042526245</t>
   </si>
   <si>
     <t xml:space="preserve">5.973473072052</t>
@@ -1031,25 +1031,25 @@
     <t xml:space="preserve">5.99538040161133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11952352523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15603637695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10491800308228</t>
+    <t xml:space="preserve">6.1195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15603590011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10491895675659</t>
   </si>
   <si>
     <t xml:space="preserve">5.98077535629272</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90044736862183</t>
+    <t xml:space="preserve">5.90044689178467</t>
   </si>
   <si>
     <t xml:space="preserve">6.1487340927124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09761619567871</t>
+    <t xml:space="preserve">6.09761571884155</t>
   </si>
   <si>
     <t xml:space="preserve">6.05380058288574</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">6.07570791244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08301067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17794418334961</t>
+    <t xml:space="preserve">6.08301115036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17794322967529</t>
   </si>
   <si>
     <t xml:space="preserve">6.17064094543457</t>
@@ -1070,16 +1070,16 @@
     <t xml:space="preserve">6.24366664886475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28017950057983</t>
+    <t xml:space="preserve">6.28017997741699</t>
   </si>
   <si>
     <t xml:space="preserve">6.38636589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31810283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23467063903809</t>
+    <t xml:space="preserve">6.31810331344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23467016220093</t>
   </si>
   <si>
     <t xml:space="preserve">6.28017902374268</t>
@@ -1088,121 +1088,121 @@
     <t xml:space="preserve">6.15882253646851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2725944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26500988006592</t>
+    <t xml:space="preserve">6.27259540557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26500940322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.21191596984863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1815767288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15123796463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02988195419312</t>
+    <t xml:space="preserve">6.18157720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15123701095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02988243103027</t>
   </si>
   <si>
     <t xml:space="preserve">6.05263614654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25742435455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22708606719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.249840259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29534816741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3711953163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1891622543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16640853881836</t>
+    <t xml:space="preserve">6.25742483139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22708559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24983978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29534912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37119579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18916130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1664080619812</t>
   </si>
   <si>
     <t xml:space="preserve">6.20433187484741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0147123336792</t>
+    <t xml:space="preserve">6.01471185684204</t>
   </si>
   <si>
     <t xml:space="preserve">6.04505157470703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00712776184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98437309265137</t>
+    <t xml:space="preserve">6.00712823867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98437404632568</t>
   </si>
   <si>
     <t xml:space="preserve">6.12089872360229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13606834411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11331510543823</t>
+    <t xml:space="preserve">6.13606882095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11331462860107</t>
   </si>
   <si>
     <t xml:space="preserve">6.09055995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96161937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08297538757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14365386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10572910308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06022119522095</t>
+    <t xml:space="preserve">5.96161890029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0829758644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14365434646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10572957992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06022071838379</t>
   </si>
   <si>
     <t xml:space="preserve">5.99954271316528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95403432846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93886518478394</t>
+    <t xml:space="preserve">5.95403480529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93886470794678</t>
   </si>
   <si>
     <t xml:space="preserve">6.06780576705933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91611051559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94644975662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818670272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746652603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02229738235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99195766448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86301755905151</t>
+    <t xml:space="preserve">5.9161114692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94645023345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818717956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746700286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02229690551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99195861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86301708221436</t>
   </si>
   <si>
     <t xml:space="preserve">6.07539081573486</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">6.24225521087646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47738265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63666296005249</t>
+    <t xml:space="preserve">6.47738218307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63666248321533</t>
   </si>
   <si>
     <t xml:space="preserve">6.46221399307251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57598495483398</t>
+    <t xml:space="preserve">6.57598447799683</t>
   </si>
   <si>
     <t xml:space="preserve">6.56081438064575</t>
@@ -1229,19 +1229,19 @@
     <t xml:space="preserve">6.60632371902466</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55323123931885</t>
+    <t xml:space="preserve">6.55323076248169</t>
   </si>
   <si>
     <t xml:space="preserve">6.65183258056641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53806018829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48496723175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61390829086304</t>
+    <t xml:space="preserve">6.53806114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48496770858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61390781402588</t>
   </si>
   <si>
     <t xml:space="preserve">6.66700220108032</t>
@@ -1253,34 +1253,34 @@
     <t xml:space="preserve">6.34085702896118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39395093917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41670513153076</t>
+    <t xml:space="preserve">6.39395046234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4167046546936</t>
   </si>
   <si>
     <t xml:space="preserve">6.42428922653198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53047609329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59115314483643</t>
+    <t xml:space="preserve">6.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59115362167358</t>
   </si>
   <si>
     <t xml:space="preserve">6.54564571380615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56839990615845</t>
+    <t xml:space="preserve">6.56840038299561</t>
   </si>
   <si>
     <t xml:space="preserve">6.44704389572144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3484411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21950101852417</t>
+    <t xml:space="preserve">6.34844160079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21950054168701</t>
   </si>
   <si>
     <t xml:space="preserve">6.40911960601807</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">6.32568740844727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28776407241821</t>
+    <t xml:space="preserve">6.28776359558105</t>
   </si>
   <si>
     <t xml:space="preserve">6.68975591659546</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">6.37878036499023</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36361122131348</t>
+    <t xml:space="preserve">6.36361074447632</t>
   </si>
   <si>
     <t xml:space="preserve">6.46979856491089</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">6.51530694961548</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31051731109619</t>
+    <t xml:space="preserve">6.31051778793335</t>
   </si>
   <si>
     <t xml:space="preserve">6.35602712631226</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">6.19674682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40153455734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72009563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75801849365234</t>
+    <t xml:space="preserve">6.40153503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72009468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7580189704895</t>
   </si>
   <si>
     <t xml:space="preserve">6.80352735519409</t>
@@ -1343,25 +1343,25 @@
     <t xml:space="preserve">6.78835773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73526382446289</t>
+    <t xml:space="preserve">6.73526430130005</t>
   </si>
   <si>
     <t xml:space="preserve">6.84903526306152</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8642053604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81111288070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84145212173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81869554519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90212917327881</t>
+    <t xml:space="preserve">6.86420488357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81111192703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8414511680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81869602203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90212869644165</t>
   </si>
   <si>
     <t xml:space="preserve">6.99314641952515</t>
@@ -1370,73 +1370,73 @@
     <t xml:space="preserve">6.89454507827759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9400520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05382442474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10691738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15242671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11450290679932</t>
+    <t xml:space="preserve">6.94005250930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05382394790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10691785812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15242624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.114501953125</t>
   </si>
   <si>
     <t xml:space="preserve">7.01590013504028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08416271209717</t>
+    <t xml:space="preserve">7.08416318893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.04623889923096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09174871444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39513731002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35721445083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34204578399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12208843231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13725566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12967157363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25102806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22827386856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20551919937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19793462753296</t>
+    <t xml:space="preserve">7.09174823760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39513778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35721492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34204530715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1220874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13725662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12967205047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25102758407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22827291488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2055196762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19793510437012</t>
   </si>
   <si>
     <t xml:space="preserve">7.16759538650513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37996864318848</t>
+    <t xml:space="preserve">7.37996816635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.4330620765686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49374008178711</t>
+    <t xml:space="preserve">7.49374103546143</t>
   </si>
   <si>
     <t xml:space="preserve">7.53924751281738</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">7.54683399200439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75162172317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79713010787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64543533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6909441947937</t>
+    <t xml:space="preserve">7.75162267684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79712915420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64543581008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69094324111938</t>
   </si>
   <si>
     <t xml:space="preserve">7.57717227935791</t>
@@ -1466,79 +1466,79 @@
     <t xml:space="preserve">7.5164942741394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59992647171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50890874862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56200313568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58475732803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55441856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47856998443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47098636627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4482307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70611238479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331792831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88814735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25221538543701</t>
+    <t xml:space="preserve">7.59992694854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50890922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56200218200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58475685119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55441904067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47857046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47098588943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44823026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7061128616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331602096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88814640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25221633911133</t>
   </si>
   <si>
     <t xml:space="preserve">8.61628437042236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49492835998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17636775970459</t>
+    <t xml:space="preserve">8.49492645263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17636871337891</t>
   </si>
   <si>
     <t xml:space="preserve">8.41908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11876964569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08742237091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93068838119507</t>
+    <t xml:space="preserve">8.11876773834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08742332458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93068933486938</t>
   </si>
   <si>
     <t xml:space="preserve">8.04040336608887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96203517913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25982761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02472972869873</t>
+    <t xml:space="preserve">7.9620361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25982856750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02472877502441</t>
   </si>
   <si>
     <t xml:space="preserve">7.86799621582031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73477220535278</t>
+    <t xml:space="preserve">7.73477268218994</t>
   </si>
   <si>
     <t xml:space="preserve">7.8366494178772</t>
@@ -1547,22 +1547,22 @@
     <t xml:space="preserve">7.82097625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91501522064209</t>
+    <t xml:space="preserve">7.91501712799072</t>
   </si>
   <si>
     <t xml:space="preserve">7.97770929336548</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07175064086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05607604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85232305526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40088844299316</t>
+    <t xml:space="preserve">8.07174873352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05607509613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85232353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40088939666748</t>
   </si>
   <si>
     <t xml:space="preserve">8.46358108520508</t>
@@ -1571,61 +1571,61 @@
     <t xml:space="preserve">8.6203145980835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30684852600098</t>
+    <t xml:space="preserve">8.30684947967529</t>
   </si>
   <si>
     <t xml:space="preserve">8.1657886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33819675445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21280860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27550315856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36954212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15011501312256</t>
+    <t xml:space="preserve">8.33819580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21280765533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27550411224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36954307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15011405944824</t>
   </si>
   <si>
     <t xml:space="preserve">8.18146228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13444232940674</t>
+    <t xml:space="preserve">8.13444328308105</t>
   </si>
   <si>
     <t xml:space="preserve">8.22848224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43223667144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99338293075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19713592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75828218460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89934301376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82881307601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88367033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313991546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67991638183594</t>
+    <t xml:space="preserve">8.43223571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99338340759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19713497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7582836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89934349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82881259918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88366937637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313943862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6799168586731</t>
   </si>
   <si>
     <t xml:space="preserve">7.79746627807617</t>
@@ -1634,19 +1634,19 @@
     <t xml:space="preserve">8.4165620803833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80530309677124</t>
+    <t xml:space="preserve">7.8053035736084</t>
   </si>
   <si>
     <t xml:space="preserve">7.68775415420532</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74261093139648</t>
+    <t xml:space="preserve">7.74261045455933</t>
   </si>
   <si>
     <t xml:space="preserve">8.00905609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94636297225952</t>
+    <t xml:space="preserve">7.94636344909668</t>
   </si>
   <si>
     <t xml:space="preserve">7.75044727325439</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">8.1030969619751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82406806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37263298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60773372650146</t>
+    <t xml:space="preserve">8.82406711578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.372633934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60773181915283</t>
   </si>
   <si>
     <t xml:space="preserve">9.48234748840332</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">9.9368724822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87417984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9995641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1562986373901</t>
+    <t xml:space="preserve">9.87417888641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99956607818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1562976837158</t>
   </si>
   <si>
     <t xml:space="preserve">10.5011100769043</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">10.5481300354004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2189912796021</t>
+    <t xml:space="preserve">10.2189903259277</t>
   </si>
   <si>
     <t xml:space="preserve">10.171971321106</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">9.95254421234131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90552520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88985157012939</t>
+    <t xml:space="preserve">9.90552616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88985061645508</t>
   </si>
   <si>
     <t xml:space="preserve">9.92119789123535</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">9.73311996459961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76446533203125</t>
+    <t xml:space="preserve">9.76446723937988</t>
   </si>
   <si>
     <t xml:space="preserve">9.57638645172119</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">9.96821880340576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0309114456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4854373931885</t>
+    <t xml:space="preserve">10.030912399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4854383468628</t>
   </si>
   <si>
     <t xml:space="preserve">10.250337600708</t>
@@ -1736,16 +1736,16 @@
     <t xml:space="preserve">10.0152378082275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1249504089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.360050201416</t>
+    <t xml:space="preserve">10.1249513626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3600511550903</t>
   </si>
   <si>
     <t xml:space="preserve">10.2973585128784</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3130311965942</t>
+    <t xml:space="preserve">10.3130302429199</t>
   </si>
   <si>
     <t xml:space="preserve">10.4384174346924</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">10.6578435897827</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6108236312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5951499938965</t>
+    <t xml:space="preserve">10.6108226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5951509475708</t>
   </si>
   <si>
     <t xml:space="preserve">10.5794763565063</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">10.9869823455811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9556360244751</t>
+    <t xml:space="preserve">10.9556350708008</t>
   </si>
   <si>
     <t xml:space="preserve">11.1280422210693</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">11.2377557754517</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1593904495239</t>
+    <t xml:space="preserve">11.1593894958496</t>
   </si>
   <si>
     <t xml:space="preserve">11.0966968536377</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">11.1750621795654</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1123695373535</t>
+    <t xml:space="preserve">11.1123704910278</t>
   </si>
   <si>
     <t xml:space="preserve">11.0810222625732</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">10.9713096618652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7989053726196</t>
+    <t xml:space="preserve">10.798903465271</t>
   </si>
   <si>
     <t xml:space="preserve">10.0622587203979</t>
@@ -1823,115 +1823,115 @@
     <t xml:space="preserve">9.54503917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98080062866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54194736480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31942987442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50751113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53885698318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49183797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66733455657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44790744781494</t>
+    <t xml:space="preserve">8.98079967498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54194831848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31943082809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5075101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53885793685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49183702468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66733551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44790935516357</t>
   </si>
   <si>
     <t xml:space="preserve">8.38521480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52627468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01214790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45099925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10618686676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93378162384033</t>
+    <t xml:space="preserve">8.52627372741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01214694976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45100021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10618782043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93378067016602</t>
   </si>
   <si>
     <t xml:space="preserve">9.38830661773682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88676166534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8710880279541</t>
+    <t xml:space="preserve">8.88675975799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87108612060547</t>
   </si>
   <si>
     <t xml:space="preserve">9.12186050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9181079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15320682525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90243339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05916595458984</t>
+    <t xml:space="preserve">8.91810703277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15320587158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90243530273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05916690826416</t>
   </si>
   <si>
     <t xml:space="preserve">9.04349422454834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21589946746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96512794494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30298137664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12407779693604</t>
+    <t xml:space="preserve">9.21590042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96512699127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30298042297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12407684326172</t>
   </si>
   <si>
     <t xml:space="preserve">9.01023006439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68495082855225</t>
+    <t xml:space="preserve">8.68495178222656</t>
   </si>
   <si>
     <t xml:space="preserve">8.50604724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70121383666992</t>
+    <t xml:space="preserve">8.70121479034424</t>
   </si>
   <si>
     <t xml:space="preserve">9.18913269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9289083480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76626968383789</t>
+    <t xml:space="preserve">8.92890930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76627063751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.71747875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97770118713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33550834655762</t>
+    <t xml:space="preserve">8.97770214080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33551025390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.48188400268555</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">9.6119966506958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2625532150269</t>
+    <t xml:space="preserve">10.2625541687012</t>
   </si>
   <si>
     <t xml:space="preserve">10.0673866271973</t>
@@ -1952,13 +1952,13 @@
     <t xml:space="preserve">10.1812343597412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2137622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2788181304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2300262451172</t>
+    <t xml:space="preserve">10.2137632369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2788190841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2300252914429</t>
   </si>
   <si>
     <t xml:space="preserve">9.953537940979</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">10.3276090621948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2462911605835</t>
+    <t xml:space="preserve">10.2462902069092</t>
   </si>
   <si>
     <t xml:space="preserve">10.555305480957</t>
@@ -1988,19 +1988,19 @@
     <t xml:space="preserve">10.8480567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8805837631226</t>
+    <t xml:space="preserve">10.8805847167969</t>
   </si>
   <si>
     <t xml:space="preserve">10.8317918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7992649078369</t>
+    <t xml:space="preserve">10.7992639541626</t>
   </si>
   <si>
     <t xml:space="preserve">10.9293756484985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.685417175293</t>
+    <t xml:space="preserve">10.6854181289673</t>
   </si>
   <si>
     <t xml:space="preserve">10.6366243362427</t>
@@ -2015,10 +2015,10 @@
     <t xml:space="preserve">11.1245431900024</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1408061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2871837615967</t>
+    <t xml:space="preserve">11.1408081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2871828079224</t>
   </si>
   <si>
     <t xml:space="preserve">11.3847665786743</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">11.4335594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4498233795166</t>
+    <t xml:space="preserve">11.4498224258423</t>
   </si>
   <si>
     <t xml:space="preserve">11.4660863876343</t>
@@ -2042,28 +2042,28 @@
     <t xml:space="preserve">11.3359746932983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.205864906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2221269607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8643198013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.539041519165</t>
+    <t xml:space="preserve">11.2058639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2221279144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8643207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5390405654907</t>
   </si>
   <si>
     <t xml:space="preserve">10.5227766036987</t>
   </si>
   <si>
-    <t xml:space="preserve">10.701681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8155288696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.604097366333</t>
+    <t xml:space="preserve">10.7016801834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8155279159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6040964126587</t>
   </si>
   <si>
     <t xml:space="preserve">10.7342090606689</t>
@@ -2072,64 +2072,64 @@
     <t xml:space="preserve">10.620361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7179460525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5065126419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.587833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4577217102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3764009475708</t>
+    <t xml:space="preserve">10.717945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5065135955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5878343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4577207565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3764019012451</t>
   </si>
   <si>
     <t xml:space="preserve">10.571569442749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089298248291</t>
+    <t xml:space="preserve">10.4089307785034</t>
   </si>
   <si>
     <t xml:space="preserve">10.8968477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0594873428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9944314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6691522598267</t>
+    <t xml:space="preserve">11.0594882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9944324493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.669153213501</t>
   </si>
   <si>
     <t xml:space="preserve">10.7829999923706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9619045257568</t>
+    <t xml:space="preserve">10.9619035720825</t>
   </si>
   <si>
     <t xml:space="preserve">10.9456396102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2709197998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1895999908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5799350738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4172954559326</t>
+    <t xml:space="preserve">11.2709188461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1895990371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5799341201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4172945022583</t>
   </si>
   <si>
     <t xml:space="preserve">11.3034467697144</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9860668182373</t>
+    <t xml:space="preserve">9.98606586456299</t>
   </si>
   <si>
     <t xml:space="preserve">10.0836505889893</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">10.4414577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7504720687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1570711135864</t>
+    <t xml:space="preserve">10.7504730224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1570720672607</t>
   </si>
   <si>
     <t xml:space="preserve">11.1082792282104</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">11.0269594192505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9131116867065</t>
+    <t xml:space="preserve">10.9131126403809</t>
   </si>
   <si>
     <t xml:space="preserve">11.2546548843384</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">11.3522386550903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4010305404663</t>
+    <t xml:space="preserve">11.401029586792</t>
   </si>
   <si>
     <t xml:space="preserve">11.3197116851807</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">11.0106954574585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5311422348022</t>
+    <t xml:space="preserve">11.5311431884766</t>
   </si>
   <si>
     <t xml:space="preserve">11.7751007080078</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7100439071655</t>
+    <t xml:space="preserve">11.7100448608398</t>
   </si>
   <si>
     <t xml:space="preserve">11.7425727844238</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">12.0190601348877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3118124008179</t>
+    <t xml:space="preserve">12.3118133544922</t>
   </si>
   <si>
     <t xml:space="preserve">12.5882987976074</t>
@@ -2201,16 +2201,16 @@
     <t xml:space="preserve">12.0027980804443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8076295852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8564205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5961980819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9540042877197</t>
+    <t xml:space="preserve">11.8076305389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8564214706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5961971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.954005241394</t>
   </si>
   <si>
     <t xml:space="preserve">11.986533164978</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">12.1166439056396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2792844772339</t>
+    <t xml:space="preserve">12.2792854309082</t>
   </si>
   <si>
     <t xml:space="preserve">12.4093961715698</t>
@@ -2234,28 +2234,28 @@
     <t xml:space="preserve">12.5069789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4581871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4907140731812</t>
+    <t xml:space="preserve">12.4581880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4907150268555</t>
   </si>
   <si>
     <t xml:space="preserve">12.8973140716553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0111627578735</t>
+    <t xml:space="preserve">13.0111618041992</t>
   </si>
   <si>
     <t xml:space="preserve">12.9786338806152</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8647871017456</t>
+    <t xml:space="preserve">12.8647861480713</t>
   </si>
   <si>
     <t xml:space="preserve">12.7997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6370916366577</t>
+    <t xml:space="preserve">12.6370906829834</t>
   </si>
   <si>
     <t xml:space="preserve">12.8810501098633</t>
@@ -2267,22 +2267,22 @@
     <t xml:space="preserve">13.2713851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3527059555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7267751693726</t>
+    <t xml:space="preserve">13.3527050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7267761230469</t>
   </si>
   <si>
     <t xml:space="preserve">13.8243598937988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.052056312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2309589385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2634878158569</t>
+    <t xml:space="preserve">14.0520553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2309579849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634868621826</t>
   </si>
   <si>
     <t xml:space="preserve">14.2146940231323</t>
@@ -2297,10 +2297,10 @@
     <t xml:space="preserve">13.8080949783325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8894147872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6454563140869</t>
+    <t xml:space="preserve">13.8894157409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6454553604126</t>
   </si>
   <si>
     <t xml:space="preserve">13.8406238555908</t>
@@ -2309,25 +2309,25 @@
     <t xml:space="preserve">13.7918310165405</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0032615661621</t>
+    <t xml:space="preserve">14.0032625198364</t>
   </si>
   <si>
     <t xml:space="preserve">13.9544706344604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3448057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1496391296387</t>
+    <t xml:space="preserve">14.3448066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1496381759644</t>
   </si>
   <si>
     <t xml:space="preserve">14.2472219467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4749164581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5579166412354</t>
+    <t xml:space="preserve">14.4749174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.557915687561</t>
   </si>
   <si>
     <t xml:space="preserve">14.192723274231</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">14.1595239639282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1429252624512</t>
+    <t xml:space="preserve">14.1429243087769</t>
   </si>
   <si>
     <t xml:space="preserve">14.2757225036621</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">14.2923192977905</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3753185272217</t>
+    <t xml:space="preserve">14.375319480896</t>
   </si>
   <si>
     <t xml:space="preserve">14.1097249984741</t>
@@ -2357,16 +2357,16 @@
     <t xml:space="preserve">14.0765247344971</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2093229293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9935274124146</t>
+    <t xml:space="preserve">14.2093238830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9935264587402</t>
   </si>
   <si>
     <t xml:space="preserve">13.8109292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3089199066162</t>
+    <t xml:space="preserve">14.3089208602905</t>
   </si>
   <si>
     <t xml:space="preserve">14.05992603302</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">14.0101261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9769277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0433263778687</t>
+    <t xml:space="preserve">13.9769268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0433254241943</t>
   </si>
   <si>
     <t xml:space="preserve">14.3255205154419</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2259216308594</t>
+    <t xml:space="preserve">14.2259206771851</t>
   </si>
   <si>
     <t xml:space="preserve">14.3421211242676</t>
@@ -2396,19 +2396,19 @@
     <t xml:space="preserve">13.9437265396118</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0931243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9603261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3587188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591218948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5081167221069</t>
+    <t xml:space="preserve">14.0931234359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9603271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.358717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5081157684326</t>
   </si>
   <si>
     <t xml:space="preserve">14.5247173309326</t>
@@ -2417,61 +2417,61 @@
     <t xml:space="preserve">14.026725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.707311630249</t>
+    <t xml:space="preserve">14.7073125839233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7737112045288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.690712928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7405109405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9397077560425</t>
+    <t xml:space="preserve">14.6907138824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7405118942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9397087097168</t>
   </si>
   <si>
     <t xml:space="preserve">15.1057052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3215007781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1721038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8899097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3713006973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7032918930054</t>
+    <t xml:space="preserve">15.3214988708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1721029281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.889910697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.371298789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.703293800354</t>
   </si>
   <si>
     <t xml:space="preserve">15.537296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3879013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2883033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2717018127441</t>
+    <t xml:space="preserve">15.3878993988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2883014678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2717008590698</t>
   </si>
   <si>
     <t xml:space="preserve">15.0725059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2219038009644</t>
+    <t xml:space="preserve">15.22190284729</t>
   </si>
   <si>
     <t xml:space="preserve">15.1223039627075</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9895057678223</t>
+    <t xml:space="preserve">14.9895067214966</t>
   </si>
   <si>
     <t xml:space="preserve">14.8567085266113</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">15.1389045715332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9729089736938</t>
+    <t xml:space="preserve">14.9729080200195</t>
   </si>
   <si>
     <t xml:space="preserve">14.873309135437</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">14.5413160324097</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4251165390015</t>
+    <t xml:space="preserve">14.4251174926758</t>
   </si>
   <si>
     <t xml:space="preserve">14.408519744873</t>
@@ -2522,22 +2522,22 @@
     <t xml:space="preserve">14.3919191360474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4708976745605</t>
+    <t xml:space="preserve">15.4708986282349</t>
   </si>
   <si>
     <t xml:space="preserve">15.2053031921387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0227079391479</t>
+    <t xml:space="preserve">15.0227060317993</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915161132812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8275299072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7777309417725</t>
+    <t xml:space="preserve">13.8275308609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7777318954468</t>
   </si>
   <si>
     <t xml:space="preserve">13.6449337005615</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">13.5287351608276</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5619354248047</t>
+    <t xml:space="preserve">13.5619344711304</t>
   </si>
   <si>
     <t xml:space="preserve">13.4125375747681</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">13.362738609314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5121374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5951347351074</t>
+    <t xml:space="preserve">13.5121364593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5951337814331</t>
   </si>
   <si>
     <t xml:space="preserve">13.6117334365845</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">13.3295392990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4955368041992</t>
+    <t xml:space="preserve">13.4955377578735</t>
   </si>
   <si>
     <t xml:space="preserve">13.0805444717407</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">12.3003597259521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7153520584106</t>
+    <t xml:space="preserve">12.7153511047363</t>
   </si>
   <si>
     <t xml:space="preserve">12.4331569671631</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">12.5991544723511</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3335580825806</t>
+    <t xml:space="preserve">12.3335590362549</t>
   </si>
   <si>
     <t xml:space="preserve">12.3501586914062</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">12.067964553833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8521671295166</t>
+    <t xml:space="preserve">11.8521680831909</t>
   </si>
   <si>
     <t xml:space="preserve">11.6695728302002</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">12.0845642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8189687728882</t>
+    <t xml:space="preserve">11.8189697265625</t>
   </si>
   <si>
     <t xml:space="preserve">11.6031723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7027721405029</t>
+    <t xml:space="preserve">11.7027711868286</t>
   </si>
   <si>
     <t xml:space="preserve">11.7857694625854</t>
@@ -2642,19 +2642,19 @@
     <t xml:space="preserve">11.5367746353149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3209781646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1715822219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.221381187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8395881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2088022232056</t>
+    <t xml:space="preserve">11.3209791183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1715812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2213821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8395891189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2088003158569</t>
   </si>
   <si>
     <t xml:space="preserve">10.6735916137695</t>
@@ -2681,16 +2681,16 @@
     <t xml:space="preserve">9.36221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62781238555908</t>
+    <t xml:space="preserve">9.62781143188477</t>
   </si>
   <si>
     <t xml:space="preserve">9.32901763916016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52821350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0096044540405</t>
+    <t xml:space="preserve">9.52821445465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0096035003662</t>
   </si>
   <si>
     <t xml:space="preserve">9.39541625976562</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">10.3913974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6071929931641</t>
+    <t xml:space="preserve">10.6071920394897</t>
   </si>
   <si>
     <t xml:space="preserve">10.3083982467651</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">10.1756019592285</t>
   </si>
   <si>
-    <t xml:space="preserve">10.109203338623</t>
+    <t xml:space="preserve">10.1092023849487</t>
   </si>
   <si>
     <t xml:space="preserve">10.1424026489258</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">9.89340686798096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69421195983887</t>
+    <t xml:space="preserve">9.69421100616455</t>
   </si>
   <si>
     <t xml:space="preserve">9.61121273040771</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">9.17962169647217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27921772003174</t>
+    <t xml:space="preserve">9.27921867370605</t>
   </si>
   <si>
     <t xml:space="preserve">9.37881660461426</t>
@@ -2747,10 +2747,10 @@
     <t xml:space="preserve">9.29581832885742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12982177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42861652374268</t>
+    <t xml:space="preserve">9.12982082366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42861557006836</t>
   </si>
   <si>
     <t xml:space="preserve">9.77720832824707</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">10.4577960968018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0760040283203</t>
+    <t xml:space="preserve">10.076003074646</t>
   </si>
   <si>
     <t xml:space="preserve">9.92660617828369</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">9.7205171585083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0639991760254</t>
+    <t xml:space="preserve">10.0639982223511</t>
   </si>
   <si>
     <t xml:space="preserve">10.0983467102051</t>
@@ -2792,16 +2792,16 @@
     <t xml:space="preserve">10.2529125213623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85790920257568</t>
+    <t xml:space="preserve">9.85791015625</t>
   </si>
   <si>
     <t xml:space="preserve">10.0811729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3559579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2700881958008</t>
+    <t xml:space="preserve">10.35595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2700872421265</t>
   </si>
   <si>
     <t xml:space="preserve">10.6479167938232</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">10.7681341171265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.957049369812</t>
+    <t xml:space="preserve">10.9570503234863</t>
   </si>
   <si>
     <t xml:space="preserve">11.1631383895874</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">10.0124759674072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.390305519104</t>
+    <t xml:space="preserve">10.3903064727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1498689651489</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">10.0468244552612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5620470046997</t>
+    <t xml:space="preserve">10.5620460510254</t>
   </si>
   <si>
     <t xml:space="preserve">10.6307430267334</t>
@@ -2882,16 +2882,16 @@
     <t xml:space="preserve">10.424654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7166128158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.459002494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5105237960815</t>
+    <t xml:space="preserve">10.4418287277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5105228424072</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509613037109</t>
@@ -2903,13 +2903,13 @@
     <t xml:space="preserve">10.493350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1155214309692</t>
+    <t xml:space="preserve">10.1155204772949</t>
   </si>
   <si>
     <t xml:space="preserve">9.7548656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61747360229492</t>
+    <t xml:space="preserve">9.61747264862061</t>
   </si>
   <si>
     <t xml:space="preserve">9.37703609466553</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">9.51442909240723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63464641571045</t>
+    <t xml:space="preserve">9.63464736938477</t>
   </si>
   <si>
     <t xml:space="preserve">9.80638790130615</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">9.49725532531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39421081542969</t>
+    <t xml:space="preserve">9.39420986175537</t>
   </si>
   <si>
     <t xml:space="preserve">9.22246932983398</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">9.32551383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25681686401367</t>
+    <t xml:space="preserve">9.25681781768799</t>
   </si>
   <si>
     <t xml:space="preserve">9.4629077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0850772857666</t>
+    <t xml:space="preserve">9.08507633209229</t>
   </si>
   <si>
     <t xml:space="preserve">9.54877662658691</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">10.3387842178345</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5963945388794</t>
+    <t xml:space="preserve">10.5963954925537</t>
   </si>
   <si>
     <t xml:space="preserve">10.8540058135986</t>
@@ -2978,13 +2978,13 @@
     <t xml:space="preserve">11.4550971984863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2661819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0429191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8883533477783</t>
+    <t xml:space="preserve">11.2661828994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0429201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8883543014526</t>
   </si>
   <si>
     <t xml:space="preserve">10.9398756027222</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">10.8196573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8024835586548</t>
+    <t xml:space="preserve">10.8024826049805</t>
   </si>
   <si>
     <t xml:space="preserve">11.3692274093628</t>
@@ -3002,25 +3002,25 @@
     <t xml:space="preserve">11.4379234313965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0733633041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4683666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5027160644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2966260910034</t>
+    <t xml:space="preserve">12.0733642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4683675765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5027151107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2966251373291</t>
   </si>
   <si>
     <t xml:space="preserve">12.0561895370483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7470569610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7127075195312</t>
+    <t xml:space="preserve">11.7470560073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7127084732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.9703187942505</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">12.0046663284302</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0218410491943</t>
+    <t xml:space="preserve">12.0218420028687</t>
   </si>
   <si>
     <t xml:space="preserve">11.8157529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2279300689697</t>
+    <t xml:space="preserve">12.227931022644</t>
   </si>
   <si>
     <t xml:space="preserve">12.3653221130371</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">12.3138008117676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5198888778687</t>
+    <t xml:space="preserve">12.519889831543</t>
   </si>
   <si>
     <t xml:space="preserve">12.485541343689</t>
@@ -3065,16 +3065,16 @@
     <t xml:space="preserve">12.2451038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2794523239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1420602798462</t>
+    <t xml:space="preserve">12.2794532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1420593261719</t>
   </si>
   <si>
     <t xml:space="preserve">12.1248865127563</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1764078140259</t>
+    <t xml:space="preserve">12.1764087677002</t>
   </si>
   <si>
     <t xml:space="preserve">12.159234046936</t>
@@ -3083,10 +3083,10 @@
     <t xml:space="preserve">12.1077117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3481492996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6572818756104</t>
+    <t xml:space="preserve">12.3481483459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.657280921936</t>
   </si>
   <si>
     <t xml:space="preserve">12.9148921966553</t>
@@ -3095,19 +3095,19 @@
     <t xml:space="preserve">13.0694599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1038084030151</t>
+    <t xml:space="preserve">13.1038074493408</t>
   </si>
   <si>
     <t xml:space="preserve">13.0866327285767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.18967628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6705513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3442430496216</t>
+    <t xml:space="preserve">13.1896772384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6705503463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3442440032959</t>
   </si>
   <si>
     <t xml:space="preserve">13.6362028121948</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">13.5503330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5675058364868</t>
+    <t xml:space="preserve">13.5675067901611</t>
   </si>
   <si>
     <t xml:space="preserve">13.4644622802734</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">13.5159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.619029045105</t>
+    <t xml:space="preserve">13.6190280914307</t>
   </si>
   <si>
     <t xml:space="preserve">14.082727432251</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">14.6151247024536</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7353429794312</t>
+    <t xml:space="preserve">14.7353420257568</t>
   </si>
   <si>
     <t xml:space="preserve">14.6494731903076</t>
@@ -3179,52 +3179,52 @@
     <t xml:space="preserve">15.3879566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1990423202515</t>
+    <t xml:space="preserve">15.1990432739258</t>
   </si>
   <si>
     <t xml:space="preserve">15.2505645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1818685531616</t>
+    <t xml:space="preserve">15.1818675994873</t>
   </si>
   <si>
     <t xml:space="preserve">15.2162160873413</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9757785797119</t>
+    <t xml:space="preserve">14.9757795333862</t>
   </si>
   <si>
     <t xml:space="preserve">14.9242563247681</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4262094497681</t>
+    <t xml:space="preserve">14.4262084960938</t>
   </si>
   <si>
     <t xml:space="preserve">14.3918619155884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9586067199707</t>
+    <t xml:space="preserve">14.9586057662964</t>
   </si>
   <si>
     <t xml:space="preserve">14.5464286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1131725311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1303462982178</t>
+    <t xml:space="preserve">15.1131715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1303472518921</t>
   </si>
   <si>
     <t xml:space="preserve">14.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2677383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4223041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9031791687012</t>
+    <t xml:space="preserve">15.2677392959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4223051071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9031782150269</t>
   </si>
   <si>
     <t xml:space="preserve">15.9375276565552</t>
@@ -3233,22 +3233,22 @@
     <t xml:space="preserve">16.1436157226562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.851655960083</t>
+    <t xml:space="preserve">15.8516550064087</t>
   </si>
   <si>
     <t xml:space="preserve">15.9546995162964</t>
   </si>
   <si>
-    <t xml:space="preserve">15.782958984375</t>
+    <t xml:space="preserve">15.7829599380493</t>
   </si>
   <si>
     <t xml:space="preserve">15.7142639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5253505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5596971511841</t>
+    <t xml:space="preserve">15.5253496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5596981048584</t>
   </si>
   <si>
     <t xml:space="preserve">14.8383884429932</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">14.4605579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3059911727905</t>
+    <t xml:space="preserve">14.3059921264648</t>
   </si>
   <si>
     <t xml:space="preserve">14.2888164520264</t>
@@ -3269,16 +3269,16 @@
     <t xml:space="preserve">14.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7009954452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5807762145996</t>
+    <t xml:space="preserve">14.7009963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5807752609253</t>
   </si>
   <si>
     <t xml:space="preserve">14.5292539596558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3746871948242</t>
+    <t xml:space="preserve">14.3746862411499</t>
   </si>
   <si>
     <t xml:space="preserve">14.1431245803833</t>
@@ -3288,9 +3288,6 @@
   </si>
   <si>
     <t xml:space="preserve">14.321249961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3746862411499</t>
   </si>
   <si>
     <t xml:space="preserve">14.6596870422363</t>
@@ -53631,7 +53628,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1878" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53657,7 +53654,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1879" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53683,7 +53680,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1880" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53709,7 +53706,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1881" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53735,7 +53732,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1882" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53761,7 +53758,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1883" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53787,7 +53784,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1884" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53813,7 +53810,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1885" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53839,7 +53836,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1886" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53865,7 +53862,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1887" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53891,7 +53888,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1888" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53917,7 +53914,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G1889" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53943,7 +53940,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1890" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53969,7 +53966,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1891" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -53995,7 +53992,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -54021,7 +54018,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1893" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -54047,7 +54044,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G1894" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -54073,7 +54070,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1895" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -54099,7 +54096,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1896" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -54125,7 +54122,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1897" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -54151,7 +54148,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -54177,7 +54174,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1899" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -54203,7 +54200,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1900" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -54229,7 +54226,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1901" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -54255,7 +54252,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1902" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -54281,7 +54278,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1903" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -54307,7 +54304,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1904" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -54333,7 +54330,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1905" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -54359,7 +54356,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1906" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -54385,7 +54382,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1907" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -54411,7 +54408,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1908" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -54437,7 +54434,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1909" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -54463,7 +54460,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1910" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -54489,7 +54486,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1911" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -54515,7 +54512,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1912" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54541,7 +54538,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1913" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -54567,7 +54564,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1914" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54593,7 +54590,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1915" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54619,7 +54616,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1916" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -54645,7 +54642,7 @@
         <v>15.5</v>
       </c>
       <c r="G1917" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54671,7 +54668,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1918" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54697,7 +54694,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1919" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54723,7 +54720,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1920" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54749,7 +54746,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1921" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54775,7 +54772,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1922" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54801,7 +54798,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1923" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54827,7 +54824,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1924" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54853,7 +54850,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1925" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54879,7 +54876,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1926" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54905,7 +54902,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1927" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54931,7 +54928,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1928" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -54957,7 +54954,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1929" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54983,7 +54980,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1930" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -55009,7 +55006,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1931" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -55035,7 +55032,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1932" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -55061,7 +55058,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1933" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -55087,7 +55084,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G1934" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -55113,7 +55110,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G1935" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -55139,7 +55136,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1936" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -55165,7 +55162,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1937" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -55191,7 +55188,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1938" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -55217,7 +55214,7 @@
         <v>16</v>
       </c>
       <c r="G1939" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -55243,7 +55240,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1940" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -55269,7 +55266,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1941" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -55295,7 +55292,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1942" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -55321,7 +55318,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1943" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -55347,7 +55344,7 @@
         <v>15</v>
       </c>
       <c r="G1944" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -55373,7 +55370,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1945" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -55399,7 +55396,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1946" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -55425,7 +55422,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1947" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -55451,7 +55448,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1948" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -55477,7 +55474,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1949" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -55503,7 +55500,7 @@
         <v>16</v>
       </c>
       <c r="G1950" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -55529,7 +55526,7 @@
         <v>16</v>
       </c>
       <c r="G1951" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -55555,7 +55552,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1952" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -55581,7 +55578,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G1953" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -55607,7 +55604,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1954" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -55633,7 +55630,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1955" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55659,7 +55656,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1956" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55685,7 +55682,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1957" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -55711,7 +55708,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1958" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -55737,7 +55734,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1959" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -55763,7 +55760,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1960" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -55789,7 +55786,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1961" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55815,7 +55812,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1962" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55841,7 +55838,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1963" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -55867,7 +55864,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1964" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55893,7 +55890,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G1965" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55919,7 +55916,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1966" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55945,7 +55942,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1967" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55971,7 +55968,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1968" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -55997,7 +55994,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G1969" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -56023,7 +56020,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1970" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56049,7 +56046,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1971" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56075,7 +56072,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1972" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -56101,7 +56098,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1973" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -56127,7 +56124,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1974" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -56153,7 +56150,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1975" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -56179,7 +56176,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1976" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -56205,7 +56202,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -56231,7 +56228,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1978" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -56257,7 +56254,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1979" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -56283,7 +56280,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1980" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -56309,7 +56306,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1981" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -56335,7 +56332,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1982" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -56361,7 +56358,7 @@
         <v>13</v>
       </c>
       <c r="G1983" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56387,7 +56384,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1984" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56413,7 +56410,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1985" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56439,7 +56436,7 @@
         <v>12.5</v>
       </c>
       <c r="G1986" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56465,7 +56462,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1987" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56491,7 +56488,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56517,7 +56514,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1989" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56543,7 +56540,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G1990" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -56569,7 +56566,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1991" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56595,7 +56592,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1992" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -56621,7 +56618,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1993" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -56647,7 +56644,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1994" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56673,7 +56670,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1995" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56699,7 +56696,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1996" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56725,7 +56722,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1997" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56751,7 +56748,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1998" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56777,7 +56774,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1999" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56803,7 +56800,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2000" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56829,7 +56826,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2001" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56855,7 +56852,7 @@
         <v>13</v>
       </c>
       <c r="G2002" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56881,7 +56878,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2003" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56907,7 +56904,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2004" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56933,7 +56930,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2005" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56959,7 +56956,7 @@
         <v>12.5</v>
       </c>
       <c r="G2006" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56985,7 +56982,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2007" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -57011,7 +57008,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2008" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -57037,7 +57034,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2009" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -57063,7 +57060,7 @@
         <v>12.5</v>
       </c>
       <c r="G2010" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -57089,7 +57086,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2011" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -57115,7 +57112,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2012" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -57141,7 +57138,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2013" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -57167,7 +57164,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G2014" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -57193,7 +57190,7 @@
         <v>13</v>
       </c>
       <c r="G2015" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -57219,7 +57216,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2016" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -57245,7 +57242,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2017" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -57271,7 +57268,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2018" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57297,7 +57294,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2019" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57323,7 +57320,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G2020" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -57349,7 +57346,7 @@
         <v>13.5</v>
       </c>
       <c r="G2021" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -57375,7 +57372,7 @@
         <v>13.5</v>
       </c>
       <c r="G2022" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57401,7 +57398,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G2023" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57427,7 +57424,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2024" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57453,7 +57450,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2025" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57479,7 +57476,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2026" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57505,7 +57502,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G2027" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57531,7 +57528,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G2028" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57557,7 +57554,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2029" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -57583,7 +57580,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G2030" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57609,7 +57606,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2031" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57635,7 +57632,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G2032" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57661,7 +57658,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G2033" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57687,7 +57684,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2034" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57713,7 +57710,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G2035" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57739,7 +57736,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G2036" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -57765,7 +57762,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G2037" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57791,7 +57788,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G2038" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57817,7 +57814,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2039" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57843,7 +57840,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G2040" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57869,7 +57866,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G2041" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57895,7 +57892,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2042" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57921,7 +57918,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G2043" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57947,7 +57944,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2044" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57973,7 +57970,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2045" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57999,7 +57996,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2046" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58025,7 +58022,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2047" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58051,7 +58048,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2048" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -58077,7 +58074,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G2049" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -58103,7 +58100,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2050" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -58129,7 +58126,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G2051" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -58155,7 +58152,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2052" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -58181,7 +58178,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2053" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -58207,7 +58204,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2054" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -58233,7 +58230,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G2055" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -58259,7 +58256,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G2056" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -58285,7 +58282,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2057" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -58311,7 +58308,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2058" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -58337,7 +58334,7 @@
         <v>13.5</v>
       </c>
       <c r="G2059" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -58363,7 +58360,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2060" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -58389,7 +58386,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G2061" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58415,7 +58412,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58441,7 +58438,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2063" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58467,7 +58464,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2064" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58493,7 +58490,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G2065" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58519,7 +58516,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2066" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58545,7 +58542,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G2067" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58571,7 +58568,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2068" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58597,7 +58594,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2069" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58623,7 +58620,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2070" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -58649,7 +58646,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G2071" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58675,7 +58672,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G2072" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58701,7 +58698,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G2073" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58727,7 +58724,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G2074" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -58753,7 +58750,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2075" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58779,7 +58776,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2076" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -58805,7 +58802,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G2077" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -58831,7 +58828,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G2078" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -58857,7 +58854,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G2079" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -58883,7 +58880,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G2080" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58909,7 +58906,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G2081" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -58935,7 +58932,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2082" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58961,7 +58958,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G2083" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -58987,7 +58984,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2084" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59013,7 +59010,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G2085" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59039,7 +59036,7 @@
         <v>13</v>
       </c>
       <c r="G2086" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59065,7 +59062,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2087" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -59091,7 +59088,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2088" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -59117,7 +59114,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G2089" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -59143,7 +59140,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2090" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -59169,7 +59166,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2091" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -59195,7 +59192,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2092" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -59221,7 +59218,7 @@
         <v>13</v>
       </c>
       <c r="G2093" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59247,7 +59244,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2094" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -59273,7 +59270,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G2095" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59299,7 +59296,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2096" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59325,7 +59322,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2097" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59351,7 +59348,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G2098" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59377,7 +59374,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2099" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59403,7 +59400,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2100" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59429,7 +59426,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G2101" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59455,7 +59452,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2102" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59481,7 +59478,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2103" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59507,7 +59504,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2104" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59533,7 +59530,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2105" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59559,7 +59556,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2106" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59585,7 +59582,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G2107" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59611,7 +59608,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2108" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59637,7 +59634,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2109" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59663,7 +59660,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G2110" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59689,7 +59686,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2111" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59715,7 +59712,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2112" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59741,7 +59738,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2113" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59767,7 +59764,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2114" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -59793,7 +59790,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2115" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -59819,7 +59816,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2116" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -59845,7 +59842,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2117" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -59871,7 +59868,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2118" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59897,7 +59894,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G2119" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59923,7 +59920,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2120" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59949,7 +59946,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2121" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59975,7 +59972,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2122" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60001,7 +59998,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2123" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60027,7 +60024,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2124" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60053,7 +60050,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2125" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -60079,7 +60076,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2126" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -60105,7 +60102,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2127" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -60131,7 +60128,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2128" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -60157,7 +60154,7 @@
         <v>12</v>
       </c>
       <c r="G2129" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -60183,7 +60180,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2130" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -60209,7 +60206,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2131" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -60235,7 +60232,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2132" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60261,7 +60258,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2133" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60287,7 +60284,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2134" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60313,7 +60310,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G2135" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60339,7 +60336,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2136" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60365,7 +60362,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2137" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60391,7 +60388,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2138" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60417,7 +60414,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2139" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60443,7 +60440,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2140" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60469,7 +60466,7 @@
         <v>12</v>
       </c>
       <c r="G2141" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60495,7 +60492,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2142" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60521,7 +60518,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2143" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60547,7 +60544,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2144" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60573,7 +60570,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2145" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60599,7 +60596,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2146" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60625,7 +60622,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2147" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60651,7 +60648,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2148" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60677,7 +60674,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2149" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60703,7 +60700,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2150" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60729,7 +60726,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G2151" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60755,7 +60752,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G2152" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60781,7 +60778,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G2153" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60807,7 +60804,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2154" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60833,7 +60830,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2155" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60859,7 +60856,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2156" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60885,7 +60882,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2157" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60911,7 +60908,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2158" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60937,7 +60934,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2159" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60963,7 +60960,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2160" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60989,7 +60986,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2161" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61015,7 +61012,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2162" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61041,7 +61038,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2163" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61067,7 +61064,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G2164" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -61093,7 +61090,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2165" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -61119,7 +61116,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2166" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -61145,7 +61142,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2167" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -61171,7 +61168,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2168" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -61197,7 +61194,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G2169" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -61223,7 +61220,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G2170" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -61249,7 +61246,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G2171" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61275,7 +61272,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G2172" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61301,7 +61298,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G2173" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61327,7 +61324,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G2174" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61353,7 +61350,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2175" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61379,7 +61376,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G2176" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61405,7 +61402,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2177" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61431,7 +61428,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G2178" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61457,7 +61454,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G2179" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61483,7 +61480,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G2180" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61509,7 +61506,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2181" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61535,7 +61532,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2182" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61561,7 +61558,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2183" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61587,7 +61584,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2184" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61613,7 +61610,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2185" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61639,7 +61636,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2186" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61665,7 +61662,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2187" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61691,7 +61688,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2188" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61717,7 +61714,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2189" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61743,7 +61740,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2190" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61769,7 +61766,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2191" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61795,7 +61792,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2192" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61821,7 +61818,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2193" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61847,7 +61844,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2194" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61873,7 +61870,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2195" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61899,7 +61896,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2196" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61925,7 +61922,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2197" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61951,7 +61948,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2198" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61977,7 +61974,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2199" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62003,7 +62000,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2200" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62029,7 +62026,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G2201" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62055,7 +62052,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2202" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62081,7 +62078,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2203" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -62107,7 +62104,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2204" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -62133,7 +62130,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2205" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -62159,7 +62156,7 @@
         <v>11</v>
       </c>
       <c r="G2206" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62185,7 +62182,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2207" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62211,7 +62208,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2208" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -62237,7 +62234,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2209" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62263,7 +62260,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2210" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62289,7 +62286,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2211" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62315,7 +62312,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2212" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62341,7 +62338,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2213" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62367,7 +62364,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2214" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62393,7 +62390,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2215" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62419,7 +62416,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2216" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62445,7 +62442,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G2217" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62471,7 +62468,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2218" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62497,7 +62494,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2219" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62523,7 +62520,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2220" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62549,7 +62546,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2221" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -62575,7 +62572,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G2222" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62601,7 +62598,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2223" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62627,7 +62624,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2224" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62653,7 +62650,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2225" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62679,7 +62676,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2226" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62705,7 +62702,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2227" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62731,7 +62728,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2228" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62757,7 +62754,7 @@
         <v>11</v>
       </c>
       <c r="G2229" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62783,7 +62780,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2230" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62809,7 +62806,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2231" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62835,7 +62832,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2232" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62861,7 +62858,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2233" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62887,7 +62884,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2234" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62913,7 +62910,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G2235" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62939,7 +62936,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2236" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62965,7 +62962,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2237" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62991,7 +62988,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G2238" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63017,7 +63014,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63043,7 +63040,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2240" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63069,7 +63066,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2241" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63095,7 +63092,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G2242" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63121,7 +63118,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2243" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63147,7 +63144,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2244" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63173,7 +63170,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2245" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63199,7 +63196,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2246" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63225,7 +63222,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2247" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63251,7 +63248,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2248" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63277,7 +63274,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2249" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63303,7 +63300,7 @@
         <v>10.5</v>
       </c>
       <c r="G2250" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63329,7 +63326,7 @@
         <v>10.5</v>
       </c>
       <c r="G2251" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63355,7 +63352,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2252" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63381,7 +63378,7 @@
         <v>10</v>
       </c>
       <c r="G2253" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63407,7 +63404,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2254" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63433,7 +63430,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2255" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63459,7 +63456,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2256" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63485,7 +63482,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2257" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63511,7 +63508,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G2258" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63537,7 +63534,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G2259" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63563,7 +63560,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2260" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63589,7 +63586,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2261" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63615,7 +63612,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G2262" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63641,7 +63638,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2263" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63667,7 +63664,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2264" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63693,7 +63690,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2265" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63719,7 +63716,7 @@
         <v>9.75</v>
       </c>
       <c r="G2266" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63745,7 +63742,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2267" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63771,7 +63768,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2268" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63797,7 +63794,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2269" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63823,7 +63820,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2270" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63849,7 +63846,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2271" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63875,7 +63872,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G2272" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63901,7 +63898,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2273" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63927,7 +63924,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2274" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63953,7 +63950,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2275" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63979,7 +63976,7 @@
         <v>9.75</v>
       </c>
       <c r="G2276" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64005,7 +64002,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2277" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64031,7 +64028,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2278" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64057,7 +64054,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2279" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64083,7 +64080,7 @@
         <v>9.75</v>
       </c>
       <c r="G2280" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64109,7 +64106,7 @@
         <v>9.75</v>
       </c>
       <c r="G2281" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64135,7 +64132,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2282" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64161,7 +64158,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2283" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64187,7 +64184,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2284" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64213,7 +64210,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2285" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -64239,7 +64236,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2286" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64265,7 +64262,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G2287" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -64291,7 +64288,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G2288" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64317,7 +64314,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G2289" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64343,7 +64340,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2290" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64369,7 +64366,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G2291" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64395,7 +64392,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2292" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64421,7 +64418,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2293" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64447,7 +64444,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2294" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64473,7 +64470,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G2295" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64499,7 +64496,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G2296" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64525,7 +64522,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2297" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64551,7 +64548,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G2298" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64577,7 +64574,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2299" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64603,7 +64600,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G2300" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64629,7 +64626,7 @@
         <v>9.5</v>
       </c>
       <c r="G2301" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64655,7 +64652,7 @@
         <v>9.75</v>
       </c>
       <c r="G2302" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64681,7 +64678,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G2303" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64707,7 +64704,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2304" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64733,7 +64730,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2305" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64759,7 +64756,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G2306" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64785,7 +64782,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G2307" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64811,7 +64808,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2308" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64837,7 +64834,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2309" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64863,7 +64860,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2310" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64889,7 +64886,7 @@
         <v>10.5</v>
       </c>
       <c r="G2311" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64915,7 +64912,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64941,7 +64938,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2313" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64967,7 +64964,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2314" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64993,7 +64990,7 @@
         <v>9.75</v>
       </c>
       <c r="G2315" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65019,7 +65016,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2316" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65045,7 +65042,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G2317" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -65071,7 +65068,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2318" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -65097,7 +65094,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2319" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -65123,7 +65120,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2320" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65149,7 +65146,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G2321" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65175,7 +65172,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G2322" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65201,7 +65198,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2323" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65227,7 +65224,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G2324" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65253,7 +65250,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2325" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65279,7 +65276,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2326" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65305,7 +65302,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2327" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65331,7 +65328,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G2328" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65357,7 +65354,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2329" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65383,7 +65380,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G2330" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65409,7 +65406,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2331" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65435,7 +65432,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2332" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65461,7 +65458,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G2333" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65487,7 +65484,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G2334" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65513,7 +65510,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2335" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65539,7 +65536,7 @@
         <v>10</v>
       </c>
       <c r="G2336" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65565,7 +65562,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2337" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65591,7 +65588,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2338" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65617,7 +65614,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G2339" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65643,7 +65640,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G2340" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65669,7 +65666,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G2341" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65695,7 +65692,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2342" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65721,7 +65718,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2343" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65747,7 +65744,7 @@
         <v>9.25</v>
       </c>
       <c r="G2344" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65773,7 +65770,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2345" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65799,7 +65796,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2346" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65825,7 +65822,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65851,7 +65848,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2348" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65877,7 +65874,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G2349" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65903,7 +65900,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65929,7 +65926,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G2351" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65955,7 +65952,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G2352" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65981,7 +65978,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G2353" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66007,7 +66004,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G2354" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66033,7 +66030,7 @@
         <v>8.5</v>
       </c>
       <c r="G2355" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66059,7 +66056,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2356" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -66085,7 +66082,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2357" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -66111,7 +66108,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2358" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -66137,7 +66134,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G2359" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66163,7 +66160,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2360" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66189,7 +66186,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G2361" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66215,7 +66212,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G2362" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66241,7 +66238,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G2363" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66267,7 +66264,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2364" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66293,7 +66290,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G2365" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66319,7 +66316,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G2366" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66345,7 +66342,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2367" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66371,7 +66368,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2368" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66397,7 +66394,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2369" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66423,7 +66420,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2370" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66449,7 +66446,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2371" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66475,7 +66472,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2372" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66501,7 +66498,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2373" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66527,7 +66524,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2374" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66553,7 +66550,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2375" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66579,7 +66576,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G2376" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66605,7 +66602,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2377" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66631,7 +66628,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G2378" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66657,7 +66654,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G2379" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66683,7 +66680,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G2380" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66709,7 +66706,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G2381" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66735,7 +66732,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2382" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66761,7 +66758,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2383" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66787,7 +66784,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2384" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66813,7 +66810,7 @@
         <v>8.5</v>
       </c>
       <c r="G2385" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66839,7 +66836,7 @@
         <v>8.5</v>
       </c>
       <c r="G2386" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66865,7 +66862,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2387" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66891,7 +66888,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2388" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66917,7 +66914,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2389" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66943,7 +66940,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2390" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66969,7 +66966,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2391" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66995,7 +66992,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G2392" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67021,7 +67018,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G2393" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67047,7 +67044,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G2394" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -67073,7 +67070,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G2395" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -67099,7 +67096,7 @@
         <v>8.5</v>
       </c>
       <c r="G2396" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -67125,7 +67122,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2397" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67151,7 +67148,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G2398" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67177,7 +67174,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2399" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67203,7 +67200,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G2400" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67229,7 +67226,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2401" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67255,7 +67252,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G2402" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67281,7 +67278,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67307,7 +67304,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G2404" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67333,7 +67330,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G2405" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67359,7 +67356,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G2406" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67385,7 +67382,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2407" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67411,7 +67408,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G2408" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67437,7 +67434,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2409" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67463,7 +67460,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2410" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67489,7 +67486,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G2411" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67515,7 +67512,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2412" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67541,7 +67538,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G2413" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67567,7 +67564,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G2414" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67593,7 +67590,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G2415" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67619,7 +67616,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2416" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67645,7 +67642,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G2417" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67671,7 +67668,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G2418" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67697,7 +67694,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2419" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67723,7 +67720,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67749,7 +67746,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2421" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67775,7 +67772,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G2422" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67801,7 +67798,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2423" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67827,7 +67824,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2424" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67853,7 +67850,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2425" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67879,7 +67876,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G2426" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67905,7 +67902,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2427" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67931,7 +67928,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G2428" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67957,7 +67954,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G2429" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67983,7 +67980,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2430" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68009,7 +68006,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2431" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -68035,7 +68032,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2432" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -68061,7 +68058,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G2433" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -68087,7 +68084,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G2434" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -68113,7 +68110,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G2435" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -68139,7 +68136,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2436" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68165,7 +68162,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2437" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68191,7 +68188,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2438" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68217,7 +68214,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2439" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68243,7 +68240,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2440" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68269,7 +68266,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G2441" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68295,7 +68292,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G2442" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68321,7 +68318,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G2443" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68347,7 +68344,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G2444" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68373,7 +68370,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G2445" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68399,7 +68396,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G2446" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68425,7 +68422,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G2447" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68451,7 +68448,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G2448" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68477,7 +68474,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2449" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68503,7 +68500,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2450" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68529,7 +68526,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2451" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68555,7 +68552,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2452" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68581,7 +68578,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G2453" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68607,7 +68604,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2454" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68633,7 +68630,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2455" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68659,7 +68656,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2456" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68685,7 +68682,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2457" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68711,7 +68708,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G2458" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68737,7 +68734,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G2459" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68763,7 +68760,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G2460" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68789,7 +68786,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G2461" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68815,7 +68812,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G2462" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68841,7 +68838,7 @@
         <v>8</v>
       </c>
       <c r="G2463" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68867,7 +68864,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G2464" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68893,7 +68890,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G2465" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68919,7 +68916,7 @@
         <v>8</v>
       </c>
       <c r="G2466" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68945,7 +68942,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G2467" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68971,7 +68968,7 @@
         <v>8</v>
       </c>
       <c r="G2468" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68997,7 +68994,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2469" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -69023,7 +69020,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G2470" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -69049,7 +69046,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G2471" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -69075,7 +69072,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2472" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -69101,7 +69098,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G2473" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -69127,7 +69124,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2474" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69153,7 +69150,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G2475" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69179,7 +69176,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2476" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69205,7 +69202,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2477" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69231,7 +69228,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2478" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69257,7 +69254,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G2479" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69283,7 +69280,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2480" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69309,7 +69306,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G2481" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69335,7 +69332,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2482" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69361,7 +69358,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G2483" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69387,7 +69384,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G2484" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69413,7 +69410,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G2485" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69439,7 +69436,7 @@
         <v>8</v>
       </c>
       <c r="G2486" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69465,7 +69462,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G2487" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69491,7 +69488,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G2488" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69517,7 +69514,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2489" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69543,7 +69540,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2490" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69569,7 +69566,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2491" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69595,7 +69592,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G2492" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69621,7 +69618,7 @@
         <v>7.75</v>
       </c>
       <c r="G2493" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69647,7 +69644,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2494" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69673,7 +69670,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G2495" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69699,7 +69696,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69725,7 +69722,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2497" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69751,7 +69748,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G2498" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69777,7 +69774,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2499" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69803,7 +69800,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G2500" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69829,7 +69826,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G2501" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69855,7 +69852,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2502" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69881,7 +69878,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2503" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69907,7 +69904,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2504" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69933,7 +69930,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2505" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -69959,7 +69956,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G2506" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -69985,7 +69982,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2507" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -70011,7 +70008,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G2508" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -70037,7 +70034,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G2509" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -70063,7 +70060,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2510" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -70089,7 +70086,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G2511" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -70115,7 +70112,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2512" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -70141,7 +70138,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2513" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -70167,7 +70164,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2514" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -70193,7 +70190,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2515" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -70219,7 +70216,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G2516" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -70245,7 +70242,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G2517" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -70271,7 +70268,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2518" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -70297,7 +70294,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G2519" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -70323,7 +70320,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2520" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -70349,7 +70346,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2521" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -70375,7 +70372,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2522" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -70401,7 +70398,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G2523" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -70427,7 +70424,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2524" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -70453,7 +70450,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G2525" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -70479,7 +70476,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G2526" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -70505,7 +70502,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G2527" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -70531,7 +70528,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2528" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -70557,7 +70554,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2529" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -70583,7 +70580,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2530" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -70609,7 +70606,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2531" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -70635,7 +70632,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G2532" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -70661,7 +70658,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G2533" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -70687,7 +70684,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G2534" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -70713,7 +70710,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G2535" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -70739,7 +70736,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2536" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -70765,7 +70762,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2537" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -70791,7 +70788,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G2538" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -70799,7 +70796,7 @@
     </row>
     <row r="2539">
       <c r="A2539" s="1" t="n">
-        <v>46014.69125</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2539" t="n">
         <v>50399</v>
@@ -70817,7 +70814,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G2539" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93978929519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82799792289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78057169914246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943188667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75685834884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74330854415894</t>
+    <t xml:space="preserve">4.02447938919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93978881835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82799816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78057050704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943212509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75685811042786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74330711364746</t>
   </si>
   <si>
     <t xml:space="preserve">3.80089735984802</t>
@@ -71,31 +71,31 @@
     <t xml:space="preserve">3.77040863037109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68571829795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66539287567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56376457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65184259414673</t>
+    <t xml:space="preserve">3.68571805953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66539263725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5637640953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65184235572815</t>
   </si>
   <si>
     <t xml:space="preserve">3.72636985778809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70265674591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65861701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69249367713928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74669528007507</t>
+    <t xml:space="preserve">3.70265626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65861773490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74669551849365</t>
   </si>
   <si>
     <t xml:space="preserve">3.59764051437378</t>
@@ -104,58 +104,58 @@
     <t xml:space="preserve">3.59086561203003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58408975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49601244926453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46213698387146</t>
+    <t xml:space="preserve">3.58408999443054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49601268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46213579177856</t>
   </si>
   <si>
     <t xml:space="preserve">3.51633810997009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38760852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40793442726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50956344604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55698943138123</t>
+    <t xml:space="preserve">3.38760924339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40793490409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50956273078918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55698919296265</t>
   </si>
   <si>
     <t xml:space="preserve">3.56715178489685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61119055747986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57731485366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54682636260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5265007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50278735160828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56037759780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58070182800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60102868080139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54343938827515</t>
+    <t xml:space="preserve">3.61119103431702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57731461524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54682683944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52650046348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50278759002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56037735939026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58070278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60102844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54343867301941</t>
   </si>
   <si>
     <t xml:space="preserve">3.57053995132446</t>
@@ -164,55 +164,55 @@
     <t xml:space="preserve">3.64506697654724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78734683990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.841548204422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86526131629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85171151161194</t>
+    <t xml:space="preserve">3.78734636306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84154844284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86526155471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85171103477478</t>
   </si>
   <si>
     <t xml:space="preserve">3.92962622642517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93640112876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91607618331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90252542495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89575052261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285084724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90930128097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97027778625488</t>
+    <t xml:space="preserve">3.9364013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91607546806335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90252494812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89574933052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285108566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9093005657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97027707099915</t>
   </si>
   <si>
     <t xml:space="preserve">3.87881183624268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85848689079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94317650794983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89913773536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94656419754028</t>
+    <t xml:space="preserve">3.85848641395569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94317626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89913845062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94656348228455</t>
   </si>
   <si>
     <t xml:space="preserve">3.95672750473022</t>
@@ -221,187 +221,187 @@
     <t xml:space="preserve">3.96350240707397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9126889705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97366499900818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91946244239807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87203693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88704800605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87291288375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85877799987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83757638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86231255531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87644696235657</t>
+    <t xml:space="preserve">3.91268849372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97366452217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91946315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87203669548035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88704824447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8729133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85877895355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83757591247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86231207847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87644743919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.89411520957947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90118265151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89058208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94358682632446</t>
+    <t xml:space="preserve">3.90118288993835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89058184623718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94358611106873</t>
   </si>
   <si>
     <t xml:space="preserve">3.95418787002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96125459671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01426029205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02486133575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08846712112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05666399002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03899669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305844306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00719261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9753897190094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97185659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80223917961121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78103756904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75630235671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74923396110535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9047167301178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9223849773407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95065474510193</t>
+    <t xml:space="preserve">3.96125507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01426076889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02486181259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08846759796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05666446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03899621963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305891990662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00719308853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97539019584656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97185564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80223989486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7810378074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75630211830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74923372268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9047155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92238521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95065379142761</t>
   </si>
   <si>
     <t xml:space="preserve">4.03546237945557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75983619689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80930733680725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83050894737244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.869380235672</t>
+    <t xml:space="preserve">3.7598352432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80930709838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83050918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86937975883484</t>
   </si>
   <si>
     <t xml:space="preserve">3.82344174385071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80577373504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84111046791077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81637406349182</t>
+    <t xml:space="preserve">3.80577349662781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84110999107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8163743019104</t>
   </si>
   <si>
     <t xml:space="preserve">3.86584568023682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89764904975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93652009963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9082498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91531729698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97892332077026</t>
+    <t xml:space="preserve">3.89764833450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93651962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90825009346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91531705856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97892379760742</t>
   </si>
   <si>
     <t xml:space="preserve">4.00012588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02132797241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9577214717865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84464383125305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81284022331238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77043676376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76690244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76336860656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7457013130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7244987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77397060394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78810501098633</t>
+    <t xml:space="preserve">4.02132749557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95772051811218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84464335441589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81284070014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77043628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76690292358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76336932182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74570107460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72449898719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77397036552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78810548782349</t>
   </si>
   <si>
     <t xml:space="preserve">3.81990838050842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72803258895874</t>
+    <t xml:space="preserve">3.72803235054016</t>
   </si>
   <si>
     <t xml:space="preserve">3.73863315582275</t>
@@ -410,109 +410,109 @@
     <t xml:space="preserve">3.73156595230103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73509955406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65382504463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63968992233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66089296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61848783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61142158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62555575370789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61495471000671</t>
+    <t xml:space="preserve">3.73510003089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65382480621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6396906375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66089272499084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.618488073349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61142063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62555551528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61495423316956</t>
   </si>
   <si>
     <t xml:space="preserve">3.64675807952881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74216747283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91885137557983</t>
+    <t xml:space="preserve">3.74216723442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9188506603241</t>
   </si>
   <si>
     <t xml:space="preserve">3.98599123954773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99659204483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87998080253601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88351392745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79517245292664</t>
+    <t xml:space="preserve">3.99659156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87998056411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8835141658783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7951717376709</t>
   </si>
   <si>
     <t xml:space="preserve">3.82697558403015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79163885116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84817719459534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71036410331726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8552451133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03192853927612</t>
+    <t xml:space="preserve">3.79163813591003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84817790985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71036386489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85524487495422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03192901611328</t>
   </si>
   <si>
     <t xml:space="preserve">4.04252958297729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08493423461914</t>
+    <t xml:space="preserve">4.08493375778198</t>
   </si>
   <si>
     <t xml:space="preserve">4.09906911849976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05313158035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04959726333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09200096130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10967016220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07786750793457</t>
+    <t xml:space="preserve">4.05313110351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04959678649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09200191497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07786655426025</t>
   </si>
   <si>
     <t xml:space="preserve">4.07433271408081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04606294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0637321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10613584518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10260248184204</t>
+    <t xml:space="preserve">4.04606342315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06373119354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10613632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10260200500488</t>
   </si>
   <si>
     <t xml:space="preserve">4.13440561294556</t>
@@ -524,13 +524,13 @@
     <t xml:space="preserve">4.16974210739136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18387746810913</t>
+    <t xml:space="preserve">4.18387699127197</t>
   </si>
   <si>
     <t xml:space="preserve">4.1591420173645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24041604995728</t>
+    <t xml:space="preserve">4.24041557312012</t>
   </si>
   <si>
     <t xml:space="preserve">4.21568059921265</t>
@@ -539,46 +539,46 @@
     <t xml:space="preserve">4.27575302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34642696380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36762857437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35349321365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31108951568604</t>
+    <t xml:space="preserve">4.34642648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36762809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35349273681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31108903884888</t>
   </si>
   <si>
     <t xml:space="preserve">4.30402231216431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38176250457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50897550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72806358337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91181516647339</t>
+    <t xml:space="preserve">4.38176345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5089750289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72806406021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91181468963623</t>
   </si>
   <si>
     <t xml:space="preserve">4.94715213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19450950622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22277879714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22984600067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22631311416626</t>
+    <t xml:space="preserve">5.19450902938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22277927398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2298469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2263126373291</t>
   </si>
   <si>
     <t xml:space="preserve">5.09203243255615</t>
@@ -587,82 +587,82 @@
     <t xml:space="preserve">5.07436466217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08496570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1167688369751</t>
+    <t xml:space="preserve">5.08496522903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11676836013794</t>
   </si>
   <si>
     <t xml:space="preserve">5.10616779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15210580825806</t>
+    <t xml:space="preserve">5.1521053314209</t>
   </si>
   <si>
     <t xml:space="preserve">5.15917253494263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17330741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1909761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14503812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1309027671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24751472473145</t>
+    <t xml:space="preserve">5.1733078956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19097518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14503765106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13090419769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2475152015686</t>
   </si>
   <si>
     <t xml:space="preserve">5.26871681213379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59734869003296</t>
+    <t xml:space="preserve">5.59734916687012</t>
   </si>
   <si>
     <t xml:space="preserve">5.51254081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35705900192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47720432281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37119388580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44186735153198</t>
+    <t xml:space="preserve">5.35705852508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47720384597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37119340896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44186639785767</t>
   </si>
   <si>
     <t xml:space="preserve">5.53020906448364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61199760437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65216064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68867444992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6229510307312</t>
+    <t xml:space="preserve">5.61199712753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65216112136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6886739730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62295055389404</t>
   </si>
   <si>
     <t xml:space="preserve">5.61929988861084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5973916053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42213201522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41847991943359</t>
+    <t xml:space="preserve">5.59739255905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42213153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41848039627075</t>
   </si>
   <si>
     <t xml:space="preserve">5.5535774230957</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">5.49880838394165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46229600906372</t>
+    <t xml:space="preserve">5.4622950553894</t>
   </si>
   <si>
     <t xml:space="preserve">5.55722856521606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45499324798584</t>
+    <t xml:space="preserve">5.45499277114868</t>
   </si>
   <si>
     <t xml:space="preserve">5.36736249923706</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">5.37466526031494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43308591842651</t>
+    <t xml:space="preserve">5.43308544158936</t>
   </si>
   <si>
     <t xml:space="preserve">5.40387535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47690057754517</t>
+    <t xml:space="preserve">5.47690010070801</t>
   </si>
   <si>
     <t xml:space="preserve">5.44769048690796</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">5.60104370117188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41117858886719</t>
+    <t xml:space="preserve">5.41117668151855</t>
   </si>
   <si>
     <t xml:space="preserve">5.51341342926025</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">5.45134210586548</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61564922332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50611066818237</t>
+    <t xml:space="preserve">5.61564874649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50611114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.34545516967773</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37101411819458</t>
+    <t xml:space="preserve">5.37101364135742</t>
   </si>
   <si>
     <t xml:space="preserve">5.31259346008301</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">5.28703451156616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15558910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12637853622437</t>
+    <t xml:space="preserve">5.15558862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12637901306152</t>
   </si>
   <si>
     <t xml:space="preserve">5.27242946624756</t>
@@ -755,58 +755,58 @@
     <t xml:space="preserve">5.31989574432373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14098358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40752696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38927030563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37831687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24321937561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46959781646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41482925415039</t>
+    <t xml:space="preserve">5.14098405838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40752649307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38926982879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37831592559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24321889877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46959733963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41482877731323</t>
   </si>
   <si>
     <t xml:space="preserve">5.42578268051147</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44038772583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48420286178589</t>
+    <t xml:space="preserve">5.44038820266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48420333862305</t>
   </si>
   <si>
     <t xml:space="preserve">5.35275793075562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48785448074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50245952606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57183408737183</t>
+    <t xml:space="preserve">5.48785400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50245904922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57183313369751</t>
   </si>
   <si>
     <t xml:space="preserve">5.57913589477539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56453037261963</t>
+    <t xml:space="preserve">5.56453084945679</t>
   </si>
   <si>
     <t xml:space="preserve">5.52071619033813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53897190093994</t>
+    <t xml:space="preserve">5.5389723777771</t>
   </si>
   <si>
     <t xml:space="preserve">5.65581274032593</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">5.57548475265503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50976228713989</t>
+    <t xml:space="preserve">5.50976181030273</t>
   </si>
   <si>
     <t xml:space="preserve">5.53166961669922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60469484329224</t>
+    <t xml:space="preserve">5.60469532012939</t>
   </si>
   <si>
     <t xml:space="preserve">5.59008979797363</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">5.92965745925903</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94426298141479</t>
+    <t xml:space="preserve">5.94426345825195</t>
   </si>
   <si>
     <t xml:space="preserve">5.99903154373169</t>
@@ -848,40 +848,40 @@
     <t xml:space="preserve">5.93696022033691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98807764053345</t>
+    <t xml:space="preserve">5.98807811737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.83107328414917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88584280014038</t>
+    <t xml:space="preserve">5.88584232330322</t>
   </si>
   <si>
     <t xml:space="preserve">5.83472442626953</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95886707305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76900196075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91140127182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83837604522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84202766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87123727798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78360748291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85298109054565</t>
+    <t xml:space="preserve">5.95886754989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76900148391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83837556838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84202718734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87123680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.783607006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85298156738281</t>
   </si>
   <si>
     <t xml:space="preserve">5.7032790184021</t>
@@ -890,31 +890,31 @@
     <t xml:space="preserve">5.82742214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86393451690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75439691543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7288384437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68502283096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66676712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88949346542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78725814819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77995634078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73614072799683</t>
+    <t xml:space="preserve">5.8639349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75439643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72883749008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68502330780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66676616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88949394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78725862503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77995538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73614025115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.6083459854126</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">5.63025379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53532075881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76169872283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62660217285156</t>
+    <t xml:space="preserve">5.53532028198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76169967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62660264968872</t>
   </si>
   <si>
     <t xml:space="preserve">5.68137168884277</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">5.73979187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76535034179688</t>
+    <t xml:space="preserve">5.76535081863403</t>
   </si>
   <si>
     <t xml:space="preserve">5.80916595458984</t>
@@ -947,25 +947,25 @@
     <t xml:space="preserve">5.80551433563232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82377099990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8785400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82011938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90409803390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92600631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92235517501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95156478881836</t>
+    <t xml:space="preserve">5.82377052307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87854051589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82011890411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90409898757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92600584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92235469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95156526565552</t>
   </si>
   <si>
     <t xml:space="preserve">6.02459049224854</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">6.06110382080078</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00998544692993</t>
+    <t xml:space="preserve">6.00998449325562</t>
   </si>
   <si>
     <t xml:space="preserve">6.09031391143799</t>
@@ -983,79 +983,79 @@
     <t xml:space="preserve">6.22906064987183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18524599075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03189325332642</t>
+    <t xml:space="preserve">6.18524646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03189277648926</t>
   </si>
   <si>
     <t xml:space="preserve">6.0391960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04649829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25096893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20715427398682</t>
+    <t xml:space="preserve">6.04649782180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25096845626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2071533203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.14143085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12682628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79821157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7251877784729</t>
+    <t xml:space="preserve">6.12682580947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79821252822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72518634796143</t>
   </si>
   <si>
     <t xml:space="preserve">5.96617031097412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00268363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8931450843811</t>
+    <t xml:space="preserve">6.00268220901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89314413070679</t>
   </si>
   <si>
     <t xml:space="preserve">5.84932994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97347259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99538040161133</t>
+    <t xml:space="preserve">5.973473072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99538087844849</t>
   </si>
   <si>
     <t xml:space="preserve">6.11952352523804</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15603637695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10491800308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98077535629272</t>
+    <t xml:space="preserve">6.15603685379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10491752624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98077487945557</t>
   </si>
   <si>
     <t xml:space="preserve">5.90044736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14873361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09761619567871</t>
+    <t xml:space="preserve">6.14873313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09761571884155</t>
   </si>
   <si>
     <t xml:space="preserve">6.05380058288574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07570743560791</t>
+    <t xml:space="preserve">6.07570838928223</t>
   </si>
   <si>
     <t xml:space="preserve">6.08301067352295</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">6.17794418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17064142227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24366617202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28017950057983</t>
+    <t xml:space="preserve">6.17064094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24366664886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28017997741699</t>
   </si>
   <si>
     <t xml:space="preserve">6.38636541366577</t>
@@ -1079,43 +1079,43 @@
     <t xml:space="preserve">6.31810283660889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23467111587524</t>
+    <t xml:space="preserve">6.23467063903809</t>
   </si>
   <si>
     <t xml:space="preserve">6.28017902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15882253646851</t>
+    <t xml:space="preserve">6.15882301330566</t>
   </si>
   <si>
     <t xml:space="preserve">6.2725944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26500988006592</t>
+    <t xml:space="preserve">6.26500940322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.21191644668579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1815767288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15123844146729</t>
+    <t xml:space="preserve">6.18157720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15123748779297</t>
   </si>
   <si>
     <t xml:space="preserve">6.02988195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05263614654541</t>
+    <t xml:space="preserve">6.05263566970825</t>
   </si>
   <si>
     <t xml:space="preserve">6.25742483139038</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22708559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24983978271484</t>
+    <t xml:space="preserve">6.22708606719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24983930587769</t>
   </si>
   <si>
     <t xml:space="preserve">6.29534912109375</t>
@@ -1127,43 +1127,43 @@
     <t xml:space="preserve">6.18916130065918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16640758514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20433139801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0147123336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04505109786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00712823867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98437309265137</t>
+    <t xml:space="preserve">6.1664080619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20433235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01471185684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04505157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00712776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98437404632568</t>
   </si>
   <si>
     <t xml:space="preserve">6.12089920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13606834411621</t>
+    <t xml:space="preserve">6.13606882095337</t>
   </si>
   <si>
     <t xml:space="preserve">6.11331462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09055995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96161937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0829758644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14365339279175</t>
+    <t xml:space="preserve">6.09055948257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96161890029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08297634124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14365434646606</t>
   </si>
   <si>
     <t xml:space="preserve">6.10572957992554</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">6.06022071838379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99954271316528</t>
+    <t xml:space="preserve">5.99954319000244</t>
   </si>
   <si>
     <t xml:space="preserve">5.95403480529785</t>
@@ -1184,22 +1184,22 @@
     <t xml:space="preserve">6.06780624389648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91611099243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94645071029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818670272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746747970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02229690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99195861816406</t>
+    <t xml:space="preserve">5.9161114692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94644975662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818717956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746700286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02229738235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9919581413269</t>
   </si>
   <si>
     <t xml:space="preserve">5.86301708221436</t>
@@ -1211,22 +1211,22 @@
     <t xml:space="preserve">6.24225521087646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47738313674927</t>
+    <t xml:space="preserve">6.47738218307495</t>
   </si>
   <si>
     <t xml:space="preserve">6.63666248321533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46221303939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57598447799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56081533432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60632371902466</t>
+    <t xml:space="preserve">6.46221399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57598400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56081438064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6063232421875</t>
   </si>
   <si>
     <t xml:space="preserve">6.55322980880737</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">6.65183258056641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53806066513062</t>
+    <t xml:space="preserve">6.53806114196777</t>
   </si>
   <si>
     <t xml:space="preserve">6.48496723175049</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">6.61390829086304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66700124740601</t>
+    <t xml:space="preserve">6.66700172424316</t>
   </si>
   <si>
     <t xml:space="preserve">6.59873914718628</t>
@@ -1256,55 +1256,55 @@
     <t xml:space="preserve">6.39395046234131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41670513153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42428922653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53047561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59115409851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54564523696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56840038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44704389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34844160079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21950054168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40912008285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32568836212158</t>
+    <t xml:space="preserve">6.4167046546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4242901802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53047657012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59115362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54564619064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56839990615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44704294204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3484411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21950101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40911960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32568788528442</t>
   </si>
   <si>
     <t xml:space="preserve">6.28776359558105</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68975591659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67458724975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74284934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75043344497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62149286270142</t>
+    <t xml:space="preserve">6.6897554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67458581924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74284982681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75043392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62149333953857</t>
   </si>
   <si>
     <t xml:space="preserve">6.37878084182739</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">6.36361169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46979713439941</t>
+    <t xml:space="preserve">6.46979808807373</t>
   </si>
   <si>
     <t xml:space="preserve">6.51530599594116</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31051731109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3560266494751</t>
+    <t xml:space="preserve">6.31051826477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35602617263794</t>
   </si>
   <si>
     <t xml:space="preserve">6.19674682617188</t>
@@ -1331,19 +1331,19 @@
     <t xml:space="preserve">6.40153455734253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72009468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75801801681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80352735519409</t>
+    <t xml:space="preserve">6.72009515762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75801944732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80352687835693</t>
   </si>
   <si>
     <t xml:space="preserve">6.78835773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73526430130005</t>
+    <t xml:space="preserve">6.73526382446289</t>
   </si>
   <si>
     <t xml:space="preserve">6.84903573989868</t>
@@ -1352,25 +1352,25 @@
     <t xml:space="preserve">6.86420488357544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81111097335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84145069122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81869602203369</t>
+    <t xml:space="preserve">6.81111145019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8414511680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81869697570801</t>
   </si>
   <si>
     <t xml:space="preserve">6.90212869644165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9931468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89454412460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94005298614502</t>
+    <t xml:space="preserve">6.99314594268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89454460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94005250930786</t>
   </si>
   <si>
     <t xml:space="preserve">7.05382442474365</t>
@@ -1379,124 +1379,124 @@
     <t xml:space="preserve">7.10691738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15242624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11450242996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01589965820312</t>
+    <t xml:space="preserve">7.15242576599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.114501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01590061187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.08416366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0462384223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09174823760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39513826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35721445083618</t>
+    <t xml:space="preserve">7.04623985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09174728393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39513921737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35721492767334</t>
   </si>
   <si>
     <t xml:space="preserve">7.34204530715942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12208700180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13725614547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1296706199646</t>
+    <t xml:space="preserve">7.12208843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13725757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12967157363892</t>
   </si>
   <si>
     <t xml:space="preserve">7.25102853775024</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22827339172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20551872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19793367385864</t>
+    <t xml:space="preserve">7.22827291488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20551919937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1979341506958</t>
   </si>
   <si>
     <t xml:space="preserve">7.16759538650513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37996768951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43306159973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49374008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53924798965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54683256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75162220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7971305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64543437957764</t>
+    <t xml:space="preserve">7.37996912002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4330620765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49374103546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5392484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54683399200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75162267684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79713010787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64543581008911</t>
   </si>
   <si>
     <t xml:space="preserve">7.6909441947937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57717227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4558162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51649475097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59992694854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50890970230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56200313568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58475637435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5544171333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47856950759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47098588943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4482307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70611238479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90331745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88814878463745</t>
+    <t xml:space="preserve">7.57717275619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45581674575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51649379730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59992790222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50890874862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56200361251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58475732803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55441808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47857046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47098636627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44823169708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70611381530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90331792831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88814735412598</t>
   </si>
   <si>
     <t xml:space="preserve">8.25221633911133</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">8.61628341674805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49492835998535</t>
+    <t xml:space="preserve">8.49492740631104</t>
   </si>
   <si>
     <t xml:space="preserve">8.17636871337891</t>
@@ -1514,19 +1514,19 @@
     <t xml:space="preserve">8.41908073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11876964569092</t>
+    <t xml:space="preserve">8.1187686920166</t>
   </si>
   <si>
     <t xml:space="preserve">8.08742237091064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93068838119507</t>
+    <t xml:space="preserve">7.9306902885437</t>
   </si>
   <si>
     <t xml:space="preserve">8.04040241241455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96203517913818</t>
+    <t xml:space="preserve">7.9620361328125</t>
   </si>
   <si>
     <t xml:space="preserve">8.25982856750488</t>
@@ -1535,13 +1535,13 @@
     <t xml:space="preserve">8.02472877502441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.867995262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7347731590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83664894104004</t>
+    <t xml:space="preserve">7.86799621582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73477268218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8366494178772</t>
   </si>
   <si>
     <t xml:space="preserve">7.82097625732422</t>
@@ -1553,49 +1553,49 @@
     <t xml:space="preserve">7.97770929336548</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07174968719482</t>
+    <t xml:space="preserve">8.07174873352051</t>
   </si>
   <si>
     <t xml:space="preserve">8.05607604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85232305526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40088844299316</t>
+    <t xml:space="preserve">7.85232448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40088939666748</t>
   </si>
   <si>
     <t xml:space="preserve">8.46358203887939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6203145980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30684852600098</t>
+    <t xml:space="preserve">8.62031555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30684757232666</t>
   </si>
   <si>
     <t xml:space="preserve">8.16578960418701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33819675445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21280860900879</t>
+    <t xml:space="preserve">8.33819580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21280765533447</t>
   </si>
   <si>
     <t xml:space="preserve">8.27550315856934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36954212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15011692047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18146324157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13444232940674</t>
+    <t xml:space="preserve">8.36954307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15011596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18146228790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13444328308105</t>
   </si>
   <si>
     <t xml:space="preserve">8.22848224639893</t>
@@ -1604,67 +1604,67 @@
     <t xml:space="preserve">8.43223571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99338293075562</t>
+    <t xml:space="preserve">7.99338340759277</t>
   </si>
   <si>
     <t xml:space="preserve">8.19713592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75828313827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89934206008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82881307601929</t>
+    <t xml:space="preserve">7.75828266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89934253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82881355285645</t>
   </si>
   <si>
     <t xml:space="preserve">7.88366937637329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81313991546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67991638183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79746532440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4165620803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80530214309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68775320053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74260997772217</t>
+    <t xml:space="preserve">7.81314039230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6799168586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79746627807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41656112670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8053035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68775463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74260950088501</t>
   </si>
   <si>
     <t xml:space="preserve">8.00905609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94636297225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75044631958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71909999847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1030969619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82406806945801</t>
+    <t xml:space="preserve">7.94636344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75044727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71910047531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10309505462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82406902313232</t>
   </si>
   <si>
     <t xml:space="preserve">9.37263298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60773372650146</t>
+    <t xml:space="preserve">9.60773277282715</t>
   </si>
   <si>
     <t xml:space="preserve">9.482346534729</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">9.87417888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9995641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1562986373901</t>
+    <t xml:space="preserve">9.99956512451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1562976837158</t>
   </si>
   <si>
     <t xml:space="preserve">10.5011100769043</t>
@@ -1697,22 +1697,22 @@
     <t xml:space="preserve">10.2189912796021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1719703674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95254421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90552520751953</t>
+    <t xml:space="preserve">10.171971321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95254707336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90552616119385</t>
   </si>
   <si>
     <t xml:space="preserve">9.88985157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92119884490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73311901092529</t>
+    <t xml:space="preserve">9.92119789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73311996459961</t>
   </si>
   <si>
     <t xml:space="preserve">9.76446533203125</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">10.4854373931885</t>
   </si>
   <si>
-    <t xml:space="preserve">10.250337600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0152378082275</t>
+    <t xml:space="preserve">10.2503385543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0152387619019</t>
   </si>
   <si>
     <t xml:space="preserve">10.1249513626099</t>
@@ -1760,76 +1760,76 @@
     <t xml:space="preserve">10.6108236312866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5951499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.579475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6421689987183</t>
+    <t xml:space="preserve">10.5951509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.579478263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6421699523926</t>
   </si>
   <si>
     <t xml:space="preserve">10.7518835067749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9869823455811</t>
+    <t xml:space="preserve">10.9869832992554</t>
   </si>
   <si>
     <t xml:space="preserve">10.9556360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1280422210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0183296203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2377548217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0966958999634</t>
+    <t xml:space="preserve">11.1280431747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0183305740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2377557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0966968536377</t>
   </si>
   <si>
     <t xml:space="preserve">11.1750612258911</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1123695373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0810222625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9713096618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7989044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0622577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0936059951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6860990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29426574707031</t>
+    <t xml:space="preserve">11.1123685836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0810232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9713087081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7989025115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0622587203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0936050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68609809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29426670074463</t>
   </si>
   <si>
     <t xml:space="preserve">9.54503917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98080158233643</t>
+    <t xml:space="preserve">8.98079967498779</t>
   </si>
   <si>
     <t xml:space="preserve">8.54194736480713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31943130493164</t>
+    <t xml:space="preserve">7.31943082809448</t>
   </si>
   <si>
     <t xml:space="preserve">7.5075101852417</t>
@@ -1838,22 +1838,22 @@
     <t xml:space="preserve">7.53885698318481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49183797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66733455657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44790840148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38521575927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52627563476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01214790344238</t>
+    <t xml:space="preserve">7.4918384552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66733551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44790744781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38521480560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52627372741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01214599609375</t>
   </si>
   <si>
     <t xml:space="preserve">9.45100021362305</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">9.10618782043457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93378162384033</t>
+    <t xml:space="preserve">8.93378067016602</t>
   </si>
   <si>
     <t xml:space="preserve">9.38830661773682</t>
@@ -1871,25 +1871,25 @@
     <t xml:space="preserve">8.88676071166992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8710880279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12185955047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9181079864502</t>
+    <t xml:space="preserve">8.87108707427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12186050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91810703277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.15320682525635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90243339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05916690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04349422454834</t>
+    <t xml:space="preserve">8.90243434906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05916786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04349517822266</t>
   </si>
   <si>
     <t xml:space="preserve">9.21589946746826</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">9.12407779693604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01023006439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68495082855225</t>
+    <t xml:space="preserve">9.01022911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68495178222656</t>
   </si>
   <si>
     <t xml:space="preserve">8.50604724884033</t>
@@ -1916,31 +1916,31 @@
     <t xml:space="preserve">8.70121479034424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.189133644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92890930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76627063751221</t>
+    <t xml:space="preserve">9.18913269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92891025543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76626968383789</t>
   </si>
   <si>
     <t xml:space="preserve">8.71747875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97770118713379</t>
+    <t xml:space="preserve">8.97770214080811</t>
   </si>
   <si>
     <t xml:space="preserve">9.33550930023193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48188400268555</t>
+    <t xml:space="preserve">9.48188495635986</t>
   </si>
   <si>
     <t xml:space="preserve">9.61199569702148</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2625532150269</t>
+    <t xml:space="preserve">10.2625541687012</t>
   </si>
   <si>
     <t xml:space="preserve">10.0673866271973</t>
@@ -1952,70 +1952,70 @@
     <t xml:space="preserve">10.1812343597412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2137622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2788181304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2300262451172</t>
+    <t xml:space="preserve">10.2137632369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2788190841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2300252914429</t>
   </si>
   <si>
     <t xml:space="preserve">9.95353889465332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88848304748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69331645965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1324424743652</t>
+    <t xml:space="preserve">9.88848209381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69331550598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1324415206909</t>
   </si>
   <si>
     <t xml:space="preserve">10.1974973678589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3276090621948</t>
+    <t xml:space="preserve">10.3276109695435</t>
   </si>
   <si>
     <t xml:space="preserve">10.2462902069092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5553045272827</t>
+    <t xml:space="preserve">10.555305480957</t>
   </si>
   <si>
     <t xml:space="preserve">10.8480567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8805837631226</t>
+    <t xml:space="preserve">10.8805847167969</t>
   </si>
   <si>
     <t xml:space="preserve">10.8317918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7992630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9293756484985</t>
+    <t xml:space="preserve">10.7992639541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9293746948242</t>
   </si>
   <si>
     <t xml:space="preserve">10.685417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6366243362427</t>
+    <t xml:space="preserve">10.636625289917</t>
   </si>
   <si>
     <t xml:space="preserve">10.7667360305786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9781665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1245431900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1408061981201</t>
+    <t xml:space="preserve">10.9781684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1245441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1408071517944</t>
   </si>
   <si>
     <t xml:space="preserve">11.2871828079224</t>
@@ -2027,64 +2027,64 @@
     <t xml:space="preserve">11.5474061965942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4335584640503</t>
+    <t xml:space="preserve">11.4335594177246</t>
   </si>
   <si>
     <t xml:space="preserve">11.4498224258423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4660863876343</t>
+    <t xml:space="preserve">11.4660873413086</t>
   </si>
   <si>
     <t xml:space="preserve">11.4823503494263</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3359746932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2058639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2221269607544</t>
+    <t xml:space="preserve">11.3359756469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2058629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2221279144287</t>
   </si>
   <si>
     <t xml:space="preserve">10.8643198013306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.539041519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.522777557373</t>
+    <t xml:space="preserve">10.5390405654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5227766036987</t>
   </si>
   <si>
     <t xml:space="preserve">10.7016801834106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8155279159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.604097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7342081069946</t>
+    <t xml:space="preserve">10.8155288696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6040964126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7342090606689</t>
   </si>
   <si>
     <t xml:space="preserve">10.620361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.717945098877</t>
+    <t xml:space="preserve">10.7179441452026</t>
   </si>
   <si>
     <t xml:space="preserve">10.5065135955811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5878343582153</t>
+    <t xml:space="preserve">10.587833404541</t>
   </si>
   <si>
     <t xml:space="preserve">10.4577207565308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3764009475708</t>
+    <t xml:space="preserve">10.3764019012451</t>
   </si>
   <si>
     <t xml:space="preserve">10.571569442749</t>
@@ -2096,10 +2096,10 @@
     <t xml:space="preserve">10.8968477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0594873428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9944314956665</t>
+    <t xml:space="preserve">11.0594882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9944324493408</t>
   </si>
   <si>
     <t xml:space="preserve">10.669153213501</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">10.9456396102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2709197998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1895999908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5799331665039</t>
+    <t xml:space="preserve">11.2709188461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1895990371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5799341201782</t>
   </si>
   <si>
     <t xml:space="preserve">11.417293548584</t>
@@ -2132,43 +2132,43 @@
     <t xml:space="preserve">9.9860668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0836496353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4414567947388</t>
+    <t xml:space="preserve">10.0836505889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4414577484131</t>
   </si>
   <si>
     <t xml:space="preserve">10.7504730224609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1570711135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1082782745361</t>
+    <t xml:space="preserve">11.1570720672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1082792282104</t>
   </si>
   <si>
     <t xml:space="preserve">11.0269603729248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9131116867065</t>
+    <t xml:space="preserve">10.9131126403809</t>
   </si>
   <si>
     <t xml:space="preserve">11.2546548843384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3522386550903</t>
+    <t xml:space="preserve">11.3522396087646</t>
   </si>
   <si>
     <t xml:space="preserve">11.4010305404663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3197107315063</t>
+    <t xml:space="preserve">11.3197116851807</t>
   </si>
   <si>
     <t xml:space="preserve">11.1733350753784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0106954574585</t>
+    <t xml:space="preserve">11.0106964111328</t>
   </si>
   <si>
     <t xml:space="preserve">11.5311422348022</t>
@@ -2177,16 +2177,16 @@
     <t xml:space="preserve">11.7751007080078</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7100448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7425737380981</t>
+    <t xml:space="preserve">11.7100439071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7425727844238</t>
   </si>
   <si>
     <t xml:space="preserve">12.019061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3118124008179</t>
+    <t xml:space="preserve">12.3118133544922</t>
   </si>
   <si>
     <t xml:space="preserve">12.5882987976074</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">12.1979646682739</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8726863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.00279712677</t>
+    <t xml:space="preserve">11.8726844787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0027980804443</t>
   </si>
   <si>
     <t xml:space="preserve">11.8076305389404</t>
@@ -2213,31 +2213,31 @@
     <t xml:space="preserve">11.954005241394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9865341186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1003818511963</t>
+    <t xml:space="preserve">11.986533164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.100380897522</t>
   </si>
   <si>
     <t xml:space="preserve">12.1816997528076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.116644859314</t>
+    <t xml:space="preserve">12.1166439056396</t>
   </si>
   <si>
     <t xml:space="preserve">12.2792844772339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4093971252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5069799423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4581871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4907150268555</t>
+    <t xml:space="preserve">12.4093952178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5069789886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4581880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4907159805298</t>
   </si>
   <si>
     <t xml:space="preserve">12.8973140716553</t>
@@ -2258,37 +2258,37 @@
     <t xml:space="preserve">12.6370916366577</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8810510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1738014221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2713842391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3527050018311</t>
+    <t xml:space="preserve">12.8810501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1738023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2713851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3527059555054</t>
   </si>
   <si>
     <t xml:space="preserve">13.7267751693726</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8243598937988</t>
+    <t xml:space="preserve">13.8243589401245</t>
   </si>
   <si>
     <t xml:space="preserve">14.0520544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2309579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2634868621826</t>
+    <t xml:space="preserve">14.23095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634878158569</t>
   </si>
   <si>
     <t xml:space="preserve">14.2146940231323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9056797027588</t>
+    <t xml:space="preserve">13.9056787490845</t>
   </si>
   <si>
     <t xml:space="preserve">13.6129274368286</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">13.8406238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7918300628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0032625198364</t>
+    <t xml:space="preserve">13.7918319702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0032634735107</t>
   </si>
   <si>
     <t xml:space="preserve">13.9544706344604</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">14.1496391296387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.247220993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4749174118042</t>
+    <t xml:space="preserve">14.2472229003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4749183654785</t>
   </si>
   <si>
     <t xml:space="preserve">14.5579166412354</t>
@@ -2333,79 +2333,79 @@
     <t xml:space="preserve">14.192723274231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1595211029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1429233551025</t>
+    <t xml:space="preserve">14.1595230102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1429243087769</t>
   </si>
   <si>
     <t xml:space="preserve">14.2757215499878</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2923212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3753185272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1097249984741</t>
+    <t xml:space="preserve">14.2923192977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.375319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1097240447998</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0765237808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2093229293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9935274124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8109292984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3089208602905</t>
+    <t xml:space="preserve">14.0765247344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.209321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9935264587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8109283447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3089199066162</t>
   </si>
   <si>
     <t xml:space="preserve">14.05992603302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0101261138916</t>
+    <t xml:space="preserve">14.0101251602173</t>
   </si>
   <si>
     <t xml:space="preserve">13.9769268035889</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0433263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3255205154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2259225845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3421201705933</t>
+    <t xml:space="preserve">14.0433254241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3255195617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2259206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3421211242676</t>
   </si>
   <si>
     <t xml:space="preserve">14.1761236190796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9437265396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0931243896484</t>
+    <t xml:space="preserve">13.9437274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0931234359741</t>
   </si>
   <si>
     <t xml:space="preserve">13.9603271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3587207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591209411621</t>
+    <t xml:space="preserve">14.3587188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591228485107</t>
   </si>
   <si>
     <t xml:space="preserve">14.5081157684326</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">14.026725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.707311630249</t>
+    <t xml:space="preserve">14.7073125839233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7737112045288</t>
@@ -2432,46 +2432,46 @@
     <t xml:space="preserve">14.9397087097168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1057043075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3215007781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1721029281616</t>
+    <t xml:space="preserve">15.1057052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3214988708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1721048355103</t>
   </si>
   <si>
     <t xml:space="preserve">14.8899087905884</t>
   </si>
   <si>
-    <t xml:space="preserve">15.371301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.703293800354</t>
+    <t xml:space="preserve">15.371298789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7032918930054</t>
   </si>
   <si>
     <t xml:space="preserve">15.537296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.387900352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2882995605469</t>
+    <t xml:space="preserve">15.3878993988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2883014678955</t>
   </si>
   <si>
     <t xml:space="preserve">15.2717008590698</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0725049972534</t>
+    <t xml:space="preserve">15.0725059509277</t>
   </si>
   <si>
     <t xml:space="preserve">15.2219018936157</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1223058700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9895076751709</t>
+    <t xml:space="preserve">15.1223039627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9895067214966</t>
   </si>
   <si>
     <t xml:space="preserve">14.85671043396</t>
@@ -2480,76 +2480,76 @@
     <t xml:space="preserve">14.8235111236572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7903108596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1389055252075</t>
+    <t xml:space="preserve">14.7903099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1389045715332</t>
   </si>
   <si>
     <t xml:space="preserve">14.9729080200195</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8733100891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8069124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8607292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6947317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.711332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4417181015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5745162963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5413150787354</t>
+    <t xml:space="preserve">14.873309135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8069105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8607301712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6947326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7113332748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4417171478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5745153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.541316986084</t>
   </si>
   <si>
     <t xml:space="preserve">14.4251174926758</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4085178375244</t>
+    <t xml:space="preserve">14.4085187911987</t>
   </si>
   <si>
     <t xml:space="preserve">14.391918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4708976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2053022384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0227069854736</t>
+    <t xml:space="preserve">15.4708986282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.20530128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227060317993</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915161132812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8275299072266</t>
+    <t xml:space="preserve">13.8275289535522</t>
   </si>
   <si>
     <t xml:space="preserve">13.7777318954468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6449346542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445316314697</t>
+    <t xml:space="preserve">13.6449337005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445306777954</t>
   </si>
   <si>
     <t xml:space="preserve">13.5287351608276</t>
   </si>
   <si>
-    <t xml:space="preserve">13.561936378479</t>
+    <t xml:space="preserve">13.5619344711304</t>
   </si>
   <si>
     <t xml:space="preserve">13.4125375747681</t>
@@ -2558,10 +2558,10 @@
     <t xml:space="preserve">13.1137437820435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2797412872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.362738609314</t>
+    <t xml:space="preserve">13.2797403335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3627395629883</t>
   </si>
   <si>
     <t xml:space="preserve">13.5121364593506</t>
@@ -2570,19 +2570,19 @@
     <t xml:space="preserve">13.5951337814331</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6117334365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1303424835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3295402526855</t>
+    <t xml:space="preserve">13.6117343902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1303434371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3295392990112</t>
   </si>
   <si>
     <t xml:space="preserve">13.4955368041992</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0805444717407</t>
+    <t xml:space="preserve">13.080545425415</t>
   </si>
   <si>
     <t xml:space="preserve">13.3129415512085</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">12.4497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3003597259521</t>
+    <t xml:space="preserve">12.3003587722778</t>
   </si>
   <si>
     <t xml:space="preserve">12.7153511047363</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">12.4331569671631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5991535186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3335580825806</t>
+    <t xml:space="preserve">12.5991544723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3335590362549</t>
   </si>
   <si>
     <t xml:space="preserve">12.3501586914062</t>
@@ -2618,10 +2618,10 @@
     <t xml:space="preserve">12.067964553833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8521690368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6695718765259</t>
+    <t xml:space="preserve">11.8521680831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6695728302002</t>
   </si>
   <si>
     <t xml:space="preserve">12.0845642089844</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">11.8189687728882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6031732559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7027721405029</t>
+    <t xml:space="preserve">11.6031723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7027711868286</t>
   </si>
   <si>
     <t xml:space="preserve">11.7857694625854</t>
@@ -2642,43 +2642,43 @@
     <t xml:space="preserve">11.5367736816406</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3209791183472</t>
+    <t xml:space="preserve">11.3209800720215</t>
   </si>
   <si>
     <t xml:space="preserve">11.1715822219849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.221381187439</t>
+    <t xml:space="preserve">11.2213821411133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8395891189575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2088012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6735906600952</t>
+    <t xml:space="preserve">10.2088003158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6735916137695</t>
   </si>
   <si>
     <t xml:space="preserve">10.6237926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.258599281311</t>
+    <t xml:space="preserve">10.2585983276367</t>
   </si>
   <si>
     <t xml:space="preserve">10.1922006607056</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97640514373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54481410980225</t>
+    <t xml:space="preserve">9.97640609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54481315612793</t>
   </si>
   <si>
     <t xml:space="preserve">9.56141376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36221790313721</t>
+    <t xml:space="preserve">9.36221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">9.62781238555908</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">9.52821350097656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0096044540405</t>
+    <t xml:space="preserve">10.0096035003662</t>
   </si>
   <si>
     <t xml:space="preserve">9.39541625976562</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">10.3913974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6071929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3083982467651</t>
+    <t xml:space="preserve">10.6071920394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3083972930908</t>
   </si>
   <si>
     <t xml:space="preserve">10.4909954071045</t>
@@ -2714,22 +2714,22 @@
     <t xml:space="preserve">10.1092023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1424026489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0594024658203</t>
+    <t xml:space="preserve">10.1424016952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0594034194946</t>
   </si>
   <si>
     <t xml:space="preserve">9.86020755767822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89340782165527</t>
+    <t xml:space="preserve">9.89340686798096</t>
   </si>
   <si>
     <t xml:space="preserve">9.69421100616455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6112117767334</t>
+    <t xml:space="preserve">9.61121273040771</t>
   </si>
   <si>
     <t xml:space="preserve">9.17962169647217</t>
@@ -2741,16 +2741,16 @@
     <t xml:space="preserve">9.37881660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19622039794922</t>
+    <t xml:space="preserve">9.1962194442749</t>
   </si>
   <si>
     <t xml:space="preserve">9.29581832885742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12982177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42861557006836</t>
+    <t xml:space="preserve">9.12982082366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42861461639404</t>
   </si>
   <si>
     <t xml:space="preserve">9.77720832824707</t>
@@ -2765,13 +2765,13 @@
     <t xml:space="preserve">10.5407934188843</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4577970504761</t>
+    <t xml:space="preserve">10.4577960968018</t>
   </si>
   <si>
     <t xml:space="preserve">10.076003074646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92660713195801</t>
+    <t xml:space="preserve">9.92660617828369</t>
   </si>
   <si>
     <t xml:space="preserve">9.66899490356445</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">9.7205171585083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0639982223511</t>
+    <t xml:space="preserve">10.0639991760254</t>
   </si>
   <si>
     <t xml:space="preserve">10.0983467102051</t>
@@ -2801,16 +2801,16 @@
     <t xml:space="preserve">10.35595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2700881958008</t>
+    <t xml:space="preserve">10.2700872421265</t>
   </si>
   <si>
     <t xml:space="preserve">10.6479167938232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7681350708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.957049369812</t>
+    <t xml:space="preserve">10.7681341171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9570503234863</t>
   </si>
   <si>
     <t xml:space="preserve">11.1631383895874</t>
@@ -2819,19 +2819,19 @@
     <t xml:space="preserve">11.060094833374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1803131103516</t>
+    <t xml:space="preserve">11.1803121566772</t>
   </si>
   <si>
     <t xml:space="preserve">11.0944423675537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1287908554077</t>
+    <t xml:space="preserve">11.1287899017334</t>
   </si>
   <si>
     <t xml:space="preserve">10.9742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9913988113403</t>
+    <t xml:space="preserve">10.991397857666</t>
   </si>
   <si>
     <t xml:space="preserve">10.0296506881714</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">10.0124759674072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.390305519104</t>
+    <t xml:space="preserve">10.3903064727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1498689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1326942443848</t>
+    <t xml:space="preserve">10.1326951980591</t>
   </si>
   <si>
     <t xml:space="preserve">9.97812843322754</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">10.3044357299805</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1670436859131</t>
+    <t xml:space="preserve">10.1670427322388</t>
   </si>
   <si>
     <t xml:space="preserve">10.1842164993286</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">10.0468244552612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5620470046997</t>
+    <t xml:space="preserve">10.5620460510254</t>
   </si>
   <si>
     <t xml:space="preserve">10.6307430267334</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">10.7166118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.459002494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5105237960815</t>
+    <t xml:space="preserve">10.4590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5105228424072</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509613037109</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">10.6822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.493350982666</t>
+    <t xml:space="preserve">10.4933500289917</t>
   </si>
   <si>
     <t xml:space="preserve">10.1155204772949</t>
@@ -2909,16 +2909,16 @@
     <t xml:space="preserve">9.75486469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61747360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37703609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51442909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63464641571045</t>
+    <t xml:space="preserve">9.61747264862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37703704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51442813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63464832305908</t>
   </si>
   <si>
     <t xml:space="preserve">9.80638790130615</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">9.39420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22246932983398</t>
+    <t xml:space="preserve">9.2224702835083</t>
   </si>
   <si>
     <t xml:space="preserve">9.325514793396</t>
@@ -2951,22 +2951,22 @@
     <t xml:space="preserve">9.0850772857666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54877758026123</t>
+    <t xml:space="preserve">9.54877662658691</t>
   </si>
   <si>
     <t xml:space="preserve">9.56595134735107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58312511444092</t>
+    <t xml:space="preserve">9.58312606811523</t>
   </si>
   <si>
     <t xml:space="preserve">9.65182113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82356071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3387842178345</t>
+    <t xml:space="preserve">9.823561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3387832641602</t>
   </si>
   <si>
     <t xml:space="preserve">10.5963945388794</t>
@@ -2975,13 +2975,13 @@
     <t xml:space="preserve">10.8540058135986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4550971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2661819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0429191589355</t>
+    <t xml:space="preserve">11.4550981521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2661828994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0429201126099</t>
   </si>
   <si>
     <t xml:space="preserve">10.8883543014526</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">10.9398756027222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8196582794189</t>
+    <t xml:space="preserve">10.8196573257446</t>
   </si>
   <si>
     <t xml:space="preserve">10.8024835586548</t>
@@ -3008,31 +3008,31 @@
     <t xml:space="preserve">12.4683666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5027160644531</t>
+    <t xml:space="preserve">12.5027151107788</t>
   </si>
   <si>
     <t xml:space="preserve">12.2966260910034</t>
   </si>
   <si>
-    <t xml:space="preserve">12.056188583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7470569610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7127084732056</t>
+    <t xml:space="preserve">12.0561895370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7470560073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7127094268799</t>
   </si>
   <si>
     <t xml:space="preserve">11.9703197479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9359712600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0046672821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0218410491943</t>
+    <t xml:space="preserve">11.9359703063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0046663284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0218420028687</t>
   </si>
   <si>
     <t xml:space="preserve">11.8157529830933</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">12.3653221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4340181350708</t>
+    <t xml:space="preserve">12.4340190887451</t>
   </si>
   <si>
     <t xml:space="preserve">12.3996696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3138008117676</t>
+    <t xml:space="preserve">12.3137998580933</t>
   </si>
   <si>
     <t xml:space="preserve">12.5198888778687</t>
@@ -3059,25 +3059,25 @@
     <t xml:space="preserve">12.485541343689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6401071548462</t>
+    <t xml:space="preserve">12.6401081085205</t>
   </si>
   <si>
     <t xml:space="preserve">12.2451038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2794513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1420602798462</t>
+    <t xml:space="preserve">12.2794532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1420593261719</t>
   </si>
   <si>
     <t xml:space="preserve">12.1248865127563</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1764078140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.159234046936</t>
+    <t xml:space="preserve">12.1764087677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1592330932617</t>
   </si>
   <si>
     <t xml:space="preserve">12.1077117919922</t>
@@ -3086,22 +3086,22 @@
     <t xml:space="preserve">12.3481483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6572818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9148931503296</t>
+    <t xml:space="preserve">12.657280921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9148921966553</t>
   </si>
   <si>
     <t xml:space="preserve">13.0694589614868</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1038084030151</t>
+    <t xml:space="preserve">13.1038074493408</t>
   </si>
   <si>
     <t xml:space="preserve">13.0866327285767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.18967628479</t>
+    <t xml:space="preserve">13.1896772384644</t>
   </si>
   <si>
     <t xml:space="preserve">13.6705513000488</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">13.3442440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6362037658691</t>
+    <t xml:space="preserve">13.6362028121948</t>
   </si>
   <si>
     <t xml:space="preserve">13.6018552780151</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">13.5675067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4644632339478</t>
+    <t xml:space="preserve">13.4644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">13.3957662582397</t>
@@ -3137,37 +3137,37 @@
     <t xml:space="preserve">14.0827283859253</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6877241134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7048997879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.722071647644</t>
+    <t xml:space="preserve">13.6877250671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7048988342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7220726013184</t>
   </si>
   <si>
     <t xml:space="preserve">13.8766393661499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6151247024536</t>
+    <t xml:space="preserve">14.6151237487793</t>
   </si>
   <si>
     <t xml:space="preserve">14.7353429794312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.649471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8040390014648</t>
+    <t xml:space="preserve">14.6494722366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8040380477905</t>
   </si>
   <si>
     <t xml:space="preserve">14.6838207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.786865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7181692123413</t>
+    <t xml:space="preserve">14.7868633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7181673049927</t>
   </si>
   <si>
     <t xml:space="preserve">15.0101270675659</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">15.0616512298584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.387957572937</t>
+    <t xml:space="preserve">15.3879566192627</t>
   </si>
   <si>
     <t xml:space="preserve">15.1990432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2505655288696</t>
+    <t xml:space="preserve">15.2505645751953</t>
   </si>
   <si>
     <t xml:space="preserve">15.1818695068359</t>
@@ -3191,31 +3191,31 @@
     <t xml:space="preserve">15.2162160873413</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9757785797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9242572784424</t>
+    <t xml:space="preserve">14.9757804870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9242563247681</t>
   </si>
   <si>
     <t xml:space="preserve">14.4262094497681</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3918619155884</t>
+    <t xml:space="preserve">14.3918609619141</t>
   </si>
   <si>
     <t xml:space="preserve">14.9586057662964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5464296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1131734848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1303472518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9929533004761</t>
+    <t xml:space="preserve">14.5464286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1131715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1303462982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9929523468018</t>
   </si>
   <si>
     <t xml:space="preserve">15.2677392959595</t>
@@ -3224,49 +3224,49 @@
     <t xml:space="preserve">15.4223031997681</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9031791687012</t>
+    <t xml:space="preserve">15.9031782150269</t>
   </si>
   <si>
     <t xml:space="preserve">15.9375257492065</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1436157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.851655960083</t>
+    <t xml:space="preserve">16.1436138153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8516550064087</t>
   </si>
   <si>
     <t xml:space="preserve">15.9546995162964</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7829608917236</t>
+    <t xml:space="preserve">15.7829599380493</t>
   </si>
   <si>
     <t xml:space="preserve">15.7142639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5253505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5596971511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8383874893188</t>
+    <t xml:space="preserve">15.5253496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5596981048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8383884429932</t>
   </si>
   <si>
     <t xml:space="preserve">14.4605579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3059911727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2888164520264</t>
+    <t xml:space="preserve">14.3059902191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2888154983521</t>
   </si>
   <si>
     <t xml:space="preserve">14.5120792388916</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6322984695435</t>
+    <t xml:space="preserve">14.6322994232178</t>
   </si>
   <si>
     <t xml:space="preserve">14.7009944915771</t>
@@ -3275,16 +3275,16 @@
     <t xml:space="preserve">14.5807752609253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5292549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3746871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1431255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2678136825562</t>
+    <t xml:space="preserve">14.5292539596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3746862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1431245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2678127288818</t>
   </si>
   <si>
     <t xml:space="preserve">14.321249961853</t>
@@ -3296,10 +3296,10 @@
     <t xml:space="preserve">14.6774997711182</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6062498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0540618896484</t>
+    <t xml:space="preserve">14.6062488555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0540628433228</t>
   </si>
   <si>
     <t xml:space="preserve">14.0362501144409</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">14.0184373855591</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0006256103516</t>
+    <t xml:space="preserve">14.0006246566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.733437538147</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">13.875937461853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2856254577637</t>
+    <t xml:space="preserve">14.285626411438</t>
   </si>
   <si>
     <t xml:space="preserve">14.0896873474121</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">14.1609373092651</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1253118515015</t>
+    <t xml:space="preserve">14.1253128051758</t>
   </si>
   <si>
     <t xml:space="preserve">14.4459371566772</t>
@@ -3341,13 +3341,13 @@
     <t xml:space="preserve">14.178750038147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9828119277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9293756484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6978130340576</t>
+    <t xml:space="preserve">13.9828128814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9293746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6978120803833</t>
   </si>
   <si>
     <t xml:space="preserve">13.6799993515015</t>
@@ -3362,16 +3362,16 @@
     <t xml:space="preserve">13.5731248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8403129577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8581247329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9115629196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4840621948242</t>
+    <t xml:space="preserve">13.8403120040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8581256866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9115619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4840631484985</t>
   </si>
   <si>
     <t xml:space="preserve">13.1278123855591</t>
@@ -3386,13 +3386,13 @@
     <t xml:space="preserve">13.8046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7690629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8225002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3034372329712</t>
+    <t xml:space="preserve">13.7690620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8225011825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3034362792969</t>
   </si>
   <si>
     <t xml:space="preserve">14.3924999237061</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">14.624062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4993753433228</t>
+    <t xml:space="preserve">14.4993762969971</t>
   </si>
   <si>
     <t xml:space="preserve">14.5349998474121</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">14.25</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0718755722046</t>
+    <t xml:space="preserve">14.0718746185303</t>
   </si>
   <si>
     <t xml:space="preserve">13.359375</t>
@@ -3425,22 +3425,22 @@
     <t xml:space="preserve">13.5018749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5196876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2321863174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6265630722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812496185303</t>
+    <t xml:space="preserve">13.5196886062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2321872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6265621185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812505722046</t>
   </si>
   <si>
     <t xml:space="preserve">13.0565624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1099996566772</t>
+    <t xml:space="preserve">13.1100006103516</t>
   </si>
   <si>
     <t xml:space="preserve">12.842812538147</t>
@@ -3449,10 +3449,10 @@
     <t xml:space="preserve">12.8249998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7181253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221881866455</t>
+    <t xml:space="preserve">12.7181243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221872329712</t>
   </si>
   <si>
     <t xml:space="preserve">12.397500038147</t>
@@ -3473,25 +3473,25 @@
     <t xml:space="preserve">12.4865627288818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2906255722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2193756103516</t>
+    <t xml:space="preserve">12.2906246185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2193746566772</t>
   </si>
   <si>
     <t xml:space="preserve">12.2550001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1481256484985</t>
+    <t xml:space="preserve">12.1481246948242</t>
   </si>
   <si>
     <t xml:space="preserve">12.1659374237061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1303119659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165630340576</t>
+    <t xml:space="preserve">12.1303129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165620803833</t>
   </si>
   <si>
     <t xml:space="preserve">11.578125</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">11.3287506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2931261062622</t>
+    <t xml:space="preserve">11.2931251525879</t>
   </si>
   <si>
     <t xml:space="preserve">11.1328125</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">10.9012498855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9190635681152</t>
+    <t xml:space="preserve">10.9190626144409</t>
   </si>
   <si>
     <t xml:space="preserve">11.061562538147</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">11.0971879959106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1684379577637</t>
+    <t xml:space="preserve">11.1684370040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.204062461853</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">11.4534368515015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8631238937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0768756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453130722046</t>
+    <t xml:space="preserve">11.8631248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0768747329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453121185303</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809375762939</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">11.9878120422363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2015619277954</t>
+    <t xml:space="preserve">12.2015628814697</t>
   </si>
   <si>
     <t xml:space="preserve">12.6468753814697</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">12.7003126144409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3618745803833</t>
+    <t xml:space="preserve">12.3618755340576</t>
   </si>
   <si>
     <t xml:space="preserve">12.3440628051758</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">12.094687461853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0590620040894</t>
+    <t xml:space="preserve">12.0590629577637</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056247711182</t>
@@ -3638,19 +3638,19 @@
     <t xml:space="preserve">11.4178123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4356250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7384376525879</t>
+    <t xml:space="preserve">11.4356260299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7384386062622</t>
   </si>
   <si>
     <t xml:space="preserve">11.7562494277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5959386825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8274993896484</t>
+    <t xml:space="preserve">11.5959377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8275003433228</t>
   </si>
   <si>
     <t xml:space="preserve">11.7206249237061</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">11.2396869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5425004959106</t>
+    <t xml:space="preserve">11.5424995422363</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028131484985</t>
@@ -3680,13 +3680,13 @@
     <t xml:space="preserve">11.9700002670288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5246877670288</t>
+    <t xml:space="preserve">11.5246868133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.9724998474121</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1149988174438</t>
+    <t xml:space="preserve">11.1149997711182</t>
   </si>
   <si>
     <t xml:space="preserve">11.3382139205933</t>
@@ -70875,6 +70875,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2542">
+      <c r="A2542" s="1" t="n">
+        <v>46024.6912037037</v>
+      </c>
+      <c r="B2542" t="n">
+        <v>50030</v>
+      </c>
+      <c r="C2542" t="n">
+        <v>7.80999994277954</v>
+      </c>
+      <c r="D2542" t="n">
+        <v>7.67000007629395</v>
+      </c>
+      <c r="E2542" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="F2542" t="n">
+        <v>7.80999994277954</v>
+      </c>
+      <c r="G2542" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H2542" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ZV.MI.xlsx
+++ b/data/ZV.MI.xlsx
@@ -44,235 +44,235 @@
     <t xml:space="preserve">ZV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02447938919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93978881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82799816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78057050704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70943212509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75685811042786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74330711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80089735984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68571805953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66539263725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5637640953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65184235572815</t>
+    <t xml:space="preserve">4.02447891235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93978810310364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82799768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78057146072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70943164825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75685858726501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74330806732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8008975982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040791511536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68571877479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66539311408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56376504898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65184211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.72636985778809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70265626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65861773490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6924934387207</t>
+    <t xml:space="preserve">3.70265650749207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6586172580719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69249367713928</t>
   </si>
   <si>
     <t xml:space="preserve">3.74669551849365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59764051437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59086561203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58408999443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49601268768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46213579177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51633810997009</t>
+    <t xml:space="preserve">3.5976402759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59086537361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58409023284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49601197242737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46213626861572</t>
+  <